--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -601,7 +601,7 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Periode Juli 2025</t>
+            <t xml:space="preserve">Periode Agustus 2025</t>
           </r>
         </is>
       </c>
@@ -979,22 +979,22 @@
       <c r="U9" s="10" t="inlineStr"/>
       <c r="V9" s="10" t="inlineStr"/>
       <c r="W9" s="11" t="n">
-        <v>5.0261287724E10</v>
+        <v>5.7092109652E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>6.830821928E9</v>
+        <v>3.331178713E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>5.7092109652E10</v>
+        <v>6.0423288365E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.6715865472622302</v>
+        <v>0.7107719062166219</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.7918690348E10</v>
+        <v>2.4587511635E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1042,23 +1042,23 @@
       <c r="U10" s="14" t="inlineStr"/>
       <c r="V10" s="14" t="inlineStr"/>
       <c r="W10" s="14" t="n">
-        <v>3.02705832E9</v>
+        <v>3.53156804E9</v>
       </c>
       <c r="X10" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>5.018E8</v>
       </c>
       <c r="Y10" s="14" t="inlineStr"/>
       <c r="Z10" s="14" t="n">
-        <v>3.53156804E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="AA10" s="14" t="inlineStr"/>
       <c r="AB10" s="14" t="inlineStr"/>
       <c r="AC10" s="15" t="n">
-        <v>0.699883637049697</v>
+        <v>0.7993300033928294</v>
       </c>
       <c r="AD10" s="15" t="inlineStr"/>
       <c r="AE10" s="14" t="n">
-        <v>1.51436796E9</v>
+        <v>1.01256796E9</v>
       </c>
       <c r="AF10" s="14" t="inlineStr"/>
       <c r="AG10" s="14" t="inlineStr"/>
@@ -1105,23 +1105,23 @@
       <c r="U11" s="14" t="inlineStr"/>
       <c r="V11" s="14" t="inlineStr"/>
       <c r="W11" s="14" t="n">
-        <v>3.02705832E9</v>
+        <v>3.53156804E9</v>
       </c>
       <c r="X11" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>5.018E8</v>
       </c>
       <c r="Y11" s="14" t="inlineStr"/>
       <c r="Z11" s="14" t="n">
-        <v>3.53156804E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="AA11" s="14" t="inlineStr"/>
       <c r="AB11" s="14" t="inlineStr"/>
       <c r="AC11" s="15" t="n">
-        <v>0.699883637049697</v>
+        <v>0.7993300033928294</v>
       </c>
       <c r="AD11" s="15" t="inlineStr"/>
       <c r="AE11" s="14" t="n">
-        <v>1.51436796E9</v>
+        <v>1.01256796E9</v>
       </c>
       <c r="AF11" s="14" t="inlineStr"/>
       <c r="AG11" s="14" t="inlineStr"/>
@@ -1717,23 +1717,23 @@
       <c r="U21" s="17" t="inlineStr"/>
       <c r="V21" s="17" t="inlineStr"/>
       <c r="W21" s="17" t="n">
-        <v>3.02705832E9</v>
+        <v>3.53156804E9</v>
       </c>
       <c r="X21" s="17" t="n">
-        <v>5.0450972E8</v>
+        <v>5.018E8</v>
       </c>
       <c r="Y21" s="17" t="inlineStr"/>
       <c r="Z21" s="17" t="n">
-        <v>3.53156804E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="AA21" s="17" t="inlineStr"/>
       <c r="AB21" s="17" t="inlineStr"/>
       <c r="AC21" s="18" t="n">
-        <v>0.699883637049697</v>
+        <v>0.7993300033928294</v>
       </c>
       <c r="AD21" s="18" t="inlineStr"/>
       <c r="AE21" s="17" t="n">
-        <v>1.51436796E9</v>
+        <v>1.01256796E9</v>
       </c>
       <c r="AF21" s="17" t="inlineStr"/>
       <c r="AG21" s="17" t="inlineStr"/>
@@ -1780,23 +1780,23 @@
       <c r="U22" s="21" t="inlineStr"/>
       <c r="V22" s="21" t="inlineStr"/>
       <c r="W22" s="22" t="n">
-        <v>3.02705832E9</v>
+        <v>3.53156804E9</v>
       </c>
       <c r="X22" s="22" t="n">
-        <v>5.0450972E8</v>
+        <v>5.018E8</v>
       </c>
       <c r="Y22" s="22" t="inlineStr"/>
       <c r="Z22" s="21" t="n">
-        <v>3.53156804E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="AA22" s="21" t="inlineStr"/>
       <c r="AB22" s="21" t="inlineStr"/>
       <c r="AC22" s="23" t="n">
-        <v>0.699883637049697</v>
+        <v>0.7993300033928294</v>
       </c>
       <c r="AD22" s="23" t="inlineStr"/>
       <c r="AE22" s="21" t="n">
-        <v>1.51436796E9</v>
+        <v>1.01256796E9</v>
       </c>
       <c r="AF22" s="21" t="inlineStr"/>
       <c r="AG22" s="21" t="inlineStr"/>
@@ -1843,23 +1843,23 @@
       <c r="U23" s="25" t="inlineStr"/>
       <c r="V23" s="25" t="inlineStr"/>
       <c r="W23" s="25" t="n">
-        <v>3.02705832E9</v>
+        <v>3.53156804E9</v>
       </c>
       <c r="X23" s="25" t="n">
-        <v>5.0450972E8</v>
+        <v>5.018E8</v>
       </c>
       <c r="Y23" s="25" t="inlineStr"/>
       <c r="Z23" s="25" t="n">
-        <v>3.53156804E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="AA23" s="25" t="inlineStr"/>
       <c r="AB23" s="25" t="inlineStr"/>
       <c r="AC23" s="26" t="n">
-        <v>0.699883637049697</v>
+        <v>0.7993300033928294</v>
       </c>
       <c r="AD23" s="26" t="inlineStr"/>
       <c r="AE23" s="25" t="n">
-        <v>1.51436796E9</v>
+        <v>1.01256796E9</v>
       </c>
       <c r="AF23" s="25" t="inlineStr"/>
       <c r="AG23" s="25" t="inlineStr"/>
@@ -1906,23 +1906,23 @@
       <c r="U24" s="14" t="inlineStr"/>
       <c r="V24" s="14" t="inlineStr"/>
       <c r="W24" s="14" t="n">
-        <v>3.02705832E9</v>
+        <v>3.53156804E9</v>
       </c>
       <c r="X24" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>5.018E8</v>
       </c>
       <c r="Y24" s="14" t="inlineStr"/>
       <c r="Z24" s="14" t="n">
-        <v>3.53156804E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="AA24" s="14" t="inlineStr"/>
       <c r="AB24" s="14" t="inlineStr"/>
       <c r="AC24" s="15" t="n">
-        <v>0.699883637049697</v>
+        <v>0.7993300033928294</v>
       </c>
       <c r="AD24" s="15" t="inlineStr"/>
       <c r="AE24" s="14" t="n">
-        <v>1.51436796E9</v>
+        <v>1.01256796E9</v>
       </c>
       <c r="AF24" s="14" t="inlineStr"/>
       <c r="AG24" s="14" t="inlineStr"/>
@@ -1969,23 +1969,23 @@
       <c r="U25" s="14" t="inlineStr"/>
       <c r="V25" s="14" t="inlineStr"/>
       <c r="W25" s="14" t="n">
-        <v>3.02705832E9</v>
+        <v>3.53156804E9</v>
       </c>
       <c r="X25" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>5.018E8</v>
       </c>
       <c r="Y25" s="14" t="inlineStr"/>
       <c r="Z25" s="14" t="n">
-        <v>3.53156804E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="AA25" s="14" t="inlineStr"/>
       <c r="AB25" s="14" t="inlineStr"/>
       <c r="AC25" s="15" t="n">
-        <v>0.699883637049697</v>
+        <v>0.7993300033928294</v>
       </c>
       <c r="AD25" s="15" t="inlineStr"/>
       <c r="AE25" s="14" t="n">
-        <v>1.51436796E9</v>
+        <v>1.01256796E9</v>
       </c>
       <c r="AF25" s="14" t="inlineStr"/>
       <c r="AG25" s="14" t="inlineStr"/>
@@ -2026,23 +2026,23 @@
       <c r="U26" s="14" t="inlineStr"/>
       <c r="V26" s="14" t="inlineStr"/>
       <c r="W26" s="14" t="n">
-        <v>2.592E8</v>
+        <v>3.024E8</v>
       </c>
       <c r="X26" s="14" t="n">
         <v>4.32E7</v>
       </c>
       <c r="Y26" s="14" t="inlineStr"/>
       <c r="Z26" s="14" t="n">
-        <v>3.024E8</v>
+        <v>3.456E8</v>
       </c>
       <c r="AA26" s="14" t="inlineStr"/>
       <c r="AB26" s="14" t="inlineStr"/>
       <c r="AC26" s="15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD26" s="15" t="inlineStr"/>
       <c r="AE26" s="14" t="n">
-        <v>1.296E8</v>
+        <v>8.64E7</v>
       </c>
       <c r="AF26" s="14" t="inlineStr"/>
       <c r="AG26" s="14" t="inlineStr"/>
@@ -2083,23 +2083,23 @@
       <c r="U27" s="14" t="inlineStr"/>
       <c r="V27" s="14" t="inlineStr"/>
       <c r="W27" s="14" t="n">
-        <v>2.6676E9</v>
+        <v>3.1122E9</v>
       </c>
       <c r="X27" s="14" t="n">
         <v>4.446E8</v>
       </c>
       <c r="Y27" s="14" t="inlineStr"/>
       <c r="Z27" s="14" t="n">
-        <v>3.1122E9</v>
+        <v>3.5568E9</v>
       </c>
       <c r="AA27" s="14" t="inlineStr"/>
       <c r="AB27" s="14" t="inlineStr"/>
       <c r="AC27" s="15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD27" s="15" t="inlineStr"/>
       <c r="AE27" s="14" t="n">
-        <v>1.3338E9</v>
+        <v>8.892E8</v>
       </c>
       <c r="AF27" s="14" t="inlineStr"/>
       <c r="AG27" s="14" t="inlineStr"/>
@@ -2140,23 +2140,23 @@
       <c r="U28" s="14" t="inlineStr"/>
       <c r="V28" s="14" t="inlineStr"/>
       <c r="W28" s="14" t="n">
-        <v>8.4E7</v>
+        <v>9.8E7</v>
       </c>
       <c r="X28" s="14" t="n">
         <v>1.4E7</v>
       </c>
       <c r="Y28" s="14" t="inlineStr"/>
       <c r="Z28" s="14" t="n">
-        <v>9.8E7</v>
+        <v>1.12E8</v>
       </c>
       <c r="AA28" s="14" t="inlineStr"/>
       <c r="AB28" s="14" t="inlineStr"/>
       <c r="AC28" s="15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD28" s="15" t="inlineStr"/>
       <c r="AE28" s="14" t="n">
-        <v>4.2E7</v>
+        <v>2.8E7</v>
       </c>
       <c r="AF28" s="14" t="inlineStr"/>
       <c r="AG28" s="14" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
       <c r="U29" s="14" t="inlineStr"/>
       <c r="V29" s="14" t="inlineStr"/>
       <c r="W29" s="14" t="n">
-        <v>1.625832E7</v>
+        <v>1.896804E7</v>
       </c>
       <c r="X29" s="14" t="n">
-        <v>2709720.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y29" s="14" t="inlineStr"/>
       <c r="Z29" s="14" t="n">
@@ -2443,23 +2443,23 @@
       <c r="U33" s="14" t="inlineStr"/>
       <c r="V33" s="14" t="inlineStr"/>
       <c r="W33" s="14" t="n">
-        <v>4.7234229404E10</v>
+        <v>5.3560541612E10</v>
       </c>
       <c r="X33" s="14" t="n">
-        <v>6.326312208E9</v>
+        <v>2.829378713E9</v>
       </c>
       <c r="Y33" s="14" t="inlineStr"/>
       <c r="Z33" s="14" t="n">
-        <v>5.3560541612E10</v>
+        <v>5.6389920325E10</v>
       </c>
       <c r="AA33" s="14" t="inlineStr"/>
       <c r="AB33" s="14" t="inlineStr"/>
       <c r="AC33" s="15" t="n">
-        <v>0.6698009467258019</v>
+        <v>0.7051837207526546</v>
       </c>
       <c r="AD33" s="15" t="inlineStr"/>
       <c r="AE33" s="14" t="n">
-        <v>2.6404322388E10</v>
+        <v>2.3574943675E10</v>
       </c>
       <c r="AF33" s="14" t="inlineStr"/>
       <c r="AG33" s="14" t="inlineStr"/>
@@ -2550,23 +2550,23 @@
       <c r="U35" s="14" t="inlineStr"/>
       <c r="V35" s="14" t="inlineStr"/>
       <c r="W35" s="14" t="n">
-        <v>4.7234229404E10</v>
+        <v>5.3560541612E10</v>
       </c>
       <c r="X35" s="14" t="n">
-        <v>6.326312208E9</v>
+        <v>2.829378713E9</v>
       </c>
       <c r="Y35" s="14" t="inlineStr"/>
       <c r="Z35" s="14" t="n">
-        <v>5.3560541612E10</v>
+        <v>5.6389920325E10</v>
       </c>
       <c r="AA35" s="14" t="inlineStr"/>
       <c r="AB35" s="14" t="inlineStr"/>
       <c r="AC35" s="15" t="n">
-        <v>0.6698009467258019</v>
+        <v>0.7051837207526546</v>
       </c>
       <c r="AD35" s="15" t="inlineStr"/>
       <c r="AE35" s="14" t="n">
-        <v>2.6404322388E10</v>
+        <v>2.3574943675E10</v>
       </c>
       <c r="AF35" s="14" t="inlineStr"/>
       <c r="AG35" s="14" t="inlineStr"/>
@@ -2613,23 +2613,23 @@
       <c r="U36" s="17" t="inlineStr"/>
       <c r="V36" s="17" t="inlineStr"/>
       <c r="W36" s="17" t="n">
-        <v>4.7233629404E10</v>
+        <v>5.3559941612E10</v>
       </c>
       <c r="X36" s="17" t="n">
-        <v>6.326312208E9</v>
+        <v>2.829378713E9</v>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
       <c r="Z36" s="17" t="n">
-        <v>5.3559941612E10</v>
+        <v>5.6389320325E10</v>
       </c>
       <c r="AA36" s="17" t="inlineStr"/>
       <c r="AB36" s="17" t="inlineStr"/>
       <c r="AC36" s="18" t="n">
-        <v>0.6697984691261587</v>
+        <v>0.7051815086424106</v>
       </c>
       <c r="AD36" s="18" t="inlineStr"/>
       <c r="AE36" s="17" t="n">
-        <v>2.6404322388E10</v>
+        <v>2.3574943675E10</v>
       </c>
       <c r="AF36" s="17" t="inlineStr"/>
       <c r="AG36" s="17" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
       <c r="U56" s="21" t="inlineStr"/>
       <c r="V56" s="21" t="inlineStr"/>
       <c r="W56" s="22" t="n">
-        <v>3949100.0</v>
+        <v>9686100.0</v>
       </c>
       <c r="X56" s="22" t="n">
-        <v>5737000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y56" s="22" t="inlineStr"/>
       <c r="Z56" s="21" t="n">
@@ -3900,10 +3900,10 @@
       <c r="U57" s="25" t="inlineStr"/>
       <c r="V57" s="25" t="inlineStr"/>
       <c r="W57" s="25" t="n">
-        <v>3949100.0</v>
+        <v>9686100.0</v>
       </c>
       <c r="X57" s="25" t="n">
-        <v>5737000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y57" s="25" t="inlineStr"/>
       <c r="Z57" s="25" t="n">
@@ -3963,10 +3963,10 @@
       <c r="U58" s="14" t="inlineStr"/>
       <c r="V58" s="14" t="inlineStr"/>
       <c r="W58" s="14" t="n">
-        <v>600000.0</v>
+        <v>2400000.0</v>
       </c>
       <c r="X58" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
@@ -4026,10 +4026,10 @@
       <c r="U59" s="14" t="inlineStr"/>
       <c r="V59" s="14" t="inlineStr"/>
       <c r="W59" s="14" t="n">
-        <v>0.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="X59" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y59" s="14" t="inlineStr"/>
       <c r="Z59" s="14" t="n">
@@ -4127,10 +4127,10 @@
       <c r="U61" s="14" t="inlineStr"/>
       <c r="V61" s="14" t="inlineStr"/>
       <c r="W61" s="14" t="n">
-        <v>0.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="X61" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y61" s="14" t="inlineStr"/>
       <c r="Z61" s="14" t="n">
@@ -4310,10 +4310,10 @@
       <c r="U64" s="14" t="inlineStr"/>
       <c r="V64" s="14" t="inlineStr"/>
       <c r="W64" s="14" t="n">
-        <v>3349100.0</v>
+        <v>7286100.0</v>
       </c>
       <c r="X64" s="14" t="n">
-        <v>3937000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y64" s="14" t="inlineStr"/>
       <c r="Z64" s="14" t="n">
@@ -4373,10 +4373,10 @@
       <c r="U65" s="14" t="inlineStr"/>
       <c r="V65" s="14" t="inlineStr"/>
       <c r="W65" s="14" t="n">
-        <v>3349100.0</v>
+        <v>7286100.0</v>
       </c>
       <c r="X65" s="14" t="n">
-        <v>3937000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y65" s="14" t="inlineStr"/>
       <c r="Z65" s="14" t="n">
@@ -4430,10 +4430,10 @@
       <c r="U66" s="14" t="inlineStr"/>
       <c r="V66" s="14" t="inlineStr"/>
       <c r="W66" s="14" t="n">
-        <v>2600000.0</v>
+        <v>6537000.0</v>
       </c>
       <c r="X66" s="14" t="n">
-        <v>3937000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
@@ -4733,23 +4733,23 @@
       <c r="U71" s="21" t="inlineStr"/>
       <c r="V71" s="21" t="inlineStr"/>
       <c r="W71" s="22" t="n">
-        <v>4.7228630304E10</v>
+        <v>5.3549205512E10</v>
       </c>
       <c r="X71" s="22" t="n">
-        <v>6.320575208E9</v>
+        <v>2.829378713E9</v>
       </c>
       <c r="Y71" s="22" t="inlineStr"/>
       <c r="Z71" s="21" t="n">
-        <v>5.3549205512E10</v>
+        <v>5.6378584225E10</v>
       </c>
       <c r="AA71" s="21" t="inlineStr"/>
       <c r="AB71" s="21" t="inlineStr"/>
       <c r="AC71" s="23" t="n">
-        <v>0.6698194241608939</v>
+        <v>0.7052106648367253</v>
       </c>
       <c r="AD71" s="23" t="inlineStr"/>
       <c r="AE71" s="21" t="n">
-        <v>2.6396528488E10</v>
+        <v>2.3567149775E10</v>
       </c>
       <c r="AF71" s="21" t="inlineStr"/>
       <c r="AG71" s="21" t="inlineStr"/>
@@ -4796,23 +4796,23 @@
       <c r="U72" s="25" t="inlineStr"/>
       <c r="V72" s="25" t="inlineStr"/>
       <c r="W72" s="25" t="n">
-        <v>4.4677440659E10</v>
+        <v>5.0573817532E10</v>
       </c>
       <c r="X72" s="25" t="n">
-        <v>5.896376873E9</v>
+        <v>2.755968713E9</v>
       </c>
       <c r="Y72" s="25" t="inlineStr"/>
       <c r="Z72" s="25" t="n">
-        <v>5.0573817532E10</v>
+        <v>5.3329786245E10</v>
       </c>
       <c r="AA72" s="25" t="inlineStr"/>
       <c r="AB72" s="25" t="inlineStr"/>
       <c r="AC72" s="26" t="n">
-        <v>0.6807624358417722</v>
+        <v>0.7178598919113772</v>
       </c>
       <c r="AD72" s="26" t="inlineStr"/>
       <c r="AE72" s="25" t="n">
-        <v>2.3716147468E10</v>
+        <v>2.0960178755E10</v>
       </c>
       <c r="AF72" s="25" t="inlineStr"/>
       <c r="AG72" s="25" t="inlineStr"/>
@@ -4859,23 +4859,23 @@
       <c r="U73" s="14" t="inlineStr"/>
       <c r="V73" s="14" t="inlineStr"/>
       <c r="W73" s="14" t="n">
-        <v>3.39277532E9</v>
+        <v>3.798075364E9</v>
       </c>
       <c r="X73" s="14" t="n">
-        <v>4.05300044E8</v>
+        <v>3.8947414E8</v>
       </c>
       <c r="Y73" s="14" t="inlineStr"/>
       <c r="Z73" s="14" t="n">
-        <v>3.798075364E9</v>
+        <v>4.187549504E9</v>
       </c>
       <c r="AA73" s="14" t="inlineStr"/>
       <c r="AB73" s="14" t="inlineStr"/>
       <c r="AC73" s="15" t="n">
-        <v>0.592813113053055</v>
+        <v>0.6536032120530656</v>
       </c>
       <c r="AD73" s="15" t="inlineStr"/>
       <c r="AE73" s="14" t="n">
-        <v>2.608792636E9</v>
+        <v>2.219318496E9</v>
       </c>
       <c r="AF73" s="14" t="inlineStr"/>
       <c r="AG73" s="14" t="inlineStr"/>
@@ -4922,23 +4922,23 @@
       <c r="U74" s="14" t="inlineStr"/>
       <c r="V74" s="14" t="inlineStr"/>
       <c r="W74" s="14" t="n">
-        <v>1.3295234E9</v>
+        <v>1.4858101E9</v>
       </c>
       <c r="X74" s="14" t="n">
-        <v>1.562867E8</v>
+        <v>1.64507E8</v>
       </c>
       <c r="Y74" s="14" t="inlineStr"/>
       <c r="Z74" s="14" t="n">
-        <v>1.4858101E9</v>
+        <v>1.6503171E9</v>
       </c>
       <c r="AA74" s="14" t="inlineStr"/>
       <c r="AB74" s="14" t="inlineStr"/>
       <c r="AC74" s="15" t="n">
-        <v>0.5301905004553227</v>
+        <v>0.5888925167213339</v>
       </c>
       <c r="AD74" s="15" t="inlineStr"/>
       <c r="AE74" s="14" t="n">
-        <v>1.3165979E9</v>
+        <v>1.1520909E9</v>
       </c>
       <c r="AF74" s="14" t="inlineStr"/>
       <c r="AG74" s="14" t="inlineStr"/>
@@ -4979,23 +4979,23 @@
       <c r="U75" s="14" t="inlineStr"/>
       <c r="V75" s="14" t="inlineStr"/>
       <c r="W75" s="14" t="n">
-        <v>9.99343E8</v>
+        <v>1.1556297E9</v>
       </c>
       <c r="X75" s="14" t="n">
-        <v>1.562867E8</v>
+        <v>1.64507E8</v>
       </c>
       <c r="Y75" s="14" t="inlineStr"/>
       <c r="Z75" s="14" t="n">
-        <v>1.1556297E9</v>
+        <v>1.3201367E9</v>
       </c>
       <c r="AA75" s="14" t="inlineStr"/>
       <c r="AB75" s="14" t="inlineStr"/>
       <c r="AC75" s="15" t="n">
-        <v>0.4699974377745242</v>
+        <v>0.5369028387831463</v>
       </c>
       <c r="AD75" s="15" t="inlineStr"/>
       <c r="AE75" s="14" t="n">
-        <v>1.3031703E9</v>
+        <v>1.1386633E9</v>
       </c>
       <c r="AF75" s="14" t="inlineStr"/>
       <c r="AG75" s="14" t="inlineStr"/>
@@ -5156,23 +5156,23 @@
       <c r="U78" s="14" t="inlineStr"/>
       <c r="V78" s="14" t="inlineStr"/>
       <c r="W78" s="14" t="n">
-        <v>16177.0</v>
+        <v>17822.0</v>
       </c>
       <c r="X78" s="14" t="n">
-        <v>1645.0</v>
+        <v>1727.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
-        <v>17822.0</v>
+        <v>19549.0</v>
       </c>
       <c r="AA78" s="14" t="inlineStr"/>
       <c r="AB78" s="14" t="inlineStr"/>
       <c r="AC78" s="15" t="n">
-        <v>0.5940666666666666</v>
+        <v>0.6516333333333333</v>
       </c>
       <c r="AD78" s="15" t="inlineStr"/>
       <c r="AE78" s="14" t="n">
-        <v>12178.0</v>
+        <v>10451.0</v>
       </c>
       <c r="AF78" s="14" t="inlineStr"/>
       <c r="AG78" s="14" t="inlineStr"/>
@@ -5213,23 +5213,23 @@
       <c r="U79" s="14" t="inlineStr"/>
       <c r="V79" s="14" t="inlineStr"/>
       <c r="W79" s="14" t="n">
-        <v>11595.0</v>
+        <v>13240.0</v>
       </c>
       <c r="X79" s="14" t="n">
-        <v>1645.0</v>
+        <v>1727.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
-        <v>13240.0</v>
+        <v>14967.0</v>
       </c>
       <c r="AA79" s="14" t="inlineStr"/>
       <c r="AB79" s="14" t="inlineStr"/>
       <c r="AC79" s="15" t="n">
-        <v>0.5516666666666666</v>
+        <v>0.623625</v>
       </c>
       <c r="AD79" s="15" t="inlineStr"/>
       <c r="AE79" s="14" t="n">
-        <v>10760.0</v>
+        <v>9033.0</v>
       </c>
       <c r="AF79" s="14" t="inlineStr"/>
       <c r="AG79" s="14" t="inlineStr"/>
@@ -5390,23 +5390,23 @@
       <c r="U82" s="14" t="inlineStr"/>
       <c r="V82" s="14" t="inlineStr"/>
       <c r="W82" s="14" t="n">
-        <v>1.0164363E8</v>
+        <v>1.1333796E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>1.169433E7</v>
+        <v>1.251636E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>1.1333796E8</v>
+        <v>1.2585432E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.622736043956044</v>
+        <v>0.6915072527472528</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>6.866204E7</v>
+        <v>5.614568E7</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5447,23 +5447,23 @@
       <c r="U83" s="14" t="inlineStr"/>
       <c r="V83" s="14" t="inlineStr"/>
       <c r="W83" s="14" t="n">
-        <v>7.644531E7</v>
+        <v>8.813964E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1.169433E7</v>
+        <v>1.251636E7</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>8.813964E7</v>
+        <v>1.00656E8</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.5649976923076923</v>
+        <v>0.6452307692307693</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>6.786036E7</v>
+        <v>5.5344E7</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5624,23 +5624,23 @@
       <c r="U86" s="14" t="inlineStr"/>
       <c r="V86" s="14" t="inlineStr"/>
       <c r="W86" s="14" t="n">
-        <v>3.0975352E7</v>
+        <v>3.4441812E7</v>
       </c>
       <c r="X86" s="14" t="n">
-        <v>3466460.0</v>
+        <v>3795272.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
-        <v>3.4441812E7</v>
+        <v>3.8237084E7</v>
       </c>
       <c r="AA86" s="14" t="inlineStr"/>
       <c r="AB86" s="14" t="inlineStr"/>
       <c r="AC86" s="15" t="n">
-        <v>0.6150323571428571</v>
+        <v>0.6828050714285714</v>
       </c>
       <c r="AD86" s="15" t="inlineStr"/>
       <c r="AE86" s="14" t="n">
-        <v>2.1558188E7</v>
+        <v>1.7762916E7</v>
       </c>
       <c r="AF86" s="14" t="inlineStr"/>
       <c r="AG86" s="14" t="inlineStr"/>
@@ -5725,23 +5725,23 @@
       <c r="U88" s="14" t="inlineStr"/>
       <c r="V88" s="14" t="inlineStr"/>
       <c r="W88" s="14" t="n">
-        <v>2.3299294E7</v>
+        <v>2.6765754E7</v>
       </c>
       <c r="X88" s="14" t="n">
-        <v>3466460.0</v>
+        <v>3795272.0</v>
       </c>
       <c r="Y88" s="14" t="inlineStr"/>
       <c r="Z88" s="14" t="n">
-        <v>2.6765754E7</v>
+        <v>3.0561026E7</v>
       </c>
       <c r="AA88" s="14" t="inlineStr"/>
       <c r="AB88" s="14" t="inlineStr"/>
       <c r="AC88" s="15" t="n">
-        <v>0.557619875</v>
+        <v>0.6366880416666667</v>
       </c>
       <c r="AD88" s="15" t="inlineStr"/>
       <c r="AE88" s="14" t="n">
-        <v>2.1234246E7</v>
+        <v>1.7438974E7</v>
       </c>
       <c r="AF88" s="14" t="inlineStr"/>
       <c r="AG88" s="14" t="inlineStr"/>
@@ -5902,23 +5902,23 @@
       <c r="U91" s="14" t="inlineStr"/>
       <c r="V91" s="14" t="inlineStr"/>
       <c r="W91" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.62E7</v>
       </c>
       <c r="X91" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y91" s="14" t="inlineStr"/>
       <c r="Z91" s="14" t="n">
-        <v>1.62E7</v>
+        <v>1.8E7</v>
       </c>
       <c r="AA91" s="14" t="inlineStr"/>
       <c r="AB91" s="14" t="inlineStr"/>
       <c r="AC91" s="15" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AD91" s="15" t="inlineStr"/>
       <c r="AE91" s="14" t="n">
-        <v>9000000.0</v>
+        <v>7200000.0</v>
       </c>
       <c r="AF91" s="14" t="inlineStr"/>
       <c r="AG91" s="14" t="inlineStr"/>
@@ -5959,23 +5959,23 @@
       <c r="U92" s="14" t="inlineStr"/>
       <c r="V92" s="14" t="inlineStr"/>
       <c r="W92" s="14" t="n">
-        <v>1.08E7</v>
+        <v>1.26E7</v>
       </c>
       <c r="X92" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y92" s="14" t="inlineStr"/>
       <c r="Z92" s="14" t="n">
-        <v>1.26E7</v>
+        <v>1.44E7</v>
       </c>
       <c r="AA92" s="14" t="inlineStr"/>
       <c r="AB92" s="14" t="inlineStr"/>
       <c r="AC92" s="15" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AD92" s="15" t="inlineStr"/>
       <c r="AE92" s="14" t="n">
-        <v>9000000.0</v>
+        <v>7200000.0</v>
       </c>
       <c r="AF92" s="14" t="inlineStr"/>
       <c r="AG92" s="14" t="inlineStr"/>
@@ -6136,23 +6136,23 @@
       <c r="U95" s="14" t="inlineStr"/>
       <c r="V95" s="14" t="inlineStr"/>
       <c r="W95" s="14" t="n">
-        <v>9.6112E7</v>
+        <v>1.06486E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>1.0374E7</v>
+        <v>1.1474E7</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>1.06486E8</v>
+        <v>1.1796E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.7343153074875529</v>
+        <v>0.8134387024701063</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>3.8528E7</v>
+        <v>2.7054E7</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6193,23 +6193,23 @@
       <c r="U96" s="14" t="inlineStr"/>
       <c r="V96" s="14" t="inlineStr"/>
       <c r="W96" s="14" t="n">
-        <v>7.2084E7</v>
+        <v>8.2458E7</v>
       </c>
       <c r="X96" s="14" t="n">
-        <v>1.0374E7</v>
+        <v>1.1474E7</v>
       </c>
       <c r="Y96" s="14" t="inlineStr"/>
       <c r="Z96" s="14" t="n">
-        <v>8.2458E7</v>
+        <v>9.3932E7</v>
       </c>
       <c r="AA96" s="14" t="inlineStr"/>
       <c r="AB96" s="14" t="inlineStr"/>
       <c r="AC96" s="15" t="n">
-        <v>0.68715</v>
+        <v>0.7827666666666667</v>
       </c>
       <c r="AD96" s="15" t="inlineStr"/>
       <c r="AE96" s="14" t="n">
-        <v>3.7542E7</v>
+        <v>2.6068E7</v>
       </c>
       <c r="AF96" s="14" t="inlineStr"/>
       <c r="AG96" s="14" t="inlineStr"/>
@@ -6370,23 +6370,23 @@
       <c r="U99" s="14" t="inlineStr"/>
       <c r="V99" s="14" t="inlineStr"/>
       <c r="W99" s="14" t="n">
-        <v>1.8974272E7</v>
+        <v>1.9186331E7</v>
       </c>
       <c r="X99" s="14" t="n">
-        <v>212059.0</v>
+        <v>198083.0</v>
       </c>
       <c r="Y99" s="14" t="inlineStr"/>
       <c r="Z99" s="14" t="n">
-        <v>1.9186331E7</v>
+        <v>1.9384414E7</v>
       </c>
       <c r="AA99" s="14" t="inlineStr"/>
       <c r="AB99" s="14" t="inlineStr"/>
       <c r="AC99" s="15" t="n">
-        <v>0.9690066161616162</v>
+        <v>0.9790108080808081</v>
       </c>
       <c r="AD99" s="15" t="inlineStr"/>
       <c r="AE99" s="14" t="n">
-        <v>613669.0</v>
+        <v>415586.0</v>
       </c>
       <c r="AF99" s="14" t="inlineStr"/>
       <c r="AG99" s="14" t="inlineStr"/>
@@ -6427,23 +6427,23 @@
       <c r="U100" s="14" t="inlineStr"/>
       <c r="V100" s="14" t="inlineStr"/>
       <c r="W100" s="14" t="n">
-        <v>1443256.0</v>
+        <v>1655315.0</v>
       </c>
       <c r="X100" s="14" t="n">
-        <v>212059.0</v>
+        <v>198083.0</v>
       </c>
       <c r="Y100" s="14" t="inlineStr"/>
       <c r="Z100" s="14" t="n">
-        <v>1655315.0</v>
+        <v>1853398.0</v>
       </c>
       <c r="AA100" s="14" t="inlineStr"/>
       <c r="AB100" s="14" t="inlineStr"/>
       <c r="AC100" s="15" t="n">
-        <v>0.6897145833333334</v>
+        <v>0.7722491666666667</v>
       </c>
       <c r="AD100" s="15" t="inlineStr"/>
       <c r="AE100" s="14" t="n">
-        <v>744685.0</v>
+        <v>546602.0</v>
       </c>
       <c r="AF100" s="14" t="inlineStr"/>
       <c r="AG100" s="14" t="inlineStr"/>
@@ -6604,23 +6604,23 @@
       <c r="U103" s="14" t="inlineStr"/>
       <c r="V103" s="14" t="inlineStr"/>
       <c r="W103" s="14" t="n">
-        <v>7.06095E7</v>
+        <v>7.864812E7</v>
       </c>
       <c r="X103" s="14" t="n">
-        <v>8038620.0</v>
+        <v>8617980.0</v>
       </c>
       <c r="Y103" s="14" t="inlineStr"/>
       <c r="Z103" s="14" t="n">
-        <v>7.864812E7</v>
+        <v>8.72661E7</v>
       </c>
       <c r="AA103" s="14" t="inlineStr"/>
       <c r="AB103" s="14" t="inlineStr"/>
       <c r="AC103" s="15" t="n">
-        <v>0.6241914285714286</v>
+        <v>0.6925880952380953</v>
       </c>
       <c r="AD103" s="15" t="inlineStr"/>
       <c r="AE103" s="14" t="n">
-        <v>4.735188E7</v>
+        <v>3.87339E7</v>
       </c>
       <c r="AF103" s="14" t="inlineStr"/>
       <c r="AG103" s="14" t="inlineStr"/>
@@ -6661,23 +6661,23 @@
       <c r="U104" s="14" t="inlineStr"/>
       <c r="V104" s="14" t="inlineStr"/>
       <c r="W104" s="14" t="n">
-        <v>5.308386E7</v>
+        <v>6.112248E7</v>
       </c>
       <c r="X104" s="14" t="n">
-        <v>8038620.0</v>
+        <v>8617980.0</v>
       </c>
       <c r="Y104" s="14" t="inlineStr"/>
       <c r="Z104" s="14" t="n">
-        <v>6.112248E7</v>
+        <v>6.974046E7</v>
       </c>
       <c r="AA104" s="14" t="inlineStr"/>
       <c r="AB104" s="14" t="inlineStr"/>
       <c r="AC104" s="15" t="n">
-        <v>0.5659488888888888</v>
+        <v>0.645745</v>
       </c>
       <c r="AD104" s="15" t="inlineStr"/>
       <c r="AE104" s="14" t="n">
-        <v>4.687752E7</v>
+        <v>3.825954E7</v>
       </c>
       <c r="AF104" s="14" t="inlineStr"/>
       <c r="AG104" s="14" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
       <c r="U107" s="14" t="inlineStr"/>
       <c r="V107" s="14" t="inlineStr"/>
       <c r="W107" s="14" t="n">
-        <v>1.28383E8</v>
+        <v>1.54008E8</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>2.5625E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
@@ -6895,10 +6895,10 @@
       <c r="U108" s="14" t="inlineStr"/>
       <c r="V108" s="14" t="inlineStr"/>
       <c r="W108" s="14" t="n">
-        <v>8260000.0</v>
+        <v>9450000.0</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>1190000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
@@ -6952,10 +6952,10 @@
       <c r="U109" s="14" t="inlineStr"/>
       <c r="V109" s="14" t="inlineStr"/>
       <c r="W109" s="14" t="n">
-        <v>1.05117E8</v>
+        <v>1.25985E8</v>
       </c>
       <c r="X109" s="14" t="n">
-        <v>2.0868E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y109" s="14" t="inlineStr"/>
       <c r="Z109" s="14" t="n">
@@ -7009,10 +7009,10 @@
       <c r="U110" s="14" t="inlineStr"/>
       <c r="V110" s="14" t="inlineStr"/>
       <c r="W110" s="14" t="n">
-        <v>1.5006E7</v>
+        <v>1.8573E7</v>
       </c>
       <c r="X110" s="14" t="n">
-        <v>3567000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y110" s="14" t="inlineStr"/>
       <c r="Z110" s="14" t="n">
@@ -7072,23 +7072,23 @@
       <c r="U111" s="14" t="inlineStr"/>
       <c r="V111" s="14" t="inlineStr"/>
       <c r="W111" s="14" t="n">
-        <v>3.23E7</v>
+        <v>3.637E7</v>
       </c>
       <c r="X111" s="14" t="n">
         <v>4070000.0</v>
       </c>
       <c r="Y111" s="14" t="inlineStr"/>
       <c r="Z111" s="14" t="n">
-        <v>3.637E7</v>
+        <v>4.044E7</v>
       </c>
       <c r="AA111" s="14" t="inlineStr"/>
       <c r="AB111" s="14" t="inlineStr"/>
       <c r="AC111" s="15" t="n">
-        <v>0.5773015873015873</v>
+        <v>0.6419047619047619</v>
       </c>
       <c r="AD111" s="15" t="inlineStr"/>
       <c r="AE111" s="14" t="n">
-        <v>2.663E7</v>
+        <v>2.256E7</v>
       </c>
       <c r="AF111" s="14" t="inlineStr"/>
       <c r="AG111" s="14" t="inlineStr"/>
@@ -7129,23 +7129,23 @@
       <c r="U112" s="14" t="inlineStr"/>
       <c r="V112" s="14" t="inlineStr"/>
       <c r="W112" s="14" t="n">
-        <v>2.437E7</v>
+        <v>2.844E7</v>
       </c>
       <c r="X112" s="14" t="n">
         <v>4070000.0</v>
       </c>
       <c r="Y112" s="14" t="inlineStr"/>
       <c r="Z112" s="14" t="n">
-        <v>2.844E7</v>
+        <v>3.251E7</v>
       </c>
       <c r="AA112" s="14" t="inlineStr"/>
       <c r="AB112" s="14" t="inlineStr"/>
       <c r="AC112" s="15" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.602037037037037</v>
       </c>
       <c r="AD112" s="15" t="inlineStr"/>
       <c r="AE112" s="14" t="n">
-        <v>2.556E7</v>
+        <v>2.149E7</v>
       </c>
       <c r="AF112" s="14" t="inlineStr"/>
       <c r="AG112" s="14" t="inlineStr"/>
@@ -7350,23 +7350,23 @@
       <c r="U116" s="14" t="inlineStr"/>
       <c r="V116" s="14" t="inlineStr"/>
       <c r="W116" s="14" t="n">
-        <v>1.569837989E9</v>
+        <v>1.753569219E9</v>
       </c>
       <c r="X116" s="14" t="n">
-        <v>1.8373123E8</v>
+        <v>1.82493718E8</v>
       </c>
       <c r="Y116" s="14" t="inlineStr"/>
       <c r="Z116" s="14" t="n">
-        <v>1.753569219E9</v>
+        <v>1.936062937E9</v>
       </c>
       <c r="AA116" s="14" t="inlineStr"/>
       <c r="AB116" s="14" t="inlineStr"/>
       <c r="AC116" s="15" t="n">
-        <v>0.6557850482423336</v>
+        <v>0.7240325119670905</v>
       </c>
       <c r="AD116" s="15" t="inlineStr"/>
       <c r="AE116" s="14" t="n">
-        <v>9.20430781E8</v>
+        <v>7.37937063E8</v>
       </c>
       <c r="AF116" s="14" t="inlineStr"/>
       <c r="AG116" s="14" t="inlineStr"/>
@@ -7407,23 +7407,23 @@
       <c r="U117" s="14" t="inlineStr"/>
       <c r="V117" s="14" t="inlineStr"/>
       <c r="W117" s="14" t="n">
-        <v>1.127223197E9</v>
+        <v>1.310954427E9</v>
       </c>
       <c r="X117" s="14" t="n">
-        <v>1.8373123E8</v>
+        <v>1.82493718E8</v>
       </c>
       <c r="Y117" s="14" t="inlineStr"/>
       <c r="Z117" s="14" t="n">
-        <v>1.310954427E9</v>
+        <v>1.493448145E9</v>
       </c>
       <c r="AA117" s="14" t="inlineStr"/>
       <c r="AB117" s="14" t="inlineStr"/>
       <c r="AC117" s="15" t="n">
-        <v>0.5879774071582347</v>
+        <v>0.6698278368317186</v>
       </c>
       <c r="AD117" s="15" t="inlineStr"/>
       <c r="AE117" s="14" t="n">
-        <v>9.18645573E8</v>
+        <v>7.36151855E8</v>
       </c>
       <c r="AF117" s="14" t="inlineStr"/>
       <c r="AG117" s="14" t="inlineStr"/>
@@ -9449,23 +9449,23 @@
       <c r="U152" s="14" t="inlineStr"/>
       <c r="V152" s="14" t="inlineStr"/>
       <c r="W152" s="14" t="n">
-        <v>2.9995561161E10</v>
+        <v>3.3898086196E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>3.902525035E9</v>
+        <v>1.646912991E9</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
-        <v>3.3898086196E10</v>
+        <v>3.5544999187E10</v>
       </c>
       <c r="AA152" s="14" t="inlineStr"/>
       <c r="AB152" s="14" t="inlineStr"/>
       <c r="AC152" s="15" t="n">
-        <v>0.640929169773647</v>
+        <v>0.672068230837679</v>
       </c>
       <c r="AD152" s="15" t="inlineStr"/>
       <c r="AE152" s="14" t="n">
-        <v>1.8990887804E10</v>
+        <v>1.7343974813E10</v>
       </c>
       <c r="AF152" s="14" t="inlineStr"/>
       <c r="AG152" s="14" t="inlineStr"/>
@@ -9512,23 +9512,23 @@
       <c r="U153" s="14" t="inlineStr"/>
       <c r="V153" s="14" t="inlineStr"/>
       <c r="W153" s="14" t="n">
-        <v>9.9508303E9</v>
+        <v>1.11880769E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>1.2372466E9</v>
+        <v>1.1951534E9</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>1.11880769E10</v>
+        <v>1.23832303E10</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.8507580690479567</v>
+        <v>0.9416393177101017</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>1.9626381E9</v>
+        <v>7.674847E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9569,23 +9569,23 @@
       <c r="U154" s="14" t="inlineStr"/>
       <c r="V154" s="14" t="inlineStr"/>
       <c r="W154" s="14" t="n">
-        <v>7.4634674E9</v>
+        <v>8.6973235E9</v>
       </c>
       <c r="X154" s="14" t="n">
-        <v>1.2338561E9</v>
+        <v>1.1951534E9</v>
       </c>
       <c r="Y154" s="14" t="inlineStr"/>
       <c r="Z154" s="14" t="n">
-        <v>8.6973235E9</v>
+        <v>9.8924769E9</v>
       </c>
       <c r="AA154" s="14" t="inlineStr"/>
       <c r="AB154" s="14" t="inlineStr"/>
       <c r="AC154" s="15" t="n">
-        <v>0.8207115758585963</v>
+        <v>0.933490665920816</v>
       </c>
       <c r="AD154" s="15" t="inlineStr"/>
       <c r="AE154" s="14" t="n">
-        <v>1.8999725E9</v>
+        <v>7.048191E8</v>
       </c>
       <c r="AF154" s="14" t="inlineStr"/>
       <c r="AG154" s="14" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
       <c r="U155" s="14" t="inlineStr"/>
       <c r="V155" s="14" t="inlineStr"/>
       <c r="W155" s="14" t="n">
-        <v>1.2339441E9</v>
+        <v>1.2373346E9</v>
       </c>
       <c r="X155" s="14" t="n">
-        <v>3390500.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y155" s="14" t="inlineStr"/>
       <c r="Z155" s="14" t="n">
@@ -9746,23 +9746,23 @@
       <c r="U157" s="14" t="inlineStr"/>
       <c r="V157" s="14" t="inlineStr"/>
       <c r="W157" s="14" t="n">
-        <v>135783.0</v>
+        <v>152199.0</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>16416.0</v>
+        <v>15915.0</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
-        <v>152199.0</v>
+        <v>168114.0</v>
       </c>
       <c r="AA157" s="14" t="inlineStr"/>
       <c r="AB157" s="14" t="inlineStr"/>
       <c r="AC157" s="15" t="n">
-        <v>0.6394915966386555</v>
+        <v>0.7063613445378151</v>
       </c>
       <c r="AD157" s="15" t="inlineStr"/>
       <c r="AE157" s="14" t="n">
-        <v>85801.0</v>
+        <v>69886.0</v>
       </c>
       <c r="AF157" s="14" t="inlineStr"/>
       <c r="AG157" s="14" t="inlineStr"/>
@@ -9803,23 +9803,23 @@
       <c r="U158" s="14" t="inlineStr"/>
       <c r="V158" s="14" t="inlineStr"/>
       <c r="W158" s="14" t="n">
-        <v>102089.0</v>
+        <v>118425.0</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>16336.0</v>
+        <v>15915.0</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
-        <v>118425.0</v>
+        <v>134340.0</v>
       </c>
       <c r="AA158" s="14" t="inlineStr"/>
       <c r="AB158" s="14" t="inlineStr"/>
       <c r="AC158" s="15" t="n">
-        <v>0.580514705882353</v>
+        <v>0.6585294117647059</v>
       </c>
       <c r="AD158" s="15" t="inlineStr"/>
       <c r="AE158" s="14" t="n">
-        <v>85575.0</v>
+        <v>69660.0</v>
       </c>
       <c r="AF158" s="14" t="inlineStr"/>
       <c r="AG158" s="14" t="inlineStr"/>
@@ -9860,10 +9860,10 @@
       <c r="U159" s="14" t="inlineStr"/>
       <c r="V159" s="14" t="inlineStr"/>
       <c r="W159" s="14" t="n">
-        <v>16986.0</v>
+        <v>17066.0</v>
       </c>
       <c r="X159" s="14" t="n">
-        <v>80.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y159" s="14" t="inlineStr"/>
       <c r="Z159" s="14" t="n">
@@ -9980,23 +9980,23 @@
       <c r="U161" s="14" t="inlineStr"/>
       <c r="V161" s="14" t="inlineStr"/>
       <c r="W161" s="14" t="n">
-        <v>7.8074705E8</v>
+        <v>8.786895E8</v>
       </c>
       <c r="X161" s="14" t="n">
-        <v>9.794245E7</v>
+        <v>9.460116E7</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
-        <v>8.786895E8</v>
+        <v>9.7329066E8</v>
       </c>
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>0.6406543691443987</v>
+        <v>0.7096282745798549</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>4.928605E8</v>
+        <v>3.9825934E8</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -10037,23 +10037,23 @@
       <c r="U162" s="14" t="inlineStr"/>
       <c r="V162" s="14" t="inlineStr"/>
       <c r="W162" s="14" t="n">
-        <v>5.8576199E8</v>
+        <v>6.8370444E8</v>
       </c>
       <c r="X162" s="14" t="n">
-        <v>9.794245E7</v>
+        <v>9.460116E7</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
-        <v>6.8370444E8</v>
+        <v>7.783056E8</v>
       </c>
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>0.5813813265306123</v>
+        <v>0.6618244897959183</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>4.9229556E8</v>
+        <v>3.976944E8</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10214,23 +10214,23 @@
       <c r="U165" s="14" t="inlineStr"/>
       <c r="V165" s="14" t="inlineStr"/>
       <c r="W165" s="14" t="n">
-        <v>2.4201339E8</v>
+        <v>2.7256082E8</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>3.054743E7</v>
+        <v>2.9746002E7</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
-        <v>2.7256082E8</v>
+        <v>3.02306822E8</v>
       </c>
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.6290973256058182</v>
+        <v>0.6977540397500791</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>1.6069618E8</v>
+        <v>1.30950178E8</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10271,23 +10271,23 @@
       <c r="U166" s="14" t="inlineStr"/>
       <c r="V166" s="14" t="inlineStr"/>
       <c r="W166" s="14" t="n">
-        <v>1.81690344E8</v>
+        <v>2.12169964E8</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>3.047962E7</v>
+        <v>2.9746002E7</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
-        <v>2.12169964E8</v>
+        <v>2.41915966E8</v>
       </c>
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.5703493655913978</v>
+        <v>0.6503117365591398</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>1.59830036E8</v>
+        <v>1.30084034E8</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -10328,10 +10328,10 @@
       <c r="U167" s="14" t="inlineStr"/>
       <c r="V167" s="14" t="inlineStr"/>
       <c r="W167" s="14" t="n">
-        <v>3.0066354E7</v>
+        <v>3.0134164E7</v>
       </c>
       <c r="X167" s="14" t="n">
-        <v>67810.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y167" s="14" t="inlineStr"/>
       <c r="Z167" s="14" t="n">
@@ -10492,23 +10492,23 @@
       <c r="U170" s="14" t="inlineStr"/>
       <c r="V170" s="14" t="inlineStr"/>
       <c r="W170" s="14" t="n">
-        <v>2.15166E9</v>
+        <v>2.41703E9</v>
       </c>
       <c r="X170" s="14" t="n">
-        <v>2.6537E8</v>
+        <v>2.5728E8</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
-        <v>2.41703E9</v>
+        <v>2.67431E9</v>
       </c>
       <c r="AA170" s="14" t="inlineStr"/>
       <c r="AB170" s="14" t="inlineStr"/>
       <c r="AC170" s="15" t="n">
-        <v>0.6278</v>
+        <v>0.694625974025974</v>
       </c>
       <c r="AD170" s="15" t="inlineStr"/>
       <c r="AE170" s="14" t="n">
-        <v>1.43297E9</v>
+        <v>1.17569E9</v>
       </c>
       <c r="AF170" s="14" t="inlineStr"/>
       <c r="AG170" s="14" t="inlineStr"/>
@@ -10549,23 +10549,23 @@
       <c r="U171" s="14" t="inlineStr"/>
       <c r="V171" s="14" t="inlineStr"/>
       <c r="W171" s="14" t="n">
-        <v>1.61394E9</v>
+        <v>1.87877E9</v>
       </c>
       <c r="X171" s="14" t="n">
-        <v>2.6483E8</v>
+        <v>2.5728E8</v>
       </c>
       <c r="Y171" s="14" t="inlineStr"/>
       <c r="Z171" s="14" t="n">
-        <v>1.87877E9</v>
+        <v>2.13605E9</v>
       </c>
       <c r="AA171" s="14" t="inlineStr"/>
       <c r="AB171" s="14" t="inlineStr"/>
       <c r="AC171" s="15" t="n">
-        <v>0.5693242424242424</v>
+        <v>0.6472878787878787</v>
       </c>
       <c r="AD171" s="15" t="inlineStr"/>
       <c r="AE171" s="14" t="n">
-        <v>1.42123E9</v>
+        <v>1.16395E9</v>
       </c>
       <c r="AF171" s="14" t="inlineStr"/>
       <c r="AG171" s="14" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
       <c r="U172" s="14" t="inlineStr"/>
       <c r="V172" s="14" t="inlineStr"/>
       <c r="W172" s="14" t="n">
-        <v>2.6553E8</v>
+        <v>2.6607E8</v>
       </c>
       <c r="X172" s="14" t="n">
-        <v>540000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y172" s="14" t="inlineStr"/>
       <c r="Z172" s="14" t="n">
@@ -10726,23 +10726,23 @@
       <c r="U174" s="14" t="inlineStr"/>
       <c r="V174" s="14" t="inlineStr"/>
       <c r="W174" s="14" t="n">
-        <v>2.10388789E8</v>
+        <v>2.14257962E8</v>
       </c>
       <c r="X174" s="14" t="n">
-        <v>3869173.0</v>
+        <v>3377534.0</v>
       </c>
       <c r="Y174" s="14" t="inlineStr"/>
       <c r="Z174" s="14" t="n">
-        <v>2.14257962E8</v>
+        <v>2.17635496E8</v>
       </c>
       <c r="AA174" s="14" t="inlineStr"/>
       <c r="AB174" s="14" t="inlineStr"/>
       <c r="AC174" s="15" t="n">
-        <v>0.8719243153054165</v>
+        <v>0.885669214178163</v>
       </c>
       <c r="AD174" s="15" t="inlineStr"/>
       <c r="AE174" s="14" t="n">
-        <v>3.1472038E7</v>
+        <v>2.8094504E7</v>
       </c>
       <c r="AF174" s="14" t="inlineStr"/>
       <c r="AG174" s="14" t="inlineStr"/>
@@ -10783,23 +10783,23 @@
       <c r="U175" s="14" t="inlineStr"/>
       <c r="V175" s="14" t="inlineStr"/>
       <c r="W175" s="14" t="n">
-        <v>2.5023751E7</v>
+        <v>2.8801831E7</v>
       </c>
       <c r="X175" s="14" t="n">
-        <v>3778080.0</v>
+        <v>3377534.0</v>
       </c>
       <c r="Y175" s="14" t="inlineStr"/>
       <c r="Z175" s="14" t="n">
-        <v>2.8801831E7</v>
+        <v>3.2179365E7</v>
       </c>
       <c r="AA175" s="14" t="inlineStr"/>
       <c r="AB175" s="14" t="inlineStr"/>
       <c r="AC175" s="15" t="n">
-        <v>0.4800305166666667</v>
+        <v>0.53632275</v>
       </c>
       <c r="AD175" s="15" t="inlineStr"/>
       <c r="AE175" s="14" t="n">
-        <v>3.1198169E7</v>
+        <v>2.7820635E7</v>
       </c>
       <c r="AF175" s="14" t="inlineStr"/>
       <c r="AG175" s="14" t="inlineStr"/>
@@ -10840,10 +10840,10 @@
       <c r="U176" s="14" t="inlineStr"/>
       <c r="V176" s="14" t="inlineStr"/>
       <c r="W176" s="14" t="n">
-        <v>9.2637075E7</v>
+        <v>9.2728168E7</v>
       </c>
       <c r="X176" s="14" t="n">
-        <v>91093.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y176" s="14" t="inlineStr"/>
       <c r="Z176" s="14" t="n">
@@ -10960,23 +10960,23 @@
       <c r="U178" s="14" t="inlineStr"/>
       <c r="V178" s="14" t="inlineStr"/>
       <c r="W178" s="14" t="n">
-        <v>5.449605E8</v>
+        <v>6.133974E8</v>
       </c>
       <c r="X178" s="14" t="n">
-        <v>6.84369E7</v>
+        <v>6.655398E7</v>
       </c>
       <c r="Y178" s="14" t="inlineStr"/>
       <c r="Z178" s="14" t="n">
-        <v>6.133974E8</v>
+        <v>6.7995138E8</v>
       </c>
       <c r="AA178" s="14" t="inlineStr"/>
       <c r="AB178" s="14" t="inlineStr"/>
       <c r="AC178" s="15" t="n">
-        <v>0.6259157142857142</v>
+        <v>0.6938279387755102</v>
       </c>
       <c r="AD178" s="15" t="inlineStr"/>
       <c r="AE178" s="14" t="n">
-        <v>3.666026E8</v>
+        <v>3.0004862E8</v>
       </c>
       <c r="AF178" s="14" t="inlineStr"/>
       <c r="AG178" s="14" t="inlineStr"/>
@@ -11017,23 +11017,23 @@
       <c r="U179" s="14" t="inlineStr"/>
       <c r="V179" s="14" t="inlineStr"/>
       <c r="W179" s="14" t="n">
-        <v>4.084488E8</v>
+        <v>4.7666844E8</v>
       </c>
       <c r="X179" s="14" t="n">
-        <v>6.821964E7</v>
+        <v>6.655398E7</v>
       </c>
       <c r="Y179" s="14" t="inlineStr"/>
       <c r="Z179" s="14" t="n">
-        <v>4.7666844E8</v>
+        <v>5.4322242E8</v>
       </c>
       <c r="AA179" s="14" t="inlineStr"/>
       <c r="AB179" s="14" t="inlineStr"/>
       <c r="AC179" s="15" t="n">
-        <v>0.5674624285714286</v>
+        <v>0.6466933571428571</v>
       </c>
       <c r="AD179" s="15" t="inlineStr"/>
       <c r="AE179" s="14" t="n">
-        <v>3.6333156E8</v>
+        <v>2.9677758E8</v>
       </c>
       <c r="AF179" s="14" t="inlineStr"/>
       <c r="AG179" s="14" t="inlineStr"/>
@@ -11074,10 +11074,10 @@
       <c r="U180" s="14" t="inlineStr"/>
       <c r="V180" s="14" t="inlineStr"/>
       <c r="W180" s="14" t="n">
-        <v>6.778512E7</v>
+        <v>6.800238E7</v>
       </c>
       <c r="X180" s="14" t="n">
-        <v>217260.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y180" s="14" t="inlineStr"/>
       <c r="Z180" s="14" t="n">
@@ -11194,10 +11194,10 @@
       <c r="U182" s="14" t="inlineStr"/>
       <c r="V182" s="14" t="inlineStr"/>
       <c r="W182" s="14" t="n">
-        <v>1.046634E9</v>
+        <v>1.249247E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>2.02613E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
@@ -11251,10 +11251,10 @@
       <c r="U183" s="14" t="inlineStr"/>
       <c r="V183" s="14" t="inlineStr"/>
       <c r="W183" s="14" t="n">
-        <v>9.1E7</v>
+        <v>1.09165E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>1.8165E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
@@ -11308,10 +11308,10 @@
       <c r="U184" s="14" t="inlineStr"/>
       <c r="V184" s="14" t="inlineStr"/>
       <c r="W184" s="14" t="n">
-        <v>7.40999E8</v>
+        <v>8.87112E8</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>1.46113E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
@@ -11365,10 +11365,10 @@
       <c r="U185" s="14" t="inlineStr"/>
       <c r="V185" s="14" t="inlineStr"/>
       <c r="W185" s="14" t="n">
-        <v>2.14635E8</v>
+        <v>2.5297E8</v>
       </c>
       <c r="X185" s="14" t="n">
-        <v>3.8335E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y185" s="14" t="inlineStr"/>
       <c r="Z185" s="14" t="n">
@@ -11428,23 +11428,23 @@
       <c r="U186" s="14" t="inlineStr"/>
       <c r="V186" s="14" t="inlineStr"/>
       <c r="W186" s="14" t="n">
-        <v>1850000.0</v>
+        <v>2035000.0</v>
       </c>
       <c r="X186" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y186" s="14" t="inlineStr"/>
       <c r="Z186" s="14" t="n">
-        <v>2035000.0</v>
+        <v>2220000.0</v>
       </c>
       <c r="AA186" s="14" t="inlineStr"/>
       <c r="AB186" s="14" t="inlineStr"/>
       <c r="AC186" s="15" t="n">
-        <v>0.39285714285714285</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AD186" s="15" t="inlineStr"/>
       <c r="AE186" s="14" t="n">
-        <v>3145000.0</v>
+        <v>2960000.0</v>
       </c>
       <c r="AF186" s="14" t="inlineStr"/>
       <c r="AG186" s="14" t="inlineStr"/>
@@ -11485,23 +11485,23 @@
       <c r="U187" s="14" t="inlineStr"/>
       <c r="V187" s="14" t="inlineStr"/>
       <c r="W187" s="14" t="n">
-        <v>1295000.0</v>
+        <v>1480000.0</v>
       </c>
       <c r="X187" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y187" s="14" t="inlineStr"/>
       <c r="Z187" s="14" t="n">
-        <v>1480000.0</v>
+        <v>1665000.0</v>
       </c>
       <c r="AA187" s="14" t="inlineStr"/>
       <c r="AB187" s="14" t="inlineStr"/>
       <c r="AC187" s="15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="AD187" s="15" t="inlineStr"/>
       <c r="AE187" s="14" t="n">
-        <v>2960000.0</v>
+        <v>2775000.0</v>
       </c>
       <c r="AF187" s="14" t="inlineStr"/>
       <c r="AG187" s="14" t="inlineStr"/>
@@ -11662,10 +11662,10 @@
       <c r="U190" s="14" t="inlineStr"/>
       <c r="V190" s="14" t="inlineStr"/>
       <c r="W190" s="14" t="n">
-        <v>1.5066341349E10</v>
+        <v>1.7062639415E10</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>1.996298066E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
@@ -11719,10 +11719,10 @@
       <c r="U191" s="14" t="inlineStr"/>
       <c r="V191" s="14" t="inlineStr"/>
       <c r="W191" s="14" t="n">
-        <v>1.0293742797E10</v>
+        <v>1.2285354215E10</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>1.991611418E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
@@ -11776,10 +11776,10 @@
       <c r="U192" s="14" t="inlineStr"/>
       <c r="V192" s="14" t="inlineStr"/>
       <c r="W192" s="14" t="n">
-        <v>2.362459773E9</v>
+        <v>2.367146421E9</v>
       </c>
       <c r="X192" s="14" t="n">
-        <v>4686648.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y192" s="14" t="inlineStr"/>
       <c r="Z192" s="14" t="n">
@@ -11896,23 +11896,23 @@
       <c r="U194" s="14" t="inlineStr"/>
       <c r="V194" s="14" t="inlineStr"/>
       <c r="W194" s="14" t="n">
-        <v>1.1289104178E10</v>
+        <v>1.2877655972E10</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>1.588551794E9</v>
+        <v>7.19581582E8</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>1.2877655972E10</v>
+        <v>1.3597237554E10</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.8588546270678621</v>
+        <v>0.9068459674637595</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>2.116332028E9</v>
+        <v>1.396750446E9</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -12003,23 +12003,23 @@
       <c r="U196" s="14" t="inlineStr"/>
       <c r="V196" s="14" t="inlineStr"/>
       <c r="W196" s="14" t="n">
-        <v>4.219166866E9</v>
+        <v>4.762388866E9</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>5.43222E8</v>
+        <v>5.493708E8</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="14" t="n">
-        <v>4.762388866E9</v>
+        <v>5.311759666E9</v>
       </c>
       <c r="AA196" s="14" t="inlineStr"/>
       <c r="AB196" s="14" t="inlineStr"/>
       <c r="AC196" s="15" t="n">
-        <v>1.0681407538457328</v>
+        <v>1.1913573489125906</v>
       </c>
       <c r="AD196" s="15" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>-3.03810866E8</v>
+        <v>-8.53181666E8</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12060,23 +12060,23 @@
       <c r="U197" s="14" t="inlineStr"/>
       <c r="V197" s="14" t="inlineStr"/>
       <c r="W197" s="14" t="n">
-        <v>3.1300532E9</v>
+        <v>3.6732752E9</v>
       </c>
       <c r="X197" s="14" t="n">
-        <v>5.43222E8</v>
+        <v>5.493708E8</v>
       </c>
       <c r="Y197" s="14" t="inlineStr"/>
       <c r="Z197" s="14" t="n">
-        <v>3.6732752E9</v>
+        <v>4.222646E9</v>
       </c>
       <c r="AA197" s="14" t="inlineStr"/>
       <c r="AB197" s="14" t="inlineStr"/>
       <c r="AC197" s="15" t="n">
-        <v>1.091031224976179</v>
+        <v>1.2542045959477153</v>
       </c>
       <c r="AD197" s="15" t="inlineStr"/>
       <c r="AE197" s="14" t="n">
-        <v>-3.064832E8</v>
+        <v>-8.55854E8</v>
       </c>
       <c r="AF197" s="14" t="inlineStr"/>
       <c r="AG197" s="14" t="inlineStr"/>
@@ -12237,23 +12237,23 @@
       <c r="U200" s="14" t="inlineStr"/>
       <c r="V200" s="14" t="inlineStr"/>
       <c r="W200" s="14" t="n">
-        <v>80109.0</v>
+        <v>91671.0</v>
       </c>
       <c r="X200" s="14" t="n">
-        <v>11562.0</v>
+        <v>10062.0</v>
       </c>
       <c r="Y200" s="14" t="inlineStr"/>
       <c r="Z200" s="14" t="n">
-        <v>91671.0</v>
+        <v>101733.0</v>
       </c>
       <c r="AA200" s="14" t="inlineStr"/>
       <c r="AB200" s="14" t="inlineStr"/>
       <c r="AC200" s="15" t="n">
-        <v>0.5801962025316456</v>
+        <v>0.643879746835443</v>
       </c>
       <c r="AD200" s="15" t="inlineStr"/>
       <c r="AE200" s="14" t="n">
-        <v>66329.0</v>
+        <v>56267.0</v>
       </c>
       <c r="AF200" s="14" t="inlineStr"/>
       <c r="AG200" s="14" t="inlineStr"/>
@@ -12294,23 +12294,23 @@
       <c r="U201" s="14" t="inlineStr"/>
       <c r="V201" s="14" t="inlineStr"/>
       <c r="W201" s="14" t="n">
-        <v>66989.0</v>
+        <v>78551.0</v>
       </c>
       <c r="X201" s="14" t="n">
-        <v>11562.0</v>
+        <v>10062.0</v>
       </c>
       <c r="Y201" s="14" t="inlineStr"/>
       <c r="Z201" s="14" t="n">
-        <v>78551.0</v>
+        <v>88613.0</v>
       </c>
       <c r="AA201" s="14" t="inlineStr"/>
       <c r="AB201" s="14" t="inlineStr"/>
       <c r="AC201" s="15" t="n">
-        <v>0.5454930555555556</v>
+        <v>0.6153680555555555</v>
       </c>
       <c r="AD201" s="15" t="inlineStr"/>
       <c r="AE201" s="14" t="n">
-        <v>65449.0</v>
+        <v>55387.0</v>
       </c>
       <c r="AF201" s="14" t="inlineStr"/>
       <c r="AG201" s="14" t="inlineStr"/>
@@ -12471,23 +12471,23 @@
       <c r="U204" s="14" t="inlineStr"/>
       <c r="V204" s="14" t="inlineStr"/>
       <c r="W204" s="14" t="n">
-        <v>2.8535144E8</v>
+        <v>3.2254353E8</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>3.719209E7</v>
+        <v>3.730664E7</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>3.2254353E8</v>
+        <v>3.5985017E8</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.8933090626090521</v>
+        <v>0.9966326654960589</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>3.852247E7</v>
+        <v>1215830.0</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12528,23 +12528,23 @@
       <c r="U205" s="14" t="inlineStr"/>
       <c r="V205" s="14" t="inlineStr"/>
       <c r="W205" s="14" t="n">
-        <v>2.1196572E8</v>
+        <v>2.4881876E8</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>3.685304E7</v>
+        <v>3.730664E7</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>2.4881876E8</v>
+        <v>2.861254E8</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.8639540277777777</v>
+        <v>0.9934909722222223</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>3.918124E7</v>
+        <v>1874600.0</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12585,10 +12585,10 @@
       <c r="U206" s="14" t="inlineStr"/>
       <c r="V206" s="14" t="inlineStr"/>
       <c r="W206" s="14" t="n">
-        <v>3.685304E7</v>
+        <v>3.719209E7</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>339050.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
@@ -12705,23 +12705,23 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>8.5898944E7</v>
+        <v>9.6747576E7</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>1.0848632E7</v>
+        <v>1.098572E7</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>9.6747576E7</v>
+        <v>1.07733296E8</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.8632935003747725</v>
+        <v>0.9613207695327837</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.5320424E7</v>
+        <v>4334704.0</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12762,23 +12762,23 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>6.401636E7</v>
+        <v>7.4864992E7</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>1.0848632E7</v>
+        <v>1.098572E7</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>7.4864992E7</v>
+        <v>8.5850712E7</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.8318332444444444</v>
+        <v>0.9538968</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>1.5135008E7</v>
+        <v>4149288.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12939,23 +12939,23 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>6.8943E8</v>
+        <v>7.7817E8</v>
       </c>
       <c r="X212" s="14" t="n">
         <v>8.874E7</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>7.7817E8</v>
+        <v>8.6691E8</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.8664239428151513</v>
+        <v>0.9652281381521812</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>1.1997E8</v>
+        <v>3.123E7</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
@@ -12996,23 +12996,23 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>5.1162E8</v>
+        <v>6.0036E8</v>
       </c>
       <c r="X213" s="14" t="n">
         <v>8.874E7</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>6.0036E8</v>
+        <v>6.891E8</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.8338333333333333</v>
+        <v>0.9570833333333333</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>1.1964E8</v>
+        <v>3.09E7</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
@@ -13173,23 +13173,23 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>2.5925153E8</v>
+        <v>2.9241989E8</v>
       </c>
       <c r="X216" s="14" t="n">
         <v>3.316836E7</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>2.9241989E8</v>
+        <v>3.2558825E8</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.8841168805253546</v>
+        <v>0.9843997544958699</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>3.832811E7</v>
+        <v>5159750.0</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
@@ -13230,23 +13230,23 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>1.9270962E8</v>
+        <v>2.2587798E8</v>
       </c>
       <c r="X217" s="14" t="n">
         <v>3.316836E7</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>2.2587798E8</v>
+        <v>2.5904634E8</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.8555984090909091</v>
+        <v>0.9812361363636364</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>3.812202E7</v>
+        <v>4953660.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
@@ -13407,10 +13407,10 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>5.34431E8</v>
+        <v>6.44264E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>1.09833E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
@@ -13464,10 +13464,10 @@
       <c r="U221" s="14" t="inlineStr"/>
       <c r="V221" s="14" t="inlineStr"/>
       <c r="W221" s="14" t="n">
-        <v>5.11E7</v>
+        <v>6.181E7</v>
       </c>
       <c r="X221" s="14" t="n">
-        <v>1.071E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="n">
@@ -13565,10 +13565,10 @@
       <c r="U223" s="14" t="inlineStr"/>
       <c r="V223" s="14" t="inlineStr"/>
       <c r="W223" s="14" t="n">
-        <v>4.83331E8</v>
+        <v>5.82454E8</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>9.9123E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
@@ -13628,10 +13628,10 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>5.215494289E9</v>
+        <v>5.981030439E9</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>7.6553615E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
@@ -13685,10 +13685,10 @@
       <c r="U225" s="14" t="inlineStr"/>
       <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="n">
-        <v>3.641050913E9</v>
+        <v>4.406587063E9</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>7.6553615E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
@@ -13862,23 +13862,23 @@
       <c r="U228" s="25" t="inlineStr"/>
       <c r="V228" s="25" t="inlineStr"/>
       <c r="W228" s="25" t="n">
-        <v>2.551189645E9</v>
+        <v>2.97538798E9</v>
       </c>
       <c r="X228" s="25" t="n">
-        <v>4.24198335E8</v>
+        <v>7.341E7</v>
       </c>
       <c r="Y228" s="25" t="inlineStr"/>
       <c r="Z228" s="25" t="n">
-        <v>2.97538798E9</v>
+        <v>3.04879798E9</v>
       </c>
       <c r="AA228" s="25" t="inlineStr"/>
       <c r="AB228" s="25" t="inlineStr"/>
       <c r="AC228" s="26" t="n">
-        <v>0.5260801811389397</v>
+        <v>0.5390598484485487</v>
       </c>
       <c r="AD228" s="26" t="inlineStr"/>
       <c r="AE228" s="25" t="n">
-        <v>2.68038102E9</v>
+        <v>2.60697102E9</v>
       </c>
       <c r="AF228" s="25" t="inlineStr"/>
       <c r="AG228" s="25" t="inlineStr"/>
@@ -13925,23 +13925,23 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>1.760022116E9</v>
+        <v>2.088338999E9</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>3.28316883E8</v>
+        <v>6.35E7</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>2.088338999E9</v>
+        <v>2.151838999E9</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.537586873631474</v>
+        <v>0.5539332457922893</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1.796315001E9</v>
+        <v>1.732815001E9</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13988,23 +13988,23 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>4.13618356E8</v>
+        <v>4.83128803E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>6.9510447E7</v>
+        <v>6.35E7</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>4.83128803E8</v>
+        <v>5.46628803E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.6575712866314513</v>
+        <v>0.7439991221109624</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>2.51588197E8</v>
+        <v>1.88088197E8</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14045,23 +14045,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>3.845E8</v>
+        <v>4.48E8</v>
       </c>
       <c r="X231" s="14" t="n">
         <v>6.35E7</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>4.48E8</v>
+        <v>5.115E8</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.6588235294117647</v>
+        <v>0.7522058823529412</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>2.32E8</v>
+        <v>1.685E8</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14102,10 +14102,10 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>2076300.0</v>
+        <v>2419200.0</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>342900.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
@@ -14159,10 +14159,10 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>2.7042056E7</v>
+        <v>3.2709603E7</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>5667547.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
@@ -14222,10 +14222,10 @@
       <c r="U234" s="14" t="inlineStr"/>
       <c r="V234" s="14" t="inlineStr"/>
       <c r="W234" s="14" t="n">
-        <v>4157000.0</v>
+        <v>5144000.0</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>987000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
@@ -14279,10 +14279,10 @@
       <c r="U235" s="14" t="inlineStr"/>
       <c r="V235" s="14" t="inlineStr"/>
       <c r="W235" s="14" t="n">
-        <v>2137000.0</v>
+        <v>2720000.0</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>583000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
@@ -14336,10 +14336,10 @@
       <c r="U236" s="14" t="inlineStr"/>
       <c r="V236" s="14" t="inlineStr"/>
       <c r="W236" s="14" t="n">
-        <v>2020000.0</v>
+        <v>2424000.0</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>404000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
@@ -14399,10 +14399,10 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>8622580.0</v>
+        <v>1.280558E7</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>4183000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
@@ -14456,10 +14456,10 @@
       <c r="U238" s="14" t="inlineStr"/>
       <c r="V238" s="14" t="inlineStr"/>
       <c r="W238" s="14" t="n">
-        <v>8622580.0</v>
+        <v>1.280558E7</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>4183000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
@@ -14639,10 +14639,10 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>1.33163418E9</v>
+        <v>1.585270616E9</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>2.53636436E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
@@ -14696,10 +14696,10 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>2.4455968E8</v>
+        <v>2.85881376E8</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>4.1321696E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
@@ -14753,10 +14753,10 @@
       <c r="U243" s="14" t="inlineStr"/>
       <c r="V243" s="14" t="inlineStr"/>
       <c r="W243" s="14" t="n">
-        <v>5.597624E7</v>
+        <v>6.5444768E7</v>
       </c>
       <c r="X243" s="14" t="n">
-        <v>9468528.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
@@ -14810,10 +14810,10 @@
       <c r="U244" s="14" t="inlineStr"/>
       <c r="V244" s="14" t="inlineStr"/>
       <c r="W244" s="14" t="n">
-        <v>8.129932E7</v>
+        <v>9.5029104E7</v>
       </c>
       <c r="X244" s="14" t="n">
-        <v>1.3729784E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
@@ -14867,10 +14867,10 @@
       <c r="U245" s="14" t="inlineStr"/>
       <c r="V245" s="14" t="inlineStr"/>
       <c r="W245" s="14" t="n">
-        <v>2.736644E7</v>
+        <v>3.1996368E7</v>
       </c>
       <c r="X245" s="14" t="n">
-        <v>4629928.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
@@ -14924,10 +14924,10 @@
       <c r="U246" s="14" t="inlineStr"/>
       <c r="V246" s="14" t="inlineStr"/>
       <c r="W246" s="14" t="n">
-        <v>9.224325E8</v>
+        <v>1.106919E9</v>
       </c>
       <c r="X246" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
@@ -14987,10 +14987,10 @@
       <c r="U247" s="14" t="inlineStr"/>
       <c r="V247" s="14" t="inlineStr"/>
       <c r="W247" s="14" t="n">
-        <v>3.80681131E8</v>
+        <v>4.32620013E8</v>
       </c>
       <c r="X247" s="14" t="n">
-        <v>5.1938882E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
@@ -15094,10 +15094,10 @@
       <c r="U249" s="14" t="inlineStr"/>
       <c r="V249" s="14" t="inlineStr"/>
       <c r="W249" s="14" t="n">
-        <v>2.73406741E8</v>
+        <v>3.10883859E8</v>
       </c>
       <c r="X249" s="14" t="n">
-        <v>3.7477118E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
@@ -15151,10 +15151,10 @@
       <c r="U250" s="14" t="inlineStr"/>
       <c r="V250" s="14" t="inlineStr"/>
       <c r="W250" s="14" t="n">
-        <v>2.73406741E8</v>
+        <v>3.10883859E8</v>
       </c>
       <c r="X250" s="14" t="n">
-        <v>3.7477118E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
@@ -15214,10 +15214,10 @@
       <c r="U251" s="14" t="inlineStr"/>
       <c r="V251" s="14" t="inlineStr"/>
       <c r="W251" s="14" t="n">
-        <v>4161834.0</v>
+        <v>4425348.0</v>
       </c>
       <c r="X251" s="14" t="n">
-        <v>263514.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
@@ -15271,10 +15271,10 @@
       <c r="U252" s="14" t="inlineStr"/>
       <c r="V252" s="14" t="inlineStr"/>
       <c r="W252" s="14" t="n">
-        <v>4161834.0</v>
+        <v>4425348.0</v>
       </c>
       <c r="X252" s="14" t="n">
-        <v>263514.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
@@ -15334,10 +15334,10 @@
       <c r="U253" s="14" t="inlineStr"/>
       <c r="V253" s="14" t="inlineStr"/>
       <c r="W253" s="14" t="n">
-        <v>2.13328E7</v>
+        <v>2.48451E7</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>3512300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
@@ -15391,10 +15391,10 @@
       <c r="U254" s="14" t="inlineStr"/>
       <c r="V254" s="14" t="inlineStr"/>
       <c r="W254" s="14" t="n">
-        <v>2.13328E7</v>
+        <v>2.48451E7</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>3512300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
@@ -15454,10 +15454,10 @@
       <c r="U255" s="14" t="inlineStr"/>
       <c r="V255" s="14" t="inlineStr"/>
       <c r="W255" s="14" t="n">
-        <v>8.1779756E7</v>
+        <v>9.2465706E7</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>1.068595E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
@@ -15511,10 +15511,10 @@
       <c r="U256" s="14" t="inlineStr"/>
       <c r="V256" s="14" t="inlineStr"/>
       <c r="W256" s="14" t="n">
-        <v>5.607995E7</v>
+        <v>6.58569E7</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>9776950.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
@@ -15568,10 +15568,10 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>2.5699806E7</v>
+        <v>2.6608806E7</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>909000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
@@ -15631,10 +15631,10 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>3.51036398E8</v>
+        <v>3.84588968E8</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>3.355257E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
@@ -15991,10 +15991,10 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>9.0095326E7</v>
+        <v>1.10331326E8</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>2.0236E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
@@ -16048,10 +16048,10 @@
       <c r="U265" s="14" t="inlineStr"/>
       <c r="V265" s="14" t="inlineStr"/>
       <c r="W265" s="14" t="n">
-        <v>1.5716622E7</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>1215000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
@@ -16105,10 +16105,10 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>1.0101299E7</v>
+        <v>1.1156299E7</v>
       </c>
       <c r="X266" s="14" t="n">
-        <v>1055000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
@@ -16162,10 +16162,10 @@
       <c r="U267" s="14" t="inlineStr"/>
       <c r="V267" s="14" t="inlineStr"/>
       <c r="W267" s="14" t="n">
-        <v>1.155E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>1.3777E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
@@ -16662,10 +16662,10 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>1.1095E7</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X276" s="14" t="n">
-        <v>4189000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
@@ -16839,10 +16839,10 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>8.3881357E7</v>
+        <v>8.8386927E7</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>4505570.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
@@ -17067,10 +17067,10 @@
       <c r="U283" s="14" t="inlineStr"/>
       <c r="V283" s="14" t="inlineStr"/>
       <c r="W283" s="14" t="n">
-        <v>6.3191077E7</v>
+        <v>6.6116077E7</v>
       </c>
       <c r="X283" s="14" t="n">
-        <v>2925000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y283" s="14" t="inlineStr"/>
       <c r="Z283" s="14" t="n">
@@ -17124,10 +17124,10 @@
       <c r="U284" s="14" t="inlineStr"/>
       <c r="V284" s="14" t="inlineStr"/>
       <c r="W284" s="14" t="n">
-        <v>2027000.0</v>
+        <v>2177000.0</v>
       </c>
       <c r="X284" s="14" t="n">
-        <v>150000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
@@ -17181,10 +17181,10 @@
       <c r="U285" s="14" t="inlineStr"/>
       <c r="V285" s="14" t="inlineStr"/>
       <c r="W285" s="14" t="n">
-        <v>4686025.0</v>
+        <v>4737535.0</v>
       </c>
       <c r="X285" s="14" t="n">
-        <v>51510.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y285" s="14" t="inlineStr"/>
       <c r="Z285" s="14" t="n">
@@ -17352,10 +17352,10 @@
       <c r="U288" s="14" t="inlineStr"/>
       <c r="V288" s="14" t="inlineStr"/>
       <c r="W288" s="14" t="n">
-        <v>2597953.0</v>
+        <v>3707013.0</v>
       </c>
       <c r="X288" s="14" t="n">
-        <v>1109060.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y288" s="14" t="inlineStr"/>
       <c r="Z288" s="14" t="n">
@@ -17523,10 +17523,10 @@
       <c r="U291" s="14" t="inlineStr"/>
       <c r="V291" s="14" t="inlineStr"/>
       <c r="W291" s="14" t="n">
-        <v>0.0</v>
+        <v>270000.0</v>
       </c>
       <c r="X291" s="14" t="n">
-        <v>270000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y291" s="14" t="inlineStr"/>
       <c r="Z291" s="14" t="n">
@@ -17586,10 +17586,10 @@
       <c r="U292" s="14" t="inlineStr"/>
       <c r="V292" s="14" t="inlineStr"/>
       <c r="W292" s="14" t="n">
-        <v>5.2605E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="X292" s="14" t="n">
-        <v>8811000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y292" s="14" t="inlineStr"/>
       <c r="Z292" s="14" t="n">
@@ -17757,10 +17757,10 @@
       <c r="U295" s="14" t="inlineStr"/>
       <c r="V295" s="14" t="inlineStr"/>
       <c r="W295" s="14" t="n">
-        <v>1965000.0</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X295" s="14" t="n">
-        <v>8811000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y295" s="14" t="inlineStr"/>
       <c r="Z295" s="14" t="n">
@@ -17820,23 +17820,23 @@
       <c r="U296" s="14" t="inlineStr"/>
       <c r="V296" s="14" t="inlineStr"/>
       <c r="W296" s="14" t="n">
-        <v>5.945E7</v>
+        <v>6.984E7</v>
       </c>
       <c r="X296" s="14" t="n">
-        <v>1.039E7</v>
+        <v>9910000.0</v>
       </c>
       <c r="Y296" s="14" t="inlineStr"/>
       <c r="Z296" s="14" t="n">
-        <v>6.984E7</v>
+        <v>7.975E7</v>
       </c>
       <c r="AA296" s="14" t="inlineStr"/>
       <c r="AB296" s="14" t="inlineStr"/>
       <c r="AC296" s="15" t="n">
-        <v>0.5283704039945529</v>
+        <v>0.6033439249508247</v>
       </c>
       <c r="AD296" s="15" t="inlineStr"/>
       <c r="AE296" s="14" t="n">
-        <v>6.234E7</v>
+        <v>5.243E7</v>
       </c>
       <c r="AF296" s="14" t="inlineStr"/>
       <c r="AG296" s="14" t="inlineStr"/>
@@ -17883,23 +17883,23 @@
       <c r="U297" s="14" t="inlineStr"/>
       <c r="V297" s="14" t="inlineStr"/>
       <c r="W297" s="14" t="n">
-        <v>5.195E7</v>
+        <v>6.234E7</v>
       </c>
       <c r="X297" s="14" t="n">
-        <v>1.039E7</v>
+        <v>9910000.0</v>
       </c>
       <c r="Y297" s="14" t="inlineStr"/>
       <c r="Z297" s="14" t="n">
-        <v>6.234E7</v>
+        <v>7.225E7</v>
       </c>
       <c r="AA297" s="14" t="inlineStr"/>
       <c r="AB297" s="14" t="inlineStr"/>
       <c r="AC297" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5794834777029195</v>
       </c>
       <c r="AD297" s="15" t="inlineStr"/>
       <c r="AE297" s="14" t="n">
-        <v>6.234E7</v>
+        <v>5.243E7</v>
       </c>
       <c r="AF297" s="14" t="inlineStr"/>
       <c r="AG297" s="14" t="inlineStr"/>
@@ -17940,23 +17940,23 @@
       <c r="U298" s="14" t="inlineStr"/>
       <c r="V298" s="14" t="inlineStr"/>
       <c r="W298" s="14" t="n">
-        <v>1.275E7</v>
+        <v>1.53E7</v>
       </c>
       <c r="X298" s="14" t="n">
         <v>2550000.0</v>
       </c>
       <c r="Y298" s="14" t="inlineStr"/>
       <c r="Z298" s="14" t="n">
-        <v>1.53E7</v>
+        <v>1.785E7</v>
       </c>
       <c r="AA298" s="14" t="inlineStr"/>
       <c r="AB298" s="14" t="inlineStr"/>
       <c r="AC298" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD298" s="15" t="inlineStr"/>
       <c r="AE298" s="14" t="n">
-        <v>1.53E7</v>
+        <v>1.275E7</v>
       </c>
       <c r="AF298" s="14" t="inlineStr"/>
       <c r="AG298" s="14" t="inlineStr"/>
@@ -17997,23 +17997,23 @@
       <c r="U299" s="14" t="inlineStr"/>
       <c r="V299" s="14" t="inlineStr"/>
       <c r="W299" s="14" t="n">
-        <v>1.24E7</v>
+        <v>1.488E7</v>
       </c>
       <c r="X299" s="14" t="n">
         <v>2480000.0</v>
       </c>
       <c r="Y299" s="14" t="inlineStr"/>
       <c r="Z299" s="14" t="n">
-        <v>1.488E7</v>
+        <v>1.736E7</v>
       </c>
       <c r="AA299" s="14" t="inlineStr"/>
       <c r="AB299" s="14" t="inlineStr"/>
       <c r="AC299" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD299" s="15" t="inlineStr"/>
       <c r="AE299" s="14" t="n">
-        <v>1.488E7</v>
+        <v>1.24E7</v>
       </c>
       <c r="AF299" s="14" t="inlineStr"/>
       <c r="AG299" s="14" t="inlineStr"/>
@@ -18054,23 +18054,23 @@
       <c r="U300" s="14" t="inlineStr"/>
       <c r="V300" s="14" t="inlineStr"/>
       <c r="W300" s="14" t="n">
-        <v>6150000.0</v>
+        <v>7380000.0</v>
       </c>
       <c r="X300" s="14" t="n">
         <v>1230000.0</v>
       </c>
       <c r="Y300" s="14" t="inlineStr"/>
       <c r="Z300" s="14" t="n">
-        <v>7380000.0</v>
+        <v>8610000.0</v>
       </c>
       <c r="AA300" s="14" t="inlineStr"/>
       <c r="AB300" s="14" t="inlineStr"/>
       <c r="AC300" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD300" s="15" t="inlineStr"/>
       <c r="AE300" s="14" t="n">
-        <v>7380000.0</v>
+        <v>6150000.0</v>
       </c>
       <c r="AF300" s="14" t="inlineStr"/>
       <c r="AG300" s="14" t="inlineStr"/>
@@ -18111,23 +18111,23 @@
       <c r="U301" s="14" t="inlineStr"/>
       <c r="V301" s="14" t="inlineStr"/>
       <c r="W301" s="14" t="n">
-        <v>5350000.0</v>
+        <v>6420000.0</v>
       </c>
       <c r="X301" s="14" t="n">
         <v>1070000.0</v>
       </c>
       <c r="Y301" s="14" t="inlineStr"/>
       <c r="Z301" s="14" t="n">
-        <v>6420000.0</v>
+        <v>7490000.0</v>
       </c>
       <c r="AA301" s="14" t="inlineStr"/>
       <c r="AB301" s="14" t="inlineStr"/>
       <c r="AC301" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD301" s="15" t="inlineStr"/>
       <c r="AE301" s="14" t="n">
-        <v>6420000.0</v>
+        <v>5350000.0</v>
       </c>
       <c r="AF301" s="14" t="inlineStr"/>
       <c r="AG301" s="14" t="inlineStr"/>
@@ -18212,23 +18212,23 @@
       <c r="U303" s="14" t="inlineStr"/>
       <c r="V303" s="14" t="inlineStr"/>
       <c r="W303" s="14" t="n">
-        <v>1.2E7</v>
+        <v>1.44E7</v>
       </c>
       <c r="X303" s="14" t="n">
         <v>2400000.0</v>
       </c>
       <c r="Y303" s="14" t="inlineStr"/>
       <c r="Z303" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.68E7</v>
       </c>
       <c r="AA303" s="14" t="inlineStr"/>
       <c r="AB303" s="14" t="inlineStr"/>
       <c r="AC303" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD303" s="15" t="inlineStr"/>
       <c r="AE303" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.2E7</v>
       </c>
       <c r="AF303" s="14" t="inlineStr"/>
       <c r="AG303" s="14" t="inlineStr"/>
@@ -18269,10 +18269,10 @@
       <c r="U304" s="14" t="inlineStr"/>
       <c r="V304" s="14" t="inlineStr"/>
       <c r="W304" s="14" t="n">
-        <v>1500000.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="X304" s="14" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y304" s="14" t="inlineStr"/>
       <c r="Z304" s="14" t="n">
@@ -18326,23 +18326,23 @@
       <c r="U305" s="14" t="inlineStr"/>
       <c r="V305" s="14" t="inlineStr"/>
       <c r="W305" s="14" t="n">
-        <v>1800000.0</v>
+        <v>2160000.0</v>
       </c>
       <c r="X305" s="14" t="n">
-        <v>360000.0</v>
+        <v>180000.0</v>
       </c>
       <c r="Y305" s="14" t="inlineStr"/>
       <c r="Z305" s="14" t="n">
-        <v>2160000.0</v>
+        <v>2340000.0</v>
       </c>
       <c r="AA305" s="14" t="inlineStr"/>
       <c r="AB305" s="14" t="inlineStr"/>
       <c r="AC305" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="AD305" s="15" t="inlineStr"/>
       <c r="AE305" s="14" t="n">
-        <v>2160000.0</v>
+        <v>1980000.0</v>
       </c>
       <c r="AF305" s="14" t="inlineStr"/>
       <c r="AG305" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>5.7092109652E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>3.331178713E9</v>
+        <v>3.516313013E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.0423288365E10</v>
+        <v>6.0608422665E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7107719062166219</v>
+        <v>0.7129496800994697</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.4587511635E10</v>
+        <v>2.4402377335E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -2446,20 +2446,20 @@
         <v>5.3560541612E10</v>
       </c>
       <c r="X33" s="14" t="n">
-        <v>2.829378713E9</v>
+        <v>3.014513013E9</v>
       </c>
       <c r="Y33" s="14" t="inlineStr"/>
       <c r="Z33" s="14" t="n">
-        <v>5.6389920325E10</v>
+        <v>5.6575054625E10</v>
       </c>
       <c r="AA33" s="14" t="inlineStr"/>
       <c r="AB33" s="14" t="inlineStr"/>
       <c r="AC33" s="15" t="n">
-        <v>0.7051837207526546</v>
+        <v>0.707498916336555</v>
       </c>
       <c r="AD33" s="15" t="inlineStr"/>
       <c r="AE33" s="14" t="n">
-        <v>2.3574943675E10</v>
+        <v>2.3389809375E10</v>
       </c>
       <c r="AF33" s="14" t="inlineStr"/>
       <c r="AG33" s="14" t="inlineStr"/>
@@ -2553,20 +2553,20 @@
         <v>5.3560541612E10</v>
       </c>
       <c r="X35" s="14" t="n">
-        <v>2.829378713E9</v>
+        <v>3.014513013E9</v>
       </c>
       <c r="Y35" s="14" t="inlineStr"/>
       <c r="Z35" s="14" t="n">
-        <v>5.6389920325E10</v>
+        <v>5.6575054625E10</v>
       </c>
       <c r="AA35" s="14" t="inlineStr"/>
       <c r="AB35" s="14" t="inlineStr"/>
       <c r="AC35" s="15" t="n">
-        <v>0.7051837207526546</v>
+        <v>0.707498916336555</v>
       </c>
       <c r="AD35" s="15" t="inlineStr"/>
       <c r="AE35" s="14" t="n">
-        <v>2.3574943675E10</v>
+        <v>2.3389809375E10</v>
       </c>
       <c r="AF35" s="14" t="inlineStr"/>
       <c r="AG35" s="14" t="inlineStr"/>
@@ -2616,20 +2616,20 @@
         <v>5.3559941612E10</v>
       </c>
       <c r="X36" s="17" t="n">
-        <v>2.829378713E9</v>
+        <v>3.014513013E9</v>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
       <c r="Z36" s="17" t="n">
-        <v>5.6389320325E10</v>
+        <v>5.6574454625E10</v>
       </c>
       <c r="AA36" s="17" t="inlineStr"/>
       <c r="AB36" s="17" t="inlineStr"/>
       <c r="AC36" s="18" t="n">
-        <v>0.7051815086424106</v>
+        <v>0.7074967215980379</v>
       </c>
       <c r="AD36" s="18" t="inlineStr"/>
       <c r="AE36" s="17" t="n">
-        <v>2.3574943675E10</v>
+        <v>2.3389809375E10</v>
       </c>
       <c r="AF36" s="17" t="inlineStr"/>
       <c r="AG36" s="17" t="inlineStr"/>
@@ -4736,20 +4736,20 @@
         <v>5.3549205512E10</v>
       </c>
       <c r="X71" s="22" t="n">
-        <v>2.829378713E9</v>
+        <v>3.014513013E9</v>
       </c>
       <c r="Y71" s="22" t="inlineStr"/>
       <c r="Z71" s="21" t="n">
-        <v>5.6378584225E10</v>
+        <v>5.6563718525E10</v>
       </c>
       <c r="AA71" s="21" t="inlineStr"/>
       <c r="AB71" s="21" t="inlineStr"/>
       <c r="AC71" s="23" t="n">
-        <v>0.7052106648367253</v>
+        <v>0.7075264144175598</v>
       </c>
       <c r="AD71" s="23" t="inlineStr"/>
       <c r="AE71" s="21" t="n">
-        <v>2.3567149775E10</v>
+        <v>2.3382015475E10</v>
       </c>
       <c r="AF71" s="21" t="inlineStr"/>
       <c r="AG71" s="21" t="inlineStr"/>
@@ -13865,20 +13865,20 @@
         <v>2.97538798E9</v>
       </c>
       <c r="X228" s="25" t="n">
-        <v>7.341E7</v>
+        <v>2.585443E8</v>
       </c>
       <c r="Y228" s="25" t="inlineStr"/>
       <c r="Z228" s="25" t="n">
-        <v>3.04879798E9</v>
+        <v>3.23393228E9</v>
       </c>
       <c r="AA228" s="25" t="inlineStr"/>
       <c r="AB228" s="25" t="inlineStr"/>
       <c r="AC228" s="26" t="n">
-        <v>0.5390598484485487</v>
+        <v>0.57179355804666</v>
       </c>
       <c r="AD228" s="26" t="inlineStr"/>
       <c r="AE228" s="25" t="n">
-        <v>2.60697102E9</v>
+        <v>2.42183672E9</v>
       </c>
       <c r="AF228" s="25" t="inlineStr"/>
       <c r="AG228" s="25" t="inlineStr"/>
@@ -13928,20 +13928,20 @@
         <v>2.088338999E9</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>6.35E7</v>
+        <v>2.479865E8</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>2.151838999E9</v>
+        <v>2.336325499E9</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.5539332457922893</v>
+        <v>0.601424347959947</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1.732815001E9</v>
+        <v>1.548328501E9</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -14642,20 +14642,20 @@
         <v>1.585270616E9</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>0.0</v>
+        <v>1.844865E8</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>1.585270616E9</v>
+        <v>1.769757116E9</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.5086802997524739</v>
+        <v>0.5678781724520109</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>1.531167384E9</v>
+        <v>1.346680884E9</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14927,20 +14927,20 @@
         <v>1.106919E9</v>
       </c>
       <c r="X246" s="14" t="n">
-        <v>0.0</v>
+        <v>1.844865E8</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>1.106919E9</v>
+        <v>1.2914055E9</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>1.106919E9</v>
+        <v>9.224325E8</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -14990,20 +14990,20 @@
         <v>4.32620013E8</v>
       </c>
       <c r="X247" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>4.32620013E8</v>
+        <v>4.33267813E8</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.4647829963472282</v>
+        <v>0.4654789568113451</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>4.98179987E8</v>
+        <v>4.97532187E8</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -15337,20 +15337,20 @@
         <v>2.48451E7</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>2.48451E7</v>
+        <v>2.54929E7</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.6274015151515151</v>
+        <v>0.6437601010101011</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>1.47549E7</v>
+        <v>1.41071E7</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15394,20 +15394,20 @@
         <v>2.48451E7</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>2.48451E7</v>
+        <v>2.54929E7</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.6274015151515151</v>
+        <v>0.6437601010101011</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>1.47549E7</v>
+        <v>1.41071E7</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>5.7092109652E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>3.516313013E9</v>
+        <v>3.567586124E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.0608422665E10</v>
+        <v>6.0659695776E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7129496800994697</v>
+        <v>0.7135528165362519</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.4402377335E10</v>
+        <v>2.4351104224E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -2446,20 +2446,20 @@
         <v>5.3560541612E10</v>
       </c>
       <c r="X33" s="14" t="n">
-        <v>3.014513013E9</v>
+        <v>3.065786124E9</v>
       </c>
       <c r="Y33" s="14" t="inlineStr"/>
       <c r="Z33" s="14" t="n">
-        <v>5.6575054625E10</v>
+        <v>5.6626327736E10</v>
       </c>
       <c r="AA33" s="14" t="inlineStr"/>
       <c r="AB33" s="14" t="inlineStr"/>
       <c r="AC33" s="15" t="n">
-        <v>0.707498916336555</v>
+        <v>0.7081401118371189</v>
       </c>
       <c r="AD33" s="15" t="inlineStr"/>
       <c r="AE33" s="14" t="n">
-        <v>2.3389809375E10</v>
+        <v>2.3338536264E10</v>
       </c>
       <c r="AF33" s="14" t="inlineStr"/>
       <c r="AG33" s="14" t="inlineStr"/>
@@ -2553,20 +2553,20 @@
         <v>5.3560541612E10</v>
       </c>
       <c r="X35" s="14" t="n">
-        <v>3.014513013E9</v>
+        <v>3.065786124E9</v>
       </c>
       <c r="Y35" s="14" t="inlineStr"/>
       <c r="Z35" s="14" t="n">
-        <v>5.6575054625E10</v>
+        <v>5.6626327736E10</v>
       </c>
       <c r="AA35" s="14" t="inlineStr"/>
       <c r="AB35" s="14" t="inlineStr"/>
       <c r="AC35" s="15" t="n">
-        <v>0.707498916336555</v>
+        <v>0.7081401118371189</v>
       </c>
       <c r="AD35" s="15" t="inlineStr"/>
       <c r="AE35" s="14" t="n">
-        <v>2.3389809375E10</v>
+        <v>2.3338536264E10</v>
       </c>
       <c r="AF35" s="14" t="inlineStr"/>
       <c r="AG35" s="14" t="inlineStr"/>
@@ -2616,20 +2616,20 @@
         <v>5.3559941612E10</v>
       </c>
       <c r="X36" s="17" t="n">
-        <v>3.014513013E9</v>
+        <v>3.065786124E9</v>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
       <c r="Z36" s="17" t="n">
-        <v>5.6574454625E10</v>
+        <v>5.6625727736E10</v>
       </c>
       <c r="AA36" s="17" t="inlineStr"/>
       <c r="AB36" s="17" t="inlineStr"/>
       <c r="AC36" s="18" t="n">
-        <v>0.7074967215980379</v>
+        <v>0.708137921909717</v>
       </c>
       <c r="AD36" s="18" t="inlineStr"/>
       <c r="AE36" s="17" t="n">
-        <v>2.3389809375E10</v>
+        <v>2.3338536264E10</v>
       </c>
       <c r="AF36" s="17" t="inlineStr"/>
       <c r="AG36" s="17" t="inlineStr"/>
@@ -4736,20 +4736,20 @@
         <v>5.3549205512E10</v>
       </c>
       <c r="X71" s="22" t="n">
-        <v>3.014513013E9</v>
+        <v>3.065786124E9</v>
       </c>
       <c r="Y71" s="22" t="inlineStr"/>
       <c r="Z71" s="21" t="n">
-        <v>5.6563718525E10</v>
+        <v>5.6614991636E10</v>
       </c>
       <c r="AA71" s="21" t="inlineStr"/>
       <c r="AB71" s="21" t="inlineStr"/>
       <c r="AC71" s="23" t="n">
-        <v>0.7075264144175598</v>
+        <v>0.7081677633480731</v>
       </c>
       <c r="AD71" s="23" t="inlineStr"/>
       <c r="AE71" s="21" t="n">
-        <v>2.3382015475E10</v>
+        <v>2.3330742364E10</v>
       </c>
       <c r="AF71" s="21" t="inlineStr"/>
       <c r="AG71" s="21" t="inlineStr"/>
@@ -13865,20 +13865,20 @@
         <v>2.97538798E9</v>
       </c>
       <c r="X228" s="25" t="n">
-        <v>2.585443E8</v>
+        <v>3.09817411E8</v>
       </c>
       <c r="Y228" s="25" t="inlineStr"/>
       <c r="Z228" s="25" t="n">
-        <v>3.23393228E9</v>
+        <v>3.285205391E9</v>
       </c>
       <c r="AA228" s="25" t="inlineStr"/>
       <c r="AB228" s="25" t="inlineStr"/>
       <c r="AC228" s="26" t="n">
-        <v>0.57179355804666</v>
+        <v>0.5808591883791576</v>
       </c>
       <c r="AD228" s="26" t="inlineStr"/>
       <c r="AE228" s="25" t="n">
-        <v>2.42183672E9</v>
+        <v>2.370563609E9</v>
       </c>
       <c r="AF228" s="25" t="inlineStr"/>
       <c r="AG228" s="25" t="inlineStr"/>
@@ -14990,20 +14990,20 @@
         <v>4.32620013E8</v>
       </c>
       <c r="X247" s="14" t="n">
-        <v>647800.0</v>
+        <v>5.1920911E7</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>4.33267813E8</v>
+        <v>4.84540924E8</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.4654789568113451</v>
+        <v>0.5205639492909325</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>4.97532187E8</v>
+        <v>4.46259076E8</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -15097,20 +15097,20 @@
         <v>3.10883859E8</v>
       </c>
       <c r="X249" s="14" t="n">
-        <v>0.0</v>
+        <v>4.1758847E7</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
-        <v>3.10883859E8</v>
+        <v>3.52642706E8</v>
       </c>
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.42470472540983606</v>
+        <v>0.4817523306010929</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>4.21116141E8</v>
+        <v>3.79357294E8</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15154,20 +15154,20 @@
         <v>3.10883859E8</v>
       </c>
       <c r="X250" s="14" t="n">
-        <v>0.0</v>
+        <v>4.1758847E7</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
-        <v>3.10883859E8</v>
+        <v>3.52642706E8</v>
       </c>
       <c r="AA250" s="14" t="inlineStr"/>
       <c r="AB250" s="14" t="inlineStr"/>
       <c r="AC250" s="15" t="n">
-        <v>0.42470472540983606</v>
+        <v>0.4817523306010929</v>
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>4.21116141E8</v>
+        <v>3.79357294E8</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15217,20 +15217,20 @@
         <v>4425348.0</v>
       </c>
       <c r="X251" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>4425348.0</v>
+        <v>4688862.0</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.9219475</v>
+        <v>0.97684625</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>374652.0</v>
+        <v>111138.0</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15274,20 +15274,20 @@
         <v>4425348.0</v>
       </c>
       <c r="X252" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>4425348.0</v>
+        <v>4688862.0</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.9219475</v>
+        <v>0.97684625</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>374652.0</v>
+        <v>111138.0</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15457,20 +15457,20 @@
         <v>9.2465706E7</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>9.2465706E7</v>
+        <v>1.01716456E8</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.5988711528497409</v>
+        <v>0.6587853367875648</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>6.1934294E7</v>
+        <v>5.2683544E7</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15514,20 +15514,20 @@
         <v>6.58569E7</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>6.58569E7</v>
+        <v>7.510765E7</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.5189669030732861</v>
+        <v>0.5918648542159181</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>6.10431E7</v>
+        <v>5.179235E7</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>5.7092109652E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>3.567586124E9</v>
+        <v>5.758858813E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.0659695776E10</v>
+        <v>6.2850968465E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7135528165362519</v>
+        <v>0.7393292201108566</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.4351104224E10</v>
+        <v>2.2159831535E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -2446,20 +2446,20 @@
         <v>5.3560541612E10</v>
       </c>
       <c r="X33" s="14" t="n">
-        <v>3.065786124E9</v>
+        <v>5.257058813E9</v>
       </c>
       <c r="Y33" s="14" t="inlineStr"/>
       <c r="Z33" s="14" t="n">
-        <v>5.6626327736E10</v>
+        <v>5.8817600425E10</v>
       </c>
       <c r="AA33" s="14" t="inlineStr"/>
       <c r="AB33" s="14" t="inlineStr"/>
       <c r="AC33" s="15" t="n">
-        <v>0.7081401118371189</v>
+        <v>0.7355430558226173</v>
       </c>
       <c r="AD33" s="15" t="inlineStr"/>
       <c r="AE33" s="14" t="n">
-        <v>2.3338536264E10</v>
+        <v>2.1147263575E10</v>
       </c>
       <c r="AF33" s="14" t="inlineStr"/>
       <c r="AG33" s="14" t="inlineStr"/>
@@ -2553,20 +2553,20 @@
         <v>5.3560541612E10</v>
       </c>
       <c r="X35" s="14" t="n">
-        <v>3.065786124E9</v>
+        <v>5.257058813E9</v>
       </c>
       <c r="Y35" s="14" t="inlineStr"/>
       <c r="Z35" s="14" t="n">
-        <v>5.6626327736E10</v>
+        <v>5.8817600425E10</v>
       </c>
       <c r="AA35" s="14" t="inlineStr"/>
       <c r="AB35" s="14" t="inlineStr"/>
       <c r="AC35" s="15" t="n">
-        <v>0.7081401118371189</v>
+        <v>0.7355430558226173</v>
       </c>
       <c r="AD35" s="15" t="inlineStr"/>
       <c r="AE35" s="14" t="n">
-        <v>2.3338536264E10</v>
+        <v>2.1147263575E10</v>
       </c>
       <c r="AF35" s="14" t="inlineStr"/>
       <c r="AG35" s="14" t="inlineStr"/>
@@ -2616,20 +2616,20 @@
         <v>5.3559941612E10</v>
       </c>
       <c r="X36" s="17" t="n">
-        <v>3.065786124E9</v>
+        <v>5.257058813E9</v>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
       <c r="Z36" s="17" t="n">
-        <v>5.6625727736E10</v>
+        <v>5.8817000425E10</v>
       </c>
       <c r="AA36" s="17" t="inlineStr"/>
       <c r="AB36" s="17" t="inlineStr"/>
       <c r="AC36" s="18" t="n">
-        <v>0.708137921909717</v>
+        <v>0.7355410715091432</v>
       </c>
       <c r="AD36" s="18" t="inlineStr"/>
       <c r="AE36" s="17" t="n">
-        <v>2.3338536264E10</v>
+        <v>2.1147263575E10</v>
       </c>
       <c r="AF36" s="17" t="inlineStr"/>
       <c r="AG36" s="17" t="inlineStr"/>
@@ -4736,20 +4736,20 @@
         <v>5.3549205512E10</v>
       </c>
       <c r="X71" s="22" t="n">
-        <v>3.065786124E9</v>
+        <v>5.257058813E9</v>
       </c>
       <c r="Y71" s="22" t="inlineStr"/>
       <c r="Z71" s="21" t="n">
-        <v>5.6614991636E10</v>
+        <v>5.8806264325E10</v>
       </c>
       <c r="AA71" s="21" t="inlineStr"/>
       <c r="AB71" s="21" t="inlineStr"/>
       <c r="AC71" s="23" t="n">
-        <v>0.7081677633480731</v>
+        <v>0.735577264510449</v>
       </c>
       <c r="AD71" s="23" t="inlineStr"/>
       <c r="AE71" s="21" t="n">
-        <v>2.3330742364E10</v>
+        <v>2.1139469675E10</v>
       </c>
       <c r="AF71" s="21" t="inlineStr"/>
       <c r="AG71" s="21" t="inlineStr"/>
@@ -4799,20 +4799,20 @@
         <v>5.0573817532E10</v>
       </c>
       <c r="X72" s="25" t="n">
-        <v>2.755968713E9</v>
+        <v>4.829393391E9</v>
       </c>
       <c r="Y72" s="25" t="inlineStr"/>
       <c r="Z72" s="25" t="n">
-        <v>5.3329786245E10</v>
+        <v>5.5403210923E10</v>
       </c>
       <c r="AA72" s="25" t="inlineStr"/>
       <c r="AB72" s="25" t="inlineStr"/>
       <c r="AC72" s="26" t="n">
-        <v>0.7178598919113772</v>
+        <v>0.7457697809253242</v>
       </c>
       <c r="AD72" s="26" t="inlineStr"/>
       <c r="AE72" s="25" t="n">
-        <v>2.0960178755E10</v>
+        <v>1.8886754077E10</v>
       </c>
       <c r="AF72" s="25" t="inlineStr"/>
       <c r="AG72" s="25" t="inlineStr"/>
@@ -4862,20 +4862,20 @@
         <v>3.798075364E9</v>
       </c>
       <c r="X73" s="14" t="n">
-        <v>3.8947414E8</v>
+        <v>4.2223914E8</v>
       </c>
       <c r="Y73" s="14" t="inlineStr"/>
       <c r="Z73" s="14" t="n">
-        <v>4.187549504E9</v>
+        <v>4.220314504E9</v>
       </c>
       <c r="AA73" s="14" t="inlineStr"/>
       <c r="AB73" s="14" t="inlineStr"/>
       <c r="AC73" s="15" t="n">
-        <v>0.6536032120530656</v>
+        <v>0.6587172552954111</v>
       </c>
       <c r="AD73" s="15" t="inlineStr"/>
       <c r="AE73" s="14" t="n">
-        <v>2.219318496E9</v>
+        <v>2.186553496E9</v>
       </c>
       <c r="AF73" s="14" t="inlineStr"/>
       <c r="AG73" s="14" t="inlineStr"/>
@@ -6841,20 +6841,20 @@
         <v>1.54008E8</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>0.0</v>
+        <v>3.2765E7</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
-        <v>1.54008E8</v>
+        <v>1.86773E8</v>
       </c>
       <c r="AA107" s="14" t="inlineStr"/>
       <c r="AB107" s="14" t="inlineStr"/>
       <c r="AC107" s="15" t="n">
-        <v>0.4913852515506547</v>
+        <v>0.5959268193072466</v>
       </c>
       <c r="AD107" s="15" t="inlineStr"/>
       <c r="AE107" s="14" t="n">
-        <v>1.59408E8</v>
+        <v>1.26643E8</v>
       </c>
       <c r="AF107" s="14" t="inlineStr"/>
       <c r="AG107" s="14" t="inlineStr"/>
@@ -6898,20 +6898,20 @@
         <v>9450000.0</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>0.0</v>
+        <v>1610000.0</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
-        <v>9450000.0</v>
+        <v>1.106E7</v>
       </c>
       <c r="AA108" s="14" t="inlineStr"/>
       <c r="AB108" s="14" t="inlineStr"/>
       <c r="AC108" s="15" t="n">
-        <v>0.3125</v>
+        <v>0.36574074074074076</v>
       </c>
       <c r="AD108" s="15" t="inlineStr"/>
       <c r="AE108" s="14" t="n">
-        <v>2.079E7</v>
+        <v>1.918E7</v>
       </c>
       <c r="AF108" s="14" t="inlineStr"/>
       <c r="AG108" s="14" t="inlineStr"/>
@@ -6955,20 +6955,20 @@
         <v>1.25985E8</v>
       </c>
       <c r="X109" s="14" t="n">
-        <v>0.0</v>
+        <v>2.6973E7</v>
       </c>
       <c r="Y109" s="14" t="inlineStr"/>
       <c r="Z109" s="14" t="n">
-        <v>1.25985E8</v>
+        <v>1.52958E8</v>
       </c>
       <c r="AA109" s="14" t="inlineStr"/>
       <c r="AB109" s="14" t="inlineStr"/>
       <c r="AC109" s="15" t="n">
-        <v>0.5085125448028673</v>
+        <v>0.6173835125448028</v>
       </c>
       <c r="AD109" s="15" t="inlineStr"/>
       <c r="AE109" s="14" t="n">
-        <v>1.21767E8</v>
+        <v>9.4794E7</v>
       </c>
       <c r="AF109" s="14" t="inlineStr"/>
       <c r="AG109" s="14" t="inlineStr"/>
@@ -7012,20 +7012,20 @@
         <v>1.8573E7</v>
       </c>
       <c r="X110" s="14" t="n">
-        <v>0.0</v>
+        <v>4182000.0</v>
       </c>
       <c r="Y110" s="14" t="inlineStr"/>
       <c r="Z110" s="14" t="n">
-        <v>1.8573E7</v>
+        <v>2.2755E7</v>
       </c>
       <c r="AA110" s="14" t="inlineStr"/>
       <c r="AB110" s="14" t="inlineStr"/>
       <c r="AC110" s="15" t="n">
-        <v>0.5243055555555556</v>
+        <v>0.6423611111111112</v>
       </c>
       <c r="AD110" s="15" t="inlineStr"/>
       <c r="AE110" s="14" t="n">
-        <v>1.6851E7</v>
+        <v>1.2669E7</v>
       </c>
       <c r="AF110" s="14" t="inlineStr"/>
       <c r="AG110" s="14" t="inlineStr"/>
@@ -9452,20 +9452,20 @@
         <v>3.3898086196E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>1.646912991E9</v>
+        <v>2.783675316E9</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
-        <v>3.5544999187E10</v>
+        <v>3.6681761512E10</v>
       </c>
       <c r="AA152" s="14" t="inlineStr"/>
       <c r="AB152" s="14" t="inlineStr"/>
       <c r="AC152" s="15" t="n">
-        <v>0.672068230837679</v>
+        <v>0.6935616015542294</v>
       </c>
       <c r="AD152" s="15" t="inlineStr"/>
       <c r="AE152" s="14" t="n">
-        <v>1.7343974813E10</v>
+        <v>1.6207212488E10</v>
       </c>
       <c r="AF152" s="14" t="inlineStr"/>
       <c r="AG152" s="14" t="inlineStr"/>
@@ -9515,20 +9515,20 @@
         <v>1.11880769E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>1.1951534E9</v>
+        <v>1.196301E9</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>1.23832303E10</v>
+        <v>1.23843779E10</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.9416393177101017</v>
+        <v>0.9417265829272401</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>7.674847E8</v>
+        <v>7.663371E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9572,20 +9572,20 @@
         <v>8.6973235E9</v>
       </c>
       <c r="X154" s="14" t="n">
-        <v>1.1951534E9</v>
+        <v>1.196301E9</v>
       </c>
       <c r="Y154" s="14" t="inlineStr"/>
       <c r="Z154" s="14" t="n">
-        <v>9.8924769E9</v>
+        <v>9.8936245E9</v>
       </c>
       <c r="AA154" s="14" t="inlineStr"/>
       <c r="AB154" s="14" t="inlineStr"/>
       <c r="AC154" s="15" t="n">
-        <v>0.933490665920816</v>
+        <v>0.9335989576963784</v>
       </c>
       <c r="AD154" s="15" t="inlineStr"/>
       <c r="AE154" s="14" t="n">
-        <v>7.048191E8</v>
+        <v>7.036715E8</v>
       </c>
       <c r="AF154" s="14" t="inlineStr"/>
       <c r="AG154" s="14" t="inlineStr"/>
@@ -9749,20 +9749,20 @@
         <v>152199.0</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>15915.0</v>
+        <v>15919.0</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
-        <v>168114.0</v>
+        <v>168118.0</v>
       </c>
       <c r="AA157" s="14" t="inlineStr"/>
       <c r="AB157" s="14" t="inlineStr"/>
       <c r="AC157" s="15" t="n">
-        <v>0.7063613445378151</v>
+        <v>0.7063781512605042</v>
       </c>
       <c r="AD157" s="15" t="inlineStr"/>
       <c r="AE157" s="14" t="n">
-        <v>69886.0</v>
+        <v>69882.0</v>
       </c>
       <c r="AF157" s="14" t="inlineStr"/>
       <c r="AG157" s="14" t="inlineStr"/>
@@ -9806,20 +9806,20 @@
         <v>118425.0</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>15915.0</v>
+        <v>15919.0</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
-        <v>134340.0</v>
+        <v>134344.0</v>
       </c>
       <c r="AA158" s="14" t="inlineStr"/>
       <c r="AB158" s="14" t="inlineStr"/>
       <c r="AC158" s="15" t="n">
-        <v>0.6585294117647059</v>
+        <v>0.6585490196078432</v>
       </c>
       <c r="AD158" s="15" t="inlineStr"/>
       <c r="AE158" s="14" t="n">
-        <v>69660.0</v>
+        <v>69656.0</v>
       </c>
       <c r="AF158" s="14" t="inlineStr"/>
       <c r="AG158" s="14" t="inlineStr"/>
@@ -9983,20 +9983,20 @@
         <v>8.786895E8</v>
       </c>
       <c r="X161" s="14" t="n">
-        <v>9.460116E7</v>
+        <v>9.469354E7</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
-        <v>9.7329066E8</v>
+        <v>9.7338304E8</v>
       </c>
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>0.7096282745798549</v>
+        <v>0.709695629032846</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>3.9825934E8</v>
+        <v>3.9816696E8</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -10040,20 +10040,20 @@
         <v>6.8370444E8</v>
       </c>
       <c r="X162" s="14" t="n">
-        <v>9.460116E7</v>
+        <v>9.469354E7</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
-        <v>7.783056E8</v>
+        <v>7.7839798E8</v>
       </c>
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>0.6618244897959183</v>
+        <v>0.6619030442176871</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>3.976944E8</v>
+        <v>3.9760202E8</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10217,20 +10217,20 @@
         <v>2.7256082E8</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>2.9746002E7</v>
+        <v>2.9760288E7</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
-        <v>3.02306822E8</v>
+        <v>3.02321108E8</v>
       </c>
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.6977540397500791</v>
+        <v>0.6977870132507957</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>1.30950178E8</v>
+        <v>1.30935892E8</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10274,20 +10274,20 @@
         <v>2.12169964E8</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>2.9746002E7</v>
+        <v>2.9760288E7</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
-        <v>2.41915966E8</v>
+        <v>2.41930252E8</v>
       </c>
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.6503117365591398</v>
+        <v>0.6503501397849463</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>1.30084034E8</v>
+        <v>1.30069748E8</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -11197,20 +11197,20 @@
         <v>1.249247E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>0.0</v>
+        <v>2.57121E8</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
-        <v>1.249247E9</v>
+        <v>1.506368E9</v>
       </c>
       <c r="AA182" s="14" t="inlineStr"/>
       <c r="AB182" s="14" t="inlineStr"/>
       <c r="AC182" s="15" t="n">
-        <v>0.47821654753811194</v>
+        <v>0.5766434534418658</v>
       </c>
       <c r="AD182" s="15" t="inlineStr"/>
       <c r="AE182" s="14" t="n">
-        <v>1.363057E9</v>
+        <v>1.105936E9</v>
       </c>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -11254,20 +11254,20 @@
         <v>1.09165E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>0.0</v>
+        <v>2.3555E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.09165E8</v>
+        <v>1.3272E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.4247004357298475</v>
+        <v>0.5163398692810458</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>1.47875E8</v>
+        <v>1.2432E8</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11311,20 +11311,20 @@
         <v>8.87112E8</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>0.0</v>
+        <v>1.84038E8</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>8.87112E8</v>
+        <v>1.07115E9</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.4911504424778761</v>
+        <v>0.5930432645034415</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>9.1908E8</v>
+        <v>7.35042E8</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11368,20 +11368,20 @@
         <v>2.5297E8</v>
       </c>
       <c r="X185" s="14" t="n">
-        <v>0.0</v>
+        <v>4.9528E7</v>
       </c>
       <c r="Y185" s="14" t="inlineStr"/>
       <c r="Z185" s="14" t="n">
-        <v>2.5297E8</v>
+        <v>3.02498E8</v>
       </c>
       <c r="AA185" s="14" t="inlineStr"/>
       <c r="AB185" s="14" t="inlineStr"/>
       <c r="AC185" s="15" t="n">
-        <v>0.46072281959378736</v>
+        <v>0.5509259259259259</v>
       </c>
       <c r="AD185" s="15" t="inlineStr"/>
       <c r="AE185" s="14" t="n">
-        <v>2.96102E8</v>
+        <v>2.46574E8</v>
       </c>
       <c r="AF185" s="14" t="inlineStr"/>
       <c r="AG185" s="14" t="inlineStr"/>
@@ -11665,20 +11665,20 @@
         <v>1.7062639415E10</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>0.0</v>
+        <v>8.78387055E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>1.7062639415E10</v>
+        <v>1.794102647E10</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.5642407213955026</v>
+        <v>0.5932879123677248</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>1.3177360585E10</v>
+        <v>1.229897353E10</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11722,20 +11722,20 @@
         <v>1.2285354215E10</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>0.0</v>
+        <v>8.78387055E8</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.2285354215E10</v>
+        <v>1.316374127E10</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.4833001392226193</v>
+        <v>0.5178554787385542</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>1.3134365785E10</v>
+        <v>1.225597873E10</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11899,20 +11899,20 @@
         <v>1.2877655972E10</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>7.19581582E8</v>
+        <v>1.623478935E9</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>1.3597237554E10</v>
+        <v>1.4501134907E10</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.9068459674637595</v>
+        <v>0.967129952818423</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>1.396750446E9</v>
+        <v>4.92853093E8</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -13410,20 +13410,20 @@
         <v>6.44264E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>0.0</v>
+        <v>1.38878E8</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>6.44264E8</v>
+        <v>7.83142E8</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.6347678726255221</v>
+        <v>0.7715988807440687</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>3.70696E8</v>
+        <v>2.31818E8</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13467,20 +13467,20 @@
         <v>6.181E7</v>
       </c>
       <c r="X221" s="14" t="n">
-        <v>0.0</v>
+        <v>1.33E7</v>
       </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="n">
-        <v>6.181E7</v>
+        <v>7.511E7</v>
       </c>
       <c r="AA221" s="14" t="inlineStr"/>
       <c r="AB221" s="14" t="inlineStr"/>
       <c r="AC221" s="15" t="n">
-        <v>0.566025641025641</v>
+        <v>0.6878205128205128</v>
       </c>
       <c r="AD221" s="15" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
-        <v>4.739E7</v>
+        <v>3.409E7</v>
       </c>
       <c r="AF221" s="14" t="inlineStr"/>
       <c r="AG221" s="14" t="inlineStr"/>
@@ -13568,20 +13568,20 @@
         <v>5.82454E8</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>0.0</v>
+        <v>1.25578E8</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>5.82454E8</v>
+        <v>7.08032E8</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.6430555555555556</v>
+        <v>0.7816993464052288</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>3.23306E8</v>
+        <v>1.97728E8</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13631,20 +13631,20 @@
         <v>5.981030439E9</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>0.0</v>
+        <v>7.65019353E8</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>5.981030439E9</v>
+        <v>6.746049792E9</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.7650068927013265</v>
+        <v>0.8628571016350164</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>1.837239561E9</v>
+        <v>1.072220208E9</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13688,20 +13688,20 @@
         <v>4.406587063E9</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>0.0</v>
+        <v>7.65019353E8</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>4.406587063E9</v>
+        <v>5.171606416E9</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.706183824198718</v>
+        <v>0.8287830794871794</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>1.833412937E9</v>
+        <v>1.068393584E9</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -13865,20 +13865,20 @@
         <v>2.97538798E9</v>
       </c>
       <c r="X228" s="25" t="n">
-        <v>3.09817411E8</v>
+        <v>4.27665422E8</v>
       </c>
       <c r="Y228" s="25" t="inlineStr"/>
       <c r="Z228" s="25" t="n">
-        <v>3.285205391E9</v>
+        <v>3.403053402E9</v>
       </c>
       <c r="AA228" s="25" t="inlineStr"/>
       <c r="AB228" s="25" t="inlineStr"/>
       <c r="AC228" s="26" t="n">
-        <v>0.5808591883791576</v>
+        <v>0.6016959677808623</v>
       </c>
       <c r="AD228" s="26" t="inlineStr"/>
       <c r="AE228" s="25" t="n">
-        <v>2.370563609E9</v>
+        <v>2.252715598E9</v>
       </c>
       <c r="AF228" s="25" t="inlineStr"/>
       <c r="AG228" s="25" t="inlineStr"/>
@@ -13928,20 +13928,20 @@
         <v>2.088338999E9</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>2.479865E8</v>
+        <v>3.23654936E8</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>2.336325499E9</v>
+        <v>2.411993935E9</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.601424347959947</v>
+        <v>0.6209031576557398</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1.548328501E9</v>
+        <v>1.472660065E9</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13991,20 +13991,20 @@
         <v>4.83128803E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>6.35E7</v>
+        <v>6.5517E7</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>5.46628803E8</v>
+        <v>5.48645803E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.7439991221109624</v>
+        <v>0.7467443968221777</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>1.88088197E8</v>
+        <v>1.86071197E8</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14162,20 +14162,20 @@
         <v>3.2709603E7</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>0.0</v>
+        <v>2017000.0</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>3.2709603E7</v>
+        <v>3.4726603E7</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.6339070348837209</v>
+        <v>0.6729961821705427</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>1.8890397E7</v>
+        <v>1.6873397E7</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14225,20 +14225,20 @@
         <v>5144000.0</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>0.0</v>
+        <v>222500.0</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>5144000.0</v>
+        <v>5366500.0</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.3956923076923077</v>
+        <v>0.4128076923076923</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>7856000.0</v>
+        <v>7633500.0</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14282,20 +14282,20 @@
         <v>2720000.0</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>0.0</v>
+        <v>222500.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>2720000.0</v>
+        <v>2942500.0</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.4689655172413793</v>
+        <v>0.5073275862068966</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>3080000.0</v>
+        <v>2857500.0</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14402,20 +14402,20 @@
         <v>1.280558E7</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>0.0</v>
+        <v>4279000.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>1.280558E7</v>
+        <v>1.708458E7</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.73178924509972</v>
+        <v>0.9763175038573633</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>4693420.0</v>
+        <v>414420.0</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14459,20 +14459,20 @@
         <v>1.280558E7</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>0.0</v>
+        <v>4279000.0</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>1.280558E7</v>
+        <v>1.708458E7</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.73178924509972</v>
+        <v>0.9763175038573633</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>4693420.0</v>
+        <v>414420.0</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -14642,20 +14642,20 @@
         <v>1.585270616E9</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>2.53636436E8</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>1.769757116E9</v>
+        <v>1.838907052E9</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.5678781724520109</v>
+        <v>0.5900669456603982</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>1.346680884E9</v>
+        <v>1.277530948E9</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14699,20 +14699,20 @@
         <v>2.85881376E8</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>0.0</v>
+        <v>4.1321696E7</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>2.85881376E8</v>
+        <v>3.27203072E8</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.5294099555555556</v>
+        <v>0.6059316148148148</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>2.54118624E8</v>
+        <v>2.12796928E8</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14756,20 +14756,20 @@
         <v>6.5444768E7</v>
       </c>
       <c r="X243" s="14" t="n">
-        <v>0.0</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>6.5444768E7</v>
+        <v>7.4913296E7</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.5338072430668842</v>
+        <v>0.6110383034257749</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>5.7155232E7</v>
+        <v>4.7686704E7</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14813,20 +14813,20 @@
         <v>9.5029104E7</v>
       </c>
       <c r="X244" s="14" t="n">
-        <v>0.0</v>
+        <v>1.3729784E7</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>9.5029104E7</v>
+        <v>1.08758888E8</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.5279394666666667</v>
+        <v>0.6042160444444444</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>8.4970896E7</v>
+        <v>7.1241112E7</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14870,20 +14870,20 @@
         <v>3.1996368E7</v>
       </c>
       <c r="X245" s="14" t="n">
-        <v>0.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>3.1996368E7</v>
+        <v>3.6626296E7</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.5332728</v>
+        <v>0.6104382666666667</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>2.8003632E7</v>
+        <v>2.3373704E7</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -15634,20 +15634,20 @@
         <v>3.84588968E8</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>0.0</v>
+        <v>4.2179575E7</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>3.84588968E8</v>
+        <v>4.26768543E8</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.543101199630014</v>
+        <v>0.6026655129318562</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>3.23546032E8</v>
+        <v>2.81366457E8</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15697,20 +15697,20 @@
         <v>9.9195E7</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>0.0</v>
+        <v>3.474E7</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>9.9195E7</v>
+        <v>1.33935E8</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.495975</v>
+        <v>0.669675</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>1.00805E8</v>
+        <v>6.6065E7</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15754,20 +15754,20 @@
         <v>8.8315E7</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5625E7</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>8.8315E7</v>
+        <v>1.1394E8</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.4906388888888889</v>
+        <v>0.633</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>9.1685E7</v>
+        <v>6.606E7</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15811,20 +15811,20 @@
         <v>1.088E7</v>
       </c>
       <c r="X261" s="14" t="n">
-        <v>0.0</v>
+        <v>9115000.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>1.088E7</v>
+        <v>1.9995E7</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.544</v>
+        <v>0.99975</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>9120000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15994,20 +15994,20 @@
         <v>1.10331326E8</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>1.10331326E8</v>
+        <v>1.11081326E8</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.5574682363640957</v>
+        <v>0.5612577419599323</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>8.7583674E7</v>
+        <v>8.6833674E7</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -16108,20 +16108,20 @@
         <v>1.1156299E7</v>
       </c>
       <c r="X266" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>1.1156299E7</v>
+        <v>1.1906299E7</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.7083364444444444</v>
+        <v>0.7559554920634921</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>4593701.0</v>
+        <v>3843701.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16842,20 +16842,20 @@
         <v>8.8386927E7</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>0.0</v>
+        <v>6689575.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>8.8386927E7</v>
+        <v>9.5076502E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>0.43356679584028257</v>
+        <v>0.4663813499460414</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>1.15473073E8</v>
+        <v>1.08783498E8</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
@@ -16899,20 +16899,20 @@
         <v>4080000.0</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>0.0</v>
+        <v>4845000.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>4080000.0</v>
+        <v>8925000.0</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
       <c r="AC280" s="15" t="n">
-        <v>0.3813084112149533</v>
+        <v>0.8341121495327103</v>
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
-        <v>6620000.0</v>
+        <v>1775000.0</v>
       </c>
       <c r="AF280" s="14" t="inlineStr"/>
       <c r="AG280" s="14" t="inlineStr"/>
@@ -17070,20 +17070,20 @@
         <v>6.6116077E7</v>
       </c>
       <c r="X283" s="14" t="n">
-        <v>0.0</v>
+        <v>1225000.0</v>
       </c>
       <c r="Y283" s="14" t="inlineStr"/>
       <c r="Z283" s="14" t="n">
-        <v>6.6116077E7</v>
+        <v>6.7341077E7</v>
       </c>
       <c r="AA283" s="14" t="inlineStr"/>
       <c r="AB283" s="14" t="inlineStr"/>
       <c r="AC283" s="15" t="n">
-        <v>0.530626621187801</v>
+        <v>0.5404580818619583</v>
       </c>
       <c r="AD283" s="15" t="inlineStr"/>
       <c r="AE283" s="14" t="n">
-        <v>5.8483923E7</v>
+        <v>5.7258923E7</v>
       </c>
       <c r="AF283" s="14" t="inlineStr"/>
       <c r="AG283" s="14" t="inlineStr"/>
@@ -17127,20 +17127,20 @@
         <v>2177000.0</v>
       </c>
       <c r="X284" s="14" t="n">
-        <v>0.0</v>
+        <v>233875.0</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
-        <v>2177000.0</v>
+        <v>2410875.0</v>
       </c>
       <c r="AA284" s="14" t="inlineStr"/>
       <c r="AB284" s="14" t="inlineStr"/>
       <c r="AC284" s="15" t="n">
-        <v>0.7256666666666667</v>
+        <v>0.803625</v>
       </c>
       <c r="AD284" s="15" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
-        <v>823000.0</v>
+        <v>589125.0</v>
       </c>
       <c r="AF284" s="14" t="inlineStr"/>
       <c r="AG284" s="14" t="inlineStr"/>
@@ -17355,20 +17355,20 @@
         <v>3707013.0</v>
       </c>
       <c r="X288" s="14" t="n">
-        <v>0.0</v>
+        <v>385700.0</v>
       </c>
       <c r="Y288" s="14" t="inlineStr"/>
       <c r="Z288" s="14" t="n">
-        <v>3707013.0</v>
+        <v>4092713.0</v>
       </c>
       <c r="AA288" s="14" t="inlineStr"/>
       <c r="AB288" s="14" t="inlineStr"/>
       <c r="AC288" s="15" t="n">
-        <v>0.3707013</v>
+        <v>0.4092713</v>
       </c>
       <c r="AD288" s="15" t="inlineStr"/>
       <c r="AE288" s="14" t="n">
-        <v>6292987.0</v>
+        <v>5907287.0</v>
       </c>
       <c r="AF288" s="14" t="inlineStr"/>
       <c r="AG288" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -601,7 +601,7 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Periode September 2025</t>
+            <t xml:space="preserve">Periode Oktober 2025</t>
           </r>
         </is>
       </c>
@@ -979,22 +979,22 @@
       <c r="U9" s="10" t="inlineStr"/>
       <c r="V9" s="10" t="inlineStr"/>
       <c r="W9" s="11" t="n">
-        <v>6.3951573791E10</v>
+        <v>7.0705642047E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>4.054400085E9</v>
+        <v>4.001499962E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.8005973876E10</v>
+        <v>7.4707142009E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7999686378201358</v>
+        <v>0.8787958942746098</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.7004826124E10</v>
+        <v>1.0303657991E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1711,23 +1711,23 @@
       <c r="U21" s="14" t="inlineStr"/>
       <c r="V21" s="14" t="inlineStr"/>
       <c r="W21" s="14" t="n">
-        <v>5.9918205751E10</v>
+        <v>6.6672274007E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>4.054400085E9</v>
+        <v>4.001499962E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>6.3972605836E10</v>
+        <v>7.0673773969E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.7900056785720461</v>
+        <v>0.8727592386147246</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.7004794164E10</v>
+        <v>1.0303626031E10</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1774,23 +1774,23 @@
       <c r="U22" s="14" t="inlineStr"/>
       <c r="V22" s="14" t="inlineStr"/>
       <c r="W22" s="14" t="n">
-        <v>5.9918205751E10</v>
+        <v>6.6672274007E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>4.054400085E9</v>
+        <v>4.001499962E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>6.3972605836E10</v>
+        <v>7.0673773969E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.7900056785720461</v>
+        <v>0.8727592386147246</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.7004794164E10</v>
+        <v>1.0303626031E10</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1837,23 +1837,23 @@
       <c r="U23" s="17" t="inlineStr"/>
       <c r="V23" s="17" t="inlineStr"/>
       <c r="W23" s="17" t="n">
-        <v>5.9917605751E10</v>
+        <v>6.6671674007E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>4.054400085E9</v>
+        <v>4.001499962E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>6.3972005836E10</v>
+        <v>7.0673173969E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.7900041226128965</v>
+        <v>0.8727582958205313</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.7004794164E10</v>
+        <v>1.0303626031E10</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
       <c r="U35" s="21" t="inlineStr"/>
       <c r="V35" s="21" t="inlineStr"/>
       <c r="W35" s="22" t="n">
-        <v>9686100.0</v>
+        <v>1.3716552E7</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>4030452.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
@@ -2625,10 +2625,10 @@
       <c r="U36" s="25" t="inlineStr"/>
       <c r="V36" s="25" t="inlineStr"/>
       <c r="W36" s="25" t="n">
-        <v>9686100.0</v>
+        <v>1.3716552E7</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>4030452.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
@@ -2991,10 +2991,10 @@
       <c r="U42" s="14" t="inlineStr"/>
       <c r="V42" s="14" t="inlineStr"/>
       <c r="W42" s="14" t="n">
-        <v>7286100.0</v>
+        <v>1.1316552E7</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>4030452.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
@@ -3054,10 +3054,10 @@
       <c r="U43" s="14" t="inlineStr"/>
       <c r="V43" s="14" t="inlineStr"/>
       <c r="W43" s="14" t="n">
-        <v>7286100.0</v>
+        <v>1.1316552E7</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>4030452.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
@@ -3111,10 +3111,10 @@
       <c r="U44" s="14" t="inlineStr"/>
       <c r="V44" s="14" t="inlineStr"/>
       <c r="W44" s="14" t="n">
-        <v>6537000.0</v>
+        <v>1.0567452E7</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>4030452.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
@@ -3231,23 +3231,23 @@
       <c r="U46" s="21" t="inlineStr"/>
       <c r="V46" s="21" t="inlineStr"/>
       <c r="W46" s="22" t="n">
-        <v>5.9906869651E10</v>
+        <v>6.6656907455E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>4.050369633E9</v>
+        <v>4.001499962E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>6.3957239284E10</v>
+        <v>7.0658407417E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.7900025443231433</v>
+        <v>0.8727756585831195</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.7001030716E10</v>
+        <v>1.0299862583E10</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3294,23 +3294,23 @@
       <c r="U47" s="25" t="inlineStr"/>
       <c r="V47" s="25" t="inlineStr"/>
       <c r="W47" s="25" t="n">
-        <v>5.6497747649E10</v>
+        <v>6.2301898661E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>3.119733104E9</v>
+        <v>3.101785341E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>5.9617480753E10</v>
+        <v>6.5403684002E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.8024970903270717</v>
+        <v>0.8803838311405854</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.4672484247E10</v>
+        <v>8.886280998E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3357,23 +3357,23 @@
       <c r="U48" s="14" t="inlineStr"/>
       <c r="V48" s="14" t="inlineStr"/>
       <c r="W48" s="14" t="n">
-        <v>4.220314504E9</v>
+        <v>4.638429667E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>4.18115163E8</v>
+        <v>4.13430911E8</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>4.638429667E9</v>
+        <v>5.051860578E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.7239777168813217</v>
+        <v>0.788507048685879</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>1.768438333E9</v>
+        <v>1.355007422E9</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -3420,23 +3420,23 @@
       <c r="U49" s="14" t="inlineStr"/>
       <c r="V49" s="14" t="inlineStr"/>
       <c r="W49" s="14" t="n">
-        <v>1.6503171E9</v>
+        <v>1.8149987E9</v>
       </c>
       <c r="X49" s="14" t="n">
         <v>1.646816E8</v>
       </c>
       <c r="Y49" s="14" t="inlineStr"/>
       <c r="Z49" s="14" t="n">
-        <v>1.8149987E9</v>
+        <v>1.9796803E9</v>
       </c>
       <c r="AA49" s="14" t="inlineStr"/>
       <c r="AB49" s="14" t="inlineStr"/>
       <c r="AC49" s="15" t="n">
-        <v>0.6476568365491392</v>
+        <v>0.7064211563769444</v>
       </c>
       <c r="AD49" s="15" t="inlineStr"/>
       <c r="AE49" s="14" t="n">
-        <v>9.874093E8</v>
+        <v>8.227277E8</v>
       </c>
       <c r="AF49" s="14" t="inlineStr"/>
       <c r="AG49" s="14" t="inlineStr"/>
@@ -3477,23 +3477,23 @@
       <c r="U50" s="14" t="inlineStr"/>
       <c r="V50" s="14" t="inlineStr"/>
       <c r="W50" s="14" t="n">
-        <v>1.3201367E9</v>
+        <v>1.4848183E9</v>
       </c>
       <c r="X50" s="14" t="n">
         <v>1.646816E8</v>
       </c>
       <c r="Y50" s="14" t="inlineStr"/>
       <c r="Z50" s="14" t="n">
-        <v>1.4848183E9</v>
+        <v>1.6494999E9</v>
       </c>
       <c r="AA50" s="14" t="inlineStr"/>
       <c r="AB50" s="14" t="inlineStr"/>
       <c r="AC50" s="15" t="n">
-        <v>0.6006021723020966</v>
+        <v>0.6672151219796328</v>
       </c>
       <c r="AD50" s="15" t="inlineStr"/>
       <c r="AE50" s="14" t="n">
-        <v>9.873977E8</v>
+        <v>8.227161E8</v>
       </c>
       <c r="AF50" s="14" t="inlineStr"/>
       <c r="AG50" s="14" t="inlineStr"/>
@@ -3654,23 +3654,23 @@
       <c r="U53" s="14" t="inlineStr"/>
       <c r="V53" s="14" t="inlineStr"/>
       <c r="W53" s="14" t="n">
-        <v>19549.0</v>
+        <v>21374.0</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>1825.0</v>
+        <v>1875.0</v>
       </c>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="n">
-        <v>21374.0</v>
+        <v>23249.0</v>
       </c>
       <c r="AA53" s="14" t="inlineStr"/>
       <c r="AB53" s="14" t="inlineStr"/>
       <c r="AC53" s="15" t="n">
-        <v>0.7124666666666667</v>
+        <v>0.7749666666666667</v>
       </c>
       <c r="AD53" s="15" t="inlineStr"/>
       <c r="AE53" s="14" t="n">
-        <v>8626.0</v>
+        <v>6751.0</v>
       </c>
       <c r="AF53" s="14" t="inlineStr"/>
       <c r="AG53" s="14" t="inlineStr"/>
@@ -3711,23 +3711,23 @@
       <c r="U54" s="14" t="inlineStr"/>
       <c r="V54" s="14" t="inlineStr"/>
       <c r="W54" s="14" t="n">
-        <v>14967.0</v>
+        <v>16792.0</v>
       </c>
       <c r="X54" s="14" t="n">
-        <v>1825.0</v>
+        <v>1875.0</v>
       </c>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="n">
-        <v>16792.0</v>
+        <v>18667.0</v>
       </c>
       <c r="AA54" s="14" t="inlineStr"/>
       <c r="AB54" s="14" t="inlineStr"/>
       <c r="AC54" s="15" t="n">
-        <v>0.6996666666666667</v>
+        <v>0.7777916666666667</v>
       </c>
       <c r="AD54" s="15" t="inlineStr"/>
       <c r="AE54" s="14" t="n">
-        <v>7208.0</v>
+        <v>5333.0</v>
       </c>
       <c r="AF54" s="14" t="inlineStr"/>
       <c r="AG54" s="14" t="inlineStr"/>
@@ -3888,23 +3888,23 @@
       <c r="U57" s="14" t="inlineStr"/>
       <c r="V57" s="14" t="inlineStr"/>
       <c r="W57" s="14" t="n">
-        <v>1.2585432E8</v>
+        <v>1.3838814E8</v>
       </c>
       <c r="X57" s="14" t="n">
         <v>1.253382E7</v>
       </c>
       <c r="Y57" s="14" t="inlineStr"/>
       <c r="Z57" s="14" t="n">
-        <v>1.3838814E8</v>
+        <v>1.5092196E8</v>
       </c>
       <c r="AA57" s="14" t="inlineStr"/>
       <c r="AB57" s="14" t="inlineStr"/>
       <c r="AC57" s="15" t="n">
-        <v>0.7603743956043956</v>
+        <v>0.8292415384615385</v>
       </c>
       <c r="AD57" s="15" t="inlineStr"/>
       <c r="AE57" s="14" t="n">
-        <v>4.361186E7</v>
+        <v>3.107804E7</v>
       </c>
       <c r="AF57" s="14" t="inlineStr"/>
       <c r="AG57" s="14" t="inlineStr"/>
@@ -3945,23 +3945,23 @@
       <c r="U58" s="14" t="inlineStr"/>
       <c r="V58" s="14" t="inlineStr"/>
       <c r="W58" s="14" t="n">
-        <v>1.00656E8</v>
+        <v>1.1318982E8</v>
       </c>
       <c r="X58" s="14" t="n">
         <v>1.253382E7</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
-        <v>1.1318982E8</v>
+        <v>1.2572364E8</v>
       </c>
       <c r="AA58" s="14" t="inlineStr"/>
       <c r="AB58" s="14" t="inlineStr"/>
       <c r="AC58" s="15" t="n">
-        <v>0.7219106842185826</v>
+        <v>0.8018498392775142</v>
       </c>
       <c r="AD58" s="15" t="inlineStr"/>
       <c r="AE58" s="14" t="n">
-        <v>4.360218E7</v>
+        <v>3.106836E7</v>
       </c>
       <c r="AF58" s="14" t="inlineStr"/>
       <c r="AG58" s="14" t="inlineStr"/>
@@ -4166,23 +4166,23 @@
       <c r="U62" s="14" t="inlineStr"/>
       <c r="V62" s="14" t="inlineStr"/>
       <c r="W62" s="14" t="n">
-        <v>3.8237084E7</v>
+        <v>4.2035848E7</v>
       </c>
       <c r="X62" s="14" t="n">
         <v>3798764.0</v>
       </c>
       <c r="Y62" s="14" t="inlineStr"/>
       <c r="Z62" s="14" t="n">
-        <v>4.2035848E7</v>
+        <v>4.5834612E7</v>
       </c>
       <c r="AA62" s="14" t="inlineStr"/>
       <c r="AB62" s="14" t="inlineStr"/>
       <c r="AC62" s="15" t="n">
-        <v>0.7506401428571429</v>
+        <v>0.8184752142857142</v>
       </c>
       <c r="AD62" s="15" t="inlineStr"/>
       <c r="AE62" s="14" t="n">
-        <v>1.3964152E7</v>
+        <v>1.0165388E7</v>
       </c>
       <c r="AF62" s="14" t="inlineStr"/>
       <c r="AG62" s="14" t="inlineStr"/>
@@ -4223,23 +4223,23 @@
       <c r="U63" s="14" t="inlineStr"/>
       <c r="V63" s="14" t="inlineStr"/>
       <c r="W63" s="14" t="n">
-        <v>3.0561026E7</v>
+        <v>3.435979E7</v>
       </c>
       <c r="X63" s="14" t="n">
         <v>3798764.0</v>
       </c>
       <c r="Y63" s="14" t="inlineStr"/>
       <c r="Z63" s="14" t="n">
-        <v>3.435979E7</v>
+        <v>3.8158554E7</v>
       </c>
       <c r="AA63" s="14" t="inlineStr"/>
       <c r="AB63" s="14" t="inlineStr"/>
       <c r="AC63" s="15" t="n">
-        <v>0.7112061185626759</v>
+        <v>0.7898359413810233</v>
       </c>
       <c r="AD63" s="15" t="inlineStr"/>
       <c r="AE63" s="14" t="n">
-        <v>1.395221E7</v>
+        <v>1.0153446E7</v>
       </c>
       <c r="AF63" s="14" t="inlineStr"/>
       <c r="AG63" s="14" t="inlineStr"/>
@@ -4400,23 +4400,23 @@
       <c r="U66" s="14" t="inlineStr"/>
       <c r="V66" s="14" t="inlineStr"/>
       <c r="W66" s="14" t="n">
-        <v>1.8E7</v>
+        <v>1.98E7</v>
       </c>
       <c r="X66" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
-        <v>1.98E7</v>
+        <v>2.16E7</v>
       </c>
       <c r="AA66" s="14" t="inlineStr"/>
       <c r="AB66" s="14" t="inlineStr"/>
       <c r="AC66" s="15" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AD66" s="15" t="inlineStr"/>
       <c r="AE66" s="14" t="n">
-        <v>5400000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="AF66" s="14" t="inlineStr"/>
       <c r="AG66" s="14" t="inlineStr"/>
@@ -4457,23 +4457,23 @@
       <c r="U67" s="14" t="inlineStr"/>
       <c r="V67" s="14" t="inlineStr"/>
       <c r="W67" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.62E7</v>
       </c>
       <c r="X67" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="n">
-        <v>1.62E7</v>
+        <v>1.8E7</v>
       </c>
       <c r="AA67" s="14" t="inlineStr"/>
       <c r="AB67" s="14" t="inlineStr"/>
       <c r="AC67" s="15" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AD67" s="15" t="inlineStr"/>
       <c r="AE67" s="14" t="n">
-        <v>5400000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="AF67" s="14" t="inlineStr"/>
       <c r="AG67" s="14" t="inlineStr"/>
@@ -4634,23 +4634,23 @@
       <c r="U70" s="14" t="inlineStr"/>
       <c r="V70" s="14" t="inlineStr"/>
       <c r="W70" s="14" t="n">
-        <v>1.1796E8</v>
+        <v>1.28894E8</v>
       </c>
       <c r="X70" s="14" t="n">
-        <v>1.0934E7</v>
+        <v>1.0394E7</v>
       </c>
       <c r="Y70" s="14" t="inlineStr"/>
       <c r="Z70" s="14" t="n">
-        <v>1.28894E8</v>
+        <v>1.39288E8</v>
       </c>
       <c r="AA70" s="14" t="inlineStr"/>
       <c r="AB70" s="14" t="inlineStr"/>
       <c r="AC70" s="15" t="n">
-        <v>0.8888383190588495</v>
+        <v>0.9605141572537824</v>
       </c>
       <c r="AD70" s="15" t="inlineStr"/>
       <c r="AE70" s="14" t="n">
-        <v>1.612E7</v>
+        <v>5726000.0</v>
       </c>
       <c r="AF70" s="14" t="inlineStr"/>
       <c r="AG70" s="14" t="inlineStr"/>
@@ -4691,23 +4691,23 @@
       <c r="U71" s="14" t="inlineStr"/>
       <c r="V71" s="14" t="inlineStr"/>
       <c r="W71" s="14" t="n">
-        <v>9.3932E7</v>
+        <v>1.04866E8</v>
       </c>
       <c r="X71" s="14" t="n">
-        <v>1.0934E7</v>
+        <v>1.0394E7</v>
       </c>
       <c r="Y71" s="14" t="inlineStr"/>
       <c r="Z71" s="14" t="n">
-        <v>1.04866E8</v>
+        <v>1.1526E8</v>
       </c>
       <c r="AA71" s="14" t="inlineStr"/>
       <c r="AB71" s="14" t="inlineStr"/>
       <c r="AC71" s="15" t="n">
-        <v>0.8667757720029095</v>
+        <v>0.9526879587383456</v>
       </c>
       <c r="AD71" s="15" t="inlineStr"/>
       <c r="AE71" s="14" t="n">
-        <v>1.6118E7</v>
+        <v>5724000.0</v>
       </c>
       <c r="AF71" s="14" t="inlineStr"/>
       <c r="AG71" s="14" t="inlineStr"/>
@@ -4868,23 +4868,23 @@
       <c r="U74" s="14" t="inlineStr"/>
       <c r="V74" s="14" t="inlineStr"/>
       <c r="W74" s="14" t="n">
-        <v>1.9384414E7</v>
+        <v>1.9581584E7</v>
       </c>
       <c r="X74" s="14" t="n">
         <v>197170.0</v>
       </c>
       <c r="Y74" s="14" t="inlineStr"/>
       <c r="Z74" s="14" t="n">
-        <v>1.9581584E7</v>
+        <v>1.9778754E7</v>
       </c>
       <c r="AA74" s="14" t="inlineStr"/>
       <c r="AB74" s="14" t="inlineStr"/>
       <c r="AC74" s="15" t="n">
-        <v>0.9889688888888889</v>
+        <v>0.9989269696969697</v>
       </c>
       <c r="AD74" s="15" t="inlineStr"/>
       <c r="AE74" s="14" t="n">
-        <v>218416.0</v>
+        <v>21246.0</v>
       </c>
       <c r="AF74" s="14" t="inlineStr"/>
       <c r="AG74" s="14" t="inlineStr"/>
@@ -4925,23 +4925,23 @@
       <c r="U75" s="14" t="inlineStr"/>
       <c r="V75" s="14" t="inlineStr"/>
       <c r="W75" s="14" t="n">
-        <v>1853398.0</v>
+        <v>2050568.0</v>
       </c>
       <c r="X75" s="14" t="n">
         <v>197170.0</v>
       </c>
       <c r="Y75" s="14" t="inlineStr"/>
       <c r="Z75" s="14" t="n">
-        <v>2050568.0</v>
+        <v>2247738.0</v>
       </c>
       <c r="AA75" s="14" t="inlineStr"/>
       <c r="AB75" s="14" t="inlineStr"/>
       <c r="AC75" s="15" t="n">
-        <v>0.9089397163120567</v>
+        <v>0.9963377659574468</v>
       </c>
       <c r="AD75" s="15" t="inlineStr"/>
       <c r="AE75" s="14" t="n">
-        <v>205432.0</v>
+        <v>8262.0</v>
       </c>
       <c r="AF75" s="14" t="inlineStr"/>
       <c r="AG75" s="14" t="inlineStr"/>
@@ -5102,23 +5102,23 @@
       <c r="U78" s="14" t="inlineStr"/>
       <c r="V78" s="14" t="inlineStr"/>
       <c r="W78" s="14" t="n">
-        <v>8.72661E7</v>
+        <v>9.588408E7</v>
       </c>
       <c r="X78" s="14" t="n">
         <v>8617980.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
-        <v>9.588408E7</v>
+        <v>1.0450206E8</v>
       </c>
       <c r="AA78" s="14" t="inlineStr"/>
       <c r="AB78" s="14" t="inlineStr"/>
       <c r="AC78" s="15" t="n">
-        <v>0.7609847619047619</v>
+        <v>0.8293814285714286</v>
       </c>
       <c r="AD78" s="15" t="inlineStr"/>
       <c r="AE78" s="14" t="n">
-        <v>3.011592E7</v>
+        <v>2.149794E7</v>
       </c>
       <c r="AF78" s="14" t="inlineStr"/>
       <c r="AG78" s="14" t="inlineStr"/>
@@ -5159,23 +5159,23 @@
       <c r="U79" s="14" t="inlineStr"/>
       <c r="V79" s="14" t="inlineStr"/>
       <c r="W79" s="14" t="n">
-        <v>6.974046E7</v>
+        <v>7.835844E7</v>
       </c>
       <c r="X79" s="14" t="n">
         <v>8617980.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
-        <v>7.835844E7</v>
+        <v>8.697642E7</v>
       </c>
       <c r="AA79" s="14" t="inlineStr"/>
       <c r="AB79" s="14" t="inlineStr"/>
       <c r="AC79" s="15" t="n">
-        <v>0.7224106648965594</v>
+        <v>0.8018624847881403</v>
       </c>
       <c r="AD79" s="15" t="inlineStr"/>
       <c r="AE79" s="14" t="n">
-        <v>3.010956E7</v>
+        <v>2.149158E7</v>
       </c>
       <c r="AF79" s="14" t="inlineStr"/>
       <c r="AG79" s="14" t="inlineStr"/>
@@ -5336,23 +5336,23 @@
       <c r="U82" s="14" t="inlineStr"/>
       <c r="V82" s="14" t="inlineStr"/>
       <c r="W82" s="14" t="n">
-        <v>1.86773E8</v>
+        <v>2.15481E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>2.8708E7</v>
+        <v>3.0512E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>2.15481E8</v>
+        <v>2.45993E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.6875239298568038</v>
+        <v>0.784876968629553</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>9.7935E7</v>
+        <v>6.7423E7</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5393,23 +5393,23 @@
       <c r="U83" s="14" t="inlineStr"/>
       <c r="V83" s="14" t="inlineStr"/>
       <c r="W83" s="14" t="n">
-        <v>1.106E7</v>
+        <v>1.246E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1400000.0</v>
+        <v>1470000.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>1.246E7</v>
+        <v>1.393E7</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.41203703703703703</v>
+        <v>0.46064814814814814</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>1.778E7</v>
+        <v>1.631E7</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5450,23 +5450,23 @@
       <c r="U84" s="14" t="inlineStr"/>
       <c r="V84" s="14" t="inlineStr"/>
       <c r="W84" s="14" t="n">
-        <v>1.52958E8</v>
+        <v>1.76453E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>2.3495E7</v>
+        <v>2.4901E7</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
-        <v>1.76453E8</v>
+        <v>2.01354E8</v>
       </c>
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.7122162485065711</v>
+        <v>0.8127240143369175</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>7.1299E7</v>
+        <v>4.6398E7</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5507,23 +5507,23 @@
       <c r="U85" s="14" t="inlineStr"/>
       <c r="V85" s="14" t="inlineStr"/>
       <c r="W85" s="14" t="n">
-        <v>2.2755E7</v>
+        <v>2.6568E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>3813000.0</v>
+        <v>4141000.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
-        <v>2.6568E7</v>
+        <v>3.0709E7</v>
       </c>
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.75</v>
+        <v>0.8668981481481481</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>8856000.0</v>
+        <v>4715000.0</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -5570,23 +5570,23 @@
       <c r="U86" s="14" t="inlineStr"/>
       <c r="V86" s="14" t="inlineStr"/>
       <c r="W86" s="14" t="n">
-        <v>4.044E7</v>
+        <v>4.4695E7</v>
       </c>
       <c r="X86" s="14" t="n">
-        <v>4255000.0</v>
+        <v>4440000.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
-        <v>4.4695E7</v>
+        <v>4.9135E7</v>
       </c>
       <c r="AA86" s="14" t="inlineStr"/>
       <c r="AB86" s="14" t="inlineStr"/>
       <c r="AC86" s="15" t="n">
-        <v>0.7094444444444444</v>
+        <v>0.7799206349206349</v>
       </c>
       <c r="AD86" s="15" t="inlineStr"/>
       <c r="AE86" s="14" t="n">
-        <v>1.8305E7</v>
+        <v>1.3865E7</v>
       </c>
       <c r="AF86" s="14" t="inlineStr"/>
       <c r="AG86" s="14" t="inlineStr"/>
@@ -5671,23 +5671,23 @@
       <c r="U88" s="14" t="inlineStr"/>
       <c r="V88" s="14" t="inlineStr"/>
       <c r="W88" s="14" t="n">
-        <v>3.251E7</v>
+        <v>3.6765E7</v>
       </c>
       <c r="X88" s="14" t="n">
-        <v>4255000.0</v>
+        <v>4440000.0</v>
       </c>
       <c r="Y88" s="14" t="inlineStr"/>
       <c r="Z88" s="14" t="n">
-        <v>3.6765E7</v>
+        <v>4.1205E7</v>
       </c>
       <c r="AA88" s="14" t="inlineStr"/>
       <c r="AB88" s="14" t="inlineStr"/>
       <c r="AC88" s="15" t="n">
-        <v>0.6682115594329335</v>
+        <v>0.7489094874591058</v>
       </c>
       <c r="AD88" s="15" t="inlineStr"/>
       <c r="AE88" s="14" t="n">
-        <v>1.8255E7</v>
+        <v>1.3815E7</v>
       </c>
       <c r="AF88" s="14" t="inlineStr"/>
       <c r="AG88" s="14" t="inlineStr"/>
@@ -5848,23 +5848,23 @@
       <c r="U91" s="14" t="inlineStr"/>
       <c r="V91" s="14" t="inlineStr"/>
       <c r="W91" s="14" t="n">
-        <v>1.936062937E9</v>
+        <v>2.118649941E9</v>
       </c>
       <c r="X91" s="14" t="n">
-        <v>1.82587004E8</v>
+        <v>1.76453702E8</v>
       </c>
       <c r="Y91" s="14" t="inlineStr"/>
       <c r="Z91" s="14" t="n">
-        <v>2.118649941E9</v>
+        <v>2.295103643E9</v>
       </c>
       <c r="AA91" s="14" t="inlineStr"/>
       <c r="AB91" s="14" t="inlineStr"/>
       <c r="AC91" s="15" t="n">
-        <v>0.7923148620044876</v>
+        <v>0.8583035314136126</v>
       </c>
       <c r="AD91" s="15" t="inlineStr"/>
       <c r="AE91" s="14" t="n">
-        <v>5.55350059E8</v>
+        <v>3.78896357E8</v>
       </c>
       <c r="AF91" s="14" t="inlineStr"/>
       <c r="AG91" s="14" t="inlineStr"/>
@@ -5905,23 +5905,23 @@
       <c r="U92" s="14" t="inlineStr"/>
       <c r="V92" s="14" t="inlineStr"/>
       <c r="W92" s="14" t="n">
-        <v>1.493448145E9</v>
+        <v>1.676035149E9</v>
       </c>
       <c r="X92" s="14" t="n">
-        <v>1.82587004E8</v>
+        <v>1.76453702E8</v>
       </c>
       <c r="Y92" s="14" t="inlineStr"/>
       <c r="Z92" s="14" t="n">
-        <v>1.676035149E9</v>
+        <v>1.852488851E9</v>
       </c>
       <c r="AA92" s="14" t="inlineStr"/>
       <c r="AB92" s="14" t="inlineStr"/>
       <c r="AC92" s="15" t="n">
-        <v>0.75112179614731</v>
+        <v>0.8302002221947354</v>
       </c>
       <c r="AD92" s="15" t="inlineStr"/>
       <c r="AE92" s="14" t="n">
-        <v>5.55340851E8</v>
+        <v>3.78887149E8</v>
       </c>
       <c r="AF92" s="14" t="inlineStr"/>
       <c r="AG92" s="14" t="inlineStr"/>
@@ -7947,23 +7947,23 @@
       <c r="U127" s="14" t="inlineStr"/>
       <c r="V127" s="14" t="inlineStr"/>
       <c r="W127" s="14" t="n">
-        <v>3.7776298238E10</v>
+        <v>4.1557585441E10</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>1.862024787E9</v>
+        <v>1.865905214E9</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
-        <v>3.9638323025E10</v>
+        <v>4.3423490655E10</v>
       </c>
       <c r="AA127" s="14" t="inlineStr"/>
       <c r="AB127" s="14" t="inlineStr"/>
       <c r="AC127" s="15" t="n">
-        <v>0.7494628847403998</v>
+        <v>0.8210310650949667</v>
       </c>
       <c r="AD127" s="15" t="inlineStr"/>
       <c r="AE127" s="14" t="n">
-        <v>1.3250650975E10</v>
+        <v>9.465483345E9</v>
       </c>
       <c r="AF127" s="14" t="inlineStr"/>
       <c r="AG127" s="14" t="inlineStr"/>
@@ -8010,23 +8010,23 @@
       <c r="U128" s="14" t="inlineStr"/>
       <c r="V128" s="14" t="inlineStr"/>
       <c r="W128" s="14" t="n">
-        <v>1.23843779E10</v>
+        <v>1.357552E10</v>
       </c>
       <c r="X128" s="14" t="n">
-        <v>1.190934E9</v>
+        <v>1.1861258E9</v>
       </c>
       <c r="Y128" s="14" t="inlineStr"/>
       <c r="Z128" s="14" t="n">
-        <v>1.35753119E10</v>
+        <v>1.47616458E10</v>
       </c>
       <c r="AA128" s="14" t="inlineStr"/>
       <c r="AB128" s="14" t="inlineStr"/>
       <c r="AC128" s="15" t="n">
-        <v>1.0322870606113097</v>
+        <v>1.122497668187446</v>
       </c>
       <c r="AD128" s="15" t="inlineStr"/>
       <c r="AE128" s="14" t="n">
-        <v>-4.245979E8</v>
+        <v>-1.6109318E9</v>
       </c>
       <c r="AF128" s="14" t="inlineStr"/>
       <c r="AG128" s="14" t="inlineStr"/>
@@ -8067,23 +8067,23 @@
       <c r="U129" s="14" t="inlineStr"/>
       <c r="V129" s="14" t="inlineStr"/>
       <c r="W129" s="14" t="n">
-        <v>9.8936245E9</v>
+        <v>1.10847666E10</v>
       </c>
       <c r="X129" s="14" t="n">
-        <v>1.190934E9</v>
+        <v>1.1861258E9</v>
       </c>
       <c r="Y129" s="14" t="inlineStr"/>
       <c r="Z129" s="14" t="n">
-        <v>1.10845585E10</v>
+        <v>1.22708924E10</v>
       </c>
       <c r="AA129" s="14" t="inlineStr"/>
       <c r="AB129" s="14" t="inlineStr"/>
       <c r="AC129" s="15" t="n">
-        <v>1.0398311532125823</v>
+        <v>1.1511199291554566</v>
       </c>
       <c r="AD129" s="15" t="inlineStr"/>
       <c r="AE129" s="14" t="n">
-        <v>-4.245985E8</v>
+        <v>-1.6109324E9</v>
       </c>
       <c r="AF129" s="14" t="inlineStr"/>
       <c r="AG129" s="14" t="inlineStr"/>
@@ -8244,23 +8244,23 @@
       <c r="U132" s="14" t="inlineStr"/>
       <c r="V132" s="14" t="inlineStr"/>
       <c r="W132" s="14" t="n">
-        <v>168118.0</v>
+        <v>183893.0</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>15731.0</v>
+        <v>15693.0</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
-        <v>183849.0</v>
+        <v>199586.0</v>
       </c>
       <c r="AA132" s="14" t="inlineStr"/>
       <c r="AB132" s="14" t="inlineStr"/>
       <c r="AC132" s="15" t="n">
-        <v>0.7692426778242678</v>
+        <v>0.8350878661087866</v>
       </c>
       <c r="AD132" s="15" t="inlineStr"/>
       <c r="AE132" s="14" t="n">
-        <v>55151.0</v>
+        <v>39414.0</v>
       </c>
       <c r="AF132" s="14" t="inlineStr"/>
       <c r="AG132" s="14" t="inlineStr"/>
@@ -8301,23 +8301,23 @@
       <c r="U133" s="14" t="inlineStr"/>
       <c r="V133" s="14" t="inlineStr"/>
       <c r="W133" s="14" t="n">
-        <v>134344.0</v>
+        <v>150119.0</v>
       </c>
       <c r="X133" s="14" t="n">
-        <v>15731.0</v>
+        <v>15693.0</v>
       </c>
       <c r="Y133" s="14" t="inlineStr"/>
       <c r="Z133" s="14" t="n">
-        <v>150075.0</v>
+        <v>165812.0</v>
       </c>
       <c r="AA133" s="14" t="inlineStr"/>
       <c r="AB133" s="14" t="inlineStr"/>
       <c r="AC133" s="15" t="n">
-        <v>0.7356617647058824</v>
+        <v>0.8128039215686275</v>
       </c>
       <c r="AD133" s="15" t="inlineStr"/>
       <c r="AE133" s="14" t="n">
-        <v>53925.0</v>
+        <v>38188.0</v>
       </c>
       <c r="AF133" s="14" t="inlineStr"/>
       <c r="AG133" s="14" t="inlineStr"/>
@@ -8478,23 +8478,23 @@
       <c r="U136" s="14" t="inlineStr"/>
       <c r="V136" s="14" t="inlineStr"/>
       <c r="W136" s="14" t="n">
-        <v>9.7338304E8</v>
+        <v>1.06754479E9</v>
       </c>
       <c r="X136" s="14" t="n">
-        <v>9.414094E7</v>
+        <v>9.360586E7</v>
       </c>
       <c r="Y136" s="14" t="inlineStr"/>
       <c r="Z136" s="14" t="n">
-        <v>1.06752398E9</v>
+        <v>1.16115065E9</v>
       </c>
       <c r="AA136" s="14" t="inlineStr"/>
       <c r="AB136" s="14" t="inlineStr"/>
       <c r="AC136" s="15" t="n">
-        <v>0.7783339870948927</v>
+        <v>0.8465973898144435</v>
       </c>
       <c r="AD136" s="15" t="inlineStr"/>
       <c r="AE136" s="14" t="n">
-        <v>3.0402602E8</v>
+        <v>2.1039935E8</v>
       </c>
       <c r="AF136" s="14" t="inlineStr"/>
       <c r="AG136" s="14" t="inlineStr"/>
@@ -8535,23 +8535,23 @@
       <c r="U137" s="14" t="inlineStr"/>
       <c r="V137" s="14" t="inlineStr"/>
       <c r="W137" s="14" t="n">
-        <v>7.7839798E8</v>
+        <v>8.7255973E8</v>
       </c>
       <c r="X137" s="14" t="n">
-        <v>9.414094E7</v>
+        <v>9.360586E7</v>
       </c>
       <c r="Y137" s="14" t="inlineStr"/>
       <c r="Z137" s="14" t="n">
-        <v>8.7253892E8</v>
+        <v>9.6616559E8</v>
       </c>
       <c r="AA137" s="14" t="inlineStr"/>
       <c r="AB137" s="14" t="inlineStr"/>
       <c r="AC137" s="15" t="n">
-        <v>0.7415991990235975</v>
+        <v>0.8211755501613172</v>
       </c>
       <c r="AD137" s="15" t="inlineStr"/>
       <c r="AE137" s="14" t="n">
-        <v>3.0402508E8</v>
+        <v>2.1039841E8</v>
       </c>
       <c r="AF137" s="14" t="inlineStr"/>
       <c r="AG137" s="14" t="inlineStr"/>
@@ -8712,23 +8712,23 @@
       <c r="U140" s="14" t="inlineStr"/>
       <c r="V140" s="14" t="inlineStr"/>
       <c r="W140" s="14" t="n">
-        <v>3.02321108E8</v>
+        <v>3.3194263E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>2.9613198E7</v>
+        <v>2.9857124E7</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
-        <v>3.31934306E8</v>
+        <v>3.61799754E8</v>
       </c>
       <c r="AA140" s="14" t="inlineStr"/>
       <c r="AB140" s="14" t="inlineStr"/>
       <c r="AC140" s="15" t="n">
-        <v>0.7661372026303095</v>
+        <v>0.8350696099543689</v>
       </c>
       <c r="AD140" s="15" t="inlineStr"/>
       <c r="AE140" s="14" t="n">
-        <v>1.01322694E8</v>
+        <v>7.1457246E7</v>
       </c>
       <c r="AF140" s="14" t="inlineStr"/>
       <c r="AG140" s="14" t="inlineStr"/>
@@ -8813,23 +8813,23 @@
       <c r="U142" s="14" t="inlineStr"/>
       <c r="V142" s="14" t="inlineStr"/>
       <c r="W142" s="14" t="n">
-        <v>2.41930252E8</v>
+        <v>2.71551774E8</v>
       </c>
       <c r="X142" s="14" t="n">
-        <v>2.9613198E7</v>
+        <v>2.9857124E7</v>
       </c>
       <c r="Y142" s="14" t="inlineStr"/>
       <c r="Z142" s="14" t="n">
-        <v>2.7154345E8</v>
+        <v>3.01408898E8</v>
       </c>
       <c r="AA142" s="14" t="inlineStr"/>
       <c r="AB142" s="14" t="inlineStr"/>
       <c r="AC142" s="15" t="n">
-        <v>0.7282640587452798</v>
+        <v>0.8083614883710951</v>
       </c>
       <c r="AD142" s="15" t="inlineStr"/>
       <c r="AE142" s="14" t="n">
-        <v>1.0132055E8</v>
+        <v>7.1455102E7</v>
       </c>
       <c r="AF142" s="14" t="inlineStr"/>
       <c r="AG142" s="14" t="inlineStr"/>
@@ -8990,23 +8990,23 @@
       <c r="U145" s="14" t="inlineStr"/>
       <c r="V145" s="14" t="inlineStr"/>
       <c r="W145" s="14" t="n">
-        <v>2.67431E9</v>
+        <v>2.93033E9</v>
       </c>
       <c r="X145" s="14" t="n">
-        <v>2.5602E8</v>
+        <v>2.5398E8</v>
       </c>
       <c r="Y145" s="14" t="inlineStr"/>
       <c r="Z145" s="14" t="n">
-        <v>2.93033E9</v>
+        <v>3.18431E9</v>
       </c>
       <c r="AA145" s="14" t="inlineStr"/>
       <c r="AB145" s="14" t="inlineStr"/>
       <c r="AC145" s="15" t="n">
-        <v>0.7611246753246753</v>
+        <v>0.8270935064935065</v>
       </c>
       <c r="AD145" s="15" t="inlineStr"/>
       <c r="AE145" s="14" t="n">
-        <v>9.1967E8</v>
+        <v>6.6569E8</v>
       </c>
       <c r="AF145" s="14" t="inlineStr"/>
       <c r="AG145" s="14" t="inlineStr"/>
@@ -9047,23 +9047,23 @@
       <c r="U146" s="14" t="inlineStr"/>
       <c r="V146" s="14" t="inlineStr"/>
       <c r="W146" s="14" t="n">
-        <v>2.13605E9</v>
+        <v>2.39207E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>2.5602E8</v>
+        <v>2.5398E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>2.39207E9</v>
+        <v>2.64605E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.7223009321999097</v>
+        <v>0.7989918278510123</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>9.19666E8</v>
+        <v>6.65686E8</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9224,23 +9224,23 @@
       <c r="U149" s="14" t="inlineStr"/>
       <c r="V149" s="14" t="inlineStr"/>
       <c r="W149" s="14" t="n">
-        <v>2.17635496E8</v>
+        <v>2.20978694E8</v>
       </c>
       <c r="X149" s="14" t="n">
-        <v>3343198.0</v>
+        <v>3341277.0</v>
       </c>
       <c r="Y149" s="14" t="inlineStr"/>
       <c r="Z149" s="14" t="n">
-        <v>2.20978694E8</v>
+        <v>2.24319971E8</v>
       </c>
       <c r="AA149" s="14" t="inlineStr"/>
       <c r="AB149" s="14" t="inlineStr"/>
       <c r="AC149" s="15" t="n">
-        <v>0.8992743824522851</v>
+        <v>0.9128717332031091</v>
       </c>
       <c r="AD149" s="15" t="inlineStr"/>
       <c r="AE149" s="14" t="n">
-        <v>2.4751306E7</v>
+        <v>2.1410029E7</v>
       </c>
       <c r="AF149" s="14" t="inlineStr"/>
       <c r="AG149" s="14" t="inlineStr"/>
@@ -9281,23 +9281,23 @@
       <c r="U150" s="14" t="inlineStr"/>
       <c r="V150" s="14" t="inlineStr"/>
       <c r="W150" s="14" t="n">
-        <v>3.2179365E7</v>
+        <v>3.5522563E7</v>
       </c>
       <c r="X150" s="14" t="n">
-        <v>3343198.0</v>
+        <v>3341277.0</v>
       </c>
       <c r="Y150" s="14" t="inlineStr"/>
       <c r="Z150" s="14" t="n">
-        <v>3.5522563E7</v>
+        <v>3.886384E7</v>
       </c>
       <c r="AA150" s="14" t="inlineStr"/>
       <c r="AB150" s="14" t="inlineStr"/>
       <c r="AC150" s="15" t="n">
-        <v>0.5894491404486925</v>
+        <v>0.644893136864463</v>
       </c>
       <c r="AD150" s="15" t="inlineStr"/>
       <c r="AE150" s="14" t="n">
-        <v>2.4741437E7</v>
+        <v>2.140016E7</v>
       </c>
       <c r="AF150" s="14" t="inlineStr"/>
       <c r="AG150" s="14" t="inlineStr"/>
@@ -9458,23 +9458,23 @@
       <c r="U153" s="14" t="inlineStr"/>
       <c r="V153" s="14" t="inlineStr"/>
       <c r="W153" s="14" t="n">
-        <v>6.7995138E8</v>
+        <v>7.462881E8</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>6.633672E7</v>
+        <v>6.611946E7</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>7.462881E8</v>
+        <v>8.1240756E8</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.7615184693877551</v>
+        <v>0.828987306122449</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>2.337119E8</v>
+        <v>1.6759244E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9515,23 +9515,23 @@
       <c r="U154" s="14" t="inlineStr"/>
       <c r="V154" s="14" t="inlineStr"/>
       <c r="W154" s="14" t="n">
-        <v>5.4322242E8</v>
+        <v>6.0955914E8</v>
       </c>
       <c r="X154" s="14" t="n">
-        <v>6.633672E7</v>
+        <v>6.611946E7</v>
       </c>
       <c r="Y154" s="14" t="inlineStr"/>
       <c r="Z154" s="14" t="n">
-        <v>6.0955914E8</v>
+        <v>6.756786E8</v>
       </c>
       <c r="AA154" s="14" t="inlineStr"/>
       <c r="AB154" s="14" t="inlineStr"/>
       <c r="AC154" s="15" t="n">
-        <v>0.7228568277550091</v>
+        <v>0.8012657957650273</v>
       </c>
       <c r="AD154" s="15" t="inlineStr"/>
       <c r="AE154" s="14" t="n">
-        <v>2.3370486E8</v>
+        <v>1.675854E8</v>
       </c>
       <c r="AF154" s="14" t="inlineStr"/>
       <c r="AG154" s="14" t="inlineStr"/>
@@ -9692,23 +9692,23 @@
       <c r="U157" s="14" t="inlineStr"/>
       <c r="V157" s="14" t="inlineStr"/>
       <c r="W157" s="14" t="n">
-        <v>1.506368E9</v>
+        <v>1.727804E9</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>2.21436E8</v>
+        <v>2.32675E8</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
-        <v>1.727804E9</v>
+        <v>1.960479E9</v>
       </c>
       <c r="AA157" s="14" t="inlineStr"/>
       <c r="AB157" s="14" t="inlineStr"/>
       <c r="AC157" s="15" t="n">
-        <v>0.6614100043486516</v>
+        <v>0.750478887602668</v>
       </c>
       <c r="AD157" s="15" t="inlineStr"/>
       <c r="AE157" s="14" t="n">
-        <v>8.845E8</v>
+        <v>6.51825E8</v>
       </c>
       <c r="AF157" s="14" t="inlineStr"/>
       <c r="AG157" s="14" t="inlineStr"/>
@@ -9749,23 +9749,23 @@
       <c r="U158" s="14" t="inlineStr"/>
       <c r="V158" s="14" t="inlineStr"/>
       <c r="W158" s="14" t="n">
-        <v>1.3272E8</v>
+        <v>1.5344E8</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>2.072E7</v>
+        <v>2.149E7</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
-        <v>1.5344E8</v>
+        <v>1.7493E8</v>
       </c>
       <c r="AA158" s="14" t="inlineStr"/>
       <c r="AB158" s="14" t="inlineStr"/>
       <c r="AC158" s="15" t="n">
-        <v>0.5969498910675382</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="AD158" s="15" t="inlineStr"/>
       <c r="AE158" s="14" t="n">
-        <v>1.036E8</v>
+        <v>8.211E7</v>
       </c>
       <c r="AF158" s="14" t="inlineStr"/>
       <c r="AG158" s="14" t="inlineStr"/>
@@ -9806,23 +9806,23 @@
       <c r="U159" s="14" t="inlineStr"/>
       <c r="V159" s="14" t="inlineStr"/>
       <c r="W159" s="14" t="n">
-        <v>1.07115E9</v>
+        <v>1.23062E9</v>
       </c>
       <c r="X159" s="14" t="n">
-        <v>1.5947E8</v>
+        <v>1.67684E8</v>
       </c>
       <c r="Y159" s="14" t="inlineStr"/>
       <c r="Z159" s="14" t="n">
-        <v>1.23062E9</v>
+        <v>1.398304E9</v>
       </c>
       <c r="AA159" s="14" t="inlineStr"/>
       <c r="AB159" s="14" t="inlineStr"/>
       <c r="AC159" s="15" t="n">
-        <v>0.6813339888561127</v>
+        <v>0.7741724024909865</v>
       </c>
       <c r="AD159" s="15" t="inlineStr"/>
       <c r="AE159" s="14" t="n">
-        <v>5.75572E8</v>
+        <v>4.07888E8</v>
       </c>
       <c r="AF159" s="14" t="inlineStr"/>
       <c r="AG159" s="14" t="inlineStr"/>
@@ -9863,23 +9863,23 @@
       <c r="U160" s="14" t="inlineStr"/>
       <c r="V160" s="14" t="inlineStr"/>
       <c r="W160" s="14" t="n">
-        <v>3.02498E8</v>
+        <v>3.43744E8</v>
       </c>
       <c r="X160" s="14" t="n">
-        <v>4.1246E7</v>
+        <v>4.3501E7</v>
       </c>
       <c r="Y160" s="14" t="inlineStr"/>
       <c r="Z160" s="14" t="n">
-        <v>3.43744E8</v>
+        <v>3.87245E8</v>
       </c>
       <c r="AA160" s="14" t="inlineStr"/>
       <c r="AB160" s="14" t="inlineStr"/>
       <c r="AC160" s="15" t="n">
-        <v>0.6260454002389486</v>
+        <v>0.7052718040621266</v>
       </c>
       <c r="AD160" s="15" t="inlineStr"/>
       <c r="AE160" s="14" t="n">
-        <v>2.05328E8</v>
+        <v>1.61827E8</v>
       </c>
       <c r="AF160" s="14" t="inlineStr"/>
       <c r="AG160" s="14" t="inlineStr"/>
@@ -9926,23 +9926,23 @@
       <c r="U161" s="14" t="inlineStr"/>
       <c r="V161" s="14" t="inlineStr"/>
       <c r="W161" s="14" t="n">
-        <v>2220000.0</v>
+        <v>2405000.0</v>
       </c>
       <c r="X161" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
-        <v>2405000.0</v>
+        <v>2590000.0</v>
       </c>
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>2775000.0</v>
+        <v>2590000.0</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -9983,23 +9983,23 @@
       <c r="U162" s="14" t="inlineStr"/>
       <c r="V162" s="14" t="inlineStr"/>
       <c r="W162" s="14" t="n">
-        <v>1665000.0</v>
+        <v>1850000.0</v>
       </c>
       <c r="X162" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
-        <v>1850000.0</v>
+        <v>2035000.0</v>
       </c>
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>0.4004329004329004</v>
+        <v>0.44047619047619047</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>2770000.0</v>
+        <v>2585000.0</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10160,23 +10160,23 @@
       <c r="U165" s="14" t="inlineStr"/>
       <c r="V165" s="14" t="inlineStr"/>
       <c r="W165" s="14" t="n">
-        <v>1.9035563196E10</v>
+        <v>2.0954588334E10</v>
       </c>
       <c r="X165" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
-        <v>1.9035563196E10</v>
+        <v>2.0954588334E10</v>
       </c>
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.6294829099206349</v>
+        <v>0.6929427359126984</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>1.1204436804E10</v>
+        <v>9.285411666E9</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10217,23 +10217,23 @@
       <c r="U166" s="14" t="inlineStr"/>
       <c r="V166" s="14" t="inlineStr"/>
       <c r="W166" s="14" t="n">
-        <v>1.4258277996E10</v>
+        <v>1.6177303134E10</v>
       </c>
       <c r="X166" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
-        <v>1.4258277996E10</v>
+        <v>1.6177303134E10</v>
       </c>
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.5599671580834463</v>
+        <v>0.6353332754447446</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>1.1204426004E10</v>
+        <v>9.285400866E9</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -10438,23 +10438,23 @@
       <c r="U170" s="14" t="inlineStr"/>
       <c r="V170" s="14" t="inlineStr"/>
       <c r="W170" s="14" t="n">
-        <v>1.4501134907E10</v>
+        <v>1.6105883553E10</v>
       </c>
       <c r="X170" s="14" t="n">
-        <v>8.39593154E8</v>
+        <v>8.22449216E8</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
-        <v>1.5340728061E10</v>
+        <v>1.6928332769E10</v>
       </c>
       <c r="AA170" s="14" t="inlineStr"/>
       <c r="AB170" s="14" t="inlineStr"/>
       <c r="AC170" s="15" t="n">
-        <v>1.0231252726759552</v>
+        <v>1.1290080243494927</v>
       </c>
       <c r="AD170" s="15" t="inlineStr"/>
       <c r="AE170" s="14" t="n">
-        <v>-3.46740061E8</v>
+        <v>-1.934344769E9</v>
       </c>
       <c r="AF170" s="14" t="inlineStr"/>
       <c r="AG170" s="14" t="inlineStr"/>
@@ -10501,23 +10501,23 @@
       <c r="U171" s="14" t="inlineStr"/>
       <c r="V171" s="14" t="inlineStr"/>
       <c r="W171" s="14" t="n">
-        <v>5.311759666E9</v>
+        <v>5.861130466E9</v>
       </c>
       <c r="X171" s="14" t="n">
         <v>5.493708E8</v>
       </c>
       <c r="Y171" s="14" t="inlineStr"/>
       <c r="Z171" s="14" t="n">
-        <v>5.861130466E9</v>
+        <v>6.410501266E9</v>
       </c>
       <c r="AA171" s="14" t="inlineStr"/>
       <c r="AB171" s="14" t="inlineStr"/>
       <c r="AC171" s="15" t="n">
-        <v>1.3145739439794482</v>
+        <v>1.4377905390463057</v>
       </c>
       <c r="AD171" s="15" t="inlineStr"/>
       <c r="AE171" s="14" t="n">
-        <v>-1.402552466E9</v>
+        <v>-1.951923266E9</v>
       </c>
       <c r="AF171" s="14" t="inlineStr"/>
       <c r="AG171" s="14" t="inlineStr"/>
@@ -10558,23 +10558,23 @@
       <c r="U172" s="14" t="inlineStr"/>
       <c r="V172" s="14" t="inlineStr"/>
       <c r="W172" s="14" t="n">
-        <v>4.222646E9</v>
+        <v>4.7720168E9</v>
       </c>
       <c r="X172" s="14" t="n">
         <v>5.493708E8</v>
       </c>
       <c r="Y172" s="14" t="inlineStr"/>
       <c r="Z172" s="14" t="n">
-        <v>4.7720168E9</v>
+        <v>5.3213876E9</v>
       </c>
       <c r="AA172" s="14" t="inlineStr"/>
       <c r="AB172" s="14" t="inlineStr"/>
       <c r="AC172" s="15" t="n">
-        <v>1.416257342431538</v>
+        <v>1.5793017033016605</v>
       </c>
       <c r="AD172" s="15" t="inlineStr"/>
       <c r="AE172" s="14" t="n">
-        <v>-1.4025608E9</v>
+        <v>-1.9519316E9</v>
       </c>
       <c r="AF172" s="14" t="inlineStr"/>
       <c r="AG172" s="14" t="inlineStr"/>
@@ -10735,23 +10735,23 @@
       <c r="U175" s="14" t="inlineStr"/>
       <c r="V175" s="14" t="inlineStr"/>
       <c r="W175" s="14" t="n">
-        <v>101733.0</v>
+        <v>111771.0</v>
       </c>
       <c r="X175" s="14" t="n">
-        <v>10038.0</v>
+        <v>10020.0</v>
       </c>
       <c r="Y175" s="14" t="inlineStr"/>
       <c r="Z175" s="14" t="n">
-        <v>111771.0</v>
+        <v>121791.0</v>
       </c>
       <c r="AA175" s="14" t="inlineStr"/>
       <c r="AB175" s="14" t="inlineStr"/>
       <c r="AC175" s="15" t="n">
-        <v>0.7074113924050633</v>
+        <v>0.7708291139240506</v>
       </c>
       <c r="AD175" s="15" t="inlineStr"/>
       <c r="AE175" s="14" t="n">
-        <v>46229.0</v>
+        <v>36209.0</v>
       </c>
       <c r="AF175" s="14" t="inlineStr"/>
       <c r="AG175" s="14" t="inlineStr"/>
@@ -10792,23 +10792,23 @@
       <c r="U176" s="14" t="inlineStr"/>
       <c r="V176" s="14" t="inlineStr"/>
       <c r="W176" s="14" t="n">
-        <v>88613.0</v>
+        <v>98651.0</v>
       </c>
       <c r="X176" s="14" t="n">
-        <v>10038.0</v>
+        <v>10020.0</v>
       </c>
       <c r="Y176" s="14" t="inlineStr"/>
       <c r="Z176" s="14" t="n">
-        <v>98651.0</v>
+        <v>108671.0</v>
       </c>
       <c r="AA176" s="14" t="inlineStr"/>
       <c r="AB176" s="14" t="inlineStr"/>
       <c r="AC176" s="15" t="n">
-        <v>0.6850763888888889</v>
+        <v>0.7546597222222222</v>
       </c>
       <c r="AD176" s="15" t="inlineStr"/>
       <c r="AE176" s="14" t="n">
-        <v>45349.0</v>
+        <v>35329.0</v>
       </c>
       <c r="AF176" s="14" t="inlineStr"/>
       <c r="AG176" s="14" t="inlineStr"/>
@@ -10969,23 +10969,23 @@
       <c r="U179" s="14" t="inlineStr"/>
       <c r="V179" s="14" t="inlineStr"/>
       <c r="W179" s="14" t="n">
-        <v>3.5985017E8</v>
+        <v>3.9715681E8</v>
       </c>
       <c r="X179" s="14" t="n">
-        <v>3.730664E7</v>
+        <v>3.791288E7</v>
       </c>
       <c r="Y179" s="14" t="inlineStr"/>
       <c r="Z179" s="14" t="n">
-        <v>3.9715681E8</v>
+        <v>4.3506969E8</v>
       </c>
       <c r="AA179" s="14" t="inlineStr"/>
       <c r="AB179" s="14" t="inlineStr"/>
       <c r="AC179" s="15" t="n">
-        <v>1.0999562683830657</v>
+        <v>1.2049588994809812</v>
       </c>
       <c r="AD179" s="15" t="inlineStr"/>
       <c r="AE179" s="14" t="n">
-        <v>-3.609081E7</v>
+        <v>-7.400369E7</v>
       </c>
       <c r="AF179" s="14" t="inlineStr"/>
       <c r="AG179" s="14" t="inlineStr"/>
@@ -11026,23 +11026,23 @@
       <c r="U180" s="14" t="inlineStr"/>
       <c r="V180" s="14" t="inlineStr"/>
       <c r="W180" s="14" t="n">
-        <v>2.861254E8</v>
+        <v>3.2343204E8</v>
       </c>
       <c r="X180" s="14" t="n">
-        <v>3.730664E7</v>
+        <v>3.791288E7</v>
       </c>
       <c r="Y180" s="14" t="inlineStr"/>
       <c r="Z180" s="14" t="n">
-        <v>3.2343204E8</v>
+        <v>3.6134492E8</v>
       </c>
       <c r="AA180" s="14" t="inlineStr"/>
       <c r="AB180" s="14" t="inlineStr"/>
       <c r="AC180" s="15" t="n">
-        <v>1.1256074337022344</v>
+        <v>1.2575517505394307</v>
       </c>
       <c r="AD180" s="15" t="inlineStr"/>
       <c r="AE180" s="14" t="n">
-        <v>-3.609204E7</v>
+        <v>-7.400492E7</v>
       </c>
       <c r="AF180" s="14" t="inlineStr"/>
       <c r="AG180" s="14" t="inlineStr"/>
@@ -11203,23 +11203,23 @@
       <c r="U183" s="14" t="inlineStr"/>
       <c r="V183" s="14" t="inlineStr"/>
       <c r="W183" s="14" t="n">
-        <v>1.07733296E8</v>
+        <v>1.18776192E8</v>
       </c>
       <c r="X183" s="14" t="n">
         <v>1.1042896E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.18776192E8</v>
+        <v>1.29819088E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>1.0598582289324339</v>
+        <v>1.158395688332084</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>-6708192.0</v>
+        <v>-1.7751088E7</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11260,23 +11260,23 @@
       <c r="U184" s="14" t="inlineStr"/>
       <c r="V184" s="14" t="inlineStr"/>
       <c r="W184" s="14" t="n">
-        <v>8.5850712E7</v>
+        <v>9.6893608E7</v>
       </c>
       <c r="X184" s="14" t="n">
         <v>1.1042896E7</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>9.6893608E7</v>
+        <v>1.07936504E8</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>1.0744467509425593</v>
+        <v>1.1969006875138613</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>-6713608.0</v>
+        <v>-1.7756504E7</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11437,23 +11437,23 @@
       <c r="U187" s="14" t="inlineStr"/>
       <c r="V187" s="14" t="inlineStr"/>
       <c r="W187" s="14" t="n">
-        <v>8.6691E8</v>
+        <v>9.5565E8</v>
       </c>
       <c r="X187" s="14" t="n">
         <v>8.874E7</v>
       </c>
       <c r="Y187" s="14" t="inlineStr"/>
       <c r="Z187" s="14" t="n">
-        <v>9.5565E8</v>
+        <v>1.04439E9</v>
       </c>
       <c r="AA187" s="14" t="inlineStr"/>
       <c r="AB187" s="14" t="inlineStr"/>
       <c r="AC187" s="15" t="n">
-        <v>1.064032333489211</v>
+        <v>1.162836528826241</v>
       </c>
       <c r="AD187" s="15" t="inlineStr"/>
       <c r="AE187" s="14" t="n">
-        <v>-5.751E7</v>
+        <v>-1.4625E8</v>
       </c>
       <c r="AF187" s="14" t="inlineStr"/>
       <c r="AG187" s="14" t="inlineStr"/>
@@ -11494,23 +11494,23 @@
       <c r="U188" s="14" t="inlineStr"/>
       <c r="V188" s="14" t="inlineStr"/>
       <c r="W188" s="14" t="n">
-        <v>6.891E8</v>
+        <v>7.7784E8</v>
       </c>
       <c r="X188" s="14" t="n">
         <v>8.874E7</v>
       </c>
       <c r="Y188" s="14" t="inlineStr"/>
       <c r="Z188" s="14" t="n">
-        <v>7.7784E8</v>
+        <v>8.6658E8</v>
       </c>
       <c r="AA188" s="14" t="inlineStr"/>
       <c r="AB188" s="14" t="inlineStr"/>
       <c r="AC188" s="15" t="n">
-        <v>1.0798474020024322</v>
+        <v>1.203041964449331</v>
       </c>
       <c r="AD188" s="15" t="inlineStr"/>
       <c r="AE188" s="14" t="n">
-        <v>-5.7516E7</v>
+        <v>-1.46256E8</v>
       </c>
       <c r="AF188" s="14" t="inlineStr"/>
       <c r="AG188" s="14" t="inlineStr"/>
@@ -11671,23 +11671,23 @@
       <c r="U191" s="14" t="inlineStr"/>
       <c r="V191" s="14" t="inlineStr"/>
       <c r="W191" s="14" t="n">
-        <v>3.2558825E8</v>
+        <v>3.5882903E8</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>3.324078E7</v>
+        <v>3.338562E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>3.5882903E8</v>
+        <v>3.9221465E8</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>1.0849015867064955</v>
+        <v>1.1858413353973418</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>-2.808103E7</v>
+        <v>-6.146665E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11728,23 +11728,23 @@
       <c r="U192" s="14" t="inlineStr"/>
       <c r="V192" s="14" t="inlineStr"/>
       <c r="W192" s="14" t="n">
-        <v>2.5904634E8</v>
+        <v>2.9228712E8</v>
       </c>
       <c r="X192" s="14" t="n">
-        <v>3.324078E7</v>
+        <v>3.338562E7</v>
       </c>
       <c r="Y192" s="14" t="inlineStr"/>
       <c r="Z192" s="14" t="n">
-        <v>2.9228712E8</v>
+        <v>3.2567274E8</v>
       </c>
       <c r="AA192" s="14" t="inlineStr"/>
       <c r="AB192" s="14" t="inlineStr"/>
       <c r="AC192" s="15" t="n">
-        <v>1.1062933187991097</v>
+        <v>1.2326563564518327</v>
       </c>
       <c r="AD192" s="15" t="inlineStr"/>
       <c r="AE192" s="14" t="n">
-        <v>-2.808312E7</v>
+        <v>-6.146874E7</v>
       </c>
       <c r="AF192" s="14" t="inlineStr"/>
       <c r="AG192" s="14" t="inlineStr"/>
@@ -11949,23 +11949,23 @@
       <c r="U196" s="14" t="inlineStr"/>
       <c r="V196" s="14" t="inlineStr"/>
       <c r="W196" s="14" t="n">
-        <v>7.83142E8</v>
+        <v>9.03024E8</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>1.19882E8</v>
+        <v>1.01987E8</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="14" t="n">
-        <v>9.03024E8</v>
+        <v>1.005011E9</v>
       </c>
       <c r="AA196" s="14" t="inlineStr"/>
       <c r="AB196" s="14" t="inlineStr"/>
       <c r="AC196" s="15" t="n">
-        <v>0.8897138803499646</v>
+        <v>0.9901976432568771</v>
       </c>
       <c r="AD196" s="15" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>1.11936E8</v>
+        <v>9949000.0</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12006,23 +12006,23 @@
       <c r="U197" s="14" t="inlineStr"/>
       <c r="V197" s="14" t="inlineStr"/>
       <c r="W197" s="14" t="n">
-        <v>7.511E7</v>
+        <v>8.673E7</v>
       </c>
       <c r="X197" s="14" t="n">
-        <v>1.162E7</v>
+        <v>1.0745E7</v>
       </c>
       <c r="Y197" s="14" t="inlineStr"/>
       <c r="Z197" s="14" t="n">
-        <v>8.673E7</v>
+        <v>9.7475E7</v>
       </c>
       <c r="AA197" s="14" t="inlineStr"/>
       <c r="AB197" s="14" t="inlineStr"/>
       <c r="AC197" s="15" t="n">
-        <v>0.7942307692307692</v>
+        <v>0.8926282051282052</v>
       </c>
       <c r="AD197" s="15" t="inlineStr"/>
       <c r="AE197" s="14" t="n">
-        <v>2.247E7</v>
+        <v>1.1725E7</v>
       </c>
       <c r="AF197" s="14" t="inlineStr"/>
       <c r="AG197" s="14" t="inlineStr"/>
@@ -12063,23 +12063,23 @@
       <c r="U198" s="14" t="inlineStr"/>
       <c r="V198" s="14" t="inlineStr"/>
       <c r="W198" s="14" t="n">
-        <v>7.08032E8</v>
+        <v>8.16294E8</v>
       </c>
       <c r="X198" s="14" t="n">
-        <v>1.08262E8</v>
+        <v>9.1242E7</v>
       </c>
       <c r="Y198" s="14" t="inlineStr"/>
       <c r="Z198" s="14" t="n">
-        <v>8.16294E8</v>
+        <v>9.07536E8</v>
       </c>
       <c r="AA198" s="14" t="inlineStr"/>
       <c r="AB198" s="14" t="inlineStr"/>
       <c r="AC198" s="15" t="n">
-        <v>0.9012254901960784</v>
+        <v>1.0019607843137255</v>
       </c>
       <c r="AD198" s="15" t="inlineStr"/>
       <c r="AE198" s="14" t="n">
-        <v>8.9466E7</v>
+        <v>-1776000.0</v>
       </c>
       <c r="AF198" s="14" t="inlineStr"/>
       <c r="AG198" s="14" t="inlineStr"/>
@@ -12126,23 +12126,23 @@
       <c r="U199" s="14" t="inlineStr"/>
       <c r="V199" s="14" t="inlineStr"/>
       <c r="W199" s="14" t="n">
-        <v>6.746049792E9</v>
+        <v>7.511205284E9</v>
       </c>
       <c r="X199" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
-        <v>6.746049792E9</v>
+        <v>7.511205284E9</v>
       </c>
       <c r="AA199" s="14" t="inlineStr"/>
       <c r="AB199" s="14" t="inlineStr"/>
       <c r="AC199" s="15" t="n">
-        <v>0.8628571016350164</v>
+        <v>0.9607247235002117</v>
       </c>
       <c r="AD199" s="15" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
-        <v>1.072220208E9</v>
+        <v>3.07064716E8</v>
       </c>
       <c r="AF199" s="14" t="inlineStr"/>
       <c r="AG199" s="14" t="inlineStr"/>
@@ -12183,23 +12183,23 @@
       <c r="U200" s="14" t="inlineStr"/>
       <c r="V200" s="14" t="inlineStr"/>
       <c r="W200" s="14" t="n">
-        <v>5.171606416E9</v>
+        <v>5.936761908E9</v>
       </c>
       <c r="X200" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y200" s="14" t="inlineStr"/>
       <c r="Z200" s="14" t="n">
-        <v>5.171606416E9</v>
+        <v>5.936761908E9</v>
       </c>
       <c r="AA200" s="14" t="inlineStr"/>
       <c r="AB200" s="14" t="inlineStr"/>
       <c r="AC200" s="15" t="n">
-        <v>0.8282765565160792</v>
+        <v>0.950822687279702</v>
       </c>
       <c r="AD200" s="15" t="inlineStr"/>
       <c r="AE200" s="14" t="n">
-        <v>1.072209584E9</v>
+        <v>3.07054092E8</v>
       </c>
       <c r="AF200" s="14" t="inlineStr"/>
       <c r="AG200" s="14" t="inlineStr"/>
@@ -12360,23 +12360,23 @@
       <c r="U203" s="25" t="inlineStr"/>
       <c r="V203" s="25" t="inlineStr"/>
       <c r="W203" s="25" t="n">
-        <v>3.409122002E9</v>
+        <v>4.355008794E9</v>
       </c>
       <c r="X203" s="25" t="n">
-        <v>9.30636529E8</v>
+        <v>8.99714621E8</v>
       </c>
       <c r="Y203" s="25" t="inlineStr"/>
       <c r="Z203" s="25" t="n">
-        <v>4.339758531E9</v>
+        <v>5.254723415E9</v>
       </c>
       <c r="AA203" s="25" t="inlineStr"/>
       <c r="AB203" s="25" t="inlineStr"/>
       <c r="AC203" s="26" t="n">
-        <v>0.6508038446051883</v>
+        <v>0.7880148575987451</v>
       </c>
       <c r="AD203" s="26" t="inlineStr"/>
       <c r="AE203" s="25" t="n">
-        <v>2.328546469E9</v>
+        <v>1.413581585E9</v>
       </c>
       <c r="AF203" s="25" t="inlineStr"/>
       <c r="AG203" s="25" t="inlineStr"/>
@@ -12413,7 +12413,7 @@
       <c r="O204" s="13" t="inlineStr"/>
       <c r="P204" s="13" t="inlineStr"/>
       <c r="Q204" s="14" t="n">
-        <v>4.91939E9</v>
+        <v>4.91139E9</v>
       </c>
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="14" t="n">
@@ -12423,23 +12423,23 @@
       <c r="U204" s="14" t="inlineStr"/>
       <c r="V204" s="14" t="inlineStr"/>
       <c r="W204" s="14" t="n">
-        <v>2.412053935E9</v>
+        <v>3.254563865E9</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>8.37025967E8</v>
+        <v>8.28823565E8</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>3.249079902E9</v>
+        <v>4.08338743E9</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.6604639806967937</v>
+        <v>0.8314117653047305</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>1.670310098E9</v>
+        <v>8.2800257E8</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12476,7 +12476,7 @@
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>1.754348E9</v>
+        <v>1.837418E9</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12486,23 +12486,23 @@
       <c r="U205" s="14" t="inlineStr"/>
       <c r="V205" s="14" t="inlineStr"/>
       <c r="W205" s="14" t="n">
-        <v>5.48705803E8</v>
+        <v>1.126483817E9</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>5.72294051E8</v>
+        <v>5.69922129E8</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>1.120999854E9</v>
+        <v>1.696405946E9</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.6389837443882286</v>
+        <v>0.923255321325904</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>6.33348146E8</v>
+        <v>1.41012054E8</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12543,23 +12543,23 @@
       <c r="U206" s="14" t="inlineStr"/>
       <c r="V206" s="14" t="inlineStr"/>
       <c r="W206" s="14" t="n">
-        <v>5.115E8</v>
+        <v>5.75E8</v>
       </c>
       <c r="X206" s="14" t="n">
         <v>6.35E7</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
-        <v>5.75E8</v>
+        <v>6.385E8</v>
       </c>
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.8455882352941176</v>
+        <v>0.9389705882352941</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>1.05E8</v>
+        <v>4.15E7</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12600,23 +12600,23 @@
       <c r="U207" s="14" t="inlineStr"/>
       <c r="V207" s="14" t="inlineStr"/>
       <c r="W207" s="14" t="n">
-        <v>2419200.0</v>
+        <v>2762100.0</v>
       </c>
       <c r="X207" s="14" t="n">
         <v>342900.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>2762100.0</v>
+        <v>3105000.0</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.8861405197305101</v>
+        <v>0.9961501443695862</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>354900.0</v>
+        <v>12000.0</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12657,23 +12657,23 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>3.4786603E7</v>
+        <v>4.4211997E7</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>3941431.0</v>
+        <v>1569509.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>3.8728034E7</v>
+        <v>4.5781506E7</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.6598182809438623</v>
+        <v>0.7799898798875543</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.9966966E7</v>
+        <v>1.2913494E7</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12714,23 +12714,23 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>0.0</v>
+        <v>4.32E7</v>
       </c>
       <c r="X209" s="14" t="n">
         <v>4.32E7</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>4.32E7</v>
+        <v>8.64E7</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>4.32E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12771,23 +12771,23 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>0.0</v>
+        <v>4.446E8</v>
       </c>
       <c r="X210" s="14" t="n">
         <v>4.446E8</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>4.446E8</v>
+        <v>8.892E8</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>4.446E8</v>
+        <v>0.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12828,23 +12828,23 @@
       <c r="U211" s="14" t="inlineStr"/>
       <c r="V211" s="14" t="inlineStr"/>
       <c r="W211" s="14" t="n">
-        <v>0.0</v>
+        <v>1.4E7</v>
       </c>
       <c r="X211" s="14" t="n">
         <v>1.4E7</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>1.4E7</v>
+        <v>2.8E7</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>1.4E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
@@ -12885,23 +12885,23 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>0.0</v>
+        <v>2709720.0</v>
       </c>
       <c r="X212" s="14" t="n">
         <v>2709720.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>2709720.0</v>
+        <v>5419440.0</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.3032363473589973</v>
+        <v>0.6064726947179946</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>6226280.0</v>
+        <v>3516560.0</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
@@ -12916,29 +12916,23 @@
       <c r="E213" s="2" t="inlineStr"/>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I213" s="13" t="inlineStr"/>
-      <c r="J213" s="13" t="inlineStr"/>
-      <c r="K213" s="13" t="inlineStr"/>
-      <c r="L213" s="13" t="inlineStr"/>
-      <c r="M213" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N213" s="13" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000294. Gaji PPPK Paruh Waktu</t>
+          </r>
+        </is>
+      </c>
       <c r="O213" s="13" t="inlineStr"/>
       <c r="P213" s="13" t="inlineStr"/>
       <c r="Q213" s="14" t="n">
-        <v>1.0E7</v>
+        <v>7.83E7</v>
       </c>
       <c r="R213" s="14" t="inlineStr"/>
       <c r="S213" s="14" t="n">
@@ -12948,23 +12942,23 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>5366500.0</v>
+        <v>0.0</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>1399500.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>6766000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.6766</v>
+        <v>0.0</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>3234000.0</v>
+        <v>7.83E7</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
@@ -12988,14 +12982,14 @@
       <c r="N214" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000133. Biaya Tol</t>
+            <t xml:space="preserve">000295. BPJS Ketenagakerjaan</t>
           </r>
         </is>
       </c>
       <c r="O214" s="13" t="inlineStr"/>
       <c r="P214" s="13" t="inlineStr"/>
       <c r="Q214" s="14" t="n">
-        <v>5800000.0</v>
+        <v>4770000.0</v>
       </c>
       <c r="R214" s="14" t="inlineStr"/>
       <c r="S214" s="14" t="n">
@@ -13005,23 +12999,23 @@
       <c r="U214" s="14" t="inlineStr"/>
       <c r="V214" s="14" t="inlineStr"/>
       <c r="W214" s="14" t="n">
-        <v>2942500.0</v>
+        <v>0.0</v>
       </c>
       <c r="X214" s="14" t="n">
-        <v>1399500.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
-        <v>4342000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA214" s="14" t="inlineStr"/>
       <c r="AB214" s="14" t="inlineStr"/>
       <c r="AC214" s="15" t="n">
-        <v>0.7486206896551724</v>
+        <v>0.0</v>
       </c>
       <c r="AD214" s="15" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
-        <v>1458000.0</v>
+        <v>4770000.0</v>
       </c>
       <c r="AF214" s="14" t="inlineStr"/>
       <c r="AG214" s="14" t="inlineStr"/>
@@ -13036,23 +13030,29 @@
       <c r="E215" s="2" t="inlineStr"/>
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="2" t="inlineStr"/>
-      <c r="J215" s="2" t="inlineStr"/>
-      <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="2" t="inlineStr"/>
-      <c r="M215" s="2" t="inlineStr"/>
-      <c r="N215" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
-          </r>
-        </is>
-      </c>
+      <c r="H215" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I215" s="13" t="inlineStr"/>
+      <c r="J215" s="13" t="inlineStr"/>
+      <c r="K215" s="13" t="inlineStr"/>
+      <c r="L215" s="13" t="inlineStr"/>
+      <c r="M215" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N215" s="13" t="inlineStr"/>
       <c r="O215" s="13" t="inlineStr"/>
       <c r="P215" s="13" t="inlineStr"/>
       <c r="Q215" s="14" t="n">
-        <v>4200000.0</v>
+        <v>1.0E7</v>
       </c>
       <c r="R215" s="14" t="inlineStr"/>
       <c r="S215" s="14" t="n">
@@ -13062,23 +13062,23 @@
       <c r="U215" s="14" t="inlineStr"/>
       <c r="V215" s="14" t="inlineStr"/>
       <c r="W215" s="14" t="n">
-        <v>2424000.0</v>
+        <v>6766000.0</v>
       </c>
       <c r="X215" s="14" t="n">
-        <v>0.0</v>
+        <v>1120000.0</v>
       </c>
       <c r="Y215" s="14" t="inlineStr"/>
       <c r="Z215" s="14" t="n">
-        <v>2424000.0</v>
+        <v>7886000.0</v>
       </c>
       <c r="AA215" s="14" t="inlineStr"/>
       <c r="AB215" s="14" t="inlineStr"/>
       <c r="AC215" s="15" t="n">
-        <v>0.5771428571428572</v>
+        <v>0.7886</v>
       </c>
       <c r="AD215" s="15" t="inlineStr"/>
       <c r="AE215" s="14" t="n">
-        <v>1776000.0</v>
+        <v>2114000.0</v>
       </c>
       <c r="AF215" s="14" t="inlineStr"/>
       <c r="AG215" s="14" t="inlineStr"/>
@@ -13093,29 +13093,23 @@
       <c r="E216" s="2" t="inlineStr"/>
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521211</t>
-          </r>
-        </is>
-      </c>
-      <c r="I216" s="13" t="inlineStr"/>
-      <c r="J216" s="13" t="inlineStr"/>
-      <c r="K216" s="13" t="inlineStr"/>
-      <c r="L216" s="13" t="inlineStr"/>
-      <c r="M216" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Bahan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N216" s="13" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr"/>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000133. Biaya Tol</t>
+          </r>
+        </is>
+      </c>
       <c r="O216" s="13" t="inlineStr"/>
       <c r="P216" s="13" t="inlineStr"/>
       <c r="Q216" s="14" t="n">
-        <v>3.2604E7</v>
+        <v>5800000.0</v>
       </c>
       <c r="R216" s="14" t="inlineStr"/>
       <c r="S216" s="14" t="n">
@@ -13125,23 +13119,23 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>1.708458E7</v>
+        <v>4342000.0</v>
       </c>
       <c r="X216" s="14" t="n">
-        <v>8738180.0</v>
+        <v>716000.0</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>2.582276E7</v>
+        <v>5058000.0</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.7920120230646547</v>
+        <v>0.8720689655172413</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>6781240.0</v>
+        <v>742000.0</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
@@ -13165,14 +13159,14 @@
       <c r="N217" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
+            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
           </r>
         </is>
       </c>
       <c r="O217" s="13" t="inlineStr"/>
       <c r="P217" s="13" t="inlineStr"/>
       <c r="Q217" s="14" t="n">
-        <v>3.2604E7</v>
+        <v>4200000.0</v>
       </c>
       <c r="R217" s="14" t="inlineStr"/>
       <c r="S217" s="14" t="n">
@@ -13182,23 +13176,23 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>1.708458E7</v>
+        <v>2424000.0</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>8738180.0</v>
+        <v>404000.0</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>2.582276E7</v>
+        <v>2828000.0</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.7920120230646547</v>
+        <v>0.6733333333333333</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>6781240.0</v>
+        <v>1372000.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
@@ -13216,7 +13210,7 @@
       <c r="H218" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">521811</t>
+            <t xml:space="preserve">521211</t>
           </r>
         </is>
       </c>
@@ -13227,7 +13221,7 @@
       <c r="M218" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+            <t xml:space="preserve">Belanja Bahan</t>
           </r>
         </is>
       </c>
@@ -13235,7 +13229,7 @@
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="n">
-        <v>6000000.0</v>
+        <v>4.6604E7</v>
       </c>
       <c r="R218" s="14" t="inlineStr"/>
       <c r="S218" s="14" t="n">
@@ -13245,23 +13239,23 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>1990000.0</v>
+        <v>2.582276E7</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>957800.0</v>
+        <v>4145000.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>2947800.0</v>
+        <v>2.996776E7</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.4913</v>
+        <v>0.6430297828512574</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>3052200.0</v>
+        <v>1.663624E7</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13285,14 +13279,14 @@
       <c r="N219" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000137. Bahan Komputer</t>
+            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
           </r>
         </is>
       </c>
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>4000000.0</v>
+        <v>4.6604E7</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13302,23 +13296,23 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>1990000.0</v>
+        <v>2.582276E7</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>957800.0</v>
+        <v>4145000.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>2947800.0</v>
+        <v>2.996776E7</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.73695</v>
+        <v>0.6430297828512574</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>1052200.0</v>
+        <v>1.663624E7</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13333,23 +13327,29 @@
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="2" t="inlineStr"/>
-      <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="inlineStr"/>
-      <c r="M220" s="2" t="inlineStr"/>
-      <c r="N220" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000292. ATK</t>
-          </r>
-        </is>
-      </c>
+      <c r="H220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I220" s="13" t="inlineStr"/>
+      <c r="J220" s="13" t="inlineStr"/>
+      <c r="K220" s="13" t="inlineStr"/>
+      <c r="L220" s="13" t="inlineStr"/>
+      <c r="M220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N220" s="13" t="inlineStr"/>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
-        <v>2000000.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="R220" s="14" t="inlineStr"/>
       <c r="S220" s="14" t="n">
@@ -13359,23 +13359,23 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>0.0</v>
+        <v>2947800.0</v>
       </c>
       <c r="X220" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>0.0</v>
+        <v>2947800.0</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.0</v>
+        <v>0.4913</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>2000000.0</v>
+        <v>3052200.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13390,29 +13390,23 @@
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I221" s="13" t="inlineStr"/>
-      <c r="J221" s="13" t="inlineStr"/>
-      <c r="K221" s="13" t="inlineStr"/>
-      <c r="L221" s="13" t="inlineStr"/>
-      <c r="M221" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N221" s="13" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr"/>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000137. Bahan Komputer</t>
+          </r>
+        </is>
+      </c>
       <c r="O221" s="13" t="inlineStr"/>
       <c r="P221" s="13" t="inlineStr"/>
       <c r="Q221" s="14" t="n">
-        <v>3.116438E9</v>
+        <v>4000000.0</v>
       </c>
       <c r="R221" s="14" t="inlineStr"/>
       <c r="S221" s="14" t="n">
@@ -13422,23 +13416,23 @@
       <c r="U221" s="14" t="inlineStr"/>
       <c r="V221" s="14" t="inlineStr"/>
       <c r="W221" s="14" t="n">
-        <v>1.838907052E9</v>
+        <v>2947800.0</v>
       </c>
       <c r="X221" s="14" t="n">
-        <v>2.53636436E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="n">
-        <v>2.092543488E9</v>
+        <v>2947800.0</v>
       </c>
       <c r="AA221" s="14" t="inlineStr"/>
       <c r="AB221" s="14" t="inlineStr"/>
       <c r="AC221" s="15" t="n">
-        <v>0.6714535915683225</v>
+        <v>0.73695</v>
       </c>
       <c r="AD221" s="15" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
-        <v>1.023894512E9</v>
+        <v>1052200.0</v>
       </c>
       <c r="AF221" s="14" t="inlineStr"/>
       <c r="AG221" s="14" t="inlineStr"/>
@@ -13489,7 +13483,7 @@
       <c r="AH222" s="2" t="inlineStr"/>
       <c r="AI222" s="2" t="inlineStr"/>
     </row>
-    <row r="223" customHeight="1" ht="18">
+    <row r="223" customHeight="1" ht="15">
       <c r="A223" s="2" t="inlineStr"/>
       <c r="B223" s="2" t="inlineStr"/>
       <c r="C223" s="2" t="inlineStr"/>
@@ -13506,14 +13500,14 @@
       <c r="N223" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (9 ORG)</t>
+            <t xml:space="preserve">000292. ATK</t>
           </r>
         </is>
       </c>
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
       <c r="Q223" s="14" t="n">
-        <v>5.4E8</v>
+        <v>2000000.0</v>
       </c>
       <c r="R223" s="14" t="inlineStr"/>
       <c r="S223" s="14" t="n">
@@ -13523,23 +13517,23 @@
       <c r="U223" s="14" t="inlineStr"/>
       <c r="V223" s="14" t="inlineStr"/>
       <c r="W223" s="14" t="n">
-        <v>3.27203072E8</v>
+        <v>0.0</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>4.1321696E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>3.68524768E8</v>
+        <v>0.0</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.6824532740740741</v>
+        <v>0.0</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>1.71475232E8</v>
+        <v>2000000.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13554,23 +13548,29 @@
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="2" t="inlineStr"/>
-      <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="2" t="inlineStr"/>
-      <c r="N224" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I224" s="13" t="inlineStr"/>
+      <c r="J224" s="13" t="inlineStr"/>
+      <c r="K224" s="13" t="inlineStr"/>
+      <c r="L224" s="13" t="inlineStr"/>
+      <c r="M224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N224" s="13" t="inlineStr"/>
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
       <c r="Q224" s="14" t="n">
-        <v>1.226E8</v>
+        <v>3.011368E9</v>
       </c>
       <c r="R224" s="14" t="inlineStr"/>
       <c r="S224" s="14" t="n">
@@ -13580,23 +13580,23 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>7.4913296E7</v>
+        <v>2.092543488E9</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>9468528.0</v>
+        <v>2.53636436E8</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>8.4381824E7</v>
+        <v>2.346179924E9</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.6882693637846656</v>
+        <v>0.7791076759798204</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>3.8218176E7</v>
+        <v>6.65188076E8</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13620,14 +13620,14 @@
       <c r="N225" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (3 ORG)</t>
+            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
       <c r="Q225" s="14" t="n">
-        <v>1.8E8</v>
+        <v>4.0995E8</v>
       </c>
       <c r="R225" s="14" t="inlineStr"/>
       <c r="S225" s="14" t="n">
@@ -13637,30 +13637,30 @@
       <c r="U225" s="14" t="inlineStr"/>
       <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="n">
-        <v>1.08758888E8</v>
+        <v>3.68524768E8</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>1.3729784E7</v>
+        <v>4.1321696E7</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>1.22488672E8</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.6804926222222222</v>
+        <v>0.9997474423710209</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>5.7511328E7</v>
+        <v>103536.0</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
       <c r="AH225" s="14" t="inlineStr"/>
       <c r="AI225" s="14" t="inlineStr"/>
     </row>
-    <row r="226" customHeight="1" ht="18">
+    <row r="226" customHeight="1" ht="15">
       <c r="A226" s="2" t="inlineStr"/>
       <c r="B226" s="2" t="inlineStr"/>
       <c r="C226" s="2" t="inlineStr"/>
@@ -13677,14 +13677,14 @@
       <c r="N226" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
       <c r="Q226" s="14" t="n">
-        <v>6.0E7</v>
+        <v>1.226E8</v>
       </c>
       <c r="R226" s="14" t="inlineStr"/>
       <c r="S226" s="14" t="n">
@@ -13694,30 +13694,30 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>3.6626296E7</v>
+        <v>8.4381824E7</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>4629928.0</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>4.1256224E7</v>
+        <v>9.3850352E7</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.6876037333333334</v>
+        <v>0.7655004241435562</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>1.8743776E7</v>
+        <v>2.8749648E7</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
       <c r="AH226" s="14" t="inlineStr"/>
       <c r="AI226" s="14" t="inlineStr"/>
     </row>
-    <row r="227" customHeight="1" ht="15">
+    <row r="227" customHeight="1" ht="18">
       <c r="A227" s="2" t="inlineStr"/>
       <c r="B227" s="2" t="inlineStr"/>
       <c r="C227" s="2" t="inlineStr"/>
@@ -13734,14 +13734,14 @@
       <c r="N227" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
+            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O227" s="13" t="inlineStr"/>
       <c r="P227" s="13" t="inlineStr"/>
       <c r="Q227" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>1.3629E8</v>
       </c>
       <c r="R227" s="14" t="inlineStr"/>
       <c r="S227" s="14" t="n">
@@ -13751,60 +13751,54 @@
       <c r="U227" s="14" t="inlineStr"/>
       <c r="V227" s="14" t="inlineStr"/>
       <c r="W227" s="14" t="n">
-        <v>1.2914055E9</v>
+        <v>1.22488672E8</v>
       </c>
       <c r="X227" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>1.3729784E7</v>
       </c>
       <c r="Y227" s="14" t="inlineStr"/>
       <c r="Z227" s="14" t="n">
-        <v>1.475892E9</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="AA227" s="14" t="inlineStr"/>
       <c r="AB227" s="14" t="inlineStr"/>
       <c r="AC227" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9994750605326876</v>
       </c>
       <c r="AD227" s="15" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
-        <v>7.37946E8</v>
+        <v>71544.0</v>
       </c>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
       <c r="AH227" s="14" t="inlineStr"/>
       <c r="AI227" s="14" t="inlineStr"/>
     </row>
-    <row r="228" customHeight="1" ht="15">
+    <row r="228" customHeight="1" ht="18">
       <c r="A228" s="2" t="inlineStr"/>
       <c r="B228" s="2" t="inlineStr"/>
       <c r="C228" s="2" t="inlineStr"/>
       <c r="D228" s="2" t="inlineStr"/>
       <c r="E228" s="2" t="inlineStr"/>
-      <c r="F228" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DB</t>
-          </r>
-        </is>
-      </c>
-      <c r="G228" s="13" t="inlineStr"/>
-      <c r="H228" s="13" t="inlineStr"/>
-      <c r="I228" s="13" t="inlineStr"/>
-      <c r="J228" s="13" t="inlineStr"/>
-      <c r="K228" s="13" t="inlineStr"/>
-      <c r="L228" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Langganan Daya dan Jasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="M228" s="13" t="inlineStr"/>
-      <c r="N228" s="13" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr"/>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
       <c r="Q228" s="14" t="n">
-        <v>8.72E8</v>
+        <v>4.59E7</v>
       </c>
       <c r="R228" s="14" t="inlineStr"/>
       <c r="S228" s="14" t="n">
@@ -13814,23 +13808,23 @@
       <c r="U228" s="14" t="inlineStr"/>
       <c r="V228" s="14" t="inlineStr"/>
       <c r="W228" s="14" t="n">
-        <v>4.85073724E8</v>
+        <v>4.1256224E7</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>5.0720588E7</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>5.35794312E8</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.6144430183486238</v>
+        <v>0.9996983006535948</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>3.36205688E8</v>
+        <v>13848.0</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13845,29 +13839,23 @@
       <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I229" s="13" t="inlineStr"/>
-      <c r="J229" s="13" t="inlineStr"/>
-      <c r="K229" s="13" t="inlineStr"/>
-      <c r="L229" s="13" t="inlineStr"/>
-      <c r="M229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
-      <c r="N229" s="13" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr"/>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>6.72E8</v>
+        <v>2.213838E9</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13877,30 +13865,30 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>3.52642706E8</v>
+        <v>1.475892E9</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>3.8612524E7</v>
+        <v>1.844865E8</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>3.9125523E8</v>
+        <v>1.6603785E9</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.5822250446428572</v>
+        <v>0.75</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>2.8074477E8</v>
+        <v>5.534595E8</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
       <c r="AH229" s="14" t="inlineStr"/>
       <c r="AI229" s="14" t="inlineStr"/>
     </row>
-    <row r="230" customHeight="1" ht="15">
+    <row r="230" customHeight="1" ht="18">
       <c r="A230" s="2" t="inlineStr"/>
       <c r="B230" s="2" t="inlineStr"/>
       <c r="C230" s="2" t="inlineStr"/>
@@ -13917,14 +13905,14 @@
       <c r="N230" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000145. Langganan Listrik</t>
+            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>6.72E8</v>
+        <v>6.89E7</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13934,30 +13922,30 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>3.52642706E8</v>
+        <v>0.0</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>3.8612524E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>3.9125523E8</v>
+        <v>0.0</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.5822250446428572</v>
+        <v>0.0</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>2.8074477E8</v>
+        <v>6.89E7</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
       <c r="AH230" s="14" t="inlineStr"/>
       <c r="AI230" s="14" t="inlineStr"/>
     </row>
-    <row r="231" customHeight="1" ht="15">
+    <row r="231" customHeight="1" ht="18">
       <c r="A231" s="2" t="inlineStr"/>
       <c r="B231" s="2" t="inlineStr"/>
       <c r="C231" s="2" t="inlineStr"/>
@@ -13965,29 +13953,23 @@
       <c r="E231" s="2" t="inlineStr"/>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522112</t>
-          </r>
-        </is>
-      </c>
-      <c r="I231" s="13" t="inlineStr"/>
-      <c r="J231" s="13" t="inlineStr"/>
-      <c r="K231" s="13" t="inlineStr"/>
-      <c r="L231" s="13" t="inlineStr"/>
-      <c r="M231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
-      <c r="N231" s="13" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O231" s="13" t="inlineStr"/>
       <c r="P231" s="13" t="inlineStr"/>
       <c r="Q231" s="14" t="n">
-        <v>6000000.0</v>
+        <v>1.389E7</v>
       </c>
       <c r="R231" s="14" t="inlineStr"/>
       <c r="S231" s="14" t="n">
@@ -13997,23 +13979,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>4688862.0</v>
+        <v>0.0</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>263514.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>4952376.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.825396</v>
+        <v>0.0</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>1047624.0</v>
+        <v>1.389E7</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14026,25 +14008,31 @@
       <c r="C232" s="2" t="inlineStr"/>
       <c r="D232" s="2" t="inlineStr"/>
       <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr"/>
-      <c r="I232" s="2" t="inlineStr"/>
-      <c r="J232" s="2" t="inlineStr"/>
-      <c r="K232" s="2" t="inlineStr"/>
-      <c r="L232" s="2" t="inlineStr"/>
-      <c r="M232" s="2" t="inlineStr"/>
-      <c r="N232" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000146. Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
+      <c r="F232" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DB</t>
+          </r>
+        </is>
+      </c>
+      <c r="G232" s="13" t="inlineStr"/>
+      <c r="H232" s="13" t="inlineStr"/>
+      <c r="I232" s="13" t="inlineStr"/>
+      <c r="J232" s="13" t="inlineStr"/>
+      <c r="K232" s="13" t="inlineStr"/>
+      <c r="L232" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Langganan Daya dan Jasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="M232" s="13" t="inlineStr"/>
+      <c r="N232" s="13" t="inlineStr"/>
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>6000000.0</v>
+        <v>8.732E8</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14054,23 +14042,23 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>4688862.0</v>
+        <v>5.35794312E8</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>263514.0</v>
+        <v>4.3771056E7</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>4952376.0</v>
+        <v>5.79565368E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.825396</v>
+        <v>0.6637257993586807</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>1047624.0</v>
+        <v>2.93634632E8</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14088,7 +14076,7 @@
       <c r="H233" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">522113</t>
+            <t xml:space="preserve">522111</t>
           </r>
         </is>
       </c>
@@ -14099,7 +14087,7 @@
       <c r="M233" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Langganan Air</t>
+            <t xml:space="preserve">Belanja Langganan Listrik</t>
           </r>
         </is>
       </c>
@@ -14107,7 +14095,7 @@
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>3.96E7</v>
+        <v>6.72E8</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14117,23 +14105,23 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>2.54929E7</v>
+        <v>3.9125523E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>2068600.0</v>
+        <v>3.9011162E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>2.75615E7</v>
+        <v>4.30266392E8</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.6959974747474748</v>
+        <v>0.640277369047619</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>1.20385E7</v>
+        <v>2.41733608E8</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14157,14 +14145,14 @@
       <c r="N234" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
+            <t xml:space="preserve">000145. Langganan Listrik</t>
           </r>
         </is>
       </c>
       <c r="O234" s="13" t="inlineStr"/>
       <c r="P234" s="13" t="inlineStr"/>
       <c r="Q234" s="14" t="n">
-        <v>3.96E7</v>
+        <v>6.72E8</v>
       </c>
       <c r="R234" s="14" t="inlineStr"/>
       <c r="S234" s="14" t="n">
@@ -14174,23 +14162,23 @@
       <c r="U234" s="14" t="inlineStr"/>
       <c r="V234" s="14" t="inlineStr"/>
       <c r="W234" s="14" t="n">
-        <v>2.54929E7</v>
+        <v>3.9125523E8</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>2068600.0</v>
+        <v>3.9011162E7</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>2.75615E7</v>
+        <v>4.30266392E8</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.6959974747474748</v>
+        <v>0.640277369047619</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>1.20385E7</v>
+        <v>2.41733608E8</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14208,7 +14196,7 @@
       <c r="H235" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">522119</t>
+            <t xml:space="preserve">522112</t>
           </r>
         </is>
       </c>
@@ -14219,7 +14207,7 @@
       <c r="M235" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
+            <t xml:space="preserve">Belanja Langganan Telepon</t>
           </r>
         </is>
       </c>
@@ -14227,7 +14215,7 @@
       <c r="O235" s="13" t="inlineStr"/>
       <c r="P235" s="13" t="inlineStr"/>
       <c r="Q235" s="14" t="n">
-        <v>1.544E8</v>
+        <v>6000000.0</v>
       </c>
       <c r="R235" s="14" t="inlineStr"/>
       <c r="S235" s="14" t="n">
@@ -14237,23 +14225,23 @@
       <c r="U235" s="14" t="inlineStr"/>
       <c r="V235" s="14" t="inlineStr"/>
       <c r="W235" s="14" t="n">
-        <v>1.02249256E8</v>
+        <v>4952376.0</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>9775950.0</v>
+        <v>266844.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>1.12025206E8</v>
+        <v>5219220.0</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.7255518523316062</v>
+        <v>0.86987</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>4.2374794E7</v>
+        <v>780780.0</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14277,14 +14265,14 @@
       <c r="N236" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000148. Langganan Internet</t>
+            <t xml:space="preserve">000146. Langganan Telepon</t>
           </r>
         </is>
       </c>
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
-        <v>1.269E8</v>
+        <v>6000000.0</v>
       </c>
       <c r="R236" s="14" t="inlineStr"/>
       <c r="S236" s="14" t="n">
@@ -14294,23 +14282,23 @@
       <c r="U236" s="14" t="inlineStr"/>
       <c r="V236" s="14" t="inlineStr"/>
       <c r="W236" s="14" t="n">
-        <v>7.510765E7</v>
+        <v>4952376.0</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>9775950.0</v>
+        <v>266844.0</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
-        <v>8.48836E7</v>
+        <v>5219220.0</v>
       </c>
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.6689014972419228</v>
+        <v>0.86987</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>4.20164E7</v>
+        <v>780780.0</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
@@ -14325,23 +14313,29 @@
       <c r="E237" s="2" t="inlineStr"/>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr"/>
-      <c r="I237" s="2" t="inlineStr"/>
-      <c r="J237" s="2" t="inlineStr"/>
-      <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="2" t="inlineStr"/>
-      <c r="M237" s="2" t="inlineStr"/>
-      <c r="N237" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
-          </r>
-        </is>
-      </c>
+      <c r="H237" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522113</t>
+          </r>
+        </is>
+      </c>
+      <c r="I237" s="13" t="inlineStr"/>
+      <c r="J237" s="13" t="inlineStr"/>
+      <c r="K237" s="13" t="inlineStr"/>
+      <c r="L237" s="13" t="inlineStr"/>
+      <c r="M237" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Air</t>
+          </r>
+        </is>
+      </c>
+      <c r="N237" s="13" t="inlineStr"/>
       <c r="O237" s="13" t="inlineStr"/>
       <c r="P237" s="13" t="inlineStr"/>
       <c r="Q237" s="14" t="n">
-        <v>2.75E7</v>
+        <v>3.96E7</v>
       </c>
       <c r="R237" s="14" t="inlineStr"/>
       <c r="S237" s="14" t="n">
@@ -14351,23 +14345,23 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>2.7141606E7</v>
+        <v>2.75615E7</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>0.0</v>
+        <v>1387100.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>2.7141606E7</v>
+        <v>2.89486E7</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.9869674909090909</v>
+        <v>0.7310252525252525</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>358394.0</v>
+        <v>1.06514E7</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14380,31 +14374,25 @@
       <c r="C238" s="2" t="inlineStr"/>
       <c r="D238" s="2" t="inlineStr"/>
       <c r="E238" s="2" t="inlineStr"/>
-      <c r="F238" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DC</t>
-          </r>
-        </is>
-      </c>
-      <c r="G238" s="13" t="inlineStr"/>
-      <c r="H238" s="13" t="inlineStr"/>
-      <c r="I238" s="13" t="inlineStr"/>
-      <c r="J238" s="13" t="inlineStr"/>
-      <c r="K238" s="13" t="inlineStr"/>
-      <c r="L238" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pemeliharaan Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M238" s="13" t="inlineStr"/>
-      <c r="N238" s="13" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
+          </r>
+        </is>
+      </c>
       <c r="O238" s="13" t="inlineStr"/>
       <c r="P238" s="13" t="inlineStr"/>
       <c r="Q238" s="14" t="n">
-        <v>7.44735E8</v>
+        <v>3.96E7</v>
       </c>
       <c r="R238" s="14" t="inlineStr"/>
       <c r="S238" s="14" t="n">
@@ -14414,23 +14402,23 @@
       <c r="U238" s="14" t="inlineStr"/>
       <c r="V238" s="14" t="inlineStr"/>
       <c r="W238" s="14" t="n">
-        <v>4.32244343E8</v>
+        <v>2.75615E7</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>3.2499974E7</v>
+        <v>1387100.0</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>4.64744317E8</v>
+        <v>2.89486E7</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.6240398490738316</v>
+        <v>0.7310252525252525</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>2.79990683E8</v>
+        <v>1.06514E7</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -14448,7 +14436,7 @@
       <c r="H239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">521811</t>
+            <t xml:space="preserve">522119</t>
           </r>
         </is>
       </c>
@@ -14459,7 +14447,7 @@
       <c r="M239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
           </r>
         </is>
       </c>
@@ -14467,7 +14455,7 @@
       <c r="O239" s="13" t="inlineStr"/>
       <c r="P239" s="13" t="inlineStr"/>
       <c r="Q239" s="14" t="n">
-        <v>2.2E8</v>
+        <v>1.556E8</v>
       </c>
       <c r="R239" s="14" t="inlineStr"/>
       <c r="S239" s="14" t="n">
@@ -14477,23 +14465,23 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>1.33935E8</v>
+        <v>1.12025206E8</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>1.9675E7</v>
+        <v>3105950.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>1.5361E8</v>
+        <v>1.15131156E8</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.6982272727272727</v>
+        <v>0.7399174550128534</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>6.639E7</v>
+        <v>4.0468844E7</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14517,14 +14505,14 @@
       <c r="N240" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
+            <t xml:space="preserve">000148. Langganan Internet</t>
           </r>
         </is>
       </c>
       <c r="O240" s="13" t="inlineStr"/>
       <c r="P240" s="13" t="inlineStr"/>
       <c r="Q240" s="14" t="n">
-        <v>1.8E8</v>
+        <v>1.269E8</v>
       </c>
       <c r="R240" s="14" t="inlineStr"/>
       <c r="S240" s="14" t="n">
@@ -14534,23 +14522,23 @@
       <c r="U240" s="14" t="inlineStr"/>
       <c r="V240" s="14" t="inlineStr"/>
       <c r="W240" s="14" t="n">
-        <v>1.1394E8</v>
+        <v>8.48836E7</v>
       </c>
       <c r="X240" s="14" t="n">
-        <v>1.9675E7</v>
+        <v>3105950.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>1.33615E8</v>
+        <v>8.798955E7</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.7423055555555556</v>
+        <v>0.6933770685579196</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>4.6385E7</v>
+        <v>3.891045E7</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -14574,14 +14562,14 @@
       <c r="N241" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
+            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
           </r>
         </is>
       </c>
       <c r="O241" s="13" t="inlineStr"/>
       <c r="P241" s="13" t="inlineStr"/>
       <c r="Q241" s="14" t="n">
-        <v>4.0E7</v>
+        <v>2.87E7</v>
       </c>
       <c r="R241" s="14" t="inlineStr"/>
       <c r="S241" s="14" t="n">
@@ -14591,23 +14579,23 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>1.9995E7</v>
+        <v>2.7141606E7</v>
       </c>
       <c r="X241" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>1.9995E7</v>
+        <v>2.7141606E7</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.499875</v>
+        <v>0.9457005574912892</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>2.0005E7</v>
+        <v>1558394.0</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14620,31 +14608,31 @@
       <c r="C242" s="2" t="inlineStr"/>
       <c r="D242" s="2" t="inlineStr"/>
       <c r="E242" s="2" t="inlineStr"/>
-      <c r="F242" s="2" t="inlineStr"/>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
+      <c r="F242" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DC</t>
+          </r>
+        </is>
+      </c>
+      <c r="G242" s="13" t="inlineStr"/>
+      <c r="H242" s="13" t="inlineStr"/>
       <c r="I242" s="13" t="inlineStr"/>
       <c r="J242" s="13" t="inlineStr"/>
       <c r="K242" s="13" t="inlineStr"/>
-      <c r="L242" s="13" t="inlineStr"/>
-      <c r="M242" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
+      <c r="L242" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pemeliharaan Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M242" s="13" t="inlineStr"/>
       <c r="N242" s="13" t="inlineStr"/>
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>3.526E7</v>
+        <v>7.51535E8</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14654,23 +14642,23 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>4.74510617E8</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>0.0</v>
+        <v>1.673E7</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>4.91240617E8</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.7163844299489507</v>
+        <v>0.6536496863086882</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>1.0000285E7</v>
+        <v>2.60294383E8</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14685,23 +14673,29 @@
       <c r="E243" s="2" t="inlineStr"/>
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr"/>
-      <c r="I243" s="2" t="inlineStr"/>
-      <c r="J243" s="2" t="inlineStr"/>
-      <c r="K243" s="2" t="inlineStr"/>
-      <c r="L243" s="2" t="inlineStr"/>
-      <c r="M243" s="2" t="inlineStr"/>
-      <c r="N243" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
-          </r>
-        </is>
-      </c>
+      <c r="H243" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I243" s="13" t="inlineStr"/>
+      <c r="J243" s="13" t="inlineStr"/>
+      <c r="K243" s="13" t="inlineStr"/>
+      <c r="L243" s="13" t="inlineStr"/>
+      <c r="M243" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N243" s="13" t="inlineStr"/>
       <c r="O243" s="13" t="inlineStr"/>
       <c r="P243" s="13" t="inlineStr"/>
       <c r="Q243" s="14" t="n">
-        <v>3.526E7</v>
+        <v>2.2E8</v>
       </c>
       <c r="R243" s="14" t="inlineStr"/>
       <c r="S243" s="14" t="n">
@@ -14711,23 +14705,23 @@
       <c r="U243" s="14" t="inlineStr"/>
       <c r="V243" s="14" t="inlineStr"/>
       <c r="W243" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>1.5361E8</v>
       </c>
       <c r="X243" s="14" t="n">
-        <v>0.0</v>
+        <v>1.002E7</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>1.6363E8</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.7163844299489507</v>
+        <v>0.7437727272727273</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>1.0000285E7</v>
+        <v>5.637E7</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14742,29 +14736,23 @@
       <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I244" s="13" t="inlineStr"/>
-      <c r="J244" s="13" t="inlineStr"/>
-      <c r="K244" s="13" t="inlineStr"/>
-      <c r="L244" s="13" t="inlineStr"/>
-      <c r="M244" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N244" s="13" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr"/>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr"/>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
+          </r>
+        </is>
+      </c>
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>1.97915E8</v>
+        <v>1.8E8</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14774,23 +14762,23 @@
       <c r="U244" s="14" t="inlineStr"/>
       <c r="V244" s="14" t="inlineStr"/>
       <c r="W244" s="14" t="n">
-        <v>1.11081326E8</v>
+        <v>1.33615E8</v>
       </c>
       <c r="X244" s="14" t="n">
-        <v>6040207.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>1.17121533E8</v>
+        <v>1.33615E8</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.5917769395952808</v>
+        <v>0.7423055555555556</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>8.0793467E7</v>
+        <v>4.6385E7</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14814,14 +14802,14 @@
       <c r="N245" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
+            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
           </r>
         </is>
       </c>
       <c r="O245" s="13" t="inlineStr"/>
       <c r="P245" s="13" t="inlineStr"/>
       <c r="Q245" s="14" t="n">
-        <v>2.56E7</v>
+        <v>4.0E7</v>
       </c>
       <c r="R245" s="14" t="inlineStr"/>
       <c r="S245" s="14" t="n">
@@ -14831,30 +14819,30 @@
       <c r="U245" s="14" t="inlineStr"/>
       <c r="V245" s="14" t="inlineStr"/>
       <c r="W245" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>1.9995E7</v>
       </c>
       <c r="X245" s="14" t="n">
-        <v>0.0</v>
+        <v>1.002E7</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>3.0015E7</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.661391484375</v>
+        <v>0.750375</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>8668378.0</v>
+        <v>9985000.0</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
       <c r="AH245" s="14" t="inlineStr"/>
       <c r="AI245" s="14" t="inlineStr"/>
     </row>
-    <row r="246" customHeight="1" ht="18">
+    <row r="246" customHeight="1" ht="15">
       <c r="A246" s="2" t="inlineStr"/>
       <c r="B246" s="2" t="inlineStr"/>
       <c r="C246" s="2" t="inlineStr"/>
@@ -14862,23 +14850,29 @@
       <c r="E246" s="2" t="inlineStr"/>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr"/>
-      <c r="I246" s="2" t="inlineStr"/>
-      <c r="J246" s="2" t="inlineStr"/>
-      <c r="K246" s="2" t="inlineStr"/>
-      <c r="L246" s="2" t="inlineStr"/>
-      <c r="M246" s="2" t="inlineStr"/>
-      <c r="N246" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H246" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I246" s="13" t="inlineStr"/>
+      <c r="J246" s="13" t="inlineStr"/>
+      <c r="K246" s="13" t="inlineStr"/>
+      <c r="L246" s="13" t="inlineStr"/>
+      <c r="M246" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N246" s="13" t="inlineStr"/>
       <c r="O246" s="13" t="inlineStr"/>
       <c r="P246" s="13" t="inlineStr"/>
       <c r="Q246" s="14" t="n">
-        <v>1.575E7</v>
+        <v>3.526E7</v>
       </c>
       <c r="R246" s="14" t="inlineStr"/>
       <c r="S246" s="14" t="n">
@@ -14888,23 +14882,23 @@
       <c r="U246" s="14" t="inlineStr"/>
       <c r="V246" s="14" t="inlineStr"/>
       <c r="W246" s="14" t="n">
-        <v>1.1906299E7</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="X246" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>1.1906299E7</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>0.7559554920634921</v>
+        <v>0.7163844299489507</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>3843701.0</v>
+        <v>1.0000285E7</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -14928,14 +14922,14 @@
       <c r="N247" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
+            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
           </r>
         </is>
       </c>
       <c r="O247" s="13" t="inlineStr"/>
       <c r="P247" s="13" t="inlineStr"/>
       <c r="Q247" s="14" t="n">
-        <v>2.595E7</v>
+        <v>3.526E7</v>
       </c>
       <c r="R247" s="14" t="inlineStr"/>
       <c r="S247" s="14" t="n">
@@ -14945,23 +14939,23 @@
       <c r="U247" s="14" t="inlineStr"/>
       <c r="V247" s="14" t="inlineStr"/>
       <c r="W247" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="X247" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.7163844299489507</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>623000.0</v>
+        <v>1.0000285E7</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -15020,23 +15014,29 @@
       <c r="E249" s="2" t="inlineStr"/>
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr"/>
-      <c r="I249" s="2" t="inlineStr"/>
-      <c r="J249" s="2" t="inlineStr"/>
-      <c r="K249" s="2" t="inlineStr"/>
-      <c r="L249" s="2" t="inlineStr"/>
-      <c r="M249" s="2" t="inlineStr"/>
-      <c r="N249" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H249" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I249" s="13" t="inlineStr"/>
+      <c r="J249" s="13" t="inlineStr"/>
+      <c r="K249" s="13" t="inlineStr"/>
+      <c r="L249" s="13" t="inlineStr"/>
+      <c r="M249" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N249" s="13" t="inlineStr"/>
       <c r="O249" s="13" t="inlineStr"/>
       <c r="P249" s="13" t="inlineStr"/>
       <c r="Q249" s="14" t="n">
-        <v>2170000.0</v>
+        <v>1.93715E8</v>
       </c>
       <c r="R249" s="14" t="inlineStr"/>
       <c r="S249" s="14" t="n">
@@ -15046,23 +15046,23 @@
       <c r="U249" s="14" t="inlineStr"/>
       <c r="V249" s="14" t="inlineStr"/>
       <c r="W249" s="14" t="n">
-        <v>2167000.0</v>
+        <v>1.17121533E8</v>
       </c>
       <c r="X249" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
-        <v>2167000.0</v>
+        <v>1.17121533E8</v>
       </c>
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.9986175115207373</v>
+        <v>0.6046074542498</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>3000.0</v>
+        <v>7.6593467E7</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15086,14 +15086,14 @@
       <c r="N250" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
+            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O250" s="13" t="inlineStr"/>
       <c r="P250" s="13" t="inlineStr"/>
       <c r="Q250" s="14" t="n">
-        <v>2.69E7</v>
+        <v>1.7E7</v>
       </c>
       <c r="R250" s="14" t="inlineStr"/>
       <c r="S250" s="14" t="n">
@@ -15103,30 +15103,30 @@
       <c r="U250" s="14" t="inlineStr"/>
       <c r="V250" s="14" t="inlineStr"/>
       <c r="W250" s="14" t="n">
-        <v>2475000.0</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X250" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
-        <v>2475000.0</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="AA250" s="14" t="inlineStr"/>
       <c r="AB250" s="14" t="inlineStr"/>
       <c r="AC250" s="15" t="n">
-        <v>0.09200743494423792</v>
+        <v>0.9959777647058824</v>
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>2.4425E7</v>
+        <v>68378.0</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
       <c r="AH250" s="14" t="inlineStr"/>
       <c r="AI250" s="14" t="inlineStr"/>
     </row>
-    <row r="251" customHeight="1" ht="15">
+    <row r="251" customHeight="1" ht="18">
       <c r="A251" s="2" t="inlineStr"/>
       <c r="B251" s="2" t="inlineStr"/>
       <c r="C251" s="2" t="inlineStr"/>
@@ -15143,14 +15143,14 @@
       <c r="N251" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
+            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O251" s="13" t="inlineStr"/>
       <c r="P251" s="13" t="inlineStr"/>
       <c r="Q251" s="14" t="n">
-        <v>2800000.0</v>
+        <v>2.695E7</v>
       </c>
       <c r="R251" s="14" t="inlineStr"/>
       <c r="S251" s="14" t="n">
@@ -15160,23 +15160,23 @@
       <c r="U251" s="14" t="inlineStr"/>
       <c r="V251" s="14" t="inlineStr"/>
       <c r="W251" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.1906299E7</v>
       </c>
       <c r="X251" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.1906299E7</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.4417921706864564</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>1440000.0</v>
+        <v>1.5043701E7</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15200,14 +15200,14 @@
       <c r="N252" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
+            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O252" s="13" t="inlineStr"/>
       <c r="P252" s="13" t="inlineStr"/>
       <c r="Q252" s="14" t="n">
-        <v>2.66E7</v>
+        <v>2.595E7</v>
       </c>
       <c r="R252" s="14" t="inlineStr"/>
       <c r="S252" s="14" t="n">
@@ -15217,23 +15217,23 @@
       <c r="U252" s="14" t="inlineStr"/>
       <c r="V252" s="14" t="inlineStr"/>
       <c r="W252" s="14" t="n">
-        <v>6578415.0</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X252" s="14" t="n">
-        <v>5565207.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.45652714285714285</v>
+        <v>0.9759922928709056</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>1.4456378E7</v>
+        <v>623000.0</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15257,14 +15257,14 @@
       <c r="N253" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
+            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O253" s="13" t="inlineStr"/>
       <c r="P253" s="13" t="inlineStr"/>
       <c r="Q253" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2170000.0</v>
       </c>
       <c r="R253" s="14" t="inlineStr"/>
       <c r="S253" s="14" t="n">
@@ -15274,23 +15274,23 @@
       <c r="U253" s="14" t="inlineStr"/>
       <c r="V253" s="14" t="inlineStr"/>
       <c r="W253" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="X253" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9986175115207373</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>0.0</v>
+        <v>3000.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15314,14 +15314,14 @@
       <c r="N254" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
+            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O254" s="13" t="inlineStr"/>
       <c r="P254" s="13" t="inlineStr"/>
       <c r="Q254" s="14" t="n">
-        <v>4115000.0</v>
+        <v>2.69E7</v>
       </c>
       <c r="R254" s="14" t="inlineStr"/>
       <c r="S254" s="14" t="n">
@@ -15331,23 +15331,23 @@
       <c r="U254" s="14" t="inlineStr"/>
       <c r="V254" s="14" t="inlineStr"/>
       <c r="W254" s="14" t="n">
-        <v>1101500.0</v>
+        <v>2475000.0</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>475000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>1576500.0</v>
+        <v>2475000.0</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.3831105710814095</v>
+        <v>0.09200743494423792</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>2538500.0</v>
+        <v>2.4425E7</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>
@@ -15371,14 +15371,14 @@
       <c r="N255" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
+            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O255" s="13" t="inlineStr"/>
       <c r="P255" s="13" t="inlineStr"/>
       <c r="Q255" s="14" t="n">
-        <v>7000000.0</v>
+        <v>2800000.0</v>
       </c>
       <c r="R255" s="14" t="inlineStr"/>
       <c r="S255" s="14" t="n">
@@ -15388,23 +15388,23 @@
       <c r="U255" s="14" t="inlineStr"/>
       <c r="V255" s="14" t="inlineStr"/>
       <c r="W255" s="14" t="n">
-        <v>3880000.0</v>
+        <v>1360000.0</v>
       </c>
       <c r="X255" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>3880000.0</v>
+        <v>1360000.0</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.5542857142857143</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>3120000.0</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15428,14 +15428,14 @@
       <c r="N256" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
+            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
           </r>
         </is>
       </c>
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>2.07E7</v>
+        <v>2.66E7</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15445,23 +15445,23 @@
       <c r="U256" s="14" t="inlineStr"/>
       <c r="V256" s="14" t="inlineStr"/>
       <c r="W256" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="X256" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.7383574879227053</v>
+        <v>0.45652714285714285</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>5416000.0</v>
+        <v>1.4456378E7</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15485,14 +15485,14 @@
       <c r="N257" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
+            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O257" s="13" t="inlineStr"/>
       <c r="P257" s="13" t="inlineStr"/>
       <c r="Q257" s="14" t="n">
-        <v>1.59E7</v>
+        <v>1.443E7</v>
       </c>
       <c r="R257" s="14" t="inlineStr"/>
       <c r="S257" s="14" t="n">
@@ -15502,23 +15502,23 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>0.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="X257" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>0.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>1.59E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15542,14 +15542,14 @@
       <c r="N258" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
+            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O258" s="13" t="inlineStr"/>
       <c r="P258" s="13" t="inlineStr"/>
       <c r="Q258" s="14" t="n">
-        <v>1.0E7</v>
+        <v>4115000.0</v>
       </c>
       <c r="R258" s="14" t="inlineStr"/>
       <c r="S258" s="14" t="n">
@@ -15559,23 +15559,23 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>9640490.0</v>
+        <v>1576500.0</v>
       </c>
       <c r="X258" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>9640490.0</v>
+        <v>1576500.0</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.964049</v>
+        <v>0.3831105710814095</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>359510.0</v>
+        <v>2538500.0</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15590,29 +15590,23 @@
       <c r="E259" s="2" t="inlineStr"/>
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523121</t>
-          </r>
-        </is>
-      </c>
-      <c r="I259" s="13" t="inlineStr"/>
-      <c r="J259" s="13" t="inlineStr"/>
-      <c r="K259" s="13" t="inlineStr"/>
-      <c r="L259" s="13" t="inlineStr"/>
-      <c r="M259" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
-          </r>
-        </is>
-      </c>
-      <c r="N259" s="13" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr"/>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr"/>
+      <c r="M259" s="2" t="inlineStr"/>
+      <c r="N259" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
+          </r>
+        </is>
+      </c>
       <c r="O259" s="13" t="inlineStr"/>
       <c r="P259" s="13" t="inlineStr"/>
       <c r="Q259" s="14" t="n">
-        <v>2.1046E8</v>
+        <v>4400000.0</v>
       </c>
       <c r="R259" s="14" t="inlineStr"/>
       <c r="S259" s="14" t="n">
@@ -15622,23 +15616,23 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>1.00552302E8</v>
+        <v>3880000.0</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>6784767.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>1.07337069E8</v>
+        <v>3880000.0</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.5100117314454053</v>
+        <v>0.8818181818181818</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>1.03122931E8</v>
+        <v>520000.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15662,14 +15656,14 @@
       <c r="N260" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
+            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O260" s="13" t="inlineStr"/>
       <c r="P260" s="13" t="inlineStr"/>
       <c r="Q260" s="14" t="n">
-        <v>1.43E7</v>
+        <v>2.71E7</v>
       </c>
       <c r="R260" s="14" t="inlineStr"/>
       <c r="S260" s="14" t="n">
@@ -15679,23 +15673,23 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>8925000.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>1370000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>1.0295E7</v>
+        <v>1.5284E7</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.7199300699300699</v>
+        <v>0.5639852398523986</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>4005000.0</v>
+        <v>1.1816E7</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15719,14 +15713,14 @@
       <c r="N261" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
+            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O261" s="13" t="inlineStr"/>
       <c r="P261" s="13" t="inlineStr"/>
       <c r="Q261" s="14" t="n">
-        <v>5000000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="R261" s="14" t="inlineStr"/>
       <c r="S261" s="14" t="n">
@@ -15739,20 +15733,20 @@
         <v>0.0</v>
       </c>
       <c r="X261" s="14" t="n">
-        <v>350000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>350000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>4650000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15776,14 +15770,14 @@
       <c r="N262" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
+            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
           </r>
         </is>
       </c>
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>3.0E7</v>
+        <v>1.0E7</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15793,23 +15787,23 @@
       <c r="U262" s="14" t="inlineStr"/>
       <c r="V262" s="14" t="inlineStr"/>
       <c r="W262" s="14" t="n">
-        <v>3861718.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="X262" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y262" s="14" t="inlineStr"/>
       <c r="Z262" s="14" t="n">
-        <v>3861718.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.12872393333333335</v>
+        <v>0.964049</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>2.6138282E7</v>
+        <v>359510.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15833,14 +15827,14 @@
       <c r="N263" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
+            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O263" s="13" t="inlineStr"/>
       <c r="P263" s="13" t="inlineStr"/>
       <c r="Q263" s="14" t="n">
-        <v>1.246E8</v>
+        <v>4300000.0</v>
       </c>
       <c r="R263" s="14" t="inlineStr"/>
       <c r="S263" s="14" t="n">
@@ -15850,23 +15844,23 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>7.0853877E7</v>
+        <v>0.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>3390000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>7.4243877E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.5958577608346709</v>
+        <v>0.0</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>5.0356123E7</v>
+        <v>4300000.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15881,23 +15875,29 @@
       <c r="E264" s="2" t="inlineStr"/>
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr"/>
-      <c r="I264" s="2" t="inlineStr"/>
-      <c r="J264" s="2" t="inlineStr"/>
-      <c r="K264" s="2" t="inlineStr"/>
-      <c r="L264" s="2" t="inlineStr"/>
-      <c r="M264" s="2" t="inlineStr"/>
-      <c r="N264" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
-          </r>
-        </is>
-      </c>
+      <c r="H264" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523121</t>
+          </r>
+        </is>
+      </c>
+      <c r="I264" s="13" t="inlineStr"/>
+      <c r="J264" s="13" t="inlineStr"/>
+      <c r="K264" s="13" t="inlineStr"/>
+      <c r="L264" s="13" t="inlineStr"/>
+      <c r="M264" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
+          </r>
+        </is>
+      </c>
+      <c r="N264" s="13" t="inlineStr"/>
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>4500000.0</v>
+        <v>2.2146E8</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15907,23 +15907,23 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>2410875.0</v>
+        <v>1.17103369E8</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>544027.0</v>
+        <v>6710000.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>2954902.0</v>
+        <v>1.23813369E8</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.6566448888888888</v>
+        <v>0.5590777973448929</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>1545098.0</v>
+        <v>9.7646631E7</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15947,14 +15947,14 @@
       <c r="N265" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
+            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
           </r>
         </is>
       </c>
       <c r="O265" s="13" t="inlineStr"/>
       <c r="P265" s="13" t="inlineStr"/>
       <c r="Q265" s="14" t="n">
-        <v>6000000.0</v>
+        <v>1.43E7</v>
       </c>
       <c r="R265" s="14" t="inlineStr"/>
       <c r="S265" s="14" t="n">
@@ -15964,23 +15964,23 @@
       <c r="U265" s="14" t="inlineStr"/>
       <c r="V265" s="14" t="inlineStr"/>
       <c r="W265" s="14" t="n">
-        <v>4737535.0</v>
+        <v>1.0295E7</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>0.0</v>
+        <v>1385000.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>4737535.0</v>
+        <v>1.168E7</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.7895891666666667</v>
+        <v>0.8167832167832167</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>1262465.0</v>
+        <v>2620000.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -16004,14 +16004,14 @@
       <c r="N266" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
+            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
           </r>
         </is>
       </c>
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>6010000.0</v>
+        <v>5000000.0</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16021,23 +16021,23 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>1000052.0</v>
+        <v>350000.0</v>
       </c>
       <c r="X266" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>1000052.0</v>
+        <v>350000.0</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.166398003327787</v>
+        <v>0.07</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>5009948.0</v>
+        <v>4650000.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16061,14 +16061,14 @@
       <c r="N267" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
           </r>
         </is>
       </c>
       <c r="O267" s="13" t="inlineStr"/>
       <c r="P267" s="13" t="inlineStr"/>
       <c r="Q267" s="14" t="n">
-        <v>4050000.0</v>
+        <v>3.0E7</v>
       </c>
       <c r="R267" s="14" t="inlineStr"/>
       <c r="S267" s="14" t="n">
@@ -16078,23 +16078,23 @@
       <c r="U267" s="14" t="inlineStr"/>
       <c r="V267" s="14" t="inlineStr"/>
       <c r="W267" s="14" t="n">
-        <v>1050000.0</v>
+        <v>3861718.0</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>158480.0</v>
+        <v>500000.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>1208480.0</v>
+        <v>4361718.0</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>0.2983901234567901</v>
+        <v>0.1453906</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>2841520.0</v>
+        <v>2.5638282E7</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16118,14 +16118,14 @@
       <c r="N268" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
+            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
           </r>
         </is>
       </c>
       <c r="O268" s="13" t="inlineStr"/>
       <c r="P268" s="13" t="inlineStr"/>
       <c r="Q268" s="14" t="n">
-        <v>1.0E7</v>
+        <v>1.246E8</v>
       </c>
       <c r="R268" s="14" t="inlineStr"/>
       <c r="S268" s="14" t="n">
@@ -16135,23 +16135,23 @@
       <c r="U268" s="14" t="inlineStr"/>
       <c r="V268" s="14" t="inlineStr"/>
       <c r="W268" s="14" t="n">
-        <v>6055713.0</v>
+        <v>8.3960177E7</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>728900.0</v>
+        <v>3550000.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>6784613.0</v>
+        <v>8.7510177E7</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.6784613</v>
+        <v>0.7023288683788123</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>3215387.0</v>
+        <v>3.7089823E7</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16175,14 +16175,14 @@
       <c r="N269" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
+            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
           </r>
         </is>
       </c>
       <c r="O269" s="13" t="inlineStr"/>
       <c r="P269" s="13" t="inlineStr"/>
       <c r="Q269" s="14" t="n">
-        <v>500000.0</v>
+        <v>4500000.0</v>
       </c>
       <c r="R269" s="14" t="inlineStr"/>
       <c r="S269" s="14" t="n">
@@ -16192,23 +16192,23 @@
       <c r="U269" s="14" t="inlineStr"/>
       <c r="V269" s="14" t="inlineStr"/>
       <c r="W269" s="14" t="n">
-        <v>417558.0</v>
+        <v>3004902.0</v>
       </c>
       <c r="X269" s="14" t="n">
-        <v>0.0</v>
+        <v>135000.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>417558.0</v>
+        <v>3139902.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.835116</v>
+        <v>0.697756</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>82442.0</v>
+        <v>1360098.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16232,14 +16232,14 @@
       <c r="N270" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
+            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
           </r>
         </is>
       </c>
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>5000000.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16249,23 +16249,23 @@
       <c r="U270" s="14" t="inlineStr"/>
       <c r="V270" s="14" t="inlineStr"/>
       <c r="W270" s="14" t="n">
-        <v>969974.0</v>
+        <v>4737535.0</v>
       </c>
       <c r="X270" s="14" t="n">
-        <v>243360.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>1213334.0</v>
+        <v>4737535.0</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.2426668</v>
+        <v>0.7895891666666667</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>3786666.0</v>
+        <v>1262465.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16289,14 +16289,14 @@
       <c r="N271" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
           </r>
         </is>
       </c>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>500000.0</v>
+        <v>6010000.0</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16306,23 +16306,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>270000.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="X271" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>270000.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.54</v>
+        <v>0.166398003327787</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>230000.0</v>
+        <v>5009948.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16337,29 +16337,23 @@
       <c r="E272" s="2" t="inlineStr"/>
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523132</t>
-          </r>
-        </is>
-      </c>
-      <c r="I272" s="13" t="inlineStr"/>
-      <c r="J272" s="13" t="inlineStr"/>
-      <c r="K272" s="13" t="inlineStr"/>
-      <c r="L272" s="13" t="inlineStr"/>
-      <c r="M272" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N272" s="13" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr"/>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+          </r>
+        </is>
+      </c>
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>8.11E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16369,23 +16363,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>1208480.0</v>
       </c>
       <c r="X272" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>1208480.0</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.7572872996300863</v>
+        <v>0.2983901234567901</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>1.9684E7</v>
+        <v>2841520.0</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16409,14 +16403,14 @@
       <c r="N273" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
+            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
           </r>
         </is>
       </c>
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>3.91E7</v>
+        <v>1.0E7</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16426,23 +16420,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>3.909E7</v>
+        <v>6784613.0</v>
       </c>
       <c r="X273" s="14" t="n">
-        <v>0.0</v>
+        <v>910000.0</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>3.909E7</v>
+        <v>7694613.0</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.9997442455242966</v>
+        <v>0.7694613</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>10000.0</v>
+        <v>2305387.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16466,14 +16460,14 @@
       <c r="N274" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
+            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
           </r>
         </is>
       </c>
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>3.0E7</v>
+        <v>1500000.0</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16483,23 +16477,23 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>1.155E7</v>
+        <v>417558.0</v>
       </c>
       <c r="X274" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.155E7</v>
+        <v>417558.0</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.385</v>
+        <v>0.278372</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>1.845E7</v>
+        <v>1082442.0</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16567,14 +16561,14 @@
       <c r="N276" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
           </r>
         </is>
       </c>
       <c r="O276" s="13" t="inlineStr"/>
       <c r="P276" s="13" t="inlineStr"/>
       <c r="Q276" s="14" t="n">
-        <v>1.2E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R276" s="14" t="inlineStr"/>
       <c r="S276" s="14" t="n">
@@ -16584,23 +16578,23 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>1213334.0</v>
       </c>
       <c r="X276" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>1213334.0</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.898</v>
+        <v>0.2426668</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>1224000.0</v>
+        <v>3786666.0</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
@@ -16613,31 +16607,25 @@
       <c r="C277" s="2" t="inlineStr"/>
       <c r="D277" s="2" t="inlineStr"/>
       <c r="E277" s="2" t="inlineStr"/>
-      <c r="F277" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DD</t>
-          </r>
-        </is>
-      </c>
-      <c r="G277" s="13" t="inlineStr"/>
-      <c r="H277" s="13" t="inlineStr"/>
-      <c r="I277" s="13" t="inlineStr"/>
-      <c r="J277" s="13" t="inlineStr"/>
-      <c r="K277" s="13" t="inlineStr"/>
-      <c r="L277" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M277" s="13" t="inlineStr"/>
-      <c r="N277" s="13" t="inlineStr"/>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr"/>
+      <c r="I277" s="2" t="inlineStr"/>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr"/>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+          </r>
+        </is>
+      </c>
       <c r="O277" s="13" t="inlineStr"/>
       <c r="P277" s="13" t="inlineStr"/>
       <c r="Q277" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>500000.0</v>
       </c>
       <c r="R277" s="14" t="inlineStr"/>
       <c r="S277" s="14" t="n">
@@ -16647,23 +16635,23 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>7.975E7</v>
+        <v>270000.0</v>
       </c>
       <c r="X277" s="14" t="n">
-        <v>1.039E7</v>
+        <v>230000.0</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>9.014E7</v>
+        <v>500000.0</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.6819488576183992</v>
+        <v>1.0</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>4.204E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
@@ -16678,29 +16666,23 @@
       <c r="E278" s="2" t="inlineStr"/>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521115</t>
-          </r>
-        </is>
-      </c>
-      <c r="I278" s="13" t="inlineStr"/>
-      <c r="J278" s="13" t="inlineStr"/>
-      <c r="K278" s="13" t="inlineStr"/>
-      <c r="L278" s="13" t="inlineStr"/>
-      <c r="M278" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
-          </r>
-        </is>
-      </c>
-      <c r="N278" s="13" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr"/>
+      <c r="I278" s="2" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr"/>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
+          </r>
+        </is>
+      </c>
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>1.2468E8</v>
+        <v>1.0E7</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16710,23 +16692,23 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>7.225E7</v>
+        <v>0.0</v>
       </c>
       <c r="X278" s="14" t="n">
-        <v>1.039E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>8.264E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="15" t="n">
-        <v>0.6628168110362528</v>
+        <v>0.0</v>
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>4.204E7</v>
+        <v>1.0E7</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
@@ -16741,23 +16723,29 @@
       <c r="E279" s="2" t="inlineStr"/>
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr"/>
-      <c r="I279" s="2" t="inlineStr"/>
-      <c r="J279" s="2" t="inlineStr"/>
-      <c r="K279" s="2" t="inlineStr"/>
-      <c r="L279" s="2" t="inlineStr"/>
-      <c r="M279" s="2" t="inlineStr"/>
-      <c r="N279" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
-          </r>
-        </is>
-      </c>
+      <c r="H279" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523132</t>
+          </r>
+        </is>
+      </c>
+      <c r="I279" s="13" t="inlineStr"/>
+      <c r="J279" s="13" t="inlineStr"/>
+      <c r="K279" s="13" t="inlineStr"/>
+      <c r="L279" s="13" t="inlineStr"/>
+      <c r="M279" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N279" s="13" t="inlineStr"/>
       <c r="O279" s="13" t="inlineStr"/>
       <c r="P279" s="13" t="inlineStr"/>
       <c r="Q279" s="14" t="n">
-        <v>3.06E7</v>
+        <v>8.11E7</v>
       </c>
       <c r="R279" s="14" t="inlineStr"/>
       <c r="S279" s="14" t="n">
@@ -16767,23 +16755,23 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>1.785E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>2550000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>2.04E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7572872996300863</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>1.02E7</v>
+        <v>1.9684E7</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
@@ -16807,14 +16795,14 @@
       <c r="N280" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
+            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O280" s="13" t="inlineStr"/>
       <c r="P280" s="13" t="inlineStr"/>
       <c r="Q280" s="14" t="n">
-        <v>2.976E7</v>
+        <v>3.91E7</v>
       </c>
       <c r="R280" s="14" t="inlineStr"/>
       <c r="S280" s="14" t="n">
@@ -16824,30 +16812,30 @@
       <c r="U280" s="14" t="inlineStr"/>
       <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="n">
-        <v>1.736E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>2480000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>1.984E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
       <c r="AC280" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9997442455242966</v>
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
-        <v>9920000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="AF280" s="14" t="inlineStr"/>
       <c r="AG280" s="14" t="inlineStr"/>
       <c r="AH280" s="14" t="inlineStr"/>
       <c r="AI280" s="14" t="inlineStr"/>
     </row>
-    <row r="281" customHeight="1" ht="18">
+    <row r="281" customHeight="1" ht="15">
       <c r="A281" s="2" t="inlineStr"/>
       <c r="B281" s="2" t="inlineStr"/>
       <c r="C281" s="2" t="inlineStr"/>
@@ -16864,14 +16852,14 @@
       <c r="N281" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O281" s="13" t="inlineStr"/>
       <c r="P281" s="13" t="inlineStr"/>
       <c r="Q281" s="14" t="n">
-        <v>1.476E7</v>
+        <v>3.0E7</v>
       </c>
       <c r="R281" s="14" t="inlineStr"/>
       <c r="S281" s="14" t="n">
@@ -16881,23 +16869,23 @@
       <c r="U281" s="14" t="inlineStr"/>
       <c r="V281" s="14" t="inlineStr"/>
       <c r="W281" s="14" t="n">
-        <v>8610000.0</v>
+        <v>1.155E7</v>
       </c>
       <c r="X281" s="14" t="n">
-        <v>1230000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y281" s="14" t="inlineStr"/>
       <c r="Z281" s="14" t="n">
-        <v>9840000.0</v>
+        <v>1.155E7</v>
       </c>
       <c r="AA281" s="14" t="inlineStr"/>
       <c r="AB281" s="14" t="inlineStr"/>
       <c r="AC281" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.385</v>
       </c>
       <c r="AD281" s="15" t="inlineStr"/>
       <c r="AE281" s="14" t="n">
-        <v>4920000.0</v>
+        <v>1.845E7</v>
       </c>
       <c r="AF281" s="14" t="inlineStr"/>
       <c r="AG281" s="14" t="inlineStr"/>
@@ -16921,14 +16909,14 @@
       <c r="N282" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
+            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O282" s="13" t="inlineStr"/>
       <c r="P282" s="13" t="inlineStr"/>
       <c r="Q282" s="14" t="n">
-        <v>1.284E7</v>
+        <v>1.2E7</v>
       </c>
       <c r="R282" s="14" t="inlineStr"/>
       <c r="S282" s="14" t="n">
@@ -16938,23 +16926,23 @@
       <c r="U282" s="14" t="inlineStr"/>
       <c r="V282" s="14" t="inlineStr"/>
       <c r="W282" s="14" t="n">
-        <v>7490000.0</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X282" s="14" t="n">
-        <v>1070000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>8560000.0</v>
+        <v>1.0776E7</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
       <c r="AC282" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.898</v>
       </c>
       <c r="AD282" s="15" t="inlineStr"/>
       <c r="AE282" s="14" t="n">
-        <v>4280000.0</v>
+        <v>1224000.0</v>
       </c>
       <c r="AF282" s="14" t="inlineStr"/>
       <c r="AG282" s="14" t="inlineStr"/>
@@ -16967,25 +16955,31 @@
       <c r="C283" s="2" t="inlineStr"/>
       <c r="D283" s="2" t="inlineStr"/>
       <c r="E283" s="2" t="inlineStr"/>
-      <c r="F283" s="2" t="inlineStr"/>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr"/>
-      <c r="I283" s="2" t="inlineStr"/>
-      <c r="J283" s="2" t="inlineStr"/>
-      <c r="K283" s="2" t="inlineStr"/>
-      <c r="L283" s="2" t="inlineStr"/>
-      <c r="M283" s="2" t="inlineStr"/>
-      <c r="N283" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
-          </r>
-        </is>
-      </c>
+      <c r="F283" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DD</t>
+          </r>
+        </is>
+      </c>
+      <c r="G283" s="13" t="inlineStr"/>
+      <c r="H283" s="13" t="inlineStr"/>
+      <c r="I283" s="13" t="inlineStr"/>
+      <c r="J283" s="13" t="inlineStr"/>
+      <c r="K283" s="13" t="inlineStr"/>
+      <c r="L283" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M283" s="13" t="inlineStr"/>
+      <c r="N283" s="13" t="inlineStr"/>
       <c r="O283" s="13" t="inlineStr"/>
       <c r="P283" s="13" t="inlineStr"/>
       <c r="Q283" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.3218E8</v>
       </c>
       <c r="R283" s="14" t="inlineStr"/>
       <c r="S283" s="14" t="n">
@@ -16995,23 +16989,23 @@
       <c r="U283" s="14" t="inlineStr"/>
       <c r="V283" s="14" t="inlineStr"/>
       <c r="W283" s="14" t="n">
-        <v>1.68E7</v>
+        <v>9.014E7</v>
       </c>
       <c r="X283" s="14" t="n">
-        <v>2400000.0</v>
+        <v>1.039E7</v>
       </c>
       <c r="Y283" s="14" t="inlineStr"/>
       <c r="Z283" s="14" t="n">
-        <v>1.92E7</v>
+        <v>1.0053E8</v>
       </c>
       <c r="AA283" s="14" t="inlineStr"/>
       <c r="AB283" s="14" t="inlineStr"/>
       <c r="AC283" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7605537902859737</v>
       </c>
       <c r="AD283" s="15" t="inlineStr"/>
       <c r="AE283" s="14" t="n">
-        <v>9600000.0</v>
+        <v>3.165E7</v>
       </c>
       <c r="AF283" s="14" t="inlineStr"/>
       <c r="AG283" s="14" t="inlineStr"/>
@@ -17026,23 +17020,29 @@
       <c r="E284" s="2" t="inlineStr"/>
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="2" t="inlineStr"/>
-      <c r="I284" s="2" t="inlineStr"/>
-      <c r="J284" s="2" t="inlineStr"/>
-      <c r="K284" s="2" t="inlineStr"/>
-      <c r="L284" s="2" t="inlineStr"/>
-      <c r="M284" s="2" t="inlineStr"/>
-      <c r="N284" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H284" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521115</t>
+          </r>
+        </is>
+      </c>
+      <c r="I284" s="13" t="inlineStr"/>
+      <c r="J284" s="13" t="inlineStr"/>
+      <c r="K284" s="13" t="inlineStr"/>
+      <c r="L284" s="13" t="inlineStr"/>
+      <c r="M284" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+          </r>
+        </is>
+      </c>
+      <c r="N284" s="13" t="inlineStr"/>
       <c r="O284" s="13" t="inlineStr"/>
       <c r="P284" s="13" t="inlineStr"/>
       <c r="Q284" s="14" t="n">
-        <v>3600000.0</v>
+        <v>1.2468E8</v>
       </c>
       <c r="R284" s="14" t="inlineStr"/>
       <c r="S284" s="14" t="n">
@@ -17052,30 +17052,30 @@
       <c r="U284" s="14" t="inlineStr"/>
       <c r="V284" s="14" t="inlineStr"/>
       <c r="W284" s="14" t="n">
-        <v>1800000.0</v>
+        <v>8.264E7</v>
       </c>
       <c r="X284" s="14" t="n">
-        <v>300000.0</v>
+        <v>1.039E7</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
-        <v>2100000.0</v>
+        <v>9.303E7</v>
       </c>
       <c r="AA284" s="14" t="inlineStr"/>
       <c r="AB284" s="14" t="inlineStr"/>
       <c r="AC284" s="15" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7461501443695862</v>
       </c>
       <c r="AD284" s="15" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
-        <v>1500000.0</v>
+        <v>3.165E7</v>
       </c>
       <c r="AF284" s="14" t="inlineStr"/>
       <c r="AG284" s="14" t="inlineStr"/>
       <c r="AH284" s="14" t="inlineStr"/>
       <c r="AI284" s="14" t="inlineStr"/>
     </row>
-    <row r="285" customHeight="1" ht="18">
+    <row r="285" customHeight="1" ht="15">
       <c r="A285" s="2" t="inlineStr"/>
       <c r="B285" s="2" t="inlineStr"/>
       <c r="C285" s="2" t="inlineStr"/>
@@ -17092,14 +17092,14 @@
       <c r="N285" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
           </r>
         </is>
       </c>
       <c r="O285" s="13" t="inlineStr"/>
       <c r="P285" s="13" t="inlineStr"/>
       <c r="Q285" s="14" t="n">
-        <v>4320000.0</v>
+        <v>3.06E7</v>
       </c>
       <c r="R285" s="14" t="inlineStr"/>
       <c r="S285" s="14" t="n">
@@ -17109,23 +17109,23 @@
       <c r="U285" s="14" t="inlineStr"/>
       <c r="V285" s="14" t="inlineStr"/>
       <c r="W285" s="14" t="n">
-        <v>2340000.0</v>
+        <v>2.04E7</v>
       </c>
       <c r="X285" s="14" t="n">
-        <v>360000.0</v>
+        <v>2550000.0</v>
       </c>
       <c r="Y285" s="14" t="inlineStr"/>
       <c r="Z285" s="14" t="n">
-        <v>2700000.0</v>
+        <v>2.295E7</v>
       </c>
       <c r="AA285" s="14" t="inlineStr"/>
       <c r="AB285" s="14" t="inlineStr"/>
       <c r="AC285" s="15" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="AD285" s="15" t="inlineStr"/>
       <c r="AE285" s="14" t="n">
-        <v>1620000.0</v>
+        <v>7650000.0</v>
       </c>
       <c r="AF285" s="14" t="inlineStr"/>
       <c r="AG285" s="14" t="inlineStr"/>
@@ -17140,29 +17140,23 @@
       <c r="E286" s="2" t="inlineStr"/>
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I286" s="13" t="inlineStr"/>
-      <c r="J286" s="13" t="inlineStr"/>
-      <c r="K286" s="13" t="inlineStr"/>
-      <c r="L286" s="13" t="inlineStr"/>
-      <c r="M286" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N286" s="13" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr"/>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr"/>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
+          </r>
+        </is>
+      </c>
       <c r="O286" s="13" t="inlineStr"/>
       <c r="P286" s="13" t="inlineStr"/>
       <c r="Q286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2.976E7</v>
       </c>
       <c r="R286" s="14" t="inlineStr"/>
       <c r="S286" s="14" t="n">
@@ -17172,30 +17166,30 @@
       <c r="U286" s="14" t="inlineStr"/>
       <c r="V286" s="14" t="inlineStr"/>
       <c r="W286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>1.984E7</v>
       </c>
       <c r="X286" s="14" t="n">
-        <v>0.0</v>
+        <v>2480000.0</v>
       </c>
       <c r="Y286" s="14" t="inlineStr"/>
       <c r="Z286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2.232E7</v>
       </c>
       <c r="AA286" s="14" t="inlineStr"/>
       <c r="AB286" s="14" t="inlineStr"/>
       <c r="AC286" s="15" t="n">
-        <v>1.0</v>
+        <v>0.75</v>
       </c>
       <c r="AD286" s="15" t="inlineStr"/>
       <c r="AE286" s="14" t="n">
-        <v>0.0</v>
+        <v>7440000.0</v>
       </c>
       <c r="AF286" s="14" t="inlineStr"/>
       <c r="AG286" s="14" t="inlineStr"/>
       <c r="AH286" s="14" t="inlineStr"/>
       <c r="AI286" s="14" t="inlineStr"/>
     </row>
-    <row r="287" customHeight="1" ht="15">
+    <row r="287" customHeight="1" ht="18">
       <c r="A287" s="2" t="inlineStr"/>
       <c r="B287" s="2" t="inlineStr"/>
       <c r="C287" s="2" t="inlineStr"/>
@@ -17212,14 +17206,14 @@
       <c r="N287" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
           </r>
         </is>
       </c>
       <c r="O287" s="13" t="inlineStr"/>
       <c r="P287" s="13" t="inlineStr"/>
       <c r="Q287" s="14" t="n">
-        <v>7500000.0</v>
+        <v>1.476E7</v>
       </c>
       <c r="R287" s="14" t="inlineStr"/>
       <c r="S287" s="14" t="n">
@@ -17229,23 +17223,23 @@
       <c r="U287" s="14" t="inlineStr"/>
       <c r="V287" s="14" t="inlineStr"/>
       <c r="W287" s="14" t="n">
-        <v>7500000.0</v>
+        <v>9840000.0</v>
       </c>
       <c r="X287" s="14" t="n">
-        <v>0.0</v>
+        <v>1230000.0</v>
       </c>
       <c r="Y287" s="14" t="inlineStr"/>
       <c r="Z287" s="14" t="n">
-        <v>7500000.0</v>
+        <v>1.107E7</v>
       </c>
       <c r="AA287" s="14" t="inlineStr"/>
       <c r="AB287" s="14" t="inlineStr"/>
       <c r="AC287" s="15" t="n">
-        <v>1.0</v>
+        <v>0.75</v>
       </c>
       <c r="AD287" s="15" t="inlineStr"/>
       <c r="AE287" s="14" t="n">
-        <v>0.0</v>
+        <v>3690000.0</v>
       </c>
       <c r="AF287" s="14" t="inlineStr"/>
       <c r="AG287" s="14" t="inlineStr"/>
@@ -17255,223 +17249,199 @@
     <row r="288" customHeight="1" ht="15">
       <c r="A288" s="2" t="inlineStr"/>
       <c r="B288" s="2" t="inlineStr"/>
-      <c r="C288" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D288" s="16" t="inlineStr"/>
-      <c r="E288" s="16" t="inlineStr"/>
-      <c r="F288" s="16" t="inlineStr"/>
-      <c r="G288" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H288" s="16" t="inlineStr"/>
-      <c r="I288" s="16" t="inlineStr"/>
-      <c r="J288" s="16" t="inlineStr"/>
-      <c r="K288" s="16" t="inlineStr"/>
-      <c r="L288" s="16" t="inlineStr"/>
-      <c r="M288" s="16" t="inlineStr"/>
-      <c r="N288" s="16" t="inlineStr"/>
-      <c r="O288" s="16" t="inlineStr"/>
-      <c r="P288" s="16" t="inlineStr"/>
-      <c r="Q288" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R288" s="17" t="inlineStr"/>
-      <c r="S288" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T288" s="17" t="inlineStr"/>
-      <c r="U288" s="17" t="inlineStr"/>
-      <c r="V288" s="17" t="inlineStr"/>
-      <c r="W288" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X288" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y288" s="17" t="inlineStr"/>
-      <c r="Z288" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA288" s="17" t="inlineStr"/>
-      <c r="AB288" s="17" t="inlineStr"/>
-      <c r="AC288" s="18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD288" s="18" t="inlineStr"/>
-      <c r="AE288" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF288" s="17" t="inlineStr"/>
-      <c r="AG288" s="17" t="inlineStr"/>
-      <c r="AH288" s="17" t="inlineStr"/>
-      <c r="AI288" s="17" t="inlineStr"/>
+      <c r="C288" s="2" t="inlineStr"/>
+      <c r="D288" s="2" t="inlineStr"/>
+      <c r="E288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr"/>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
+          </r>
+        </is>
+      </c>
+      <c r="O288" s="13" t="inlineStr"/>
+      <c r="P288" s="13" t="inlineStr"/>
+      <c r="Q288" s="14" t="n">
+        <v>1.284E7</v>
+      </c>
+      <c r="R288" s="14" t="inlineStr"/>
+      <c r="S288" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T288" s="14" t="inlineStr"/>
+      <c r="U288" s="14" t="inlineStr"/>
+      <c r="V288" s="14" t="inlineStr"/>
+      <c r="W288" s="14" t="n">
+        <v>8560000.0</v>
+      </c>
+      <c r="X288" s="14" t="n">
+        <v>1070000.0</v>
+      </c>
+      <c r="Y288" s="14" t="inlineStr"/>
+      <c r="Z288" s="14" t="n">
+        <v>9630000.0</v>
+      </c>
+      <c r="AA288" s="14" t="inlineStr"/>
+      <c r="AB288" s="14" t="inlineStr"/>
+      <c r="AC288" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD288" s="15" t="inlineStr"/>
+      <c r="AE288" s="14" t="n">
+        <v>3210000.0</v>
+      </c>
+      <c r="AF288" s="14" t="inlineStr"/>
+      <c r="AG288" s="14" t="inlineStr"/>
+      <c r="AH288" s="14" t="inlineStr"/>
+      <c r="AI288" s="14" t="inlineStr"/>
     </row>
     <row r="289" customHeight="1" ht="15">
       <c r="A289" s="2" t="inlineStr"/>
       <c r="B289" s="2" t="inlineStr"/>
-      <c r="C289" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D289" s="28" t="inlineStr"/>
-      <c r="E289" s="28" t="inlineStr"/>
-      <c r="F289" s="28" t="inlineStr"/>
-      <c r="G289" s="28" t="inlineStr"/>
-      <c r="H289" s="28" t="inlineStr"/>
-      <c r="I289" s="28" t="inlineStr"/>
-      <c r="J289" s="28" t="inlineStr"/>
-      <c r="K289" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L289" s="20" t="inlineStr"/>
-      <c r="M289" s="20" t="inlineStr"/>
-      <c r="N289" s="20" t="inlineStr"/>
-      <c r="O289" s="20" t="inlineStr"/>
-      <c r="P289" s="20" t="inlineStr"/>
-      <c r="Q289" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R289" s="21" t="inlineStr"/>
-      <c r="S289" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T289" s="21" t="inlineStr"/>
-      <c r="U289" s="21" t="inlineStr"/>
-      <c r="V289" s="21" t="inlineStr"/>
-      <c r="W289" s="22" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X289" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y289" s="22" t="inlineStr"/>
-      <c r="Z289" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA289" s="21" t="inlineStr"/>
-      <c r="AB289" s="21" t="inlineStr"/>
-      <c r="AC289" s="23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD289" s="23" t="inlineStr"/>
-      <c r="AE289" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF289" s="21" t="inlineStr"/>
-      <c r="AG289" s="21" t="inlineStr"/>
-      <c r="AH289" s="21" t="inlineStr"/>
-      <c r="AI289" s="21" t="inlineStr"/>
+      <c r="C289" s="2" t="inlineStr"/>
+      <c r="D289" s="2" t="inlineStr"/>
+      <c r="E289" s="2" t="inlineStr"/>
+      <c r="F289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr"/>
+      <c r="I289" s="2" t="inlineStr"/>
+      <c r="J289" s="2" t="inlineStr"/>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr"/>
+      <c r="M289" s="2" t="inlineStr"/>
+      <c r="N289" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
+          </r>
+        </is>
+      </c>
+      <c r="O289" s="13" t="inlineStr"/>
+      <c r="P289" s="13" t="inlineStr"/>
+      <c r="Q289" s="14" t="n">
+        <v>2.88E7</v>
+      </c>
+      <c r="R289" s="14" t="inlineStr"/>
+      <c r="S289" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T289" s="14" t="inlineStr"/>
+      <c r="U289" s="14" t="inlineStr"/>
+      <c r="V289" s="14" t="inlineStr"/>
+      <c r="W289" s="14" t="n">
+        <v>1.92E7</v>
+      </c>
+      <c r="X289" s="14" t="n">
+        <v>2400000.0</v>
+      </c>
+      <c r="Y289" s="14" t="inlineStr"/>
+      <c r="Z289" s="14" t="n">
+        <v>2.16E7</v>
+      </c>
+      <c r="AA289" s="14" t="inlineStr"/>
+      <c r="AB289" s="14" t="inlineStr"/>
+      <c r="AC289" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD289" s="15" t="inlineStr"/>
+      <c r="AE289" s="14" t="n">
+        <v>7200000.0</v>
+      </c>
+      <c r="AF289" s="14" t="inlineStr"/>
+      <c r="AG289" s="14" t="inlineStr"/>
+      <c r="AH289" s="14" t="inlineStr"/>
+      <c r="AI289" s="14" t="inlineStr"/>
     </row>
     <row r="290" customHeight="1" ht="15">
       <c r="A290" s="2" t="inlineStr"/>
       <c r="B290" s="2" t="inlineStr"/>
       <c r="C290" s="2" t="inlineStr"/>
       <c r="D290" s="2" t="inlineStr"/>
-      <c r="E290" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F290" s="24" t="inlineStr"/>
-      <c r="G290" s="24" t="inlineStr"/>
-      <c r="H290" s="24" t="inlineStr"/>
-      <c r="I290" s="24" t="inlineStr"/>
-      <c r="J290" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K290" s="24" t="inlineStr"/>
-      <c r="L290" s="24" t="inlineStr"/>
-      <c r="M290" s="24" t="inlineStr"/>
-      <c r="N290" s="24" t="inlineStr"/>
-      <c r="O290" s="24" t="inlineStr"/>
-      <c r="P290" s="24" t="inlineStr"/>
-      <c r="Q290" s="25" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R290" s="25" t="inlineStr"/>
-      <c r="S290" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T290" s="25" t="inlineStr"/>
-      <c r="U290" s="25" t="inlineStr"/>
-      <c r="V290" s="25" t="inlineStr"/>
-      <c r="W290" s="25" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X290" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y290" s="25" t="inlineStr"/>
-      <c r="Z290" s="25" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA290" s="25" t="inlineStr"/>
-      <c r="AB290" s="25" t="inlineStr"/>
-      <c r="AC290" s="26" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD290" s="26" t="inlineStr"/>
-      <c r="AE290" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF290" s="25" t="inlineStr"/>
-      <c r="AG290" s="25" t="inlineStr"/>
-      <c r="AH290" s="25" t="inlineStr"/>
-      <c r="AI290" s="25" t="inlineStr"/>
-    </row>
-    <row r="291" customHeight="1" ht="15">
+      <c r="E290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr"/>
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr"/>
+      <c r="J290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr"/>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O290" s="13" t="inlineStr"/>
+      <c r="P290" s="13" t="inlineStr"/>
+      <c r="Q290" s="14" t="n">
+        <v>3600000.0</v>
+      </c>
+      <c r="R290" s="14" t="inlineStr"/>
+      <c r="S290" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T290" s="14" t="inlineStr"/>
+      <c r="U290" s="14" t="inlineStr"/>
+      <c r="V290" s="14" t="inlineStr"/>
+      <c r="W290" s="14" t="n">
+        <v>2100000.0</v>
+      </c>
+      <c r="X290" s="14" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="Y290" s="14" t="inlineStr"/>
+      <c r="Z290" s="14" t="n">
+        <v>2400000.0</v>
+      </c>
+      <c r="AA290" s="14" t="inlineStr"/>
+      <c r="AB290" s="14" t="inlineStr"/>
+      <c r="AC290" s="15" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AD290" s="15" t="inlineStr"/>
+      <c r="AE290" s="14" t="n">
+        <v>1200000.0</v>
+      </c>
+      <c r="AF290" s="14" t="inlineStr"/>
+      <c r="AG290" s="14" t="inlineStr"/>
+      <c r="AH290" s="14" t="inlineStr"/>
+      <c r="AI290" s="14" t="inlineStr"/>
+    </row>
+    <row r="291" customHeight="1" ht="18">
       <c r="A291" s="2" t="inlineStr"/>
       <c r="B291" s="2" t="inlineStr"/>
       <c r="C291" s="2" t="inlineStr"/>
       <c r="D291" s="2" t="inlineStr"/>
       <c r="E291" s="2" t="inlineStr"/>
-      <c r="F291" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G291" s="13" t="inlineStr"/>
-      <c r="H291" s="13" t="inlineStr"/>
-      <c r="I291" s="13" t="inlineStr"/>
-      <c r="J291" s="13" t="inlineStr"/>
-      <c r="K291" s="13" t="inlineStr"/>
-      <c r="L291" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M291" s="13" t="inlineStr"/>
-      <c r="N291" s="13" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="2" t="inlineStr"/>
+      <c r="I291" s="2" t="inlineStr"/>
+      <c r="J291" s="2" t="inlineStr"/>
+      <c r="K291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr"/>
+      <c r="M291" s="2" t="inlineStr"/>
+      <c r="N291" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+          </r>
+        </is>
+      </c>
       <c r="O291" s="13" t="inlineStr"/>
       <c r="P291" s="13" t="inlineStr"/>
       <c r="Q291" s="14" t="n">
-        <v>600000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="R291" s="14" t="inlineStr"/>
       <c r="S291" s="14" t="n">
@@ -17481,23 +17451,23 @@
       <c r="U291" s="14" t="inlineStr"/>
       <c r="V291" s="14" t="inlineStr"/>
       <c r="W291" s="14" t="n">
-        <v>600000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="X291" s="14" t="n">
-        <v>0.0</v>
+        <v>360000.0</v>
       </c>
       <c r="Y291" s="14" t="inlineStr"/>
       <c r="Z291" s="14" t="n">
-        <v>600000.0</v>
+        <v>3060000.0</v>
       </c>
       <c r="AA291" s="14" t="inlineStr"/>
       <c r="AB291" s="14" t="inlineStr"/>
       <c r="AC291" s="15" t="n">
-        <v>1.0</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="AD291" s="15" t="inlineStr"/>
       <c r="AE291" s="14" t="n">
-        <v>0.0</v>
+        <v>1260000.0</v>
       </c>
       <c r="AF291" s="14" t="inlineStr"/>
       <c r="AG291" s="14" t="inlineStr"/>
@@ -17515,7 +17485,7 @@
       <c r="H292" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">524111</t>
+            <t xml:space="preserve">521119</t>
           </r>
         </is>
       </c>
@@ -17526,7 +17496,7 @@
       <c r="M292" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
           </r>
         </is>
       </c>
@@ -17534,7 +17504,7 @@
       <c r="O292" s="13" t="inlineStr"/>
       <c r="P292" s="13" t="inlineStr"/>
       <c r="Q292" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="R292" s="14" t="inlineStr"/>
       <c r="S292" s="14" t="n">
@@ -17544,14 +17514,14 @@
       <c r="U292" s="14" t="inlineStr"/>
       <c r="V292" s="14" t="inlineStr"/>
       <c r="W292" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="X292" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y292" s="14" t="inlineStr"/>
       <c r="Z292" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="AA292" s="14" t="inlineStr"/>
       <c r="AB292" s="14" t="inlineStr"/>
@@ -17584,14 +17554,14 @@
       <c r="N293" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000231. Uang Harian</t>
+            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
           </r>
         </is>
       </c>
       <c r="O293" s="13" t="inlineStr"/>
       <c r="P293" s="13" t="inlineStr"/>
       <c r="Q293" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="R293" s="14" t="inlineStr"/>
       <c r="S293" s="14" t="n">
@@ -17601,14 +17571,14 @@
       <c r="U293" s="14" t="inlineStr"/>
       <c r="V293" s="14" t="inlineStr"/>
       <c r="W293" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="X293" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y293" s="14" t="inlineStr"/>
       <c r="Z293" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="AA293" s="14" t="inlineStr"/>
       <c r="AB293" s="14" t="inlineStr"/>
@@ -17624,9 +17594,381 @@
       <c r="AH293" s="14" t="inlineStr"/>
       <c r="AI293" s="14" t="inlineStr"/>
     </row>
-    <row r="294" customHeight="1" ht="24">
+    <row r="294" customHeight="1" ht="15">
       <c r="A294" s="2" t="inlineStr"/>
-      <c r="B294" s="27" t="inlineStr">
+      <c r="B294" s="2" t="inlineStr"/>
+      <c r="C294" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D294" s="16" t="inlineStr"/>
+      <c r="E294" s="16" t="inlineStr"/>
+      <c r="F294" s="16" t="inlineStr"/>
+      <c r="G294" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H294" s="16" t="inlineStr"/>
+      <c r="I294" s="16" t="inlineStr"/>
+      <c r="J294" s="16" t="inlineStr"/>
+      <c r="K294" s="16" t="inlineStr"/>
+      <c r="L294" s="16" t="inlineStr"/>
+      <c r="M294" s="16" t="inlineStr"/>
+      <c r="N294" s="16" t="inlineStr"/>
+      <c r="O294" s="16" t="inlineStr"/>
+      <c r="P294" s="16" t="inlineStr"/>
+      <c r="Q294" s="17" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R294" s="17" t="inlineStr"/>
+      <c r="S294" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T294" s="17" t="inlineStr"/>
+      <c r="U294" s="17" t="inlineStr"/>
+      <c r="V294" s="17" t="inlineStr"/>
+      <c r="W294" s="17" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X294" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y294" s="17" t="inlineStr"/>
+      <c r="Z294" s="17" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA294" s="17" t="inlineStr"/>
+      <c r="AB294" s="17" t="inlineStr"/>
+      <c r="AC294" s="18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD294" s="18" t="inlineStr"/>
+      <c r="AE294" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF294" s="17" t="inlineStr"/>
+      <c r="AG294" s="17" t="inlineStr"/>
+      <c r="AH294" s="17" t="inlineStr"/>
+      <c r="AI294" s="17" t="inlineStr"/>
+    </row>
+    <row r="295" customHeight="1" ht="15">
+      <c r="A295" s="2" t="inlineStr"/>
+      <c r="B295" s="2" t="inlineStr"/>
+      <c r="C295" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D295" s="28" t="inlineStr"/>
+      <c r="E295" s="28" t="inlineStr"/>
+      <c r="F295" s="28" t="inlineStr"/>
+      <c r="G295" s="28" t="inlineStr"/>
+      <c r="H295" s="28" t="inlineStr"/>
+      <c r="I295" s="28" t="inlineStr"/>
+      <c r="J295" s="28" t="inlineStr"/>
+      <c r="K295" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L295" s="20" t="inlineStr"/>
+      <c r="M295" s="20" t="inlineStr"/>
+      <c r="N295" s="20" t="inlineStr"/>
+      <c r="O295" s="20" t="inlineStr"/>
+      <c r="P295" s="20" t="inlineStr"/>
+      <c r="Q295" s="21" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R295" s="21" t="inlineStr"/>
+      <c r="S295" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T295" s="21" t="inlineStr"/>
+      <c r="U295" s="21" t="inlineStr"/>
+      <c r="V295" s="21" t="inlineStr"/>
+      <c r="W295" s="22" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X295" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y295" s="22" t="inlineStr"/>
+      <c r="Z295" s="21" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA295" s="21" t="inlineStr"/>
+      <c r="AB295" s="21" t="inlineStr"/>
+      <c r="AC295" s="23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD295" s="23" t="inlineStr"/>
+      <c r="AE295" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF295" s="21" t="inlineStr"/>
+      <c r="AG295" s="21" t="inlineStr"/>
+      <c r="AH295" s="21" t="inlineStr"/>
+      <c r="AI295" s="21" t="inlineStr"/>
+    </row>
+    <row r="296" customHeight="1" ht="15">
+      <c r="A296" s="2" t="inlineStr"/>
+      <c r="B296" s="2" t="inlineStr"/>
+      <c r="C296" s="2" t="inlineStr"/>
+      <c r="D296" s="2" t="inlineStr"/>
+      <c r="E296" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F296" s="24" t="inlineStr"/>
+      <c r="G296" s="24" t="inlineStr"/>
+      <c r="H296" s="24" t="inlineStr"/>
+      <c r="I296" s="24" t="inlineStr"/>
+      <c r="J296" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K296" s="24" t="inlineStr"/>
+      <c r="L296" s="24" t="inlineStr"/>
+      <c r="M296" s="24" t="inlineStr"/>
+      <c r="N296" s="24" t="inlineStr"/>
+      <c r="O296" s="24" t="inlineStr"/>
+      <c r="P296" s="24" t="inlineStr"/>
+      <c r="Q296" s="25" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R296" s="25" t="inlineStr"/>
+      <c r="S296" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T296" s="25" t="inlineStr"/>
+      <c r="U296" s="25" t="inlineStr"/>
+      <c r="V296" s="25" t="inlineStr"/>
+      <c r="W296" s="25" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X296" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y296" s="25" t="inlineStr"/>
+      <c r="Z296" s="25" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA296" s="25" t="inlineStr"/>
+      <c r="AB296" s="25" t="inlineStr"/>
+      <c r="AC296" s="26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD296" s="26" t="inlineStr"/>
+      <c r="AE296" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF296" s="25" t="inlineStr"/>
+      <c r="AG296" s="25" t="inlineStr"/>
+      <c r="AH296" s="25" t="inlineStr"/>
+      <c r="AI296" s="25" t="inlineStr"/>
+    </row>
+    <row r="297" customHeight="1" ht="15">
+      <c r="A297" s="2" t="inlineStr"/>
+      <c r="B297" s="2" t="inlineStr"/>
+      <c r="C297" s="2" t="inlineStr"/>
+      <c r="D297" s="2" t="inlineStr"/>
+      <c r="E297" s="2" t="inlineStr"/>
+      <c r="F297" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G297" s="13" t="inlineStr"/>
+      <c r="H297" s="13" t="inlineStr"/>
+      <c r="I297" s="13" t="inlineStr"/>
+      <c r="J297" s="13" t="inlineStr"/>
+      <c r="K297" s="13" t="inlineStr"/>
+      <c r="L297" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M297" s="13" t="inlineStr"/>
+      <c r="N297" s="13" t="inlineStr"/>
+      <c r="O297" s="13" t="inlineStr"/>
+      <c r="P297" s="13" t="inlineStr"/>
+      <c r="Q297" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R297" s="14" t="inlineStr"/>
+      <c r="S297" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T297" s="14" t="inlineStr"/>
+      <c r="U297" s="14" t="inlineStr"/>
+      <c r="V297" s="14" t="inlineStr"/>
+      <c r="W297" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X297" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y297" s="14" t="inlineStr"/>
+      <c r="Z297" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA297" s="14" t="inlineStr"/>
+      <c r="AB297" s="14" t="inlineStr"/>
+      <c r="AC297" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD297" s="15" t="inlineStr"/>
+      <c r="AE297" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF297" s="14" t="inlineStr"/>
+      <c r="AG297" s="14" t="inlineStr"/>
+      <c r="AH297" s="14" t="inlineStr"/>
+      <c r="AI297" s="14" t="inlineStr"/>
+    </row>
+    <row r="298" customHeight="1" ht="15">
+      <c r="A298" s="2" t="inlineStr"/>
+      <c r="B298" s="2" t="inlineStr"/>
+      <c r="C298" s="2" t="inlineStr"/>
+      <c r="D298" s="2" t="inlineStr"/>
+      <c r="E298" s="2" t="inlineStr"/>
+      <c r="F298" s="2" t="inlineStr"/>
+      <c r="G298" s="2" t="inlineStr"/>
+      <c r="H298" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I298" s="13" t="inlineStr"/>
+      <c r="J298" s="13" t="inlineStr"/>
+      <c r="K298" s="13" t="inlineStr"/>
+      <c r="L298" s="13" t="inlineStr"/>
+      <c r="M298" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N298" s="13" t="inlineStr"/>
+      <c r="O298" s="13" t="inlineStr"/>
+      <c r="P298" s="13" t="inlineStr"/>
+      <c r="Q298" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R298" s="14" t="inlineStr"/>
+      <c r="S298" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T298" s="14" t="inlineStr"/>
+      <c r="U298" s="14" t="inlineStr"/>
+      <c r="V298" s="14" t="inlineStr"/>
+      <c r="W298" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X298" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y298" s="14" t="inlineStr"/>
+      <c r="Z298" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA298" s="14" t="inlineStr"/>
+      <c r="AB298" s="14" t="inlineStr"/>
+      <c r="AC298" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD298" s="15" t="inlineStr"/>
+      <c r="AE298" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF298" s="14" t="inlineStr"/>
+      <c r="AG298" s="14" t="inlineStr"/>
+      <c r="AH298" s="14" t="inlineStr"/>
+      <c r="AI298" s="14" t="inlineStr"/>
+    </row>
+    <row r="299" customHeight="1" ht="15">
+      <c r="A299" s="2" t="inlineStr"/>
+      <c r="B299" s="2" t="inlineStr"/>
+      <c r="C299" s="2" t="inlineStr"/>
+      <c r="D299" s="2" t="inlineStr"/>
+      <c r="E299" s="2" t="inlineStr"/>
+      <c r="F299" s="2" t="inlineStr"/>
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr"/>
+      <c r="I299" s="2" t="inlineStr"/>
+      <c r="J299" s="2" t="inlineStr"/>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr"/>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000231. Uang Harian</t>
+          </r>
+        </is>
+      </c>
+      <c r="O299" s="13" t="inlineStr"/>
+      <c r="P299" s="13" t="inlineStr"/>
+      <c r="Q299" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R299" s="14" t="inlineStr"/>
+      <c r="S299" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T299" s="14" t="inlineStr"/>
+      <c r="U299" s="14" t="inlineStr"/>
+      <c r="V299" s="14" t="inlineStr"/>
+      <c r="W299" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X299" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y299" s="14" t="inlineStr"/>
+      <c r="Z299" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA299" s="14" t="inlineStr"/>
+      <c r="AB299" s="14" t="inlineStr"/>
+      <c r="AC299" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD299" s="15" t="inlineStr"/>
+      <c r="AE299" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF299" s="14" t="inlineStr"/>
+      <c r="AG299" s="14" t="inlineStr"/>
+      <c r="AH299" s="14" t="inlineStr"/>
+      <c r="AI299" s="14" t="inlineStr"/>
+    </row>
+    <row r="300" customHeight="1" ht="24">
+      <c r="A300" s="2" t="inlineStr"/>
+      <c r="B300" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.
@@ -17634,39 +17976,39 @@
           </r>
         </is>
       </c>
-      <c r="C294" s="27" t="inlineStr"/>
-      <c r="D294" s="27" t="inlineStr"/>
-      <c r="E294" s="27" t="inlineStr"/>
-      <c r="F294" s="27" t="inlineStr"/>
-      <c r="G294" s="27" t="inlineStr"/>
-      <c r="H294" s="27" t="inlineStr"/>
-      <c r="I294" s="27" t="inlineStr"/>
-      <c r="J294" s="27" t="inlineStr"/>
-      <c r="K294" s="27" t="inlineStr"/>
-      <c r="L294" s="27" t="inlineStr"/>
-      <c r="M294" s="27" t="inlineStr"/>
-      <c r="N294" s="27" t="inlineStr"/>
-      <c r="O294" s="27" t="inlineStr"/>
-      <c r="P294" s="27" t="inlineStr"/>
-      <c r="Q294" s="27" t="inlineStr"/>
-      <c r="R294" s="27" t="inlineStr"/>
-      <c r="S294" s="27" t="inlineStr"/>
-      <c r="T294" s="27" t="inlineStr"/>
-      <c r="U294" s="27" t="inlineStr"/>
-      <c r="V294" s="27" t="inlineStr"/>
-      <c r="W294" s="27" t="inlineStr"/>
-      <c r="X294" s="27" t="inlineStr"/>
-      <c r="Y294" s="27" t="inlineStr"/>
-      <c r="Z294" s="27" t="inlineStr"/>
-      <c r="AA294" s="27" t="inlineStr"/>
-      <c r="AB294" s="27" t="inlineStr"/>
-      <c r="AC294" s="27" t="inlineStr"/>
-      <c r="AD294" s="27" t="inlineStr"/>
-      <c r="AE294" s="27" t="inlineStr"/>
-      <c r="AF294" s="27" t="inlineStr"/>
-      <c r="AG294" s="2" t="inlineStr"/>
-      <c r="AH294" s="2" t="inlineStr"/>
-      <c r="AI294" s="2" t="inlineStr"/>
+      <c r="C300" s="27" t="inlineStr"/>
+      <c r="D300" s="27" t="inlineStr"/>
+      <c r="E300" s="27" t="inlineStr"/>
+      <c r="F300" s="27" t="inlineStr"/>
+      <c r="G300" s="27" t="inlineStr"/>
+      <c r="H300" s="27" t="inlineStr"/>
+      <c r="I300" s="27" t="inlineStr"/>
+      <c r="J300" s="27" t="inlineStr"/>
+      <c r="K300" s="27" t="inlineStr"/>
+      <c r="L300" s="27" t="inlineStr"/>
+      <c r="M300" s="27" t="inlineStr"/>
+      <c r="N300" s="27" t="inlineStr"/>
+      <c r="O300" s="27" t="inlineStr"/>
+      <c r="P300" s="27" t="inlineStr"/>
+      <c r="Q300" s="27" t="inlineStr"/>
+      <c r="R300" s="27" t="inlineStr"/>
+      <c r="S300" s="27" t="inlineStr"/>
+      <c r="T300" s="27" t="inlineStr"/>
+      <c r="U300" s="27" t="inlineStr"/>
+      <c r="V300" s="27" t="inlineStr"/>
+      <c r="W300" s="27" t="inlineStr"/>
+      <c r="X300" s="27" t="inlineStr"/>
+      <c r="Y300" s="27" t="inlineStr"/>
+      <c r="Z300" s="27" t="inlineStr"/>
+      <c r="AA300" s="27" t="inlineStr"/>
+      <c r="AB300" s="27" t="inlineStr"/>
+      <c r="AC300" s="27" t="inlineStr"/>
+      <c r="AD300" s="27" t="inlineStr"/>
+      <c r="AE300" s="27" t="inlineStr"/>
+      <c r="AF300" s="27" t="inlineStr"/>
+      <c r="AG300" s="2" t="inlineStr"/>
+      <c r="AH300" s="2" t="inlineStr"/>
+      <c r="AI300" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -19142,8 +19484,7 @@
     <mergeCell ref="Z212:AB212"/>
     <mergeCell ref="AC212:AD212"/>
     <mergeCell ref="AE212:AI212"/>
-    <mergeCell ref="H213:L213"/>
-    <mergeCell ref="M213:P213"/>
+    <mergeCell ref="N213:P213"/>
     <mergeCell ref="Q213:R213"/>
     <mergeCell ref="S213:V213"/>
     <mergeCell ref="X213:Y213"/>
@@ -19157,15 +19498,15 @@
     <mergeCell ref="Z214:AB214"/>
     <mergeCell ref="AC214:AD214"/>
     <mergeCell ref="AE214:AI214"/>
-    <mergeCell ref="N215:P215"/>
+    <mergeCell ref="H215:L215"/>
+    <mergeCell ref="M215:P215"/>
     <mergeCell ref="Q215:R215"/>
     <mergeCell ref="S215:V215"/>
     <mergeCell ref="X215:Y215"/>
     <mergeCell ref="Z215:AB215"/>
     <mergeCell ref="AC215:AD215"/>
     <mergeCell ref="AE215:AI215"/>
-    <mergeCell ref="H216:L216"/>
-    <mergeCell ref="M216:P216"/>
+    <mergeCell ref="N216:P216"/>
     <mergeCell ref="Q216:R216"/>
     <mergeCell ref="S216:V216"/>
     <mergeCell ref="X216:Y216"/>
@@ -19194,15 +19535,15 @@
     <mergeCell ref="Z219:AB219"/>
     <mergeCell ref="AC219:AD219"/>
     <mergeCell ref="AE219:AI219"/>
-    <mergeCell ref="N220:P220"/>
+    <mergeCell ref="H220:L220"/>
+    <mergeCell ref="M220:P220"/>
     <mergeCell ref="Q220:R220"/>
     <mergeCell ref="S220:V220"/>
     <mergeCell ref="X220:Y220"/>
     <mergeCell ref="Z220:AB220"/>
     <mergeCell ref="AC220:AD220"/>
     <mergeCell ref="AE220:AI220"/>
-    <mergeCell ref="H221:L221"/>
-    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="N221:P221"/>
     <mergeCell ref="Q221:R221"/>
     <mergeCell ref="S221:V221"/>
     <mergeCell ref="X221:Y221"/>
@@ -19217,7 +19558,8 @@
     <mergeCell ref="Z223:AB223"/>
     <mergeCell ref="AC223:AD223"/>
     <mergeCell ref="AE223:AI223"/>
-    <mergeCell ref="N224:P224"/>
+    <mergeCell ref="H224:L224"/>
+    <mergeCell ref="M224:P224"/>
     <mergeCell ref="Q224:R224"/>
     <mergeCell ref="S224:V224"/>
     <mergeCell ref="X224:Y224"/>
@@ -19245,16 +19587,14 @@
     <mergeCell ref="Z227:AB227"/>
     <mergeCell ref="AC227:AD227"/>
     <mergeCell ref="AE227:AI227"/>
-    <mergeCell ref="F228:K228"/>
-    <mergeCell ref="L228:P228"/>
+    <mergeCell ref="N228:P228"/>
     <mergeCell ref="Q228:R228"/>
     <mergeCell ref="S228:V228"/>
     <mergeCell ref="X228:Y228"/>
     <mergeCell ref="Z228:AB228"/>
     <mergeCell ref="AC228:AD228"/>
     <mergeCell ref="AE228:AI228"/>
-    <mergeCell ref="H229:L229"/>
-    <mergeCell ref="M229:P229"/>
+    <mergeCell ref="N229:P229"/>
     <mergeCell ref="Q229:R229"/>
     <mergeCell ref="S229:V229"/>
     <mergeCell ref="X229:Y229"/>
@@ -19268,15 +19608,15 @@
     <mergeCell ref="Z230:AB230"/>
     <mergeCell ref="AC230:AD230"/>
     <mergeCell ref="AE230:AI230"/>
-    <mergeCell ref="H231:L231"/>
-    <mergeCell ref="M231:P231"/>
+    <mergeCell ref="N231:P231"/>
     <mergeCell ref="Q231:R231"/>
     <mergeCell ref="S231:V231"/>
     <mergeCell ref="X231:Y231"/>
     <mergeCell ref="Z231:AB231"/>
     <mergeCell ref="AC231:AD231"/>
     <mergeCell ref="AE231:AI231"/>
-    <mergeCell ref="N232:P232"/>
+    <mergeCell ref="F232:K232"/>
+    <mergeCell ref="L232:P232"/>
     <mergeCell ref="Q232:R232"/>
     <mergeCell ref="S232:V232"/>
     <mergeCell ref="X232:Y232"/>
@@ -19313,15 +19653,15 @@
     <mergeCell ref="Z236:AB236"/>
     <mergeCell ref="AC236:AD236"/>
     <mergeCell ref="AE236:AI236"/>
-    <mergeCell ref="N237:P237"/>
+    <mergeCell ref="H237:L237"/>
+    <mergeCell ref="M237:P237"/>
     <mergeCell ref="Q237:R237"/>
     <mergeCell ref="S237:V237"/>
     <mergeCell ref="X237:Y237"/>
     <mergeCell ref="Z237:AB237"/>
     <mergeCell ref="AC237:AD237"/>
     <mergeCell ref="AE237:AI237"/>
-    <mergeCell ref="F238:K238"/>
-    <mergeCell ref="L238:P238"/>
+    <mergeCell ref="N238:P238"/>
     <mergeCell ref="Q238:R238"/>
     <mergeCell ref="S238:V238"/>
     <mergeCell ref="X238:Y238"/>
@@ -19350,23 +19690,23 @@
     <mergeCell ref="Z241:AB241"/>
     <mergeCell ref="AC241:AD241"/>
     <mergeCell ref="AE241:AI241"/>
-    <mergeCell ref="H242:L242"/>
-    <mergeCell ref="M242:P242"/>
+    <mergeCell ref="F242:K242"/>
+    <mergeCell ref="L242:P242"/>
     <mergeCell ref="Q242:R242"/>
     <mergeCell ref="S242:V242"/>
     <mergeCell ref="X242:Y242"/>
     <mergeCell ref="Z242:AB242"/>
     <mergeCell ref="AC242:AD242"/>
     <mergeCell ref="AE242:AI242"/>
-    <mergeCell ref="N243:P243"/>
+    <mergeCell ref="H243:L243"/>
+    <mergeCell ref="M243:P243"/>
     <mergeCell ref="Q243:R243"/>
     <mergeCell ref="S243:V243"/>
     <mergeCell ref="X243:Y243"/>
     <mergeCell ref="Z243:AB243"/>
     <mergeCell ref="AC243:AD243"/>
     <mergeCell ref="AE243:AI243"/>
-    <mergeCell ref="H244:L244"/>
-    <mergeCell ref="M244:P244"/>
+    <mergeCell ref="N244:P244"/>
     <mergeCell ref="Q244:R244"/>
     <mergeCell ref="S244:V244"/>
     <mergeCell ref="X244:Y244"/>
@@ -19380,7 +19720,8 @@
     <mergeCell ref="Z245:AB245"/>
     <mergeCell ref="AC245:AD245"/>
     <mergeCell ref="AE245:AI245"/>
-    <mergeCell ref="N246:P246"/>
+    <mergeCell ref="H246:L246"/>
+    <mergeCell ref="M246:P246"/>
     <mergeCell ref="Q246:R246"/>
     <mergeCell ref="S246:V246"/>
     <mergeCell ref="X246:Y246"/>
@@ -19395,7 +19736,8 @@
     <mergeCell ref="AC247:AD247"/>
     <mergeCell ref="AE247:AI247"/>
     <mergeCell ref="B248:AF248"/>
-    <mergeCell ref="N249:P249"/>
+    <mergeCell ref="H249:L249"/>
+    <mergeCell ref="M249:P249"/>
     <mergeCell ref="Q249:R249"/>
     <mergeCell ref="S249:V249"/>
     <mergeCell ref="X249:Y249"/>
@@ -19465,8 +19807,7 @@
     <mergeCell ref="Z258:AB258"/>
     <mergeCell ref="AC258:AD258"/>
     <mergeCell ref="AE258:AI258"/>
-    <mergeCell ref="H259:L259"/>
-    <mergeCell ref="M259:P259"/>
+    <mergeCell ref="N259:P259"/>
     <mergeCell ref="Q259:R259"/>
     <mergeCell ref="S259:V259"/>
     <mergeCell ref="X259:Y259"/>
@@ -19501,7 +19842,8 @@
     <mergeCell ref="Z263:AB263"/>
     <mergeCell ref="AC263:AD263"/>
     <mergeCell ref="AE263:AI263"/>
-    <mergeCell ref="N264:P264"/>
+    <mergeCell ref="H264:L264"/>
+    <mergeCell ref="M264:P264"/>
     <mergeCell ref="Q264:R264"/>
     <mergeCell ref="S264:V264"/>
     <mergeCell ref="X264:Y264"/>
@@ -19557,8 +19899,7 @@
     <mergeCell ref="Z271:AB271"/>
     <mergeCell ref="AC271:AD271"/>
     <mergeCell ref="AE271:AI271"/>
-    <mergeCell ref="H272:L272"/>
-    <mergeCell ref="M272:P272"/>
+    <mergeCell ref="N272:P272"/>
     <mergeCell ref="Q272:R272"/>
     <mergeCell ref="S272:V272"/>
     <mergeCell ref="X272:Y272"/>
@@ -19587,23 +19928,22 @@
     <mergeCell ref="Z276:AB276"/>
     <mergeCell ref="AC276:AD276"/>
     <mergeCell ref="AE276:AI276"/>
-    <mergeCell ref="F277:K277"/>
-    <mergeCell ref="L277:P277"/>
+    <mergeCell ref="N277:P277"/>
     <mergeCell ref="Q277:R277"/>
     <mergeCell ref="S277:V277"/>
     <mergeCell ref="X277:Y277"/>
     <mergeCell ref="Z277:AB277"/>
     <mergeCell ref="AC277:AD277"/>
     <mergeCell ref="AE277:AI277"/>
-    <mergeCell ref="H278:L278"/>
-    <mergeCell ref="M278:P278"/>
+    <mergeCell ref="N278:P278"/>
     <mergeCell ref="Q278:R278"/>
     <mergeCell ref="S278:V278"/>
     <mergeCell ref="X278:Y278"/>
     <mergeCell ref="Z278:AB278"/>
     <mergeCell ref="AC278:AD278"/>
     <mergeCell ref="AE278:AI278"/>
-    <mergeCell ref="N279:P279"/>
+    <mergeCell ref="H279:L279"/>
+    <mergeCell ref="M279:P279"/>
     <mergeCell ref="Q279:R279"/>
     <mergeCell ref="S279:V279"/>
     <mergeCell ref="X279:Y279"/>
@@ -19631,14 +19971,16 @@
     <mergeCell ref="Z282:AB282"/>
     <mergeCell ref="AC282:AD282"/>
     <mergeCell ref="AE282:AI282"/>
-    <mergeCell ref="N283:P283"/>
+    <mergeCell ref="F283:K283"/>
+    <mergeCell ref="L283:P283"/>
     <mergeCell ref="Q283:R283"/>
     <mergeCell ref="S283:V283"/>
     <mergeCell ref="X283:Y283"/>
     <mergeCell ref="Z283:AB283"/>
     <mergeCell ref="AC283:AD283"/>
     <mergeCell ref="AE283:AI283"/>
-    <mergeCell ref="N284:P284"/>
+    <mergeCell ref="H284:L284"/>
+    <mergeCell ref="M284:P284"/>
     <mergeCell ref="Q284:R284"/>
     <mergeCell ref="S284:V284"/>
     <mergeCell ref="X284:Y284"/>
@@ -19652,8 +19994,7 @@
     <mergeCell ref="Z285:AB285"/>
     <mergeCell ref="AC285:AD285"/>
     <mergeCell ref="AE285:AI285"/>
-    <mergeCell ref="H286:L286"/>
-    <mergeCell ref="M286:P286"/>
+    <mergeCell ref="N286:P286"/>
     <mergeCell ref="Q286:R286"/>
     <mergeCell ref="S286:V286"/>
     <mergeCell ref="X286:Y286"/>
@@ -19667,32 +20008,28 @@
     <mergeCell ref="Z287:AB287"/>
     <mergeCell ref="AC287:AD287"/>
     <mergeCell ref="AE287:AI287"/>
-    <mergeCell ref="C288:F288"/>
-    <mergeCell ref="G288:P288"/>
+    <mergeCell ref="N288:P288"/>
     <mergeCell ref="Q288:R288"/>
     <mergeCell ref="S288:V288"/>
     <mergeCell ref="X288:Y288"/>
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="C289:J289"/>
-    <mergeCell ref="K289:P289"/>
+    <mergeCell ref="N289:P289"/>
     <mergeCell ref="Q289:R289"/>
     <mergeCell ref="S289:V289"/>
     <mergeCell ref="X289:Y289"/>
     <mergeCell ref="Z289:AB289"/>
     <mergeCell ref="AC289:AD289"/>
     <mergeCell ref="AE289:AI289"/>
-    <mergeCell ref="E290:I290"/>
-    <mergeCell ref="J290:P290"/>
+    <mergeCell ref="N290:P290"/>
     <mergeCell ref="Q290:R290"/>
     <mergeCell ref="S290:V290"/>
     <mergeCell ref="X290:Y290"/>
     <mergeCell ref="Z290:AB290"/>
     <mergeCell ref="AC290:AD290"/>
     <mergeCell ref="AE290:AI290"/>
-    <mergeCell ref="F291:K291"/>
-    <mergeCell ref="L291:P291"/>
+    <mergeCell ref="N291:P291"/>
     <mergeCell ref="Q291:R291"/>
     <mergeCell ref="S291:V291"/>
     <mergeCell ref="X291:Y291"/>
@@ -19714,7 +20051,54 @@
     <mergeCell ref="Z293:AB293"/>
     <mergeCell ref="AC293:AD293"/>
     <mergeCell ref="AE293:AI293"/>
-    <mergeCell ref="B294:AF294"/>
+    <mergeCell ref="C294:F294"/>
+    <mergeCell ref="G294:P294"/>
+    <mergeCell ref="Q294:R294"/>
+    <mergeCell ref="S294:V294"/>
+    <mergeCell ref="X294:Y294"/>
+    <mergeCell ref="Z294:AB294"/>
+    <mergeCell ref="AC294:AD294"/>
+    <mergeCell ref="AE294:AI294"/>
+    <mergeCell ref="C295:J295"/>
+    <mergeCell ref="K295:P295"/>
+    <mergeCell ref="Q295:R295"/>
+    <mergeCell ref="S295:V295"/>
+    <mergeCell ref="X295:Y295"/>
+    <mergeCell ref="Z295:AB295"/>
+    <mergeCell ref="AC295:AD295"/>
+    <mergeCell ref="AE295:AI295"/>
+    <mergeCell ref="E296:I296"/>
+    <mergeCell ref="J296:P296"/>
+    <mergeCell ref="Q296:R296"/>
+    <mergeCell ref="S296:V296"/>
+    <mergeCell ref="X296:Y296"/>
+    <mergeCell ref="Z296:AB296"/>
+    <mergeCell ref="AC296:AD296"/>
+    <mergeCell ref="AE296:AI296"/>
+    <mergeCell ref="F297:K297"/>
+    <mergeCell ref="L297:P297"/>
+    <mergeCell ref="Q297:R297"/>
+    <mergeCell ref="S297:V297"/>
+    <mergeCell ref="X297:Y297"/>
+    <mergeCell ref="Z297:AB297"/>
+    <mergeCell ref="AC297:AD297"/>
+    <mergeCell ref="AE297:AI297"/>
+    <mergeCell ref="H298:L298"/>
+    <mergeCell ref="M298:P298"/>
+    <mergeCell ref="Q298:R298"/>
+    <mergeCell ref="S298:V298"/>
+    <mergeCell ref="X298:Y298"/>
+    <mergeCell ref="Z298:AB298"/>
+    <mergeCell ref="AC298:AD298"/>
+    <mergeCell ref="AE298:AI298"/>
+    <mergeCell ref="N299:P299"/>
+    <mergeCell ref="Q299:R299"/>
+    <mergeCell ref="S299:V299"/>
+    <mergeCell ref="X299:Y299"/>
+    <mergeCell ref="Z299:AB299"/>
+    <mergeCell ref="AC299:AD299"/>
+    <mergeCell ref="AE299:AI299"/>
+    <mergeCell ref="B300:AF300"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>7.0705642047E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>4.001499962E9</v>
+        <v>6.710706981E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>7.4707142009E10</v>
+        <v>7.7416349028E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.8787958942746098</v>
+        <v>0.9106648687931416</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.0303657991E10</v>
+        <v>7.594450972E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>6.6672274007E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>4.001499962E9</v>
+        <v>6.710706981E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>7.0673773969E10</v>
+        <v>7.3382980988E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.8727592386147246</v>
+        <v>0.9062155735797889</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.0303626031E10</v>
+        <v>7.594419012E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>6.6672274007E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>4.001499962E9</v>
+        <v>6.710706981E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>7.0673773969E10</v>
+        <v>7.3382980988E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.8727592386147246</v>
+        <v>0.9062155735797889</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.0303626031E10</v>
+        <v>7.594419012E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>6.6671674007E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>4.001499962E9</v>
+        <v>6.710706981E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>7.0673173969E10</v>
+        <v>7.3382380988E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.8727582958205313</v>
+        <v>0.9062148786813014</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.0303626031E10</v>
+        <v>7.594419012E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2565,20 +2565,20 @@
         <v>1.3716552E7</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>0.0</v>
+        <v>944500.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
-        <v>1.3716552E7</v>
+        <v>1.4661052E7</v>
       </c>
       <c r="AA35" s="21" t="inlineStr"/>
       <c r="AB35" s="21" t="inlineStr"/>
       <c r="AC35" s="23" t="n">
-        <v>0.784699771167048</v>
+        <v>0.8387329519450801</v>
       </c>
       <c r="AD35" s="23" t="inlineStr"/>
       <c r="AE35" s="21" t="n">
-        <v>3763448.0</v>
+        <v>2818948.0</v>
       </c>
       <c r="AF35" s="21" t="inlineStr"/>
       <c r="AG35" s="21" t="inlineStr"/>
@@ -2628,20 +2628,20 @@
         <v>1.3716552E7</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>0.0</v>
+        <v>944500.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
-        <v>1.3716552E7</v>
+        <v>1.4661052E7</v>
       </c>
       <c r="AA36" s="25" t="inlineStr"/>
       <c r="AB36" s="25" t="inlineStr"/>
       <c r="AC36" s="26" t="n">
-        <v>0.784699771167048</v>
+        <v>0.8387329519450801</v>
       </c>
       <c r="AD36" s="26" t="inlineStr"/>
       <c r="AE36" s="25" t="n">
-        <v>3763448.0</v>
+        <v>2818948.0</v>
       </c>
       <c r="AF36" s="25" t="inlineStr"/>
       <c r="AG36" s="25" t="inlineStr"/>
@@ -2994,20 +2994,20 @@
         <v>1.1316552E7</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>0.0</v>
+        <v>944500.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
-        <v>1.1316552E7</v>
+        <v>1.2261052E7</v>
       </c>
       <c r="AA42" s="14" t="inlineStr"/>
       <c r="AB42" s="14" t="inlineStr"/>
       <c r="AC42" s="15" t="n">
-        <v>0.7504344827586207</v>
+        <v>0.8130671087533157</v>
       </c>
       <c r="AD42" s="15" t="inlineStr"/>
       <c r="AE42" s="14" t="n">
-        <v>3763448.0</v>
+        <v>2818948.0</v>
       </c>
       <c r="AF42" s="14" t="inlineStr"/>
       <c r="AG42" s="14" t="inlineStr"/>
@@ -3057,20 +3057,20 @@
         <v>1.1316552E7</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>0.0</v>
+        <v>944500.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
-        <v>1.1316552E7</v>
+        <v>1.2261052E7</v>
       </c>
       <c r="AA43" s="14" t="inlineStr"/>
       <c r="AB43" s="14" t="inlineStr"/>
       <c r="AC43" s="15" t="n">
-        <v>0.7504344827586207</v>
+        <v>0.8130671087533157</v>
       </c>
       <c r="AD43" s="15" t="inlineStr"/>
       <c r="AE43" s="14" t="n">
-        <v>3763448.0</v>
+        <v>2818948.0</v>
       </c>
       <c r="AF43" s="14" t="inlineStr"/>
       <c r="AG43" s="14" t="inlineStr"/>
@@ -3114,20 +3114,20 @@
         <v>1.0567452E7</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>0.0</v>
+        <v>944500.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
-        <v>1.0567452E7</v>
+        <v>1.1511952E7</v>
       </c>
       <c r="AA44" s="14" t="inlineStr"/>
       <c r="AB44" s="14" t="inlineStr"/>
       <c r="AC44" s="15" t="n">
-        <v>0.7679834302325581</v>
+        <v>0.8366244186046512</v>
       </c>
       <c r="AD44" s="15" t="inlineStr"/>
       <c r="AE44" s="14" t="n">
-        <v>3192548.0</v>
+        <v>2248048.0</v>
       </c>
       <c r="AF44" s="14" t="inlineStr"/>
       <c r="AG44" s="14" t="inlineStr"/>
@@ -3234,20 +3234,20 @@
         <v>6.6656907455E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>4.001499962E9</v>
+        <v>6.709762481E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>7.0658407417E10</v>
+        <v>7.3366669936E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.8727756585831195</v>
+        <v>0.9062282325943971</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.0299862583E10</v>
+        <v>7.591600064E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3297,20 +3297,20 @@
         <v>6.2301898661E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>3.101785341E9</v>
+        <v>5.80206786E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>6.5403684002E10</v>
+        <v>6.8103966521E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.8803838311405854</v>
+        <v>0.9167317082596552</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>8.886280998E9</v>
+        <v>6.185998479E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -7937,7 +7937,7 @@
       <c r="O127" s="13" t="inlineStr"/>
       <c r="P127" s="13" t="inlineStr"/>
       <c r="Q127" s="14" t="n">
-        <v>5.2888974E10</v>
+        <v>5.2357002E10</v>
       </c>
       <c r="R127" s="14" t="inlineStr"/>
       <c r="S127" s="14" t="n">
@@ -7950,20 +7950,20 @@
         <v>4.1557585441E10</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>1.865905214E9</v>
+        <v>3.774902719E9</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
-        <v>4.3423490655E10</v>
+        <v>4.533248816E10</v>
       </c>
       <c r="AA127" s="14" t="inlineStr"/>
       <c r="AB127" s="14" t="inlineStr"/>
       <c r="AC127" s="15" t="n">
-        <v>0.8210310650949667</v>
+        <v>0.8658342996797257</v>
       </c>
       <c r="AD127" s="15" t="inlineStr"/>
       <c r="AE127" s="14" t="n">
-        <v>9.465483345E9</v>
+        <v>7.02451384E9</v>
       </c>
       <c r="AF127" s="14" t="inlineStr"/>
       <c r="AG127" s="14" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
       <c r="O157" s="13" t="inlineStr"/>
       <c r="P157" s="13" t="inlineStr"/>
       <c r="Q157" s="14" t="n">
-        <v>2.612304E9</v>
+        <v>2.580336E9</v>
       </c>
       <c r="R157" s="14" t="inlineStr"/>
       <c r="S157" s="14" t="n">
@@ -9704,11 +9704,11 @@
       <c r="AA157" s="14" t="inlineStr"/>
       <c r="AB157" s="14" t="inlineStr"/>
       <c r="AC157" s="15" t="n">
-        <v>0.750478887602668</v>
+        <v>0.7597766337407221</v>
       </c>
       <c r="AD157" s="15" t="inlineStr"/>
       <c r="AE157" s="14" t="n">
-        <v>6.51825E8</v>
+        <v>6.19857E8</v>
       </c>
       <c r="AF157" s="14" t="inlineStr"/>
       <c r="AG157" s="14" t="inlineStr"/>
@@ -9796,7 +9796,7 @@
       <c r="O159" s="13" t="inlineStr"/>
       <c r="P159" s="13" t="inlineStr"/>
       <c r="Q159" s="14" t="n">
-        <v>1.806192E9</v>
+        <v>1.774224E9</v>
       </c>
       <c r="R159" s="14" t="inlineStr"/>
       <c r="S159" s="14" t="n">
@@ -9818,11 +9818,11 @@
       <c r="AA159" s="14" t="inlineStr"/>
       <c r="AB159" s="14" t="inlineStr"/>
       <c r="AC159" s="15" t="n">
-        <v>0.7741724024909865</v>
+        <v>0.7881214547881215</v>
       </c>
       <c r="AD159" s="15" t="inlineStr"/>
       <c r="AE159" s="14" t="n">
-        <v>4.07888E8</v>
+        <v>3.7592E8</v>
       </c>
       <c r="AF159" s="14" t="inlineStr"/>
       <c r="AG159" s="14" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
       <c r="O165" s="13" t="inlineStr"/>
       <c r="P165" s="13" t="inlineStr"/>
       <c r="Q165" s="14" t="n">
-        <v>3.024E10</v>
+        <v>2.9739996E10</v>
       </c>
       <c r="R165" s="14" t="inlineStr"/>
       <c r="S165" s="14" t="n">
@@ -10163,20 +10163,20 @@
         <v>2.0954588334E10</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>0.0</v>
+        <v>1.908997505E9</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
-        <v>2.0954588334E10</v>
+        <v>2.2863585839E10</v>
       </c>
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.6929427359126984</v>
+        <v>0.7687824113695241</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>9.285411666E9</v>
+        <v>6.876410161E9</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10207,7 +10207,7 @@
       <c r="O166" s="13" t="inlineStr"/>
       <c r="P166" s="13" t="inlineStr"/>
       <c r="Q166" s="14" t="n">
-        <v>2.5462704E10</v>
+        <v>2.49627E10</v>
       </c>
       <c r="R166" s="14" t="inlineStr"/>
       <c r="S166" s="14" t="n">
@@ -10220,20 +10220,20 @@
         <v>1.6177303134E10</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>0.0</v>
+        <v>1.908997505E9</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
-        <v>1.6177303134E10</v>
+        <v>1.8086300639E10</v>
       </c>
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.6353332754447446</v>
+        <v>0.7245330288390278</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>9.285400866E9</v>
+        <v>6.876399361E9</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -10428,7 +10428,7 @@
       <c r="O170" s="13" t="inlineStr"/>
       <c r="P170" s="13" t="inlineStr"/>
       <c r="Q170" s="14" t="n">
-        <v>1.4993988E10</v>
+        <v>1.552596E10</v>
       </c>
       <c r="R170" s="14" t="inlineStr"/>
       <c r="S170" s="14" t="n">
@@ -10441,20 +10441,20 @@
         <v>1.6105883553E10</v>
       </c>
       <c r="X170" s="14" t="n">
-        <v>8.22449216E8</v>
+        <v>1.61373423E9</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
-        <v>1.6928332769E10</v>
+        <v>1.7719617783E10</v>
       </c>
       <c r="AA170" s="14" t="inlineStr"/>
       <c r="AB170" s="14" t="inlineStr"/>
       <c r="AC170" s="15" t="n">
-        <v>1.1290080243494927</v>
+        <v>1.141289671170092</v>
       </c>
       <c r="AD170" s="15" t="inlineStr"/>
       <c r="AE170" s="14" t="n">
-        <v>-1.934344769E9</v>
+        <v>-2.193657783E9</v>
       </c>
       <c r="AF170" s="14" t="inlineStr"/>
       <c r="AG170" s="14" t="inlineStr"/>
@@ -10491,7 +10491,7 @@
       <c r="O171" s="13" t="inlineStr"/>
       <c r="P171" s="13" t="inlineStr"/>
       <c r="Q171" s="14" t="n">
-        <v>4.458578E9</v>
+        <v>4.463906E9</v>
       </c>
       <c r="R171" s="14" t="inlineStr"/>
       <c r="S171" s="14" t="n">
@@ -10513,11 +10513,11 @@
       <c r="AA171" s="14" t="inlineStr"/>
       <c r="AB171" s="14" t="inlineStr"/>
       <c r="AC171" s="15" t="n">
-        <v>1.4377905390463057</v>
+        <v>1.4360744303307462</v>
       </c>
       <c r="AD171" s="15" t="inlineStr"/>
       <c r="AE171" s="14" t="n">
-        <v>-1.951923266E9</v>
+        <v>-1.946595266E9</v>
       </c>
       <c r="AF171" s="14" t="inlineStr"/>
       <c r="AG171" s="14" t="inlineStr"/>
@@ -10548,7 +10548,7 @@
       <c r="O172" s="13" t="inlineStr"/>
       <c r="P172" s="13" t="inlineStr"/>
       <c r="Q172" s="14" t="n">
-        <v>3.369456E9</v>
+        <v>3.374784E9</v>
       </c>
       <c r="R172" s="14" t="inlineStr"/>
       <c r="S172" s="14" t="n">
@@ -10570,11 +10570,11 @@
       <c r="AA172" s="14" t="inlineStr"/>
       <c r="AB172" s="14" t="inlineStr"/>
       <c r="AC172" s="15" t="n">
-        <v>1.5793017033016605</v>
+        <v>1.5768083527716144</v>
       </c>
       <c r="AD172" s="15" t="inlineStr"/>
       <c r="AE172" s="14" t="n">
-        <v>-1.9519316E9</v>
+        <v>-1.9466036E9</v>
       </c>
       <c r="AF172" s="14" t="inlineStr"/>
       <c r="AG172" s="14" t="inlineStr"/>
@@ -11939,7 +11939,7 @@
       <c r="O196" s="13" t="inlineStr"/>
       <c r="P196" s="13" t="inlineStr"/>
       <c r="Q196" s="14" t="n">
-        <v>1.01496E9</v>
+        <v>1.0416E9</v>
       </c>
       <c r="R196" s="14" t="inlineStr"/>
       <c r="S196" s="14" t="n">
@@ -11952,20 +11952,20 @@
         <v>9.03024E8</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>1.01987E8</v>
+        <v>1.27613E8</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="14" t="n">
-        <v>1.005011E9</v>
+        <v>1.030637E9</v>
       </c>
       <c r="AA196" s="14" t="inlineStr"/>
       <c r="AB196" s="14" t="inlineStr"/>
       <c r="AC196" s="15" t="n">
-        <v>0.9901976432568771</v>
+        <v>0.9894748463901689</v>
       </c>
       <c r="AD196" s="15" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>9949000.0</v>
+        <v>1.0963E7</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12009,20 +12009,20 @@
         <v>8.673E7</v>
       </c>
       <c r="X197" s="14" t="n">
-        <v>1.0745E7</v>
+        <v>1.295E7</v>
       </c>
       <c r="Y197" s="14" t="inlineStr"/>
       <c r="Z197" s="14" t="n">
-        <v>9.7475E7</v>
+        <v>9.968E7</v>
       </c>
       <c r="AA197" s="14" t="inlineStr"/>
       <c r="AB197" s="14" t="inlineStr"/>
       <c r="AC197" s="15" t="n">
-        <v>0.8926282051282052</v>
+        <v>0.9128205128205128</v>
       </c>
       <c r="AD197" s="15" t="inlineStr"/>
       <c r="AE197" s="14" t="n">
-        <v>1.1725E7</v>
+        <v>9520000.0</v>
       </c>
       <c r="AF197" s="14" t="inlineStr"/>
       <c r="AG197" s="14" t="inlineStr"/>
@@ -12053,7 +12053,7 @@
       <c r="O198" s="13" t="inlineStr"/>
       <c r="P198" s="13" t="inlineStr"/>
       <c r="Q198" s="14" t="n">
-        <v>9.0576E8</v>
+        <v>9.324E8</v>
       </c>
       <c r="R198" s="14" t="inlineStr"/>
       <c r="S198" s="14" t="n">
@@ -12066,20 +12066,20 @@
         <v>8.16294E8</v>
       </c>
       <c r="X198" s="14" t="n">
-        <v>9.1242E7</v>
+        <v>1.14663E8</v>
       </c>
       <c r="Y198" s="14" t="inlineStr"/>
       <c r="Z198" s="14" t="n">
-        <v>9.07536E8</v>
+        <v>9.30957E8</v>
       </c>
       <c r="AA198" s="14" t="inlineStr"/>
       <c r="AB198" s="14" t="inlineStr"/>
       <c r="AC198" s="15" t="n">
-        <v>1.0019607843137255</v>
+        <v>0.998452380952381</v>
       </c>
       <c r="AD198" s="15" t="inlineStr"/>
       <c r="AE198" s="14" t="n">
-        <v>-1776000.0</v>
+        <v>1443000.0</v>
       </c>
       <c r="AF198" s="14" t="inlineStr"/>
       <c r="AG198" s="14" t="inlineStr"/>
@@ -12116,7 +12116,7 @@
       <c r="O199" s="13" t="inlineStr"/>
       <c r="P199" s="13" t="inlineStr"/>
       <c r="Q199" s="14" t="n">
-        <v>7.81827E9</v>
+        <v>8.318274E9</v>
       </c>
       <c r="R199" s="14" t="inlineStr"/>
       <c r="S199" s="14" t="n">
@@ -12129,20 +12129,20 @@
         <v>7.511205284E9</v>
       </c>
       <c r="X199" s="14" t="n">
-        <v>0.0</v>
+        <v>7.65659014E8</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
-        <v>7.511205284E9</v>
+        <v>8.276864298E9</v>
       </c>
       <c r="AA199" s="14" t="inlineStr"/>
       <c r="AB199" s="14" t="inlineStr"/>
       <c r="AC199" s="15" t="n">
-        <v>0.9607247235002117</v>
+        <v>0.9950218396268264</v>
       </c>
       <c r="AD199" s="15" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
-        <v>3.07064716E8</v>
+        <v>4.1409702E7</v>
       </c>
       <c r="AF199" s="14" t="inlineStr"/>
       <c r="AG199" s="14" t="inlineStr"/>
@@ -12173,7 +12173,7 @@
       <c r="O200" s="13" t="inlineStr"/>
       <c r="P200" s="13" t="inlineStr"/>
       <c r="Q200" s="14" t="n">
-        <v>6.243816E9</v>
+        <v>6.74382E9</v>
       </c>
       <c r="R200" s="14" t="inlineStr"/>
       <c r="S200" s="14" t="n">
@@ -12186,20 +12186,20 @@
         <v>5.936761908E9</v>
       </c>
       <c r="X200" s="14" t="n">
-        <v>0.0</v>
+        <v>7.65659014E8</v>
       </c>
       <c r="Y200" s="14" t="inlineStr"/>
       <c r="Z200" s="14" t="n">
-        <v>5.936761908E9</v>
+        <v>6.702420922E9</v>
       </c>
       <c r="AA200" s="14" t="inlineStr"/>
       <c r="AB200" s="14" t="inlineStr"/>
       <c r="AC200" s="15" t="n">
-        <v>0.950822687279702</v>
+        <v>0.9938611828310957</v>
       </c>
       <c r="AD200" s="15" t="inlineStr"/>
       <c r="AE200" s="14" t="n">
-        <v>3.07054092E8</v>
+        <v>4.1399078E7</v>
       </c>
       <c r="AF200" s="14" t="inlineStr"/>
       <c r="AG200" s="14" t="inlineStr"/>
@@ -12363,20 +12363,20 @@
         <v>4.355008794E9</v>
       </c>
       <c r="X203" s="25" t="n">
-        <v>8.99714621E8</v>
+        <v>9.07694621E8</v>
       </c>
       <c r="Y203" s="25" t="inlineStr"/>
       <c r="Z203" s="25" t="n">
-        <v>5.254723415E9</v>
+        <v>5.262703415E9</v>
       </c>
       <c r="AA203" s="25" t="inlineStr"/>
       <c r="AB203" s="25" t="inlineStr"/>
       <c r="AC203" s="26" t="n">
-        <v>0.7880148575987451</v>
+        <v>0.7892115635082678</v>
       </c>
       <c r="AD203" s="26" t="inlineStr"/>
       <c r="AE203" s="25" t="n">
-        <v>1.413581585E9</v>
+        <v>1.405601585E9</v>
       </c>
       <c r="AF203" s="25" t="inlineStr"/>
       <c r="AG203" s="25" t="inlineStr"/>
@@ -12413,7 +12413,7 @@
       <c r="O204" s="13" t="inlineStr"/>
       <c r="P204" s="13" t="inlineStr"/>
       <c r="Q204" s="14" t="n">
-        <v>4.91139E9</v>
+        <v>4.92941E9</v>
       </c>
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="14" t="n">
@@ -12426,20 +12426,20 @@
         <v>3.254563865E9</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>8.28823565E8</v>
+        <v>8.29133565E8</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>4.08338743E9</v>
+        <v>4.08369743E9</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.8314117653047305</v>
+        <v>0.8284353360747027</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>8.2800257E8</v>
+        <v>8.4571257E8</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12476,7 +12476,7 @@
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>1.837418E9</v>
+        <v>1.842437E9</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12498,11 +12498,11 @@
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.923255321325904</v>
+        <v>0.9207402728017294</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>1.41012054E8</v>
+        <v>1.46031054E8</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12647,7 +12647,7 @@
       <c r="O208" s="13" t="inlineStr"/>
       <c r="P208" s="13" t="inlineStr"/>
       <c r="Q208" s="14" t="n">
-        <v>5.8695E7</v>
+        <v>6.3714E7</v>
       </c>
       <c r="R208" s="14" t="inlineStr"/>
       <c r="S208" s="14" t="n">
@@ -12669,11 +12669,11 @@
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.7799898798875543</v>
+        <v>0.7185470383275261</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.2913494E7</v>
+        <v>1.7932494E7</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -13229,7 +13229,7 @@
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="n">
-        <v>4.6604E7</v>
+        <v>5.9605E7</v>
       </c>
       <c r="R218" s="14" t="inlineStr"/>
       <c r="S218" s="14" t="n">
@@ -13251,11 +13251,11 @@
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.6430297828512574</v>
+        <v>0.5027725861924335</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>1.663624E7</v>
+        <v>2.963724E7</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>4.6604E7</v>
+        <v>5.9605E7</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13308,11 +13308,11 @@
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.6430297828512574</v>
+        <v>0.5027725861924335</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>1.663624E7</v>
+        <v>2.963724E7</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13362,20 +13362,20 @@
         <v>2947800.0</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>0.0</v>
+        <v>310000.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>2947800.0</v>
+        <v>3257800.0</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.4913</v>
+        <v>0.5429666666666667</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>3052200.0</v>
+        <v>2742200.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13520,20 +13520,20 @@
         <v>0.0</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>0.0</v>
+        <v>310000.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>0.0</v>
+        <v>310000.0</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.0</v>
+        <v>0.155</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>2000000.0</v>
+        <v>1690000.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -14032,7 +14032,7 @@
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>8.732E8</v>
+        <v>8.4668E8</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14045,20 +14045,20 @@
         <v>5.35794312E8</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>4.3771056E7</v>
+        <v>5.0441056E7</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>5.79565368E8</v>
+        <v>5.86235368E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.6637257993586807</v>
+        <v>0.692393074124817</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>2.93634632E8</v>
+        <v>2.60444632E8</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14095,7 +14095,7 @@
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>6.72E8</v>
+        <v>6.4548E8</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14117,11 +14117,11 @@
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.640277369047619</v>
+        <v>0.6665836152940448</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>2.41733608E8</v>
+        <v>2.15213608E8</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14152,7 +14152,7 @@
       <c r="O234" s="13" t="inlineStr"/>
       <c r="P234" s="13" t="inlineStr"/>
       <c r="Q234" s="14" t="n">
-        <v>6.72E8</v>
+        <v>6.4548E8</v>
       </c>
       <c r="R234" s="14" t="inlineStr"/>
       <c r="S234" s="14" t="n">
@@ -14174,11 +14174,11 @@
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.640277369047619</v>
+        <v>0.6665836152940448</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>2.41733608E8</v>
+        <v>2.15213608E8</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14468,20 +14468,20 @@
         <v>1.12025206E8</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>3105950.0</v>
+        <v>9775950.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>1.15131156E8</v>
+        <v>1.21801156E8</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.7399174550128534</v>
+        <v>0.7827837789203085</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>4.0468844E7</v>
+        <v>3.3798844E7</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14525,20 +14525,20 @@
         <v>8.48836E7</v>
       </c>
       <c r="X240" s="14" t="n">
-        <v>3105950.0</v>
+        <v>9775950.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>8.798955E7</v>
+        <v>9.465955E7</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.6933770685579196</v>
+        <v>0.7459381402679275</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>3.891045E7</v>
+        <v>3.224045E7</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -14632,7 +14632,7 @@
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>7.51535E8</v>
+        <v>7.60035E8</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14645,20 +14645,20 @@
         <v>4.74510617E8</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>1.673E7</v>
+        <v>1.773E7</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>4.91240617E8</v>
+        <v>4.92240617E8</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.6536496863086882</v>
+        <v>0.647655196142283</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>2.60294383E8</v>
+        <v>2.67794383E8</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>1.8E8</v>
+        <v>1.7E8</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14774,11 +14774,11 @@
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.7423055555555556</v>
+        <v>0.7859705882352941</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>4.6385E7</v>
+        <v>3.6385E7</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       <c r="O245" s="13" t="inlineStr"/>
       <c r="P245" s="13" t="inlineStr"/>
       <c r="Q245" s="14" t="n">
-        <v>4.0E7</v>
+        <v>5.0E7</v>
       </c>
       <c r="R245" s="14" t="inlineStr"/>
       <c r="S245" s="14" t="n">
@@ -14831,11 +14831,11 @@
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.750375</v>
+        <v>0.6003</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>9985000.0</v>
+        <v>1.9985E7</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -15897,7 +15897,7 @@
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>2.2146E8</v>
+        <v>2.2996E8</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15910,20 +15910,20 @@
         <v>1.17103369E8</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>6710000.0</v>
+        <v>7710000.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>1.23813369E8</v>
+        <v>1.24813369E8</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.5590777973448929</v>
+        <v>0.542761214993912</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>9.7646631E7</v>
+        <v>1.05146631E8</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -16138,20 +16138,20 @@
         <v>8.3960177E7</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>3550000.0</v>
+        <v>4550000.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>8.7510177E7</v>
+        <v>8.8510177E7</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.7023288683788123</v>
+        <v>0.7103545505617977</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>3.7089823E7</v>
+        <v>3.6089823E7</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16239,7 +16239,7 @@
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>6000000.0</v>
+        <v>1.45E7</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16261,11 +16261,11 @@
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.7895891666666667</v>
+        <v>0.32672655172413795</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>1262465.0</v>
+        <v>9762465.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{750E3824-E2F3-4B3A-AB68-C9F0E157CE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E1573BC-A2DF-430B-BE3E-F60F3B920BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E1573BC-A2DF-430B-BE3E-F60F3B920BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F86B8D7-4AB1-4730-849D-C080AF177903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2156,19 +2156,19 @@
         <v>77645055879</v>
       </c>
       <c r="X9" s="4">
-        <v>2721304996</v>
+        <v>2905791496</v>
       </c>
       <c r="Y9" s="18">
-        <v>80366360875</v>
+        <v>80550847375</v>
       </c>
       <c r="Z9" s="18"/>
       <c r="AA9" s="18"/>
       <c r="AB9" s="18"/>
       <c r="AC9" s="5">
-        <v>0.94536648137648394</v>
+        <v>0.94753663505107588</v>
       </c>
       <c r="AD9" s="18">
-        <v>4644439125</v>
+        <v>4459952625</v>
       </c>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
@@ -2808,20 +2808,20 @@
         <v>73611687839</v>
       </c>
       <c r="X21" s="20">
-        <v>2721304996</v>
+        <v>2905791496</v>
       </c>
       <c r="Y21" s="20"/>
       <c r="Z21" s="20">
-        <v>76332992835</v>
+        <v>76517479335</v>
       </c>
       <c r="AA21" s="20"/>
       <c r="AB21" s="20"/>
       <c r="AC21" s="21">
-        <v>0.94264563736301732</v>
+        <v>0.9449238841331038</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="20">
-        <v>4644407165</v>
+        <v>4459920665</v>
       </c>
       <c r="AF21" s="20"/>
       <c r="AG21" s="20"/>
@@ -2863,20 +2863,20 @@
         <v>73611687839</v>
       </c>
       <c r="X22" s="20">
-        <v>2721304996</v>
+        <v>2905791496</v>
       </c>
       <c r="Y22" s="20"/>
       <c r="Z22" s="20">
-        <v>76332992835</v>
+        <v>76517479335</v>
       </c>
       <c r="AA22" s="20"/>
       <c r="AB22" s="20"/>
       <c r="AC22" s="21">
-        <v>0.94264563736301732</v>
+        <v>0.9449238841331038</v>
       </c>
       <c r="AD22" s="21"/>
       <c r="AE22" s="20">
-        <v>4644407165</v>
+        <v>4459920665</v>
       </c>
       <c r="AF22" s="20"/>
       <c r="AG22" s="20"/>
@@ -2918,20 +2918,20 @@
         <v>73611087839</v>
       </c>
       <c r="X23" s="23">
-        <v>2721304996</v>
+        <v>2905791496</v>
       </c>
       <c r="Y23" s="23"/>
       <c r="Z23" s="23">
-        <v>76332392835</v>
+        <v>76516879335</v>
       </c>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
       <c r="AC23" s="24">
-        <v>0.94264521239416721</v>
+        <v>0.94492347604499072</v>
       </c>
       <c r="AD23" s="24"/>
       <c r="AE23" s="23">
-        <v>4644407165</v>
+        <v>4459920665</v>
       </c>
       <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
@@ -4155,20 +4155,20 @@
         <v>73595376787</v>
       </c>
       <c r="X46" s="28">
-        <v>2721304996</v>
+        <v>2905791496</v>
       </c>
       <c r="Y46" s="28"/>
       <c r="Z46" s="27">
-        <v>76316681783</v>
+        <v>76501168283</v>
       </c>
       <c r="AA46" s="27"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="29">
-        <v>0.94266690460406333</v>
+        <v>0.94494568971150195</v>
       </c>
       <c r="AD46" s="29"/>
       <c r="AE46" s="27">
-        <v>4641588217</v>
+        <v>4457101717</v>
       </c>
       <c r="AF46" s="27"/>
       <c r="AG46" s="27"/>
@@ -12692,20 +12692,20 @@
         <v>5354544346</v>
       </c>
       <c r="X207" s="31">
-        <v>9910000</v>
+        <v>194396500</v>
       </c>
       <c r="Y207" s="31"/>
       <c r="Z207" s="31">
-        <v>5364454346</v>
+        <v>5548940846</v>
       </c>
       <c r="AA207" s="31"/>
       <c r="AB207" s="31"/>
       <c r="AC207" s="32">
-        <v>0.80447045328610489</v>
+        <v>0.83213662932334376</v>
       </c>
       <c r="AD207" s="32"/>
       <c r="AE207" s="31">
-        <v>1303850654</v>
+        <v>1119364154</v>
       </c>
       <c r="AF207" s="31"/>
       <c r="AG207" s="31"/>
@@ -12747,20 +12747,20 @@
         <v>4105668591</v>
       </c>
       <c r="X208" s="20">
-        <v>0</v>
+        <v>184486500</v>
       </c>
       <c r="Y208" s="20"/>
       <c r="Z208" s="20">
-        <v>4105668591</v>
+        <v>4290155091</v>
       </c>
       <c r="AA208" s="20"/>
       <c r="AB208" s="20"/>
       <c r="AC208" s="21">
-        <v>0.83289249443645386</v>
+        <v>0.87031817012583657</v>
       </c>
       <c r="AD208" s="21"/>
       <c r="AE208" s="20">
-        <v>823741409</v>
+        <v>639254909</v>
       </c>
       <c r="AF208" s="20"/>
       <c r="AG208" s="20"/>
@@ -13803,20 +13803,20 @@
         <v>2346179924</v>
       </c>
       <c r="X228" s="20">
-        <v>0</v>
+        <v>184486500</v>
       </c>
       <c r="Y228" s="20"/>
       <c r="Z228" s="20">
-        <v>2346179924</v>
+        <v>2530666424</v>
       </c>
       <c r="AA228" s="20"/>
       <c r="AB228" s="20"/>
       <c r="AC228" s="21">
-        <v>0.77910767597982045</v>
+        <v>0.84037102871518854</v>
       </c>
       <c r="AD228" s="21"/>
       <c r="AE228" s="20">
-        <v>665188076</v>
+        <v>480701576</v>
       </c>
       <c r="AF228" s="20"/>
       <c r="AG228" s="20"/>
@@ -14068,20 +14068,20 @@
         <v>1660378500</v>
       </c>
       <c r="X233" s="20">
-        <v>0</v>
+        <v>184486500</v>
       </c>
       <c r="Y233" s="20"/>
       <c r="Z233" s="20">
-        <v>1660378500</v>
+        <v>1844865000</v>
       </c>
       <c r="AA233" s="20"/>
       <c r="AB233" s="20"/>
       <c r="AC233" s="21">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="AD233" s="21"/>
       <c r="AE233" s="20">
-        <v>553459500</v>
+        <v>368973000</v>
       </c>
       <c r="AF233" s="20"/>
       <c r="AG233" s="20"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F86B8D7-4AB1-4730-849D-C080AF177903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC9D15B1-95EC-4EB2-A765-A5470211AD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="600" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLP039_LAPORAN REALISASI SUPER " sheetId="1" r:id="rId1"/>
@@ -2156,19 +2156,19 @@
         <v>77645055879</v>
       </c>
       <c r="X9" s="4">
-        <v>2905791496</v>
+        <v>4799993081</v>
       </c>
       <c r="Y9" s="18">
-        <v>80550847375</v>
+        <v>82445048960</v>
       </c>
       <c r="Z9" s="18"/>
       <c r="AA9" s="18"/>
       <c r="AB9" s="18"/>
       <c r="AC9" s="5">
-        <v>0.94753663505107588</v>
+        <v>0.96981852846932393</v>
       </c>
       <c r="AD9" s="18">
-        <v>4459952625</v>
+        <v>2565751040</v>
       </c>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
@@ -2808,20 +2808,20 @@
         <v>73611687839</v>
       </c>
       <c r="X21" s="20">
-        <v>2905791496</v>
+        <v>4799993081</v>
       </c>
       <c r="Y21" s="20"/>
       <c r="Z21" s="20">
-        <v>76517479335</v>
+        <v>78411680920</v>
       </c>
       <c r="AA21" s="20"/>
       <c r="AB21" s="20"/>
       <c r="AC21" s="21">
-        <v>0.9449238841331038</v>
+        <v>0.96831561546801947</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="20">
-        <v>4459920665</v>
+        <v>2565719080</v>
       </c>
       <c r="AF21" s="20"/>
       <c r="AG21" s="20"/>
@@ -2863,20 +2863,20 @@
         <v>73611687839</v>
       </c>
       <c r="X22" s="20">
-        <v>2905791496</v>
+        <v>4799993081</v>
       </c>
       <c r="Y22" s="20"/>
       <c r="Z22" s="20">
-        <v>76517479335</v>
+        <v>78411680920</v>
       </c>
       <c r="AA22" s="20"/>
       <c r="AB22" s="20"/>
       <c r="AC22" s="21">
-        <v>0.9449238841331038</v>
+        <v>0.96831561546801947</v>
       </c>
       <c r="AD22" s="21"/>
       <c r="AE22" s="20">
-        <v>4459920665</v>
+        <v>2565719080</v>
       </c>
       <c r="AF22" s="20"/>
       <c r="AG22" s="20"/>
@@ -2918,20 +2918,20 @@
         <v>73611087839</v>
       </c>
       <c r="X23" s="23">
-        <v>2905791496</v>
+        <v>4799993081</v>
       </c>
       <c r="Y23" s="23"/>
       <c r="Z23" s="23">
-        <v>76516879335</v>
+        <v>78411080920</v>
       </c>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
       <c r="AC23" s="24">
-        <v>0.94492347604499072</v>
+        <v>0.96831538070163303</v>
       </c>
       <c r="AD23" s="24"/>
       <c r="AE23" s="23">
-        <v>4459920665</v>
+        <v>2565719080</v>
       </c>
       <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
@@ -4155,20 +4155,20 @@
         <v>73595376787</v>
       </c>
       <c r="X46" s="28">
-        <v>2905791496</v>
+        <v>4799993081</v>
       </c>
       <c r="Y46" s="28"/>
       <c r="Z46" s="27">
-        <v>76501168283</v>
+        <v>78395369868</v>
       </c>
       <c r="AA46" s="27"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="29">
-        <v>0.94494568971150195</v>
+        <v>0.96834294838563129</v>
       </c>
       <c r="AD46" s="29"/>
       <c r="AE46" s="27">
-        <v>4457101717</v>
+        <v>2562900132</v>
       </c>
       <c r="AF46" s="27"/>
       <c r="AG46" s="27"/>
@@ -4210,20 +4210,20 @@
         <v>68240832441</v>
       </c>
       <c r="X47" s="31">
-        <v>2711394996</v>
+        <v>4522292680</v>
       </c>
       <c r="Y47" s="31"/>
       <c r="Z47" s="31">
-        <v>70952227437</v>
+        <v>72763125121</v>
       </c>
       <c r="AA47" s="31"/>
       <c r="AB47" s="31"/>
       <c r="AC47" s="32">
-        <v>0.95507148828243493</v>
+        <v>0.97944756227843155</v>
       </c>
       <c r="AD47" s="32"/>
       <c r="AE47" s="31">
-        <v>3337737563</v>
+        <v>1526839879</v>
       </c>
       <c r="AF47" s="31"/>
       <c r="AG47" s="31"/>
@@ -4265,20 +4265,20 @@
         <v>5051860578</v>
       </c>
       <c r="X48" s="20">
-        <v>376665314</v>
+        <v>408413314</v>
       </c>
       <c r="Y48" s="20"/>
       <c r="Z48" s="20">
-        <v>5428525892</v>
+        <v>5460273892</v>
       </c>
       <c r="AA48" s="20"/>
       <c r="AB48" s="20"/>
       <c r="AC48" s="21">
-        <v>0.84729791405098409</v>
+        <v>0.85225322138679926</v>
       </c>
       <c r="AD48" s="21"/>
       <c r="AE48" s="20">
-        <v>978342108</v>
+        <v>946594108</v>
       </c>
       <c r="AF48" s="20"/>
       <c r="AG48" s="20"/>
@@ -6071,20 +6071,20 @@
         <v>245993000</v>
       </c>
       <c r="X82" s="20">
-        <v>0</v>
+        <v>31748000</v>
       </c>
       <c r="Y82" s="20"/>
       <c r="Z82" s="20">
-        <v>245993000</v>
+        <v>277741000</v>
       </c>
       <c r="AA82" s="20"/>
       <c r="AB82" s="20"/>
       <c r="AC82" s="21">
-        <v>0.78487696862955303</v>
+        <v>0.88617364780355823</v>
       </c>
       <c r="AD82" s="21"/>
       <c r="AE82" s="20">
-        <v>67423000</v>
+        <v>35675000</v>
       </c>
       <c r="AF82" s="20"/>
       <c r="AG82" s="20"/>
@@ -6124,20 +6124,20 @@
         <v>13930000</v>
       </c>
       <c r="X83" s="20">
-        <v>0</v>
+        <v>1610000</v>
       </c>
       <c r="Y83" s="20"/>
       <c r="Z83" s="20">
-        <v>13930000</v>
+        <v>15540000</v>
       </c>
       <c r="AA83" s="20"/>
       <c r="AB83" s="20"/>
       <c r="AC83" s="21">
-        <v>0.46064814814814814</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="AD83" s="21"/>
       <c r="AE83" s="20">
-        <v>16310000</v>
+        <v>14700000</v>
       </c>
       <c r="AF83" s="20"/>
       <c r="AG83" s="20"/>
@@ -6177,20 +6177,20 @@
         <v>201354000</v>
       </c>
       <c r="X84" s="20">
-        <v>0</v>
+        <v>26899000</v>
       </c>
       <c r="Y84" s="20"/>
       <c r="Z84" s="20">
-        <v>201354000</v>
+        <v>228253000</v>
       </c>
       <c r="AA84" s="20"/>
       <c r="AB84" s="20"/>
       <c r="AC84" s="21">
-        <v>0.81272401433691754</v>
+        <v>0.92129629629629628</v>
       </c>
       <c r="AD84" s="21"/>
       <c r="AE84" s="20">
-        <v>46398000</v>
+        <v>19499000</v>
       </c>
       <c r="AF84" s="20"/>
       <c r="AG84" s="20"/>
@@ -6230,20 +6230,20 @@
         <v>30709000</v>
       </c>
       <c r="X85" s="20">
-        <v>0</v>
+        <v>3239000</v>
       </c>
       <c r="Y85" s="20"/>
       <c r="Z85" s="20">
-        <v>30709000</v>
+        <v>33948000</v>
       </c>
       <c r="AA85" s="20"/>
       <c r="AB85" s="20"/>
       <c r="AC85" s="21">
-        <v>0.86689814814814814</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="AD85" s="21"/>
       <c r="AE85" s="20">
-        <v>4715000</v>
+        <v>1476000</v>
       </c>
       <c r="AF85" s="20"/>
       <c r="AG85" s="20"/>
@@ -6752,20 +6752,20 @@
         <v>136865920</v>
       </c>
       <c r="X95" s="20">
-        <v>0</v>
+        <v>143788036</v>
       </c>
       <c r="Y95" s="20"/>
       <c r="Z95" s="20">
-        <v>136865920</v>
+        <v>280653956</v>
       </c>
       <c r="AA95" s="20"/>
       <c r="AB95" s="20"/>
       <c r="AC95" s="21">
-        <v>1013.8216296296297</v>
+        <v>2078.9181925925927</v>
       </c>
       <c r="AD95" s="21"/>
       <c r="AE95" s="20">
-        <v>-136730920</v>
+        <v>-280518956</v>
       </c>
       <c r="AF95" s="20"/>
       <c r="AG95" s="20"/>
@@ -6807,20 +6807,20 @@
         <v>112205200</v>
       </c>
       <c r="X96" s="20">
-        <v>0</v>
+        <v>118612400</v>
       </c>
       <c r="Y96" s="20"/>
       <c r="Z96" s="20">
-        <v>112205200</v>
+        <v>230817600</v>
       </c>
       <c r="AA96" s="20"/>
       <c r="AB96" s="20"/>
       <c r="AC96" s="21">
-        <v>8014.6571428571433</v>
+        <v>16486.971428571429</v>
       </c>
       <c r="AD96" s="21"/>
       <c r="AE96" s="20">
-        <v>-112191200</v>
+        <v>-230803600</v>
       </c>
       <c r="AF96" s="20"/>
       <c r="AG96" s="20"/>
@@ -6860,20 +6860,20 @@
         <v>112205200</v>
       </c>
       <c r="X97" s="20">
-        <v>0</v>
+        <v>118612400</v>
       </c>
       <c r="Y97" s="20"/>
       <c r="Z97" s="20">
-        <v>112205200</v>
+        <v>230817600</v>
       </c>
       <c r="AA97" s="20"/>
       <c r="AB97" s="20"/>
       <c r="AC97" s="21">
-        <v>9350.4333333333325</v>
+        <v>19234.8</v>
       </c>
       <c r="AD97" s="21"/>
       <c r="AE97" s="20">
-        <v>-112193200</v>
+        <v>-230805600</v>
       </c>
       <c r="AF97" s="20"/>
       <c r="AG97" s="20"/>
@@ -7021,20 +7021,20 @@
         <v>2086</v>
       </c>
       <c r="X100" s="20">
-        <v>0</v>
+        <v>2162</v>
       </c>
       <c r="Y100" s="20"/>
       <c r="Z100" s="20">
-        <v>2086</v>
+        <v>4248</v>
       </c>
       <c r="AA100" s="20"/>
       <c r="AB100" s="20"/>
       <c r="AC100" s="21">
-        <v>0.14899999999999999</v>
+        <v>0.30342857142857144</v>
       </c>
       <c r="AD100" s="21"/>
       <c r="AE100" s="20">
-        <v>11914</v>
+        <v>9752</v>
       </c>
       <c r="AF100" s="20"/>
       <c r="AG100" s="20"/>
@@ -7074,20 +7074,20 @@
         <v>2086</v>
       </c>
       <c r="X101" s="20">
-        <v>0</v>
+        <v>2162</v>
       </c>
       <c r="Y101" s="20"/>
       <c r="Z101" s="20">
-        <v>2086</v>
+        <v>4248</v>
       </c>
       <c r="AA101" s="20"/>
       <c r="AB101" s="20"/>
       <c r="AC101" s="21">
-        <v>0.17383333333333334</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="AD101" s="21"/>
       <c r="AE101" s="20">
-        <v>9914</v>
+        <v>7752</v>
       </c>
       <c r="AF101" s="20"/>
       <c r="AG101" s="20"/>
@@ -7235,20 +7235,20 @@
         <v>7571670</v>
       </c>
       <c r="X104" s="20">
-        <v>0</v>
+        <v>7571670</v>
       </c>
       <c r="Y104" s="20"/>
       <c r="Z104" s="20">
-        <v>7571670</v>
+        <v>15143340</v>
       </c>
       <c r="AA104" s="20"/>
       <c r="AB104" s="20"/>
       <c r="AC104" s="21">
-        <v>540.83357142857142</v>
+        <v>1081.6671428571428</v>
       </c>
       <c r="AD104" s="21"/>
       <c r="AE104" s="20">
-        <v>-7557670</v>
+        <v>-15129340</v>
       </c>
       <c r="AF104" s="20"/>
       <c r="AG104" s="20"/>
@@ -7288,20 +7288,20 @@
         <v>7571670</v>
       </c>
       <c r="X105" s="20">
-        <v>0</v>
+        <v>7571670</v>
       </c>
       <c r="Y105" s="20"/>
       <c r="Z105" s="20">
-        <v>7571670</v>
+        <v>15143340</v>
       </c>
       <c r="AA105" s="20"/>
       <c r="AB105" s="20"/>
       <c r="AC105" s="21">
-        <v>630.97249999999997</v>
+        <v>1261.9449999999999</v>
       </c>
       <c r="AD105" s="21"/>
       <c r="AE105" s="20">
-        <v>-7559670</v>
+        <v>-15131340</v>
       </c>
       <c r="AF105" s="20"/>
       <c r="AG105" s="20"/>
@@ -7449,20 +7449,20 @@
         <v>2630444</v>
       </c>
       <c r="X108" s="20">
-        <v>0</v>
+        <v>2630444</v>
       </c>
       <c r="Y108" s="20"/>
       <c r="Z108" s="20">
-        <v>2630444</v>
+        <v>5260888</v>
       </c>
       <c r="AA108" s="20"/>
       <c r="AB108" s="20"/>
       <c r="AC108" s="21">
-        <v>187.88885714285715</v>
+        <v>375.7777142857143</v>
       </c>
       <c r="AD108" s="21"/>
       <c r="AE108" s="20">
-        <v>-2616444</v>
+        <v>-5246888</v>
       </c>
       <c r="AF108" s="20"/>
       <c r="AG108" s="20"/>
@@ -7502,20 +7502,20 @@
         <v>2630444</v>
       </c>
       <c r="X109" s="20">
-        <v>0</v>
+        <v>2630444</v>
       </c>
       <c r="Y109" s="20"/>
       <c r="Z109" s="20">
-        <v>2630444</v>
+        <v>5260888</v>
       </c>
       <c r="AA109" s="20"/>
       <c r="AB109" s="20"/>
       <c r="AC109" s="21">
-        <v>219.20366666666666</v>
+        <v>438.40733333333333</v>
       </c>
       <c r="AD109" s="21"/>
       <c r="AE109" s="20">
-        <v>-2618444</v>
+        <v>-5248888</v>
       </c>
       <c r="AF109" s="20"/>
       <c r="AG109" s="20"/>
@@ -7916,20 +7916,20 @@
         <v>7676520</v>
       </c>
       <c r="X117" s="20">
-        <v>0</v>
+        <v>7821360</v>
       </c>
       <c r="Y117" s="20"/>
       <c r="Z117" s="20">
-        <v>7676520</v>
+        <v>15497880</v>
       </c>
       <c r="AA117" s="20"/>
       <c r="AB117" s="20"/>
       <c r="AC117" s="21">
-        <v>548.32285714285717</v>
+        <v>1106.9914285714285</v>
       </c>
       <c r="AD117" s="21"/>
       <c r="AE117" s="20">
-        <v>-7662520</v>
+        <v>-15483880</v>
       </c>
       <c r="AF117" s="20"/>
       <c r="AG117" s="20"/>
@@ -7969,20 +7969,20 @@
         <v>7676520</v>
       </c>
       <c r="X118" s="20">
-        <v>0</v>
+        <v>7821360</v>
       </c>
       <c r="Y118" s="20"/>
       <c r="Z118" s="20">
-        <v>7676520</v>
+        <v>15497880</v>
       </c>
       <c r="AA118" s="20"/>
       <c r="AB118" s="20"/>
       <c r="AC118" s="21">
-        <v>639.71</v>
+        <v>1291.49</v>
       </c>
       <c r="AD118" s="21"/>
       <c r="AE118" s="20">
-        <v>-7664520</v>
+        <v>-15485880</v>
       </c>
       <c r="AF118" s="20"/>
       <c r="AG118" s="20"/>
@@ -8238,20 +8238,20 @@
         <v>6780000</v>
       </c>
       <c r="X123" s="20">
-        <v>0</v>
+        <v>7150000</v>
       </c>
       <c r="Y123" s="20"/>
       <c r="Z123" s="20">
-        <v>6780000</v>
+        <v>13930000</v>
       </c>
       <c r="AA123" s="20"/>
       <c r="AB123" s="20"/>
       <c r="AC123" s="21">
-        <v>484.28571428571428</v>
+        <v>995</v>
       </c>
       <c r="AD123" s="21"/>
       <c r="AE123" s="20">
-        <v>-6766000</v>
+        <v>-13916000</v>
       </c>
       <c r="AF123" s="20"/>
       <c r="AG123" s="20"/>
@@ -8291,20 +8291,20 @@
         <v>6780000</v>
       </c>
       <c r="X124" s="20">
-        <v>0</v>
+        <v>7150000</v>
       </c>
       <c r="Y124" s="20"/>
       <c r="Z124" s="20">
-        <v>6780000</v>
+        <v>13930000</v>
       </c>
       <c r="AA124" s="20"/>
       <c r="AB124" s="20"/>
       <c r="AC124" s="21">
-        <v>565</v>
+        <v>1160.8333333333333</v>
       </c>
       <c r="AD124" s="21"/>
       <c r="AE124" s="20">
-        <v>-6768000</v>
+        <v>-13918000</v>
       </c>
       <c r="AF124" s="20"/>
       <c r="AG124" s="20"/>
@@ -8666,20 +8666,20 @@
         <v>45332488160</v>
       </c>
       <c r="X131" s="20">
-        <v>1613290947</v>
+        <v>1866079947</v>
       </c>
       <c r="Y131" s="20"/>
       <c r="Z131" s="20">
-        <v>46945779107</v>
+        <v>47198568107</v>
       </c>
       <c r="AA131" s="20"/>
       <c r="AB131" s="20"/>
       <c r="AC131" s="21">
-        <v>0.89664757938202799</v>
+        <v>0.90147575881063624</v>
       </c>
       <c r="AD131" s="21"/>
       <c r="AE131" s="20">
-        <v>5411222893</v>
+        <v>5158433893</v>
       </c>
       <c r="AF131" s="20"/>
       <c r="AG131" s="20"/>
@@ -10258,20 +10258,20 @@
         <v>1960479000</v>
       </c>
       <c r="X161" s="20">
-        <v>0</v>
+        <v>252789000</v>
       </c>
       <c r="Y161" s="20"/>
       <c r="Z161" s="20">
-        <v>1960479000</v>
+        <v>2213268000</v>
       </c>
       <c r="AA161" s="20"/>
       <c r="AB161" s="20"/>
       <c r="AC161" s="21">
-        <v>0.75977663374072213</v>
+        <v>0.8577441077441077</v>
       </c>
       <c r="AD161" s="21"/>
       <c r="AE161" s="20">
-        <v>619857000</v>
+        <v>367068000</v>
       </c>
       <c r="AF161" s="20"/>
       <c r="AG161" s="20"/>
@@ -10311,20 +10311,20 @@
         <v>174930000</v>
       </c>
       <c r="X162" s="20">
-        <v>0</v>
+        <v>24010000</v>
       </c>
       <c r="Y162" s="20"/>
       <c r="Z162" s="20">
-        <v>174930000</v>
+        <v>198940000</v>
       </c>
       <c r="AA162" s="20"/>
       <c r="AB162" s="20"/>
       <c r="AC162" s="21">
-        <v>0.68055555555555558</v>
+        <v>0.77396514161220042</v>
       </c>
       <c r="AD162" s="21"/>
       <c r="AE162" s="20">
-        <v>82110000</v>
+        <v>58100000</v>
       </c>
       <c r="AF162" s="20"/>
       <c r="AG162" s="20"/>
@@ -10364,20 +10364,20 @@
         <v>1398304000</v>
       </c>
       <c r="X163" s="20">
-        <v>0</v>
+        <v>183187000</v>
       </c>
       <c r="Y163" s="20"/>
       <c r="Z163" s="20">
-        <v>1398304000</v>
+        <v>1581491000</v>
       </c>
       <c r="AA163" s="20"/>
       <c r="AB163" s="20"/>
       <c r="AC163" s="21">
-        <v>0.78812145478812146</v>
+        <v>0.89137053720387049</v>
       </c>
       <c r="AD163" s="21"/>
       <c r="AE163" s="20">
-        <v>375920000</v>
+        <v>192733000</v>
       </c>
       <c r="AF163" s="20"/>
       <c r="AG163" s="20"/>
@@ -10417,20 +10417,20 @@
         <v>387245000</v>
       </c>
       <c r="X164" s="20">
-        <v>0</v>
+        <v>45592000</v>
       </c>
       <c r="Y164" s="20"/>
       <c r="Z164" s="20">
-        <v>387245000</v>
+        <v>432837000</v>
       </c>
       <c r="AA164" s="20"/>
       <c r="AB164" s="20"/>
       <c r="AC164" s="21">
-        <v>0.70527180406212664</v>
+        <v>0.78830645161290325</v>
       </c>
       <c r="AD164" s="21"/>
       <c r="AE164" s="20">
-        <v>161827000</v>
+        <v>116235000</v>
       </c>
       <c r="AF164" s="20"/>
       <c r="AG164" s="20"/>
@@ -10939,20 +10939,20 @@
         <v>17719617783</v>
       </c>
       <c r="X174" s="20">
-        <v>721438735</v>
+        <v>2104011383</v>
       </c>
       <c r="Y174" s="20"/>
       <c r="Z174" s="20">
-        <v>18441056518</v>
+        <v>19823629166</v>
       </c>
       <c r="AA174" s="20"/>
       <c r="AB174" s="20"/>
       <c r="AC174" s="21">
-        <v>1.1877562816083513</v>
+        <v>1.2768053740960301</v>
       </c>
       <c r="AD174" s="21"/>
       <c r="AE174" s="20">
-        <v>-2915096518</v>
+        <v>-4297669166</v>
       </c>
       <c r="AF174" s="20"/>
       <c r="AG174" s="20"/>
@@ -10994,20 +10994,20 @@
         <v>6410501266</v>
       </c>
       <c r="X175" s="20">
-        <v>550000800</v>
+        <v>1603941600</v>
       </c>
       <c r="Y175" s="20"/>
       <c r="Z175" s="20">
-        <v>6960502066</v>
+        <v>8014442866</v>
       </c>
       <c r="AA175" s="20"/>
       <c r="AB175" s="20"/>
       <c r="AC175" s="21">
-        <v>1.5592850893365586</v>
+        <v>1.7953879104981154</v>
       </c>
       <c r="AD175" s="21"/>
       <c r="AE175" s="20">
-        <v>-2496596066</v>
+        <v>-3550536866</v>
       </c>
       <c r="AF175" s="20"/>
       <c r="AG175" s="20"/>
@@ -11047,20 +11047,20 @@
         <v>5321387600</v>
       </c>
       <c r="X176" s="20">
-        <v>550000800</v>
+        <v>1603941600</v>
       </c>
       <c r="Y176" s="20"/>
       <c r="Z176" s="20">
-        <v>5871388400</v>
+        <v>6925329200</v>
       </c>
       <c r="AA176" s="20"/>
       <c r="AB176" s="20"/>
       <c r="AC176" s="21">
-        <v>1.7397819830839545</v>
+        <v>2.052080725759041</v>
       </c>
       <c r="AD176" s="21"/>
       <c r="AE176" s="20">
-        <v>-2496604400</v>
+        <v>-3550545200</v>
       </c>
       <c r="AF176" s="20"/>
       <c r="AG176" s="20"/>
@@ -11208,20 +11208,20 @@
         <v>121791</v>
       </c>
       <c r="X179" s="20">
-        <v>9755</v>
+        <v>15643</v>
       </c>
       <c r="Y179" s="20"/>
       <c r="Z179" s="20">
-        <v>131546</v>
+        <v>137434</v>
       </c>
       <c r="AA179" s="20"/>
       <c r="AB179" s="20"/>
       <c r="AC179" s="21">
-        <v>0.83256962025316461</v>
+        <v>0.86983544303797466</v>
       </c>
       <c r="AD179" s="21"/>
       <c r="AE179" s="20">
-        <v>26454</v>
+        <v>20566</v>
       </c>
       <c r="AF179" s="20"/>
       <c r="AG179" s="20"/>
@@ -11261,20 +11261,20 @@
         <v>108671</v>
       </c>
       <c r="X180" s="20">
-        <v>9755</v>
+        <v>15643</v>
       </c>
       <c r="Y180" s="20"/>
       <c r="Z180" s="20">
-        <v>118426</v>
+        <v>124314</v>
       </c>
       <c r="AA180" s="20"/>
       <c r="AB180" s="20"/>
       <c r="AC180" s="21">
-        <v>0.82240277777777782</v>
+        <v>0.86329166666666668</v>
       </c>
       <c r="AD180" s="21"/>
       <c r="AE180" s="20">
-        <v>25574</v>
+        <v>19686</v>
       </c>
       <c r="AF180" s="20"/>
       <c r="AG180" s="20"/>
@@ -11422,20 +11422,20 @@
         <v>435069690</v>
       </c>
       <c r="X183" s="20">
-        <v>37966880</v>
+        <v>108032320</v>
       </c>
       <c r="Y183" s="20"/>
       <c r="Z183" s="20">
-        <v>473036570</v>
+        <v>543102010</v>
       </c>
       <c r="AA183" s="20"/>
       <c r="AB183" s="20"/>
       <c r="AC183" s="21">
-        <v>1.310111087723574</v>
+        <v>1.5041627015559482</v>
       </c>
       <c r="AD183" s="21"/>
       <c r="AE183" s="20">
-        <v>-111970570</v>
+        <v>-182036010</v>
       </c>
       <c r="AF183" s="20"/>
       <c r="AG183" s="20"/>
@@ -11475,20 +11475,20 @@
         <v>361344920</v>
       </c>
       <c r="X184" s="20">
-        <v>37966880</v>
+        <v>108032320</v>
       </c>
       <c r="Y184" s="20"/>
       <c r="Z184" s="20">
-        <v>399311800</v>
+        <v>469377240</v>
       </c>
       <c r="AA184" s="20"/>
       <c r="AB184" s="20"/>
       <c r="AC184" s="21">
-        <v>1.3896839980510893</v>
+        <v>1.6335255794529129</v>
       </c>
       <c r="AD184" s="21"/>
       <c r="AE184" s="20">
-        <v>-111971800</v>
+        <v>-182037240</v>
       </c>
       <c r="AF184" s="20"/>
       <c r="AG184" s="20"/>
@@ -11636,20 +11636,20 @@
         <v>129819088</v>
       </c>
       <c r="X187" s="20">
-        <v>11190840</v>
+        <v>31926600</v>
       </c>
       <c r="Y187" s="20"/>
       <c r="Z187" s="20">
-        <v>141009928</v>
+        <v>161745688</v>
       </c>
       <c r="AA187" s="20"/>
       <c r="AB187" s="20"/>
       <c r="AC187" s="21">
-        <v>1.2582532747974444</v>
+        <v>1.4432816504265267</v>
       </c>
       <c r="AD187" s="21"/>
       <c r="AE187" s="20">
-        <v>-28941928</v>
+        <v>-49677688</v>
       </c>
       <c r="AF187" s="20"/>
       <c r="AG187" s="20"/>
@@ -11689,20 +11689,20 @@
         <v>107936504</v>
       </c>
       <c r="X188" s="20">
-        <v>11190840</v>
+        <v>31926600</v>
       </c>
       <c r="Y188" s="20"/>
       <c r="Z188" s="20">
-        <v>119127344</v>
+        <v>139863104</v>
       </c>
       <c r="AA188" s="20"/>
       <c r="AB188" s="20"/>
       <c r="AC188" s="21">
-        <v>1.3209951652251053</v>
+        <v>1.5509326236416057</v>
       </c>
       <c r="AD188" s="21"/>
       <c r="AE188" s="20">
-        <v>-28947344</v>
+        <v>-49683104</v>
       </c>
       <c r="AF188" s="20"/>
       <c r="AG188" s="20"/>
@@ -11850,20 +11850,20 @@
         <v>1044390000</v>
       </c>
       <c r="X191" s="20">
-        <v>88740000</v>
+        <v>262980000</v>
       </c>
       <c r="Y191" s="20"/>
       <c r="Z191" s="20">
-        <v>1133130000</v>
+        <v>1307370000</v>
       </c>
       <c r="AA191" s="20"/>
       <c r="AB191" s="20"/>
       <c r="AC191" s="21">
-        <v>1.2616407241632708</v>
+        <v>1.4556416594294876</v>
       </c>
       <c r="AD191" s="21"/>
       <c r="AE191" s="20">
-        <v>-234990000</v>
+        <v>-409230000</v>
       </c>
       <c r="AF191" s="20"/>
       <c r="AG191" s="20"/>
@@ -11903,20 +11903,20 @@
         <v>866580000</v>
       </c>
       <c r="X192" s="20">
-        <v>88740000</v>
+        <v>262980000</v>
       </c>
       <c r="Y192" s="20"/>
       <c r="Z192" s="20">
-        <v>955320000</v>
+        <v>1129560000</v>
       </c>
       <c r="AA192" s="20"/>
       <c r="AB192" s="20"/>
       <c r="AC192" s="21">
-        <v>1.32623652689623</v>
+        <v>1.5681276758791878</v>
       </c>
       <c r="AD192" s="21"/>
       <c r="AE192" s="20">
-        <v>-234996000</v>
+        <v>-409236000</v>
       </c>
       <c r="AF192" s="20"/>
       <c r="AG192" s="20"/>
@@ -12103,20 +12103,20 @@
         <v>392214650</v>
       </c>
       <c r="X196" s="20">
-        <v>33530460</v>
+        <v>97115220</v>
       </c>
       <c r="Y196" s="20"/>
       <c r="Z196" s="20">
-        <v>425745110</v>
+        <v>489329870</v>
       </c>
       <c r="AA196" s="20"/>
       <c r="AB196" s="20"/>
       <c r="AC196" s="21">
-        <v>1.2872190005684085</v>
+        <v>1.4794643353852479</v>
       </c>
       <c r="AD196" s="21"/>
       <c r="AE196" s="20">
-        <v>-94997110</v>
+        <v>-158581870</v>
       </c>
       <c r="AF196" s="20"/>
       <c r="AG196" s="20"/>
@@ -12156,20 +12156,20 @@
         <v>325672740</v>
       </c>
       <c r="X197" s="20">
-        <v>33530460</v>
+        <v>97115220</v>
       </c>
       <c r="Y197" s="20"/>
       <c r="Z197" s="20">
-        <v>359203200</v>
+        <v>422787960</v>
       </c>
       <c r="AA197" s="20"/>
       <c r="AB197" s="20"/>
       <c r="AC197" s="21">
-        <v>1.3595676068492528</v>
+        <v>1.6002330017713584</v>
       </c>
       <c r="AD197" s="21"/>
       <c r="AE197" s="20">
-        <v>-94999200</v>
+        <v>-158583960</v>
       </c>
       <c r="AF197" s="20"/>
       <c r="AG197" s="20"/>
@@ -12692,20 +12692,20 @@
         <v>5354544346</v>
       </c>
       <c r="X207" s="31">
-        <v>194396500</v>
+        <v>277700401</v>
       </c>
       <c r="Y207" s="31"/>
       <c r="Z207" s="31">
-        <v>5548940846</v>
+        <v>5632244747</v>
       </c>
       <c r="AA207" s="31"/>
       <c r="AB207" s="31"/>
       <c r="AC207" s="32">
-        <v>0.83213662932334376</v>
+        <v>0.84462914443775439</v>
       </c>
       <c r="AD207" s="32"/>
       <c r="AE207" s="31">
-        <v>1119364154</v>
+        <v>1036060253</v>
       </c>
       <c r="AF207" s="31"/>
       <c r="AG207" s="31"/>
@@ -12747,20 +12747,20 @@
         <v>4105668591</v>
       </c>
       <c r="X208" s="20">
-        <v>184486500</v>
+        <v>207886500</v>
       </c>
       <c r="Y208" s="20"/>
       <c r="Z208" s="20">
-        <v>4290155091</v>
+        <v>4313555091</v>
       </c>
       <c r="AA208" s="20"/>
       <c r="AB208" s="20"/>
       <c r="AC208" s="21">
-        <v>0.87031817012583657</v>
+        <v>0.87506518853169035</v>
       </c>
       <c r="AD208" s="21"/>
       <c r="AE208" s="20">
-        <v>639254909</v>
+        <v>615854909</v>
       </c>
       <c r="AF208" s="20"/>
       <c r="AG208" s="20"/>
@@ -12802,20 +12802,20 @@
         <v>1700954357</v>
       </c>
       <c r="X209" s="20">
-        <v>0</v>
+        <v>23400000</v>
       </c>
       <c r="Y209" s="20"/>
       <c r="Z209" s="20">
-        <v>1700954357</v>
+        <v>1724354357</v>
       </c>
       <c r="AA209" s="20"/>
       <c r="AB209" s="20"/>
       <c r="AC209" s="21">
-        <v>0.92320896562541899</v>
+        <v>0.93590953557706447</v>
       </c>
       <c r="AD209" s="21"/>
       <c r="AE209" s="20">
-        <v>141482643</v>
+        <v>118082643</v>
       </c>
       <c r="AF209" s="20"/>
       <c r="AG209" s="20"/>
@@ -13226,20 +13226,20 @@
         <v>0</v>
       </c>
       <c r="X217" s="20">
-        <v>0</v>
+        <v>23400000</v>
       </c>
       <c r="Y217" s="20"/>
       <c r="Z217" s="20">
-        <v>0</v>
+        <v>23400000</v>
       </c>
       <c r="AA217" s="20"/>
       <c r="AB217" s="20"/>
       <c r="AC217" s="21">
-        <v>0</v>
+        <v>0.2988505747126437</v>
       </c>
       <c r="AD217" s="21"/>
       <c r="AE217" s="20">
-        <v>78300000</v>
+        <v>54900000</v>
       </c>
       <c r="AF217" s="20"/>
       <c r="AG217" s="20"/>
@@ -14229,20 +14229,20 @@
         <v>587220368</v>
       </c>
       <c r="X236" s="20">
-        <v>0</v>
+        <v>50455581</v>
       </c>
       <c r="Y236" s="20"/>
       <c r="Z236" s="20">
-        <v>587220368</v>
+        <v>637675949</v>
       </c>
       <c r="AA236" s="20"/>
       <c r="AB236" s="20"/>
       <c r="AC236" s="21">
-        <v>0.69355644163084051</v>
+        <v>0.75314870907544762</v>
       </c>
       <c r="AD236" s="21"/>
       <c r="AE236" s="20">
-        <v>259459632</v>
+        <v>209004051</v>
       </c>
       <c r="AF236" s="20"/>
       <c r="AG236" s="20"/>
@@ -14284,20 +14284,20 @@
         <v>430266392</v>
       </c>
       <c r="X237" s="20">
-        <v>0</v>
+        <v>40247519</v>
       </c>
       <c r="Y237" s="20"/>
       <c r="Z237" s="20">
-        <v>430266392</v>
+        <v>470513911</v>
       </c>
       <c r="AA237" s="20"/>
       <c r="AB237" s="20"/>
       <c r="AC237" s="21">
-        <v>0.66658361529404475</v>
+        <v>0.72893646743508711</v>
       </c>
       <c r="AD237" s="21"/>
       <c r="AE237" s="20">
-        <v>215213608</v>
+        <v>174966089</v>
       </c>
       <c r="AF237" s="20"/>
       <c r="AG237" s="20"/>
@@ -14337,20 +14337,20 @@
         <v>430266392</v>
       </c>
       <c r="X238" s="20">
-        <v>0</v>
+        <v>40247519</v>
       </c>
       <c r="Y238" s="20"/>
       <c r="Z238" s="20">
-        <v>430266392</v>
+        <v>470513911</v>
       </c>
       <c r="AA238" s="20"/>
       <c r="AB238" s="20"/>
       <c r="AC238" s="21">
-        <v>0.66658361529404475</v>
+        <v>0.72893646743508711</v>
       </c>
       <c r="AD238" s="21"/>
       <c r="AE238" s="20">
-        <v>215213608</v>
+        <v>174966089</v>
       </c>
       <c r="AF238" s="20"/>
       <c r="AG238" s="20"/>
@@ -14392,20 +14392,20 @@
         <v>5219220</v>
       </c>
       <c r="X239" s="20">
-        <v>0</v>
+        <v>266012</v>
       </c>
       <c r="Y239" s="20"/>
       <c r="Z239" s="20">
-        <v>5219220</v>
+        <v>5485232</v>
       </c>
       <c r="AA239" s="20"/>
       <c r="AB239" s="20"/>
       <c r="AC239" s="21">
-        <v>0.86987000000000003</v>
+        <v>0.91420533333333331</v>
       </c>
       <c r="AD239" s="21"/>
       <c r="AE239" s="20">
-        <v>780780</v>
+        <v>514768</v>
       </c>
       <c r="AF239" s="20"/>
       <c r="AG239" s="20"/>
@@ -14445,20 +14445,20 @@
         <v>5219220</v>
       </c>
       <c r="X240" s="20">
-        <v>0</v>
+        <v>266012</v>
       </c>
       <c r="Y240" s="20"/>
       <c r="Z240" s="20">
-        <v>5219220</v>
+        <v>5485232</v>
       </c>
       <c r="AA240" s="20"/>
       <c r="AB240" s="20"/>
       <c r="AC240" s="21">
-        <v>0.86987000000000003</v>
+        <v>0.91420533333333331</v>
       </c>
       <c r="AD240" s="21"/>
       <c r="AE240" s="20">
-        <v>780780</v>
+        <v>514768</v>
       </c>
       <c r="AF240" s="20"/>
       <c r="AG240" s="20"/>
@@ -14500,20 +14500,20 @@
         <v>29408400</v>
       </c>
       <c r="X241" s="20">
-        <v>0</v>
+        <v>691300</v>
       </c>
       <c r="Y241" s="20"/>
       <c r="Z241" s="20">
-        <v>29408400</v>
+        <v>30099700</v>
       </c>
       <c r="AA241" s="20"/>
       <c r="AB241" s="20"/>
       <c r="AC241" s="21">
-        <v>0.74263636363636365</v>
+        <v>0.76009343434343435</v>
       </c>
       <c r="AD241" s="21"/>
       <c r="AE241" s="20">
-        <v>10191600</v>
+        <v>9500300</v>
       </c>
       <c r="AF241" s="20"/>
       <c r="AG241" s="20"/>
@@ -14553,20 +14553,20 @@
         <v>29408400</v>
       </c>
       <c r="X242" s="20">
-        <v>0</v>
+        <v>691300</v>
       </c>
       <c r="Y242" s="20"/>
       <c r="Z242" s="20">
-        <v>29408400</v>
+        <v>30099700</v>
       </c>
       <c r="AA242" s="20"/>
       <c r="AB242" s="20"/>
       <c r="AC242" s="21">
-        <v>0.74263636363636365</v>
+        <v>0.76009343434343435</v>
       </c>
       <c r="AD242" s="21"/>
       <c r="AE242" s="20">
-        <v>10191600</v>
+        <v>9500300</v>
       </c>
       <c r="AF242" s="20"/>
       <c r="AG242" s="20"/>
@@ -14608,20 +14608,20 @@
         <v>122326356</v>
       </c>
       <c r="X243" s="20">
-        <v>0</v>
+        <v>9250750</v>
       </c>
       <c r="Y243" s="20"/>
       <c r="Z243" s="20">
-        <v>122326356</v>
+        <v>131577106</v>
       </c>
       <c r="AA243" s="20"/>
       <c r="AB243" s="20"/>
       <c r="AC243" s="21">
-        <v>0.78615910025706937</v>
+        <v>0.84561122107969156</v>
       </c>
       <c r="AD243" s="21"/>
       <c r="AE243" s="20">
-        <v>33273644</v>
+        <v>24022894</v>
       </c>
       <c r="AF243" s="20"/>
       <c r="AG243" s="20"/>
@@ -14661,20 +14661,20 @@
         <v>95184750</v>
       </c>
       <c r="X244" s="20">
-        <v>0</v>
+        <v>9250750</v>
       </c>
       <c r="Y244" s="20"/>
       <c r="Z244" s="20">
-        <v>95184750</v>
+        <v>104435500</v>
       </c>
       <c r="AA244" s="20"/>
       <c r="AB244" s="20"/>
       <c r="AC244" s="21">
-        <v>0.75007683215130028</v>
+        <v>0.82297478329393225</v>
       </c>
       <c r="AD244" s="21"/>
       <c r="AE244" s="20">
-        <v>31715250</v>
+        <v>22464500</v>
       </c>
       <c r="AF244" s="20"/>
       <c r="AG244" s="20"/>
@@ -14769,20 +14769,20 @@
         <v>560645387</v>
       </c>
       <c r="X246" s="20">
-        <v>0</v>
+        <v>9448320</v>
       </c>
       <c r="Y246" s="20"/>
       <c r="Z246" s="20">
-        <v>560645387</v>
+        <v>570093707</v>
       </c>
       <c r="AA246" s="20"/>
       <c r="AB246" s="20"/>
       <c r="AC246" s="21">
-        <v>0.73765732762307001</v>
+        <v>0.75008875512311934</v>
       </c>
       <c r="AD246" s="21"/>
       <c r="AE246" s="20">
-        <v>199389613</v>
+        <v>189941293</v>
       </c>
       <c r="AF246" s="20"/>
       <c r="AG246" s="20"/>
@@ -15929,20 +15929,20 @@
         <v>158031069</v>
       </c>
       <c r="X268" s="20">
-        <v>0</v>
+        <v>9448320</v>
       </c>
       <c r="Y268" s="20"/>
       <c r="Z268" s="20">
-        <v>158031069</v>
+        <v>167479389</v>
       </c>
       <c r="AA268" s="20"/>
       <c r="AB268" s="20"/>
       <c r="AC268" s="21">
-        <v>0.68721111932510004</v>
+        <v>0.72829791702904856</v>
       </c>
       <c r="AD268" s="21"/>
       <c r="AE268" s="20">
-        <v>71928931</v>
+        <v>62480611</v>
       </c>
       <c r="AF268" s="20"/>
       <c r="AG268" s="20"/>
@@ -16247,20 +16247,20 @@
         <v>4737535</v>
       </c>
       <c r="X274" s="20">
-        <v>0</v>
+        <v>9448320</v>
       </c>
       <c r="Y274" s="20"/>
       <c r="Z274" s="20">
-        <v>4737535</v>
+        <v>14185855</v>
       </c>
       <c r="AA274" s="20"/>
       <c r="AB274" s="20"/>
       <c r="AC274" s="21">
-        <v>0.32672655172413795</v>
+        <v>0.97833482758620693</v>
       </c>
       <c r="AD274" s="21"/>
       <c r="AE274" s="20">
-        <v>9762465</v>
+        <v>314145</v>
       </c>
       <c r="AF274" s="20"/>
       <c r="AG274" s="20"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F19C99CC-53DB-4EAD-9F58-7C3BEE9194C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87A8FFCA-33AD-41AE-A1A5-C492BBF00E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="600" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLP039_LAPORAN REALISASI SUPER " sheetId="1" r:id="rId1"/>
@@ -2129,19 +2129,19 @@
         <v>77645055879</v>
       </c>
       <c r="X9" s="4">
-        <v>7012495292</v>
+        <v>8911140550</v>
       </c>
       <c r="Y9" s="18">
-        <v>84657551171</v>
+        <v>86556196429</v>
       </c>
       <c r="Z9" s="18"/>
       <c r="AA9" s="18"/>
       <c r="AB9" s="18"/>
       <c r="AC9" s="5">
-        <v>0.84660905436073375</v>
+        <v>0.86559625921379002</v>
       </c>
       <c r="AD9" s="18">
-        <v>15338486829</v>
+        <v>13439841571</v>
       </c>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
@@ -2781,20 +2781,20 @@
         <v>73611687839</v>
       </c>
       <c r="X21" s="20">
-        <v>7012495292</v>
+        <v>8911140550</v>
       </c>
       <c r="Y21" s="20"/>
       <c r="Z21" s="20">
-        <v>80624183131</v>
+        <v>82522828389</v>
       </c>
       <c r="AA21" s="20"/>
       <c r="AB21" s="20"/>
       <c r="AC21" s="21">
-        <v>0.84016222158252885</v>
+        <v>0.85994747652727099</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="20">
-        <v>15338454869</v>
+        <v>13439809611</v>
       </c>
       <c r="AF21" s="20"/>
       <c r="AG21" s="20"/>
@@ -2836,20 +2836,20 @@
         <v>73611687839</v>
       </c>
       <c r="X22" s="20">
-        <v>7012495292</v>
+        <v>8911140550</v>
       </c>
       <c r="Y22" s="20"/>
       <c r="Z22" s="20">
-        <v>80624183131</v>
+        <v>82522828389</v>
       </c>
       <c r="AA22" s="20"/>
       <c r="AB22" s="20"/>
       <c r="AC22" s="21">
-        <v>0.84016222158252885</v>
+        <v>0.85994747652727099</v>
       </c>
       <c r="AD22" s="21"/>
       <c r="AE22" s="20">
-        <v>15338454869</v>
+        <v>13439809611</v>
       </c>
       <c r="AF22" s="20"/>
       <c r="AG22" s="20"/>
@@ -2891,20 +2891,20 @@
         <v>73611087839</v>
       </c>
       <c r="X23" s="23">
-        <v>7012495292</v>
+        <v>8911140550</v>
       </c>
       <c r="Y23" s="23"/>
       <c r="Z23" s="23">
-        <v>80623583131</v>
+        <v>82522228389</v>
       </c>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
       <c r="AC23" s="24">
-        <v>0.84016122220122091</v>
+        <v>0.85994660085272467</v>
       </c>
       <c r="AD23" s="24"/>
       <c r="AE23" s="23">
-        <v>15338454869</v>
+        <v>13439809611</v>
       </c>
       <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
@@ -4128,20 +4128,20 @@
         <v>73595376787</v>
       </c>
       <c r="X46" s="28">
-        <v>7010695292</v>
+        <v>8909340550</v>
       </c>
       <c r="Y46" s="28"/>
       <c r="Z46" s="27">
-        <v>80606072079</v>
+        <v>82504717337</v>
       </c>
       <c r="AA46" s="27"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="29">
-        <v>0.8401409721124643</v>
+        <v>0.85993017200288324</v>
       </c>
       <c r="AD46" s="29"/>
       <c r="AE46" s="27">
-        <v>15337435921</v>
+        <v>13438790663</v>
       </c>
       <c r="AF46" s="27"/>
       <c r="AG46" s="27"/>
@@ -4183,20 +4183,20 @@
         <v>68240832441</v>
       </c>
       <c r="X47" s="31">
-        <v>6732994891</v>
+        <v>8511338734</v>
       </c>
       <c r="Y47" s="31"/>
       <c r="Z47" s="31">
-        <v>74973827332</v>
+        <v>76752171175</v>
       </c>
       <c r="AA47" s="31"/>
       <c r="AB47" s="31"/>
       <c r="AC47" s="32">
-        <v>0.84243357288559939</v>
+        <v>0.86241570012639679</v>
       </c>
       <c r="AD47" s="32"/>
       <c r="AE47" s="31">
-        <v>14022895668</v>
+        <v>12244551825</v>
       </c>
       <c r="AF47" s="31"/>
       <c r="AG47" s="31"/>
@@ -6725,20 +6725,20 @@
         <v>136865920</v>
       </c>
       <c r="X95" s="20">
-        <v>174621036</v>
+        <v>316721150</v>
       </c>
       <c r="Y95" s="20"/>
       <c r="Z95" s="20">
-        <v>311486956</v>
+        <v>453587070</v>
       </c>
       <c r="AA95" s="20"/>
       <c r="AB95" s="20"/>
       <c r="AC95" s="21">
-        <v>0.32198628477390756</v>
+        <v>0.46887618462836161</v>
       </c>
       <c r="AD95" s="21"/>
       <c r="AE95" s="20">
-        <v>655905044</v>
+        <v>513804930</v>
       </c>
       <c r="AF95" s="20"/>
       <c r="AG95" s="20"/>
@@ -7589,20 +7589,20 @@
         <v>0</v>
       </c>
       <c r="X111" s="20">
-        <v>0</v>
+        <v>142100114</v>
       </c>
       <c r="Y111" s="20"/>
       <c r="Z111" s="20">
-        <v>0</v>
+        <v>142100114</v>
       </c>
       <c r="AA111" s="20"/>
       <c r="AB111" s="20"/>
       <c r="AC111" s="21">
-        <v>0</v>
+        <v>0.31577803111111113</v>
       </c>
       <c r="AD111" s="21"/>
       <c r="AE111" s="20">
-        <v>450000000</v>
+        <v>307899886</v>
       </c>
       <c r="AF111" s="20"/>
       <c r="AG111" s="20"/>
@@ -7642,20 +7642,20 @@
         <v>0</v>
       </c>
       <c r="X112" s="20">
-        <v>0</v>
+        <v>142100114</v>
       </c>
       <c r="Y112" s="20"/>
       <c r="Z112" s="20">
-        <v>0</v>
+        <v>142100114</v>
       </c>
       <c r="AA112" s="20"/>
       <c r="AB112" s="20"/>
       <c r="AC112" s="21">
-        <v>0</v>
+        <v>0.31577803111111113</v>
       </c>
       <c r="AD112" s="21"/>
       <c r="AE112" s="20">
-        <v>450000000</v>
+        <v>307899886</v>
       </c>
       <c r="AF112" s="20"/>
       <c r="AG112" s="20"/>
@@ -9970,20 +9970,20 @@
         <v>17719617783</v>
       </c>
       <c r="X156" s="20">
-        <v>2390581455</v>
+        <v>4026825184</v>
       </c>
       <c r="Y156" s="20"/>
       <c r="Z156" s="20">
-        <v>20110199238</v>
+        <v>21746442967</v>
       </c>
       <c r="AA156" s="20"/>
       <c r="AB156" s="20"/>
       <c r="AC156" s="21">
-        <v>0.74622099908168604</v>
+        <v>0.80693643087553601</v>
       </c>
       <c r="AD156" s="21"/>
       <c r="AE156" s="20">
-        <v>6839188762</v>
+        <v>5202945033</v>
       </c>
       <c r="AF156" s="20"/>
       <c r="AG156" s="20"/>
@@ -10025,20 +10025,20 @@
         <v>6410501266</v>
       </c>
       <c r="X157" s="20">
-        <v>1610348800</v>
+        <v>1718104000</v>
       </c>
       <c r="Y157" s="20"/>
       <c r="Z157" s="20">
-        <v>8020850066</v>
+        <v>8128605266</v>
       </c>
       <c r="AA157" s="20"/>
       <c r="AB157" s="20"/>
       <c r="AC157" s="21">
-        <v>0.86847637810536726</v>
+        <v>0.88014382545171688</v>
       </c>
       <c r="AD157" s="21"/>
       <c r="AE157" s="20">
-        <v>1214691934</v>
+        <v>1106936734</v>
       </c>
       <c r="AF157" s="20"/>
       <c r="AG157" s="20"/>
@@ -10078,20 +10078,20 @@
         <v>5321387600</v>
       </c>
       <c r="X158" s="20">
-        <v>1610348800</v>
+        <v>1718104000</v>
       </c>
       <c r="Y158" s="20"/>
       <c r="Z158" s="20">
-        <v>6931736400</v>
+        <v>7039491600</v>
       </c>
       <c r="AA158" s="20"/>
       <c r="AB158" s="20"/>
       <c r="AC158" s="21">
-        <v>0.85256805921465306</v>
+        <v>0.86582139668061431</v>
       </c>
       <c r="AD158" s="21"/>
       <c r="AE158" s="20">
-        <v>1198683600</v>
+        <v>1090928400</v>
       </c>
       <c r="AF158" s="20"/>
       <c r="AG158" s="20"/>
@@ -10239,20 +10239,20 @@
         <v>121791</v>
       </c>
       <c r="X161" s="20">
-        <v>15675</v>
+        <v>49081</v>
       </c>
       <c r="Y161" s="20"/>
       <c r="Z161" s="20">
-        <v>137466</v>
+        <v>170872</v>
       </c>
       <c r="AA161" s="20"/>
       <c r="AB161" s="20"/>
       <c r="AC161" s="21">
-        <v>0.75530769230769235</v>
+        <v>0.93885714285714283</v>
       </c>
       <c r="AD161" s="21"/>
       <c r="AE161" s="20">
-        <v>44534</v>
+        <v>11128</v>
       </c>
       <c r="AF161" s="20"/>
       <c r="AG161" s="20"/>
@@ -10292,20 +10292,20 @@
         <v>108671</v>
       </c>
       <c r="X162" s="20">
-        <v>15675</v>
+        <v>49081</v>
       </c>
       <c r="Y162" s="20"/>
       <c r="Z162" s="20">
-        <v>124346</v>
+        <v>157752</v>
       </c>
       <c r="AA162" s="20"/>
       <c r="AB162" s="20"/>
       <c r="AC162" s="21">
-        <v>0.74015476190476193</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="AD162" s="21"/>
       <c r="AE162" s="20">
-        <v>43654</v>
+        <v>10248</v>
       </c>
       <c r="AF162" s="20"/>
       <c r="AG162" s="20"/>
@@ -10453,20 +10453,20 @@
         <v>435069690</v>
       </c>
       <c r="X165" s="20">
-        <v>108032320</v>
+        <v>116287840</v>
       </c>
       <c r="Y165" s="20"/>
       <c r="Z165" s="20">
-        <v>543102010</v>
+        <v>551357530</v>
       </c>
       <c r="AA165" s="20"/>
       <c r="AB165" s="20"/>
       <c r="AC165" s="21">
-        <v>0.84769885964556302</v>
+        <v>0.86058445896378521</v>
       </c>
       <c r="AD165" s="21"/>
       <c r="AE165" s="20">
-        <v>97575990</v>
+        <v>89320470</v>
       </c>
       <c r="AF165" s="20"/>
       <c r="AG165" s="20"/>
@@ -10506,20 +10506,20 @@
         <v>361344920</v>
       </c>
       <c r="X166" s="20">
-        <v>108032320</v>
+        <v>116287840</v>
       </c>
       <c r="Y166" s="20"/>
       <c r="Z166" s="20">
-        <v>469377240</v>
+        <v>477632760</v>
       </c>
       <c r="AA166" s="20"/>
       <c r="AB166" s="20"/>
       <c r="AC166" s="21">
-        <v>0.82789590653176992</v>
+        <v>0.84245713922871779</v>
       </c>
       <c r="AD166" s="21"/>
       <c r="AE166" s="20">
-        <v>97574760</v>
+        <v>89319240</v>
       </c>
       <c r="AF166" s="20"/>
       <c r="AG166" s="20"/>
@@ -10706,20 +10706,20 @@
         <v>129819088</v>
       </c>
       <c r="X170" s="20">
-        <v>31926600</v>
+        <v>34309512</v>
       </c>
       <c r="Y170" s="20"/>
       <c r="Z170" s="20">
-        <v>161745688</v>
+        <v>164128600</v>
       </c>
       <c r="AA170" s="20"/>
       <c r="AB170" s="20"/>
       <c r="AC170" s="21">
-        <v>0.84644607720003351</v>
+        <v>0.85891631080967934</v>
       </c>
       <c r="AD170" s="21"/>
       <c r="AE170" s="20">
-        <v>29342312</v>
+        <v>26959400</v>
       </c>
       <c r="AF170" s="20"/>
       <c r="AG170" s="20"/>
@@ -10759,20 +10759,20 @@
         <v>107936504</v>
       </c>
       <c r="X171" s="20">
-        <v>31926600</v>
+        <v>34309512</v>
       </c>
       <c r="Y171" s="20"/>
       <c r="Z171" s="20">
-        <v>139863104</v>
+        <v>142246016</v>
       </c>
       <c r="AA171" s="20"/>
       <c r="AB171" s="20"/>
       <c r="AC171" s="21">
-        <v>0.82661408983451534</v>
+        <v>0.84069749408983452</v>
       </c>
       <c r="AD171" s="21"/>
       <c r="AE171" s="20">
-        <v>29336896</v>
+        <v>26953984</v>
       </c>
       <c r="AF171" s="20"/>
       <c r="AG171" s="20"/>
@@ -11509,20 +11509,20 @@
         <v>8276864298</v>
       </c>
       <c r="X185" s="20">
-        <v>0</v>
+        <v>1517816691</v>
       </c>
       <c r="Y185" s="20"/>
       <c r="Z185" s="20">
-        <v>8276864298</v>
+        <v>9794680989</v>
       </c>
       <c r="AA185" s="20"/>
       <c r="AB185" s="20"/>
       <c r="AC185" s="21">
-        <v>0.63441486077366305</v>
+        <v>0.75075426541188894</v>
       </c>
       <c r="AD185" s="21"/>
       <c r="AE185" s="20">
-        <v>4769589702</v>
+        <v>3251773011</v>
       </c>
       <c r="AF185" s="20"/>
       <c r="AG185" s="20"/>
@@ -11562,20 +11562,20 @@
         <v>6702420922</v>
       </c>
       <c r="X186" s="20">
-        <v>0</v>
+        <v>1517816691</v>
       </c>
       <c r="Y186" s="20"/>
       <c r="Z186" s="20">
-        <v>6702420922</v>
+        <v>8220237613</v>
       </c>
       <c r="AA186" s="20"/>
       <c r="AB186" s="20"/>
       <c r="AC186" s="21">
-        <v>0.58424171216875875</v>
+        <v>0.71654790908298471</v>
       </c>
       <c r="AD186" s="21"/>
       <c r="AE186" s="20">
-        <v>4769579078</v>
+        <v>3251762387</v>
       </c>
       <c r="AF186" s="20"/>
       <c r="AG186" s="20"/>
@@ -11723,20 +11723,20 @@
         <v>5354544346</v>
       </c>
       <c r="X189" s="31">
-        <v>277700401</v>
+        <v>398001816</v>
       </c>
       <c r="Y189" s="31"/>
       <c r="Z189" s="31">
-        <v>5632244747</v>
+        <v>5752546162</v>
       </c>
       <c r="AA189" s="31"/>
       <c r="AB189" s="31"/>
       <c r="AC189" s="32">
-        <v>0.81076998165338354</v>
+        <v>0.82808754870058598</v>
       </c>
       <c r="AD189" s="32"/>
       <c r="AE189" s="31">
-        <v>1314540253</v>
+        <v>1194238838</v>
       </c>
       <c r="AF189" s="31"/>
       <c r="AG189" s="31"/>
@@ -11778,20 +11778,20 @@
         <v>4105668591</v>
       </c>
       <c r="X190" s="20">
-        <v>207886500</v>
+        <v>277090765</v>
       </c>
       <c r="Y190" s="20"/>
       <c r="Z190" s="20">
-        <v>4313555091</v>
+        <v>4382759356</v>
       </c>
       <c r="AA190" s="20"/>
       <c r="AB190" s="20"/>
       <c r="AC190" s="21">
-        <v>0.86135180505162856</v>
+        <v>0.87517085159618124</v>
       </c>
       <c r="AD190" s="21"/>
       <c r="AE190" s="20">
-        <v>694334909</v>
+        <v>625130644</v>
       </c>
       <c r="AF190" s="20"/>
       <c r="AG190" s="20"/>
@@ -11833,20 +11833,20 @@
         <v>1700954357</v>
       </c>
       <c r="X191" s="20">
-        <v>23400000</v>
+        <v>51408997</v>
       </c>
       <c r="Y191" s="20"/>
       <c r="Z191" s="20">
-        <v>1724354357</v>
+        <v>1752363354</v>
       </c>
       <c r="AA191" s="20"/>
       <c r="AB191" s="20"/>
       <c r="AC191" s="21">
-        <v>0.89767249548002337</v>
+        <v>0.91225355077809189</v>
       </c>
       <c r="AD191" s="21"/>
       <c r="AE191" s="20">
-        <v>196562643</v>
+        <v>168553646</v>
       </c>
       <c r="AF191" s="20"/>
       <c r="AG191" s="20"/>
@@ -11992,20 +11992,20 @@
         <v>50329917</v>
       </c>
       <c r="X194" s="20">
-        <v>0</v>
+        <v>2708197</v>
       </c>
       <c r="Y194" s="20"/>
       <c r="Z194" s="20">
-        <v>50329917</v>
+        <v>53038114</v>
       </c>
       <c r="AA194" s="20"/>
       <c r="AB194" s="20"/>
       <c r="AC194" s="21">
-        <v>0.78993497504473109</v>
+        <v>0.83244049973318268</v>
       </c>
       <c r="AD194" s="21"/>
       <c r="AE194" s="20">
-        <v>13384083</v>
+        <v>10675886</v>
       </c>
       <c r="AF194" s="20"/>
       <c r="AG194" s="20"/>
@@ -12084,7 +12084,7 @@
         <v>50329917</v>
       </c>
       <c r="X196" s="20">
-        <v>0</v>
+        <v>2708197</v>
       </c>
       <c r="Y196" s="20"/>
       <c r="Z196" s="1"/>
@@ -12093,7 +12093,7 @@
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
       <c r="AE196" s="20">
-        <v>13384083</v>
+        <v>10675886</v>
       </c>
       <c r="AF196" s="20"/>
       <c r="AG196" s="20"/>
@@ -12345,20 +12345,20 @@
         <v>0</v>
       </c>
       <c r="X201" s="20">
-        <v>23400000</v>
+        <v>48700800</v>
       </c>
       <c r="Y201" s="20"/>
       <c r="Z201" s="20">
-        <v>23400000</v>
+        <v>48700800</v>
       </c>
       <c r="AA201" s="20"/>
       <c r="AB201" s="20"/>
       <c r="AC201" s="21">
-        <v>0.2988505747126437</v>
+        <v>0.62197701149425288</v>
       </c>
       <c r="AD201" s="21"/>
       <c r="AE201" s="20">
-        <v>54900000</v>
+        <v>29599200</v>
       </c>
       <c r="AF201" s="20"/>
       <c r="AG201" s="20"/>
@@ -12506,20 +12506,20 @@
         <v>8928000</v>
       </c>
       <c r="X204" s="20">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="Y204" s="20"/>
       <c r="Z204" s="20">
-        <v>8928000</v>
+        <v>9332000</v>
       </c>
       <c r="AA204" s="20"/>
       <c r="AB204" s="20"/>
       <c r="AC204" s="21">
-        <v>0.89280000000000004</v>
+        <v>0.93320000000000003</v>
       </c>
       <c r="AD204" s="21"/>
       <c r="AE204" s="20">
-        <v>1072000</v>
+        <v>668000</v>
       </c>
       <c r="AF204" s="20"/>
       <c r="AG204" s="20"/>
@@ -12612,20 +12612,20 @@
         <v>3232000</v>
       </c>
       <c r="X206" s="20">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="Y206" s="20"/>
       <c r="Z206" s="20">
-        <v>3232000</v>
+        <v>3636000</v>
       </c>
       <c r="AA206" s="20"/>
       <c r="AB206" s="20"/>
       <c r="AC206" s="21">
-        <v>0.7695238095238095</v>
+        <v>0.86571428571428577</v>
       </c>
       <c r="AD206" s="21"/>
       <c r="AE206" s="20">
-        <v>968000</v>
+        <v>564000</v>
       </c>
       <c r="AF206" s="20"/>
       <c r="AG206" s="20"/>
@@ -12667,20 +12667,20 @@
         <v>46348510</v>
       </c>
       <c r="X207" s="20">
-        <v>0</v>
+        <v>2722500</v>
       </c>
       <c r="Y207" s="20"/>
       <c r="Z207" s="20">
-        <v>46348510</v>
+        <v>49071010</v>
       </c>
       <c r="AA207" s="20"/>
       <c r="AB207" s="20"/>
       <c r="AC207" s="21">
-        <v>0.77759432933478734</v>
+        <v>0.82327002768224145</v>
       </c>
       <c r="AD207" s="21"/>
       <c r="AE207" s="20">
-        <v>13256490</v>
+        <v>10533990</v>
       </c>
       <c r="AF207" s="20"/>
       <c r="AG207" s="20"/>
@@ -12720,20 +12720,20 @@
         <v>46348510</v>
       </c>
       <c r="X208" s="20">
-        <v>0</v>
+        <v>2722500</v>
       </c>
       <c r="Y208" s="20"/>
       <c r="Z208" s="20">
-        <v>46348510</v>
+        <v>49071010</v>
       </c>
       <c r="AA208" s="20"/>
       <c r="AB208" s="20"/>
       <c r="AC208" s="21">
-        <v>0.77759432933478734</v>
+        <v>0.82327002768224145</v>
       </c>
       <c r="AD208" s="21"/>
       <c r="AE208" s="20">
-        <v>13256490</v>
+        <v>10533990</v>
       </c>
       <c r="AF208" s="20"/>
       <c r="AG208" s="20"/>
@@ -12775,20 +12775,20 @@
         <v>3257800</v>
       </c>
       <c r="X209" s="20">
-        <v>0</v>
+        <v>1017000</v>
       </c>
       <c r="Y209" s="20"/>
       <c r="Z209" s="20">
-        <v>3257800</v>
+        <v>4274800</v>
       </c>
       <c r="AA209" s="20"/>
       <c r="AB209" s="20"/>
       <c r="AC209" s="21">
-        <v>0.54296666666666671</v>
+        <v>0.71246666666666669</v>
       </c>
       <c r="AD209" s="21"/>
       <c r="AE209" s="20">
-        <v>2742200</v>
+        <v>1725200</v>
       </c>
       <c r="AF209" s="20"/>
       <c r="AG209" s="20"/>
@@ -12828,20 +12828,20 @@
         <v>2947800</v>
       </c>
       <c r="X210" s="20">
-        <v>0</v>
+        <v>1017000</v>
       </c>
       <c r="Y210" s="20"/>
       <c r="Z210" s="20">
-        <v>2947800</v>
+        <v>3964800</v>
       </c>
       <c r="AA210" s="20"/>
       <c r="AB210" s="20"/>
       <c r="AC210" s="21">
-        <v>0.73694999999999999</v>
+        <v>0.99119999999999997</v>
       </c>
       <c r="AD210" s="21"/>
       <c r="AE210" s="20">
-        <v>1052200</v>
+        <v>35200</v>
       </c>
       <c r="AF210" s="20"/>
       <c r="AG210" s="20"/>
@@ -12936,20 +12936,20 @@
         <v>2346179924</v>
       </c>
       <c r="X212" s="20">
-        <v>184486500</v>
+        <v>221538268</v>
       </c>
       <c r="Y212" s="20"/>
       <c r="Z212" s="20">
-        <v>2530666424</v>
+        <v>2567718192</v>
       </c>
       <c r="AA212" s="20"/>
       <c r="AB212" s="20"/>
       <c r="AC212" s="21">
-        <v>0.84037102871518854</v>
+        <v>0.85267499422189519</v>
       </c>
       <c r="AD212" s="21"/>
       <c r="AE212" s="20">
-        <v>480701576</v>
+        <v>443649808</v>
       </c>
       <c r="AF212" s="20"/>
       <c r="AG212" s="20"/>
@@ -13042,20 +13042,20 @@
         <v>93850352</v>
       </c>
       <c r="X214" s="20">
-        <v>0</v>
+        <v>9468528</v>
       </c>
       <c r="Y214" s="20"/>
       <c r="Z214" s="20">
-        <v>93850352</v>
+        <v>103318880</v>
       </c>
       <c r="AA214" s="20"/>
       <c r="AB214" s="20"/>
       <c r="AC214" s="21">
-        <v>0.76550042414355624</v>
+        <v>0.84273148450244695</v>
       </c>
       <c r="AD214" s="21"/>
       <c r="AE214" s="20">
-        <v>28749648</v>
+        <v>19281120</v>
       </c>
       <c r="AF214" s="20"/>
       <c r="AG214" s="20"/>
@@ -13254,20 +13254,20 @@
         <v>0</v>
       </c>
       <c r="X218" s="20">
-        <v>0</v>
+        <v>22953312</v>
       </c>
       <c r="Y218" s="20"/>
       <c r="Z218" s="20">
-        <v>0</v>
+        <v>22953312</v>
       </c>
       <c r="AA218" s="20"/>
       <c r="AB218" s="20"/>
       <c r="AC218" s="21">
-        <v>0</v>
+        <v>0.33313950653120467</v>
       </c>
       <c r="AD218" s="21"/>
       <c r="AE218" s="20">
-        <v>68900000</v>
+        <v>45946688</v>
       </c>
       <c r="AF218" s="20"/>
       <c r="AG218" s="20"/>
@@ -13307,20 +13307,20 @@
         <v>0</v>
       </c>
       <c r="X219" s="20">
-        <v>0</v>
+        <v>4629928</v>
       </c>
       <c r="Y219" s="20"/>
       <c r="Z219" s="20">
-        <v>0</v>
+        <v>4629928</v>
       </c>
       <c r="AA219" s="20"/>
       <c r="AB219" s="20"/>
       <c r="AC219" s="21">
-        <v>0</v>
+        <v>0.33332814974802016</v>
       </c>
       <c r="AD219" s="21"/>
       <c r="AE219" s="20">
-        <v>13890000</v>
+        <v>9260072</v>
       </c>
       <c r="AF219" s="20"/>
       <c r="AG219" s="20"/>
@@ -13362,20 +13362,20 @@
         <v>587220368</v>
       </c>
       <c r="X220" s="20">
-        <v>50455581</v>
+        <v>52010239</v>
       </c>
       <c r="Y220" s="20"/>
       <c r="Z220" s="20">
-        <v>637675949</v>
+        <v>639230607</v>
       </c>
       <c r="AA220" s="20"/>
       <c r="AB220" s="20"/>
       <c r="AC220" s="21">
-        <v>0.75314870907544762</v>
+        <v>0.75498489039542682</v>
       </c>
       <c r="AD220" s="21"/>
       <c r="AE220" s="20">
-        <v>209004051</v>
+        <v>207449393</v>
       </c>
       <c r="AF220" s="20"/>
       <c r="AG220" s="20"/>
@@ -13672,20 +13672,20 @@
         <v>29408400</v>
       </c>
       <c r="X226" s="20">
-        <v>691300</v>
+        <v>801600</v>
       </c>
       <c r="Y226" s="20"/>
       <c r="Z226" s="20">
-        <v>30099700</v>
+        <v>30210000</v>
       </c>
       <c r="AA226" s="20"/>
       <c r="AB226" s="20"/>
       <c r="AC226" s="21">
-        <v>0.76009343434343435</v>
+        <v>0.76287878787878793</v>
       </c>
       <c r="AD226" s="21"/>
       <c r="AE226" s="20">
-        <v>9500300</v>
+        <v>9390000</v>
       </c>
       <c r="AF226" s="20"/>
       <c r="AG226" s="20"/>
@@ -13725,20 +13725,20 @@
         <v>29408400</v>
       </c>
       <c r="X227" s="20">
-        <v>691300</v>
+        <v>801600</v>
       </c>
       <c r="Y227" s="20"/>
       <c r="Z227" s="20">
-        <v>30099700</v>
+        <v>30210000</v>
       </c>
       <c r="AA227" s="20"/>
       <c r="AB227" s="20"/>
       <c r="AC227" s="21">
-        <v>0.76009343434343435</v>
+        <v>0.76287878787878793</v>
       </c>
       <c r="AD227" s="21"/>
       <c r="AE227" s="20">
-        <v>9500300</v>
+        <v>9390000</v>
       </c>
       <c r="AF227" s="20"/>
       <c r="AG227" s="20"/>
@@ -13780,20 +13780,20 @@
         <v>122326356</v>
       </c>
       <c r="X228" s="20">
-        <v>9250750</v>
+        <v>10695108</v>
       </c>
       <c r="Y228" s="20"/>
       <c r="Z228" s="20">
-        <v>131577106</v>
+        <v>133021464</v>
       </c>
       <c r="AA228" s="20"/>
       <c r="AB228" s="20"/>
       <c r="AC228" s="21">
-        <v>0.84561122107969156</v>
+        <v>0.85489372750642678</v>
       </c>
       <c r="AD228" s="21"/>
       <c r="AE228" s="20">
-        <v>24022894</v>
+        <v>22578536</v>
       </c>
       <c r="AF228" s="20"/>
       <c r="AG228" s="20"/>
@@ -13886,20 +13886,20 @@
         <v>27141606</v>
       </c>
       <c r="X230" s="20">
-        <v>0</v>
+        <v>1444358</v>
       </c>
       <c r="Y230" s="20"/>
       <c r="Z230" s="20">
-        <v>27141606</v>
+        <v>28585964</v>
       </c>
       <c r="AA230" s="20"/>
       <c r="AB230" s="20"/>
       <c r="AC230" s="21">
-        <v>0.94570055749128923</v>
+        <v>0.99602662020905919</v>
       </c>
       <c r="AD230" s="21"/>
       <c r="AE230" s="20">
-        <v>1558394</v>
+        <v>114036</v>
       </c>
       <c r="AF230" s="20"/>
       <c r="AG230" s="20"/>
@@ -13941,20 +13941,20 @@
         <v>560645387</v>
       </c>
       <c r="X231" s="20">
-        <v>9448320</v>
+        <v>58990812</v>
       </c>
       <c r="Y231" s="20"/>
       <c r="Z231" s="20">
-        <v>570093707</v>
+        <v>619636199</v>
       </c>
       <c r="AA231" s="20"/>
       <c r="AB231" s="20"/>
       <c r="AC231" s="21">
-        <v>0.59382596155348499</v>
+        <v>0.6454308426255293</v>
       </c>
       <c r="AD231" s="21"/>
       <c r="AE231" s="20">
-        <v>389941293</v>
+        <v>340398801</v>
       </c>
       <c r="AF231" s="20"/>
       <c r="AG231" s="20"/>
@@ -14265,20 +14265,20 @@
         <v>117911533</v>
       </c>
       <c r="X237" s="20">
-        <v>0</v>
+        <v>10897000</v>
       </c>
       <c r="Y237" s="20"/>
       <c r="Z237" s="20">
-        <v>117911533</v>
+        <v>128808533</v>
       </c>
       <c r="AA237" s="20"/>
       <c r="AB237" s="20"/>
       <c r="AC237" s="21">
-        <v>0.29948448243018427</v>
+        <v>0.32716186327673569</v>
       </c>
       <c r="AD237" s="21"/>
       <c r="AE237" s="20">
-        <v>275803467</v>
+        <v>264906467</v>
       </c>
       <c r="AF237" s="20"/>
       <c r="AG237" s="20"/>
@@ -14371,20 +14371,20 @@
         <v>12396299</v>
       </c>
       <c r="X239" s="20">
-        <v>0</v>
+        <v>8951000</v>
       </c>
       <c r="Y239" s="20"/>
       <c r="Z239" s="20">
-        <v>12396299</v>
+        <v>21347299</v>
       </c>
       <c r="AA239" s="20"/>
       <c r="AB239" s="20"/>
       <c r="AC239" s="21">
-        <v>0.45997398886827456</v>
+        <v>0.79210756957328388</v>
       </c>
       <c r="AD239" s="21"/>
       <c r="AE239" s="20">
-        <v>14553701</v>
+        <v>5602701</v>
       </c>
       <c r="AF239" s="20"/>
       <c r="AG239" s="20"/>
@@ -14530,20 +14530,20 @@
         <v>2475000</v>
       </c>
       <c r="X242" s="20">
-        <v>0</v>
+        <v>1946000</v>
       </c>
       <c r="Y242" s="20"/>
       <c r="Z242" s="20">
-        <v>2475000</v>
+        <v>4421000</v>
       </c>
       <c r="AA242" s="20"/>
       <c r="AB242" s="20"/>
       <c r="AC242" s="21">
-        <v>1.2030038641942305E-2</v>
+        <v>2.1488808418596739E-2</v>
       </c>
       <c r="AD242" s="21"/>
       <c r="AE242" s="20">
-        <v>203260000</v>
+        <v>201314000</v>
       </c>
       <c r="AF242" s="20"/>
       <c r="AG242" s="20"/>
@@ -15207,20 +15207,20 @@
         <v>158031069</v>
       </c>
       <c r="X255" s="20">
-        <v>9448320</v>
+        <v>48093812</v>
       </c>
       <c r="Y255" s="20"/>
       <c r="Z255" s="20">
-        <v>167479389</v>
+        <v>206124881</v>
       </c>
       <c r="AA255" s="20"/>
       <c r="AB255" s="20"/>
       <c r="AC255" s="21">
-        <v>0.72829791702904856</v>
+        <v>0.89635102191685512</v>
       </c>
       <c r="AD255" s="21"/>
       <c r="AE255" s="20">
-        <v>62480611</v>
+        <v>23835119</v>
       </c>
       <c r="AF255" s="20"/>
       <c r="AG255" s="20"/>
@@ -15313,20 +15313,20 @@
         <v>350000</v>
       </c>
       <c r="X257" s="20">
-        <v>0</v>
+        <v>937928</v>
       </c>
       <c r="Y257" s="20"/>
       <c r="Z257" s="20">
-        <v>350000</v>
+        <v>1287928</v>
       </c>
       <c r="AA257" s="20"/>
       <c r="AB257" s="20"/>
       <c r="AC257" s="21">
-        <v>7.0000000000000007E-2</v>
+        <v>0.25758560000000003</v>
       </c>
       <c r="AD257" s="21"/>
       <c r="AE257" s="20">
-        <v>4650000</v>
+        <v>3712072</v>
       </c>
       <c r="AF257" s="20"/>
       <c r="AG257" s="20"/>
@@ -15366,20 +15366,20 @@
         <v>27531718</v>
       </c>
       <c r="X258" s="20">
-        <v>0</v>
+        <v>509000</v>
       </c>
       <c r="Y258" s="20"/>
       <c r="Z258" s="20">
-        <v>27531718</v>
+        <v>28040718</v>
       </c>
       <c r="AA258" s="20"/>
       <c r="AB258" s="20"/>
       <c r="AC258" s="21">
-        <v>0.91772393333333335</v>
+        <v>0.93469060000000004</v>
       </c>
       <c r="AD258" s="21"/>
       <c r="AE258" s="20">
-        <v>2468282</v>
+        <v>1959282</v>
       </c>
       <c r="AF258" s="20"/>
       <c r="AG258" s="20"/>
@@ -15419,20 +15419,20 @@
         <v>94757877</v>
       </c>
       <c r="X259" s="20">
-        <v>0</v>
+        <v>26080619</v>
       </c>
       <c r="Y259" s="20"/>
       <c r="Z259" s="20">
-        <v>94757877</v>
+        <v>120838496</v>
       </c>
       <c r="AA259" s="20"/>
       <c r="AB259" s="20"/>
       <c r="AC259" s="21">
-        <v>0.76049660513643658</v>
+        <v>0.96981136436597115</v>
       </c>
       <c r="AD259" s="21"/>
       <c r="AE259" s="20">
-        <v>29842123</v>
+        <v>3761504</v>
       </c>
       <c r="AF259" s="20"/>
       <c r="AG259" s="20"/>
@@ -15472,20 +15472,20 @@
         <v>3229902</v>
       </c>
       <c r="X260" s="20">
-        <v>0</v>
+        <v>182090</v>
       </c>
       <c r="Y260" s="20"/>
       <c r="Z260" s="20">
-        <v>3229902</v>
+        <v>3411992</v>
       </c>
       <c r="AA260" s="20"/>
       <c r="AB260" s="20"/>
       <c r="AC260" s="21">
-        <v>0.71775599999999995</v>
+        <v>0.75822044444444447</v>
       </c>
       <c r="AD260" s="21"/>
       <c r="AE260" s="20">
-        <v>1270098</v>
+        <v>1088008</v>
       </c>
       <c r="AF260" s="20"/>
       <c r="AG260" s="20"/>
@@ -15525,20 +15525,20 @@
         <v>4737535</v>
       </c>
       <c r="X261" s="20">
-        <v>9448320</v>
+        <v>9553020</v>
       </c>
       <c r="Y261" s="20"/>
       <c r="Z261" s="20">
-        <v>14185855</v>
+        <v>14290555</v>
       </c>
       <c r="AA261" s="20"/>
       <c r="AB261" s="20"/>
       <c r="AC261" s="21">
-        <v>0.97833482758620693</v>
+        <v>0.98555551724137935</v>
       </c>
       <c r="AD261" s="21"/>
       <c r="AE261" s="20">
-        <v>314145</v>
+        <v>209445</v>
       </c>
       <c r="AF261" s="20"/>
       <c r="AG261" s="20"/>
@@ -15631,20 +15631,20 @@
         <v>1358480</v>
       </c>
       <c r="X263" s="20">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="Y263" s="20"/>
       <c r="Z263" s="20">
-        <v>1358480</v>
+        <v>1658480</v>
       </c>
       <c r="AA263" s="20"/>
       <c r="AB263" s="20"/>
       <c r="AC263" s="21">
-        <v>0.33542716049382715</v>
+        <v>0.40950123456790122</v>
       </c>
       <c r="AD263" s="21"/>
       <c r="AE263" s="20">
-        <v>2691520</v>
+        <v>2391520</v>
       </c>
       <c r="AF263" s="20"/>
       <c r="AG263" s="20"/>
@@ -15684,20 +15684,20 @@
         <v>8224613</v>
       </c>
       <c r="X264" s="20">
-        <v>0</v>
+        <v>94643</v>
       </c>
       <c r="Y264" s="20"/>
       <c r="Z264" s="20">
-        <v>8224613</v>
+        <v>8319256</v>
       </c>
       <c r="AA264" s="20"/>
       <c r="AB264" s="20"/>
       <c r="AC264" s="21">
-        <v>0.82246129999999995</v>
+        <v>0.83192560000000004</v>
       </c>
       <c r="AD264" s="21"/>
       <c r="AE264" s="20">
-        <v>1775387</v>
+        <v>1680744</v>
       </c>
       <c r="AF264" s="20"/>
       <c r="AG264" s="20"/>
@@ -15790,20 +15790,20 @@
         <v>1213334</v>
       </c>
       <c r="X266" s="20">
-        <v>0</v>
+        <v>2547512</v>
       </c>
       <c r="Y266" s="20"/>
       <c r="Z266" s="20">
-        <v>1213334</v>
+        <v>3760846</v>
       </c>
       <c r="AA266" s="20"/>
       <c r="AB266" s="20"/>
       <c r="AC266" s="21">
-        <v>0.24266679999999999</v>
+        <v>0.75216919999999998</v>
       </c>
       <c r="AD266" s="21"/>
       <c r="AE266" s="20">
-        <v>3786666</v>
+        <v>1239154</v>
       </c>
       <c r="AF266" s="20"/>
       <c r="AG266" s="20"/>
@@ -15896,20 +15896,20 @@
         <v>0</v>
       </c>
       <c r="X268" s="20">
-        <v>0</v>
+        <v>7889000</v>
       </c>
       <c r="Y268" s="20"/>
       <c r="Z268" s="20">
-        <v>0</v>
+        <v>7889000</v>
       </c>
       <c r="AA268" s="20"/>
       <c r="AB268" s="20"/>
       <c r="AC268" s="21">
-        <v>0</v>
+        <v>0.78890000000000005</v>
       </c>
       <c r="AD268" s="21"/>
       <c r="AE268" s="20">
-        <v>10000000</v>
+        <v>2111000</v>
       </c>
       <c r="AF268" s="20"/>
       <c r="AG268" s="20"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -601,7 +601,7 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Periode November 2025</t>
+            <t xml:space="preserve">Periode Desember 2025</t>
           </r>
         </is>
       </c>
@@ -979,22 +979,22 @@
       <c r="U9" s="10" t="inlineStr"/>
       <c r="V9" s="10" t="inlineStr"/>
       <c r="W9" s="11" t="n">
-        <v>7.7645055879E10</v>
+        <v>8.6557047429E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>8.91199155E9</v>
+        <v>3.613859066E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>8.6557047429E10</v>
+        <v>9.0170906495E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.8656047695509697</v>
+        <v>0.9017447920786622</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.3438990571E10</v>
+        <v>9.825131505E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1711,23 +1711,23 @@
       <c r="U21" s="14" t="inlineStr"/>
       <c r="V21" s="14" t="inlineStr"/>
       <c r="W21" s="14" t="n">
-        <v>7.3611687839E10</v>
+        <v>8.2523679389E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>8.91199155E9</v>
+        <v>3.613859066E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.2523679389E10</v>
+        <v>8.6137538455E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.8599563445619325</v>
+        <v>0.8976153662532703</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.3438958611E10</v>
+        <v>9.825099545E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1774,23 +1774,23 @@
       <c r="U22" s="14" t="inlineStr"/>
       <c r="V22" s="14" t="inlineStr"/>
       <c r="W22" s="14" t="n">
-        <v>7.3611687839E10</v>
+        <v>8.2523679389E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>8.91199155E9</v>
+        <v>3.613859066E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.2523679389E10</v>
+        <v>8.6137538455E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.8599563445619325</v>
+        <v>0.8976153662532703</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.3438958611E10</v>
+        <v>9.825099545E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1837,23 +1837,23 @@
       <c r="U23" s="17" t="inlineStr"/>
       <c r="V23" s="17" t="inlineStr"/>
       <c r="W23" s="17" t="n">
-        <v>7.3611087839E10</v>
+        <v>8.2523079389E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>8.91199155E9</v>
+        <v>3.613859066E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.2523079389E10</v>
+        <v>8.6136938455E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.8599554689428334</v>
+        <v>0.8976147260961673</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.3438958611E10</v>
+        <v>9.825099545E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
       <c r="U35" s="21" t="inlineStr"/>
       <c r="V35" s="21" t="inlineStr"/>
       <c r="W35" s="22" t="n">
-        <v>1.4661052E7</v>
+        <v>1.6461052E7</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
@@ -2625,10 +2625,10 @@
       <c r="U36" s="25" t="inlineStr"/>
       <c r="V36" s="25" t="inlineStr"/>
       <c r="W36" s="25" t="n">
-        <v>1.4661052E7</v>
+        <v>1.6461052E7</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
@@ -2991,10 +2991,10 @@
       <c r="U42" s="14" t="inlineStr"/>
       <c r="V42" s="14" t="inlineStr"/>
       <c r="W42" s="14" t="n">
-        <v>1.2261052E7</v>
+        <v>1.4061052E7</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
@@ -3054,10 +3054,10 @@
       <c r="U43" s="14" t="inlineStr"/>
       <c r="V43" s="14" t="inlineStr"/>
       <c r="W43" s="14" t="n">
-        <v>1.2261052E7</v>
+        <v>1.4061052E7</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
@@ -3101,7 +3101,7 @@
       <c r="O44" s="13" t="inlineStr"/>
       <c r="P44" s="13" t="inlineStr"/>
       <c r="Q44" s="14" t="n">
-        <v>1.376E7</v>
+        <v>1.431E7</v>
       </c>
       <c r="R44" s="14" t="inlineStr"/>
       <c r="S44" s="14" t="n">
@@ -3111,10 +3111,10 @@
       <c r="U44" s="14" t="inlineStr"/>
       <c r="V44" s="14" t="inlineStr"/>
       <c r="W44" s="14" t="n">
-        <v>1.1511952E7</v>
+        <v>1.3311952E7</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
@@ -3123,11 +3123,11 @@
       <c r="AA44" s="14" t="inlineStr"/>
       <c r="AB44" s="14" t="inlineStr"/>
       <c r="AC44" s="15" t="n">
-        <v>0.9674383720930233</v>
+        <v>0.9302552061495458</v>
       </c>
       <c r="AD44" s="15" t="inlineStr"/>
       <c r="AE44" s="14" t="n">
-        <v>448048.0</v>
+        <v>998048.0</v>
       </c>
       <c r="AF44" s="14" t="inlineStr"/>
       <c r="AG44" s="14" t="inlineStr"/>
@@ -3158,7 +3158,7 @@
       <c r="O45" s="13" t="inlineStr"/>
       <c r="P45" s="13" t="inlineStr"/>
       <c r="Q45" s="14" t="n">
-        <v>1320000.0</v>
+        <v>770000.0</v>
       </c>
       <c r="R45" s="14" t="inlineStr"/>
       <c r="S45" s="14" t="n">
@@ -3180,11 +3180,11 @@
       <c r="AA45" s="14" t="inlineStr"/>
       <c r="AB45" s="14" t="inlineStr"/>
       <c r="AC45" s="15" t="n">
-        <v>0.5675</v>
+        <v>0.9728571428571429</v>
       </c>
       <c r="AD45" s="15" t="inlineStr"/>
       <c r="AE45" s="14" t="n">
-        <v>570900.0</v>
+        <v>20900.0</v>
       </c>
       <c r="AF45" s="14" t="inlineStr"/>
       <c r="AG45" s="14" t="inlineStr"/>
@@ -3231,23 +3231,23 @@
       <c r="U46" s="21" t="inlineStr"/>
       <c r="V46" s="21" t="inlineStr"/>
       <c r="W46" s="22" t="n">
-        <v>7.3595376787E10</v>
+        <v>8.2505568337E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>8.91019155E9</v>
+        <v>3.613859066E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.2505568337E10</v>
+        <v>8.6119427403E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.8599390418057259</v>
+        <v>0.897605572260293</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.3437939663E10</v>
+        <v>9.824080597E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3294,23 +3294,23 @@
       <c r="U47" s="25" t="inlineStr"/>
       <c r="V47" s="25" t="inlineStr"/>
       <c r="W47" s="25" t="n">
-        <v>6.8240832441E10</v>
+        <v>7.6753022175E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>8.512189734E9</v>
+        <v>3.526529172E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>7.6753022175E10</v>
+        <v>8.0279551347E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.8624252622762301</v>
+        <v>0.9020506445726097</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.2243700825E10</v>
+        <v>8.717171653E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3357,23 +3357,23 @@
       <c r="U48" s="14" t="inlineStr"/>
       <c r="V48" s="14" t="inlineStr"/>
       <c r="W48" s="14" t="n">
-        <v>5.051860578E9</v>
+        <v>5.460273892E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>4.08413314E8</v>
+        <v>3.70964212E8</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>5.460273892E9</v>
+        <v>5.831238104E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.9187888432995047</v>
+        <v>0.981210213727161</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>4.82630108E8</v>
+        <v>1.11665896E8</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -3420,23 +3420,23 @@
       <c r="U49" s="14" t="inlineStr"/>
       <c r="V49" s="14" t="inlineStr"/>
       <c r="W49" s="14" t="n">
-        <v>1.9796803E9</v>
+        <v>2.1400157E9</v>
       </c>
       <c r="X49" s="14" t="n">
-        <v>1.603354E8</v>
+        <v>1.612308E8</v>
       </c>
       <c r="Y49" s="14" t="inlineStr"/>
       <c r="Z49" s="14" t="n">
-        <v>2.1400157E9</v>
+        <v>2.3012465E9</v>
       </c>
       <c r="AA49" s="14" t="inlineStr"/>
       <c r="AB49" s="14" t="inlineStr"/>
       <c r="AC49" s="15" t="n">
-        <v>0.9230101728776744</v>
+        <v>0.9925506293244218</v>
       </c>
       <c r="AD49" s="15" t="inlineStr"/>
       <c r="AE49" s="14" t="n">
-        <v>1.785023E8</v>
+        <v>1.72715E7</v>
       </c>
       <c r="AF49" s="14" t="inlineStr"/>
       <c r="AG49" s="14" t="inlineStr"/>
@@ -3477,23 +3477,23 @@
       <c r="U50" s="14" t="inlineStr"/>
       <c r="V50" s="14" t="inlineStr"/>
       <c r="W50" s="14" t="n">
-        <v>1.6494999E9</v>
+        <v>1.8098353E9</v>
       </c>
       <c r="X50" s="14" t="n">
-        <v>1.603354E8</v>
+        <v>1.612308E8</v>
       </c>
       <c r="Y50" s="14" t="inlineStr"/>
       <c r="Z50" s="14" t="n">
-        <v>1.8098353E9</v>
+        <v>1.9710661E9</v>
       </c>
       <c r="AA50" s="14" t="inlineStr"/>
       <c r="AB50" s="14" t="inlineStr"/>
       <c r="AC50" s="15" t="n">
-        <v>0.9114123745812661</v>
+        <v>0.9926063629423271</v>
       </c>
       <c r="AD50" s="15" t="inlineStr"/>
       <c r="AE50" s="14" t="n">
-        <v>1.759127E8</v>
+        <v>1.46819E7</v>
       </c>
       <c r="AF50" s="14" t="inlineStr"/>
       <c r="AG50" s="14" t="inlineStr"/>
@@ -3654,23 +3654,23 @@
       <c r="U53" s="14" t="inlineStr"/>
       <c r="V53" s="14" t="inlineStr"/>
       <c r="W53" s="14" t="n">
-        <v>23249.0</v>
+        <v>25093.0</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>1844.0</v>
+        <v>1803.0</v>
       </c>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="n">
-        <v>25093.0</v>
+        <v>26896.0</v>
       </c>
       <c r="AA53" s="14" t="inlineStr"/>
       <c r="AB53" s="14" t="inlineStr"/>
       <c r="AC53" s="15" t="n">
-        <v>0.8364333333333334</v>
+        <v>0.8965333333333333</v>
       </c>
       <c r="AD53" s="15" t="inlineStr"/>
       <c r="AE53" s="14" t="n">
-        <v>4907.0</v>
+        <v>3104.0</v>
       </c>
       <c r="AF53" s="14" t="inlineStr"/>
       <c r="AG53" s="14" t="inlineStr"/>
@@ -3711,23 +3711,23 @@
       <c r="U54" s="14" t="inlineStr"/>
       <c r="V54" s="14" t="inlineStr"/>
       <c r="W54" s="14" t="n">
-        <v>18667.0</v>
+        <v>20511.0</v>
       </c>
       <c r="X54" s="14" t="n">
-        <v>1844.0</v>
+        <v>1803.0</v>
       </c>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="n">
-        <v>20511.0</v>
+        <v>22314.0</v>
       </c>
       <c r="AA54" s="14" t="inlineStr"/>
       <c r="AB54" s="14" t="inlineStr"/>
       <c r="AC54" s="15" t="n">
-        <v>0.854625</v>
+        <v>0.92975</v>
       </c>
       <c r="AD54" s="15" t="inlineStr"/>
       <c r="AE54" s="14" t="n">
-        <v>3489.0</v>
+        <v>1686.0</v>
       </c>
       <c r="AF54" s="14" t="inlineStr"/>
       <c r="AG54" s="14" t="inlineStr"/>
@@ -3888,23 +3888,23 @@
       <c r="U57" s="14" t="inlineStr"/>
       <c r="V57" s="14" t="inlineStr"/>
       <c r="W57" s="14" t="n">
-        <v>1.5092196E8</v>
+        <v>1.6302116E8</v>
       </c>
       <c r="X57" s="14" t="n">
-        <v>1.20992E7</v>
+        <v>1.217561E7</v>
       </c>
       <c r="Y57" s="14" t="inlineStr"/>
       <c r="Z57" s="14" t="n">
-        <v>1.6302116E8</v>
+        <v>1.7519677E8</v>
       </c>
       <c r="AA57" s="14" t="inlineStr"/>
       <c r="AB57" s="14" t="inlineStr"/>
       <c r="AC57" s="15" t="n">
-        <v>0.9302205991440798</v>
+        <v>0.9996962624821684</v>
       </c>
       <c r="AD57" s="15" t="inlineStr"/>
       <c r="AE57" s="14" t="n">
-        <v>1.222884E7</v>
+        <v>53230.0</v>
       </c>
       <c r="AF57" s="14" t="inlineStr"/>
       <c r="AG57" s="14" t="inlineStr"/>
@@ -3945,23 +3945,23 @@
       <c r="U58" s="14" t="inlineStr"/>
       <c r="V58" s="14" t="inlineStr"/>
       <c r="W58" s="14" t="n">
-        <v>1.2572364E8</v>
+        <v>1.3782284E8</v>
       </c>
       <c r="X58" s="14" t="n">
-        <v>1.20992E7</v>
+        <v>1.217561E7</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
-        <v>1.3782284E8</v>
+        <v>1.4999845E8</v>
       </c>
       <c r="AA58" s="14" t="inlineStr"/>
       <c r="AB58" s="14" t="inlineStr"/>
       <c r="AC58" s="15" t="n">
-        <v>0.9185250053316272</v>
+        <v>0.999669772339518</v>
       </c>
       <c r="AD58" s="15" t="inlineStr"/>
       <c r="AE58" s="14" t="n">
-        <v>1.222516E7</v>
+        <v>49550.0</v>
       </c>
       <c r="AF58" s="14" t="inlineStr"/>
       <c r="AG58" s="14" t="inlineStr"/>
@@ -4166,23 +4166,23 @@
       <c r="U62" s="14" t="inlineStr"/>
       <c r="V62" s="14" t="inlineStr"/>
       <c r="W62" s="14" t="n">
-        <v>4.5834612E7</v>
+        <v>4.9459528E7</v>
       </c>
       <c r="X62" s="14" t="n">
-        <v>3624916.0</v>
+        <v>3650984.0</v>
       </c>
       <c r="Y62" s="14" t="inlineStr"/>
       <c r="Z62" s="14" t="n">
-        <v>4.9459528E7</v>
+        <v>5.3110512E7</v>
       </c>
       <c r="AA62" s="14" t="inlineStr"/>
       <c r="AB62" s="14" t="inlineStr"/>
       <c r="AC62" s="15" t="n">
-        <v>0.9283641414520609</v>
+        <v>0.9968937607928523</v>
       </c>
       <c r="AD62" s="15" t="inlineStr"/>
       <c r="AE62" s="14" t="n">
-        <v>3816472.0</v>
+        <v>165488.0</v>
       </c>
       <c r="AF62" s="14" t="inlineStr"/>
       <c r="AG62" s="14" t="inlineStr"/>
@@ -4223,23 +4223,23 @@
       <c r="U63" s="14" t="inlineStr"/>
       <c r="V63" s="14" t="inlineStr"/>
       <c r="W63" s="14" t="n">
-        <v>3.8158554E7</v>
+        <v>4.178347E7</v>
       </c>
       <c r="X63" s="14" t="n">
-        <v>3624916.0</v>
+        <v>3650984.0</v>
       </c>
       <c r="Y63" s="14" t="inlineStr"/>
       <c r="Z63" s="14" t="n">
-        <v>4.178347E7</v>
+        <v>4.5434454E7</v>
       </c>
       <c r="AA63" s="14" t="inlineStr"/>
       <c r="AB63" s="14" t="inlineStr"/>
       <c r="AC63" s="15" t="n">
-        <v>0.9165453628147758</v>
+        <v>0.9966318768096868</v>
       </c>
       <c r="AD63" s="15" t="inlineStr"/>
       <c r="AE63" s="14" t="n">
-        <v>3804530.0</v>
+        <v>153546.0</v>
       </c>
       <c r="AF63" s="14" t="inlineStr"/>
       <c r="AG63" s="14" t="inlineStr"/>
@@ -4400,23 +4400,23 @@
       <c r="U66" s="14" t="inlineStr"/>
       <c r="V66" s="14" t="inlineStr"/>
       <c r="W66" s="14" t="n">
-        <v>2.16E7</v>
+        <v>2.34E7</v>
       </c>
       <c r="X66" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
-        <v>2.34E7</v>
+        <v>2.52E7</v>
       </c>
       <c r="AA66" s="14" t="inlineStr"/>
       <c r="AB66" s="14" t="inlineStr"/>
       <c r="AC66" s="15" t="n">
-        <v>0.9285714285714286</v>
+        <v>1.0</v>
       </c>
       <c r="AD66" s="15" t="inlineStr"/>
       <c r="AE66" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF66" s="14" t="inlineStr"/>
       <c r="AG66" s="14" t="inlineStr"/>
@@ -4457,23 +4457,23 @@
       <c r="U67" s="14" t="inlineStr"/>
       <c r="V67" s="14" t="inlineStr"/>
       <c r="W67" s="14" t="n">
-        <v>1.8E7</v>
+        <v>1.98E7</v>
       </c>
       <c r="X67" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="n">
-        <v>1.98E7</v>
+        <v>2.16E7</v>
       </c>
       <c r="AA67" s="14" t="inlineStr"/>
       <c r="AB67" s="14" t="inlineStr"/>
       <c r="AC67" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>1.0</v>
       </c>
       <c r="AD67" s="15" t="inlineStr"/>
       <c r="AE67" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF67" s="14" t="inlineStr"/>
       <c r="AG67" s="14" t="inlineStr"/>
@@ -4634,23 +4634,23 @@
       <c r="U70" s="14" t="inlineStr"/>
       <c r="V70" s="14" t="inlineStr"/>
       <c r="W70" s="14" t="n">
-        <v>1.39288E8</v>
+        <v>1.49682E8</v>
       </c>
       <c r="X70" s="14" t="n">
         <v>1.0394E7</v>
       </c>
       <c r="Y70" s="14" t="inlineStr"/>
       <c r="Z70" s="14" t="n">
-        <v>1.49682E8</v>
+        <v>1.60076E8</v>
       </c>
       <c r="AA70" s="14" t="inlineStr"/>
       <c r="AB70" s="14" t="inlineStr"/>
       <c r="AC70" s="15" t="n">
-        <v>0.9348697770282931</v>
+        <v>0.9997876459933795</v>
       </c>
       <c r="AD70" s="15" t="inlineStr"/>
       <c r="AE70" s="14" t="n">
-        <v>1.0428E7</v>
+        <v>34000.0</v>
       </c>
       <c r="AF70" s="14" t="inlineStr"/>
       <c r="AG70" s="14" t="inlineStr"/>
@@ -4691,23 +4691,23 @@
       <c r="U71" s="14" t="inlineStr"/>
       <c r="V71" s="14" t="inlineStr"/>
       <c r="W71" s="14" t="n">
-        <v>1.1526E8</v>
+        <v>1.25654E8</v>
       </c>
       <c r="X71" s="14" t="n">
         <v>1.0394E7</v>
       </c>
       <c r="Y71" s="14" t="inlineStr"/>
       <c r="Z71" s="14" t="n">
-        <v>1.25654E8</v>
+        <v>1.36048E8</v>
       </c>
       <c r="AA71" s="14" t="inlineStr"/>
       <c r="AB71" s="14" t="inlineStr"/>
       <c r="AC71" s="15" t="n">
-        <v>0.9233833039388595</v>
+        <v>0.9997648442092887</v>
       </c>
       <c r="AD71" s="15" t="inlineStr"/>
       <c r="AE71" s="14" t="n">
-        <v>1.0426E7</v>
+        <v>32000.0</v>
       </c>
       <c r="AF71" s="14" t="inlineStr"/>
       <c r="AG71" s="14" t="inlineStr"/>
@@ -4868,23 +4868,23 @@
       <c r="U74" s="14" t="inlineStr"/>
       <c r="V74" s="14" t="inlineStr"/>
       <c r="W74" s="14" t="n">
-        <v>1.9778754E7</v>
+        <v>1.9962339E7</v>
       </c>
       <c r="X74" s="14" t="n">
-        <v>183585.0</v>
+        <v>307406.0</v>
       </c>
       <c r="Y74" s="14" t="inlineStr"/>
       <c r="Z74" s="14" t="n">
-        <v>1.9962339E7</v>
+        <v>2.0269745E7</v>
       </c>
       <c r="AA74" s="14" t="inlineStr"/>
       <c r="AB74" s="14" t="inlineStr"/>
       <c r="AC74" s="15" t="n">
-        <v>0.9901953869047619</v>
+        <v>1.0054437003968253</v>
       </c>
       <c r="AD74" s="15" t="inlineStr"/>
       <c r="AE74" s="14" t="n">
-        <v>197661.0</v>
+        <v>-109745.0</v>
       </c>
       <c r="AF74" s="14" t="inlineStr"/>
       <c r="AG74" s="14" t="inlineStr"/>
@@ -4925,23 +4925,23 @@
       <c r="U75" s="14" t="inlineStr"/>
       <c r="V75" s="14" t="inlineStr"/>
       <c r="W75" s="14" t="n">
-        <v>2247738.0</v>
+        <v>2431323.0</v>
       </c>
       <c r="X75" s="14" t="n">
-        <v>183585.0</v>
+        <v>307406.0</v>
       </c>
       <c r="Y75" s="14" t="inlineStr"/>
       <c r="Z75" s="14" t="n">
-        <v>2431323.0</v>
+        <v>2738729.0</v>
       </c>
       <c r="AA75" s="14" t="inlineStr"/>
       <c r="AB75" s="14" t="inlineStr"/>
       <c r="AC75" s="15" t="n">
-        <v>0.9294048165137615</v>
+        <v>1.046914755351682</v>
       </c>
       <c r="AD75" s="15" t="inlineStr"/>
       <c r="AE75" s="14" t="n">
-        <v>184677.0</v>
+        <v>-122729.0</v>
       </c>
       <c r="AF75" s="14" t="inlineStr"/>
       <c r="AG75" s="14" t="inlineStr"/>
@@ -5102,23 +5102,23 @@
       <c r="U78" s="14" t="inlineStr"/>
       <c r="V78" s="14" t="inlineStr"/>
       <c r="W78" s="14" t="n">
-        <v>1.0450206E8</v>
+        <v>1.1283036E8</v>
       </c>
       <c r="X78" s="14" t="n">
         <v>8328300.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
-        <v>1.1283036E8</v>
+        <v>1.2115866E8</v>
       </c>
       <c r="AA78" s="14" t="inlineStr"/>
       <c r="AB78" s="14" t="inlineStr"/>
       <c r="AC78" s="15" t="n">
-        <v>0.9311279461279461</v>
+        <v>0.9998569023569024</v>
       </c>
       <c r="AD78" s="15" t="inlineStr"/>
       <c r="AE78" s="14" t="n">
-        <v>8345640.0</v>
+        <v>17340.0</v>
       </c>
       <c r="AF78" s="14" t="inlineStr"/>
       <c r="AG78" s="14" t="inlineStr"/>
@@ -5159,23 +5159,23 @@
       <c r="U79" s="14" t="inlineStr"/>
       <c r="V79" s="14" t="inlineStr"/>
       <c r="W79" s="14" t="n">
-        <v>8.697642E7</v>
+        <v>9.530472E7</v>
       </c>
       <c r="X79" s="14" t="n">
         <v>8328300.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
-        <v>9.530472E7</v>
+        <v>1.0363302E8</v>
       </c>
       <c r="AA79" s="14" t="inlineStr"/>
       <c r="AB79" s="14" t="inlineStr"/>
       <c r="AC79" s="15" t="n">
-        <v>0.9195391918490217</v>
+        <v>0.9998940604376519</v>
       </c>
       <c r="AD79" s="15" t="inlineStr"/>
       <c r="AE79" s="14" t="n">
-        <v>8339280.0</v>
+        <v>10980.0</v>
       </c>
       <c r="AF79" s="14" t="inlineStr"/>
       <c r="AG79" s="14" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
       <c r="U82" s="14" t="inlineStr"/>
       <c r="V82" s="14" t="inlineStr"/>
       <c r="W82" s="14" t="n">
-        <v>2.45993E8</v>
+        <v>2.77741E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>3.1748E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
@@ -5393,10 +5393,10 @@
       <c r="U83" s="14" t="inlineStr"/>
       <c r="V83" s="14" t="inlineStr"/>
       <c r="W83" s="14" t="n">
-        <v>1.393E7</v>
+        <v>1.554E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1610000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
@@ -5450,10 +5450,10 @@
       <c r="U84" s="14" t="inlineStr"/>
       <c r="V84" s="14" t="inlineStr"/>
       <c r="W84" s="14" t="n">
-        <v>2.01354E8</v>
+        <v>2.28253E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>2.6899E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
@@ -5507,10 +5507,10 @@
       <c r="U85" s="14" t="inlineStr"/>
       <c r="V85" s="14" t="inlineStr"/>
       <c r="W85" s="14" t="n">
-        <v>3.0709E7</v>
+        <v>3.3948E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>3239000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
@@ -5570,23 +5570,23 @@
       <c r="U86" s="14" t="inlineStr"/>
       <c r="V86" s="14" t="inlineStr"/>
       <c r="W86" s="14" t="n">
-        <v>4.9135E7</v>
+        <v>5.3385E7</v>
       </c>
       <c r="X86" s="14" t="n">
         <v>4250000.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
-        <v>5.3385E7</v>
+        <v>5.7635E7</v>
       </c>
       <c r="AA86" s="14" t="inlineStr"/>
       <c r="AB86" s="14" t="inlineStr"/>
       <c r="AC86" s="15" t="n">
-        <v>0.9229771784232366</v>
+        <v>0.9964557399723375</v>
       </c>
       <c r="AD86" s="15" t="inlineStr"/>
       <c r="AE86" s="14" t="n">
-        <v>4455000.0</v>
+        <v>205000.0</v>
       </c>
       <c r="AF86" s="14" t="inlineStr"/>
       <c r="AG86" s="14" t="inlineStr"/>
@@ -5671,23 +5671,23 @@
       <c r="U88" s="14" t="inlineStr"/>
       <c r="V88" s="14" t="inlineStr"/>
       <c r="W88" s="14" t="n">
-        <v>4.1205E7</v>
+        <v>4.5455E7</v>
       </c>
       <c r="X88" s="14" t="n">
         <v>4250000.0</v>
       </c>
       <c r="Y88" s="14" t="inlineStr"/>
       <c r="Z88" s="14" t="n">
-        <v>4.5455E7</v>
+        <v>4.9705E7</v>
       </c>
       <c r="AA88" s="14" t="inlineStr"/>
       <c r="AB88" s="14" t="inlineStr"/>
       <c r="AC88" s="15" t="n">
-        <v>0.9116526273565985</v>
+        <v>0.9968912956277577</v>
       </c>
       <c r="AD88" s="15" t="inlineStr"/>
       <c r="AE88" s="14" t="n">
-        <v>4405000.0</v>
+        <v>155000.0</v>
       </c>
       <c r="AF88" s="14" t="inlineStr"/>
       <c r="AG88" s="14" t="inlineStr"/>
@@ -5848,23 +5848,23 @@
       <c r="U91" s="14" t="inlineStr"/>
       <c r="V91" s="14" t="inlineStr"/>
       <c r="W91" s="14" t="n">
-        <v>2.295103643E9</v>
+        <v>2.470751712E9</v>
       </c>
       <c r="X91" s="14" t="n">
-        <v>1.75648069E8</v>
+        <v>1.68825309E8</v>
       </c>
       <c r="Y91" s="14" t="inlineStr"/>
       <c r="Z91" s="14" t="n">
-        <v>2.470751712E9</v>
+        <v>2.639577021E9</v>
       </c>
       <c r="AA91" s="14" t="inlineStr"/>
       <c r="AB91" s="14" t="inlineStr"/>
       <c r="AC91" s="15" t="n">
-        <v>0.9321396440988989</v>
+        <v>0.9958323100522745</v>
       </c>
       <c r="AD91" s="15" t="inlineStr"/>
       <c r="AE91" s="14" t="n">
-        <v>1.79872288E8</v>
+        <v>1.1046979E7</v>
       </c>
       <c r="AF91" s="14" t="inlineStr"/>
       <c r="AG91" s="14" t="inlineStr"/>
@@ -5905,23 +5905,23 @@
       <c r="U92" s="14" t="inlineStr"/>
       <c r="V92" s="14" t="inlineStr"/>
       <c r="W92" s="14" t="n">
-        <v>1.852488851E9</v>
+        <v>2.02813692E9</v>
       </c>
       <c r="X92" s="14" t="n">
-        <v>1.75648069E8</v>
+        <v>1.68825309E8</v>
       </c>
       <c r="Y92" s="14" t="inlineStr"/>
       <c r="Z92" s="14" t="n">
-        <v>2.02813692E9</v>
+        <v>2.196962229E9</v>
       </c>
       <c r="AA92" s="14" t="inlineStr"/>
       <c r="AB92" s="14" t="inlineStr"/>
       <c r="AC92" s="15" t="n">
-        <v>0.9185402717391304</v>
+        <v>0.9950010095108696</v>
       </c>
       <c r="AD92" s="15" t="inlineStr"/>
       <c r="AE92" s="14" t="n">
-        <v>1.7986308E8</v>
+        <v>1.1037771E7</v>
       </c>
       <c r="AF92" s="14" t="inlineStr"/>
       <c r="AG92" s="14" t="inlineStr"/>
@@ -6082,23 +6082,23 @@
       <c r="U95" s="14" t="inlineStr"/>
       <c r="V95" s="14" t="inlineStr"/>
       <c r="W95" s="14" t="n">
-        <v>1.3686592E8</v>
+        <v>4.5358707E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>3.1672115E8</v>
+        <v>1.40326965E8</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>4.5358707E8</v>
+        <v>5.93914035E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.4688761846283616</v>
+        <v>0.6139331677334524</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>5.1380493E8</v>
+        <v>3.73477965E8</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6145,23 +6145,23 @@
       <c r="U96" s="14" t="inlineStr"/>
       <c r="V96" s="14" t="inlineStr"/>
       <c r="W96" s="14" t="n">
-        <v>1.122052E8</v>
+        <v>2.308176E8</v>
       </c>
       <c r="X96" s="14" t="n">
-        <v>1.186124E8</v>
+        <v>1.154088E8</v>
       </c>
       <c r="Y96" s="14" t="inlineStr"/>
       <c r="Z96" s="14" t="n">
-        <v>2.308176E8</v>
+        <v>3.462264E8</v>
       </c>
       <c r="AA96" s="14" t="inlineStr"/>
       <c r="AB96" s="14" t="inlineStr"/>
       <c r="AC96" s="15" t="n">
-        <v>0.664638349703268</v>
+        <v>0.9969575245549019</v>
       </c>
       <c r="AD96" s="15" t="inlineStr"/>
       <c r="AE96" s="14" t="n">
-        <v>1.164654E8</v>
+        <v>1056600.0</v>
       </c>
       <c r="AF96" s="14" t="inlineStr"/>
       <c r="AG96" s="14" t="inlineStr"/>
@@ -6202,23 +6202,23 @@
       <c r="U97" s="14" t="inlineStr"/>
       <c r="V97" s="14" t="inlineStr"/>
       <c r="W97" s="14" t="n">
-        <v>1.122052E8</v>
+        <v>2.308176E8</v>
       </c>
       <c r="X97" s="14" t="n">
-        <v>1.186124E8</v>
+        <v>1.154088E8</v>
       </c>
       <c r="Y97" s="14" t="inlineStr"/>
       <c r="Z97" s="14" t="n">
-        <v>2.308176E8</v>
+        <v>3.462264E8</v>
       </c>
       <c r="AA97" s="14" t="inlineStr"/>
       <c r="AB97" s="14" t="inlineStr"/>
       <c r="AC97" s="15" t="n">
-        <v>0.664638349703268</v>
+        <v>0.9969575245549019</v>
       </c>
       <c r="AD97" s="15" t="inlineStr"/>
       <c r="AE97" s="14" t="n">
-        <v>1.164654E8</v>
+        <v>1056600.0</v>
       </c>
       <c r="AF97" s="14" t="inlineStr"/>
       <c r="AG97" s="14" t="inlineStr"/>
@@ -6265,23 +6265,23 @@
       <c r="U98" s="14" t="inlineStr"/>
       <c r="V98" s="14" t="inlineStr"/>
       <c r="W98" s="14" t="n">
-        <v>2086.0</v>
+        <v>4248.0</v>
       </c>
       <c r="X98" s="14" t="n">
-        <v>2162.0</v>
+        <v>2111.0</v>
       </c>
       <c r="Y98" s="14" t="inlineStr"/>
       <c r="Z98" s="14" t="n">
-        <v>4248.0</v>
+        <v>6359.0</v>
       </c>
       <c r="AA98" s="14" t="inlineStr"/>
       <c r="AB98" s="14" t="inlineStr"/>
       <c r="AC98" s="15" t="n">
-        <v>0.708</v>
+        <v>1.0598333333333334</v>
       </c>
       <c r="AD98" s="15" t="inlineStr"/>
       <c r="AE98" s="14" t="n">
-        <v>1752.0</v>
+        <v>-359.0</v>
       </c>
       <c r="AF98" s="14" t="inlineStr"/>
       <c r="AG98" s="14" t="inlineStr"/>
@@ -6322,23 +6322,23 @@
       <c r="U99" s="14" t="inlineStr"/>
       <c r="V99" s="14" t="inlineStr"/>
       <c r="W99" s="14" t="n">
-        <v>2086.0</v>
+        <v>4248.0</v>
       </c>
       <c r="X99" s="14" t="n">
-        <v>2162.0</v>
+        <v>2111.0</v>
       </c>
       <c r="Y99" s="14" t="inlineStr"/>
       <c r="Z99" s="14" t="n">
-        <v>4248.0</v>
+        <v>6359.0</v>
       </c>
       <c r="AA99" s="14" t="inlineStr"/>
       <c r="AB99" s="14" t="inlineStr"/>
       <c r="AC99" s="15" t="n">
-        <v>0.708</v>
+        <v>1.0598333333333334</v>
       </c>
       <c r="AD99" s="15" t="inlineStr"/>
       <c r="AE99" s="14" t="n">
-        <v>1752.0</v>
+        <v>-359.0</v>
       </c>
       <c r="AF99" s="14" t="inlineStr"/>
       <c r="AG99" s="14" t="inlineStr"/>
@@ -6385,23 +6385,23 @@
       <c r="U100" s="14" t="inlineStr"/>
       <c r="V100" s="14" t="inlineStr"/>
       <c r="W100" s="14" t="n">
-        <v>7571670.0</v>
+        <v>1.514334E7</v>
       </c>
       <c r="X100" s="14" t="n">
         <v>7571670.0</v>
       </c>
       <c r="Y100" s="14" t="inlineStr"/>
       <c r="Z100" s="14" t="n">
-        <v>1.514334E7</v>
+        <v>2.271501E7</v>
       </c>
       <c r="AA100" s="14" t="inlineStr"/>
       <c r="AB100" s="14" t="inlineStr"/>
       <c r="AC100" s="15" t="n">
-        <v>0.531625065824118</v>
+        <v>0.7974375987361769</v>
       </c>
       <c r="AD100" s="15" t="inlineStr"/>
       <c r="AE100" s="14" t="n">
-        <v>1.334166E7</v>
+        <v>5769990.0</v>
       </c>
       <c r="AF100" s="14" t="inlineStr"/>
       <c r="AG100" s="14" t="inlineStr"/>
@@ -6442,23 +6442,23 @@
       <c r="U101" s="14" t="inlineStr"/>
       <c r="V101" s="14" t="inlineStr"/>
       <c r="W101" s="14" t="n">
-        <v>7571670.0</v>
+        <v>1.514334E7</v>
       </c>
       <c r="X101" s="14" t="n">
         <v>7571670.0</v>
       </c>
       <c r="Y101" s="14" t="inlineStr"/>
       <c r="Z101" s="14" t="n">
-        <v>1.514334E7</v>
+        <v>2.271501E7</v>
       </c>
       <c r="AA101" s="14" t="inlineStr"/>
       <c r="AB101" s="14" t="inlineStr"/>
       <c r="AC101" s="15" t="n">
-        <v>0.531625065824118</v>
+        <v>0.7974375987361769</v>
       </c>
       <c r="AD101" s="15" t="inlineStr"/>
       <c r="AE101" s="14" t="n">
-        <v>1.334166E7</v>
+        <v>5769990.0</v>
       </c>
       <c r="AF101" s="14" t="inlineStr"/>
       <c r="AG101" s="14" t="inlineStr"/>
@@ -6505,23 +6505,23 @@
       <c r="U102" s="14" t="inlineStr"/>
       <c r="V102" s="14" t="inlineStr"/>
       <c r="W102" s="14" t="n">
-        <v>2630444.0</v>
+        <v>5260888.0</v>
       </c>
       <c r="X102" s="14" t="n">
         <v>2630444.0</v>
       </c>
       <c r="Y102" s="14" t="inlineStr"/>
       <c r="Z102" s="14" t="n">
-        <v>5260888.0</v>
+        <v>7891332.0</v>
       </c>
       <c r="AA102" s="14" t="inlineStr"/>
       <c r="AB102" s="14" t="inlineStr"/>
       <c r="AC102" s="15" t="n">
-        <v>0.48005182954649145</v>
+        <v>0.7200777443197373</v>
       </c>
       <c r="AD102" s="15" t="inlineStr"/>
       <c r="AE102" s="14" t="n">
-        <v>5698112.0</v>
+        <v>3067668.0</v>
       </c>
       <c r="AF102" s="14" t="inlineStr"/>
       <c r="AG102" s="14" t="inlineStr"/>
@@ -6562,23 +6562,23 @@
       <c r="U103" s="14" t="inlineStr"/>
       <c r="V103" s="14" t="inlineStr"/>
       <c r="W103" s="14" t="n">
-        <v>2630444.0</v>
+        <v>5260888.0</v>
       </c>
       <c r="X103" s="14" t="n">
         <v>2630444.0</v>
       </c>
       <c r="Y103" s="14" t="inlineStr"/>
       <c r="Z103" s="14" t="n">
-        <v>5260888.0</v>
+        <v>7891332.0</v>
       </c>
       <c r="AA103" s="14" t="inlineStr"/>
       <c r="AB103" s="14" t="inlineStr"/>
       <c r="AC103" s="15" t="n">
-        <v>0.48005182954649145</v>
+        <v>0.7200777443197373</v>
       </c>
       <c r="AD103" s="15" t="inlineStr"/>
       <c r="AE103" s="14" t="n">
-        <v>5698112.0</v>
+        <v>3067668.0</v>
       </c>
       <c r="AF103" s="14" t="inlineStr"/>
       <c r="AG103" s="14" t="inlineStr"/>
@@ -6625,23 +6625,23 @@
       <c r="U104" s="14" t="inlineStr"/>
       <c r="V104" s="14" t="inlineStr"/>
       <c r="W104" s="14" t="n">
-        <v>7676520.0</v>
+        <v>1.549788E7</v>
       </c>
       <c r="X104" s="14" t="n">
-        <v>7821360.0</v>
+        <v>7748940.0</v>
       </c>
       <c r="Y104" s="14" t="inlineStr"/>
       <c r="Z104" s="14" t="n">
-        <v>1.549788E7</v>
+        <v>2.324682E7</v>
       </c>
       <c r="AA104" s="14" t="inlineStr"/>
       <c r="AB104" s="14" t="inlineStr"/>
       <c r="AC104" s="15" t="n">
-        <v>0.5799236641221374</v>
+        <v>0.8698854961832061</v>
       </c>
       <c r="AD104" s="15" t="inlineStr"/>
       <c r="AE104" s="14" t="n">
-        <v>1.122612E7</v>
+        <v>3477180.0</v>
       </c>
       <c r="AF104" s="14" t="inlineStr"/>
       <c r="AG104" s="14" t="inlineStr"/>
@@ -6682,23 +6682,23 @@
       <c r="U105" s="14" t="inlineStr"/>
       <c r="V105" s="14" t="inlineStr"/>
       <c r="W105" s="14" t="n">
-        <v>7676520.0</v>
+        <v>1.549788E7</v>
       </c>
       <c r="X105" s="14" t="n">
-        <v>7821360.0</v>
+        <v>7748940.0</v>
       </c>
       <c r="Y105" s="14" t="inlineStr"/>
       <c r="Z105" s="14" t="n">
-        <v>1.549788E7</v>
+        <v>2.324682E7</v>
       </c>
       <c r="AA105" s="14" t="inlineStr"/>
       <c r="AB105" s="14" t="inlineStr"/>
       <c r="AC105" s="15" t="n">
-        <v>0.5799236641221374</v>
+        <v>0.8698854961832061</v>
       </c>
       <c r="AD105" s="15" t="inlineStr"/>
       <c r="AE105" s="14" t="n">
-        <v>1.122612E7</v>
+        <v>3477180.0</v>
       </c>
       <c r="AF105" s="14" t="inlineStr"/>
       <c r="AG105" s="14" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
       <c r="U106" s="14" t="inlineStr"/>
       <c r="V106" s="14" t="inlineStr"/>
       <c r="W106" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0833E7</v>
       </c>
       <c r="X106" s="14" t="n">
-        <v>3.0833E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y106" s="14" t="inlineStr"/>
       <c r="Z106" s="14" t="n">
@@ -6802,10 +6802,10 @@
       <c r="U107" s="14" t="inlineStr"/>
       <c r="V107" s="14" t="inlineStr"/>
       <c r="W107" s="14" t="n">
-        <v>0.0</v>
+        <v>8855000.0</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>8855000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
@@ -6859,10 +6859,10 @@
       <c r="U108" s="14" t="inlineStr"/>
       <c r="V108" s="14" t="inlineStr"/>
       <c r="W108" s="14" t="n">
-        <v>0.0</v>
+        <v>2.1978E7</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>2.1978E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
@@ -6922,23 +6922,23 @@
       <c r="U109" s="14" t="inlineStr"/>
       <c r="V109" s="14" t="inlineStr"/>
       <c r="W109" s="14" t="n">
-        <v>6780000.0</v>
+        <v>1.393E7</v>
       </c>
       <c r="X109" s="14" t="n">
-        <v>7150000.0</v>
+        <v>6965000.0</v>
       </c>
       <c r="Y109" s="14" t="inlineStr"/>
       <c r="Z109" s="14" t="n">
-        <v>1.393E7</v>
+        <v>2.0895E7</v>
       </c>
       <c r="AA109" s="14" t="inlineStr"/>
       <c r="AB109" s="14" t="inlineStr"/>
       <c r="AC109" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.0</v>
       </c>
       <c r="AD109" s="15" t="inlineStr"/>
       <c r="AE109" s="14" t="n">
-        <v>6965000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF109" s="14" t="inlineStr"/>
       <c r="AG109" s="14" t="inlineStr"/>
@@ -6979,23 +6979,23 @@
       <c r="U110" s="14" t="inlineStr"/>
       <c r="V110" s="14" t="inlineStr"/>
       <c r="W110" s="14" t="n">
-        <v>6780000.0</v>
+        <v>1.393E7</v>
       </c>
       <c r="X110" s="14" t="n">
-        <v>7150000.0</v>
+        <v>6965000.0</v>
       </c>
       <c r="Y110" s="14" t="inlineStr"/>
       <c r="Z110" s="14" t="n">
-        <v>1.393E7</v>
+        <v>2.0895E7</v>
       </c>
       <c r="AA110" s="14" t="inlineStr"/>
       <c r="AB110" s="14" t="inlineStr"/>
       <c r="AC110" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.0</v>
       </c>
       <c r="AD110" s="15" t="inlineStr"/>
       <c r="AE110" s="14" t="n">
-        <v>6965000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF110" s="14" t="inlineStr"/>
       <c r="AG110" s="14" t="inlineStr"/>
@@ -7042,10 +7042,10 @@
       <c r="U111" s="14" t="inlineStr"/>
       <c r="V111" s="14" t="inlineStr"/>
       <c r="W111" s="14" t="n">
-        <v>0.0</v>
+        <v>1.42100114E8</v>
       </c>
       <c r="X111" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y111" s="14" t="inlineStr"/>
       <c r="Z111" s="14" t="n">
@@ -7099,10 +7099,10 @@
       <c r="U112" s="14" t="inlineStr"/>
       <c r="V112" s="14" t="inlineStr"/>
       <c r="W112" s="14" t="n">
-        <v>0.0</v>
+        <v>1.42100114E8</v>
       </c>
       <c r="X112" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y112" s="14" t="inlineStr"/>
       <c r="Z112" s="14" t="n">
@@ -7162,23 +7162,23 @@
       <c r="U113" s="14" t="inlineStr"/>
       <c r="V113" s="14" t="inlineStr"/>
       <c r="W113" s="14" t="n">
-        <v>4.533248816E10</v>
+        <v>4.9091867246E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>3.759379086E9</v>
+        <v>1.598020754E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>4.9091867246E10</v>
+        <v>5.0689888E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.8903609649041908</v>
+        <v>0.9193436738595991</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>6.045171754E9</v>
+        <v>4.447151E9</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -7269,23 +7269,23 @@
       <c r="U115" s="14" t="inlineStr"/>
       <c r="V115" s="14" t="inlineStr"/>
       <c r="W115" s="14" t="n">
-        <v>1.47616458E10</v>
+        <v>1.59343583E10</v>
       </c>
       <c r="X115" s="14" t="n">
-        <v>1.1727125E9</v>
+        <v>1.1547953E9</v>
       </c>
       <c r="Y115" s="14" t="inlineStr"/>
       <c r="Z115" s="14" t="n">
-        <v>1.59343583E10</v>
+        <v>1.70891536E10</v>
       </c>
       <c r="AA115" s="14" t="inlineStr"/>
       <c r="AB115" s="14" t="inlineStr"/>
       <c r="AC115" s="15" t="n">
-        <v>0.9313796213647625</v>
+        <v>0.9988785936495647</v>
       </c>
       <c r="AD115" s="15" t="inlineStr"/>
       <c r="AE115" s="14" t="n">
-        <v>1.1739807E9</v>
+        <v>1.91854E7</v>
       </c>
       <c r="AF115" s="14" t="inlineStr"/>
       <c r="AG115" s="14" t="inlineStr"/>
@@ -7326,23 +7326,23 @@
       <c r="U116" s="14" t="inlineStr"/>
       <c r="V116" s="14" t="inlineStr"/>
       <c r="W116" s="14" t="n">
-        <v>1.22708924E10</v>
+        <v>1.34436049E10</v>
       </c>
       <c r="X116" s="14" t="n">
-        <v>1.1727125E9</v>
+        <v>1.1547953E9</v>
       </c>
       <c r="Y116" s="14" t="inlineStr"/>
       <c r="Z116" s="14" t="n">
-        <v>1.34436049E10</v>
+        <v>1.45984002E10</v>
       </c>
       <c r="AA116" s="14" t="inlineStr"/>
       <c r="AB116" s="14" t="inlineStr"/>
       <c r="AC116" s="15" t="n">
-        <v>0.9185199464886965</v>
+        <v>0.9974201019939656</v>
       </c>
       <c r="AD116" s="15" t="inlineStr"/>
       <c r="AE116" s="14" t="n">
-        <v>1.1925551E9</v>
+        <v>3.77598E7</v>
       </c>
       <c r="AF116" s="14" t="inlineStr"/>
       <c r="AG116" s="14" t="inlineStr"/>
@@ -7503,23 +7503,23 @@
       <c r="U119" s="14" t="inlineStr"/>
       <c r="V119" s="14" t="inlineStr"/>
       <c r="W119" s="14" t="n">
-        <v>199586.0</v>
+        <v>215142.0</v>
       </c>
       <c r="X119" s="14" t="n">
-        <v>15556.0</v>
+        <v>15003.0</v>
       </c>
       <c r="Y119" s="14" t="inlineStr"/>
       <c r="Z119" s="14" t="n">
-        <v>215142.0</v>
+        <v>230145.0</v>
       </c>
       <c r="AA119" s="14" t="inlineStr"/>
       <c r="AB119" s="14" t="inlineStr"/>
       <c r="AC119" s="15" t="n">
-        <v>0.9001757322175732</v>
+        <v>0.9629497907949791</v>
       </c>
       <c r="AD119" s="15" t="inlineStr"/>
       <c r="AE119" s="14" t="n">
-        <v>23858.0</v>
+        <v>8855.0</v>
       </c>
       <c r="AF119" s="14" t="inlineStr"/>
       <c r="AG119" s="14" t="inlineStr"/>
@@ -7560,23 +7560,23 @@
       <c r="U120" s="14" t="inlineStr"/>
       <c r="V120" s="14" t="inlineStr"/>
       <c r="W120" s="14" t="n">
-        <v>165812.0</v>
+        <v>181368.0</v>
       </c>
       <c r="X120" s="14" t="n">
-        <v>15556.0</v>
+        <v>15003.0</v>
       </c>
       <c r="Y120" s="14" t="inlineStr"/>
       <c r="Z120" s="14" t="n">
-        <v>181368.0</v>
+        <v>196371.0</v>
       </c>
       <c r="AA120" s="14" t="inlineStr"/>
       <c r="AB120" s="14" t="inlineStr"/>
       <c r="AC120" s="15" t="n">
-        <v>0.8890588235294118</v>
+        <v>0.9626029411764706</v>
       </c>
       <c r="AD120" s="15" t="inlineStr"/>
       <c r="AE120" s="14" t="n">
-        <v>22632.0</v>
+        <v>7629.0</v>
       </c>
       <c r="AF120" s="14" t="inlineStr"/>
       <c r="AG120" s="14" t="inlineStr"/>
@@ -7737,23 +7737,23 @@
       <c r="U123" s="14" t="inlineStr"/>
       <c r="V123" s="14" t="inlineStr"/>
       <c r="W123" s="14" t="n">
-        <v>1.16115065E9</v>
+        <v>1.25340484E9</v>
       </c>
       <c r="X123" s="14" t="n">
-        <v>9.225419E7</v>
+        <v>9.106439E7</v>
       </c>
       <c r="Y123" s="14" t="inlineStr"/>
       <c r="Z123" s="14" t="n">
-        <v>1.25340484E9</v>
+        <v>1.34446923E9</v>
       </c>
       <c r="AA123" s="14" t="inlineStr"/>
       <c r="AB123" s="14" t="inlineStr"/>
       <c r="AC123" s="15" t="n">
-        <v>0.9312888054079035</v>
+        <v>0.998950301735219</v>
       </c>
       <c r="AD123" s="15" t="inlineStr"/>
       <c r="AE123" s="14" t="n">
-        <v>9.247716E7</v>
+        <v>1412770.0</v>
       </c>
       <c r="AF123" s="14" t="inlineStr"/>
       <c r="AG123" s="14" t="inlineStr"/>
@@ -7794,23 +7794,23 @@
       <c r="U124" s="14" t="inlineStr"/>
       <c r="V124" s="14" t="inlineStr"/>
       <c r="W124" s="14" t="n">
-        <v>9.6616559E8</v>
+        <v>1.05841978E9</v>
       </c>
       <c r="X124" s="14" t="n">
-        <v>9.225419E7</v>
+        <v>9.106439E7</v>
       </c>
       <c r="Y124" s="14" t="inlineStr"/>
       <c r="Z124" s="14" t="n">
-        <v>1.05841978E9</v>
+        <v>1.14948417E9</v>
       </c>
       <c r="AA124" s="14" t="inlineStr"/>
       <c r="AB124" s="14" t="inlineStr"/>
       <c r="AC124" s="15" t="n">
-        <v>0.9196484999513422</v>
+        <v>0.9987732775159528</v>
       </c>
       <c r="AD124" s="15" t="inlineStr"/>
       <c r="AE124" s="14" t="n">
-        <v>9.247622E7</v>
+        <v>1411830.0</v>
       </c>
       <c r="AF124" s="14" t="inlineStr"/>
       <c r="AG124" s="14" t="inlineStr"/>
@@ -7971,23 +7971,23 @@
       <c r="U127" s="14" t="inlineStr"/>
       <c r="V127" s="14" t="inlineStr"/>
       <c r="W127" s="14" t="n">
-        <v>3.61799754E8</v>
+        <v>3.91185426E8</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>2.9385672E7</v>
+        <v>2.9286128E7</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
-        <v>3.91185426E8</v>
+        <v>4.20471554E8</v>
       </c>
       <c r="AA127" s="14" t="inlineStr"/>
       <c r="AB127" s="14" t="inlineStr"/>
       <c r="AC127" s="15" t="n">
-        <v>0.929912653416344</v>
+        <v>0.9995306381026413</v>
       </c>
       <c r="AD127" s="15" t="inlineStr"/>
       <c r="AE127" s="14" t="n">
-        <v>2.9483574E7</v>
+        <v>197446.0</v>
       </c>
       <c r="AF127" s="14" t="inlineStr"/>
       <c r="AG127" s="14" t="inlineStr"/>
@@ -8028,23 +8028,23 @@
       <c r="U128" s="14" t="inlineStr"/>
       <c r="V128" s="14" t="inlineStr"/>
       <c r="W128" s="14" t="n">
-        <v>3.01408898E8</v>
+        <v>3.3079457E8</v>
       </c>
       <c r="X128" s="14" t="n">
-        <v>2.9385672E7</v>
+        <v>2.9286128E7</v>
       </c>
       <c r="Y128" s="14" t="inlineStr"/>
       <c r="Z128" s="14" t="n">
-        <v>3.3079457E8</v>
+        <v>3.60080698E8</v>
       </c>
       <c r="AA128" s="14" t="inlineStr"/>
       <c r="AB128" s="14" t="inlineStr"/>
       <c r="AC128" s="15" t="n">
-        <v>0.9181698753178119</v>
+        <v>0.9994579100467419</v>
       </c>
       <c r="AD128" s="15" t="inlineStr"/>
       <c r="AE128" s="14" t="n">
-        <v>2.948143E7</v>
+        <v>195302.0</v>
       </c>
       <c r="AF128" s="14" t="inlineStr"/>
       <c r="AG128" s="14" t="inlineStr"/>
@@ -8205,23 +8205,23 @@
       <c r="U131" s="14" t="inlineStr"/>
       <c r="V131" s="14" t="inlineStr"/>
       <c r="W131" s="14" t="n">
-        <v>3.18431E9</v>
+        <v>3.43577E9</v>
       </c>
       <c r="X131" s="14" t="n">
-        <v>2.5146E8</v>
+        <v>2.4768E8</v>
       </c>
       <c r="Y131" s="14" t="inlineStr"/>
       <c r="Z131" s="14" t="n">
-        <v>3.43577E9</v>
+        <v>3.68345E9</v>
       </c>
       <c r="AA131" s="14" t="inlineStr"/>
       <c r="AB131" s="14" t="inlineStr"/>
       <c r="AC131" s="15" t="n">
-        <v>0.9317989262440999</v>
+        <v>0.9989710472103284</v>
       </c>
       <c r="AD131" s="15" t="inlineStr"/>
       <c r="AE131" s="14" t="n">
-        <v>2.51474E8</v>
+        <v>3794000.0</v>
       </c>
       <c r="AF131" s="14" t="inlineStr"/>
       <c r="AG131" s="14" t="inlineStr"/>
@@ -8262,23 +8262,23 @@
       <c r="U132" s="14" t="inlineStr"/>
       <c r="V132" s="14" t="inlineStr"/>
       <c r="W132" s="14" t="n">
-        <v>2.64605E9</v>
+        <v>2.89751E9</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>2.5146E8</v>
+        <v>2.4768E8</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
-        <v>2.89751E9</v>
+        <v>3.14519E9</v>
       </c>
       <c r="AA132" s="14" t="inlineStr"/>
       <c r="AB132" s="14" t="inlineStr"/>
       <c r="AC132" s="15" t="n">
-        <v>0.9201423953153085</v>
+        <v>0.9987964356712332</v>
       </c>
       <c r="AD132" s="15" t="inlineStr"/>
       <c r="AE132" s="14" t="n">
-        <v>2.5147E8</v>
+        <v>3790000.0</v>
       </c>
       <c r="AF132" s="14" t="inlineStr"/>
       <c r="AG132" s="14" t="inlineStr"/>
@@ -8439,23 +8439,23 @@
       <c r="U135" s="14" t="inlineStr"/>
       <c r="V135" s="14" t="inlineStr"/>
       <c r="W135" s="14" t="n">
-        <v>2.24319971E8</v>
+        <v>2.27384598E8</v>
       </c>
       <c r="X135" s="14" t="n">
-        <v>3064627.0</v>
+        <v>9889353.0</v>
       </c>
       <c r="Y135" s="14" t="inlineStr"/>
       <c r="Z135" s="14" t="n">
-        <v>2.27384598E8</v>
+        <v>2.37273951E8</v>
       </c>
       <c r="AA135" s="14" t="inlineStr"/>
       <c r="AB135" s="14" t="inlineStr"/>
       <c r="AC135" s="15" t="n">
-        <v>0.9862702147039688</v>
+        <v>1.0291648275862069</v>
       </c>
       <c r="AD135" s="15" t="inlineStr"/>
       <c r="AE135" s="14" t="n">
-        <v>3165402.0</v>
+        <v>-6723951.0</v>
       </c>
       <c r="AF135" s="14" t="inlineStr"/>
       <c r="AG135" s="14" t="inlineStr"/>
@@ -8496,23 +8496,23 @@
       <c r="U136" s="14" t="inlineStr"/>
       <c r="V136" s="14" t="inlineStr"/>
       <c r="W136" s="14" t="n">
-        <v>3.886384E7</v>
+        <v>4.1928467E7</v>
       </c>
       <c r="X136" s="14" t="n">
-        <v>3064627.0</v>
+        <v>9889353.0</v>
       </c>
       <c r="Y136" s="14" t="inlineStr"/>
       <c r="Z136" s="14" t="n">
-        <v>4.1928467E7</v>
+        <v>5.181782E7</v>
       </c>
       <c r="AA136" s="14" t="inlineStr"/>
       <c r="AB136" s="14" t="inlineStr"/>
       <c r="AC136" s="15" t="n">
-        <v>0.9300076967438559</v>
+        <v>1.1493616360571377</v>
       </c>
       <c r="AD136" s="15" t="inlineStr"/>
       <c r="AE136" s="14" t="n">
-        <v>3155533.0</v>
+        <v>-6733820.0</v>
       </c>
       <c r="AF136" s="14" t="inlineStr"/>
       <c r="AG136" s="14" t="inlineStr"/>
@@ -8673,23 +8673,23 @@
       <c r="U139" s="14" t="inlineStr"/>
       <c r="V139" s="14" t="inlineStr"/>
       <c r="W139" s="14" t="n">
-        <v>8.1240756E8</v>
+        <v>8.7794766E8</v>
       </c>
       <c r="X139" s="14" t="n">
-        <v>6.55401E7</v>
+        <v>6.510558E7</v>
       </c>
       <c r="Y139" s="14" t="inlineStr"/>
       <c r="Z139" s="14" t="n">
-        <v>8.7794766E8</v>
+        <v>9.4305324E8</v>
       </c>
       <c r="AA139" s="14" t="inlineStr"/>
       <c r="AB139" s="14" t="inlineStr"/>
       <c r="AC139" s="15" t="n">
-        <v>0.9305261071589068</v>
+        <v>0.9995307240306265</v>
       </c>
       <c r="AD139" s="15" t="inlineStr"/>
       <c r="AE139" s="14" t="n">
-        <v>6.554834E7</v>
+        <v>442760.0</v>
       </c>
       <c r="AF139" s="14" t="inlineStr"/>
       <c r="AG139" s="14" t="inlineStr"/>
@@ -8730,23 +8730,23 @@
       <c r="U140" s="14" t="inlineStr"/>
       <c r="V140" s="14" t="inlineStr"/>
       <c r="W140" s="14" t="n">
-        <v>6.756786E8</v>
+        <v>7.412187E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>6.55401E7</v>
+        <v>6.510558E7</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
-        <v>7.412187E8</v>
+        <v>8.0632428E8</v>
       </c>
       <c r="AA140" s="14" t="inlineStr"/>
       <c r="AB140" s="14" t="inlineStr"/>
       <c r="AC140" s="15" t="n">
-        <v>0.9187598542317418</v>
+        <v>0.99945991372899</v>
       </c>
       <c r="AD140" s="15" t="inlineStr"/>
       <c r="AE140" s="14" t="n">
-        <v>6.55413E7</v>
+        <v>435720.0</v>
       </c>
       <c r="AF140" s="14" t="inlineStr"/>
       <c r="AG140" s="14" t="inlineStr"/>
@@ -8951,10 +8951,10 @@
       <c r="U144" s="14" t="inlineStr"/>
       <c r="V144" s="14" t="inlineStr"/>
       <c r="W144" s="14" t="n">
-        <v>1.960479E9</v>
+        <v>2.213268E9</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>2.52789E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
@@ -9008,10 +9008,10 @@
       <c r="U145" s="14" t="inlineStr"/>
       <c r="V145" s="14" t="inlineStr"/>
       <c r="W145" s="14" t="n">
-        <v>1.7493E8</v>
+        <v>1.9894E8</v>
       </c>
       <c r="X145" s="14" t="n">
-        <v>2.401E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y145" s="14" t="inlineStr"/>
       <c r="Z145" s="14" t="n">
@@ -9065,10 +9065,10 @@
       <c r="U146" s="14" t="inlineStr"/>
       <c r="V146" s="14" t="inlineStr"/>
       <c r="W146" s="14" t="n">
-        <v>1.398304E9</v>
+        <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>1.83187E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
@@ -9122,10 +9122,10 @@
       <c r="U147" s="14" t="inlineStr"/>
       <c r="V147" s="14" t="inlineStr"/>
       <c r="W147" s="14" t="n">
-        <v>3.87245E8</v>
+        <v>4.32837E8</v>
       </c>
       <c r="X147" s="14" t="n">
-        <v>4.5592E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y147" s="14" t="inlineStr"/>
       <c r="Z147" s="14" t="n">
@@ -9185,23 +9185,23 @@
       <c r="U148" s="14" t="inlineStr"/>
       <c r="V148" s="14" t="inlineStr"/>
       <c r="W148" s="14" t="n">
-        <v>2590000.0</v>
+        <v>2775000.0</v>
       </c>
       <c r="X148" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y148" s="14" t="inlineStr"/>
       <c r="Z148" s="14" t="n">
-        <v>2775000.0</v>
+        <v>2960000.0</v>
       </c>
       <c r="AA148" s="14" t="inlineStr"/>
       <c r="AB148" s="14" t="inlineStr"/>
       <c r="AC148" s="15" t="n">
-        <v>0.9337146702557201</v>
+        <v>0.9959623149394348</v>
       </c>
       <c r="AD148" s="15" t="inlineStr"/>
       <c r="AE148" s="14" t="n">
-        <v>197000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="AF148" s="14" t="inlineStr"/>
       <c r="AG148" s="14" t="inlineStr"/>
@@ -9242,23 +9242,23 @@
       <c r="U149" s="14" t="inlineStr"/>
       <c r="V149" s="14" t="inlineStr"/>
       <c r="W149" s="14" t="n">
-        <v>2035000.0</v>
+        <v>2220000.0</v>
       </c>
       <c r="X149" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y149" s="14" t="inlineStr"/>
       <c r="Z149" s="14" t="n">
-        <v>2220000.0</v>
+        <v>2405000.0</v>
       </c>
       <c r="AA149" s="14" t="inlineStr"/>
       <c r="AB149" s="14" t="inlineStr"/>
       <c r="AC149" s="15" t="n">
-        <v>0.9203980099502488</v>
+        <v>0.9970978441127695</v>
       </c>
       <c r="AD149" s="15" t="inlineStr"/>
       <c r="AE149" s="14" t="n">
-        <v>192000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="AF149" s="14" t="inlineStr"/>
       <c r="AG149" s="14" t="inlineStr"/>
@@ -9419,10 +9419,10 @@
       <c r="U152" s="14" t="inlineStr"/>
       <c r="V152" s="14" t="inlineStr"/>
       <c r="W152" s="14" t="n">
-        <v>2.2863585839E10</v>
+        <v>2.475555828E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>1.891972441E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
@@ -9476,10 +9476,10 @@
       <c r="U153" s="14" t="inlineStr"/>
       <c r="V153" s="14" t="inlineStr"/>
       <c r="W153" s="14" t="n">
-        <v>1.8086300639E10</v>
+        <v>1.997827308E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>1.891972441E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
@@ -9653,23 +9653,23 @@
       <c r="U156" s="14" t="inlineStr"/>
       <c r="V156" s="14" t="inlineStr"/>
       <c r="W156" s="14" t="n">
-        <v>1.7719617783E10</v>
+        <v>2.1747293967E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>4.027676184E9</v>
+        <v>1.417217241E9</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
-        <v>2.1747293967E10</v>
+        <v>2.3164511208E10</v>
       </c>
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.8069680085870595</v>
+        <v>0.8595561134078443</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>5.202094033E9</v>
+        <v>3.784876792E9</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -9716,23 +9716,23 @@
       <c r="U157" s="14" t="inlineStr"/>
       <c r="V157" s="14" t="inlineStr"/>
       <c r="W157" s="14" t="n">
-        <v>6.410501266E9</v>
+        <v>8.128605266E9</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>1.718104E9</v>
+        <v>1.0801748E9</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
-        <v>8.128605266E9</v>
+        <v>9.208780066E9</v>
       </c>
       <c r="AA157" s="14" t="inlineStr"/>
       <c r="AB157" s="14" t="inlineStr"/>
       <c r="AC157" s="15" t="n">
-        <v>0.8801438254517169</v>
+        <v>0.9971022887449378</v>
       </c>
       <c r="AD157" s="15" t="inlineStr"/>
       <c r="AE157" s="14" t="n">
-        <v>1.106936734E9</v>
+        <v>2.6761934E7</v>
       </c>
       <c r="AF157" s="14" t="inlineStr"/>
       <c r="AG157" s="14" t="inlineStr"/>
@@ -9773,23 +9773,23 @@
       <c r="U158" s="14" t="inlineStr"/>
       <c r="V158" s="14" t="inlineStr"/>
       <c r="W158" s="14" t="n">
-        <v>5.3213876E9</v>
+        <v>7.0394916E9</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>1.718104E9</v>
+        <v>1.0801748E9</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
-        <v>7.0394916E9</v>
+        <v>8.1196664E9</v>
       </c>
       <c r="AA158" s="14" t="inlineStr"/>
       <c r="AB158" s="14" t="inlineStr"/>
       <c r="AC158" s="15" t="n">
-        <v>0.8658213966806143</v>
+        <v>0.9986773623010865</v>
       </c>
       <c r="AD158" s="15" t="inlineStr"/>
       <c r="AE158" s="14" t="n">
-        <v>1.0909284E9</v>
+        <v>1.07536E7</v>
       </c>
       <c r="AF158" s="14" t="inlineStr"/>
       <c r="AG158" s="14" t="inlineStr"/>
@@ -9950,23 +9950,23 @@
       <c r="U161" s="14" t="inlineStr"/>
       <c r="V161" s="14" t="inlineStr"/>
       <c r="W161" s="14" t="n">
-        <v>121791.0</v>
+        <v>170872.0</v>
       </c>
       <c r="X161" s="14" t="n">
-        <v>49081.0</v>
+        <v>23097.0</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
-        <v>170872.0</v>
+        <v>193969.0</v>
       </c>
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>0.9388571428571428</v>
+        <v>1.0657637362637362</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>11128.0</v>
+        <v>-11969.0</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -10007,23 +10007,23 @@
       <c r="U162" s="14" t="inlineStr"/>
       <c r="V162" s="14" t="inlineStr"/>
       <c r="W162" s="14" t="n">
-        <v>108671.0</v>
+        <v>157752.0</v>
       </c>
       <c r="X162" s="14" t="n">
-        <v>49081.0</v>
+        <v>23097.0</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
-        <v>157752.0</v>
+        <v>180849.0</v>
       </c>
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>0.939</v>
+        <v>1.076482142857143</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>10248.0</v>
+        <v>-12849.0</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10184,23 +10184,23 @@
       <c r="U165" s="14" t="inlineStr"/>
       <c r="V165" s="14" t="inlineStr"/>
       <c r="W165" s="14" t="n">
-        <v>4.3506969E8</v>
+        <v>5.5135753E8</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>1.1628784E8</v>
+        <v>7.331996E7</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
-        <v>5.5135753E8</v>
+        <v>6.2467749E8</v>
       </c>
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.8605844589637852</v>
+        <v>0.9750256603161026</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>8.932047E7</v>
+        <v>1.600051E7</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10241,23 +10241,23 @@
       <c r="U166" s="14" t="inlineStr"/>
       <c r="V166" s="14" t="inlineStr"/>
       <c r="W166" s="14" t="n">
-        <v>3.6134492E8</v>
+        <v>4.7763276E8</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>1.1628784E8</v>
+        <v>7.331996E7</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
-        <v>4.7763276E8</v>
+        <v>5.5095272E8</v>
       </c>
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.8424571392287178</v>
+        <v>0.9717801859769434</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>8.931924E7</v>
+        <v>1.599928E7</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -10462,23 +10462,23 @@
       <c r="U170" s="14" t="inlineStr"/>
       <c r="V170" s="14" t="inlineStr"/>
       <c r="W170" s="14" t="n">
-        <v>1.29819088E8</v>
+        <v>1.641286E8</v>
       </c>
       <c r="X170" s="14" t="n">
-        <v>3.4309512E7</v>
+        <v>2.1686864E7</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
-        <v>1.641286E8</v>
+        <v>1.85815464E8</v>
       </c>
       <c r="AA170" s="14" t="inlineStr"/>
       <c r="AB170" s="14" t="inlineStr"/>
       <c r="AC170" s="15" t="n">
-        <v>0.8589163108096793</v>
+        <v>0.9724078121075107</v>
       </c>
       <c r="AD170" s="15" t="inlineStr"/>
       <c r="AE170" s="14" t="n">
-        <v>2.69594E7</v>
+        <v>5272536.0</v>
       </c>
       <c r="AF170" s="14" t="inlineStr"/>
       <c r="AG170" s="14" t="inlineStr"/>
@@ -10519,23 +10519,23 @@
       <c r="U171" s="14" t="inlineStr"/>
       <c r="V171" s="14" t="inlineStr"/>
       <c r="W171" s="14" t="n">
-        <v>1.07936504E8</v>
+        <v>1.42246016E8</v>
       </c>
       <c r="X171" s="14" t="n">
-        <v>3.4309512E7</v>
+        <v>2.1686864E7</v>
       </c>
       <c r="Y171" s="14" t="inlineStr"/>
       <c r="Z171" s="14" t="n">
-        <v>1.42246016E8</v>
+        <v>1.6393288E8</v>
       </c>
       <c r="AA171" s="14" t="inlineStr"/>
       <c r="AB171" s="14" t="inlineStr"/>
       <c r="AC171" s="15" t="n">
-        <v>0.8406974940898345</v>
+        <v>0.9688704491725768</v>
       </c>
       <c r="AD171" s="15" t="inlineStr"/>
       <c r="AE171" s="14" t="n">
-        <v>2.6953984E7</v>
+        <v>5267120.0</v>
       </c>
       <c r="AF171" s="14" t="inlineStr"/>
       <c r="AG171" s="14" t="inlineStr"/>
@@ -10696,23 +10696,23 @@
       <c r="U174" s="14" t="inlineStr"/>
       <c r="V174" s="14" t="inlineStr"/>
       <c r="W174" s="14" t="n">
-        <v>1.04439E9</v>
+        <v>1.30845E9</v>
       </c>
       <c r="X174" s="14" t="n">
-        <v>2.6406E8</v>
+        <v>1.764E8</v>
       </c>
       <c r="Y174" s="14" t="inlineStr"/>
       <c r="Z174" s="14" t="n">
-        <v>1.30845E9</v>
+        <v>1.48485E9</v>
       </c>
       <c r="AA174" s="14" t="inlineStr"/>
       <c r="AB174" s="14" t="inlineStr"/>
       <c r="AC174" s="15" t="n">
-        <v>0.8806272109063302</v>
+        <v>0.9993498522024261</v>
       </c>
       <c r="AD174" s="15" t="inlineStr"/>
       <c r="AE174" s="14" t="n">
-        <v>1.77366E8</v>
+        <v>966000.0</v>
       </c>
       <c r="AF174" s="14" t="inlineStr"/>
       <c r="AG174" s="14" t="inlineStr"/>
@@ -10753,23 +10753,23 @@
       <c r="U175" s="14" t="inlineStr"/>
       <c r="V175" s="14" t="inlineStr"/>
       <c r="W175" s="14" t="n">
-        <v>8.6658E8</v>
+        <v>1.13064E9</v>
       </c>
       <c r="X175" s="14" t="n">
-        <v>2.6406E8</v>
+        <v>1.764E8</v>
       </c>
       <c r="Y175" s="14" t="inlineStr"/>
       <c r="Z175" s="14" t="n">
-        <v>1.13064E9</v>
+        <v>1.30704E9</v>
       </c>
       <c r="AA175" s="14" t="inlineStr"/>
       <c r="AB175" s="14" t="inlineStr"/>
       <c r="AC175" s="15" t="n">
-        <v>0.8644036697247707</v>
+        <v>0.9992660550458715</v>
       </c>
       <c r="AD175" s="15" t="inlineStr"/>
       <c r="AE175" s="14" t="n">
-        <v>1.7736E8</v>
+        <v>960000.0</v>
       </c>
       <c r="AF175" s="14" t="inlineStr"/>
       <c r="AG175" s="14" t="inlineStr"/>
@@ -10930,23 +10930,23 @@
       <c r="U178" s="14" t="inlineStr"/>
       <c r="V178" s="14" t="inlineStr"/>
       <c r="W178" s="14" t="n">
-        <v>3.9221465E8</v>
+        <v>4.8947471E8</v>
       </c>
       <c r="X178" s="14" t="n">
-        <v>9.726006E7</v>
+        <v>6.561252E7</v>
       </c>
       <c r="Y178" s="14" t="inlineStr"/>
       <c r="Z178" s="14" t="n">
-        <v>4.8947471E8</v>
+        <v>5.5508723E8</v>
       </c>
       <c r="AA178" s="14" t="inlineStr"/>
       <c r="AB178" s="14" t="inlineStr"/>
       <c r="AC178" s="15" t="n">
-        <v>0.8656099195710456</v>
+        <v>0.9816421618906817</v>
       </c>
       <c r="AD178" s="15" t="inlineStr"/>
       <c r="AE178" s="14" t="n">
-        <v>7.599329E7</v>
+        <v>1.038077E7</v>
       </c>
       <c r="AF178" s="14" t="inlineStr"/>
       <c r="AG178" s="14" t="inlineStr"/>
@@ -10987,23 +10987,23 @@
       <c r="U179" s="14" t="inlineStr"/>
       <c r="V179" s="14" t="inlineStr"/>
       <c r="W179" s="14" t="n">
-        <v>3.2567274E8</v>
+        <v>4.229328E8</v>
       </c>
       <c r="X179" s="14" t="n">
-        <v>9.726006E7</v>
+        <v>6.561252E7</v>
       </c>
       <c r="Y179" s="14" t="inlineStr"/>
       <c r="Z179" s="14" t="n">
-        <v>4.229328E8</v>
+        <v>4.8854532E8</v>
       </c>
       <c r="AA179" s="14" t="inlineStr"/>
       <c r="AB179" s="14" t="inlineStr"/>
       <c r="AC179" s="15" t="n">
-        <v>0.8476898285109555</v>
+        <v>0.9791978738244702</v>
       </c>
       <c r="AD179" s="15" t="inlineStr"/>
       <c r="AE179" s="14" t="n">
-        <v>7.59912E7</v>
+        <v>1.037868E7</v>
       </c>
       <c r="AF179" s="14" t="inlineStr"/>
       <c r="AG179" s="14" t="inlineStr"/>
@@ -11164,10 +11164,10 @@
       <c r="U182" s="14" t="inlineStr"/>
       <c r="V182" s="14" t="inlineStr"/>
       <c r="W182" s="14" t="n">
-        <v>1.030637E9</v>
+        <v>1.310426E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>2.79789E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
@@ -11221,10 +11221,10 @@
       <c r="U183" s="14" t="inlineStr"/>
       <c r="V183" s="14" t="inlineStr"/>
       <c r="W183" s="14" t="n">
-        <v>9.968E7</v>
+        <v>1.2502E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>2.534E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
@@ -11278,10 +11278,10 @@
       <c r="U184" s="14" t="inlineStr"/>
       <c r="V184" s="14" t="inlineStr"/>
       <c r="W184" s="14" t="n">
-        <v>9.30957E8</v>
+        <v>1.185406E9</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>2.54449E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
@@ -11341,10 +11341,10 @@
       <c r="U185" s="14" t="inlineStr"/>
       <c r="V185" s="14" t="inlineStr"/>
       <c r="W185" s="14" t="n">
-        <v>8.276864298E9</v>
+        <v>9.794680989E9</v>
       </c>
       <c r="X185" s="14" t="n">
-        <v>1.517816691E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y185" s="14" t="inlineStr"/>
       <c r="Z185" s="14" t="n">
@@ -11398,10 +11398,10 @@
       <c r="U186" s="14" t="inlineStr"/>
       <c r="V186" s="14" t="inlineStr"/>
       <c r="W186" s="14" t="n">
-        <v>6.702420922E9</v>
+        <v>8.220237613E9</v>
       </c>
       <c r="X186" s="14" t="n">
-        <v>1.517816691E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y186" s="14" t="inlineStr"/>
       <c r="Z186" s="14" t="n">
@@ -11575,23 +11575,23 @@
       <c r="U189" s="25" t="inlineStr"/>
       <c r="V189" s="25" t="inlineStr"/>
       <c r="W189" s="25" t="n">
-        <v>5.354544346E9</v>
+        <v>5.752546162E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>3.98001816E8</v>
+        <v>8.7329894E7</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>5.752546162E9</v>
+        <v>5.839876056E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.828087548700586</v>
+        <v>0.840658816416515</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>1.194238838E9</v>
+        <v>1.106908944E9</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
       <c r="Q190" s="14" t="n">
-        <v>5.00789E9</v>
+        <v>5.000041E9</v>
       </c>
       <c r="R190" s="14" t="inlineStr"/>
       <c r="S190" s="14" t="n">
@@ -11638,23 +11638,23 @@
       <c r="U190" s="14" t="inlineStr"/>
       <c r="V190" s="14" t="inlineStr"/>
       <c r="W190" s="14" t="n">
-        <v>4.105668591E9</v>
+        <v>4.382759356E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>2.77090765E8</v>
+        <v>3.174114E7</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.382759356E9</v>
+        <v>4.414500496E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.8751708515961812</v>
+        <v>0.8828928594785522</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>6.25130644E8</v>
+        <v>5.85540504E8</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11691,7 +11691,7 @@
       <c r="O191" s="13" t="inlineStr"/>
       <c r="P191" s="13" t="inlineStr"/>
       <c r="Q191" s="14" t="n">
-        <v>1.920917E9</v>
+        <v>1.890817E9</v>
       </c>
       <c r="R191" s="14" t="inlineStr"/>
       <c r="S191" s="14" t="n">
@@ -11701,23 +11701,23 @@
       <c r="U191" s="14" t="inlineStr"/>
       <c r="V191" s="14" t="inlineStr"/>
       <c r="W191" s="14" t="n">
-        <v>1.700954357E9</v>
+        <v>1.752363354E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>5.1408997E7</v>
+        <v>2.554614E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.752363354E9</v>
+        <v>1.777909494E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9122535507780919</v>
+        <v>0.9402863915439728</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>1.68553646E8</v>
+        <v>1.12907506E8</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11748,7 +11748,7 @@
       <c r="O192" s="13" t="inlineStr"/>
       <c r="P192" s="13" t="inlineStr"/>
       <c r="Q192" s="14" t="n">
-        <v>6.8E8</v>
+        <v>6.385E8</v>
       </c>
       <c r="R192" s="14" t="inlineStr"/>
       <c r="S192" s="14" t="n">
@@ -11770,11 +11770,11 @@
       <c r="AA192" s="14" t="inlineStr"/>
       <c r="AB192" s="14" t="inlineStr"/>
       <c r="AC192" s="15" t="n">
-        <v>0.9389705882352941</v>
+        <v>1.0</v>
       </c>
       <c r="AD192" s="15" t="inlineStr"/>
       <c r="AE192" s="14" t="n">
-        <v>4.15E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF192" s="14" t="inlineStr"/>
       <c r="AG192" s="14" t="inlineStr"/>
@@ -11862,7 +11862,7 @@
       <c r="O194" s="13" t="inlineStr"/>
       <c r="P194" s="13" t="inlineStr"/>
       <c r="Q194" s="14" t="n">
-        <v>6.3714E7</v>
+        <v>9.393E7</v>
       </c>
       <c r="R194" s="14" t="inlineStr"/>
       <c r="S194" s="14" t="n">
@@ -11872,23 +11872,23 @@
       <c r="U194" s="14" t="inlineStr"/>
       <c r="V194" s="14" t="inlineStr"/>
       <c r="W194" s="14" t="n">
-        <v>5.0329917E7</v>
+        <v>5.3038114E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>2708197.0</v>
+        <v>2146140.0</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>5.3038114E7</v>
+        <v>5.5184254E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.8324404997331827</v>
+        <v>0.587504034919621</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>1.0675886E7</v>
+        <v>3.8745746E7</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       <c r="O196" s="13" t="inlineStr"/>
       <c r="P196" s="13" t="inlineStr"/>
       <c r="Q196" s="14" t="n">
-        <v>6.3714E7</v>
+        <v>9.393E7</v>
       </c>
       <c r="R196" s="14" t="inlineStr"/>
       <c r="S196" s="14" t="n">
@@ -11973,10 +11973,10 @@
       <c r="U196" s="14" t="inlineStr"/>
       <c r="V196" s="14" t="inlineStr"/>
       <c r="W196" s="14" t="n">
-        <v>5.0329917E7</v>
+        <v>5.3038114E7</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>2708197.0</v>
+        <v>2146140.0</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="2" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
       <c r="AC196" s="2" t="inlineStr"/>
       <c r="AD196" s="2" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>1.0675886E7</v>
+        <v>3.8745746E7</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       <c r="O200" s="13" t="inlineStr"/>
       <c r="P200" s="13" t="inlineStr"/>
       <c r="Q200" s="14" t="n">
-        <v>8936000.0</v>
+        <v>5420000.0</v>
       </c>
       <c r="R200" s="14" t="inlineStr"/>
       <c r="S200" s="14" t="n">
@@ -12209,11 +12209,11 @@
       <c r="AA200" s="14" t="inlineStr"/>
       <c r="AB200" s="14" t="inlineStr"/>
       <c r="AC200" s="15" t="n">
-        <v>0.6064726947179946</v>
+        <v>0.9998966789667897</v>
       </c>
       <c r="AD200" s="15" t="inlineStr"/>
       <c r="AE200" s="14" t="n">
-        <v>3516560.0</v>
+        <v>560.0</v>
       </c>
       <c r="AF200" s="14" t="inlineStr"/>
       <c r="AG200" s="14" t="inlineStr"/>
@@ -12244,7 +12244,7 @@
       <c r="O201" s="13" t="inlineStr"/>
       <c r="P201" s="13" t="inlineStr"/>
       <c r="Q201" s="14" t="n">
-        <v>7.83E7</v>
+        <v>9.945E7</v>
       </c>
       <c r="R201" s="14" t="inlineStr"/>
       <c r="S201" s="14" t="n">
@@ -12254,10 +12254,10 @@
       <c r="U201" s="14" t="inlineStr"/>
       <c r="V201" s="14" t="inlineStr"/>
       <c r="W201" s="14" t="n">
-        <v>0.0</v>
+        <v>4.87008E7</v>
       </c>
       <c r="X201" s="14" t="n">
-        <v>4.87008E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y201" s="14" t="inlineStr"/>
       <c r="Z201" s="14" t="n">
@@ -12266,11 +12266,11 @@
       <c r="AA201" s="14" t="inlineStr"/>
       <c r="AB201" s="14" t="inlineStr"/>
       <c r="AC201" s="15" t="n">
-        <v>0.6219770114942529</v>
+        <v>0.48970135746606336</v>
       </c>
       <c r="AD201" s="15" t="inlineStr"/>
       <c r="AE201" s="14" t="n">
-        <v>2.95992E7</v>
+        <v>5.07492E7</v>
       </c>
       <c r="AF201" s="14" t="inlineStr"/>
       <c r="AG201" s="14" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       <c r="O202" s="13" t="inlineStr"/>
       <c r="P202" s="13" t="inlineStr"/>
       <c r="Q202" s="14" t="n">
-        <v>5250000.0</v>
+        <v>0.0</v>
       </c>
       <c r="R202" s="14" t="inlineStr"/>
       <c r="S202" s="14" t="n">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="AD202" s="15" t="inlineStr"/>
       <c r="AE202" s="14" t="n">
-        <v>5250000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF202" s="14" t="inlineStr"/>
       <c r="AG202" s="14" t="inlineStr"/>
@@ -12358,7 +12358,7 @@
       <c r="O203" s="13" t="inlineStr"/>
       <c r="P203" s="13" t="inlineStr"/>
       <c r="Q203" s="14" t="n">
-        <v>7.8E7</v>
+        <v>4.68E7</v>
       </c>
       <c r="R203" s="14" t="inlineStr"/>
       <c r="S203" s="14" t="n">
@@ -12371,20 +12371,20 @@
         <v>0.0</v>
       </c>
       <c r="X203" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="Y203" s="14" t="inlineStr"/>
       <c r="Z203" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>7.8E7</v>
+        <v>2.34E7</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12421,7 +12421,7 @@
       <c r="O204" s="13" t="inlineStr"/>
       <c r="P204" s="13" t="inlineStr"/>
       <c r="Q204" s="14" t="n">
-        <v>1.0E7</v>
+        <v>1.23E7</v>
       </c>
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="14" t="n">
@@ -12431,10 +12431,10 @@
       <c r="U204" s="14" t="inlineStr"/>
       <c r="V204" s="14" t="inlineStr"/>
       <c r="W204" s="14" t="n">
-        <v>8928000.0</v>
+        <v>9332000.0</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>404000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
@@ -12443,11 +12443,11 @@
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.9332</v>
+        <v>0.7586991869918699</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>668000.0</v>
+        <v>2968000.0</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12478,7 +12478,7 @@
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>5800000.0</v>
+        <v>7800000.0</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12500,11 +12500,11 @@
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.9820689655172414</v>
+        <v>0.7302564102564103</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>104000.0</v>
+        <v>2104000.0</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12535,7 +12535,7 @@
       <c r="O206" s="13" t="inlineStr"/>
       <c r="P206" s="13" t="inlineStr"/>
       <c r="Q206" s="14" t="n">
-        <v>4200000.0</v>
+        <v>4500000.0</v>
       </c>
       <c r="R206" s="14" t="inlineStr"/>
       <c r="S206" s="14" t="n">
@@ -12545,10 +12545,10 @@
       <c r="U206" s="14" t="inlineStr"/>
       <c r="V206" s="14" t="inlineStr"/>
       <c r="W206" s="14" t="n">
-        <v>3232000.0</v>
+        <v>3636000.0</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>404000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
@@ -12557,11 +12557,11 @@
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.8657142857142858</v>
+        <v>0.808</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>564000.0</v>
+        <v>864000.0</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       <c r="O207" s="13" t="inlineStr"/>
       <c r="P207" s="13" t="inlineStr"/>
       <c r="Q207" s="14" t="n">
-        <v>5.9605E7</v>
+        <v>7.4556E7</v>
       </c>
       <c r="R207" s="14" t="inlineStr"/>
       <c r="S207" s="14" t="n">
@@ -12608,23 +12608,23 @@
       <c r="U207" s="14" t="inlineStr"/>
       <c r="V207" s="14" t="inlineStr"/>
       <c r="W207" s="14" t="n">
-        <v>4.634851E7</v>
+        <v>4.907101E7</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>2722500.0</v>
+        <v>6195000.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>4.907101E7</v>
+        <v>5.526601E7</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.8232700276822414</v>
+        <v>0.7412684425130104</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>1.053399E7</v>
+        <v>1.928999E7</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12655,7 +12655,7 @@
       <c r="O208" s="13" t="inlineStr"/>
       <c r="P208" s="13" t="inlineStr"/>
       <c r="Q208" s="14" t="n">
-        <v>5.9605E7</v>
+        <v>7.4556E7</v>
       </c>
       <c r="R208" s="14" t="inlineStr"/>
       <c r="S208" s="14" t="n">
@@ -12665,23 +12665,23 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>4.634851E7</v>
+        <v>4.907101E7</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>2722500.0</v>
+        <v>6195000.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>4.907101E7</v>
+        <v>5.526601E7</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.8232700276822414</v>
+        <v>0.7412684425130104</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.053399E7</v>
+        <v>1.928999E7</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12718,7 +12718,7 @@
       <c r="O209" s="13" t="inlineStr"/>
       <c r="P209" s="13" t="inlineStr"/>
       <c r="Q209" s="14" t="n">
-        <v>6000000.0</v>
+        <v>1.1E7</v>
       </c>
       <c r="R209" s="14" t="inlineStr"/>
       <c r="S209" s="14" t="n">
@@ -12728,10 +12728,10 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>3257800.0</v>
+        <v>4274800.0</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>1017000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
@@ -12740,11 +12740,11 @@
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.7124666666666667</v>
+        <v>0.3886181818181818</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>1725200.0</v>
+        <v>6725200.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12775,7 +12775,7 @@
       <c r="O210" s="13" t="inlineStr"/>
       <c r="P210" s="13" t="inlineStr"/>
       <c r="Q210" s="14" t="n">
-        <v>4000000.0</v>
+        <v>9000000.0</v>
       </c>
       <c r="R210" s="14" t="inlineStr"/>
       <c r="S210" s="14" t="n">
@@ -12785,10 +12785,10 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>2947800.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>1017000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
@@ -12797,11 +12797,11 @@
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.9912</v>
+        <v>0.44053333333333333</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>35200.0</v>
+        <v>5035200.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12905,10 +12905,10 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>2.346179924E9</v>
+        <v>2.567718192E9</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>2.21538268E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
@@ -13019,10 +13019,10 @@
       <c r="U214" s="14" t="inlineStr"/>
       <c r="V214" s="14" t="inlineStr"/>
       <c r="W214" s="14" t="n">
-        <v>9.3850352E7</v>
+        <v>1.0331888E8</v>
       </c>
       <c r="X214" s="14" t="n">
-        <v>9468528.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
@@ -13190,10 +13190,10 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>1.6603785E9</v>
+        <v>1.844865E9</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
@@ -13247,10 +13247,10 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>0.0</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
@@ -13304,10 +13304,10 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>0.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>4629928.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
@@ -13357,7 +13357,7 @@
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
-        <v>8.4668E8</v>
+        <v>7.00144E8</v>
       </c>
       <c r="R220" s="14" t="inlineStr"/>
       <c r="S220" s="14" t="n">
@@ -13367,23 +13367,23 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>5.87220368E8</v>
+        <v>6.39230607E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>5.2010239E7</v>
+        <v>611800.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>6.39230607E8</v>
+        <v>6.39842407E8</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.7549848903954268</v>
+        <v>0.9138725847825591</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>2.07449393E8</v>
+        <v>6.0301593E7</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13464,7 +13464,7 @@
       <c r="O222" s="13" t="inlineStr"/>
       <c r="P222" s="13" t="inlineStr"/>
       <c r="Q222" s="14" t="n">
-        <v>6.4548E8</v>
+        <v>5.16E8</v>
       </c>
       <c r="R222" s="14" t="inlineStr"/>
       <c r="S222" s="14" t="n">
@@ -13474,10 +13474,10 @@
       <c r="U222" s="14" t="inlineStr"/>
       <c r="V222" s="14" t="inlineStr"/>
       <c r="W222" s="14" t="n">
-        <v>4.30266392E8</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>4.0247519E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
@@ -13486,11 +13486,11 @@
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.7289364674350871</v>
+        <v>0.9118486647286822</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>1.74966089E8</v>
+        <v>4.5486089E7</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13521,7 +13521,7 @@
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
       <c r="Q223" s="14" t="n">
-        <v>6.4548E8</v>
+        <v>5.16E8</v>
       </c>
       <c r="R223" s="14" t="inlineStr"/>
       <c r="S223" s="14" t="n">
@@ -13531,10 +13531,10 @@
       <c r="U223" s="14" t="inlineStr"/>
       <c r="V223" s="14" t="inlineStr"/>
       <c r="W223" s="14" t="n">
-        <v>4.30266392E8</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>4.0247519E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
@@ -13543,11 +13543,11 @@
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.7289364674350871</v>
+        <v>0.9118486647286822</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>1.74966089E8</v>
+        <v>4.5486089E7</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13594,10 +13594,10 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>5219220.0</v>
+        <v>5485232.0</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>266012.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
@@ -13651,10 +13651,10 @@
       <c r="U225" s="14" t="inlineStr"/>
       <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="n">
-        <v>5219220.0</v>
+        <v>5485232.0</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>266012.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
@@ -13704,7 +13704,7 @@
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
       <c r="Q226" s="14" t="n">
-        <v>3.96E7</v>
+        <v>3.3444E7</v>
       </c>
       <c r="R226" s="14" t="inlineStr"/>
       <c r="S226" s="14" t="n">
@@ -13714,23 +13714,23 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>2.94084E7</v>
+        <v>3.021E7</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>801600.0</v>
+        <v>611800.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>3.021E7</v>
+        <v>3.08218E7</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.7628787878787879</v>
+        <v>0.9215943069010883</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>9390000.0</v>
+        <v>2622200.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13761,7 +13761,7 @@
       <c r="O227" s="13" t="inlineStr"/>
       <c r="P227" s="13" t="inlineStr"/>
       <c r="Q227" s="14" t="n">
-        <v>3.96E7</v>
+        <v>3.3444E7</v>
       </c>
       <c r="R227" s="14" t="inlineStr"/>
       <c r="S227" s="14" t="n">
@@ -13771,23 +13771,23 @@
       <c r="U227" s="14" t="inlineStr"/>
       <c r="V227" s="14" t="inlineStr"/>
       <c r="W227" s="14" t="n">
-        <v>2.94084E7</v>
+        <v>3.021E7</v>
       </c>
       <c r="X227" s="14" t="n">
-        <v>801600.0</v>
+        <v>611800.0</v>
       </c>
       <c r="Y227" s="14" t="inlineStr"/>
       <c r="Z227" s="14" t="n">
-        <v>3.021E7</v>
+        <v>3.08218E7</v>
       </c>
       <c r="AA227" s="14" t="inlineStr"/>
       <c r="AB227" s="14" t="inlineStr"/>
       <c r="AC227" s="15" t="n">
-        <v>0.7628787878787879</v>
+        <v>0.9215943069010883</v>
       </c>
       <c r="AD227" s="15" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
-        <v>9390000.0</v>
+        <v>2622200.0</v>
       </c>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
       <c r="Q228" s="14" t="n">
-        <v>1.556E8</v>
+        <v>1.447E8</v>
       </c>
       <c r="R228" s="14" t="inlineStr"/>
       <c r="S228" s="14" t="n">
@@ -13834,10 +13834,10 @@
       <c r="U228" s="14" t="inlineStr"/>
       <c r="V228" s="14" t="inlineStr"/>
       <c r="W228" s="14" t="n">
-        <v>1.22326356E8</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>1.0695108E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
@@ -13846,11 +13846,11 @@
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.8548937275064268</v>
+        <v>0.919291389080857</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>2.2578536E7</v>
+        <v>1.1678536E7</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13881,7 +13881,7 @@
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>1.269E8</v>
+        <v>1.146E8</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13891,10 +13891,10 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>9.518475E7</v>
+        <v>1.044355E8</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>9250750.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
@@ -13903,11 +13903,11 @@
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.8229747832939323</v>
+        <v>0.9113045375218151</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>2.24645E7</v>
+        <v>1.01645E7</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13938,7 +13938,7 @@
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>2.87E7</v>
+        <v>3.01E7</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13948,10 +13948,10 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>2.7141606E7</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>1444358.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
@@ -13960,11 +13960,11 @@
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.9960266202090592</v>
+        <v>0.9496998006644518</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>114036.0</v>
+        <v>1514036.0</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14001,7 +14001,7 @@
       <c r="O231" s="13" t="inlineStr"/>
       <c r="P231" s="13" t="inlineStr"/>
       <c r="Q231" s="14" t="n">
-        <v>9.60035E8</v>
+        <v>1.11442E9</v>
       </c>
       <c r="R231" s="14" t="inlineStr"/>
       <c r="S231" s="14" t="n">
@@ -14011,23 +14011,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>5.60645387E8</v>
+        <v>6.19636199E8</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>5.8990812E7</v>
+        <v>5.4976954E7</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>6.19636199E8</v>
+        <v>6.74613153E8</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.6454308426255293</v>
+        <v>0.6053491080562086</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>3.40398801E8</v>
+        <v>4.39806847E8</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14064,7 +14064,7 @@
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>2.2E8</v>
+        <v>2.3E8</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14077,20 +14077,20 @@
         <v>1.9288E8</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>0.0</v>
+        <v>2.50325E7</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>1.9288E8</v>
+        <v>2.179125E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.8767272727272727</v>
+        <v>0.9474456521739131</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>2.712E7</v>
+        <v>1.20875E7</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14121,7 +14121,7 @@
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>1.7E8</v>
+        <v>1.8E8</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14134,20 +14134,20 @@
         <v>1.5279E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>0.0</v>
+        <v>1.5125E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>1.5279E8</v>
+        <v>1.67915E8</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.8987647058823529</v>
+        <v>0.9328611111111111</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>1.721E7</v>
+        <v>1.2085E7</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14191,20 +14191,20 @@
         <v>4.009E7</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>0.0</v>
+        <v>9907500.0</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>4.009E7</v>
+        <v>4.99975E7</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.8018</v>
+        <v>0.99995</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>9910000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       <c r="O235" s="13" t="inlineStr"/>
       <c r="P235" s="13" t="inlineStr"/>
       <c r="Q235" s="14" t="n">
-        <v>3.526E7</v>
+        <v>3.041E7</v>
       </c>
       <c r="R235" s="14" t="inlineStr"/>
       <c r="S235" s="14" t="n">
@@ -14263,11 +14263,11 @@
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.8623591888825864</v>
+        <v>0.9998942781979612</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>4853215.0</v>
+        <v>3215.0</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14298,7 +14298,7 @@
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
-        <v>3.526E7</v>
+        <v>3.041E7</v>
       </c>
       <c r="R236" s="14" t="inlineStr"/>
       <c r="S236" s="14" t="n">
@@ -14320,11 +14320,11 @@
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.8623591888825864</v>
+        <v>0.9998942781979612</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>4853215.0</v>
+        <v>3215.0</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
@@ -14361,7 +14361,7 @@
       <c r="O237" s="13" t="inlineStr"/>
       <c r="P237" s="13" t="inlineStr"/>
       <c r="Q237" s="14" t="n">
-        <v>3.93715E8</v>
+        <v>3.7109E8</v>
       </c>
       <c r="R237" s="14" t="inlineStr"/>
       <c r="S237" s="14" t="n">
@@ -14371,23 +14371,23 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>1.17911533E8</v>
+        <v>1.28808533E8</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>1.0897E7</v>
+        <v>5413000.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>1.28808533E8</v>
+        <v>1.34221533E8</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.3271618632767357</v>
+        <v>0.36169536500579375</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>2.64906467E8</v>
+        <v>2.36868467E8</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14475,7 +14475,7 @@
       <c r="O239" s="13" t="inlineStr"/>
       <c r="P239" s="13" t="inlineStr"/>
       <c r="Q239" s="14" t="n">
-        <v>2.695E7</v>
+        <v>3.73E7</v>
       </c>
       <c r="R239" s="14" t="inlineStr"/>
       <c r="S239" s="14" t="n">
@@ -14485,10 +14485,10 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>1.2396299E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>8951000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
@@ -14497,11 +14497,11 @@
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.7921075695732839</v>
+        <v>0.5723136461126005</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>5602701.0</v>
+        <v>1.5952701E7</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14646,7 +14646,7 @@
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>2.05735E8</v>
+        <v>1.341E8</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14656,10 +14656,10 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>2475000.0</v>
+        <v>4421000.0</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>1946000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
@@ -14668,11 +14668,11 @@
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.02148880841859674</v>
+        <v>0.03296793437733035</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>2.01314E8</v>
+        <v>1.29679E8</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -15032,7 +15032,7 @@
       <c r="O249" s="13" t="inlineStr"/>
       <c r="P249" s="13" t="inlineStr"/>
       <c r="Q249" s="14" t="n">
-        <v>2.71E7</v>
+        <v>4.21E7</v>
       </c>
       <c r="R249" s="14" t="inlineStr"/>
       <c r="S249" s="14" t="n">
@@ -15054,11 +15054,11 @@
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.5639852398523986</v>
+        <v>0.36304038004750594</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>1.1816E7</v>
+        <v>2.6816E7</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15089,7 +15089,7 @@
       <c r="O250" s="13" t="inlineStr"/>
       <c r="P250" s="13" t="inlineStr"/>
       <c r="Q250" s="14" t="n">
-        <v>6930000.0</v>
+        <v>3.059E7</v>
       </c>
       <c r="R250" s="14" t="inlineStr"/>
       <c r="S250" s="14" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>6930000.0</v>
+        <v>3.059E7</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15330,20 +15330,20 @@
         <v>0.0</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>0.0</v>
+        <v>5413000.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>0.0</v>
+        <v>5413000.0</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.0</v>
+        <v>0.5697894736842105</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>9500000.0</v>
+        <v>4087000.0</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>
@@ -15380,7 +15380,7 @@
       <c r="O255" s="13" t="inlineStr"/>
       <c r="P255" s="13" t="inlineStr"/>
       <c r="Q255" s="14" t="n">
-        <v>2.2996E8</v>
+        <v>3.3E8</v>
       </c>
       <c r="R255" s="14" t="inlineStr"/>
       <c r="S255" s="14" t="n">
@@ -15390,23 +15390,23 @@
       <c r="U255" s="14" t="inlineStr"/>
       <c r="V255" s="14" t="inlineStr"/>
       <c r="W255" s="14" t="n">
-        <v>1.58031069E8</v>
+        <v>2.06124881E8</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>4.8093812E7</v>
+        <v>5396454.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>2.06124881E8</v>
+        <v>2.11521335E8</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.8963510219168551</v>
+        <v>0.6409737424242424</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>2.3835119E7</v>
+        <v>1.18478665E8</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15437,7 +15437,7 @@
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>1.43E7</v>
+        <v>2.257E7</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15459,11 +15459,11 @@
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.9762237762237762</v>
+        <v>0.618520159503766</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>340000.0</v>
+        <v>8610000.0</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15504,23 +15504,23 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>350000.0</v>
+        <v>1287928.0</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>937928.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>1287928.0</v>
+        <v>2487928.0</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.2575856</v>
+        <v>0.4975856</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>3712072.0</v>
+        <v>2512072.0</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15551,7 +15551,7 @@
       <c r="O258" s="13" t="inlineStr"/>
       <c r="P258" s="13" t="inlineStr"/>
       <c r="Q258" s="14" t="n">
-        <v>3.0E7</v>
+        <v>4.5E7</v>
       </c>
       <c r="R258" s="14" t="inlineStr"/>
       <c r="S258" s="14" t="n">
@@ -15561,23 +15561,23 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>2.7531718E7</v>
+        <v>2.8040718E7</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>509000.0</v>
+        <v>1804500.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>2.8040718E7</v>
+        <v>2.9845218E7</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.9346906</v>
+        <v>0.6632270666666666</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>1959282.0</v>
+        <v>1.5154782E7</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15608,7 +15608,7 @@
       <c r="O259" s="13" t="inlineStr"/>
       <c r="P259" s="13" t="inlineStr"/>
       <c r="Q259" s="14" t="n">
-        <v>1.246E8</v>
+        <v>1.6975E8</v>
       </c>
       <c r="R259" s="14" t="inlineStr"/>
       <c r="S259" s="14" t="n">
@@ -15618,23 +15618,23 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>9.4757877E7</v>
+        <v>1.20838496E8</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>2.6080619E7</v>
+        <v>1205000.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>1.20838496E8</v>
+        <v>1.22043496E8</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.9698113643659712</v>
+        <v>0.7189602120765832</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>3761504.0</v>
+        <v>4.7706504E7</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15675,23 +15675,23 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>3229902.0</v>
+        <v>3411992.0</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>182090.0</v>
+        <v>736000.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>3411992.0</v>
+        <v>4147992.0</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.7582204444444445</v>
+        <v>0.921776</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>1088008.0</v>
+        <v>352008.0</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15722,7 +15722,7 @@
       <c r="O261" s="13" t="inlineStr"/>
       <c r="P261" s="13" t="inlineStr"/>
       <c r="Q261" s="14" t="n">
-        <v>1.45E7</v>
+        <v>2.1E7</v>
       </c>
       <c r="R261" s="14" t="inlineStr"/>
       <c r="S261" s="14" t="n">
@@ -15732,10 +15732,10 @@
       <c r="U261" s="14" t="inlineStr"/>
       <c r="V261" s="14" t="inlineStr"/>
       <c r="W261" s="14" t="n">
-        <v>4737535.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="X261" s="14" t="n">
-        <v>9553020.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
@@ -15744,11 +15744,11 @@
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.9855555172413794</v>
+        <v>0.680502619047619</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>209445.0</v>
+        <v>6709445.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15779,7 +15779,7 @@
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>6010000.0</v>
+        <v>9010000.0</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15801,11 +15801,11 @@
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.166398003327787</v>
+        <v>0.11099356270810211</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>5009948.0</v>
+        <v>8009948.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15846,23 +15846,23 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>1358480.0</v>
+        <v>1658480.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>300000.0</v>
+        <v>319926.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>1658480.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.4095012345679012</v>
+        <v>0.4884953086419753</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>2391520.0</v>
+        <v>2071594.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15893,7 +15893,7 @@
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>1.0E7</v>
+        <v>1.2E7</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15903,23 +15903,23 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>8224613.0</v>
+        <v>8319256.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>94643.0</v>
+        <v>131028.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>8319256.0</v>
+        <v>8450284.0</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.8319256</v>
+        <v>0.7041903333333334</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>1680744.0</v>
+        <v>3549716.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -16007,7 +16007,7 @@
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>5000000.0</v>
+        <v>1.562E7</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16017,10 +16017,10 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>1213334.0</v>
+        <v>3760846.0</v>
       </c>
       <c r="X266" s="14" t="n">
-        <v>2547512.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
@@ -16029,11 +16029,11 @@
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.7521692</v>
+        <v>0.24077119078104994</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>1239154.0</v>
+        <v>1.1859154E7</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16121,7 +16121,7 @@
       <c r="O268" s="13" t="inlineStr"/>
       <c r="P268" s="13" t="inlineStr"/>
       <c r="Q268" s="14" t="n">
-        <v>1.0E7</v>
+        <v>1.3E7</v>
       </c>
       <c r="R268" s="14" t="inlineStr"/>
       <c r="S268" s="14" t="n">
@@ -16131,10 +16131,10 @@
       <c r="U268" s="14" t="inlineStr"/>
       <c r="V268" s="14" t="inlineStr"/>
       <c r="W268" s="14" t="n">
-        <v>0.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>7889000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
@@ -16143,11 +16143,11 @@
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.7889</v>
+        <v>0.6068461538461538</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>2111000.0</v>
+        <v>5111000.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16162,29 +16162,23 @@
       <c r="E269" s="2" t="inlineStr"/>
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523132</t>
-          </r>
-        </is>
-      </c>
-      <c r="I269" s="13" t="inlineStr"/>
-      <c r="J269" s="13" t="inlineStr"/>
-      <c r="K269" s="13" t="inlineStr"/>
-      <c r="L269" s="13" t="inlineStr"/>
-      <c r="M269" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N269" s="13" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr"/>
+      <c r="I269" s="2" t="inlineStr"/>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr"/>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
+          </r>
+        </is>
+      </c>
       <c r="O269" s="13" t="inlineStr"/>
       <c r="P269" s="13" t="inlineStr"/>
       <c r="Q269" s="14" t="n">
-        <v>8.11E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R269" s="14" t="inlineStr"/>
       <c r="S269" s="14" t="n">
@@ -16194,23 +16188,23 @@
       <c r="U269" s="14" t="inlineStr"/>
       <c r="V269" s="14" t="inlineStr"/>
       <c r="W269" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>0.0</v>
       </c>
       <c r="X269" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.7572872996300863</v>
+        <v>0.0</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>1.9684E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16234,14 +16228,14 @@
       <c r="N270" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
+            <t xml:space="preserve">000305. Pemeliharaan TV</t>
           </r>
         </is>
       </c>
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>3.91E7</v>
+        <v>1500000.0</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16251,23 +16245,23 @@
       <c r="U270" s="14" t="inlineStr"/>
       <c r="V270" s="14" t="inlineStr"/>
       <c r="W270" s="14" t="n">
-        <v>3.909E7</v>
+        <v>0.0</v>
       </c>
       <c r="X270" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>3.909E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.9997442455242966</v>
+        <v>0.0</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>10000.0</v>
+        <v>1500000.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16282,23 +16276,29 @@
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr"/>
-      <c r="I271" s="2" t="inlineStr"/>
-      <c r="J271" s="2" t="inlineStr"/>
-      <c r="K271" s="2" t="inlineStr"/>
-      <c r="L271" s="2" t="inlineStr"/>
-      <c r="M271" s="2" t="inlineStr"/>
-      <c r="N271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H271" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523132</t>
+          </r>
+        </is>
+      </c>
+      <c r="I271" s="13" t="inlineStr"/>
+      <c r="J271" s="13" t="inlineStr"/>
+      <c r="K271" s="13" t="inlineStr"/>
+      <c r="L271" s="13" t="inlineStr"/>
+      <c r="M271" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N271" s="13" t="inlineStr"/>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>3.0E7</v>
+        <v>1.5292E8</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16308,23 +16308,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>1.155E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="X271" s="14" t="n">
-        <v>0.0</v>
+        <v>1.9135E7</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>1.155E7</v>
+        <v>8.0551E7</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.385</v>
+        <v>0.5267525503531258</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>1.845E7</v>
+        <v>7.2369E7</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16348,14 +16348,14 @@
       <c r="N272" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>1.2E7</v>
+        <v>6.216E7</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16365,23 +16365,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="X272" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.898</v>
+        <v>0.6288610038610039</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>1224000.0</v>
+        <v>2.307E7</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16394,31 +16394,25 @@
       <c r="C273" s="2" t="inlineStr"/>
       <c r="D273" s="2" t="inlineStr"/>
       <c r="E273" s="2" t="inlineStr"/>
-      <c r="F273" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DD</t>
-          </r>
-        </is>
-      </c>
-      <c r="G273" s="13" t="inlineStr"/>
-      <c r="H273" s="13" t="inlineStr"/>
-      <c r="I273" s="13" t="inlineStr"/>
-      <c r="J273" s="13" t="inlineStr"/>
-      <c r="K273" s="13" t="inlineStr"/>
-      <c r="L273" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M273" s="13" t="inlineStr"/>
-      <c r="N273" s="13" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr"/>
+      <c r="I273" s="2" t="inlineStr"/>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr"/>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
+          </r>
+        </is>
+      </c>
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>3.07E7</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16428,23 +16422,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>1.0101E8</v>
+        <v>1.155E7</v>
       </c>
       <c r="X273" s="14" t="n">
-        <v>9910000.0</v>
+        <v>1.9135E7</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>1.1092E8</v>
+        <v>3.0685E7</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.8391587229535482</v>
+        <v>0.9995114006514658</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>2.126E7</v>
+        <v>15000.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16459,29 +16453,23 @@
       <c r="E274" s="2" t="inlineStr"/>
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521115</t>
-          </r>
-        </is>
-      </c>
-      <c r="I274" s="13" t="inlineStr"/>
-      <c r="J274" s="13" t="inlineStr"/>
-      <c r="K274" s="13" t="inlineStr"/>
-      <c r="L274" s="13" t="inlineStr"/>
-      <c r="M274" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
-          </r>
-        </is>
-      </c>
-      <c r="N274" s="13" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr"/>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr"/>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+          </r>
+        </is>
+      </c>
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>1.2468E8</v>
+        <v>6.006E7</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16491,23 +16479,23 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>9.351E7</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X274" s="14" t="n">
-        <v>9910000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.0342E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.8294834777029195</v>
+        <v>0.17942057942057943</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>2.126E7</v>
+        <v>4.9284E7</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16564,25 +16552,31 @@
       <c r="C276" s="2" t="inlineStr"/>
       <c r="D276" s="2" t="inlineStr"/>
       <c r="E276" s="2" t="inlineStr"/>
-      <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr"/>
-      <c r="I276" s="2" t="inlineStr"/>
-      <c r="J276" s="2" t="inlineStr"/>
-      <c r="K276" s="2" t="inlineStr"/>
-      <c r="L276" s="2" t="inlineStr"/>
-      <c r="M276" s="2" t="inlineStr"/>
-      <c r="N276" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
-          </r>
-        </is>
-      </c>
+      <c r="F276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DD</t>
+          </r>
+        </is>
+      </c>
+      <c r="G276" s="13" t="inlineStr"/>
+      <c r="H276" s="13" t="inlineStr"/>
+      <c r="I276" s="13" t="inlineStr"/>
+      <c r="J276" s="13" t="inlineStr"/>
+      <c r="K276" s="13" t="inlineStr"/>
+      <c r="L276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M276" s="13" t="inlineStr"/>
+      <c r="N276" s="13" t="inlineStr"/>
       <c r="O276" s="13" t="inlineStr"/>
       <c r="P276" s="13" t="inlineStr"/>
       <c r="Q276" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.3218E8</v>
       </c>
       <c r="R276" s="14" t="inlineStr"/>
       <c r="S276" s="14" t="n">
@@ -16592,23 +16586,23 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>2.295E7</v>
+        <v>1.1092E8</v>
       </c>
       <c r="X276" s="14" t="n">
-        <v>2550000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>2.55E7</v>
+        <v>1.1092E8</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8391587229535482</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>5100000.0</v>
+        <v>2.126E7</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
@@ -16623,23 +16617,29 @@
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="2" t="inlineStr"/>
-      <c r="J277" s="2" t="inlineStr"/>
-      <c r="K277" s="2" t="inlineStr"/>
-      <c r="L277" s="2" t="inlineStr"/>
-      <c r="M277" s="2" t="inlineStr"/>
-      <c r="N277" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
-          </r>
-        </is>
-      </c>
+      <c r="H277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521115</t>
+          </r>
+        </is>
+      </c>
+      <c r="I277" s="13" t="inlineStr"/>
+      <c r="J277" s="13" t="inlineStr"/>
+      <c r="K277" s="13" t="inlineStr"/>
+      <c r="L277" s="13" t="inlineStr"/>
+      <c r="M277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+          </r>
+        </is>
+      </c>
+      <c r="N277" s="13" t="inlineStr"/>
       <c r="O277" s="13" t="inlineStr"/>
       <c r="P277" s="13" t="inlineStr"/>
       <c r="Q277" s="14" t="n">
-        <v>2.976E7</v>
+        <v>1.2468E8</v>
       </c>
       <c r="R277" s="14" t="inlineStr"/>
       <c r="S277" s="14" t="n">
@@ -16649,30 +16649,30 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>2.232E7</v>
+        <v>1.0342E8</v>
       </c>
       <c r="X277" s="14" t="n">
-        <v>2480000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>2.48E7</v>
+        <v>1.0342E8</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8294834777029195</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>4960000.0</v>
+        <v>2.126E7</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
       <c r="AH277" s="14" t="inlineStr"/>
       <c r="AI277" s="14" t="inlineStr"/>
     </row>
-    <row r="278" customHeight="1" ht="18">
+    <row r="278" customHeight="1" ht="15">
       <c r="A278" s="2" t="inlineStr"/>
       <c r="B278" s="2" t="inlineStr"/>
       <c r="C278" s="2" t="inlineStr"/>
@@ -16689,14 +16689,14 @@
       <c r="N278" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
           </r>
         </is>
       </c>
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>1.476E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16706,14 +16706,14 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>1.107E7</v>
+        <v>2.55E7</v>
       </c>
       <c r="X278" s="14" t="n">
-        <v>1230000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>1.23E7</v>
+        <v>2.55E7</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>2460000.0</v>
+        <v>5100000.0</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
@@ -16746,14 +16746,14 @@
       <c r="N279" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
+            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
           </r>
         </is>
       </c>
       <c r="O279" s="13" t="inlineStr"/>
       <c r="P279" s="13" t="inlineStr"/>
       <c r="Q279" s="14" t="n">
-        <v>1.284E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="R279" s="14" t="inlineStr"/>
       <c r="S279" s="14" t="n">
@@ -16763,14 +16763,14 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>9630000.0</v>
+        <v>2.48E7</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>1070000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>1.07E7</v>
+        <v>2.48E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
@@ -16779,14 +16779,14 @@
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>2140000.0</v>
+        <v>4960000.0</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
       <c r="AH279" s="14" t="inlineStr"/>
       <c r="AI279" s="14" t="inlineStr"/>
     </row>
-    <row r="280" customHeight="1" ht="15">
+    <row r="280" customHeight="1" ht="18">
       <c r="A280" s="2" t="inlineStr"/>
       <c r="B280" s="2" t="inlineStr"/>
       <c r="C280" s="2" t="inlineStr"/>
@@ -16803,14 +16803,14 @@
       <c r="N280" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
+            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
           </r>
         </is>
       </c>
       <c r="O280" s="13" t="inlineStr"/>
       <c r="P280" s="13" t="inlineStr"/>
       <c r="Q280" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="R280" s="14" t="inlineStr"/>
       <c r="S280" s="14" t="n">
@@ -16820,14 +16820,14 @@
       <c r="U280" s="14" t="inlineStr"/>
       <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="n">
-        <v>2.16E7</v>
+        <v>1.23E7</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>2400000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>2.4E7</v>
+        <v>1.23E7</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
-        <v>4800000.0</v>
+        <v>2460000.0</v>
       </c>
       <c r="AF280" s="14" t="inlineStr"/>
       <c r="AG280" s="14" t="inlineStr"/>
@@ -16860,14 +16860,14 @@
       <c r="N281" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
           </r>
         </is>
       </c>
       <c r="O281" s="13" t="inlineStr"/>
       <c r="P281" s="13" t="inlineStr"/>
       <c r="Q281" s="14" t="n">
-        <v>3600000.0</v>
+        <v>1.284E7</v>
       </c>
       <c r="R281" s="14" t="inlineStr"/>
       <c r="S281" s="14" t="n">
@@ -16877,30 +16877,30 @@
       <c r="U281" s="14" t="inlineStr"/>
       <c r="V281" s="14" t="inlineStr"/>
       <c r="W281" s="14" t="n">
-        <v>2700000.0</v>
+        <v>1.07E7</v>
       </c>
       <c r="X281" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y281" s="14" t="inlineStr"/>
       <c r="Z281" s="14" t="n">
-        <v>2700000.0</v>
+        <v>1.07E7</v>
       </c>
       <c r="AA281" s="14" t="inlineStr"/>
       <c r="AB281" s="14" t="inlineStr"/>
       <c r="AC281" s="15" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AD281" s="15" t="inlineStr"/>
       <c r="AE281" s="14" t="n">
-        <v>900000.0</v>
+        <v>2140000.0</v>
       </c>
       <c r="AF281" s="14" t="inlineStr"/>
       <c r="AG281" s="14" t="inlineStr"/>
       <c r="AH281" s="14" t="inlineStr"/>
       <c r="AI281" s="14" t="inlineStr"/>
     </row>
-    <row r="282" customHeight="1" ht="18">
+    <row r="282" customHeight="1" ht="15">
       <c r="A282" s="2" t="inlineStr"/>
       <c r="B282" s="2" t="inlineStr"/>
       <c r="C282" s="2" t="inlineStr"/>
@@ -16917,14 +16917,14 @@
       <c r="N282" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
           </r>
         </is>
       </c>
       <c r="O282" s="13" t="inlineStr"/>
       <c r="P282" s="13" t="inlineStr"/>
       <c r="Q282" s="14" t="n">
-        <v>4320000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="R282" s="14" t="inlineStr"/>
       <c r="S282" s="14" t="n">
@@ -16934,23 +16934,23 @@
       <c r="U282" s="14" t="inlineStr"/>
       <c r="V282" s="14" t="inlineStr"/>
       <c r="W282" s="14" t="n">
-        <v>3240000.0</v>
+        <v>2.4E7</v>
       </c>
       <c r="X282" s="14" t="n">
-        <v>180000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>3420000.0</v>
+        <v>2.4E7</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
       <c r="AC282" s="15" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AD282" s="15" t="inlineStr"/>
       <c r="AE282" s="14" t="n">
-        <v>900000.0</v>
+        <v>4800000.0</v>
       </c>
       <c r="AF282" s="14" t="inlineStr"/>
       <c r="AG282" s="14" t="inlineStr"/>
@@ -16965,29 +16965,23 @@
       <c r="E283" s="2" t="inlineStr"/>
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I283" s="13" t="inlineStr"/>
-      <c r="J283" s="13" t="inlineStr"/>
-      <c r="K283" s="13" t="inlineStr"/>
-      <c r="L283" s="13" t="inlineStr"/>
-      <c r="M283" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N283" s="13" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr"/>
+      <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr"/>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+          </r>
+        </is>
+      </c>
       <c r="O283" s="13" t="inlineStr"/>
       <c r="P283" s="13" t="inlineStr"/>
       <c r="Q283" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="R283" s="14" t="inlineStr"/>
       <c r="S283" s="14" t="n">
@@ -16997,30 +16991,30 @@
       <c r="U283" s="14" t="inlineStr"/>
       <c r="V283" s="14" t="inlineStr"/>
       <c r="W283" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="X283" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y283" s="14" t="inlineStr"/>
       <c r="Z283" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="AA283" s="14" t="inlineStr"/>
       <c r="AB283" s="14" t="inlineStr"/>
       <c r="AC283" s="15" t="n">
-        <v>1.0</v>
+        <v>0.75</v>
       </c>
       <c r="AD283" s="15" t="inlineStr"/>
       <c r="AE283" s="14" t="n">
-        <v>0.0</v>
+        <v>900000.0</v>
       </c>
       <c r="AF283" s="14" t="inlineStr"/>
       <c r="AG283" s="14" t="inlineStr"/>
       <c r="AH283" s="14" t="inlineStr"/>
       <c r="AI283" s="14" t="inlineStr"/>
     </row>
-    <row r="284" customHeight="1" ht="15">
+    <row r="284" customHeight="1" ht="18">
       <c r="A284" s="2" t="inlineStr"/>
       <c r="B284" s="2" t="inlineStr"/>
       <c r="C284" s="2" t="inlineStr"/>
@@ -17037,14 +17031,14 @@
       <c r="N284" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
           </r>
         </is>
       </c>
       <c r="O284" s="13" t="inlineStr"/>
       <c r="P284" s="13" t="inlineStr"/>
       <c r="Q284" s="14" t="n">
-        <v>7500000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="R284" s="14" t="inlineStr"/>
       <c r="S284" s="14" t="n">
@@ -17054,23 +17048,23 @@
       <c r="U284" s="14" t="inlineStr"/>
       <c r="V284" s="14" t="inlineStr"/>
       <c r="W284" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3420000.0</v>
       </c>
       <c r="X284" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3420000.0</v>
       </c>
       <c r="AA284" s="14" t="inlineStr"/>
       <c r="AB284" s="14" t="inlineStr"/>
       <c r="AC284" s="15" t="n">
-        <v>1.0</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="AD284" s="15" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
-        <v>0.0</v>
+        <v>900000.0</v>
       </c>
       <c r="AF284" s="14" t="inlineStr"/>
       <c r="AG284" s="14" t="inlineStr"/>
@@ -17080,317 +17074,311 @@
     <row r="285" customHeight="1" ht="15">
       <c r="A285" s="2" t="inlineStr"/>
       <c r="B285" s="2" t="inlineStr"/>
-      <c r="C285" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D285" s="16" t="inlineStr"/>
-      <c r="E285" s="16" t="inlineStr"/>
-      <c r="F285" s="16" t="inlineStr"/>
-      <c r="G285" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H285" s="16" t="inlineStr"/>
-      <c r="I285" s="16" t="inlineStr"/>
-      <c r="J285" s="16" t="inlineStr"/>
-      <c r="K285" s="16" t="inlineStr"/>
-      <c r="L285" s="16" t="inlineStr"/>
-      <c r="M285" s="16" t="inlineStr"/>
-      <c r="N285" s="16" t="inlineStr"/>
-      <c r="O285" s="16" t="inlineStr"/>
-      <c r="P285" s="16" t="inlineStr"/>
-      <c r="Q285" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R285" s="17" t="inlineStr"/>
-      <c r="S285" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T285" s="17" t="inlineStr"/>
-      <c r="U285" s="17" t="inlineStr"/>
-      <c r="V285" s="17" t="inlineStr"/>
-      <c r="W285" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X285" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y285" s="17" t="inlineStr"/>
-      <c r="Z285" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA285" s="17" t="inlineStr"/>
-      <c r="AB285" s="17" t="inlineStr"/>
-      <c r="AC285" s="18" t="n">
+      <c r="C285" s="2" t="inlineStr"/>
+      <c r="D285" s="2" t="inlineStr"/>
+      <c r="E285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I285" s="13" t="inlineStr"/>
+      <c r="J285" s="13" t="inlineStr"/>
+      <c r="K285" s="13" t="inlineStr"/>
+      <c r="L285" s="13" t="inlineStr"/>
+      <c r="M285" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N285" s="13" t="inlineStr"/>
+      <c r="O285" s="13" t="inlineStr"/>
+      <c r="P285" s="13" t="inlineStr"/>
+      <c r="Q285" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R285" s="14" t="inlineStr"/>
+      <c r="S285" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T285" s="14" t="inlineStr"/>
+      <c r="U285" s="14" t="inlineStr"/>
+      <c r="V285" s="14" t="inlineStr"/>
+      <c r="W285" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X285" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y285" s="14" t="inlineStr"/>
+      <c r="Z285" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA285" s="14" t="inlineStr"/>
+      <c r="AB285" s="14" t="inlineStr"/>
+      <c r="AC285" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD285" s="18" t="inlineStr"/>
-      <c r="AE285" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF285" s="17" t="inlineStr"/>
-      <c r="AG285" s="17" t="inlineStr"/>
-      <c r="AH285" s="17" t="inlineStr"/>
-      <c r="AI285" s="17" t="inlineStr"/>
+      <c r="AD285" s="15" t="inlineStr"/>
+      <c r="AE285" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF285" s="14" t="inlineStr"/>
+      <c r="AG285" s="14" t="inlineStr"/>
+      <c r="AH285" s="14" t="inlineStr"/>
+      <c r="AI285" s="14" t="inlineStr"/>
     </row>
     <row r="286" customHeight="1" ht="15">
       <c r="A286" s="2" t="inlineStr"/>
       <c r="B286" s="2" t="inlineStr"/>
-      <c r="C286" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D286" s="28" t="inlineStr"/>
-      <c r="E286" s="28" t="inlineStr"/>
-      <c r="F286" s="28" t="inlineStr"/>
-      <c r="G286" s="28" t="inlineStr"/>
-      <c r="H286" s="28" t="inlineStr"/>
-      <c r="I286" s="28" t="inlineStr"/>
-      <c r="J286" s="28" t="inlineStr"/>
-      <c r="K286" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L286" s="20" t="inlineStr"/>
-      <c r="M286" s="20" t="inlineStr"/>
-      <c r="N286" s="20" t="inlineStr"/>
-      <c r="O286" s="20" t="inlineStr"/>
-      <c r="P286" s="20" t="inlineStr"/>
-      <c r="Q286" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R286" s="21" t="inlineStr"/>
-      <c r="S286" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T286" s="21" t="inlineStr"/>
-      <c r="U286" s="21" t="inlineStr"/>
-      <c r="V286" s="21" t="inlineStr"/>
-      <c r="W286" s="22" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X286" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y286" s="22" t="inlineStr"/>
-      <c r="Z286" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA286" s="21" t="inlineStr"/>
-      <c r="AB286" s="21" t="inlineStr"/>
-      <c r="AC286" s="23" t="n">
+      <c r="C286" s="2" t="inlineStr"/>
+      <c r="D286" s="2" t="inlineStr"/>
+      <c r="E286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr"/>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr"/>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="O286" s="13" t="inlineStr"/>
+      <c r="P286" s="13" t="inlineStr"/>
+      <c r="Q286" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R286" s="14" t="inlineStr"/>
+      <c r="S286" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T286" s="14" t="inlineStr"/>
+      <c r="U286" s="14" t="inlineStr"/>
+      <c r="V286" s="14" t="inlineStr"/>
+      <c r="W286" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X286" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y286" s="14" t="inlineStr"/>
+      <c r="Z286" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA286" s="14" t="inlineStr"/>
+      <c r="AB286" s="14" t="inlineStr"/>
+      <c r="AC286" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD286" s="23" t="inlineStr"/>
-      <c r="AE286" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF286" s="21" t="inlineStr"/>
-      <c r="AG286" s="21" t="inlineStr"/>
-      <c r="AH286" s="21" t="inlineStr"/>
-      <c r="AI286" s="21" t="inlineStr"/>
+      <c r="AD286" s="15" t="inlineStr"/>
+      <c r="AE286" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF286" s="14" t="inlineStr"/>
+      <c r="AG286" s="14" t="inlineStr"/>
+      <c r="AH286" s="14" t="inlineStr"/>
+      <c r="AI286" s="14" t="inlineStr"/>
     </row>
     <row r="287" customHeight="1" ht="15">
       <c r="A287" s="2" t="inlineStr"/>
       <c r="B287" s="2" t="inlineStr"/>
-      <c r="C287" s="2" t="inlineStr"/>
-      <c r="D287" s="2" t="inlineStr"/>
-      <c r="E287" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F287" s="24" t="inlineStr"/>
-      <c r="G287" s="24" t="inlineStr"/>
-      <c r="H287" s="24" t="inlineStr"/>
-      <c r="I287" s="24" t="inlineStr"/>
-      <c r="J287" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K287" s="24" t="inlineStr"/>
-      <c r="L287" s="24" t="inlineStr"/>
-      <c r="M287" s="24" t="inlineStr"/>
-      <c r="N287" s="24" t="inlineStr"/>
-      <c r="O287" s="24" t="inlineStr"/>
-      <c r="P287" s="24" t="inlineStr"/>
-      <c r="Q287" s="25" t="n">
+      <c r="C287" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D287" s="16" t="inlineStr"/>
+      <c r="E287" s="16" t="inlineStr"/>
+      <c r="F287" s="16" t="inlineStr"/>
+      <c r="G287" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H287" s="16" t="inlineStr"/>
+      <c r="I287" s="16" t="inlineStr"/>
+      <c r="J287" s="16" t="inlineStr"/>
+      <c r="K287" s="16" t="inlineStr"/>
+      <c r="L287" s="16" t="inlineStr"/>
+      <c r="M287" s="16" t="inlineStr"/>
+      <c r="N287" s="16" t="inlineStr"/>
+      <c r="O287" s="16" t="inlineStr"/>
+      <c r="P287" s="16" t="inlineStr"/>
+      <c r="Q287" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R287" s="25" t="inlineStr"/>
-      <c r="S287" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T287" s="25" t="inlineStr"/>
-      <c r="U287" s="25" t="inlineStr"/>
-      <c r="V287" s="25" t="inlineStr"/>
-      <c r="W287" s="25" t="n">
+      <c r="R287" s="17" t="inlineStr"/>
+      <c r="S287" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T287" s="17" t="inlineStr"/>
+      <c r="U287" s="17" t="inlineStr"/>
+      <c r="V287" s="17" t="inlineStr"/>
+      <c r="W287" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X287" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y287" s="25" t="inlineStr"/>
-      <c r="Z287" s="25" t="n">
+      <c r="X287" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y287" s="17" t="inlineStr"/>
+      <c r="Z287" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA287" s="25" t="inlineStr"/>
-      <c r="AB287" s="25" t="inlineStr"/>
-      <c r="AC287" s="26" t="n">
+      <c r="AA287" s="17" t="inlineStr"/>
+      <c r="AB287" s="17" t="inlineStr"/>
+      <c r="AC287" s="18" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD287" s="26" t="inlineStr"/>
-      <c r="AE287" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF287" s="25" t="inlineStr"/>
-      <c r="AG287" s="25" t="inlineStr"/>
-      <c r="AH287" s="25" t="inlineStr"/>
-      <c r="AI287" s="25" t="inlineStr"/>
+      <c r="AD287" s="18" t="inlineStr"/>
+      <c r="AE287" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF287" s="17" t="inlineStr"/>
+      <c r="AG287" s="17" t="inlineStr"/>
+      <c r="AH287" s="17" t="inlineStr"/>
+      <c r="AI287" s="17" t="inlineStr"/>
     </row>
     <row r="288" customHeight="1" ht="15">
       <c r="A288" s="2" t="inlineStr"/>
       <c r="B288" s="2" t="inlineStr"/>
-      <c r="C288" s="2" t="inlineStr"/>
-      <c r="D288" s="2" t="inlineStr"/>
-      <c r="E288" s="2" t="inlineStr"/>
-      <c r="F288" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G288" s="13" t="inlineStr"/>
-      <c r="H288" s="13" t="inlineStr"/>
-      <c r="I288" s="13" t="inlineStr"/>
-      <c r="J288" s="13" t="inlineStr"/>
-      <c r="K288" s="13" t="inlineStr"/>
-      <c r="L288" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M288" s="13" t="inlineStr"/>
-      <c r="N288" s="13" t="inlineStr"/>
-      <c r="O288" s="13" t="inlineStr"/>
-      <c r="P288" s="13" t="inlineStr"/>
-      <c r="Q288" s="14" t="n">
+      <c r="C288" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D288" s="28" t="inlineStr"/>
+      <c r="E288" s="28" t="inlineStr"/>
+      <c r="F288" s="28" t="inlineStr"/>
+      <c r="G288" s="28" t="inlineStr"/>
+      <c r="H288" s="28" t="inlineStr"/>
+      <c r="I288" s="28" t="inlineStr"/>
+      <c r="J288" s="28" t="inlineStr"/>
+      <c r="K288" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L288" s="20" t="inlineStr"/>
+      <c r="M288" s="20" t="inlineStr"/>
+      <c r="N288" s="20" t="inlineStr"/>
+      <c r="O288" s="20" t="inlineStr"/>
+      <c r="P288" s="20" t="inlineStr"/>
+      <c r="Q288" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R288" s="14" t="inlineStr"/>
-      <c r="S288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T288" s="14" t="inlineStr"/>
-      <c r="U288" s="14" t="inlineStr"/>
-      <c r="V288" s="14" t="inlineStr"/>
-      <c r="W288" s="14" t="n">
+      <c r="R288" s="21" t="inlineStr"/>
+      <c r="S288" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T288" s="21" t="inlineStr"/>
+      <c r="U288" s="21" t="inlineStr"/>
+      <c r="V288" s="21" t="inlineStr"/>
+      <c r="W288" s="22" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y288" s="14" t="inlineStr"/>
-      <c r="Z288" s="14" t="n">
+      <c r="X288" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y288" s="22" t="inlineStr"/>
+      <c r="Z288" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA288" s="14" t="inlineStr"/>
-      <c r="AB288" s="14" t="inlineStr"/>
-      <c r="AC288" s="15" t="n">
+      <c r="AA288" s="21" t="inlineStr"/>
+      <c r="AB288" s="21" t="inlineStr"/>
+      <c r="AC288" s="23" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD288" s="15" t="inlineStr"/>
-      <c r="AE288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF288" s="14" t="inlineStr"/>
-      <c r="AG288" s="14" t="inlineStr"/>
-      <c r="AH288" s="14" t="inlineStr"/>
-      <c r="AI288" s="14" t="inlineStr"/>
+      <c r="AD288" s="23" t="inlineStr"/>
+      <c r="AE288" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF288" s="21" t="inlineStr"/>
+      <c r="AG288" s="21" t="inlineStr"/>
+      <c r="AH288" s="21" t="inlineStr"/>
+      <c r="AI288" s="21" t="inlineStr"/>
     </row>
     <row r="289" customHeight="1" ht="15">
       <c r="A289" s="2" t="inlineStr"/>
       <c r="B289" s="2" t="inlineStr"/>
       <c r="C289" s="2" t="inlineStr"/>
       <c r="D289" s="2" t="inlineStr"/>
-      <c r="E289" s="2" t="inlineStr"/>
-      <c r="F289" s="2" t="inlineStr"/>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">524111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I289" s="13" t="inlineStr"/>
-      <c r="J289" s="13" t="inlineStr"/>
-      <c r="K289" s="13" t="inlineStr"/>
-      <c r="L289" s="13" t="inlineStr"/>
-      <c r="M289" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="N289" s="13" t="inlineStr"/>
-      <c r="O289" s="13" t="inlineStr"/>
-      <c r="P289" s="13" t="inlineStr"/>
-      <c r="Q289" s="14" t="n">
+      <c r="E289" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F289" s="24" t="inlineStr"/>
+      <c r="G289" s="24" t="inlineStr"/>
+      <c r="H289" s="24" t="inlineStr"/>
+      <c r="I289" s="24" t="inlineStr"/>
+      <c r="J289" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K289" s="24" t="inlineStr"/>
+      <c r="L289" s="24" t="inlineStr"/>
+      <c r="M289" s="24" t="inlineStr"/>
+      <c r="N289" s="24" t="inlineStr"/>
+      <c r="O289" s="24" t="inlineStr"/>
+      <c r="P289" s="24" t="inlineStr"/>
+      <c r="Q289" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R289" s="14" t="inlineStr"/>
-      <c r="S289" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T289" s="14" t="inlineStr"/>
-      <c r="U289" s="14" t="inlineStr"/>
-      <c r="V289" s="14" t="inlineStr"/>
-      <c r="W289" s="14" t="n">
+      <c r="R289" s="25" t="inlineStr"/>
+      <c r="S289" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T289" s="25" t="inlineStr"/>
+      <c r="U289" s="25" t="inlineStr"/>
+      <c r="V289" s="25" t="inlineStr"/>
+      <c r="W289" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X289" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y289" s="14" t="inlineStr"/>
-      <c r="Z289" s="14" t="n">
+      <c r="X289" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y289" s="25" t="inlineStr"/>
+      <c r="Z289" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA289" s="14" t="inlineStr"/>
-      <c r="AB289" s="14" t="inlineStr"/>
-      <c r="AC289" s="15" t="n">
+      <c r="AA289" s="25" t="inlineStr"/>
+      <c r="AB289" s="25" t="inlineStr"/>
+      <c r="AC289" s="26" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD289" s="15" t="inlineStr"/>
-      <c r="AE289" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF289" s="14" t="inlineStr"/>
-      <c r="AG289" s="14" t="inlineStr"/>
-      <c r="AH289" s="14" t="inlineStr"/>
-      <c r="AI289" s="14" t="inlineStr"/>
+      <c r="AD289" s="26" t="inlineStr"/>
+      <c r="AE289" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF289" s="25" t="inlineStr"/>
+      <c r="AG289" s="25" t="inlineStr"/>
+      <c r="AH289" s="25" t="inlineStr"/>
+      <c r="AI289" s="25" t="inlineStr"/>
     </row>
     <row r="290" customHeight="1" ht="15">
       <c r="A290" s="2" t="inlineStr"/>
@@ -17398,21 +17386,27 @@
       <c r="C290" s="2" t="inlineStr"/>
       <c r="D290" s="2" t="inlineStr"/>
       <c r="E290" s="2" t="inlineStr"/>
-      <c r="F290" s="2" t="inlineStr"/>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr"/>
-      <c r="I290" s="2" t="inlineStr"/>
-      <c r="J290" s="2" t="inlineStr"/>
-      <c r="K290" s="2" t="inlineStr"/>
-      <c r="L290" s="2" t="inlineStr"/>
-      <c r="M290" s="2" t="inlineStr"/>
-      <c r="N290" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000231. Uang Harian</t>
-          </r>
-        </is>
-      </c>
+      <c r="F290" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G290" s="13" t="inlineStr"/>
+      <c r="H290" s="13" t="inlineStr"/>
+      <c r="I290" s="13" t="inlineStr"/>
+      <c r="J290" s="13" t="inlineStr"/>
+      <c r="K290" s="13" t="inlineStr"/>
+      <c r="L290" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M290" s="13" t="inlineStr"/>
+      <c r="N290" s="13" t="inlineStr"/>
       <c r="O290" s="13" t="inlineStr"/>
       <c r="P290" s="13" t="inlineStr"/>
       <c r="Q290" s="14" t="n">
@@ -17449,9 +17443,129 @@
       <c r="AH290" s="14" t="inlineStr"/>
       <c r="AI290" s="14" t="inlineStr"/>
     </row>
-    <row r="291" customHeight="1" ht="24">
+    <row r="291" customHeight="1" ht="15">
       <c r="A291" s="2" t="inlineStr"/>
-      <c r="B291" s="27" t="inlineStr">
+      <c r="B291" s="2" t="inlineStr"/>
+      <c r="C291" s="2" t="inlineStr"/>
+      <c r="D291" s="2" t="inlineStr"/>
+      <c r="E291" s="2" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I291" s="13" t="inlineStr"/>
+      <c r="J291" s="13" t="inlineStr"/>
+      <c r="K291" s="13" t="inlineStr"/>
+      <c r="L291" s="13" t="inlineStr"/>
+      <c r="M291" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N291" s="13" t="inlineStr"/>
+      <c r="O291" s="13" t="inlineStr"/>
+      <c r="P291" s="13" t="inlineStr"/>
+      <c r="Q291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R291" s="14" t="inlineStr"/>
+      <c r="S291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T291" s="14" t="inlineStr"/>
+      <c r="U291" s="14" t="inlineStr"/>
+      <c r="V291" s="14" t="inlineStr"/>
+      <c r="W291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y291" s="14" t="inlineStr"/>
+      <c r="Z291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA291" s="14" t="inlineStr"/>
+      <c r="AB291" s="14" t="inlineStr"/>
+      <c r="AC291" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD291" s="15" t="inlineStr"/>
+      <c r="AE291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF291" s="14" t="inlineStr"/>
+      <c r="AG291" s="14" t="inlineStr"/>
+      <c r="AH291" s="14" t="inlineStr"/>
+      <c r="AI291" s="14" t="inlineStr"/>
+    </row>
+    <row r="292" customHeight="1" ht="15">
+      <c r="A292" s="2" t="inlineStr"/>
+      <c r="B292" s="2" t="inlineStr"/>
+      <c r="C292" s="2" t="inlineStr"/>
+      <c r="D292" s="2" t="inlineStr"/>
+      <c r="E292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="2" t="inlineStr"/>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr"/>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000231. Uang Harian</t>
+          </r>
+        </is>
+      </c>
+      <c r="O292" s="13" t="inlineStr"/>
+      <c r="P292" s="13" t="inlineStr"/>
+      <c r="Q292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R292" s="14" t="inlineStr"/>
+      <c r="S292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T292" s="14" t="inlineStr"/>
+      <c r="U292" s="14" t="inlineStr"/>
+      <c r="V292" s="14" t="inlineStr"/>
+      <c r="W292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y292" s="14" t="inlineStr"/>
+      <c r="Z292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA292" s="14" t="inlineStr"/>
+      <c r="AB292" s="14" t="inlineStr"/>
+      <c r="AC292" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD292" s="15" t="inlineStr"/>
+      <c r="AE292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF292" s="14" t="inlineStr"/>
+      <c r="AG292" s="14" t="inlineStr"/>
+      <c r="AH292" s="14" t="inlineStr"/>
+      <c r="AI292" s="14" t="inlineStr"/>
+    </row>
+    <row r="293" customHeight="1" ht="24">
+      <c r="A293" s="2" t="inlineStr"/>
+      <c r="B293" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.
@@ -17459,39 +17573,39 @@
           </r>
         </is>
       </c>
-      <c r="C291" s="27" t="inlineStr"/>
-      <c r="D291" s="27" t="inlineStr"/>
-      <c r="E291" s="27" t="inlineStr"/>
-      <c r="F291" s="27" t="inlineStr"/>
-      <c r="G291" s="27" t="inlineStr"/>
-      <c r="H291" s="27" t="inlineStr"/>
-      <c r="I291" s="27" t="inlineStr"/>
-      <c r="J291" s="27" t="inlineStr"/>
-      <c r="K291" s="27" t="inlineStr"/>
-      <c r="L291" s="27" t="inlineStr"/>
-      <c r="M291" s="27" t="inlineStr"/>
-      <c r="N291" s="27" t="inlineStr"/>
-      <c r="O291" s="27" t="inlineStr"/>
-      <c r="P291" s="27" t="inlineStr"/>
-      <c r="Q291" s="27" t="inlineStr"/>
-      <c r="R291" s="27" t="inlineStr"/>
-      <c r="S291" s="27" t="inlineStr"/>
-      <c r="T291" s="27" t="inlineStr"/>
-      <c r="U291" s="27" t="inlineStr"/>
-      <c r="V291" s="27" t="inlineStr"/>
-      <c r="W291" s="27" t="inlineStr"/>
-      <c r="X291" s="27" t="inlineStr"/>
-      <c r="Y291" s="27" t="inlineStr"/>
-      <c r="Z291" s="27" t="inlineStr"/>
-      <c r="AA291" s="27" t="inlineStr"/>
-      <c r="AB291" s="27" t="inlineStr"/>
-      <c r="AC291" s="27" t="inlineStr"/>
-      <c r="AD291" s="27" t="inlineStr"/>
-      <c r="AE291" s="27" t="inlineStr"/>
-      <c r="AF291" s="27" t="inlineStr"/>
-      <c r="AG291" s="2" t="inlineStr"/>
-      <c r="AH291" s="2" t="inlineStr"/>
-      <c r="AI291" s="2" t="inlineStr"/>
+      <c r="C293" s="27" t="inlineStr"/>
+      <c r="D293" s="27" t="inlineStr"/>
+      <c r="E293" s="27" t="inlineStr"/>
+      <c r="F293" s="27" t="inlineStr"/>
+      <c r="G293" s="27" t="inlineStr"/>
+      <c r="H293" s="27" t="inlineStr"/>
+      <c r="I293" s="27" t="inlineStr"/>
+      <c r="J293" s="27" t="inlineStr"/>
+      <c r="K293" s="27" t="inlineStr"/>
+      <c r="L293" s="27" t="inlineStr"/>
+      <c r="M293" s="27" t="inlineStr"/>
+      <c r="N293" s="27" t="inlineStr"/>
+      <c r="O293" s="27" t="inlineStr"/>
+      <c r="P293" s="27" t="inlineStr"/>
+      <c r="Q293" s="27" t="inlineStr"/>
+      <c r="R293" s="27" t="inlineStr"/>
+      <c r="S293" s="27" t="inlineStr"/>
+      <c r="T293" s="27" t="inlineStr"/>
+      <c r="U293" s="27" t="inlineStr"/>
+      <c r="V293" s="27" t="inlineStr"/>
+      <c r="W293" s="27" t="inlineStr"/>
+      <c r="X293" s="27" t="inlineStr"/>
+      <c r="Y293" s="27" t="inlineStr"/>
+      <c r="Z293" s="27" t="inlineStr"/>
+      <c r="AA293" s="27" t="inlineStr"/>
+      <c r="AB293" s="27" t="inlineStr"/>
+      <c r="AC293" s="27" t="inlineStr"/>
+      <c r="AD293" s="27" t="inlineStr"/>
+      <c r="AE293" s="27" t="inlineStr"/>
+      <c r="AF293" s="27" t="inlineStr"/>
+      <c r="AG293" s="2" t="inlineStr"/>
+      <c r="AH293" s="2" t="inlineStr"/>
+      <c r="AI293" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -19359,8 +19473,7 @@
     <mergeCell ref="Z268:AB268"/>
     <mergeCell ref="AC268:AD268"/>
     <mergeCell ref="AE268:AI268"/>
-    <mergeCell ref="H269:L269"/>
-    <mergeCell ref="M269:P269"/>
+    <mergeCell ref="N269:P269"/>
     <mergeCell ref="Q269:R269"/>
     <mergeCell ref="S269:V269"/>
     <mergeCell ref="X269:Y269"/>
@@ -19374,7 +19487,8 @@
     <mergeCell ref="Z270:AB270"/>
     <mergeCell ref="AC270:AD270"/>
     <mergeCell ref="AE270:AI270"/>
-    <mergeCell ref="N271:P271"/>
+    <mergeCell ref="H271:L271"/>
+    <mergeCell ref="M271:P271"/>
     <mergeCell ref="Q271:R271"/>
     <mergeCell ref="S271:V271"/>
     <mergeCell ref="X271:Y271"/>
@@ -19388,16 +19502,14 @@
     <mergeCell ref="Z272:AB272"/>
     <mergeCell ref="AC272:AD272"/>
     <mergeCell ref="AE272:AI272"/>
-    <mergeCell ref="F273:K273"/>
-    <mergeCell ref="L273:P273"/>
+    <mergeCell ref="N273:P273"/>
     <mergeCell ref="Q273:R273"/>
     <mergeCell ref="S273:V273"/>
     <mergeCell ref="X273:Y273"/>
     <mergeCell ref="Z273:AB273"/>
     <mergeCell ref="AC273:AD273"/>
     <mergeCell ref="AE273:AI273"/>
-    <mergeCell ref="H274:L274"/>
-    <mergeCell ref="M274:P274"/>
+    <mergeCell ref="N274:P274"/>
     <mergeCell ref="Q274:R274"/>
     <mergeCell ref="S274:V274"/>
     <mergeCell ref="X274:Y274"/>
@@ -19405,14 +19517,16 @@
     <mergeCell ref="AC274:AD274"/>
     <mergeCell ref="AE274:AI274"/>
     <mergeCell ref="B275:AF275"/>
-    <mergeCell ref="N276:P276"/>
+    <mergeCell ref="F276:K276"/>
+    <mergeCell ref="L276:P276"/>
     <mergeCell ref="Q276:R276"/>
     <mergeCell ref="S276:V276"/>
     <mergeCell ref="X276:Y276"/>
     <mergeCell ref="Z276:AB276"/>
     <mergeCell ref="AC276:AD276"/>
     <mergeCell ref="AE276:AI276"/>
-    <mergeCell ref="N277:P277"/>
+    <mergeCell ref="H277:L277"/>
+    <mergeCell ref="M277:P277"/>
     <mergeCell ref="Q277:R277"/>
     <mergeCell ref="S277:V277"/>
     <mergeCell ref="X277:Y277"/>
@@ -19454,8 +19568,7 @@
     <mergeCell ref="Z282:AB282"/>
     <mergeCell ref="AC282:AD282"/>
     <mergeCell ref="AE282:AI282"/>
-    <mergeCell ref="H283:L283"/>
-    <mergeCell ref="M283:P283"/>
+    <mergeCell ref="N283:P283"/>
     <mergeCell ref="Q283:R283"/>
     <mergeCell ref="S283:V283"/>
     <mergeCell ref="X283:Y283"/>
@@ -19469,54 +19582,69 @@
     <mergeCell ref="Z284:AB284"/>
     <mergeCell ref="AC284:AD284"/>
     <mergeCell ref="AE284:AI284"/>
-    <mergeCell ref="C285:F285"/>
-    <mergeCell ref="G285:P285"/>
+    <mergeCell ref="H285:L285"/>
+    <mergeCell ref="M285:P285"/>
     <mergeCell ref="Q285:R285"/>
     <mergeCell ref="S285:V285"/>
     <mergeCell ref="X285:Y285"/>
     <mergeCell ref="Z285:AB285"/>
     <mergeCell ref="AC285:AD285"/>
     <mergeCell ref="AE285:AI285"/>
-    <mergeCell ref="C286:J286"/>
-    <mergeCell ref="K286:P286"/>
+    <mergeCell ref="N286:P286"/>
     <mergeCell ref="Q286:R286"/>
     <mergeCell ref="S286:V286"/>
     <mergeCell ref="X286:Y286"/>
     <mergeCell ref="Z286:AB286"/>
     <mergeCell ref="AC286:AD286"/>
     <mergeCell ref="AE286:AI286"/>
-    <mergeCell ref="E287:I287"/>
-    <mergeCell ref="J287:P287"/>
+    <mergeCell ref="C287:F287"/>
+    <mergeCell ref="G287:P287"/>
     <mergeCell ref="Q287:R287"/>
     <mergeCell ref="S287:V287"/>
     <mergeCell ref="X287:Y287"/>
     <mergeCell ref="Z287:AB287"/>
     <mergeCell ref="AC287:AD287"/>
     <mergeCell ref="AE287:AI287"/>
-    <mergeCell ref="F288:K288"/>
-    <mergeCell ref="L288:P288"/>
+    <mergeCell ref="C288:J288"/>
+    <mergeCell ref="K288:P288"/>
     <mergeCell ref="Q288:R288"/>
     <mergeCell ref="S288:V288"/>
     <mergeCell ref="X288:Y288"/>
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="H289:L289"/>
-    <mergeCell ref="M289:P289"/>
+    <mergeCell ref="E289:I289"/>
+    <mergeCell ref="J289:P289"/>
     <mergeCell ref="Q289:R289"/>
     <mergeCell ref="S289:V289"/>
     <mergeCell ref="X289:Y289"/>
     <mergeCell ref="Z289:AB289"/>
     <mergeCell ref="AC289:AD289"/>
     <mergeCell ref="AE289:AI289"/>
-    <mergeCell ref="N290:P290"/>
+    <mergeCell ref="F290:K290"/>
+    <mergeCell ref="L290:P290"/>
     <mergeCell ref="Q290:R290"/>
     <mergeCell ref="S290:V290"/>
     <mergeCell ref="X290:Y290"/>
     <mergeCell ref="Z290:AB290"/>
     <mergeCell ref="AC290:AD290"/>
     <mergeCell ref="AE290:AI290"/>
-    <mergeCell ref="B291:AF291"/>
+    <mergeCell ref="H291:L291"/>
+    <mergeCell ref="M291:P291"/>
+    <mergeCell ref="Q291:R291"/>
+    <mergeCell ref="S291:V291"/>
+    <mergeCell ref="X291:Y291"/>
+    <mergeCell ref="Z291:AB291"/>
+    <mergeCell ref="AC291:AD291"/>
+    <mergeCell ref="AE291:AI291"/>
+    <mergeCell ref="N292:P292"/>
+    <mergeCell ref="Q292:R292"/>
+    <mergeCell ref="S292:V292"/>
+    <mergeCell ref="X292:Y292"/>
+    <mergeCell ref="Z292:AB292"/>
+    <mergeCell ref="AC292:AD292"/>
+    <mergeCell ref="AE292:AI292"/>
+    <mergeCell ref="B293:AF293"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>8.6557047429E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>3.613859066E9</v>
+        <v>4.386145866E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.0170906495E10</v>
+        <v>9.0943193295E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9017447920786622</v>
+        <v>0.9094679660708157</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>9.825131505E9</v>
+        <v>9.052844705E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>3.613859066E9</v>
+        <v>4.386145866E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.6137538455E10</v>
+        <v>8.6909825255E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.8976153662532703</v>
+        <v>0.9056631525177539</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>9.825099545E9</v>
+        <v>9.052812745E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>3.613859066E9</v>
+        <v>4.386145866E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.6137538455E10</v>
+        <v>8.6909825255E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.8976153662532703</v>
+        <v>0.9056631525177539</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>9.825099545E9</v>
+        <v>9.052812745E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.2523079389E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>3.613859066E9</v>
+        <v>4.386145866E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.6136938455E10</v>
+        <v>8.6909225255E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.8976147260961673</v>
+        <v>0.9056625626792127</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>9.825099545E9</v>
+        <v>9.052812745E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3234,20 +3234,20 @@
         <v>8.2505568337E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>3.613859066E9</v>
+        <v>4.386145866E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.6119427403E10</v>
+        <v>8.6891714203E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.897605572260293</v>
+        <v>0.9056549631581118</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>9.824080597E9</v>
+        <v>9.051793797E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3297,20 +3297,20 @@
         <v>7.6753022175E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>3.526529172E9</v>
+        <v>4.045429172E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.0279551347E10</v>
+        <v>8.0798451347E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9020506445726097</v>
+        <v>0.9078811963334875</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>8.717171653E9</v>
+        <v>8.198271653E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3360,20 +3360,20 @@
         <v>5.460273892E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>3.70964212E8</v>
+        <v>3.99287212E8</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>5.831238104E9</v>
+        <v>5.859561104E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.981210213727161</v>
+        <v>0.9859760655733292</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>1.11665896E8</v>
+        <v>8.3342896E7</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -5339,20 +5339,20 @@
         <v>2.77741E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>0.0</v>
+        <v>2.8323E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>2.77741E8</v>
+        <v>3.06064E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.7699628520736305</v>
+        <v>0.8484808161454868</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>8.2979E7</v>
+        <v>5.4656E7</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5396,20 +5396,20 @@
         <v>1.554E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>0.0</v>
+        <v>1400000.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>1.554E7</v>
+        <v>1.694E7</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>2940000.0</v>
+        <v>1540000.0</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5453,20 +5453,20 @@
         <v>2.28253E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>0.0</v>
+        <v>2.3643E7</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
-        <v>2.28253E8</v>
+        <v>2.51896E8</v>
       </c>
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.7789141414141414</v>
+        <v>0.8595959595959596</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>6.4787E7</v>
+        <v>4.1144E7</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5510,20 +5510,20 @@
         <v>3.3948E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>0.0</v>
+        <v>3280000.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
-        <v>3.3948E7</v>
+        <v>3.7228E7</v>
       </c>
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.69</v>
+        <v>0.7566666666666667</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>1.5252E7</v>
+        <v>1.1972E7</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -6085,20 +6085,20 @@
         <v>4.5358707E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>1.40326965E8</v>
+        <v>1.67266965E8</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>5.93914035E8</v>
+        <v>6.20854035E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.6139331677334524</v>
+        <v>0.6417812375955145</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>3.73477965E8</v>
+        <v>3.46537965E8</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6748,20 +6748,20 @@
         <v>3.0833E7</v>
       </c>
       <c r="X106" s="14" t="n">
-        <v>0.0</v>
+        <v>2.694E7</v>
       </c>
       <c r="Y106" s="14" t="inlineStr"/>
       <c r="Z106" s="14" t="n">
-        <v>3.0833E7</v>
+        <v>5.7773E7</v>
       </c>
       <c r="AA106" s="14" t="inlineStr"/>
       <c r="AB106" s="14" t="inlineStr"/>
       <c r="AC106" s="15" t="n">
-        <v>0.3713029865125241</v>
+        <v>0.6957249518304431</v>
       </c>
       <c r="AD106" s="15" t="inlineStr"/>
       <c r="AE106" s="14" t="n">
-        <v>5.2207E7</v>
+        <v>2.5267E7</v>
       </c>
       <c r="AF106" s="14" t="inlineStr"/>
       <c r="AG106" s="14" t="inlineStr"/>
@@ -6805,20 +6805,20 @@
         <v>8855000.0</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>0.0</v>
+        <v>7700000.0</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
-        <v>8855000.0</v>
+        <v>1.6555E7</v>
       </c>
       <c r="AA107" s="14" t="inlineStr"/>
       <c r="AB107" s="14" t="inlineStr"/>
       <c r="AC107" s="15" t="n">
-        <v>0.38333333333333336</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="AD107" s="15" t="inlineStr"/>
       <c r="AE107" s="14" t="n">
-        <v>1.4245E7</v>
+        <v>6545000.0</v>
       </c>
       <c r="AF107" s="14" t="inlineStr"/>
       <c r="AG107" s="14" t="inlineStr"/>
@@ -6862,20 +6862,20 @@
         <v>2.1978E7</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>0.0</v>
+        <v>1.924E7</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
-        <v>2.1978E7</v>
+        <v>4.1218E7</v>
       </c>
       <c r="AA108" s="14" t="inlineStr"/>
       <c r="AB108" s="14" t="inlineStr"/>
       <c r="AC108" s="15" t="n">
-        <v>0.36666666666666664</v>
+        <v>0.6876543209876543</v>
       </c>
       <c r="AD108" s="15" t="inlineStr"/>
       <c r="AE108" s="14" t="n">
-        <v>3.7962E7</v>
+        <v>1.8722E7</v>
       </c>
       <c r="AF108" s="14" t="inlineStr"/>
       <c r="AG108" s="14" t="inlineStr"/>
@@ -7165,20 +7165,20 @@
         <v>4.9091867246E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>1.598020754E9</v>
+        <v>1.816472754E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.0689888E10</v>
+        <v>5.090834E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.9193436738595991</v>
+        <v>0.9233056566566804</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>4.447151E9</v>
+        <v>4.228699E9</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -8954,20 +8954,20 @@
         <v>2.213268E9</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>0.0</v>
+        <v>2.18452E8</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
-        <v>2.213268E9</v>
+        <v>2.43172E9</v>
       </c>
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.8282097567985056</v>
+        <v>0.9099549759911868</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>4.59084E8</v>
+        <v>2.40632E8</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -9011,20 +9011,20 @@
         <v>1.9894E8</v>
       </c>
       <c r="X145" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0567E7</v>
       </c>
       <c r="Y145" s="14" t="inlineStr"/>
       <c r="Z145" s="14" t="n">
-        <v>1.9894E8</v>
+        <v>2.29507E8</v>
       </c>
       <c r="AA145" s="14" t="inlineStr"/>
       <c r="AB145" s="14" t="inlineStr"/>
       <c r="AC145" s="15" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.9421469622331692</v>
       </c>
       <c r="AD145" s="15" t="inlineStr"/>
       <c r="AE145" s="14" t="n">
-        <v>4.466E7</v>
+        <v>1.4093E7</v>
       </c>
       <c r="AF145" s="14" t="inlineStr"/>
       <c r="AG145" s="14" t="inlineStr"/>
@@ -9068,20 +9068,20 @@
         <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>0.0</v>
+        <v>1.59359E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>1.581491E9</v>
+        <v>1.74085E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.8283527131782946</v>
+        <v>0.9118217054263565</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>3.27709E8</v>
+        <v>1.6835E8</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9125,20 +9125,20 @@
         <v>4.32837E8</v>
       </c>
       <c r="X147" s="14" t="n">
-        <v>0.0</v>
+        <v>2.8526E7</v>
       </c>
       <c r="Y147" s="14" t="inlineStr"/>
       <c r="Z147" s="14" t="n">
-        <v>4.32837E8</v>
+        <v>4.61363E8</v>
       </c>
       <c r="AA147" s="14" t="inlineStr"/>
       <c r="AB147" s="14" t="inlineStr"/>
       <c r="AC147" s="15" t="n">
-        <v>0.8330965909090909</v>
+        <v>0.8880015859817689</v>
       </c>
       <c r="AD147" s="15" t="inlineStr"/>
       <c r="AE147" s="14" t="n">
-        <v>8.6715E7</v>
+        <v>5.8189E7</v>
       </c>
       <c r="AF147" s="14" t="inlineStr"/>
       <c r="AG147" s="14" t="inlineStr"/>
@@ -9656,20 +9656,20 @@
         <v>2.1747293967E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>1.417217241E9</v>
+        <v>1.662402241E9</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
-        <v>2.3164511208E10</v>
+        <v>2.3409696208E10</v>
       </c>
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.8595561134078443</v>
+        <v>0.8686540936662458</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.784876792E9</v>
+        <v>3.539691792E9</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11167,20 +11167,20 @@
         <v>1.310426E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>0.0</v>
+        <v>2.45185E8</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
-        <v>1.310426E9</v>
+        <v>1.555611E9</v>
       </c>
       <c r="AA182" s="14" t="inlineStr"/>
       <c r="AB182" s="14" t="inlineStr"/>
       <c r="AC182" s="15" t="n">
-        <v>0.7344778495202224</v>
+        <v>0.871901062684961</v>
       </c>
       <c r="AD182" s="15" t="inlineStr"/>
       <c r="AE182" s="14" t="n">
-        <v>4.73734E8</v>
+        <v>2.28549E8</v>
       </c>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -11224,20 +11224,20 @@
         <v>1.2502E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>0.0</v>
+        <v>2.226E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.2502E8</v>
+        <v>1.4728E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.7441666666666666</v>
+        <v>0.8766666666666667</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>4.298E7</v>
+        <v>2.072E7</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11281,20 +11281,20 @@
         <v>1.185406E9</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>0.0</v>
+        <v>2.22925E8</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>1.185406E9</v>
+        <v>1.408331E9</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.7334706959706959</v>
+        <v>0.8714056776556777</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>4.30754E8</v>
+        <v>2.07829E8</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11578,20 +11578,20 @@
         <v>5.752546162E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>8.7329894E7</v>
+        <v>3.40716694E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>5.839876056E9</v>
+        <v>6.093262856E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.840658816416515</v>
+        <v>0.8771342219458353</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>1.106908944E9</v>
+        <v>8.53522144E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11641,20 +11641,20 @@
         <v>4.382759356E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>3.174114E7</v>
+        <v>2.3962764E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.414500496E9</v>
+        <v>4.622386996E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.8828928594785522</v>
+        <v>0.9244698185474879</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>5.85540504E8</v>
+        <v>3.77654004E8</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11704,20 +11704,20 @@
         <v>1.752363354E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>2.554614E7</v>
+        <v>4.894614E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.777909494E9</v>
+        <v>1.801309494E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9402863915439728</v>
+        <v>0.9526619942596243</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>1.12907506E8</v>
+        <v>8.9507506E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -12257,20 +12257,20 @@
         <v>4.87008E7</v>
       </c>
       <c r="X201" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="Y201" s="14" t="inlineStr"/>
       <c r="Z201" s="14" t="n">
-        <v>4.87008E7</v>
+        <v>7.21008E7</v>
       </c>
       <c r="AA201" s="14" t="inlineStr"/>
       <c r="AB201" s="14" t="inlineStr"/>
       <c r="AC201" s="15" t="n">
-        <v>0.48970135746606336</v>
+        <v>0.7249954751131221</v>
       </c>
       <c r="AD201" s="15" t="inlineStr"/>
       <c r="AE201" s="14" t="n">
-        <v>5.07492E7</v>
+        <v>2.73492E7</v>
       </c>
       <c r="AF201" s="14" t="inlineStr"/>
       <c r="AG201" s="14" t="inlineStr"/>
@@ -12908,20 +12908,20 @@
         <v>2.567718192E9</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>0.0</v>
+        <v>1.844865E8</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>2.567718192E9</v>
+        <v>2.752204692E9</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.8526749942218952</v>
+        <v>0.9139383469572633</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>4.43649808E8</v>
+        <v>2.59163308E8</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
@@ -13193,20 +13193,20 @@
         <v>1.844865E9</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>0.0</v>
+        <v>1.844865E8</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>1.844865E9</v>
+        <v>2.0293515E9</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>3.68973E8</v>
+        <v>1.844865E8</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
@@ -13370,20 +13370,20 @@
         <v>6.39230607E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>611800.0</v>
+        <v>1216100.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>6.39842407E8</v>
+        <v>6.40446707E8</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.9138725847825591</v>
+        <v>0.9147356929431659</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>6.0301593E7</v>
+        <v>5.9697293E7</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13717,20 +13717,20 @@
         <v>3.021E7</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>611800.0</v>
+        <v>1216100.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>3.08218E7</v>
+        <v>3.14261E7</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9215943069010883</v>
+        <v>0.9396633177849539</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>2622200.0</v>
+        <v>2017900.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13774,20 +13774,20 @@
         <v>3.021E7</v>
       </c>
       <c r="X227" s="14" t="n">
-        <v>611800.0</v>
+        <v>1216100.0</v>
       </c>
       <c r="Y227" s="14" t="inlineStr"/>
       <c r="Z227" s="14" t="n">
-        <v>3.08218E7</v>
+        <v>3.14261E7</v>
       </c>
       <c r="AA227" s="14" t="inlineStr"/>
       <c r="AB227" s="14" t="inlineStr"/>
       <c r="AC227" s="15" t="n">
-        <v>0.9215943069010883</v>
+        <v>0.9396633177849539</v>
       </c>
       <c r="AD227" s="15" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
-        <v>2622200.0</v>
+        <v>2017900.0</v>
       </c>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
@@ -14014,20 +14014,20 @@
         <v>6.19636199E8</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>5.4976954E7</v>
+        <v>8.0052954E7</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>6.74613153E8</v>
+        <v>6.99689153E8</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.6053491080562086</v>
+        <v>0.6278504989142334</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>4.39806847E8</v>
+        <v>4.14730847E8</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14374,20 +14374,20 @@
         <v>1.28808533E8</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>5413000.0</v>
+        <v>3.0489E7</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>1.34221533E8</v>
+        <v>1.59297533E8</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.36169536500579375</v>
+        <v>0.4292692689105069</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>2.36868467E8</v>
+        <v>2.11792467E8</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14659,20 +14659,20 @@
         <v>4421000.0</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5076E7</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>4421000.0</v>
+        <v>2.9497E7</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.03296793437733035</v>
+        <v>0.2199627143922446</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>1.29679E8</v>
+        <v>1.04603E8</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -16589,20 +16589,20 @@
         <v>1.1092E8</v>
       </c>
       <c r="X276" s="14" t="n">
-        <v>0.0</v>
+        <v>1.982E7</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>1.1092E8</v>
+        <v>1.3074E8</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.8391587229535482</v>
+        <v>0.9891057648660917</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>2.126E7</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
@@ -16652,20 +16652,20 @@
         <v>1.0342E8</v>
       </c>
       <c r="X277" s="14" t="n">
-        <v>0.0</v>
+        <v>1.982E7</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>1.0342E8</v>
+        <v>1.2324E8</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.8294834777029195</v>
+        <v>0.9884504331087585</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>2.126E7</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
@@ -16709,20 +16709,20 @@
         <v>2.55E7</v>
       </c>
       <c r="X278" s="14" t="n">
-        <v>0.0</v>
+        <v>5100000.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>2.55E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>5100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
@@ -16766,20 +16766,20 @@
         <v>2.48E7</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>0.0</v>
+        <v>4960000.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>2.48E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>4960000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
@@ -16823,20 +16823,20 @@
         <v>1.23E7</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>0.0</v>
+        <v>2460000.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>1.23E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
       <c r="AC280" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
-        <v>2460000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF280" s="14" t="inlineStr"/>
       <c r="AG280" s="14" t="inlineStr"/>
@@ -16880,20 +16880,20 @@
         <v>1.07E7</v>
       </c>
       <c r="X281" s="14" t="n">
-        <v>0.0</v>
+        <v>2140000.0</v>
       </c>
       <c r="Y281" s="14" t="inlineStr"/>
       <c r="Z281" s="14" t="n">
-        <v>1.07E7</v>
+        <v>1.284E7</v>
       </c>
       <c r="AA281" s="14" t="inlineStr"/>
       <c r="AB281" s="14" t="inlineStr"/>
       <c r="AC281" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD281" s="15" t="inlineStr"/>
       <c r="AE281" s="14" t="n">
-        <v>2140000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF281" s="14" t="inlineStr"/>
       <c r="AG281" s="14" t="inlineStr"/>
@@ -16937,20 +16937,20 @@
         <v>2.4E7</v>
       </c>
       <c r="X282" s="14" t="n">
-        <v>0.0</v>
+        <v>4800000.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>2.4E7</v>
+        <v>2.88E7</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
       <c r="AC282" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD282" s="15" t="inlineStr"/>
       <c r="AE282" s="14" t="n">
-        <v>4800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF282" s="14" t="inlineStr"/>
       <c r="AG282" s="14" t="inlineStr"/>
@@ -17051,20 +17051,20 @@
         <v>3420000.0</v>
       </c>
       <c r="X284" s="14" t="n">
-        <v>0.0</v>
+        <v>360000.0</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
-        <v>3420000.0</v>
+        <v>3780000.0</v>
       </c>
       <c r="AA284" s="14" t="inlineStr"/>
       <c r="AB284" s="14" t="inlineStr"/>
       <c r="AC284" s="15" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="AD284" s="15" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
-        <v>900000.0</v>
+        <v>540000.0</v>
       </c>
       <c r="AF284" s="14" t="inlineStr"/>
       <c r="AG284" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>8.6557047429E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>4.386145866E9</v>
+        <v>4.486302984E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.0943193295E10</v>
+        <v>9.1043350413E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9094679660708157</v>
+        <v>0.9104695769346381</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>9.052844705E9</v>
+        <v>8.952687587E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>4.386145866E9</v>
+        <v>4.486302984E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.6909825255E10</v>
+        <v>8.7009982373E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9056631525177539</v>
+        <v>0.9067068620289492</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>9.052812745E9</v>
+        <v>8.952655627E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>4.386145866E9</v>
+        <v>4.486302984E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.6909825255E10</v>
+        <v>8.7009982373E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9056631525177539</v>
+        <v>0.9067068620289492</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>9.052812745E9</v>
+        <v>8.952655627E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.2523079389E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>4.386145866E9</v>
+        <v>4.486302984E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.6909225255E10</v>
+        <v>8.7009382373E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9056625626792127</v>
+        <v>0.9067062787161732</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>9.052812745E9</v>
+        <v>8.952655627E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3234,20 +3234,20 @@
         <v>8.2505568337E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>4.386145866E9</v>
+        <v>4.486302984E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.6891714203E10</v>
+        <v>8.6991871321E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9056549631581118</v>
+        <v>0.9066988807726313</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>9.051793797E9</v>
+        <v>8.951636679E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
       <c r="O62" s="13" t="inlineStr"/>
       <c r="P62" s="13" t="inlineStr"/>
       <c r="Q62" s="14" t="n">
-        <v>5.3276E7</v>
+        <v>5.3132E7</v>
       </c>
       <c r="R62" s="14" t="inlineStr"/>
       <c r="S62" s="14" t="n">
@@ -4178,11 +4178,11 @@
       <c r="AA62" s="14" t="inlineStr"/>
       <c r="AB62" s="14" t="inlineStr"/>
       <c r="AC62" s="15" t="n">
-        <v>0.9968937607928523</v>
+        <v>0.9995955732891666</v>
       </c>
       <c r="AD62" s="15" t="inlineStr"/>
       <c r="AE62" s="14" t="n">
-        <v>165488.0</v>
+        <v>21488.0</v>
       </c>
       <c r="AF62" s="14" t="inlineStr"/>
       <c r="AG62" s="14" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
       <c r="O63" s="13" t="inlineStr"/>
       <c r="P63" s="13" t="inlineStr"/>
       <c r="Q63" s="14" t="n">
-        <v>4.5588E7</v>
+        <v>4.5444E7</v>
       </c>
       <c r="R63" s="14" t="inlineStr"/>
       <c r="S63" s="14" t="n">
@@ -4235,11 +4235,11 @@
       <c r="AA63" s="14" t="inlineStr"/>
       <c r="AB63" s="14" t="inlineStr"/>
       <c r="AC63" s="15" t="n">
-        <v>0.9966318768096868</v>
+        <v>0.9997899392659096</v>
       </c>
       <c r="AD63" s="15" t="inlineStr"/>
       <c r="AE63" s="14" t="n">
-        <v>153546.0</v>
+        <v>9546.0</v>
       </c>
       <c r="AF63" s="14" t="inlineStr"/>
       <c r="AG63" s="14" t="inlineStr"/>
@@ -4858,7 +4858,7 @@
       <c r="O74" s="13" t="inlineStr"/>
       <c r="P74" s="13" t="inlineStr"/>
       <c r="Q74" s="14" t="n">
-        <v>2.016E7</v>
+        <v>2.0304E7</v>
       </c>
       <c r="R74" s="14" t="inlineStr"/>
       <c r="S74" s="14" t="n">
@@ -4880,11 +4880,11 @@
       <c r="AA74" s="14" t="inlineStr"/>
       <c r="AB74" s="14" t="inlineStr"/>
       <c r="AC74" s="15" t="n">
-        <v>1.0054437003968253</v>
+        <v>0.9983128940110323</v>
       </c>
       <c r="AD74" s="15" t="inlineStr"/>
       <c r="AE74" s="14" t="n">
-        <v>-109745.0</v>
+        <v>34255.0</v>
       </c>
       <c r="AF74" s="14" t="inlineStr"/>
       <c r="AG74" s="14" t="inlineStr"/>
@@ -4915,7 +4915,7 @@
       <c r="O75" s="13" t="inlineStr"/>
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="14" t="n">
-        <v>2616000.0</v>
+        <v>2760000.0</v>
       </c>
       <c r="R75" s="14" t="inlineStr"/>
       <c r="S75" s="14" t="n">
@@ -4937,11 +4937,11 @@
       <c r="AA75" s="14" t="inlineStr"/>
       <c r="AB75" s="14" t="inlineStr"/>
       <c r="AC75" s="15" t="n">
-        <v>1.046914755351682</v>
+        <v>0.992293115942029</v>
       </c>
       <c r="AD75" s="15" t="inlineStr"/>
       <c r="AE75" s="14" t="n">
-        <v>-122729.0</v>
+        <v>21271.0</v>
       </c>
       <c r="AF75" s="14" t="inlineStr"/>
       <c r="AG75" s="14" t="inlineStr"/>
@@ -6135,7 +6135,7 @@
       <c r="O96" s="13" t="inlineStr"/>
       <c r="P96" s="13" t="inlineStr"/>
       <c r="Q96" s="14" t="n">
-        <v>3.47283E8</v>
+        <v>3.4728E8</v>
       </c>
       <c r="R96" s="14" t="inlineStr"/>
       <c r="S96" s="14" t="n">
@@ -6157,11 +6157,11 @@
       <c r="AA96" s="14" t="inlineStr"/>
       <c r="AB96" s="14" t="inlineStr"/>
       <c r="AC96" s="15" t="n">
-        <v>0.9969575245549019</v>
+        <v>0.9969661368348307</v>
       </c>
       <c r="AD96" s="15" t="inlineStr"/>
       <c r="AE96" s="14" t="n">
-        <v>1056600.0</v>
+        <v>1053600.0</v>
       </c>
       <c r="AF96" s="14" t="inlineStr"/>
       <c r="AG96" s="14" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       <c r="O97" s="13" t="inlineStr"/>
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="14" t="n">
-        <v>3.47283E8</v>
+        <v>3.4728E8</v>
       </c>
       <c r="R97" s="14" t="inlineStr"/>
       <c r="S97" s="14" t="n">
@@ -6214,11 +6214,11 @@
       <c r="AA97" s="14" t="inlineStr"/>
       <c r="AB97" s="14" t="inlineStr"/>
       <c r="AC97" s="15" t="n">
-        <v>0.9969575245549019</v>
+        <v>0.9969661368348307</v>
       </c>
       <c r="AD97" s="15" t="inlineStr"/>
       <c r="AE97" s="14" t="n">
-        <v>1056600.0</v>
+        <v>1053600.0</v>
       </c>
       <c r="AF97" s="14" t="inlineStr"/>
       <c r="AG97" s="14" t="inlineStr"/>
@@ -6255,7 +6255,7 @@
       <c r="O98" s="13" t="inlineStr"/>
       <c r="P98" s="13" t="inlineStr"/>
       <c r="Q98" s="14" t="n">
-        <v>6000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="R98" s="14" t="inlineStr"/>
       <c r="S98" s="14" t="n">
@@ -6277,11 +6277,11 @@
       <c r="AA98" s="14" t="inlineStr"/>
       <c r="AB98" s="14" t="inlineStr"/>
       <c r="AC98" s="15" t="n">
-        <v>1.0598333333333334</v>
+        <v>0.7065555555555556</v>
       </c>
       <c r="AD98" s="15" t="inlineStr"/>
       <c r="AE98" s="14" t="n">
-        <v>-359.0</v>
+        <v>2641.0</v>
       </c>
       <c r="AF98" s="14" t="inlineStr"/>
       <c r="AG98" s="14" t="inlineStr"/>
@@ -6312,7 +6312,7 @@
       <c r="O99" s="13" t="inlineStr"/>
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="14" t="n">
-        <v>6000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="R99" s="14" t="inlineStr"/>
       <c r="S99" s="14" t="n">
@@ -6334,11 +6334,11 @@
       <c r="AA99" s="14" t="inlineStr"/>
       <c r="AB99" s="14" t="inlineStr"/>
       <c r="AC99" s="15" t="n">
-        <v>1.0598333333333334</v>
+        <v>0.7065555555555556</v>
       </c>
       <c r="AD99" s="15" t="inlineStr"/>
       <c r="AE99" s="14" t="n">
-        <v>-359.0</v>
+        <v>2641.0</v>
       </c>
       <c r="AF99" s="14" t="inlineStr"/>
       <c r="AG99" s="14" t="inlineStr"/>
@@ -7259,7 +7259,7 @@
       <c r="O115" s="13" t="inlineStr"/>
       <c r="P115" s="13" t="inlineStr"/>
       <c r="Q115" s="14" t="n">
-        <v>1.7108339E10</v>
+        <v>1.7101139E10</v>
       </c>
       <c r="R115" s="14" t="inlineStr"/>
       <c r="S115" s="14" t="n">
@@ -7281,11 +7281,11 @@
       <c r="AA115" s="14" t="inlineStr"/>
       <c r="AB115" s="14" t="inlineStr"/>
       <c r="AC115" s="15" t="n">
-        <v>0.9988785936495647</v>
+        <v>0.9992991460978126</v>
       </c>
       <c r="AD115" s="15" t="inlineStr"/>
       <c r="AE115" s="14" t="n">
-        <v>1.91854E7</v>
+        <v>1.19854E7</v>
       </c>
       <c r="AF115" s="14" t="inlineStr"/>
       <c r="AG115" s="14" t="inlineStr"/>
@@ -7316,7 +7316,7 @@
       <c r="O116" s="13" t="inlineStr"/>
       <c r="P116" s="13" t="inlineStr"/>
       <c r="Q116" s="14" t="n">
-        <v>1.463616E10</v>
+        <v>1.460406E10</v>
       </c>
       <c r="R116" s="14" t="inlineStr"/>
       <c r="S116" s="14" t="n">
@@ -7338,11 +7338,11 @@
       <c r="AA116" s="14" t="inlineStr"/>
       <c r="AB116" s="14" t="inlineStr"/>
       <c r="AC116" s="15" t="n">
-        <v>0.9974201019939656</v>
+        <v>0.9996124502364411</v>
       </c>
       <c r="AD116" s="15" t="inlineStr"/>
       <c r="AE116" s="14" t="n">
-        <v>3.77598E7</v>
+        <v>5659800.0</v>
       </c>
       <c r="AF116" s="14" t="inlineStr"/>
       <c r="AG116" s="14" t="inlineStr"/>
@@ -7373,7 +7373,7 @@
       <c r="O117" s="13" t="inlineStr"/>
       <c r="P117" s="13" t="inlineStr"/>
       <c r="Q117" s="14" t="n">
-        <v>1.250844E9</v>
+        <v>1.243644E9</v>
       </c>
       <c r="R117" s="14" t="inlineStr"/>
       <c r="S117" s="14" t="n">
@@ -7395,11 +7395,11 @@
       <c r="AA117" s="14" t="inlineStr"/>
       <c r="AB117" s="14" t="inlineStr"/>
       <c r="AC117" s="15" t="n">
-        <v>0.9891997723137338</v>
+        <v>0.9949266831987289</v>
       </c>
       <c r="AD117" s="15" t="inlineStr"/>
       <c r="AE117" s="14" t="n">
-        <v>1.35094E7</v>
+        <v>6309400.0</v>
       </c>
       <c r="AF117" s="14" t="inlineStr"/>
       <c r="AG117" s="14" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       <c r="O118" s="13" t="inlineStr"/>
       <c r="P118" s="13" t="inlineStr"/>
       <c r="Q118" s="14" t="n">
-        <v>1.221335E9</v>
+        <v>1.253435E9</v>
       </c>
       <c r="R118" s="14" t="inlineStr"/>
       <c r="S118" s="14" t="n">
@@ -7452,11 +7452,11 @@
       <c r="AA118" s="14" t="inlineStr"/>
       <c r="AB118" s="14" t="inlineStr"/>
       <c r="AC118" s="15" t="n">
-        <v>1.0262694510515133</v>
+        <v>0.9999870755164807</v>
       </c>
       <c r="AD118" s="15" t="inlineStr"/>
       <c r="AE118" s="14" t="n">
-        <v>-3.20838E7</v>
+        <v>16200.0</v>
       </c>
       <c r="AF118" s="14" t="inlineStr"/>
       <c r="AG118" s="14" t="inlineStr"/>
@@ -8429,7 +8429,7 @@
       <c r="O135" s="13" t="inlineStr"/>
       <c r="P135" s="13" t="inlineStr"/>
       <c r="Q135" s="14" t="n">
-        <v>2.3055E8</v>
+        <v>2.3775E8</v>
       </c>
       <c r="R135" s="14" t="inlineStr"/>
       <c r="S135" s="14" t="n">
@@ -8451,11 +8451,11 @@
       <c r="AA135" s="14" t="inlineStr"/>
       <c r="AB135" s="14" t="inlineStr"/>
       <c r="AC135" s="15" t="n">
-        <v>1.0291648275862069</v>
+        <v>0.9979976908517351</v>
       </c>
       <c r="AD135" s="15" t="inlineStr"/>
       <c r="AE135" s="14" t="n">
-        <v>-6723951.0</v>
+        <v>476049.0</v>
       </c>
       <c r="AF135" s="14" t="inlineStr"/>
       <c r="AG135" s="14" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       <c r="O136" s="13" t="inlineStr"/>
       <c r="P136" s="13" t="inlineStr"/>
       <c r="Q136" s="14" t="n">
-        <v>4.5084E7</v>
+        <v>5.2284E7</v>
       </c>
       <c r="R136" s="14" t="inlineStr"/>
       <c r="S136" s="14" t="n">
@@ -8508,11 +8508,11 @@
       <c r="AA136" s="14" t="inlineStr"/>
       <c r="AB136" s="14" t="inlineStr"/>
       <c r="AC136" s="15" t="n">
-        <v>1.1493616360571377</v>
+        <v>0.9910836967332263</v>
       </c>
       <c r="AD136" s="15" t="inlineStr"/>
       <c r="AE136" s="14" t="n">
-        <v>-6733820.0</v>
+        <v>466180.0</v>
       </c>
       <c r="AF136" s="14" t="inlineStr"/>
       <c r="AG136" s="14" t="inlineStr"/>
@@ -9940,7 +9940,7 @@
       <c r="O161" s="13" t="inlineStr"/>
       <c r="P161" s="13" t="inlineStr"/>
       <c r="Q161" s="14" t="n">
-        <v>182000.0</v>
+        <v>206000.0</v>
       </c>
       <c r="R161" s="14" t="inlineStr"/>
       <c r="S161" s="14" t="n">
@@ -9962,11 +9962,11 @@
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>1.0657637362637362</v>
+        <v>0.9415970873786408</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>-11969.0</v>
+        <v>12031.0</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -9997,7 +9997,7 @@
       <c r="O162" s="13" t="inlineStr"/>
       <c r="P162" s="13" t="inlineStr"/>
       <c r="Q162" s="14" t="n">
-        <v>168000.0</v>
+        <v>192000.0</v>
       </c>
       <c r="R162" s="14" t="inlineStr"/>
       <c r="S162" s="14" t="n">
@@ -10019,11 +10019,11 @@
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>1.076482142857143</v>
+        <v>0.941921875</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>-12849.0</v>
+        <v>11151.0</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10174,7 +10174,7 @@
       <c r="O165" s="13" t="inlineStr"/>
       <c r="P165" s="13" t="inlineStr"/>
       <c r="Q165" s="14" t="n">
-        <v>6.40678E8</v>
+        <v>6.40654E8</v>
       </c>
       <c r="R165" s="14" t="inlineStr"/>
       <c r="S165" s="14" t="n">
@@ -10196,11 +10196,11 @@
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.9750256603161026</v>
+        <v>0.9750621864532181</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>1.600051E7</v>
+        <v>1.597651E7</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10231,7 +10231,7 @@
       <c r="O166" s="13" t="inlineStr"/>
       <c r="P166" s="13" t="inlineStr"/>
       <c r="Q166" s="14" t="n">
-        <v>5.66952E8</v>
+        <v>5.66928E8</v>
       </c>
       <c r="R166" s="14" t="inlineStr"/>
       <c r="S166" s="14" t="n">
@@ -10253,11 +10253,11 @@
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.9717801859769434</v>
+        <v>0.9718213247537606</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>1.599928E7</v>
+        <v>1.597528E7</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -11578,20 +11578,20 @@
         <v>5.752546162E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>3.40716694E8</v>
+        <v>4.40873812E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.093262856E9</v>
+        <v>6.193419974E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.8771342219458353</v>
+        <v>0.891551987574108</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>8.53522144E8</v>
+        <v>7.53365026E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
       <c r="Q190" s="14" t="n">
-        <v>5.000041E9</v>
+        <v>5.006041E9</v>
       </c>
       <c r="R190" s="14" t="inlineStr"/>
       <c r="S190" s="14" t="n">
@@ -11641,20 +11641,20 @@
         <v>4.382759356E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>2.3962764E8</v>
+        <v>3.3261462E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.622386996E9</v>
+        <v>4.715373976E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9244698185474879</v>
+        <v>0.9419367472220064</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>3.77654004E8</v>
+        <v>2.90667024E8</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11704,20 +11704,20 @@
         <v>1.752363354E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>4.894614E7</v>
+        <v>1.03500852E8</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.801309494E9</v>
+        <v>1.855864206E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9526619942596243</v>
+        <v>0.9815144490450425</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>8.9507506E7</v>
+        <v>3.4952794E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11875,20 +11875,20 @@
         <v>5.3038114E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>2146140.0</v>
+        <v>6099252.0</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>5.5184254E7</v>
+        <v>5.9137366E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.587504034919621</v>
+        <v>0.6295897583306718</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>3.8745746E7</v>
+        <v>3.4792634E7</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
         <v>5.3038114E7</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>2146140.0</v>
+        <v>6099252.0</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="2" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
       <c r="AC196" s="2" t="inlineStr"/>
       <c r="AD196" s="2" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>3.8745746E7</v>
+        <v>3.4792634E7</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12244,7 +12244,7 @@
       <c r="O201" s="13" t="inlineStr"/>
       <c r="P201" s="13" t="inlineStr"/>
       <c r="Q201" s="14" t="n">
-        <v>9.945E7</v>
+        <v>1.2285E8</v>
       </c>
       <c r="R201" s="14" t="inlineStr"/>
       <c r="S201" s="14" t="n">
@@ -12257,20 +12257,20 @@
         <v>4.87008E7</v>
       </c>
       <c r="X201" s="14" t="n">
-        <v>2.34E7</v>
+        <v>7.40016E7</v>
       </c>
       <c r="Y201" s="14" t="inlineStr"/>
       <c r="Z201" s="14" t="n">
-        <v>7.21008E7</v>
+        <v>1.227024E8</v>
       </c>
       <c r="AA201" s="14" t="inlineStr"/>
       <c r="AB201" s="14" t="inlineStr"/>
       <c r="AC201" s="15" t="n">
-        <v>0.7249954751131221</v>
+        <v>0.9987985347985348</v>
       </c>
       <c r="AD201" s="15" t="inlineStr"/>
       <c r="AE201" s="14" t="n">
-        <v>2.73492E7</v>
+        <v>147600.0</v>
       </c>
       <c r="AF201" s="14" t="inlineStr"/>
       <c r="AG201" s="14" t="inlineStr"/>
@@ -12358,7 +12358,7 @@
       <c r="O203" s="13" t="inlineStr"/>
       <c r="P203" s="13" t="inlineStr"/>
       <c r="Q203" s="14" t="n">
-        <v>4.68E7</v>
+        <v>2.34E7</v>
       </c>
       <c r="R203" s="14" t="inlineStr"/>
       <c r="S203" s="14" t="n">
@@ -12380,11 +12380,11 @@
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>2.34E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12434,20 +12434,20 @@
         <v>9332000.0</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>0.0</v>
+        <v>1380500.0</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>9332000.0</v>
+        <v>1.07125E7</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.7586991869918699</v>
+        <v>0.8709349593495935</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>2968000.0</v>
+        <v>1587500.0</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12491,20 +12491,20 @@
         <v>5696000.0</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>0.0</v>
+        <v>1380500.0</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>5696000.0</v>
+        <v>7076500.0</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.7302564102564103</v>
+        <v>0.9072435897435898</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>2104000.0</v>
+        <v>723500.0</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       <c r="O207" s="13" t="inlineStr"/>
       <c r="P207" s="13" t="inlineStr"/>
       <c r="Q207" s="14" t="n">
-        <v>7.4556E7</v>
+        <v>8.0556E7</v>
       </c>
       <c r="R207" s="14" t="inlineStr"/>
       <c r="S207" s="14" t="n">
@@ -12620,11 +12620,11 @@
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.7412684425130104</v>
+        <v>0.6860570286508764</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>1.928999E7</v>
+        <v>2.528999E7</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12655,7 +12655,7 @@
       <c r="O208" s="13" t="inlineStr"/>
       <c r="P208" s="13" t="inlineStr"/>
       <c r="Q208" s="14" t="n">
-        <v>7.4556E7</v>
+        <v>7.4476E7</v>
       </c>
       <c r="R208" s="14" t="inlineStr"/>
       <c r="S208" s="14" t="n">
@@ -12677,11 +12677,11 @@
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.7412684425130104</v>
+        <v>0.7420646919813094</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.928999E7</v>
+        <v>1.920999E7</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12696,29 +12696,23 @@
       <c r="E209" s="2" t="inlineStr"/>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I209" s="13" t="inlineStr"/>
-      <c r="J209" s="13" t="inlineStr"/>
-      <c r="K209" s="13" t="inlineStr"/>
-      <c r="L209" s="13" t="inlineStr"/>
-      <c r="M209" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N209" s="13" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000306. Konsumsi Rapat</t>
+          </r>
+        </is>
+      </c>
       <c r="O209" s="13" t="inlineStr"/>
       <c r="P209" s="13" t="inlineStr"/>
       <c r="Q209" s="14" t="n">
-        <v>1.1E7</v>
+        <v>6080000.0</v>
       </c>
       <c r="R209" s="14" t="inlineStr"/>
       <c r="S209" s="14" t="n">
@@ -12728,23 +12722,23 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>4274800.0</v>
+        <v>0.0</v>
       </c>
       <c r="X209" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>4274800.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.3886181818181818</v>
+        <v>0.0</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>6725200.0</v>
+        <v>6080000.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12759,23 +12753,29 @@
       <c r="E210" s="2" t="inlineStr"/>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="2" t="inlineStr"/>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr"/>
-      <c r="N210" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000137. Bahan Komputer</t>
-          </r>
-        </is>
-      </c>
+      <c r="H210" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I210" s="13" t="inlineStr"/>
+      <c r="J210" s="13" t="inlineStr"/>
+      <c r="K210" s="13" t="inlineStr"/>
+      <c r="L210" s="13" t="inlineStr"/>
+      <c r="M210" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N210" s="13" t="inlineStr"/>
       <c r="O210" s="13" t="inlineStr"/>
       <c r="P210" s="13" t="inlineStr"/>
       <c r="Q210" s="14" t="n">
-        <v>9000000.0</v>
+        <v>1.1E7</v>
       </c>
       <c r="R210" s="14" t="inlineStr"/>
       <c r="S210" s="14" t="n">
@@ -12785,23 +12785,23 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>3964800.0</v>
+        <v>4274800.0</v>
       </c>
       <c r="X210" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>3964800.0</v>
+        <v>4274800.0</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.44053333333333333</v>
+        <v>0.3886181818181818</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>5035200.0</v>
+        <v>6725200.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12825,14 +12825,14 @@
       <c r="N211" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000292. ATK</t>
+            <t xml:space="preserve">000137. Bahan Komputer</t>
           </r>
         </is>
       </c>
       <c r="O211" s="13" t="inlineStr"/>
       <c r="P211" s="13" t="inlineStr"/>
       <c r="Q211" s="14" t="n">
-        <v>2000000.0</v>
+        <v>9000000.0</v>
       </c>
       <c r="R211" s="14" t="inlineStr"/>
       <c r="S211" s="14" t="n">
@@ -12842,23 +12842,23 @@
       <c r="U211" s="14" t="inlineStr"/>
       <c r="V211" s="14" t="inlineStr"/>
       <c r="W211" s="14" t="n">
-        <v>310000.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="X211" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>310000.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.155</v>
+        <v>0.44053333333333333</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>1690000.0</v>
+        <v>5035200.0</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
@@ -12873,29 +12873,23 @@
       <c r="E212" s="2" t="inlineStr"/>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I212" s="13" t="inlineStr"/>
-      <c r="J212" s="13" t="inlineStr"/>
-      <c r="K212" s="13" t="inlineStr"/>
-      <c r="L212" s="13" t="inlineStr"/>
-      <c r="M212" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N212" s="13" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000292. ATK</t>
+          </r>
+        </is>
+      </c>
       <c r="O212" s="13" t="inlineStr"/>
       <c r="P212" s="13" t="inlineStr"/>
       <c r="Q212" s="14" t="n">
-        <v>3.011368E9</v>
+        <v>2000000.0</v>
       </c>
       <c r="R212" s="14" t="inlineStr"/>
       <c r="S212" s="14" t="n">
@@ -12905,30 +12899,30 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>2.567718192E9</v>
+        <v>310000.0</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>2.752204692E9</v>
+        <v>310000.0</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.9139383469572633</v>
+        <v>0.155</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>2.59163308E8</v>
+        <v>1690000.0</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
       <c r="AH212" s="14" t="inlineStr"/>
       <c r="AI212" s="14" t="inlineStr"/>
     </row>
-    <row r="213" customHeight="1" ht="18">
+    <row r="213" customHeight="1" ht="15">
       <c r="A213" s="2" t="inlineStr"/>
       <c r="B213" s="2" t="inlineStr"/>
       <c r="C213" s="2" t="inlineStr"/>
@@ -12936,23 +12930,29 @@
       <c r="E213" s="2" t="inlineStr"/>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="inlineStr"/>
-      <c r="M213" s="2" t="inlineStr"/>
-      <c r="N213" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H213" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I213" s="13" t="inlineStr"/>
+      <c r="J213" s="13" t="inlineStr"/>
+      <c r="K213" s="13" t="inlineStr"/>
+      <c r="L213" s="13" t="inlineStr"/>
+      <c r="M213" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N213" s="13" t="inlineStr"/>
       <c r="O213" s="13" t="inlineStr"/>
       <c r="P213" s="13" t="inlineStr"/>
       <c r="Q213" s="14" t="n">
-        <v>4.0995E8</v>
+        <v>3.011368E9</v>
       </c>
       <c r="R213" s="14" t="inlineStr"/>
       <c r="S213" s="14" t="n">
@@ -12962,30 +12962,30 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>2.567718192E9</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>0.0</v>
+        <v>2.21538268E8</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>2.78925646E9</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.9997474423710209</v>
+        <v>0.9262423124639698</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>103536.0</v>
+        <v>2.2211154E8</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
       <c r="AH213" s="14" t="inlineStr"/>
       <c r="AI213" s="14" t="inlineStr"/>
     </row>
-    <row r="214" customHeight="1" ht="15">
+    <row r="214" customHeight="1" ht="18">
       <c r="A214" s="2" t="inlineStr"/>
       <c r="B214" s="2" t="inlineStr"/>
       <c r="C214" s="2" t="inlineStr"/>
@@ -13002,14 +13002,14 @@
       <c r="N214" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
+            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O214" s="13" t="inlineStr"/>
       <c r="P214" s="13" t="inlineStr"/>
       <c r="Q214" s="14" t="n">
-        <v>1.226E8</v>
+        <v>4.0995E8</v>
       </c>
       <c r="R214" s="14" t="inlineStr"/>
       <c r="S214" s="14" t="n">
@@ -13019,30 +13019,30 @@
       <c r="U214" s="14" t="inlineStr"/>
       <c r="V214" s="14" t="inlineStr"/>
       <c r="W214" s="14" t="n">
-        <v>1.0331888E8</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="X214" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
-        <v>1.0331888E8</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="AA214" s="14" t="inlineStr"/>
       <c r="AB214" s="14" t="inlineStr"/>
       <c r="AC214" s="15" t="n">
-        <v>0.842731484502447</v>
+        <v>0.9997474423710209</v>
       </c>
       <c r="AD214" s="15" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
-        <v>1.928112E7</v>
+        <v>103536.0</v>
       </c>
       <c r="AF214" s="14" t="inlineStr"/>
       <c r="AG214" s="14" t="inlineStr"/>
       <c r="AH214" s="14" t="inlineStr"/>
       <c r="AI214" s="14" t="inlineStr"/>
     </row>
-    <row r="215" customHeight="1" ht="18">
+    <row r="215" customHeight="1" ht="15">
       <c r="A215" s="2" t="inlineStr"/>
       <c r="B215" s="2" t="inlineStr"/>
       <c r="C215" s="2" t="inlineStr"/>
@@ -13059,14 +13059,14 @@
       <c r="N215" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
+            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O215" s="13" t="inlineStr"/>
       <c r="P215" s="13" t="inlineStr"/>
       <c r="Q215" s="14" t="n">
-        <v>1.3629E8</v>
+        <v>1.226E8</v>
       </c>
       <c r="R215" s="14" t="inlineStr"/>
       <c r="S215" s="14" t="n">
@@ -13076,23 +13076,23 @@
       <c r="U215" s="14" t="inlineStr"/>
       <c r="V215" s="14" t="inlineStr"/>
       <c r="W215" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>1.0331888E8</v>
       </c>
       <c r="X215" s="14" t="n">
-        <v>0.0</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y215" s="14" t="inlineStr"/>
       <c r="Z215" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>1.12787408E8</v>
       </c>
       <c r="AA215" s="14" t="inlineStr"/>
       <c r="AB215" s="14" t="inlineStr"/>
       <c r="AC215" s="15" t="n">
-        <v>0.9994750605326876</v>
+        <v>0.9199625448613377</v>
       </c>
       <c r="AD215" s="15" t="inlineStr"/>
       <c r="AE215" s="14" t="n">
-        <v>71544.0</v>
+        <v>9812592.0</v>
       </c>
       <c r="AF215" s="14" t="inlineStr"/>
       <c r="AG215" s="14" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       <c r="N216" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O216" s="13" t="inlineStr"/>
       <c r="P216" s="13" t="inlineStr"/>
       <c r="Q216" s="14" t="n">
-        <v>4.59E7</v>
+        <v>1.3629E8</v>
       </c>
       <c r="R216" s="14" t="inlineStr"/>
       <c r="S216" s="14" t="n">
@@ -13133,30 +13133,30 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="X216" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.9996983006535948</v>
+        <v>0.9994750605326876</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>13848.0</v>
+        <v>71544.0</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
       <c r="AH216" s="14" t="inlineStr"/>
       <c r="AI216" s="14" t="inlineStr"/>
     </row>
-    <row r="217" customHeight="1" ht="15">
+    <row r="217" customHeight="1" ht="18">
       <c r="A217" s="2" t="inlineStr"/>
       <c r="B217" s="2" t="inlineStr"/>
       <c r="C217" s="2" t="inlineStr"/>
@@ -13173,14 +13173,14 @@
       <c r="N217" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
+            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O217" s="13" t="inlineStr"/>
       <c r="P217" s="13" t="inlineStr"/>
       <c r="Q217" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>4.59E7</v>
       </c>
       <c r="R217" s="14" t="inlineStr"/>
       <c r="S217" s="14" t="n">
@@ -13190,30 +13190,30 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>1.844865E9</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>2.0293515E9</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9996983006535948</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>13848.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
       <c r="AH217" s="14" t="inlineStr"/>
       <c r="AI217" s="14" t="inlineStr"/>
     </row>
-    <row r="218" customHeight="1" ht="18">
+    <row r="218" customHeight="1" ht="15">
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="2" t="inlineStr"/>
       <c r="C218" s="2" t="inlineStr"/>
@@ -13230,14 +13230,14 @@
       <c r="N218" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
+            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="n">
-        <v>6.89E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="R218" s="14" t="inlineStr"/>
       <c r="S218" s="14" t="n">
@@ -13247,23 +13247,23 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>1.844865E9</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>0.0</v>
+        <v>1.844865E8</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>2.0293515E9</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.33313950653120467</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>4.5946688E7</v>
+        <v>1.844865E8</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13287,14 +13287,14 @@
       <c r="N219" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
+            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>1.389E7</v>
+        <v>6.89E7</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13304,60 +13304,54 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>4629928.0</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>0.0</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>4629928.0</v>
+        <v>4.5906624E7</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.33332814974802016</v>
+        <v>0.6662790130624093</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>9260072.0</v>
+        <v>2.2993376E7</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
       <c r="AH219" s="14" t="inlineStr"/>
       <c r="AI219" s="14" t="inlineStr"/>
     </row>
-    <row r="220" customHeight="1" ht="15">
+    <row r="220" customHeight="1" ht="18">
       <c r="A220" s="2" t="inlineStr"/>
       <c r="B220" s="2" t="inlineStr"/>
       <c r="C220" s="2" t="inlineStr"/>
       <c r="D220" s="2" t="inlineStr"/>
       <c r="E220" s="2" t="inlineStr"/>
-      <c r="F220" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DB</t>
-          </r>
-        </is>
-      </c>
-      <c r="G220" s="13" t="inlineStr"/>
-      <c r="H220" s="13" t="inlineStr"/>
-      <c r="I220" s="13" t="inlineStr"/>
-      <c r="J220" s="13" t="inlineStr"/>
-      <c r="K220" s="13" t="inlineStr"/>
-      <c r="L220" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Langganan Daya dan Jasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="M220" s="13" t="inlineStr"/>
-      <c r="N220" s="13" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
-        <v>7.00144E8</v>
+        <v>1.389E7</v>
       </c>
       <c r="R220" s="14" t="inlineStr"/>
       <c r="S220" s="14" t="n">
@@ -13367,23 +13361,23 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>6.39230607E8</v>
+        <v>4629928.0</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>1216100.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>6.40446707E8</v>
+        <v>9259856.0</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.9147356929431659</v>
+        <v>0.6666562994960403</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>5.9697293E7</v>
+        <v>4630144.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13440,31 +13434,31 @@
       <c r="C222" s="2" t="inlineStr"/>
       <c r="D222" s="2" t="inlineStr"/>
       <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522111</t>
-          </r>
-        </is>
-      </c>
+      <c r="F222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DB</t>
+          </r>
+        </is>
+      </c>
+      <c r="G222" s="13" t="inlineStr"/>
+      <c r="H222" s="13" t="inlineStr"/>
       <c r="I222" s="13" t="inlineStr"/>
       <c r="J222" s="13" t="inlineStr"/>
       <c r="K222" s="13" t="inlineStr"/>
-      <c r="L222" s="13" t="inlineStr"/>
-      <c r="M222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
+      <c r="L222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Langganan Daya dan Jasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="M222" s="13" t="inlineStr"/>
       <c r="N222" s="13" t="inlineStr"/>
       <c r="O222" s="13" t="inlineStr"/>
       <c r="P222" s="13" t="inlineStr"/>
       <c r="Q222" s="14" t="n">
-        <v>5.16E8</v>
+        <v>7.00144E8</v>
       </c>
       <c r="R222" s="14" t="inlineStr"/>
       <c r="S222" s="14" t="n">
@@ -13474,23 +13468,23 @@
       <c r="U222" s="14" t="inlineStr"/>
       <c r="V222" s="14" t="inlineStr"/>
       <c r="W222" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>6.39230607E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>0.0</v>
+        <v>1216100.0</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>6.40446707E8</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.9118486647286822</v>
+        <v>0.9147356929431659</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>4.5486089E7</v>
+        <v>5.9697293E7</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13505,19 +13499,25 @@
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="2" t="inlineStr"/>
-      <c r="J223" s="2" t="inlineStr"/>
-      <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="2" t="inlineStr"/>
-      <c r="M223" s="2" t="inlineStr"/>
-      <c r="N223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000145. Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
+      <c r="H223" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I223" s="13" t="inlineStr"/>
+      <c r="J223" s="13" t="inlineStr"/>
+      <c r="K223" s="13" t="inlineStr"/>
+      <c r="L223" s="13" t="inlineStr"/>
+      <c r="M223" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
+      <c r="N223" s="13" t="inlineStr"/>
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
       <c r="Q223" s="14" t="n">
@@ -13562,29 +13562,23 @@
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522112</t>
-          </r>
-        </is>
-      </c>
-      <c r="I224" s="13" t="inlineStr"/>
-      <c r="J224" s="13" t="inlineStr"/>
-      <c r="K224" s="13" t="inlineStr"/>
-      <c r="L224" s="13" t="inlineStr"/>
-      <c r="M224" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
-      <c r="N224" s="13" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr"/>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000145. Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
       <c r="Q224" s="14" t="n">
-        <v>6000000.0</v>
+        <v>5.16E8</v>
       </c>
       <c r="R224" s="14" t="inlineStr"/>
       <c r="S224" s="14" t="n">
@@ -13594,23 +13588,23 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>5485232.0</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="X224" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>5485232.0</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.9142053333333333</v>
+        <v>0.9118486647286822</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>514768.0</v>
+        <v>4.5486089E7</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13625,19 +13619,25 @@
       <c r="E225" s="2" t="inlineStr"/>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr"/>
-      <c r="I225" s="2" t="inlineStr"/>
-      <c r="J225" s="2" t="inlineStr"/>
-      <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="2" t="inlineStr"/>
-      <c r="M225" s="2" t="inlineStr"/>
-      <c r="N225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000146. Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
+      <c r="H225" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522112</t>
+          </r>
+        </is>
+      </c>
+      <c r="I225" s="13" t="inlineStr"/>
+      <c r="J225" s="13" t="inlineStr"/>
+      <c r="K225" s="13" t="inlineStr"/>
+      <c r="L225" s="13" t="inlineStr"/>
+      <c r="M225" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
+      <c r="N225" s="13" t="inlineStr"/>
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
       <c r="Q225" s="14" t="n">
@@ -13682,29 +13682,23 @@
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522113</t>
-          </r>
-        </is>
-      </c>
-      <c r="I226" s="13" t="inlineStr"/>
-      <c r="J226" s="13" t="inlineStr"/>
-      <c r="K226" s="13" t="inlineStr"/>
-      <c r="L226" s="13" t="inlineStr"/>
-      <c r="M226" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Air</t>
-          </r>
-        </is>
-      </c>
-      <c r="N226" s="13" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr"/>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000146. Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
       <c r="Q226" s="14" t="n">
-        <v>3.3444E7</v>
+        <v>6000000.0</v>
       </c>
       <c r="R226" s="14" t="inlineStr"/>
       <c r="S226" s="14" t="n">
@@ -13714,23 +13708,23 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>3.021E7</v>
+        <v>5485232.0</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>1216100.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>3.14261E7</v>
+        <v>5485232.0</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9396633177849539</v>
+        <v>0.9142053333333333</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>2017900.0</v>
+        <v>514768.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13745,19 +13739,25 @@
       <c r="E227" s="2" t="inlineStr"/>
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr"/>
-      <c r="I227" s="2" t="inlineStr"/>
-      <c r="J227" s="2" t="inlineStr"/>
-      <c r="K227" s="2" t="inlineStr"/>
-      <c r="L227" s="2" t="inlineStr"/>
-      <c r="M227" s="2" t="inlineStr"/>
-      <c r="N227" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H227" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522113</t>
+          </r>
+        </is>
+      </c>
+      <c r="I227" s="13" t="inlineStr"/>
+      <c r="J227" s="13" t="inlineStr"/>
+      <c r="K227" s="13" t="inlineStr"/>
+      <c r="L227" s="13" t="inlineStr"/>
+      <c r="M227" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Air</t>
+          </r>
+        </is>
+      </c>
+      <c r="N227" s="13" t="inlineStr"/>
       <c r="O227" s="13" t="inlineStr"/>
       <c r="P227" s="13" t="inlineStr"/>
       <c r="Q227" s="14" t="n">
@@ -13802,29 +13802,23 @@
       <c r="E228" s="2" t="inlineStr"/>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I228" s="13" t="inlineStr"/>
-      <c r="J228" s="13" t="inlineStr"/>
-      <c r="K228" s="13" t="inlineStr"/>
-      <c r="L228" s="13" t="inlineStr"/>
-      <c r="M228" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N228" s="13" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr"/>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
+          </r>
+        </is>
+      </c>
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
       <c r="Q228" s="14" t="n">
-        <v>1.447E8</v>
+        <v>3.3444E7</v>
       </c>
       <c r="R228" s="14" t="inlineStr"/>
       <c r="S228" s="14" t="n">
@@ -13834,23 +13828,23 @@
       <c r="U228" s="14" t="inlineStr"/>
       <c r="V228" s="14" t="inlineStr"/>
       <c r="W228" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>3.021E7</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>0.0</v>
+        <v>1216100.0</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>3.14261E7</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.919291389080857</v>
+        <v>0.9396633177849539</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>1.1678536E7</v>
+        <v>2017900.0</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13865,23 +13859,29 @@
       <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="2" t="inlineStr"/>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="2" t="inlineStr"/>
-      <c r="N229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000148. Langganan Internet</t>
-          </r>
-        </is>
-      </c>
+      <c r="H229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I229" s="13" t="inlineStr"/>
+      <c r="J229" s="13" t="inlineStr"/>
+      <c r="K229" s="13" t="inlineStr"/>
+      <c r="L229" s="13" t="inlineStr"/>
+      <c r="M229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N229" s="13" t="inlineStr"/>
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>1.146E8</v>
+        <v>1.447E8</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13891,23 +13891,23 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="X229" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.9113045375218151</v>
+        <v>0.919291389080857</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1.01645E7</v>
+        <v>1.1678536E7</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13931,14 +13931,14 @@
       <c r="N230" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
+            <t xml:space="preserve">000148. Langganan Internet</t>
           </r>
         </is>
       </c>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>3.01E7</v>
+        <v>1.146E8</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13948,23 +13948,23 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>1.044355E8</v>
       </c>
       <c r="X230" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>1.044355E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.9496998006644518</v>
+        <v>0.9113045375218151</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>1514036.0</v>
+        <v>1.01645E7</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -13977,31 +13977,25 @@
       <c r="C231" s="2" t="inlineStr"/>
       <c r="D231" s="2" t="inlineStr"/>
       <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DC</t>
-          </r>
-        </is>
-      </c>
-      <c r="G231" s="13" t="inlineStr"/>
-      <c r="H231" s="13" t="inlineStr"/>
-      <c r="I231" s="13" t="inlineStr"/>
-      <c r="J231" s="13" t="inlineStr"/>
-      <c r="K231" s="13" t="inlineStr"/>
-      <c r="L231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pemeliharaan Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M231" s="13" t="inlineStr"/>
-      <c r="N231" s="13" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
+          </r>
+        </is>
+      </c>
       <c r="O231" s="13" t="inlineStr"/>
       <c r="P231" s="13" t="inlineStr"/>
       <c r="Q231" s="14" t="n">
-        <v>1.11442E9</v>
+        <v>3.01E7</v>
       </c>
       <c r="R231" s="14" t="inlineStr"/>
       <c r="S231" s="14" t="n">
@@ -14011,23 +14005,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>6.19636199E8</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>8.0052954E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>6.99689153E8</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.6278504989142334</v>
+        <v>0.9496998006644518</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>4.14730847E8</v>
+        <v>1514036.0</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14040,31 +14034,31 @@
       <c r="C232" s="2" t="inlineStr"/>
       <c r="D232" s="2" t="inlineStr"/>
       <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
+      <c r="F232" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DC</t>
+          </r>
+        </is>
+      </c>
+      <c r="G232" s="13" t="inlineStr"/>
+      <c r="H232" s="13" t="inlineStr"/>
       <c r="I232" s="13" t="inlineStr"/>
       <c r="J232" s="13" t="inlineStr"/>
       <c r="K232" s="13" t="inlineStr"/>
-      <c r="L232" s="13" t="inlineStr"/>
-      <c r="M232" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
+      <c r="L232" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pemeliharaan Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M232" s="13" t="inlineStr"/>
       <c r="N232" s="13" t="inlineStr"/>
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>2.3E8</v>
+        <v>1.10842E9</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14074,23 +14068,23 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>1.9288E8</v>
+        <v>6.19636199E8</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>2.50325E7</v>
+        <v>8.6743092E7</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>2.179125E8</v>
+        <v>7.06379291E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.9474456521739131</v>
+        <v>0.6372848658450768</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>1.20875E7</v>
+        <v>4.02040709E8</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14105,23 +14099,29 @@
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr"/>
-      <c r="I233" s="2" t="inlineStr"/>
-      <c r="J233" s="2" t="inlineStr"/>
-      <c r="K233" s="2" t="inlineStr"/>
-      <c r="L233" s="2" t="inlineStr"/>
-      <c r="M233" s="2" t="inlineStr"/>
-      <c r="N233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
-          </r>
-        </is>
-      </c>
+      <c r="H233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I233" s="13" t="inlineStr"/>
+      <c r="J233" s="13" t="inlineStr"/>
+      <c r="K233" s="13" t="inlineStr"/>
+      <c r="L233" s="13" t="inlineStr"/>
+      <c r="M233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N233" s="13" t="inlineStr"/>
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>1.8E8</v>
+        <v>2.4E8</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14131,23 +14131,23 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>1.5279E8</v>
+        <v>1.9288E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>1.5125E7</v>
+        <v>2.50325E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>1.67915E8</v>
+        <v>2.179125E8</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.9328611111111111</v>
+        <v>0.90796875</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>1.2085E7</v>
+        <v>2.20875E7</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14171,14 +14171,14 @@
       <c r="N234" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
+            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
           </r>
         </is>
       </c>
       <c r="O234" s="13" t="inlineStr"/>
       <c r="P234" s="13" t="inlineStr"/>
       <c r="Q234" s="14" t="n">
-        <v>5.0E7</v>
+        <v>1.8E8</v>
       </c>
       <c r="R234" s="14" t="inlineStr"/>
       <c r="S234" s="14" t="n">
@@ -14188,23 +14188,23 @@
       <c r="U234" s="14" t="inlineStr"/>
       <c r="V234" s="14" t="inlineStr"/>
       <c r="W234" s="14" t="n">
-        <v>4.009E7</v>
+        <v>1.5279E8</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>9907500.0</v>
+        <v>1.5125E7</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>4.99975E7</v>
+        <v>1.67915E8</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.99995</v>
+        <v>0.9328611111111111</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>2500.0</v>
+        <v>1.2085E7</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14219,29 +14219,23 @@
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I235" s="13" t="inlineStr"/>
-      <c r="J235" s="13" t="inlineStr"/>
-      <c r="K235" s="13" t="inlineStr"/>
-      <c r="L235" s="13" t="inlineStr"/>
-      <c r="M235" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N235" s="13" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr"/>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
+          </r>
+        </is>
+      </c>
       <c r="O235" s="13" t="inlineStr"/>
       <c r="P235" s="13" t="inlineStr"/>
       <c r="Q235" s="14" t="n">
-        <v>3.041E7</v>
+        <v>6.0E7</v>
       </c>
       <c r="R235" s="14" t="inlineStr"/>
       <c r="S235" s="14" t="n">
@@ -14251,23 +14245,23 @@
       <c r="U235" s="14" t="inlineStr"/>
       <c r="V235" s="14" t="inlineStr"/>
       <c r="W235" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>4.009E7</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>0.0</v>
+        <v>9907500.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>4.99975E7</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.9998942781979612</v>
+        <v>0.8332916666666667</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>3215.0</v>
+        <v>1.00025E7</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14282,19 +14276,25 @@
       <c r="E236" s="2" t="inlineStr"/>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="2" t="inlineStr"/>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="2" t="inlineStr"/>
-      <c r="M236" s="2" t="inlineStr"/>
-      <c r="N236" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
-          </r>
-        </is>
-      </c>
+      <c r="H236" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I236" s="13" t="inlineStr"/>
+      <c r="J236" s="13" t="inlineStr"/>
+      <c r="K236" s="13" t="inlineStr"/>
+      <c r="L236" s="13" t="inlineStr"/>
+      <c r="M236" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N236" s="13" t="inlineStr"/>
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
@@ -14339,29 +14339,23 @@
       <c r="E237" s="2" t="inlineStr"/>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I237" s="13" t="inlineStr"/>
-      <c r="J237" s="13" t="inlineStr"/>
-      <c r="K237" s="13" t="inlineStr"/>
-      <c r="L237" s="13" t="inlineStr"/>
-      <c r="M237" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N237" s="13" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr"/>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr"/>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
+          </r>
+        </is>
+      </c>
       <c r="O237" s="13" t="inlineStr"/>
       <c r="P237" s="13" t="inlineStr"/>
       <c r="Q237" s="14" t="n">
-        <v>3.7109E8</v>
+        <v>3.041E7</v>
       </c>
       <c r="R237" s="14" t="inlineStr"/>
       <c r="S237" s="14" t="n">
@@ -14371,23 +14365,23 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>1.28808533E8</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>3.0489E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>1.59297533E8</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.4292692689105069</v>
+        <v>0.9998942781979612</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>2.11792467E8</v>
+        <v>3215.0</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14402,23 +14396,29 @@
       <c r="E238" s="2" t="inlineStr"/>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr"/>
-      <c r="I238" s="2" t="inlineStr"/>
-      <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="2" t="inlineStr"/>
-      <c r="M238" s="2" t="inlineStr"/>
-      <c r="N238" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H238" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I238" s="13" t="inlineStr"/>
+      <c r="J238" s="13" t="inlineStr"/>
+      <c r="K238" s="13" t="inlineStr"/>
+      <c r="L238" s="13" t="inlineStr"/>
+      <c r="M238" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N238" s="13" t="inlineStr"/>
       <c r="O238" s="13" t="inlineStr"/>
       <c r="P238" s="13" t="inlineStr"/>
       <c r="Q238" s="14" t="n">
-        <v>1.7E7</v>
+        <v>3.5259E8</v>
       </c>
       <c r="R238" s="14" t="inlineStr"/>
       <c r="S238" s="14" t="n">
@@ -14428,30 +14428,30 @@
       <c r="U238" s="14" t="inlineStr"/>
       <c r="V238" s="14" t="inlineStr"/>
       <c r="W238" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>1.28808533E8</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0489E7</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>1.59297533E8</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.9959777647058824</v>
+        <v>0.4517925437476956</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>68378.0</v>
+        <v>1.93292467E8</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
       <c r="AH238" s="14" t="inlineStr"/>
       <c r="AI238" s="14" t="inlineStr"/>
     </row>
-    <row r="239" customHeight="1" ht="18">
+    <row r="239" customHeight="1" ht="15">
       <c r="A239" s="2" t="inlineStr"/>
       <c r="B239" s="2" t="inlineStr"/>
       <c r="C239" s="2" t="inlineStr"/>
@@ -14468,14 +14468,14 @@
       <c r="N239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
+            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O239" s="13" t="inlineStr"/>
       <c r="P239" s="13" t="inlineStr"/>
       <c r="Q239" s="14" t="n">
-        <v>3.73E7</v>
+        <v>1.7E7</v>
       </c>
       <c r="R239" s="14" t="inlineStr"/>
       <c r="S239" s="14" t="n">
@@ -14485,30 +14485,30 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X239" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.5723136461126005</v>
+        <v>0.9959777647058824</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>1.5952701E7</v>
+        <v>68378.0</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
       <c r="AH239" s="14" t="inlineStr"/>
       <c r="AI239" s="14" t="inlineStr"/>
     </row>
-    <row r="240" customHeight="1" ht="15">
+    <row r="240" customHeight="1" ht="18">
       <c r="A240" s="2" t="inlineStr"/>
       <c r="B240" s="2" t="inlineStr"/>
       <c r="C240" s="2" t="inlineStr"/>
@@ -14525,14 +14525,14 @@
       <c r="N240" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
+            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O240" s="13" t="inlineStr"/>
       <c r="P240" s="13" t="inlineStr"/>
       <c r="Q240" s="14" t="n">
-        <v>2.595E7</v>
+        <v>3.73E7</v>
       </c>
       <c r="R240" s="14" t="inlineStr"/>
       <c r="S240" s="14" t="n">
@@ -14542,23 +14542,23 @@
       <c r="U240" s="14" t="inlineStr"/>
       <c r="V240" s="14" t="inlineStr"/>
       <c r="W240" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="X240" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.5723136461126005</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>623000.0</v>
+        <v>1.5952701E7</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -14582,14 +14582,14 @@
       <c r="N241" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
+            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O241" s="13" t="inlineStr"/>
       <c r="P241" s="13" t="inlineStr"/>
       <c r="Q241" s="14" t="n">
-        <v>2170000.0</v>
+        <v>2.595E7</v>
       </c>
       <c r="R241" s="14" t="inlineStr"/>
       <c r="S241" s="14" t="n">
@@ -14599,23 +14599,23 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>2167000.0</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X241" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>2167000.0</v>
+        <v>2.5327E7</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.9986175115207373</v>
+        <v>0.9759922928709056</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>3000.0</v>
+        <v>623000.0</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14639,14 +14639,14 @@
       <c r="N242" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
+            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>1.341E8</v>
+        <v>2170000.0</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14656,23 +14656,23 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>4421000.0</v>
+        <v>2167000.0</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>2.5076E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>2.9497E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.2199627143922446</v>
+        <v>0.9986175115207373</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>1.04603E8</v>
+        <v>3000.0</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14696,14 +14696,14 @@
       <c r="N243" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
+            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O243" s="13" t="inlineStr"/>
       <c r="P243" s="13" t="inlineStr"/>
       <c r="Q243" s="14" t="n">
-        <v>2800000.0</v>
+        <v>1.156E8</v>
       </c>
       <c r="R243" s="14" t="inlineStr"/>
       <c r="S243" s="14" t="n">
@@ -14713,23 +14713,23 @@
       <c r="U243" s="14" t="inlineStr"/>
       <c r="V243" s="14" t="inlineStr"/>
       <c r="W243" s="14" t="n">
-        <v>1360000.0</v>
+        <v>4421000.0</v>
       </c>
       <c r="X243" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5076E7</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>1360000.0</v>
+        <v>2.9497E7</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.2551643598615917</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>1440000.0</v>
+        <v>8.6103E7</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14753,14 +14753,14 @@
       <c r="N244" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
+            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>2.66E7</v>
+        <v>2800000.0</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14770,23 +14770,23 @@
       <c r="U244" s="14" t="inlineStr"/>
       <c r="V244" s="14" t="inlineStr"/>
       <c r="W244" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1360000.0</v>
       </c>
       <c r="X244" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1360000.0</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.45652714285714285</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>1.4456378E7</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14810,14 +14810,14 @@
       <c r="N245" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
+            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
           </r>
         </is>
       </c>
       <c r="O245" s="13" t="inlineStr"/>
       <c r="P245" s="13" t="inlineStr"/>
       <c r="Q245" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2.66E7</v>
       </c>
       <c r="R245" s="14" t="inlineStr"/>
       <c r="S245" s="14" t="n">
@@ -14827,23 +14827,23 @@
       <c r="U245" s="14" t="inlineStr"/>
       <c r="V245" s="14" t="inlineStr"/>
       <c r="W245" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="X245" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>1.0</v>
+        <v>0.45652714285714285</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>0.0</v>
+        <v>1.4456378E7</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -14867,14 +14867,14 @@
       <c r="N246" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
+            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O246" s="13" t="inlineStr"/>
       <c r="P246" s="13" t="inlineStr"/>
       <c r="Q246" s="14" t="n">
-        <v>4150000.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="R246" s="14" t="inlineStr"/>
       <c r="S246" s="14" t="n">
@@ -14884,23 +14884,23 @@
       <c r="U246" s="14" t="inlineStr"/>
       <c r="V246" s="14" t="inlineStr"/>
       <c r="W246" s="14" t="n">
-        <v>1576500.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="X246" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>1576500.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>0.37987951807228915</v>
+        <v>1.0</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>2573500.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -14924,14 +14924,14 @@
       <c r="N247" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
+            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O247" s="13" t="inlineStr"/>
       <c r="P247" s="13" t="inlineStr"/>
       <c r="Q247" s="14" t="n">
-        <v>4400000.0</v>
+        <v>4150000.0</v>
       </c>
       <c r="R247" s="14" t="inlineStr"/>
       <c r="S247" s="14" t="n">
@@ -14941,23 +14941,23 @@
       <c r="U247" s="14" t="inlineStr"/>
       <c r="V247" s="14" t="inlineStr"/>
       <c r="W247" s="14" t="n">
-        <v>4180000.0</v>
+        <v>1576500.0</v>
       </c>
       <c r="X247" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>4180000.0</v>
+        <v>1576500.0</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.95</v>
+        <v>0.37987951807228915</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>220000.0</v>
+        <v>2573500.0</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
       <c r="N249" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
+            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O249" s="13" t="inlineStr"/>
       <c r="P249" s="13" t="inlineStr"/>
       <c r="Q249" s="14" t="n">
-        <v>4.21E7</v>
+        <v>4400000.0</v>
       </c>
       <c r="R249" s="14" t="inlineStr"/>
       <c r="S249" s="14" t="n">
@@ -15042,23 +15042,23 @@
       <c r="U249" s="14" t="inlineStr"/>
       <c r="V249" s="14" t="inlineStr"/>
       <c r="W249" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>4180000.0</v>
       </c>
       <c r="X249" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>4180000.0</v>
       </c>
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.36304038004750594</v>
+        <v>0.95</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>2.6816E7</v>
+        <v>220000.0</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15082,14 +15082,14 @@
       <c r="N250" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
+            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O250" s="13" t="inlineStr"/>
       <c r="P250" s="13" t="inlineStr"/>
       <c r="Q250" s="14" t="n">
-        <v>3.059E7</v>
+        <v>4.21E7</v>
       </c>
       <c r="R250" s="14" t="inlineStr"/>
       <c r="S250" s="14" t="n">
@@ -15099,23 +15099,23 @@
       <c r="U250" s="14" t="inlineStr"/>
       <c r="V250" s="14" t="inlineStr"/>
       <c r="W250" s="14" t="n">
-        <v>0.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X250" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
-        <v>0.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="AA250" s="14" t="inlineStr"/>
       <c r="AB250" s="14" t="inlineStr"/>
       <c r="AC250" s="15" t="n">
-        <v>0.0</v>
+        <v>0.36304038004750594</v>
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>3.059E7</v>
+        <v>2.6816E7</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15139,14 +15139,14 @@
       <c r="N251" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
+            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O251" s="13" t="inlineStr"/>
       <c r="P251" s="13" t="inlineStr"/>
       <c r="Q251" s="14" t="n">
-        <v>1.0E7</v>
+        <v>3.059E7</v>
       </c>
       <c r="R251" s="14" t="inlineStr"/>
       <c r="S251" s="14" t="n">
@@ -15156,23 +15156,23 @@
       <c r="U251" s="14" t="inlineStr"/>
       <c r="V251" s="14" t="inlineStr"/>
       <c r="W251" s="14" t="n">
-        <v>9640490.0</v>
+        <v>0.0</v>
       </c>
       <c r="X251" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>9640490.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.964049</v>
+        <v>0.0</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>359510.0</v>
+        <v>3.059E7</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15196,14 +15196,14 @@
       <c r="N252" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
+            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
           </r>
         </is>
       </c>
       <c r="O252" s="13" t="inlineStr"/>
       <c r="P252" s="13" t="inlineStr"/>
       <c r="Q252" s="14" t="n">
-        <v>4300000.0</v>
+        <v>1.0E7</v>
       </c>
       <c r="R252" s="14" t="inlineStr"/>
       <c r="S252" s="14" t="n">
@@ -15213,23 +15213,23 @@
       <c r="U252" s="14" t="inlineStr"/>
       <c r="V252" s="14" t="inlineStr"/>
       <c r="W252" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="X252" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.0</v>
+        <v>0.964049</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>4300000.0</v>
+        <v>359510.0</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15253,14 +15253,14 @@
       <c r="N253" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
+            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O253" s="13" t="inlineStr"/>
       <c r="P253" s="13" t="inlineStr"/>
       <c r="Q253" s="14" t="n">
-        <v>5700000.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="R253" s="14" t="inlineStr"/>
       <c r="S253" s="14" t="n">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>5700000.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15310,14 +15310,14 @@
       <c r="N254" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
+            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
           </r>
         </is>
       </c>
       <c r="O254" s="13" t="inlineStr"/>
       <c r="P254" s="13" t="inlineStr"/>
       <c r="Q254" s="14" t="n">
-        <v>9500000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="R254" s="14" t="inlineStr"/>
       <c r="S254" s="14" t="n">
@@ -15330,20 +15330,20 @@
         <v>0.0</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>5413000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>5413000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.5697894736842105</v>
+        <v>0.0</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>4087000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>
@@ -15358,29 +15358,23 @@
       <c r="E255" s="2" t="inlineStr"/>
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523121</t>
-          </r>
-        </is>
-      </c>
-      <c r="I255" s="13" t="inlineStr"/>
-      <c r="J255" s="13" t="inlineStr"/>
-      <c r="K255" s="13" t="inlineStr"/>
-      <c r="L255" s="13" t="inlineStr"/>
-      <c r="M255" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
-          </r>
-        </is>
-      </c>
-      <c r="N255" s="13" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr"/>
+      <c r="I255" s="2" t="inlineStr"/>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr"/>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
+          </r>
+        </is>
+      </c>
       <c r="O255" s="13" t="inlineStr"/>
       <c r="P255" s="13" t="inlineStr"/>
       <c r="Q255" s="14" t="n">
-        <v>3.3E8</v>
+        <v>9500000.0</v>
       </c>
       <c r="R255" s="14" t="inlineStr"/>
       <c r="S255" s="14" t="n">
@@ -15390,23 +15384,23 @@
       <c r="U255" s="14" t="inlineStr"/>
       <c r="V255" s="14" t="inlineStr"/>
       <c r="W255" s="14" t="n">
-        <v>2.06124881E8</v>
+        <v>0.0</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>5396454.0</v>
+        <v>5413000.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>2.11521335E8</v>
+        <v>5413000.0</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.6409737424242424</v>
+        <v>0.5697894736842105</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>1.18478665E8</v>
+        <v>4087000.0</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15421,23 +15415,29 @@
       <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr"/>
-      <c r="I256" s="2" t="inlineStr"/>
-      <c r="J256" s="2" t="inlineStr"/>
-      <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="2" t="inlineStr"/>
-      <c r="M256" s="2" t="inlineStr"/>
-      <c r="N256" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
-          </r>
-        </is>
-      </c>
+      <c r="H256" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523121</t>
+          </r>
+        </is>
+      </c>
+      <c r="I256" s="13" t="inlineStr"/>
+      <c r="J256" s="13" t="inlineStr"/>
+      <c r="K256" s="13" t="inlineStr"/>
+      <c r="L256" s="13" t="inlineStr"/>
+      <c r="M256" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
+          </r>
+        </is>
+      </c>
+      <c r="N256" s="13" t="inlineStr"/>
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>2.257E7</v>
+        <v>3.325E8</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15447,23 +15447,23 @@
       <c r="U256" s="14" t="inlineStr"/>
       <c r="V256" s="14" t="inlineStr"/>
       <c r="W256" s="14" t="n">
-        <v>1.396E7</v>
+        <v>2.06124881E8</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>0.0</v>
+        <v>1.2086592E7</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>1.396E7</v>
+        <v>2.18211473E8</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.618520159503766</v>
+        <v>0.6562751067669172</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>8610000.0</v>
+        <v>1.14288527E8</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15487,14 +15487,14 @@
       <c r="N257" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
+            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
           </r>
         </is>
       </c>
       <c r="O257" s="13" t="inlineStr"/>
       <c r="P257" s="13" t="inlineStr"/>
       <c r="Q257" s="14" t="n">
-        <v>5000000.0</v>
+        <v>2.257E7</v>
       </c>
       <c r="R257" s="14" t="inlineStr"/>
       <c r="S257" s="14" t="n">
@@ -15504,23 +15504,23 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>1287928.0</v>
+        <v>1.396E7</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>1200000.0</v>
+        <v>2890000.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>2487928.0</v>
+        <v>1.685E7</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.4975856</v>
+        <v>0.7465662383695171</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>2512072.0</v>
+        <v>5720000.0</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15544,14 +15544,14 @@
       <c r="N258" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
+            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
           </r>
         </is>
       </c>
       <c r="O258" s="13" t="inlineStr"/>
       <c r="P258" s="13" t="inlineStr"/>
       <c r="Q258" s="14" t="n">
-        <v>4.5E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R258" s="14" t="inlineStr"/>
       <c r="S258" s="14" t="n">
@@ -15561,23 +15561,23 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>2.8040718E7</v>
+        <v>1287928.0</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>1804500.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>2.9845218E7</v>
+        <v>2487928.0</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.6632270666666666</v>
+        <v>0.4975856</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>1.5154782E7</v>
+        <v>2512072.0</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15601,14 +15601,14 @@
       <c r="N259" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
+            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
           </r>
         </is>
       </c>
       <c r="O259" s="13" t="inlineStr"/>
       <c r="P259" s="13" t="inlineStr"/>
       <c r="Q259" s="14" t="n">
-        <v>1.6975E8</v>
+        <v>4.5E7</v>
       </c>
       <c r="R259" s="14" t="inlineStr"/>
       <c r="S259" s="14" t="n">
@@ -15618,23 +15618,23 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>1.20838496E8</v>
+        <v>2.8040718E7</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>1205000.0</v>
+        <v>1804500.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>1.22043496E8</v>
+        <v>2.9845218E7</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.7189602120765832</v>
+        <v>0.6632270666666666</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>4.7706504E7</v>
+        <v>1.5154782E7</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15658,14 +15658,14 @@
       <c r="N260" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
+            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
           </r>
         </is>
       </c>
       <c r="O260" s="13" t="inlineStr"/>
       <c r="P260" s="13" t="inlineStr"/>
       <c r="Q260" s="14" t="n">
-        <v>4500000.0</v>
+        <v>1.6975E8</v>
       </c>
       <c r="R260" s="14" t="inlineStr"/>
       <c r="S260" s="14" t="n">
@@ -15675,23 +15675,23 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>3411992.0</v>
+        <v>1.20838496E8</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>736000.0</v>
+        <v>2695000.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>4147992.0</v>
+        <v>1.23533496E8</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.921776</v>
+        <v>0.7277378262150221</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>352008.0</v>
+        <v>4.6216504E7</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15715,14 +15715,14 @@
       <c r="N261" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
+            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
           </r>
         </is>
       </c>
       <c r="O261" s="13" t="inlineStr"/>
       <c r="P261" s="13" t="inlineStr"/>
       <c r="Q261" s="14" t="n">
-        <v>2.1E7</v>
+        <v>4500000.0</v>
       </c>
       <c r="R261" s="14" t="inlineStr"/>
       <c r="S261" s="14" t="n">
@@ -15732,23 +15732,23 @@
       <c r="U261" s="14" t="inlineStr"/>
       <c r="V261" s="14" t="inlineStr"/>
       <c r="W261" s="14" t="n">
-        <v>1.4290555E7</v>
+        <v>3411992.0</v>
       </c>
       <c r="X261" s="14" t="n">
-        <v>0.0</v>
+        <v>736000.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>1.4290555E7</v>
+        <v>4147992.0</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.680502619047619</v>
+        <v>0.921776</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>6709445.0</v>
+        <v>352008.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15772,14 +15772,14 @@
       <c r="N262" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
+            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
           </r>
         </is>
       </c>
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>9010000.0</v>
+        <v>2.1E7</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15789,23 +15789,23 @@
       <c r="U262" s="14" t="inlineStr"/>
       <c r="V262" s="14" t="inlineStr"/>
       <c r="W262" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="X262" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y262" s="14" t="inlineStr"/>
       <c r="Z262" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.11099356270810211</v>
+        <v>0.680502619047619</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>8009948.0</v>
+        <v>6709445.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15829,14 +15829,14 @@
       <c r="N263" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
           </r>
         </is>
       </c>
       <c r="O263" s="13" t="inlineStr"/>
       <c r="P263" s="13" t="inlineStr"/>
       <c r="Q263" s="14" t="n">
-        <v>4050000.0</v>
+        <v>9010000.0</v>
       </c>
       <c r="R263" s="14" t="inlineStr"/>
       <c r="S263" s="14" t="n">
@@ -15846,23 +15846,23 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>1658480.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>319926.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>1978406.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.4884953086419753</v>
+        <v>0.11099356270810211</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>2071594.0</v>
+        <v>8009948.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15886,14 +15886,14 @@
       <c r="N264" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
+            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
           </r>
         </is>
       </c>
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>1.2E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15903,23 +15903,23 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>8319256.0</v>
+        <v>1658480.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>131028.0</v>
+        <v>319926.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>8450284.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.7041903333333334</v>
+        <v>0.4884953086419753</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>3549716.0</v>
+        <v>2071594.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15943,14 +15943,14 @@
       <c r="N265" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
+            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
           </r>
         </is>
       </c>
       <c r="O265" s="13" t="inlineStr"/>
       <c r="P265" s="13" t="inlineStr"/>
       <c r="Q265" s="14" t="n">
-        <v>1500000.0</v>
+        <v>1.2E7</v>
       </c>
       <c r="R265" s="14" t="inlineStr"/>
       <c r="S265" s="14" t="n">
@@ -15960,23 +15960,23 @@
       <c r="U265" s="14" t="inlineStr"/>
       <c r="V265" s="14" t="inlineStr"/>
       <c r="W265" s="14" t="n">
-        <v>1167558.0</v>
+        <v>8319256.0</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>0.0</v>
+        <v>131028.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>1167558.0</v>
+        <v>8450284.0</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.778372</v>
+        <v>0.7041903333333334</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>332442.0</v>
+        <v>3549716.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -16000,14 +16000,14 @@
       <c r="N266" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
+            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
           </r>
         </is>
       </c>
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>1.562E7</v>
+        <v>1500000.0</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16017,23 +16017,23 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>3760846.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="X266" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>3760846.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.24077119078104994</v>
+        <v>0.778372</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>1.1859154E7</v>
+        <v>332442.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16057,14 +16057,14 @@
       <c r="N267" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
           </r>
         </is>
       </c>
       <c r="O267" s="13" t="inlineStr"/>
       <c r="P267" s="13" t="inlineStr"/>
       <c r="Q267" s="14" t="n">
-        <v>500000.0</v>
+        <v>1.562E7</v>
       </c>
       <c r="R267" s="14" t="inlineStr"/>
       <c r="S267" s="14" t="n">
@@ -16074,23 +16074,23 @@
       <c r="U267" s="14" t="inlineStr"/>
       <c r="V267" s="14" t="inlineStr"/>
       <c r="W267" s="14" t="n">
-        <v>500000.0</v>
+        <v>3760846.0</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>0.0</v>
+        <v>1560138.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>500000.0</v>
+        <v>5320984.0</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>1.0</v>
+        <v>0.3406519846350832</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>0.0</v>
+        <v>1.0299016E7</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16114,14 +16114,14 @@
       <c r="N268" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
+            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
           </r>
         </is>
       </c>
       <c r="O268" s="13" t="inlineStr"/>
       <c r="P268" s="13" t="inlineStr"/>
       <c r="Q268" s="14" t="n">
-        <v>1.3E7</v>
+        <v>500000.0</v>
       </c>
       <c r="R268" s="14" t="inlineStr"/>
       <c r="S268" s="14" t="n">
@@ -16131,23 +16131,23 @@
       <c r="U268" s="14" t="inlineStr"/>
       <c r="V268" s="14" t="inlineStr"/>
       <c r="W268" s="14" t="n">
-        <v>7889000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="X268" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>7889000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.6068461538461538</v>
+        <v>1.0</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>5111000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16171,14 +16171,14 @@
       <c r="N269" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
+            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
           </r>
         </is>
       </c>
       <c r="O269" s="13" t="inlineStr"/>
       <c r="P269" s="13" t="inlineStr"/>
       <c r="Q269" s="14" t="n">
-        <v>5000000.0</v>
+        <v>1.3E7</v>
       </c>
       <c r="R269" s="14" t="inlineStr"/>
       <c r="S269" s="14" t="n">
@@ -16188,23 +16188,23 @@
       <c r="U269" s="14" t="inlineStr"/>
       <c r="V269" s="14" t="inlineStr"/>
       <c r="W269" s="14" t="n">
-        <v>0.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="X269" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>0.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.0</v>
+        <v>0.6068461538461538</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>5000000.0</v>
+        <v>5111000.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16228,14 +16228,14 @@
       <c r="N270" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000305. Pemeliharaan TV</t>
+            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
           </r>
         </is>
       </c>
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>1500000.0</v>
+        <v>2500000.0</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>1500000.0</v>
+        <v>2500000.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16276,29 +16276,23 @@
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523132</t>
-          </r>
-        </is>
-      </c>
-      <c r="I271" s="13" t="inlineStr"/>
-      <c r="J271" s="13" t="inlineStr"/>
-      <c r="K271" s="13" t="inlineStr"/>
-      <c r="L271" s="13" t="inlineStr"/>
-      <c r="M271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N271" s="13" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr"/>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr"/>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000305. Pemeliharaan TV</t>
+          </r>
+        </is>
+      </c>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>1.5292E8</v>
+        <v>1500000.0</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16308,23 +16302,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>0.0</v>
       </c>
       <c r="X271" s="14" t="n">
-        <v>1.9135E7</v>
+        <v>750000.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>8.0551E7</v>
+        <v>750000.0</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.5267525503531258</v>
+        <v>0.5</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>7.2369E7</v>
+        <v>750000.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16348,14 +16342,14 @@
       <c r="N272" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
+            <t xml:space="preserve">000307. Pemeliharaan Meubelair</t>
           </r>
         </is>
       </c>
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>6.216E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16365,23 +16359,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>3.909E7</v>
+        <v>0.0</v>
       </c>
       <c r="X272" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>3.909E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.6288610038610039</v>
+        <v>0.0</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>2.307E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16396,23 +16390,29 @@
       <c r="E273" s="2" t="inlineStr"/>
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr"/>
-      <c r="I273" s="2" t="inlineStr"/>
-      <c r="J273" s="2" t="inlineStr"/>
-      <c r="K273" s="2" t="inlineStr"/>
-      <c r="L273" s="2" t="inlineStr"/>
-      <c r="M273" s="2" t="inlineStr"/>
-      <c r="N273" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H273" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523132</t>
+          </r>
+        </is>
+      </c>
+      <c r="I273" s="13" t="inlineStr"/>
+      <c r="J273" s="13" t="inlineStr"/>
+      <c r="K273" s="13" t="inlineStr"/>
+      <c r="L273" s="13" t="inlineStr"/>
+      <c r="M273" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N273" s="13" t="inlineStr"/>
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>3.07E7</v>
+        <v>1.5292E8</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16422,23 +16422,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>1.155E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="X273" s="14" t="n">
         <v>1.9135E7</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>3.0685E7</v>
+        <v>8.0551E7</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.9995114006514658</v>
+        <v>0.5267525503531258</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>15000.0</v>
+        <v>7.2369E7</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16462,14 +16462,14 @@
       <c r="N274" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>6.006E7</v>
+        <v>6.216E7</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16479,23 +16479,23 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="X274" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.17942057942057943</v>
+        <v>0.6288610038610039</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>4.9284E7</v>
+        <v>2.307E7</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16552,31 +16552,25 @@
       <c r="C276" s="2" t="inlineStr"/>
       <c r="D276" s="2" t="inlineStr"/>
       <c r="E276" s="2" t="inlineStr"/>
-      <c r="F276" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DD</t>
-          </r>
-        </is>
-      </c>
-      <c r="G276" s="13" t="inlineStr"/>
-      <c r="H276" s="13" t="inlineStr"/>
-      <c r="I276" s="13" t="inlineStr"/>
-      <c r="J276" s="13" t="inlineStr"/>
-      <c r="K276" s="13" t="inlineStr"/>
-      <c r="L276" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M276" s="13" t="inlineStr"/>
-      <c r="N276" s="13" t="inlineStr"/>
+      <c r="F276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr"/>
+      <c r="I276" s="2" t="inlineStr"/>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr"/>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
+          </r>
+        </is>
+      </c>
       <c r="O276" s="13" t="inlineStr"/>
       <c r="P276" s="13" t="inlineStr"/>
       <c r="Q276" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>3.07E7</v>
       </c>
       <c r="R276" s="14" t="inlineStr"/>
       <c r="S276" s="14" t="n">
@@ -16586,23 +16580,23 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>1.1092E8</v>
+        <v>1.155E7</v>
       </c>
       <c r="X276" s="14" t="n">
-        <v>1.982E7</v>
+        <v>1.9135E7</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>1.3074E8</v>
+        <v>3.0685E7</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.9891057648660917</v>
+        <v>0.9995114006514658</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>1440000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
@@ -16617,29 +16611,23 @@
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521115</t>
-          </r>
-        </is>
-      </c>
-      <c r="I277" s="13" t="inlineStr"/>
-      <c r="J277" s="13" t="inlineStr"/>
-      <c r="K277" s="13" t="inlineStr"/>
-      <c r="L277" s="13" t="inlineStr"/>
-      <c r="M277" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
-          </r>
-        </is>
-      </c>
-      <c r="N277" s="13" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr"/>
+      <c r="I277" s="2" t="inlineStr"/>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr"/>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+          </r>
+        </is>
+      </c>
       <c r="O277" s="13" t="inlineStr"/>
       <c r="P277" s="13" t="inlineStr"/>
       <c r="Q277" s="14" t="n">
-        <v>1.2468E8</v>
+        <v>6.006E7</v>
       </c>
       <c r="R277" s="14" t="inlineStr"/>
       <c r="S277" s="14" t="n">
@@ -16649,23 +16637,23 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>1.0342E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X277" s="14" t="n">
-        <v>1.982E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>1.2324E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.9884504331087585</v>
+        <v>0.17942057942057943</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>1440000.0</v>
+        <v>4.9284E7</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
@@ -16678,25 +16666,31 @@
       <c r="C278" s="2" t="inlineStr"/>
       <c r="D278" s="2" t="inlineStr"/>
       <c r="E278" s="2" t="inlineStr"/>
-      <c r="F278" s="2" t="inlineStr"/>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr"/>
-      <c r="I278" s="2" t="inlineStr"/>
-      <c r="J278" s="2" t="inlineStr"/>
-      <c r="K278" s="2" t="inlineStr"/>
-      <c r="L278" s="2" t="inlineStr"/>
-      <c r="M278" s="2" t="inlineStr"/>
-      <c r="N278" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
-          </r>
-        </is>
-      </c>
+      <c r="F278" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DD</t>
+          </r>
+        </is>
+      </c>
+      <c r="G278" s="13" t="inlineStr"/>
+      <c r="H278" s="13" t="inlineStr"/>
+      <c r="I278" s="13" t="inlineStr"/>
+      <c r="J278" s="13" t="inlineStr"/>
+      <c r="K278" s="13" t="inlineStr"/>
+      <c r="L278" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M278" s="13" t="inlineStr"/>
+      <c r="N278" s="13" t="inlineStr"/>
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.3218E8</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16706,23 +16700,23 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>2.55E7</v>
+        <v>1.1092E8</v>
       </c>
       <c r="X278" s="14" t="n">
-        <v>5100000.0</v>
+        <v>2.03E7</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.3122E8</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9927371765773945</v>
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>0.0</v>
+        <v>960000.0</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
@@ -16737,23 +16731,29 @@
       <c r="E279" s="2" t="inlineStr"/>
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr"/>
-      <c r="I279" s="2" t="inlineStr"/>
-      <c r="J279" s="2" t="inlineStr"/>
-      <c r="K279" s="2" t="inlineStr"/>
-      <c r="L279" s="2" t="inlineStr"/>
-      <c r="M279" s="2" t="inlineStr"/>
-      <c r="N279" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
-          </r>
-        </is>
-      </c>
+      <c r="H279" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521115</t>
+          </r>
+        </is>
+      </c>
+      <c r="I279" s="13" t="inlineStr"/>
+      <c r="J279" s="13" t="inlineStr"/>
+      <c r="K279" s="13" t="inlineStr"/>
+      <c r="L279" s="13" t="inlineStr"/>
+      <c r="M279" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+          </r>
+        </is>
+      </c>
+      <c r="N279" s="13" t="inlineStr"/>
       <c r="O279" s="13" t="inlineStr"/>
       <c r="P279" s="13" t="inlineStr"/>
       <c r="Q279" s="14" t="n">
-        <v>2.976E7</v>
+        <v>1.2468E8</v>
       </c>
       <c r="R279" s="14" t="inlineStr"/>
       <c r="S279" s="14" t="n">
@@ -16763,30 +16763,30 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>2.48E7</v>
+        <v>1.0342E8</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>4960000.0</v>
+        <v>2.03E7</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>2.976E7</v>
+        <v>1.2372E8</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9923002887391723</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>0.0</v>
+        <v>960000.0</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
       <c r="AH279" s="14" t="inlineStr"/>
       <c r="AI279" s="14" t="inlineStr"/>
     </row>
-    <row r="280" customHeight="1" ht="18">
+    <row r="280" customHeight="1" ht="15">
       <c r="A280" s="2" t="inlineStr"/>
       <c r="B280" s="2" t="inlineStr"/>
       <c r="C280" s="2" t="inlineStr"/>
@@ -16803,14 +16803,14 @@
       <c r="N280" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
           </r>
         </is>
       </c>
       <c r="O280" s="13" t="inlineStr"/>
       <c r="P280" s="13" t="inlineStr"/>
       <c r="Q280" s="14" t="n">
-        <v>1.476E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="R280" s="14" t="inlineStr"/>
       <c r="S280" s="14" t="n">
@@ -16820,14 +16820,14 @@
       <c r="U280" s="14" t="inlineStr"/>
       <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="n">
-        <v>1.23E7</v>
+        <v>2.55E7</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>2460000.0</v>
+        <v>5100000.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>1.476E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
@@ -16860,14 +16860,14 @@
       <c r="N281" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
+            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
           </r>
         </is>
       </c>
       <c r="O281" s="13" t="inlineStr"/>
       <c r="P281" s="13" t="inlineStr"/>
       <c r="Q281" s="14" t="n">
-        <v>1.284E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="R281" s="14" t="inlineStr"/>
       <c r="S281" s="14" t="n">
@@ -16877,14 +16877,14 @@
       <c r="U281" s="14" t="inlineStr"/>
       <c r="V281" s="14" t="inlineStr"/>
       <c r="W281" s="14" t="n">
-        <v>1.07E7</v>
+        <v>2.48E7</v>
       </c>
       <c r="X281" s="14" t="n">
-        <v>2140000.0</v>
+        <v>4960000.0</v>
       </c>
       <c r="Y281" s="14" t="inlineStr"/>
       <c r="Z281" s="14" t="n">
-        <v>1.284E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="AA281" s="14" t="inlineStr"/>
       <c r="AB281" s="14" t="inlineStr"/>
@@ -16900,7 +16900,7 @@
       <c r="AH281" s="14" t="inlineStr"/>
       <c r="AI281" s="14" t="inlineStr"/>
     </row>
-    <row r="282" customHeight="1" ht="15">
+    <row r="282" customHeight="1" ht="18">
       <c r="A282" s="2" t="inlineStr"/>
       <c r="B282" s="2" t="inlineStr"/>
       <c r="C282" s="2" t="inlineStr"/>
@@ -16917,14 +16917,14 @@
       <c r="N282" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
+            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
           </r>
         </is>
       </c>
       <c r="O282" s="13" t="inlineStr"/>
       <c r="P282" s="13" t="inlineStr"/>
       <c r="Q282" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="R282" s="14" t="inlineStr"/>
       <c r="S282" s="14" t="n">
@@ -16934,14 +16934,14 @@
       <c r="U282" s="14" t="inlineStr"/>
       <c r="V282" s="14" t="inlineStr"/>
       <c r="W282" s="14" t="n">
-        <v>2.4E7</v>
+        <v>1.23E7</v>
       </c>
       <c r="X282" s="14" t="n">
-        <v>4800000.0</v>
+        <v>2460000.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
@@ -16974,14 +16974,14 @@
       <c r="N283" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
           </r>
         </is>
       </c>
       <c r="O283" s="13" t="inlineStr"/>
       <c r="P283" s="13" t="inlineStr"/>
       <c r="Q283" s="14" t="n">
-        <v>3600000.0</v>
+        <v>1.284E7</v>
       </c>
       <c r="R283" s="14" t="inlineStr"/>
       <c r="S283" s="14" t="n">
@@ -16991,30 +16991,30 @@
       <c r="U283" s="14" t="inlineStr"/>
       <c r="V283" s="14" t="inlineStr"/>
       <c r="W283" s="14" t="n">
-        <v>2700000.0</v>
+        <v>1.07E7</v>
       </c>
       <c r="X283" s="14" t="n">
-        <v>0.0</v>
+        <v>2140000.0</v>
       </c>
       <c r="Y283" s="14" t="inlineStr"/>
       <c r="Z283" s="14" t="n">
-        <v>2700000.0</v>
+        <v>1.284E7</v>
       </c>
       <c r="AA283" s="14" t="inlineStr"/>
       <c r="AB283" s="14" t="inlineStr"/>
       <c r="AC283" s="15" t="n">
-        <v>0.75</v>
+        <v>1.0</v>
       </c>
       <c r="AD283" s="15" t="inlineStr"/>
       <c r="AE283" s="14" t="n">
-        <v>900000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF283" s="14" t="inlineStr"/>
       <c r="AG283" s="14" t="inlineStr"/>
       <c r="AH283" s="14" t="inlineStr"/>
       <c r="AI283" s="14" t="inlineStr"/>
     </row>
-    <row r="284" customHeight="1" ht="18">
+    <row r="284" customHeight="1" ht="15">
       <c r="A284" s="2" t="inlineStr"/>
       <c r="B284" s="2" t="inlineStr"/>
       <c r="C284" s="2" t="inlineStr"/>
@@ -17031,14 +17031,14 @@
       <c r="N284" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
           </r>
         </is>
       </c>
       <c r="O284" s="13" t="inlineStr"/>
       <c r="P284" s="13" t="inlineStr"/>
       <c r="Q284" s="14" t="n">
-        <v>4320000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="R284" s="14" t="inlineStr"/>
       <c r="S284" s="14" t="n">
@@ -17048,23 +17048,23 @@
       <c r="U284" s="14" t="inlineStr"/>
       <c r="V284" s="14" t="inlineStr"/>
       <c r="W284" s="14" t="n">
-        <v>3420000.0</v>
+        <v>2.4E7</v>
       </c>
       <c r="X284" s="14" t="n">
-        <v>360000.0</v>
+        <v>4800000.0</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
-        <v>3780000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="AA284" s="14" t="inlineStr"/>
       <c r="AB284" s="14" t="inlineStr"/>
       <c r="AC284" s="15" t="n">
-        <v>0.875</v>
+        <v>1.0</v>
       </c>
       <c r="AD284" s="15" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
-        <v>540000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF284" s="14" t="inlineStr"/>
       <c r="AG284" s="14" t="inlineStr"/>
@@ -17079,29 +17079,23 @@
       <c r="E285" s="2" t="inlineStr"/>
       <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I285" s="13" t="inlineStr"/>
-      <c r="J285" s="13" t="inlineStr"/>
-      <c r="K285" s="13" t="inlineStr"/>
-      <c r="L285" s="13" t="inlineStr"/>
-      <c r="M285" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N285" s="13" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
+      <c r="I285" s="2" t="inlineStr"/>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr"/>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+          </r>
+        </is>
+      </c>
       <c r="O285" s="13" t="inlineStr"/>
       <c r="P285" s="13" t="inlineStr"/>
       <c r="Q285" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="R285" s="14" t="inlineStr"/>
       <c r="S285" s="14" t="n">
@@ -17111,30 +17105,30 @@
       <c r="U285" s="14" t="inlineStr"/>
       <c r="V285" s="14" t="inlineStr"/>
       <c r="W285" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="X285" s="14" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="Y285" s="14" t="inlineStr"/>
       <c r="Z285" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="AA285" s="14" t="inlineStr"/>
       <c r="AB285" s="14" t="inlineStr"/>
       <c r="AC285" s="15" t="n">
-        <v>1.0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AD285" s="15" t="inlineStr"/>
       <c r="AE285" s="14" t="n">
-        <v>0.0</v>
+        <v>600000.0</v>
       </c>
       <c r="AF285" s="14" t="inlineStr"/>
       <c r="AG285" s="14" t="inlineStr"/>
       <c r="AH285" s="14" t="inlineStr"/>
       <c r="AI285" s="14" t="inlineStr"/>
     </row>
-    <row r="286" customHeight="1" ht="15">
+    <row r="286" customHeight="1" ht="18">
       <c r="A286" s="2" t="inlineStr"/>
       <c r="B286" s="2" t="inlineStr"/>
       <c r="C286" s="2" t="inlineStr"/>
@@ -17151,14 +17145,14 @@
       <c r="N286" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
           </r>
         </is>
       </c>
       <c r="O286" s="13" t="inlineStr"/>
       <c r="P286" s="13" t="inlineStr"/>
       <c r="Q286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="R286" s="14" t="inlineStr"/>
       <c r="S286" s="14" t="n">
@@ -17168,23 +17162,23 @@
       <c r="U286" s="14" t="inlineStr"/>
       <c r="V286" s="14" t="inlineStr"/>
       <c r="W286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3420000.0</v>
       </c>
       <c r="X286" s="14" t="n">
-        <v>0.0</v>
+        <v>540000.0</v>
       </c>
       <c r="Y286" s="14" t="inlineStr"/>
       <c r="Z286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3960000.0</v>
       </c>
       <c r="AA286" s="14" t="inlineStr"/>
       <c r="AB286" s="14" t="inlineStr"/>
       <c r="AC286" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AD286" s="15" t="inlineStr"/>
       <c r="AE286" s="14" t="n">
-        <v>0.0</v>
+        <v>360000.0</v>
       </c>
       <c r="AF286" s="14" t="inlineStr"/>
       <c r="AG286" s="14" t="inlineStr"/>
@@ -17194,317 +17188,311 @@
     <row r="287" customHeight="1" ht="15">
       <c r="A287" s="2" t="inlineStr"/>
       <c r="B287" s="2" t="inlineStr"/>
-      <c r="C287" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D287" s="16" t="inlineStr"/>
-      <c r="E287" s="16" t="inlineStr"/>
-      <c r="F287" s="16" t="inlineStr"/>
-      <c r="G287" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H287" s="16" t="inlineStr"/>
-      <c r="I287" s="16" t="inlineStr"/>
-      <c r="J287" s="16" t="inlineStr"/>
-      <c r="K287" s="16" t="inlineStr"/>
-      <c r="L287" s="16" t="inlineStr"/>
-      <c r="M287" s="16" t="inlineStr"/>
-      <c r="N287" s="16" t="inlineStr"/>
-      <c r="O287" s="16" t="inlineStr"/>
-      <c r="P287" s="16" t="inlineStr"/>
-      <c r="Q287" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R287" s="17" t="inlineStr"/>
-      <c r="S287" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T287" s="17" t="inlineStr"/>
-      <c r="U287" s="17" t="inlineStr"/>
-      <c r="V287" s="17" t="inlineStr"/>
-      <c r="W287" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X287" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y287" s="17" t="inlineStr"/>
-      <c r="Z287" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA287" s="17" t="inlineStr"/>
-      <c r="AB287" s="17" t="inlineStr"/>
-      <c r="AC287" s="18" t="n">
+      <c r="C287" s="2" t="inlineStr"/>
+      <c r="D287" s="2" t="inlineStr"/>
+      <c r="E287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I287" s="13" t="inlineStr"/>
+      <c r="J287" s="13" t="inlineStr"/>
+      <c r="K287" s="13" t="inlineStr"/>
+      <c r="L287" s="13" t="inlineStr"/>
+      <c r="M287" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N287" s="13" t="inlineStr"/>
+      <c r="O287" s="13" t="inlineStr"/>
+      <c r="P287" s="13" t="inlineStr"/>
+      <c r="Q287" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R287" s="14" t="inlineStr"/>
+      <c r="S287" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T287" s="14" t="inlineStr"/>
+      <c r="U287" s="14" t="inlineStr"/>
+      <c r="V287" s="14" t="inlineStr"/>
+      <c r="W287" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X287" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y287" s="14" t="inlineStr"/>
+      <c r="Z287" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA287" s="14" t="inlineStr"/>
+      <c r="AB287" s="14" t="inlineStr"/>
+      <c r="AC287" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD287" s="18" t="inlineStr"/>
-      <c r="AE287" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF287" s="17" t="inlineStr"/>
-      <c r="AG287" s="17" t="inlineStr"/>
-      <c r="AH287" s="17" t="inlineStr"/>
-      <c r="AI287" s="17" t="inlineStr"/>
+      <c r="AD287" s="15" t="inlineStr"/>
+      <c r="AE287" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF287" s="14" t="inlineStr"/>
+      <c r="AG287" s="14" t="inlineStr"/>
+      <c r="AH287" s="14" t="inlineStr"/>
+      <c r="AI287" s="14" t="inlineStr"/>
     </row>
     <row r="288" customHeight="1" ht="15">
       <c r="A288" s="2" t="inlineStr"/>
       <c r="B288" s="2" t="inlineStr"/>
-      <c r="C288" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D288" s="28" t="inlineStr"/>
-      <c r="E288" s="28" t="inlineStr"/>
-      <c r="F288" s="28" t="inlineStr"/>
-      <c r="G288" s="28" t="inlineStr"/>
-      <c r="H288" s="28" t="inlineStr"/>
-      <c r="I288" s="28" t="inlineStr"/>
-      <c r="J288" s="28" t="inlineStr"/>
-      <c r="K288" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L288" s="20" t="inlineStr"/>
-      <c r="M288" s="20" t="inlineStr"/>
-      <c r="N288" s="20" t="inlineStr"/>
-      <c r="O288" s="20" t="inlineStr"/>
-      <c r="P288" s="20" t="inlineStr"/>
-      <c r="Q288" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R288" s="21" t="inlineStr"/>
-      <c r="S288" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T288" s="21" t="inlineStr"/>
-      <c r="U288" s="21" t="inlineStr"/>
-      <c r="V288" s="21" t="inlineStr"/>
-      <c r="W288" s="22" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X288" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y288" s="22" t="inlineStr"/>
-      <c r="Z288" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA288" s="21" t="inlineStr"/>
-      <c r="AB288" s="21" t="inlineStr"/>
-      <c r="AC288" s="23" t="n">
+      <c r="C288" s="2" t="inlineStr"/>
+      <c r="D288" s="2" t="inlineStr"/>
+      <c r="E288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr"/>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="O288" s="13" t="inlineStr"/>
+      <c r="P288" s="13" t="inlineStr"/>
+      <c r="Q288" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R288" s="14" t="inlineStr"/>
+      <c r="S288" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T288" s="14" t="inlineStr"/>
+      <c r="U288" s="14" t="inlineStr"/>
+      <c r="V288" s="14" t="inlineStr"/>
+      <c r="W288" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X288" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y288" s="14" t="inlineStr"/>
+      <c r="Z288" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA288" s="14" t="inlineStr"/>
+      <c r="AB288" s="14" t="inlineStr"/>
+      <c r="AC288" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD288" s="23" t="inlineStr"/>
-      <c r="AE288" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF288" s="21" t="inlineStr"/>
-      <c r="AG288" s="21" t="inlineStr"/>
-      <c r="AH288" s="21" t="inlineStr"/>
-      <c r="AI288" s="21" t="inlineStr"/>
+      <c r="AD288" s="15" t="inlineStr"/>
+      <c r="AE288" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF288" s="14" t="inlineStr"/>
+      <c r="AG288" s="14" t="inlineStr"/>
+      <c r="AH288" s="14" t="inlineStr"/>
+      <c r="AI288" s="14" t="inlineStr"/>
     </row>
     <row r="289" customHeight="1" ht="15">
       <c r="A289" s="2" t="inlineStr"/>
       <c r="B289" s="2" t="inlineStr"/>
-      <c r="C289" s="2" t="inlineStr"/>
-      <c r="D289" s="2" t="inlineStr"/>
-      <c r="E289" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F289" s="24" t="inlineStr"/>
-      <c r="G289" s="24" t="inlineStr"/>
-      <c r="H289" s="24" t="inlineStr"/>
-      <c r="I289" s="24" t="inlineStr"/>
-      <c r="J289" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K289" s="24" t="inlineStr"/>
-      <c r="L289" s="24" t="inlineStr"/>
-      <c r="M289" s="24" t="inlineStr"/>
-      <c r="N289" s="24" t="inlineStr"/>
-      <c r="O289" s="24" t="inlineStr"/>
-      <c r="P289" s="24" t="inlineStr"/>
-      <c r="Q289" s="25" t="n">
+      <c r="C289" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D289" s="16" t="inlineStr"/>
+      <c r="E289" s="16" t="inlineStr"/>
+      <c r="F289" s="16" t="inlineStr"/>
+      <c r="G289" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H289" s="16" t="inlineStr"/>
+      <c r="I289" s="16" t="inlineStr"/>
+      <c r="J289" s="16" t="inlineStr"/>
+      <c r="K289" s="16" t="inlineStr"/>
+      <c r="L289" s="16" t="inlineStr"/>
+      <c r="M289" s="16" t="inlineStr"/>
+      <c r="N289" s="16" t="inlineStr"/>
+      <c r="O289" s="16" t="inlineStr"/>
+      <c r="P289" s="16" t="inlineStr"/>
+      <c r="Q289" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R289" s="25" t="inlineStr"/>
-      <c r="S289" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T289" s="25" t="inlineStr"/>
-      <c r="U289" s="25" t="inlineStr"/>
-      <c r="V289" s="25" t="inlineStr"/>
-      <c r="W289" s="25" t="n">
+      <c r="R289" s="17" t="inlineStr"/>
+      <c r="S289" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T289" s="17" t="inlineStr"/>
+      <c r="U289" s="17" t="inlineStr"/>
+      <c r="V289" s="17" t="inlineStr"/>
+      <c r="W289" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X289" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y289" s="25" t="inlineStr"/>
-      <c r="Z289" s="25" t="n">
+      <c r="X289" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y289" s="17" t="inlineStr"/>
+      <c r="Z289" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA289" s="25" t="inlineStr"/>
-      <c r="AB289" s="25" t="inlineStr"/>
-      <c r="AC289" s="26" t="n">
+      <c r="AA289" s="17" t="inlineStr"/>
+      <c r="AB289" s="17" t="inlineStr"/>
+      <c r="AC289" s="18" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD289" s="26" t="inlineStr"/>
-      <c r="AE289" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF289" s="25" t="inlineStr"/>
-      <c r="AG289" s="25" t="inlineStr"/>
-      <c r="AH289" s="25" t="inlineStr"/>
-      <c r="AI289" s="25" t="inlineStr"/>
+      <c r="AD289" s="18" t="inlineStr"/>
+      <c r="AE289" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF289" s="17" t="inlineStr"/>
+      <c r="AG289" s="17" t="inlineStr"/>
+      <c r="AH289" s="17" t="inlineStr"/>
+      <c r="AI289" s="17" t="inlineStr"/>
     </row>
     <row r="290" customHeight="1" ht="15">
       <c r="A290" s="2" t="inlineStr"/>
       <c r="B290" s="2" t="inlineStr"/>
-      <c r="C290" s="2" t="inlineStr"/>
-      <c r="D290" s="2" t="inlineStr"/>
-      <c r="E290" s="2" t="inlineStr"/>
-      <c r="F290" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G290" s="13" t="inlineStr"/>
-      <c r="H290" s="13" t="inlineStr"/>
-      <c r="I290" s="13" t="inlineStr"/>
-      <c r="J290" s="13" t="inlineStr"/>
-      <c r="K290" s="13" t="inlineStr"/>
-      <c r="L290" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M290" s="13" t="inlineStr"/>
-      <c r="N290" s="13" t="inlineStr"/>
-      <c r="O290" s="13" t="inlineStr"/>
-      <c r="P290" s="13" t="inlineStr"/>
-      <c r="Q290" s="14" t="n">
+      <c r="C290" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D290" s="28" t="inlineStr"/>
+      <c r="E290" s="28" t="inlineStr"/>
+      <c r="F290" s="28" t="inlineStr"/>
+      <c r="G290" s="28" t="inlineStr"/>
+      <c r="H290" s="28" t="inlineStr"/>
+      <c r="I290" s="28" t="inlineStr"/>
+      <c r="J290" s="28" t="inlineStr"/>
+      <c r="K290" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L290" s="20" t="inlineStr"/>
+      <c r="M290" s="20" t="inlineStr"/>
+      <c r="N290" s="20" t="inlineStr"/>
+      <c r="O290" s="20" t="inlineStr"/>
+      <c r="P290" s="20" t="inlineStr"/>
+      <c r="Q290" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R290" s="14" t="inlineStr"/>
-      <c r="S290" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T290" s="14" t="inlineStr"/>
-      <c r="U290" s="14" t="inlineStr"/>
-      <c r="V290" s="14" t="inlineStr"/>
-      <c r="W290" s="14" t="n">
+      <c r="R290" s="21" t="inlineStr"/>
+      <c r="S290" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T290" s="21" t="inlineStr"/>
+      <c r="U290" s="21" t="inlineStr"/>
+      <c r="V290" s="21" t="inlineStr"/>
+      <c r="W290" s="22" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X290" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y290" s="14" t="inlineStr"/>
-      <c r="Z290" s="14" t="n">
+      <c r="X290" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y290" s="22" t="inlineStr"/>
+      <c r="Z290" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA290" s="14" t="inlineStr"/>
-      <c r="AB290" s="14" t="inlineStr"/>
-      <c r="AC290" s="15" t="n">
+      <c r="AA290" s="21" t="inlineStr"/>
+      <c r="AB290" s="21" t="inlineStr"/>
+      <c r="AC290" s="23" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD290" s="15" t="inlineStr"/>
-      <c r="AE290" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF290" s="14" t="inlineStr"/>
-      <c r="AG290" s="14" t="inlineStr"/>
-      <c r="AH290" s="14" t="inlineStr"/>
-      <c r="AI290" s="14" t="inlineStr"/>
+      <c r="AD290" s="23" t="inlineStr"/>
+      <c r="AE290" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF290" s="21" t="inlineStr"/>
+      <c r="AG290" s="21" t="inlineStr"/>
+      <c r="AH290" s="21" t="inlineStr"/>
+      <c r="AI290" s="21" t="inlineStr"/>
     </row>
     <row r="291" customHeight="1" ht="15">
       <c r="A291" s="2" t="inlineStr"/>
       <c r="B291" s="2" t="inlineStr"/>
       <c r="C291" s="2" t="inlineStr"/>
       <c r="D291" s="2" t="inlineStr"/>
-      <c r="E291" s="2" t="inlineStr"/>
-      <c r="F291" s="2" t="inlineStr"/>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">524111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I291" s="13" t="inlineStr"/>
-      <c r="J291" s="13" t="inlineStr"/>
-      <c r="K291" s="13" t="inlineStr"/>
-      <c r="L291" s="13" t="inlineStr"/>
-      <c r="M291" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="N291" s="13" t="inlineStr"/>
-      <c r="O291" s="13" t="inlineStr"/>
-      <c r="P291" s="13" t="inlineStr"/>
-      <c r="Q291" s="14" t="n">
+      <c r="E291" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F291" s="24" t="inlineStr"/>
+      <c r="G291" s="24" t="inlineStr"/>
+      <c r="H291" s="24" t="inlineStr"/>
+      <c r="I291" s="24" t="inlineStr"/>
+      <c r="J291" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K291" s="24" t="inlineStr"/>
+      <c r="L291" s="24" t="inlineStr"/>
+      <c r="M291" s="24" t="inlineStr"/>
+      <c r="N291" s="24" t="inlineStr"/>
+      <c r="O291" s="24" t="inlineStr"/>
+      <c r="P291" s="24" t="inlineStr"/>
+      <c r="Q291" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R291" s="14" t="inlineStr"/>
-      <c r="S291" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T291" s="14" t="inlineStr"/>
-      <c r="U291" s="14" t="inlineStr"/>
-      <c r="V291" s="14" t="inlineStr"/>
-      <c r="W291" s="14" t="n">
+      <c r="R291" s="25" t="inlineStr"/>
+      <c r="S291" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T291" s="25" t="inlineStr"/>
+      <c r="U291" s="25" t="inlineStr"/>
+      <c r="V291" s="25" t="inlineStr"/>
+      <c r="W291" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X291" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y291" s="14" t="inlineStr"/>
-      <c r="Z291" s="14" t="n">
+      <c r="X291" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y291" s="25" t="inlineStr"/>
+      <c r="Z291" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA291" s="14" t="inlineStr"/>
-      <c r="AB291" s="14" t="inlineStr"/>
-      <c r="AC291" s="15" t="n">
+      <c r="AA291" s="25" t="inlineStr"/>
+      <c r="AB291" s="25" t="inlineStr"/>
+      <c r="AC291" s="26" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD291" s="15" t="inlineStr"/>
-      <c r="AE291" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF291" s="14" t="inlineStr"/>
-      <c r="AG291" s="14" t="inlineStr"/>
-      <c r="AH291" s="14" t="inlineStr"/>
-      <c r="AI291" s="14" t="inlineStr"/>
+      <c r="AD291" s="26" t="inlineStr"/>
+      <c r="AE291" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF291" s="25" t="inlineStr"/>
+      <c r="AG291" s="25" t="inlineStr"/>
+      <c r="AH291" s="25" t="inlineStr"/>
+      <c r="AI291" s="25" t="inlineStr"/>
     </row>
     <row r="292" customHeight="1" ht="15">
       <c r="A292" s="2" t="inlineStr"/>
@@ -17512,21 +17500,27 @@
       <c r="C292" s="2" t="inlineStr"/>
       <c r="D292" s="2" t="inlineStr"/>
       <c r="E292" s="2" t="inlineStr"/>
-      <c r="F292" s="2" t="inlineStr"/>
-      <c r="G292" s="2" t="inlineStr"/>
-      <c r="H292" s="2" t="inlineStr"/>
-      <c r="I292" s="2" t="inlineStr"/>
-      <c r="J292" s="2" t="inlineStr"/>
-      <c r="K292" s="2" t="inlineStr"/>
-      <c r="L292" s="2" t="inlineStr"/>
-      <c r="M292" s="2" t="inlineStr"/>
-      <c r="N292" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000231. Uang Harian</t>
-          </r>
-        </is>
-      </c>
+      <c r="F292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G292" s="13" t="inlineStr"/>
+      <c r="H292" s="13" t="inlineStr"/>
+      <c r="I292" s="13" t="inlineStr"/>
+      <c r="J292" s="13" t="inlineStr"/>
+      <c r="K292" s="13" t="inlineStr"/>
+      <c r="L292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M292" s="13" t="inlineStr"/>
+      <c r="N292" s="13" t="inlineStr"/>
       <c r="O292" s="13" t="inlineStr"/>
       <c r="P292" s="13" t="inlineStr"/>
       <c r="Q292" s="14" t="n">
@@ -17563,9 +17557,129 @@
       <c r="AH292" s="14" t="inlineStr"/>
       <c r="AI292" s="14" t="inlineStr"/>
     </row>
-    <row r="293" customHeight="1" ht="24">
+    <row r="293" customHeight="1" ht="15">
       <c r="A293" s="2" t="inlineStr"/>
-      <c r="B293" s="27" t="inlineStr">
+      <c r="B293" s="2" t="inlineStr"/>
+      <c r="C293" s="2" t="inlineStr"/>
+      <c r="D293" s="2" t="inlineStr"/>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I293" s="13" t="inlineStr"/>
+      <c r="J293" s="13" t="inlineStr"/>
+      <c r="K293" s="13" t="inlineStr"/>
+      <c r="L293" s="13" t="inlineStr"/>
+      <c r="M293" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N293" s="13" t="inlineStr"/>
+      <c r="O293" s="13" t="inlineStr"/>
+      <c r="P293" s="13" t="inlineStr"/>
+      <c r="Q293" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R293" s="14" t="inlineStr"/>
+      <c r="S293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T293" s="14" t="inlineStr"/>
+      <c r="U293" s="14" t="inlineStr"/>
+      <c r="V293" s="14" t="inlineStr"/>
+      <c r="W293" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y293" s="14" t="inlineStr"/>
+      <c r="Z293" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA293" s="14" t="inlineStr"/>
+      <c r="AB293" s="14" t="inlineStr"/>
+      <c r="AC293" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD293" s="15" t="inlineStr"/>
+      <c r="AE293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF293" s="14" t="inlineStr"/>
+      <c r="AG293" s="14" t="inlineStr"/>
+      <c r="AH293" s="14" t="inlineStr"/>
+      <c r="AI293" s="14" t="inlineStr"/>
+    </row>
+    <row r="294" customHeight="1" ht="15">
+      <c r="A294" s="2" t="inlineStr"/>
+      <c r="B294" s="2" t="inlineStr"/>
+      <c r="C294" s="2" t="inlineStr"/>
+      <c r="D294" s="2" t="inlineStr"/>
+      <c r="E294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr"/>
+      <c r="I294" s="2" t="inlineStr"/>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr"/>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000231. Uang Harian</t>
+          </r>
+        </is>
+      </c>
+      <c r="O294" s="13" t="inlineStr"/>
+      <c r="P294" s="13" t="inlineStr"/>
+      <c r="Q294" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R294" s="14" t="inlineStr"/>
+      <c r="S294" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T294" s="14" t="inlineStr"/>
+      <c r="U294" s="14" t="inlineStr"/>
+      <c r="V294" s="14" t="inlineStr"/>
+      <c r="W294" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X294" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y294" s="14" t="inlineStr"/>
+      <c r="Z294" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA294" s="14" t="inlineStr"/>
+      <c r="AB294" s="14" t="inlineStr"/>
+      <c r="AC294" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD294" s="15" t="inlineStr"/>
+      <c r="AE294" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF294" s="14" t="inlineStr"/>
+      <c r="AG294" s="14" t="inlineStr"/>
+      <c r="AH294" s="14" t="inlineStr"/>
+      <c r="AI294" s="14" t="inlineStr"/>
+    </row>
+    <row r="295" customHeight="1" ht="24">
+      <c r="A295" s="2" t="inlineStr"/>
+      <c r="B295" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.
@@ -17573,39 +17687,39 @@
           </r>
         </is>
       </c>
-      <c r="C293" s="27" t="inlineStr"/>
-      <c r="D293" s="27" t="inlineStr"/>
-      <c r="E293" s="27" t="inlineStr"/>
-      <c r="F293" s="27" t="inlineStr"/>
-      <c r="G293" s="27" t="inlineStr"/>
-      <c r="H293" s="27" t="inlineStr"/>
-      <c r="I293" s="27" t="inlineStr"/>
-      <c r="J293" s="27" t="inlineStr"/>
-      <c r="K293" s="27" t="inlineStr"/>
-      <c r="L293" s="27" t="inlineStr"/>
-      <c r="M293" s="27" t="inlineStr"/>
-      <c r="N293" s="27" t="inlineStr"/>
-      <c r="O293" s="27" t="inlineStr"/>
-      <c r="P293" s="27" t="inlineStr"/>
-      <c r="Q293" s="27" t="inlineStr"/>
-      <c r="R293" s="27" t="inlineStr"/>
-      <c r="S293" s="27" t="inlineStr"/>
-      <c r="T293" s="27" t="inlineStr"/>
-      <c r="U293" s="27" t="inlineStr"/>
-      <c r="V293" s="27" t="inlineStr"/>
-      <c r="W293" s="27" t="inlineStr"/>
-      <c r="X293" s="27" t="inlineStr"/>
-      <c r="Y293" s="27" t="inlineStr"/>
-      <c r="Z293" s="27" t="inlineStr"/>
-      <c r="AA293" s="27" t="inlineStr"/>
-      <c r="AB293" s="27" t="inlineStr"/>
-      <c r="AC293" s="27" t="inlineStr"/>
-      <c r="AD293" s="27" t="inlineStr"/>
-      <c r="AE293" s="27" t="inlineStr"/>
-      <c r="AF293" s="27" t="inlineStr"/>
-      <c r="AG293" s="2" t="inlineStr"/>
-      <c r="AH293" s="2" t="inlineStr"/>
-      <c r="AI293" s="2" t="inlineStr"/>
+      <c r="C295" s="27" t="inlineStr"/>
+      <c r="D295" s="27" t="inlineStr"/>
+      <c r="E295" s="27" t="inlineStr"/>
+      <c r="F295" s="27" t="inlineStr"/>
+      <c r="G295" s="27" t="inlineStr"/>
+      <c r="H295" s="27" t="inlineStr"/>
+      <c r="I295" s="27" t="inlineStr"/>
+      <c r="J295" s="27" t="inlineStr"/>
+      <c r="K295" s="27" t="inlineStr"/>
+      <c r="L295" s="27" t="inlineStr"/>
+      <c r="M295" s="27" t="inlineStr"/>
+      <c r="N295" s="27" t="inlineStr"/>
+      <c r="O295" s="27" t="inlineStr"/>
+      <c r="P295" s="27" t="inlineStr"/>
+      <c r="Q295" s="27" t="inlineStr"/>
+      <c r="R295" s="27" t="inlineStr"/>
+      <c r="S295" s="27" t="inlineStr"/>
+      <c r="T295" s="27" t="inlineStr"/>
+      <c r="U295" s="27" t="inlineStr"/>
+      <c r="V295" s="27" t="inlineStr"/>
+      <c r="W295" s="27" t="inlineStr"/>
+      <c r="X295" s="27" t="inlineStr"/>
+      <c r="Y295" s="27" t="inlineStr"/>
+      <c r="Z295" s="27" t="inlineStr"/>
+      <c r="AA295" s="27" t="inlineStr"/>
+      <c r="AB295" s="27" t="inlineStr"/>
+      <c r="AC295" s="27" t="inlineStr"/>
+      <c r="AD295" s="27" t="inlineStr"/>
+      <c r="AE295" s="27" t="inlineStr"/>
+      <c r="AF295" s="27" t="inlineStr"/>
+      <c r="AG295" s="2" t="inlineStr"/>
+      <c r="AH295" s="2" t="inlineStr"/>
+      <c r="AI295" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -19053,15 +19167,15 @@
     <mergeCell ref="Z208:AB208"/>
     <mergeCell ref="AC208:AD208"/>
     <mergeCell ref="AE208:AI208"/>
-    <mergeCell ref="H209:L209"/>
-    <mergeCell ref="M209:P209"/>
+    <mergeCell ref="N209:P209"/>
     <mergeCell ref="Q209:R209"/>
     <mergeCell ref="S209:V209"/>
     <mergeCell ref="X209:Y209"/>
     <mergeCell ref="Z209:AB209"/>
     <mergeCell ref="AC209:AD209"/>
     <mergeCell ref="AE209:AI209"/>
-    <mergeCell ref="N210:P210"/>
+    <mergeCell ref="H210:L210"/>
+    <mergeCell ref="M210:P210"/>
     <mergeCell ref="Q210:R210"/>
     <mergeCell ref="S210:V210"/>
     <mergeCell ref="X210:Y210"/>
@@ -19075,15 +19189,15 @@
     <mergeCell ref="Z211:AB211"/>
     <mergeCell ref="AC211:AD211"/>
     <mergeCell ref="AE211:AI211"/>
-    <mergeCell ref="H212:L212"/>
-    <mergeCell ref="M212:P212"/>
+    <mergeCell ref="N212:P212"/>
     <mergeCell ref="Q212:R212"/>
     <mergeCell ref="S212:V212"/>
     <mergeCell ref="X212:Y212"/>
     <mergeCell ref="Z212:AB212"/>
     <mergeCell ref="AC212:AD212"/>
     <mergeCell ref="AE212:AI212"/>
-    <mergeCell ref="N213:P213"/>
+    <mergeCell ref="H213:L213"/>
+    <mergeCell ref="M213:P213"/>
     <mergeCell ref="Q213:R213"/>
     <mergeCell ref="S213:V213"/>
     <mergeCell ref="X213:Y213"/>
@@ -19132,8 +19246,7 @@
     <mergeCell ref="Z219:AB219"/>
     <mergeCell ref="AC219:AD219"/>
     <mergeCell ref="AE219:AI219"/>
-    <mergeCell ref="F220:K220"/>
-    <mergeCell ref="L220:P220"/>
+    <mergeCell ref="N220:P220"/>
     <mergeCell ref="Q220:R220"/>
     <mergeCell ref="S220:V220"/>
     <mergeCell ref="X220:Y220"/>
@@ -19141,60 +19254,61 @@
     <mergeCell ref="AC220:AD220"/>
     <mergeCell ref="AE220:AI220"/>
     <mergeCell ref="B221:AF221"/>
-    <mergeCell ref="H222:L222"/>
-    <mergeCell ref="M222:P222"/>
+    <mergeCell ref="F222:K222"/>
+    <mergeCell ref="L222:P222"/>
     <mergeCell ref="Q222:R222"/>
     <mergeCell ref="S222:V222"/>
     <mergeCell ref="X222:Y222"/>
     <mergeCell ref="Z222:AB222"/>
     <mergeCell ref="AC222:AD222"/>
     <mergeCell ref="AE222:AI222"/>
-    <mergeCell ref="N223:P223"/>
+    <mergeCell ref="H223:L223"/>
+    <mergeCell ref="M223:P223"/>
     <mergeCell ref="Q223:R223"/>
     <mergeCell ref="S223:V223"/>
     <mergeCell ref="X223:Y223"/>
     <mergeCell ref="Z223:AB223"/>
     <mergeCell ref="AC223:AD223"/>
     <mergeCell ref="AE223:AI223"/>
-    <mergeCell ref="H224:L224"/>
-    <mergeCell ref="M224:P224"/>
+    <mergeCell ref="N224:P224"/>
     <mergeCell ref="Q224:R224"/>
     <mergeCell ref="S224:V224"/>
     <mergeCell ref="X224:Y224"/>
     <mergeCell ref="Z224:AB224"/>
     <mergeCell ref="AC224:AD224"/>
     <mergeCell ref="AE224:AI224"/>
-    <mergeCell ref="N225:P225"/>
+    <mergeCell ref="H225:L225"/>
+    <mergeCell ref="M225:P225"/>
     <mergeCell ref="Q225:R225"/>
     <mergeCell ref="S225:V225"/>
     <mergeCell ref="X225:Y225"/>
     <mergeCell ref="Z225:AB225"/>
     <mergeCell ref="AC225:AD225"/>
     <mergeCell ref="AE225:AI225"/>
-    <mergeCell ref="H226:L226"/>
-    <mergeCell ref="M226:P226"/>
+    <mergeCell ref="N226:P226"/>
     <mergeCell ref="Q226:R226"/>
     <mergeCell ref="S226:V226"/>
     <mergeCell ref="X226:Y226"/>
     <mergeCell ref="Z226:AB226"/>
     <mergeCell ref="AC226:AD226"/>
     <mergeCell ref="AE226:AI226"/>
-    <mergeCell ref="N227:P227"/>
+    <mergeCell ref="H227:L227"/>
+    <mergeCell ref="M227:P227"/>
     <mergeCell ref="Q227:R227"/>
     <mergeCell ref="S227:V227"/>
     <mergeCell ref="X227:Y227"/>
     <mergeCell ref="Z227:AB227"/>
     <mergeCell ref="AC227:AD227"/>
     <mergeCell ref="AE227:AI227"/>
-    <mergeCell ref="H228:L228"/>
-    <mergeCell ref="M228:P228"/>
+    <mergeCell ref="N228:P228"/>
     <mergeCell ref="Q228:R228"/>
     <mergeCell ref="S228:V228"/>
     <mergeCell ref="X228:Y228"/>
     <mergeCell ref="Z228:AB228"/>
     <mergeCell ref="AC228:AD228"/>
     <mergeCell ref="AE228:AI228"/>
-    <mergeCell ref="N229:P229"/>
+    <mergeCell ref="H229:L229"/>
+    <mergeCell ref="M229:P229"/>
     <mergeCell ref="Q229:R229"/>
     <mergeCell ref="S229:V229"/>
     <mergeCell ref="X229:Y229"/>
@@ -19208,23 +19322,23 @@
     <mergeCell ref="Z230:AB230"/>
     <mergeCell ref="AC230:AD230"/>
     <mergeCell ref="AE230:AI230"/>
-    <mergeCell ref="F231:K231"/>
-    <mergeCell ref="L231:P231"/>
+    <mergeCell ref="N231:P231"/>
     <mergeCell ref="Q231:R231"/>
     <mergeCell ref="S231:V231"/>
     <mergeCell ref="X231:Y231"/>
     <mergeCell ref="Z231:AB231"/>
     <mergeCell ref="AC231:AD231"/>
     <mergeCell ref="AE231:AI231"/>
-    <mergeCell ref="H232:L232"/>
-    <mergeCell ref="M232:P232"/>
+    <mergeCell ref="F232:K232"/>
+    <mergeCell ref="L232:P232"/>
     <mergeCell ref="Q232:R232"/>
     <mergeCell ref="S232:V232"/>
     <mergeCell ref="X232:Y232"/>
     <mergeCell ref="Z232:AB232"/>
     <mergeCell ref="AC232:AD232"/>
     <mergeCell ref="AE232:AI232"/>
-    <mergeCell ref="N233:P233"/>
+    <mergeCell ref="H233:L233"/>
+    <mergeCell ref="M233:P233"/>
     <mergeCell ref="Q233:R233"/>
     <mergeCell ref="S233:V233"/>
     <mergeCell ref="X233:Y233"/>
@@ -19238,30 +19352,30 @@
     <mergeCell ref="Z234:AB234"/>
     <mergeCell ref="AC234:AD234"/>
     <mergeCell ref="AE234:AI234"/>
-    <mergeCell ref="H235:L235"/>
-    <mergeCell ref="M235:P235"/>
+    <mergeCell ref="N235:P235"/>
     <mergeCell ref="Q235:R235"/>
     <mergeCell ref="S235:V235"/>
     <mergeCell ref="X235:Y235"/>
     <mergeCell ref="Z235:AB235"/>
     <mergeCell ref="AC235:AD235"/>
     <mergeCell ref="AE235:AI235"/>
-    <mergeCell ref="N236:P236"/>
+    <mergeCell ref="H236:L236"/>
+    <mergeCell ref="M236:P236"/>
     <mergeCell ref="Q236:R236"/>
     <mergeCell ref="S236:V236"/>
     <mergeCell ref="X236:Y236"/>
     <mergeCell ref="Z236:AB236"/>
     <mergeCell ref="AC236:AD236"/>
     <mergeCell ref="AE236:AI236"/>
-    <mergeCell ref="H237:L237"/>
-    <mergeCell ref="M237:P237"/>
+    <mergeCell ref="N237:P237"/>
     <mergeCell ref="Q237:R237"/>
     <mergeCell ref="S237:V237"/>
     <mergeCell ref="X237:Y237"/>
     <mergeCell ref="Z237:AB237"/>
     <mergeCell ref="AC237:AD237"/>
     <mergeCell ref="AE237:AI237"/>
-    <mergeCell ref="N238:P238"/>
+    <mergeCell ref="H238:L238"/>
+    <mergeCell ref="M238:P238"/>
     <mergeCell ref="Q238:R238"/>
     <mergeCell ref="S238:V238"/>
     <mergeCell ref="X238:Y238"/>
@@ -19374,15 +19488,15 @@
     <mergeCell ref="Z254:AB254"/>
     <mergeCell ref="AC254:AD254"/>
     <mergeCell ref="AE254:AI254"/>
-    <mergeCell ref="H255:L255"/>
-    <mergeCell ref="M255:P255"/>
+    <mergeCell ref="N255:P255"/>
     <mergeCell ref="Q255:R255"/>
     <mergeCell ref="S255:V255"/>
     <mergeCell ref="X255:Y255"/>
     <mergeCell ref="Z255:AB255"/>
     <mergeCell ref="AC255:AD255"/>
     <mergeCell ref="AE255:AI255"/>
-    <mergeCell ref="N256:P256"/>
+    <mergeCell ref="H256:L256"/>
+    <mergeCell ref="M256:P256"/>
     <mergeCell ref="Q256:R256"/>
     <mergeCell ref="S256:V256"/>
     <mergeCell ref="X256:Y256"/>
@@ -19487,8 +19601,7 @@
     <mergeCell ref="Z270:AB270"/>
     <mergeCell ref="AC270:AD270"/>
     <mergeCell ref="AE270:AI270"/>
-    <mergeCell ref="H271:L271"/>
-    <mergeCell ref="M271:P271"/>
+    <mergeCell ref="N271:P271"/>
     <mergeCell ref="Q271:R271"/>
     <mergeCell ref="S271:V271"/>
     <mergeCell ref="X271:Y271"/>
@@ -19502,7 +19615,8 @@
     <mergeCell ref="Z272:AB272"/>
     <mergeCell ref="AC272:AD272"/>
     <mergeCell ref="AE272:AI272"/>
-    <mergeCell ref="N273:P273"/>
+    <mergeCell ref="H273:L273"/>
+    <mergeCell ref="M273:P273"/>
     <mergeCell ref="Q273:R273"/>
     <mergeCell ref="S273:V273"/>
     <mergeCell ref="X273:Y273"/>
@@ -19517,30 +19631,30 @@
     <mergeCell ref="AC274:AD274"/>
     <mergeCell ref="AE274:AI274"/>
     <mergeCell ref="B275:AF275"/>
-    <mergeCell ref="F276:K276"/>
-    <mergeCell ref="L276:P276"/>
+    <mergeCell ref="N276:P276"/>
     <mergeCell ref="Q276:R276"/>
     <mergeCell ref="S276:V276"/>
     <mergeCell ref="X276:Y276"/>
     <mergeCell ref="Z276:AB276"/>
     <mergeCell ref="AC276:AD276"/>
     <mergeCell ref="AE276:AI276"/>
-    <mergeCell ref="H277:L277"/>
-    <mergeCell ref="M277:P277"/>
+    <mergeCell ref="N277:P277"/>
     <mergeCell ref="Q277:R277"/>
     <mergeCell ref="S277:V277"/>
     <mergeCell ref="X277:Y277"/>
     <mergeCell ref="Z277:AB277"/>
     <mergeCell ref="AC277:AD277"/>
     <mergeCell ref="AE277:AI277"/>
-    <mergeCell ref="N278:P278"/>
+    <mergeCell ref="F278:K278"/>
+    <mergeCell ref="L278:P278"/>
     <mergeCell ref="Q278:R278"/>
     <mergeCell ref="S278:V278"/>
     <mergeCell ref="X278:Y278"/>
     <mergeCell ref="Z278:AB278"/>
     <mergeCell ref="AC278:AD278"/>
     <mergeCell ref="AE278:AI278"/>
-    <mergeCell ref="N279:P279"/>
+    <mergeCell ref="H279:L279"/>
+    <mergeCell ref="M279:P279"/>
     <mergeCell ref="Q279:R279"/>
     <mergeCell ref="S279:V279"/>
     <mergeCell ref="X279:Y279"/>
@@ -19582,8 +19696,7 @@
     <mergeCell ref="Z284:AB284"/>
     <mergeCell ref="AC284:AD284"/>
     <mergeCell ref="AE284:AI284"/>
-    <mergeCell ref="H285:L285"/>
-    <mergeCell ref="M285:P285"/>
+    <mergeCell ref="N285:P285"/>
     <mergeCell ref="Q285:R285"/>
     <mergeCell ref="S285:V285"/>
     <mergeCell ref="X285:Y285"/>
@@ -19597,54 +19710,69 @@
     <mergeCell ref="Z286:AB286"/>
     <mergeCell ref="AC286:AD286"/>
     <mergeCell ref="AE286:AI286"/>
-    <mergeCell ref="C287:F287"/>
-    <mergeCell ref="G287:P287"/>
+    <mergeCell ref="H287:L287"/>
+    <mergeCell ref="M287:P287"/>
     <mergeCell ref="Q287:R287"/>
     <mergeCell ref="S287:V287"/>
     <mergeCell ref="X287:Y287"/>
     <mergeCell ref="Z287:AB287"/>
     <mergeCell ref="AC287:AD287"/>
     <mergeCell ref="AE287:AI287"/>
-    <mergeCell ref="C288:J288"/>
-    <mergeCell ref="K288:P288"/>
+    <mergeCell ref="N288:P288"/>
     <mergeCell ref="Q288:R288"/>
     <mergeCell ref="S288:V288"/>
     <mergeCell ref="X288:Y288"/>
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="E289:I289"/>
-    <mergeCell ref="J289:P289"/>
+    <mergeCell ref="C289:F289"/>
+    <mergeCell ref="G289:P289"/>
     <mergeCell ref="Q289:R289"/>
     <mergeCell ref="S289:V289"/>
     <mergeCell ref="X289:Y289"/>
     <mergeCell ref="Z289:AB289"/>
     <mergeCell ref="AC289:AD289"/>
     <mergeCell ref="AE289:AI289"/>
-    <mergeCell ref="F290:K290"/>
-    <mergeCell ref="L290:P290"/>
+    <mergeCell ref="C290:J290"/>
+    <mergeCell ref="K290:P290"/>
     <mergeCell ref="Q290:R290"/>
     <mergeCell ref="S290:V290"/>
     <mergeCell ref="X290:Y290"/>
     <mergeCell ref="Z290:AB290"/>
     <mergeCell ref="AC290:AD290"/>
     <mergeCell ref="AE290:AI290"/>
-    <mergeCell ref="H291:L291"/>
-    <mergeCell ref="M291:P291"/>
+    <mergeCell ref="E291:I291"/>
+    <mergeCell ref="J291:P291"/>
     <mergeCell ref="Q291:R291"/>
     <mergeCell ref="S291:V291"/>
     <mergeCell ref="X291:Y291"/>
     <mergeCell ref="Z291:AB291"/>
     <mergeCell ref="AC291:AD291"/>
     <mergeCell ref="AE291:AI291"/>
-    <mergeCell ref="N292:P292"/>
+    <mergeCell ref="F292:K292"/>
+    <mergeCell ref="L292:P292"/>
     <mergeCell ref="Q292:R292"/>
     <mergeCell ref="S292:V292"/>
     <mergeCell ref="X292:Y292"/>
     <mergeCell ref="Z292:AB292"/>
     <mergeCell ref="AC292:AD292"/>
     <mergeCell ref="AE292:AI292"/>
-    <mergeCell ref="B293:AF293"/>
+    <mergeCell ref="H293:L293"/>
+    <mergeCell ref="M293:P293"/>
+    <mergeCell ref="Q293:R293"/>
+    <mergeCell ref="S293:V293"/>
+    <mergeCell ref="X293:Y293"/>
+    <mergeCell ref="Z293:AB293"/>
+    <mergeCell ref="AC293:AD293"/>
+    <mergeCell ref="AE293:AI293"/>
+    <mergeCell ref="N294:P294"/>
+    <mergeCell ref="Q294:R294"/>
+    <mergeCell ref="S294:V294"/>
+    <mergeCell ref="X294:Y294"/>
+    <mergeCell ref="Z294:AB294"/>
+    <mergeCell ref="AC294:AD294"/>
+    <mergeCell ref="AE294:AI294"/>
+    <mergeCell ref="B295:AF295"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>8.6557047429E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>4.486302984E9</v>
+        <v>4.534703726E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.1043350413E10</v>
+        <v>9.1091751155E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9104695769346381</v>
+        <v>0.9109536035317719</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>8.952687587E9</v>
+        <v>8.904286845E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>4.486302984E9</v>
+        <v>4.534703726E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.7009982373E10</v>
+        <v>8.7058383115E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9067068620289492</v>
+        <v>0.9072112327195507</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>8.952655627E9</v>
+        <v>8.904254885E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>4.486302984E9</v>
+        <v>4.534703726E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.7009982373E10</v>
+        <v>8.7058383115E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9067068620289492</v>
+        <v>0.9072112327195507</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>8.952655627E9</v>
+        <v>8.904254885E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.2523079389E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>4.486302984E9</v>
+        <v>4.534703726E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.7009382373E10</v>
+        <v>8.7057783115E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9067062787161732</v>
+        <v>0.9072106525603385</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>8.952655627E9</v>
+        <v>8.904254885E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3234,20 +3234,20 @@
         <v>8.2505568337E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>4.486302984E9</v>
+        <v>4.534703726E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.6991871321E10</v>
+        <v>8.7040272063E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9066988807726313</v>
+        <v>0.9072033520287792</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>8.951636679E9</v>
+        <v>8.903235937E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -11578,20 +11578,20 @@
         <v>5.752546162E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>4.40873812E8</v>
+        <v>4.89274554E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.193419974E9</v>
+        <v>6.241820716E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.891551987574108</v>
+        <v>0.8985193461435758</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>7.53365026E8</v>
+        <v>7.04964284E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -13471,20 +13471,20 @@
         <v>6.39230607E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>1216100.0</v>
+        <v>4.9616842E7</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>6.40446707E8</v>
+        <v>6.88847449E8</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.9147356929431659</v>
+        <v>0.9838653891199525</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>5.9697293E7</v>
+        <v>1.1296551E7</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13534,20 +13534,20 @@
         <v>4.70513911E8</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>0.0</v>
+        <v>3.8886478E7</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>5.09400389E8</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.9118486647286822</v>
+        <v>0.9872100562015503</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>4.5486089E7</v>
+        <v>6599611.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13591,20 +13591,20 @@
         <v>4.70513911E8</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>0.0</v>
+        <v>3.8886478E7</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>5.09400389E8</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.9118486647286822</v>
+        <v>0.9872100562015503</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>4.5486089E7</v>
+        <v>6599611.0</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13654,20 +13654,20 @@
         <v>5485232.0</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>5485232.0</v>
+        <v>5748746.0</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.9142053333333333</v>
+        <v>0.9581243333333334</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>514768.0</v>
+        <v>251254.0</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -13711,20 +13711,20 @@
         <v>5485232.0</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>5485232.0</v>
+        <v>5748746.0</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9142053333333333</v>
+        <v>0.9581243333333334</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>514768.0</v>
+        <v>251254.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13894,20 +13894,20 @@
         <v>1.33021464E8</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>1.42272214E8</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.919291389080857</v>
+        <v>0.9832219350380097</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1.1678536E7</v>
+        <v>2427786.0</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13951,20 +13951,20 @@
         <v>1.044355E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>1.1368625E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.9113045375218151</v>
+        <v>0.9920266143106458</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>1.01645E7</v>
+        <v>913750.0</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>8.6557047429E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>4.534703726E9</v>
+        <v>1.1497693468E10</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.1091751155E10</v>
+        <v>9.8054740897E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9109536035317719</v>
+        <v>0.9805862597976132</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>8.904286845E9</v>
+        <v>1.941297103E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>4.534703726E9</v>
+        <v>1.1497693468E10</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.7058383115E10</v>
+        <v>9.4021372857E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9072112327195507</v>
+        <v>0.9797706150700025</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>8.904254885E9</v>
+        <v>1.941265143E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>4.534703726E9</v>
+        <v>1.1497693468E10</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.7058383115E10</v>
+        <v>9.4021372857E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9072112327195507</v>
+        <v>0.9797706150700025</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>8.904254885E9</v>
+        <v>1.941265143E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.2523079389E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>4.534703726E9</v>
+        <v>1.1497693468E10</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.7057783115E10</v>
+        <v>9.4020772857E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9072106525603385</v>
+        <v>0.9797704885863303</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>8.904254885E9</v>
+        <v>1.941265143E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3234,20 +3234,20 @@
         <v>8.2505568337E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>4.534703726E9</v>
+        <v>1.1497693468E10</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.7040272063E10</v>
+        <v>9.4003261805E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9072033520287792</v>
+        <v>0.9797772018613287</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>8.903235937E9</v>
+        <v>1.940246195E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3297,20 +3297,20 @@
         <v>7.6753022175E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>4.045429172E9</v>
+        <v>1.1008418914E10</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.0798451347E10</v>
+        <v>8.7761441089E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9078811963334875</v>
+        <v>0.9861199168985132</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>8.198271653E9</v>
+        <v>1.235281911E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -6085,20 +6085,20 @@
         <v>4.5358707E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>1.67266965E8</v>
+        <v>4.51030727E8</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>6.20854035E8</v>
+        <v>9.04617797E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.6417812375955145</v>
+        <v>0.9351098592917866</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>3.46537965E8</v>
+        <v>6.2774203E7</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -7045,20 +7045,20 @@
         <v>1.42100114E8</v>
       </c>
       <c r="X111" s="14" t="n">
-        <v>0.0</v>
+        <v>2.83763762E8</v>
       </c>
       <c r="Y111" s="14" t="inlineStr"/>
       <c r="Z111" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>4.25863876E8</v>
       </c>
       <c r="AA111" s="14" t="inlineStr"/>
       <c r="AB111" s="14" t="inlineStr"/>
       <c r="AC111" s="15" t="n">
-        <v>0.31577803111111113</v>
+        <v>0.9463641688888889</v>
       </c>
       <c r="AD111" s="15" t="inlineStr"/>
       <c r="AE111" s="14" t="n">
-        <v>3.07899886E8</v>
+        <v>2.4136124E7</v>
       </c>
       <c r="AF111" s="14" t="inlineStr"/>
       <c r="AG111" s="14" t="inlineStr"/>
@@ -7102,20 +7102,20 @@
         <v>1.42100114E8</v>
       </c>
       <c r="X112" s="14" t="n">
-        <v>0.0</v>
+        <v>2.83763762E8</v>
       </c>
       <c r="Y112" s="14" t="inlineStr"/>
       <c r="Z112" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>4.25863876E8</v>
       </c>
       <c r="AA112" s="14" t="inlineStr"/>
       <c r="AB112" s="14" t="inlineStr"/>
       <c r="AC112" s="15" t="n">
-        <v>0.31577803111111113</v>
+        <v>0.9463641688888889</v>
       </c>
       <c r="AD112" s="15" t="inlineStr"/>
       <c r="AE112" s="14" t="n">
-        <v>3.07899886E8</v>
+        <v>2.4136124E7</v>
       </c>
       <c r="AF112" s="14" t="inlineStr"/>
       <c r="AG112" s="14" t="inlineStr"/>
@@ -7165,20 +7165,20 @@
         <v>4.9091867246E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>1.816472754E9</v>
+        <v>5.34332067E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.090834E10</v>
+        <v>5.4435187916E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.9233056566566804</v>
+        <v>0.9872707875372125</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>4.228699E9</v>
+        <v>7.01851084E8</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -9422,20 +9422,20 @@
         <v>2.475555828E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>0.0</v>
+        <v>3.526847916E9</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
-        <v>2.475555828E10</v>
+        <v>2.8282406196E10</v>
       </c>
       <c r="AA152" s="14" t="inlineStr"/>
       <c r="AB152" s="14" t="inlineStr"/>
       <c r="AC152" s="15" t="n">
-        <v>0.8618034181440637</v>
+        <v>0.9845818889385857</v>
       </c>
       <c r="AD152" s="15" t="inlineStr"/>
       <c r="AE152" s="14" t="n">
-        <v>3.96973772E9</v>
+        <v>4.42889804E8</v>
       </c>
       <c r="AF152" s="14" t="inlineStr"/>
       <c r="AG152" s="14" t="inlineStr"/>
@@ -9479,20 +9479,20 @@
         <v>1.997827308E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>0.0</v>
+        <v>3.526847916E9</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>1.997827308E10</v>
+        <v>2.3505120996E10</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.8342358340523915</v>
+        <v>0.9815069670977007</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>3.96971892E9</v>
+        <v>4.42871004E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9656,20 +9656,20 @@
         <v>2.1747293967E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>1.662402241E9</v>
+        <v>4.814780305E9</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
-        <v>2.3409696208E10</v>
+        <v>2.6562074272E10</v>
       </c>
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.8686540936662458</v>
+        <v>0.9856281067310323</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.539691792E9</v>
+        <v>3.87313728E8</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11344,20 +11344,20 @@
         <v>9.794680989E9</v>
       </c>
       <c r="X185" s="14" t="n">
-        <v>0.0</v>
+        <v>3.152378064E9</v>
       </c>
       <c r="Y185" s="14" t="inlineStr"/>
       <c r="Z185" s="14" t="n">
-        <v>9.794680989E9</v>
+        <v>1.2947059053E10</v>
       </c>
       <c r="AA185" s="14" t="inlineStr"/>
       <c r="AB185" s="14" t="inlineStr"/>
       <c r="AC185" s="15" t="n">
-        <v>0.7507542654118889</v>
+        <v>0.9923814588239839</v>
       </c>
       <c r="AD185" s="15" t="inlineStr"/>
       <c r="AE185" s="14" t="n">
-        <v>3.251773011E9</v>
+        <v>9.9394947E7</v>
       </c>
       <c r="AF185" s="14" t="inlineStr"/>
       <c r="AG185" s="14" t="inlineStr"/>
@@ -11401,20 +11401,20 @@
         <v>8.220237613E9</v>
       </c>
       <c r="X186" s="14" t="n">
-        <v>0.0</v>
+        <v>3.152378064E9</v>
       </c>
       <c r="Y186" s="14" t="inlineStr"/>
       <c r="Z186" s="14" t="n">
-        <v>8.220237613E9</v>
+        <v>1.1372615677E10</v>
       </c>
       <c r="AA186" s="14" t="inlineStr"/>
       <c r="AB186" s="14" t="inlineStr"/>
       <c r="AC186" s="15" t="n">
-        <v>0.7165479090829847</v>
+        <v>0.9913367919281729</v>
       </c>
       <c r="AD186" s="15" t="inlineStr"/>
       <c r="AE186" s="14" t="n">
-        <v>3.251762387E9</v>
+        <v>9.9384323E7</v>
       </c>
       <c r="AF186" s="14" t="inlineStr"/>
       <c r="AG186" s="14" t="inlineStr"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>8.6557047429E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>1.1497693468E10</v>
+        <v>1.1909697651E10</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.8054740897E10</v>
+        <v>9.846674508E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9805862597976132</v>
+        <v>0.9847064648701381</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.941297103E9</v>
+        <v>1.52929292E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>1.1497693468E10</v>
+        <v>1.1909697651E10</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>9.4021372857E10</v>
+        <v>9.443337704E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9797706150700025</v>
+        <v>0.98406399623987</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.941265143E9</v>
+        <v>1.52926096E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>1.1497693468E10</v>
+        <v>1.1909697651E10</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>9.4021372857E10</v>
+        <v>9.443337704E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9797706150700025</v>
+        <v>0.98406399623987</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.941265143E9</v>
+        <v>1.52926096E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.2523079389E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>1.1497693468E10</v>
+        <v>1.1909697651E10</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>9.4020772857E10</v>
+        <v>9.443277704E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9797704885863303</v>
+        <v>0.9840638966004452</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.941265143E9</v>
+        <v>1.52926096E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2565,20 +2565,20 @@
         <v>1.6461052E7</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
-        <v>1.6461052E7</v>
+        <v>1.7261052E7</v>
       </c>
       <c r="AA35" s="21" t="inlineStr"/>
       <c r="AB35" s="21" t="inlineStr"/>
       <c r="AC35" s="23" t="n">
-        <v>0.9417077803203662</v>
+        <v>0.9874743707093822</v>
       </c>
       <c r="AD35" s="23" t="inlineStr"/>
       <c r="AE35" s="21" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF35" s="21" t="inlineStr"/>
       <c r="AG35" s="21" t="inlineStr"/>
@@ -2628,20 +2628,20 @@
         <v>1.6461052E7</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
-        <v>1.6461052E7</v>
+        <v>1.7261052E7</v>
       </c>
       <c r="AA36" s="25" t="inlineStr"/>
       <c r="AB36" s="25" t="inlineStr"/>
       <c r="AC36" s="26" t="n">
-        <v>0.9417077803203662</v>
+        <v>0.9874743707093822</v>
       </c>
       <c r="AD36" s="26" t="inlineStr"/>
       <c r="AE36" s="25" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF36" s="25" t="inlineStr"/>
       <c r="AG36" s="25" t="inlineStr"/>
@@ -2994,20 +2994,20 @@
         <v>1.4061052E7</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
-        <v>1.4061052E7</v>
+        <v>1.4861052E7</v>
       </c>
       <c r="AA42" s="14" t="inlineStr"/>
       <c r="AB42" s="14" t="inlineStr"/>
       <c r="AC42" s="15" t="n">
-        <v>0.9324305039787798</v>
+        <v>0.985480901856764</v>
       </c>
       <c r="AD42" s="15" t="inlineStr"/>
       <c r="AE42" s="14" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF42" s="14" t="inlineStr"/>
       <c r="AG42" s="14" t="inlineStr"/>
@@ -3057,20 +3057,20 @@
         <v>1.4061052E7</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
-        <v>1.4061052E7</v>
+        <v>1.4861052E7</v>
       </c>
       <c r="AA43" s="14" t="inlineStr"/>
       <c r="AB43" s="14" t="inlineStr"/>
       <c r="AC43" s="15" t="n">
-        <v>0.9324305039787798</v>
+        <v>0.985480901856764</v>
       </c>
       <c r="AD43" s="15" t="inlineStr"/>
       <c r="AE43" s="14" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF43" s="14" t="inlineStr"/>
       <c r="AG43" s="14" t="inlineStr"/>
@@ -3114,20 +3114,20 @@
         <v>1.3311952E7</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
-        <v>1.3311952E7</v>
+        <v>1.4111952E7</v>
       </c>
       <c r="AA44" s="14" t="inlineStr"/>
       <c r="AB44" s="14" t="inlineStr"/>
       <c r="AC44" s="15" t="n">
-        <v>0.9302552061495458</v>
+        <v>0.9861601677148847</v>
       </c>
       <c r="AD44" s="15" t="inlineStr"/>
       <c r="AE44" s="14" t="n">
-        <v>998048.0</v>
+        <v>198048.0</v>
       </c>
       <c r="AF44" s="14" t="inlineStr"/>
       <c r="AG44" s="14" t="inlineStr"/>
@@ -3234,20 +3234,20 @@
         <v>8.2505568337E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>1.1497693468E10</v>
+        <v>1.1908897651E10</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>9.4003261805E10</v>
+        <v>9.4414465988E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9797772018613287</v>
+        <v>0.9840631008405488</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.940246195E9</v>
+        <v>1.529042012E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3297,20 +3297,20 @@
         <v>7.6753022175E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>1.1008418914E10</v>
+        <v>1.102235221E10</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.7761441089E10</v>
+        <v>8.7775374385E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9861199168985132</v>
+        <v>0.9862764765507153</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.235281911E9</v>
+        <v>1.221348615E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
       <c r="O48" s="13" t="inlineStr"/>
       <c r="P48" s="13" t="inlineStr"/>
       <c r="Q48" s="14" t="n">
-        <v>5.942904E9</v>
+        <v>5.92038E9</v>
       </c>
       <c r="R48" s="14" t="inlineStr"/>
       <c r="S48" s="14" t="n">
@@ -3369,11 +3369,11 @@
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.9859760655733292</v>
+        <v>0.9897271972407177</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>8.3342896E7</v>
+        <v>6.0818896E7</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -5326,7 +5326,7 @@
       <c r="O82" s="13" t="inlineStr"/>
       <c r="P82" s="13" t="inlineStr"/>
       <c r="Q82" s="14" t="n">
-        <v>3.6072E8</v>
+        <v>3.38196E8</v>
       </c>
       <c r="R82" s="14" t="inlineStr"/>
       <c r="S82" s="14" t="n">
@@ -5348,11 +5348,11 @@
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.8484808161454868</v>
+        <v>0.9049900057954559</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>5.4656E7</v>
+        <v>3.2132E7</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5440,7 +5440,7 @@
       <c r="O84" s="13" t="inlineStr"/>
       <c r="P84" s="13" t="inlineStr"/>
       <c r="Q84" s="14" t="n">
-        <v>2.9304E8</v>
+        <v>2.78388E8</v>
       </c>
       <c r="R84" s="14" t="inlineStr"/>
       <c r="S84" s="14" t="n">
@@ -5462,11 +5462,11 @@
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.8595959595959596</v>
+        <v>0.9048378522062732</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>4.1144E7</v>
+        <v>2.6492E7</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5497,7 +5497,7 @@
       <c r="O85" s="13" t="inlineStr"/>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="14" t="n">
-        <v>4.92E7</v>
+        <v>4.1328E7</v>
       </c>
       <c r="R85" s="14" t="inlineStr"/>
       <c r="S85" s="14" t="n">
@@ -5519,11 +5519,11 @@
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.7566666666666667</v>
+        <v>0.9007936507936508</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>1.1972E7</v>
+        <v>4100000.0</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -6072,7 +6072,7 @@
       <c r="O95" s="13" t="inlineStr"/>
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="14" t="n">
-        <v>9.67392E8</v>
+        <v>9.72489E8</v>
       </c>
       <c r="R95" s="14" t="inlineStr"/>
       <c r="S95" s="14" t="n">
@@ -6094,11 +6094,11 @@
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.9351098592917866</v>
+        <v>0.9302087704848075</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>6.2774203E7</v>
+        <v>6.7871203E7</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6735,7 +6735,7 @@
       <c r="O106" s="13" t="inlineStr"/>
       <c r="P106" s="13" t="inlineStr"/>
       <c r="Q106" s="14" t="n">
-        <v>8.304E7</v>
+        <v>8.8137E7</v>
       </c>
       <c r="R106" s="14" t="inlineStr"/>
       <c r="S106" s="14" t="n">
@@ -6757,11 +6757,11 @@
       <c r="AA106" s="14" t="inlineStr"/>
       <c r="AB106" s="14" t="inlineStr"/>
       <c r="AC106" s="15" t="n">
-        <v>0.6957249518304431</v>
+        <v>0.6554908835108978</v>
       </c>
       <c r="AD106" s="15" t="inlineStr"/>
       <c r="AE106" s="14" t="n">
-        <v>2.5267E7</v>
+        <v>3.0364E7</v>
       </c>
       <c r="AF106" s="14" t="inlineStr"/>
       <c r="AG106" s="14" t="inlineStr"/>
@@ -6792,7 +6792,7 @@
       <c r="O107" s="13" t="inlineStr"/>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="14" t="n">
-        <v>2.31E7</v>
+        <v>2.52E7</v>
       </c>
       <c r="R107" s="14" t="inlineStr"/>
       <c r="S107" s="14" t="n">
@@ -6814,11 +6814,11 @@
       <c r="AA107" s="14" t="inlineStr"/>
       <c r="AB107" s="14" t="inlineStr"/>
       <c r="AC107" s="15" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.6569444444444444</v>
       </c>
       <c r="AD107" s="15" t="inlineStr"/>
       <c r="AE107" s="14" t="n">
-        <v>6545000.0</v>
+        <v>8645000.0</v>
       </c>
       <c r="AF107" s="14" t="inlineStr"/>
       <c r="AG107" s="14" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
       <c r="O108" s="13" t="inlineStr"/>
       <c r="P108" s="13" t="inlineStr"/>
       <c r="Q108" s="14" t="n">
-        <v>5.994E7</v>
+        <v>6.2937E7</v>
       </c>
       <c r="R108" s="14" t="inlineStr"/>
       <c r="S108" s="14" t="n">
@@ -6871,11 +6871,11 @@
       <c r="AA108" s="14" t="inlineStr"/>
       <c r="AB108" s="14" t="inlineStr"/>
       <c r="AC108" s="15" t="n">
-        <v>0.6876543209876543</v>
+        <v>0.6549088771310994</v>
       </c>
       <c r="AD108" s="15" t="inlineStr"/>
       <c r="AE108" s="14" t="n">
-        <v>1.8722E7</v>
+        <v>2.1719E7</v>
       </c>
       <c r="AF108" s="14" t="inlineStr"/>
       <c r="AG108" s="14" t="inlineStr"/>
@@ -7152,7 +7152,7 @@
       <c r="O113" s="13" t="inlineStr"/>
       <c r="P113" s="13" t="inlineStr"/>
       <c r="Q113" s="14" t="n">
-        <v>5.5137039E10</v>
+        <v>5.5154319E10</v>
       </c>
       <c r="R113" s="14" t="inlineStr"/>
       <c r="S113" s="14" t="n">
@@ -7165,20 +7165,20 @@
         <v>4.9091867246E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>5.34332067E9</v>
+        <v>5.357253966E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.4435187916E10</v>
+        <v>5.4449121212E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.9872707875372125</v>
+        <v>0.987214096723776</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>7.01851084E8</v>
+        <v>7.05197788E8</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -7272,20 +7272,20 @@
         <v>1.59343583E10</v>
       </c>
       <c r="X115" s="14" t="n">
-        <v>1.1547953E9</v>
+        <v>1.1581858E9</v>
       </c>
       <c r="Y115" s="14" t="inlineStr"/>
       <c r="Z115" s="14" t="n">
-        <v>1.70891536E10</v>
+        <v>1.70925441E10</v>
       </c>
       <c r="AA115" s="14" t="inlineStr"/>
       <c r="AB115" s="14" t="inlineStr"/>
       <c r="AC115" s="15" t="n">
-        <v>0.9992991460978126</v>
+        <v>0.9994974077457648</v>
       </c>
       <c r="AD115" s="15" t="inlineStr"/>
       <c r="AE115" s="14" t="n">
-        <v>1.19854E7</v>
+        <v>8594900.0</v>
       </c>
       <c r="AF115" s="14" t="inlineStr"/>
       <c r="AG115" s="14" t="inlineStr"/>
@@ -7329,20 +7329,20 @@
         <v>1.34436049E10</v>
       </c>
       <c r="X116" s="14" t="n">
-        <v>1.1547953E9</v>
+        <v>1.1581858E9</v>
       </c>
       <c r="Y116" s="14" t="inlineStr"/>
       <c r="Z116" s="14" t="n">
-        <v>1.45984002E10</v>
+        <v>1.46017907E10</v>
       </c>
       <c r="AA116" s="14" t="inlineStr"/>
       <c r="AB116" s="14" t="inlineStr"/>
       <c r="AC116" s="15" t="n">
-        <v>0.9996124502364411</v>
+        <v>0.9998446117038686</v>
       </c>
       <c r="AD116" s="15" t="inlineStr"/>
       <c r="AE116" s="14" t="n">
-        <v>5659800.0</v>
+        <v>2269300.0</v>
       </c>
       <c r="AF116" s="14" t="inlineStr"/>
       <c r="AG116" s="14" t="inlineStr"/>
@@ -7506,20 +7506,20 @@
         <v>215142.0</v>
       </c>
       <c r="X119" s="14" t="n">
-        <v>15003.0</v>
+        <v>15079.0</v>
       </c>
       <c r="Y119" s="14" t="inlineStr"/>
       <c r="Z119" s="14" t="n">
-        <v>230145.0</v>
+        <v>230221.0</v>
       </c>
       <c r="AA119" s="14" t="inlineStr"/>
       <c r="AB119" s="14" t="inlineStr"/>
       <c r="AC119" s="15" t="n">
-        <v>0.9629497907949791</v>
+        <v>0.9632677824267782</v>
       </c>
       <c r="AD119" s="15" t="inlineStr"/>
       <c r="AE119" s="14" t="n">
-        <v>8855.0</v>
+        <v>8779.0</v>
       </c>
       <c r="AF119" s="14" t="inlineStr"/>
       <c r="AG119" s="14" t="inlineStr"/>
@@ -7563,20 +7563,20 @@
         <v>181368.0</v>
       </c>
       <c r="X120" s="14" t="n">
-        <v>15003.0</v>
+        <v>15079.0</v>
       </c>
       <c r="Y120" s="14" t="inlineStr"/>
       <c r="Z120" s="14" t="n">
-        <v>196371.0</v>
+        <v>196447.0</v>
       </c>
       <c r="AA120" s="14" t="inlineStr"/>
       <c r="AB120" s="14" t="inlineStr"/>
       <c r="AC120" s="15" t="n">
-        <v>0.9626029411764706</v>
+        <v>0.9629754901960784</v>
       </c>
       <c r="AD120" s="15" t="inlineStr"/>
       <c r="AE120" s="14" t="n">
-        <v>7629.0</v>
+        <v>7553.0</v>
       </c>
       <c r="AF120" s="14" t="inlineStr"/>
       <c r="AG120" s="14" t="inlineStr"/>
@@ -8208,20 +8208,20 @@
         <v>3.43577E9</v>
       </c>
       <c r="X131" s="14" t="n">
-        <v>2.4768E8</v>
+        <v>2.4822E8</v>
       </c>
       <c r="Y131" s="14" t="inlineStr"/>
       <c r="Z131" s="14" t="n">
-        <v>3.68345E9</v>
+        <v>3.68399E9</v>
       </c>
       <c r="AA131" s="14" t="inlineStr"/>
       <c r="AB131" s="14" t="inlineStr"/>
       <c r="AC131" s="15" t="n">
-        <v>0.9989710472103284</v>
+        <v>0.9991174980554582</v>
       </c>
       <c r="AD131" s="15" t="inlineStr"/>
       <c r="AE131" s="14" t="n">
-        <v>3794000.0</v>
+        <v>3254000.0</v>
       </c>
       <c r="AF131" s="14" t="inlineStr"/>
       <c r="AG131" s="14" t="inlineStr"/>
@@ -8265,20 +8265,20 @@
         <v>2.89751E9</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>2.4768E8</v>
+        <v>2.4822E8</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
-        <v>3.14519E9</v>
+        <v>3.14573E9</v>
       </c>
       <c r="AA132" s="14" t="inlineStr"/>
       <c r="AB132" s="14" t="inlineStr"/>
       <c r="AC132" s="15" t="n">
-        <v>0.9987964356712332</v>
+        <v>0.9989679197708464</v>
       </c>
       <c r="AD132" s="15" t="inlineStr"/>
       <c r="AE132" s="14" t="n">
-        <v>3790000.0</v>
+        <v>3250000.0</v>
       </c>
       <c r="AF132" s="14" t="inlineStr"/>
       <c r="AG132" s="14" t="inlineStr"/>
@@ -8676,20 +8676,20 @@
         <v>8.7794766E8</v>
       </c>
       <c r="X139" s="14" t="n">
-        <v>6.510558E7</v>
+        <v>6.5178E7</v>
       </c>
       <c r="Y139" s="14" t="inlineStr"/>
       <c r="Z139" s="14" t="n">
-        <v>9.4305324E8</v>
+        <v>9.4312566E8</v>
       </c>
       <c r="AA139" s="14" t="inlineStr"/>
       <c r="AB139" s="14" t="inlineStr"/>
       <c r="AC139" s="15" t="n">
-        <v>0.9995307240306265</v>
+        <v>0.9996074811127975</v>
       </c>
       <c r="AD139" s="15" t="inlineStr"/>
       <c r="AE139" s="14" t="n">
-        <v>442760.0</v>
+        <v>370340.0</v>
       </c>
       <c r="AF139" s="14" t="inlineStr"/>
       <c r="AG139" s="14" t="inlineStr"/>
@@ -8733,20 +8733,20 @@
         <v>7.412187E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>6.510558E7</v>
+        <v>6.5178E7</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
-        <v>8.0632428E8</v>
+        <v>8.063967E8</v>
       </c>
       <c r="AA140" s="14" t="inlineStr"/>
       <c r="AB140" s="14" t="inlineStr"/>
       <c r="AC140" s="15" t="n">
-        <v>0.99945991372899</v>
+        <v>0.9995496802022906</v>
       </c>
       <c r="AD140" s="15" t="inlineStr"/>
       <c r="AE140" s="14" t="n">
-        <v>435720.0</v>
+        <v>363300.0</v>
       </c>
       <c r="AF140" s="14" t="inlineStr"/>
       <c r="AG140" s="14" t="inlineStr"/>
@@ -8941,7 +8941,7 @@
       <c r="O144" s="13" t="inlineStr"/>
       <c r="P144" s="13" t="inlineStr"/>
       <c r="Q144" s="14" t="n">
-        <v>2.672352E9</v>
+        <v>2.689632E9</v>
       </c>
       <c r="R144" s="14" t="inlineStr"/>
       <c r="S144" s="14" t="n">
@@ -8954,20 +8954,20 @@
         <v>2.213268E9</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>2.18452E8</v>
+        <v>2.19192E8</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
-        <v>2.43172E9</v>
+        <v>2.43246E9</v>
       </c>
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.9099549759911868</v>
+        <v>0.904383945461684</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>2.40632E8</v>
+        <v>2.57172E8</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -8998,7 +8998,7 @@
       <c r="O145" s="13" t="inlineStr"/>
       <c r="P145" s="13" t="inlineStr"/>
       <c r="Q145" s="14" t="n">
-        <v>2.436E8</v>
+        <v>2.52E8</v>
       </c>
       <c r="R145" s="14" t="inlineStr"/>
       <c r="S145" s="14" t="n">
@@ -9020,11 +9020,11 @@
       <c r="AA145" s="14" t="inlineStr"/>
       <c r="AB145" s="14" t="inlineStr"/>
       <c r="AC145" s="15" t="n">
-        <v>0.9421469622331692</v>
+        <v>0.9107420634920635</v>
       </c>
       <c r="AD145" s="15" t="inlineStr"/>
       <c r="AE145" s="14" t="n">
-        <v>1.4093E7</v>
+        <v>2.2493E7</v>
       </c>
       <c r="AF145" s="14" t="inlineStr"/>
       <c r="AG145" s="14" t="inlineStr"/>
@@ -9055,7 +9055,7 @@
       <c r="O146" s="13" t="inlineStr"/>
       <c r="P146" s="13" t="inlineStr"/>
       <c r="Q146" s="14" t="n">
-        <v>1.9092E9</v>
+        <v>1.91808E9</v>
       </c>
       <c r="R146" s="14" t="inlineStr"/>
       <c r="S146" s="14" t="n">
@@ -9068,20 +9068,20 @@
         <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>1.59359E8</v>
+        <v>1.60099E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>1.74085E9</v>
+        <v>1.74159E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.9118217054263565</v>
+        <v>0.9079861111111112</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>1.6835E8</v>
+        <v>1.7649E8</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9422,20 +9422,20 @@
         <v>2.475555828E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>3.526847916E9</v>
+        <v>3.536038216E9</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
-        <v>2.8282406196E10</v>
+        <v>2.8291596496E10</v>
       </c>
       <c r="AA152" s="14" t="inlineStr"/>
       <c r="AB152" s="14" t="inlineStr"/>
       <c r="AC152" s="15" t="n">
-        <v>0.9845818889385857</v>
+        <v>0.9849018264598561</v>
       </c>
       <c r="AD152" s="15" t="inlineStr"/>
       <c r="AE152" s="14" t="n">
-        <v>4.42889804E8</v>
+        <v>4.33699504E8</v>
       </c>
       <c r="AF152" s="14" t="inlineStr"/>
       <c r="AG152" s="14" t="inlineStr"/>
@@ -9479,20 +9479,20 @@
         <v>1.997827308E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>3.526847916E9</v>
+        <v>3.536038216E9</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>2.3505120996E10</v>
+        <v>2.3514311296E10</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.9815069670977007</v>
+        <v>0.9818907278739696</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>4.42871004E8</v>
+        <v>4.33680704E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       <c r="O156" s="13" t="inlineStr"/>
       <c r="P156" s="13" t="inlineStr"/>
       <c r="Q156" s="14" t="n">
-        <v>2.6949388E10</v>
+        <v>2.6949535E10</v>
       </c>
       <c r="R156" s="14" t="inlineStr"/>
       <c r="S156" s="14" t="n">
@@ -9665,11 +9665,11 @@
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.9856281067310323</v>
+        <v>0.9856227304849602</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.87313728E8</v>
+        <v>3.87460728E8</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11154,7 +11154,7 @@
       <c r="O182" s="13" t="inlineStr"/>
       <c r="P182" s="13" t="inlineStr"/>
       <c r="Q182" s="14" t="n">
-        <v>1.78416E9</v>
+        <v>1.82808E9</v>
       </c>
       <c r="R182" s="14" t="inlineStr"/>
       <c r="S182" s="14" t="n">
@@ -11176,11 +11176,11 @@
       <c r="AA182" s="14" t="inlineStr"/>
       <c r="AB182" s="14" t="inlineStr"/>
       <c r="AC182" s="15" t="n">
-        <v>0.871901062684961</v>
+        <v>0.8509534593672049</v>
       </c>
       <c r="AD182" s="15" t="inlineStr"/>
       <c r="AE182" s="14" t="n">
-        <v>2.28549E8</v>
+        <v>2.72469E8</v>
       </c>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -11211,7 +11211,7 @@
       <c r="O183" s="13" t="inlineStr"/>
       <c r="P183" s="13" t="inlineStr"/>
       <c r="Q183" s="14" t="n">
-        <v>1.68E8</v>
+        <v>1.764E8</v>
       </c>
       <c r="R183" s="14" t="inlineStr"/>
       <c r="S183" s="14" t="n">
@@ -11233,11 +11233,11 @@
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.8766666666666667</v>
+        <v>0.834920634920635</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>2.072E7</v>
+        <v>2.912E7</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11268,7 +11268,7 @@
       <c r="O184" s="13" t="inlineStr"/>
       <c r="P184" s="13" t="inlineStr"/>
       <c r="Q184" s="14" t="n">
-        <v>1.61616E9</v>
+        <v>1.65168E9</v>
       </c>
       <c r="R184" s="14" t="inlineStr"/>
       <c r="S184" s="14" t="n">
@@ -11290,11 +11290,11 @@
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.8714056776556777</v>
+        <v>0.852665770609319</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>2.07829E8</v>
+        <v>2.43349E8</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11331,7 +11331,7 @@
       <c r="O185" s="13" t="inlineStr"/>
       <c r="P185" s="13" t="inlineStr"/>
       <c r="Q185" s="14" t="n">
-        <v>1.3046454E10</v>
+        <v>1.3002681E10</v>
       </c>
       <c r="R185" s="14" t="inlineStr"/>
       <c r="S185" s="14" t="n">
@@ -11353,11 +11353,11 @@
       <c r="AA185" s="14" t="inlineStr"/>
       <c r="AB185" s="14" t="inlineStr"/>
       <c r="AC185" s="15" t="n">
-        <v>0.9923814588239839</v>
+        <v>0.9957222708916723</v>
       </c>
       <c r="AD185" s="15" t="inlineStr"/>
       <c r="AE185" s="14" t="n">
-        <v>9.9394947E7</v>
+        <v>5.5621947E7</v>
       </c>
       <c r="AF185" s="14" t="inlineStr"/>
       <c r="AG185" s="14" t="inlineStr"/>
@@ -11388,7 +11388,7 @@
       <c r="O186" s="13" t="inlineStr"/>
       <c r="P186" s="13" t="inlineStr"/>
       <c r="Q186" s="14" t="n">
-        <v>1.1472E10</v>
+        <v>1.1428224E10</v>
       </c>
       <c r="R186" s="14" t="inlineStr"/>
       <c r="S186" s="14" t="n">
@@ -11410,11 +11410,11 @@
       <c r="AA186" s="14" t="inlineStr"/>
       <c r="AB186" s="14" t="inlineStr"/>
       <c r="AC186" s="15" t="n">
-        <v>0.9913367919281729</v>
+        <v>0.995134123814864</v>
       </c>
       <c r="AD186" s="15" t="inlineStr"/>
       <c r="AE186" s="14" t="n">
-        <v>9.9384323E7</v>
+        <v>5.5608323E7</v>
       </c>
       <c r="AF186" s="14" t="inlineStr"/>
       <c r="AG186" s="14" t="inlineStr"/>
@@ -11502,7 +11502,7 @@
       <c r="O188" s="13" t="inlineStr"/>
       <c r="P188" s="13" t="inlineStr"/>
       <c r="Q188" s="14" t="n">
-        <v>7.89135E8</v>
+        <v>7.89138E8</v>
       </c>
       <c r="R188" s="14" t="inlineStr"/>
       <c r="S188" s="14" t="n">
@@ -11524,11 +11524,11 @@
       <c r="AA188" s="14" t="inlineStr"/>
       <c r="AB188" s="14" t="inlineStr"/>
       <c r="AC188" s="15" t="n">
-        <v>0.9999994703060946</v>
+        <v>0.999995668691661</v>
       </c>
       <c r="AD188" s="15" t="inlineStr"/>
       <c r="AE188" s="14" t="n">
-        <v>418.0</v>
+        <v>3418.0</v>
       </c>
       <c r="AF188" s="14" t="inlineStr"/>
       <c r="AG188" s="14" t="inlineStr"/>
@@ -11578,20 +11578,20 @@
         <v>5.752546162E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>4.89274554E8</v>
+        <v>8.86545441E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.241820716E9</v>
+        <v>6.639091603E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.8985193461435758</v>
+        <v>0.9557070793179867</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>7.04964284E8</v>
+        <v>3.07693397E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
       <c r="Q190" s="14" t="n">
-        <v>5.006041E9</v>
+        <v>5.008716E9</v>
       </c>
       <c r="R190" s="14" t="inlineStr"/>
       <c r="S190" s="14" t="n">
@@ -11641,20 +11641,20 @@
         <v>4.382759356E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>3.3261462E8</v>
+        <v>5.49326489E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.715373976E9</v>
+        <v>4.932085845E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9419367472220064</v>
+        <v>0.984700638846363</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>2.90667024E8</v>
+        <v>7.6630155E7</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11691,7 +11691,7 @@
       <c r="O191" s="13" t="inlineStr"/>
       <c r="P191" s="13" t="inlineStr"/>
       <c r="Q191" s="14" t="n">
-        <v>1.890817E9</v>
+        <v>1.892887E9</v>
       </c>
       <c r="R191" s="14" t="inlineStr"/>
       <c r="S191" s="14" t="n">
@@ -11704,20 +11704,20 @@
         <v>1.752363354E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>1.03500852E8</v>
+        <v>1.30338121E8</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.855864206E9</v>
+        <v>1.882701475E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9815144490450425</v>
+        <v>0.9946190528013558</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>3.4952794E7</v>
+        <v>1.0185525E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11862,7 +11862,7 @@
       <c r="O194" s="13" t="inlineStr"/>
       <c r="P194" s="13" t="inlineStr"/>
       <c r="Q194" s="14" t="n">
-        <v>9.393E7</v>
+        <v>9.6E7</v>
       </c>
       <c r="R194" s="14" t="inlineStr"/>
       <c r="S194" s="14" t="n">
@@ -11875,20 +11875,20 @@
         <v>5.3038114E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>6099252.0</v>
+        <v>3.2936521E7</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>5.9137366E7</v>
+        <v>8.5974635E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.6295897583306718</v>
+        <v>0.8955691145833333</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>3.4792634E7</v>
+        <v>1.0025365E7</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       <c r="O196" s="13" t="inlineStr"/>
       <c r="P196" s="13" t="inlineStr"/>
       <c r="Q196" s="14" t="n">
-        <v>9.393E7</v>
+        <v>9.6E7</v>
       </c>
       <c r="R196" s="14" t="inlineStr"/>
       <c r="S196" s="14" t="n">
@@ -11976,7 +11976,7 @@
         <v>5.3038114E7</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>6099252.0</v>
+        <v>3.2936521E7</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="2" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
       <c r="AC196" s="2" t="inlineStr"/>
       <c r="AD196" s="2" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>3.4792634E7</v>
+        <v>1.0025365E7</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12294,14 +12294,14 @@
       <c r="N202" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000295. BPJS Ketenagakerjaan</t>
+            <t xml:space="preserve">000301. Gaji PPPK Paruh Waktu (PPB)</t>
           </r>
         </is>
       </c>
       <c r="O202" s="13" t="inlineStr"/>
       <c r="P202" s="13" t="inlineStr"/>
       <c r="Q202" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="R202" s="14" t="inlineStr"/>
       <c r="S202" s="14" t="n">
@@ -12314,16 +12314,16 @@
         <v>0.0</v>
       </c>
       <c r="X202" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="Y202" s="14" t="inlineStr"/>
       <c r="Z202" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="AA202" s="14" t="inlineStr"/>
       <c r="AB202" s="14" t="inlineStr"/>
       <c r="AC202" s="15" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD202" s="15" t="inlineStr"/>
       <c r="AE202" s="14" t="n">
@@ -12342,23 +12342,29 @@
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr"/>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr"/>
-      <c r="K203" s="2" t="inlineStr"/>
-      <c r="L203" s="2" t="inlineStr"/>
-      <c r="M203" s="2" t="inlineStr"/>
-      <c r="N203" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000301. Gaji PPPK Paruh Waktu (PPB)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H203" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I203" s="13" t="inlineStr"/>
+      <c r="J203" s="13" t="inlineStr"/>
+      <c r="K203" s="13" t="inlineStr"/>
+      <c r="L203" s="13" t="inlineStr"/>
+      <c r="M203" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N203" s="13" t="inlineStr"/>
       <c r="O203" s="13" t="inlineStr"/>
       <c r="P203" s="13" t="inlineStr"/>
       <c r="Q203" s="14" t="n">
-        <v>2.34E7</v>
+        <v>1.488E7</v>
       </c>
       <c r="R203" s="14" t="inlineStr"/>
       <c r="S203" s="14" t="n">
@@ -12368,23 +12374,23 @@
       <c r="U203" s="14" t="inlineStr"/>
       <c r="V203" s="14" t="inlineStr"/>
       <c r="W203" s="14" t="n">
-        <v>0.0</v>
+        <v>9332000.0</v>
       </c>
       <c r="X203" s="14" t="n">
-        <v>2.34E7</v>
+        <v>1380500.0</v>
       </c>
       <c r="Y203" s="14" t="inlineStr"/>
       <c r="Z203" s="14" t="n">
-        <v>2.34E7</v>
+        <v>1.07125E7</v>
       </c>
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>1.0</v>
+        <v>0.7199260752688172</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>0.0</v>
+        <v>4167500.0</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12399,29 +12405,23 @@
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I204" s="13" t="inlineStr"/>
-      <c r="J204" s="13" t="inlineStr"/>
-      <c r="K204" s="13" t="inlineStr"/>
-      <c r="L204" s="13" t="inlineStr"/>
-      <c r="M204" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N204" s="13" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr"/>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000133. Biaya Tol</t>
+          </r>
+        </is>
+      </c>
       <c r="O204" s="13" t="inlineStr"/>
       <c r="P204" s="13" t="inlineStr"/>
       <c r="Q204" s="14" t="n">
-        <v>1.23E7</v>
+        <v>1.038E7</v>
       </c>
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="14" t="n">
@@ -12431,23 +12431,23 @@
       <c r="U204" s="14" t="inlineStr"/>
       <c r="V204" s="14" t="inlineStr"/>
       <c r="W204" s="14" t="n">
-        <v>9332000.0</v>
+        <v>5696000.0</v>
       </c>
       <c r="X204" s="14" t="n">
         <v>1380500.0</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>1.07125E7</v>
+        <v>7076500.0</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.8709349593495935</v>
+        <v>0.6817437379576108</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>1587500.0</v>
+        <v>3303500.0</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12471,14 +12471,14 @@
       <c r="N205" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000133. Biaya Tol</t>
+            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
           </r>
         </is>
       </c>
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>7800000.0</v>
+        <v>4500000.0</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12488,23 +12488,23 @@
       <c r="U205" s="14" t="inlineStr"/>
       <c r="V205" s="14" t="inlineStr"/>
       <c r="W205" s="14" t="n">
-        <v>5696000.0</v>
+        <v>3636000.0</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>1380500.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>7076500.0</v>
+        <v>3636000.0</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.9072435897435898</v>
+        <v>0.808</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>723500.0</v>
+        <v>864000.0</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12519,23 +12519,29 @@
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr"/>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="2" t="inlineStr"/>
-      <c r="M206" s="2" t="inlineStr"/>
-      <c r="N206" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
-          </r>
-        </is>
-      </c>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521211</t>
+          </r>
+        </is>
+      </c>
+      <c r="I206" s="13" t="inlineStr"/>
+      <c r="J206" s="13" t="inlineStr"/>
+      <c r="K206" s="13" t="inlineStr"/>
+      <c r="L206" s="13" t="inlineStr"/>
+      <c r="M206" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Bahan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N206" s="13" t="inlineStr"/>
       <c r="O206" s="13" t="inlineStr"/>
       <c r="P206" s="13" t="inlineStr"/>
       <c r="Q206" s="14" t="n">
-        <v>4500000.0</v>
+        <v>7.8581E7</v>
       </c>
       <c r="R206" s="14" t="inlineStr"/>
       <c r="S206" s="14" t="n">
@@ -12545,23 +12551,23 @@
       <c r="U206" s="14" t="inlineStr"/>
       <c r="V206" s="14" t="inlineStr"/>
       <c r="W206" s="14" t="n">
-        <v>3636000.0</v>
+        <v>4.907101E7</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>0.0</v>
+        <v>1.15831E7</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
-        <v>3636000.0</v>
+        <v>6.065411E7</v>
       </c>
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.808</v>
+        <v>0.7718673725200749</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>864000.0</v>
+        <v>1.792689E7</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12576,29 +12582,23 @@
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521211</t>
-          </r>
-        </is>
-      </c>
-      <c r="I207" s="13" t="inlineStr"/>
-      <c r="J207" s="13" t="inlineStr"/>
-      <c r="K207" s="13" t="inlineStr"/>
-      <c r="L207" s="13" t="inlineStr"/>
-      <c r="M207" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Bahan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N207" s="13" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
+          </r>
+        </is>
+      </c>
       <c r="O207" s="13" t="inlineStr"/>
       <c r="P207" s="13" t="inlineStr"/>
       <c r="Q207" s="14" t="n">
-        <v>8.0556E7</v>
+        <v>7.2501E7</v>
       </c>
       <c r="R207" s="14" t="inlineStr"/>
       <c r="S207" s="14" t="n">
@@ -12611,20 +12611,20 @@
         <v>4.907101E7</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>6195000.0</v>
+        <v>1.15831E7</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>5.526601E7</v>
+        <v>6.065411E7</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.6860570286508764</v>
+        <v>0.8365968745258686</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>2.528999E7</v>
+        <v>1.184689E7</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12648,14 +12648,14 @@
       <c r="N208" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
+            <t xml:space="preserve">000306. Konsumsi Rapat</t>
           </r>
         </is>
       </c>
       <c r="O208" s="13" t="inlineStr"/>
       <c r="P208" s="13" t="inlineStr"/>
       <c r="Q208" s="14" t="n">
-        <v>7.4476E7</v>
+        <v>6080000.0</v>
       </c>
       <c r="R208" s="14" t="inlineStr"/>
       <c r="S208" s="14" t="n">
@@ -12665,23 +12665,23 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>4.907101E7</v>
+        <v>0.0</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>6195000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>5.526601E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.7420646919813094</v>
+        <v>0.0</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.920999E7</v>
+        <v>6080000.0</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12696,23 +12696,29 @@
       <c r="E209" s="2" t="inlineStr"/>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr"/>
-      <c r="I209" s="2" t="inlineStr"/>
-      <c r="J209" s="2" t="inlineStr"/>
-      <c r="K209" s="2" t="inlineStr"/>
-      <c r="L209" s="2" t="inlineStr"/>
-      <c r="M209" s="2" t="inlineStr"/>
-      <c r="N209" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000306. Konsumsi Rapat</t>
-          </r>
-        </is>
-      </c>
+      <c r="H209" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I209" s="13" t="inlineStr"/>
+      <c r="J209" s="13" t="inlineStr"/>
+      <c r="K209" s="13" t="inlineStr"/>
+      <c r="L209" s="13" t="inlineStr"/>
+      <c r="M209" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N209" s="13" t="inlineStr"/>
       <c r="O209" s="13" t="inlineStr"/>
       <c r="P209" s="13" t="inlineStr"/>
       <c r="Q209" s="14" t="n">
-        <v>6080000.0</v>
+        <v>1.1E7</v>
       </c>
       <c r="R209" s="14" t="inlineStr"/>
       <c r="S209" s="14" t="n">
@@ -12722,23 +12728,23 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>0.0</v>
+        <v>4274800.0</v>
       </c>
       <c r="X209" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>0.0</v>
+        <v>4274800.0</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.0</v>
+        <v>0.3886181818181818</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>6080000.0</v>
+        <v>6725200.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12753,29 +12759,23 @@
       <c r="E210" s="2" t="inlineStr"/>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I210" s="13" t="inlineStr"/>
-      <c r="J210" s="13" t="inlineStr"/>
-      <c r="K210" s="13" t="inlineStr"/>
-      <c r="L210" s="13" t="inlineStr"/>
-      <c r="M210" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N210" s="13" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000137. Bahan Komputer</t>
+          </r>
+        </is>
+      </c>
       <c r="O210" s="13" t="inlineStr"/>
       <c r="P210" s="13" t="inlineStr"/>
       <c r="Q210" s="14" t="n">
-        <v>1.1E7</v>
+        <v>9000000.0</v>
       </c>
       <c r="R210" s="14" t="inlineStr"/>
       <c r="S210" s="14" t="n">
@@ -12785,23 +12785,23 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>4274800.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="X210" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>4274800.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.3886181818181818</v>
+        <v>0.44053333333333333</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>6725200.0</v>
+        <v>5035200.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12825,14 +12825,14 @@
       <c r="N211" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000137. Bahan Komputer</t>
+            <t xml:space="preserve">000292. ATK</t>
           </r>
         </is>
       </c>
       <c r="O211" s="13" t="inlineStr"/>
       <c r="P211" s="13" t="inlineStr"/>
       <c r="Q211" s="14" t="n">
-        <v>9000000.0</v>
+        <v>2000000.0</v>
       </c>
       <c r="R211" s="14" t="inlineStr"/>
       <c r="S211" s="14" t="n">
@@ -12842,23 +12842,23 @@
       <c r="U211" s="14" t="inlineStr"/>
       <c r="V211" s="14" t="inlineStr"/>
       <c r="W211" s="14" t="n">
-        <v>3964800.0</v>
+        <v>310000.0</v>
       </c>
       <c r="X211" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>3964800.0</v>
+        <v>310000.0</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.44053333333333333</v>
+        <v>0.155</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>5035200.0</v>
+        <v>1690000.0</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
@@ -12873,23 +12873,29 @@
       <c r="E212" s="2" t="inlineStr"/>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="inlineStr"/>
-      <c r="M212" s="2" t="inlineStr"/>
-      <c r="N212" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000292. ATK</t>
-          </r>
-        </is>
-      </c>
+      <c r="H212" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I212" s="13" t="inlineStr"/>
+      <c r="J212" s="13" t="inlineStr"/>
+      <c r="K212" s="13" t="inlineStr"/>
+      <c r="L212" s="13" t="inlineStr"/>
+      <c r="M212" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N212" s="13" t="inlineStr"/>
       <c r="O212" s="13" t="inlineStr"/>
       <c r="P212" s="13" t="inlineStr"/>
       <c r="Q212" s="14" t="n">
-        <v>2000000.0</v>
+        <v>3.011368E9</v>
       </c>
       <c r="R212" s="14" t="inlineStr"/>
       <c r="S212" s="14" t="n">
@@ -12899,30 +12905,30 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>310000.0</v>
+        <v>2.567718192E9</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>0.0</v>
+        <v>4.06024768E8</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>310000.0</v>
+        <v>2.97374296E9</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.155</v>
+        <v>0.987505665199338</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>1690000.0</v>
+        <v>3.762504E7</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
       <c r="AH212" s="14" t="inlineStr"/>
       <c r="AI212" s="14" t="inlineStr"/>
     </row>
-    <row r="213" customHeight="1" ht="15">
+    <row r="213" customHeight="1" ht="18">
       <c r="A213" s="2" t="inlineStr"/>
       <c r="B213" s="2" t="inlineStr"/>
       <c r="C213" s="2" t="inlineStr"/>
@@ -12930,29 +12936,23 @@
       <c r="E213" s="2" t="inlineStr"/>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I213" s="13" t="inlineStr"/>
-      <c r="J213" s="13" t="inlineStr"/>
-      <c r="K213" s="13" t="inlineStr"/>
-      <c r="L213" s="13" t="inlineStr"/>
-      <c r="M213" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N213" s="13" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O213" s="13" t="inlineStr"/>
       <c r="P213" s="13" t="inlineStr"/>
       <c r="Q213" s="14" t="n">
-        <v>3.011368E9</v>
+        <v>4.0995E8</v>
       </c>
       <c r="R213" s="14" t="inlineStr"/>
       <c r="S213" s="14" t="n">
@@ -12962,30 +12962,30 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>2.567718192E9</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>2.21538268E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>2.78925646E9</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.9262423124639698</v>
+        <v>0.9997474423710209</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>2.2211154E8</v>
+        <v>103536.0</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
       <c r="AH213" s="14" t="inlineStr"/>
       <c r="AI213" s="14" t="inlineStr"/>
     </row>
-    <row r="214" customHeight="1" ht="18">
+    <row r="214" customHeight="1" ht="15">
       <c r="A214" s="2" t="inlineStr"/>
       <c r="B214" s="2" t="inlineStr"/>
       <c r="C214" s="2" t="inlineStr"/>
@@ -13002,14 +13002,14 @@
       <c r="N214" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
+            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O214" s="13" t="inlineStr"/>
       <c r="P214" s="13" t="inlineStr"/>
       <c r="Q214" s="14" t="n">
-        <v>4.0995E8</v>
+        <v>1.226E8</v>
       </c>
       <c r="R214" s="14" t="inlineStr"/>
       <c r="S214" s="14" t="n">
@@ -13019,30 +13019,30 @@
       <c r="U214" s="14" t="inlineStr"/>
       <c r="V214" s="14" t="inlineStr"/>
       <c r="W214" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>1.0331888E8</v>
       </c>
       <c r="X214" s="14" t="n">
-        <v>0.0</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>1.12787408E8</v>
       </c>
       <c r="AA214" s="14" t="inlineStr"/>
       <c r="AB214" s="14" t="inlineStr"/>
       <c r="AC214" s="15" t="n">
-        <v>0.9997474423710209</v>
+        <v>0.9199625448613377</v>
       </c>
       <c r="AD214" s="15" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
-        <v>103536.0</v>
+        <v>9812592.0</v>
       </c>
       <c r="AF214" s="14" t="inlineStr"/>
       <c r="AG214" s="14" t="inlineStr"/>
       <c r="AH214" s="14" t="inlineStr"/>
       <c r="AI214" s="14" t="inlineStr"/>
     </row>
-    <row r="215" customHeight="1" ht="15">
+    <row r="215" customHeight="1" ht="18">
       <c r="A215" s="2" t="inlineStr"/>
       <c r="B215" s="2" t="inlineStr"/>
       <c r="C215" s="2" t="inlineStr"/>
@@ -13059,14 +13059,14 @@
       <c r="N215" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
+            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O215" s="13" t="inlineStr"/>
       <c r="P215" s="13" t="inlineStr"/>
       <c r="Q215" s="14" t="n">
-        <v>1.226E8</v>
+        <v>1.3629E8</v>
       </c>
       <c r="R215" s="14" t="inlineStr"/>
       <c r="S215" s="14" t="n">
@@ -13076,23 +13076,23 @@
       <c r="U215" s="14" t="inlineStr"/>
       <c r="V215" s="14" t="inlineStr"/>
       <c r="W215" s="14" t="n">
-        <v>1.0331888E8</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="X215" s="14" t="n">
-        <v>9468528.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y215" s="14" t="inlineStr"/>
       <c r="Z215" s="14" t="n">
-        <v>1.12787408E8</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="AA215" s="14" t="inlineStr"/>
       <c r="AB215" s="14" t="inlineStr"/>
       <c r="AC215" s="15" t="n">
-        <v>0.9199625448613377</v>
+        <v>0.9994750605326876</v>
       </c>
       <c r="AD215" s="15" t="inlineStr"/>
       <c r="AE215" s="14" t="n">
-        <v>9812592.0</v>
+        <v>71544.0</v>
       </c>
       <c r="AF215" s="14" t="inlineStr"/>
       <c r="AG215" s="14" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       <c r="N216" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
+            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O216" s="13" t="inlineStr"/>
       <c r="P216" s="13" t="inlineStr"/>
       <c r="Q216" s="14" t="n">
-        <v>1.3629E8</v>
+        <v>4.59E7</v>
       </c>
       <c r="R216" s="14" t="inlineStr"/>
       <c r="S216" s="14" t="n">
@@ -13133,30 +13133,30 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="X216" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.9994750605326876</v>
+        <v>0.9996983006535948</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>71544.0</v>
+        <v>13848.0</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
       <c r="AH216" s="14" t="inlineStr"/>
       <c r="AI216" s="14" t="inlineStr"/>
     </row>
-    <row r="217" customHeight="1" ht="18">
+    <row r="217" customHeight="1" ht="15">
       <c r="A217" s="2" t="inlineStr"/>
       <c r="B217" s="2" t="inlineStr"/>
       <c r="C217" s="2" t="inlineStr"/>
@@ -13173,14 +13173,14 @@
       <c r="N217" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O217" s="13" t="inlineStr"/>
       <c r="P217" s="13" t="inlineStr"/>
       <c r="Q217" s="14" t="n">
-        <v>4.59E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="R217" s="14" t="inlineStr"/>
       <c r="S217" s="14" t="n">
@@ -13190,30 +13190,30 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>1.844865E9</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>0.0</v>
+        <v>3.68973E8</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.9996983006535948</v>
+        <v>1.0</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>13848.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
       <c r="AH217" s="14" t="inlineStr"/>
       <c r="AI217" s="14" t="inlineStr"/>
     </row>
-    <row r="218" customHeight="1" ht="15">
+    <row r="218" customHeight="1" ht="18">
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="2" t="inlineStr"/>
       <c r="C218" s="2" t="inlineStr"/>
@@ -13230,14 +13230,14 @@
       <c r="N218" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
+            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>6.89E7</v>
       </c>
       <c r="R218" s="14" t="inlineStr"/>
       <c r="S218" s="14" t="n">
@@ -13247,23 +13247,23 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>1.844865E9</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>2.0293515E9</v>
+        <v>4.5906624E7</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6662790130624093</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>1.844865E8</v>
+        <v>2.2993376E7</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13287,14 +13287,14 @@
       <c r="N219" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
+            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>6.89E7</v>
+        <v>1.389E7</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13304,54 +13304,60 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>4629928.0</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>4.5906624E7</v>
+        <v>9259856.0</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.6662790130624093</v>
+        <v>0.6666562994960403</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>2.2993376E7</v>
+        <v>4630144.0</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
       <c r="AH219" s="14" t="inlineStr"/>
       <c r="AI219" s="14" t="inlineStr"/>
     </row>
-    <row r="220" customHeight="1" ht="18">
+    <row r="220" customHeight="1" ht="15">
       <c r="A220" s="2" t="inlineStr"/>
       <c r="B220" s="2" t="inlineStr"/>
       <c r="C220" s="2" t="inlineStr"/>
       <c r="D220" s="2" t="inlineStr"/>
       <c r="E220" s="2" t="inlineStr"/>
-      <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="2" t="inlineStr"/>
-      <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="inlineStr"/>
-      <c r="M220" s="2" t="inlineStr"/>
-      <c r="N220" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
-          </r>
-        </is>
-      </c>
+      <c r="F220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DB</t>
+          </r>
+        </is>
+      </c>
+      <c r="G220" s="13" t="inlineStr"/>
+      <c r="H220" s="13" t="inlineStr"/>
+      <c r="I220" s="13" t="inlineStr"/>
+      <c r="J220" s="13" t="inlineStr"/>
+      <c r="K220" s="13" t="inlineStr"/>
+      <c r="L220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Langganan Daya dan Jasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="M220" s="13" t="inlineStr"/>
+      <c r="N220" s="13" t="inlineStr"/>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
-        <v>1.389E7</v>
+        <v>6.92704E8</v>
       </c>
       <c r="R220" s="14" t="inlineStr"/>
       <c r="S220" s="14" t="n">
@@ -13361,23 +13367,23 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>4629928.0</v>
+        <v>6.39230607E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>4629928.0</v>
+        <v>5.0385842E7</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>9259856.0</v>
+        <v>6.89616449E8</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.6666562994960403</v>
+        <v>0.9955427556358849</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>4630144.0</v>
+        <v>3087551.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13434,31 +13440,31 @@
       <c r="C222" s="2" t="inlineStr"/>
       <c r="D222" s="2" t="inlineStr"/>
       <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DB</t>
-          </r>
-        </is>
-      </c>
-      <c r="G222" s="13" t="inlineStr"/>
-      <c r="H222" s="13" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522111</t>
+          </r>
+        </is>
+      </c>
       <c r="I222" s="13" t="inlineStr"/>
       <c r="J222" s="13" t="inlineStr"/>
       <c r="K222" s="13" t="inlineStr"/>
-      <c r="L222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Langganan Daya dan Jasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="M222" s="13" t="inlineStr"/>
+      <c r="L222" s="13" t="inlineStr"/>
+      <c r="M222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
       <c r="N222" s="13" t="inlineStr"/>
       <c r="O222" s="13" t="inlineStr"/>
       <c r="P222" s="13" t="inlineStr"/>
       <c r="Q222" s="14" t="n">
-        <v>7.00144E8</v>
+        <v>5.0946E8</v>
       </c>
       <c r="R222" s="14" t="inlineStr"/>
       <c r="S222" s="14" t="n">
@@ -13468,23 +13474,23 @@
       <c r="U222" s="14" t="inlineStr"/>
       <c r="V222" s="14" t="inlineStr"/>
       <c r="W222" s="14" t="n">
-        <v>6.39230607E8</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>4.9616842E7</v>
+        <v>3.8886478E7</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>6.88847449E8</v>
+        <v>5.09400389E8</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.9838653891199525</v>
+        <v>0.9998829917952342</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>1.1296551E7</v>
+        <v>59611.0</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13499,29 +13505,23 @@
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I223" s="13" t="inlineStr"/>
-      <c r="J223" s="13" t="inlineStr"/>
-      <c r="K223" s="13" t="inlineStr"/>
-      <c r="L223" s="13" t="inlineStr"/>
-      <c r="M223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
-      <c r="N223" s="13" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000145. Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
       <c r="Q223" s="14" t="n">
-        <v>5.16E8</v>
+        <v>5.0946E8</v>
       </c>
       <c r="R223" s="14" t="inlineStr"/>
       <c r="S223" s="14" t="n">
@@ -13543,11 +13543,11 @@
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.9872100562015503</v>
+        <v>0.9998829917952342</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>6599611.0</v>
+        <v>59611.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13562,23 +13562,29 @@
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="2" t="inlineStr"/>
-      <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="2" t="inlineStr"/>
-      <c r="N224" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000145. Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
+      <c r="H224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522112</t>
+          </r>
+        </is>
+      </c>
+      <c r="I224" s="13" t="inlineStr"/>
+      <c r="J224" s="13" t="inlineStr"/>
+      <c r="K224" s="13" t="inlineStr"/>
+      <c r="L224" s="13" t="inlineStr"/>
+      <c r="M224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
+      <c r="N224" s="13" t="inlineStr"/>
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
       <c r="Q224" s="14" t="n">
-        <v>5.16E8</v>
+        <v>6000000.0</v>
       </c>
       <c r="R224" s="14" t="inlineStr"/>
       <c r="S224" s="14" t="n">
@@ -13588,23 +13594,23 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>5485232.0</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>3.8886478E7</v>
+        <v>263514.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>5.09400389E8</v>
+        <v>5748746.0</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.9872100562015503</v>
+        <v>0.9581243333333334</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>6599611.0</v>
+        <v>251254.0</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13619,25 +13625,19 @@
       <c r="E225" s="2" t="inlineStr"/>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522112</t>
-          </r>
-        </is>
-      </c>
-      <c r="I225" s="13" t="inlineStr"/>
-      <c r="J225" s="13" t="inlineStr"/>
-      <c r="K225" s="13" t="inlineStr"/>
-      <c r="L225" s="13" t="inlineStr"/>
-      <c r="M225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
-      <c r="N225" s="13" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000146. Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
       <c r="Q225" s="14" t="n">
@@ -13682,23 +13682,29 @@
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="2" t="inlineStr"/>
-      <c r="J226" s="2" t="inlineStr"/>
-      <c r="K226" s="2" t="inlineStr"/>
-      <c r="L226" s="2" t="inlineStr"/>
-      <c r="M226" s="2" t="inlineStr"/>
-      <c r="N226" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000146. Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
+      <c r="H226" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522113</t>
+          </r>
+        </is>
+      </c>
+      <c r="I226" s="13" t="inlineStr"/>
+      <c r="J226" s="13" t="inlineStr"/>
+      <c r="K226" s="13" t="inlineStr"/>
+      <c r="L226" s="13" t="inlineStr"/>
+      <c r="M226" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Air</t>
+          </r>
+        </is>
+      </c>
+      <c r="N226" s="13" t="inlineStr"/>
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
       <c r="Q226" s="14" t="n">
-        <v>6000000.0</v>
+        <v>3.2544E7</v>
       </c>
       <c r="R226" s="14" t="inlineStr"/>
       <c r="S226" s="14" t="n">
@@ -13708,23 +13714,23 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>5485232.0</v>
+        <v>3.021E7</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>263514.0</v>
+        <v>1216100.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>5748746.0</v>
+        <v>3.14261E7</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9581243333333334</v>
+        <v>0.9656495821042281</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>251254.0</v>
+        <v>1117900.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13739,29 +13745,23 @@
       <c r="E227" s="2" t="inlineStr"/>
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522113</t>
-          </r>
-        </is>
-      </c>
-      <c r="I227" s="13" t="inlineStr"/>
-      <c r="J227" s="13" t="inlineStr"/>
-      <c r="K227" s="13" t="inlineStr"/>
-      <c r="L227" s="13" t="inlineStr"/>
-      <c r="M227" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Air</t>
-          </r>
-        </is>
-      </c>
-      <c r="N227" s="13" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr"/>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr"/>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
+          </r>
+        </is>
+      </c>
       <c r="O227" s="13" t="inlineStr"/>
       <c r="P227" s="13" t="inlineStr"/>
       <c r="Q227" s="14" t="n">
-        <v>3.3444E7</v>
+        <v>3.2544E7</v>
       </c>
       <c r="R227" s="14" t="inlineStr"/>
       <c r="S227" s="14" t="n">
@@ -13783,11 +13783,11 @@
       <c r="AA227" s="14" t="inlineStr"/>
       <c r="AB227" s="14" t="inlineStr"/>
       <c r="AC227" s="15" t="n">
-        <v>0.9396633177849539</v>
+        <v>0.9656495821042281</v>
       </c>
       <c r="AD227" s="15" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
-        <v>2017900.0</v>
+        <v>1117900.0</v>
       </c>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
@@ -13802,23 +13802,29 @@
       <c r="E228" s="2" t="inlineStr"/>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr"/>
-      <c r="I228" s="2" t="inlineStr"/>
-      <c r="J228" s="2" t="inlineStr"/>
-      <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="2" t="inlineStr"/>
-      <c r="M228" s="2" t="inlineStr"/>
-      <c r="N228" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H228" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I228" s="13" t="inlineStr"/>
+      <c r="J228" s="13" t="inlineStr"/>
+      <c r="K228" s="13" t="inlineStr"/>
+      <c r="L228" s="13" t="inlineStr"/>
+      <c r="M228" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N228" s="13" t="inlineStr"/>
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
       <c r="Q228" s="14" t="n">
-        <v>3.3444E7</v>
+        <v>1.447E8</v>
       </c>
       <c r="R228" s="14" t="inlineStr"/>
       <c r="S228" s="14" t="n">
@@ -13828,23 +13834,23 @@
       <c r="U228" s="14" t="inlineStr"/>
       <c r="V228" s="14" t="inlineStr"/>
       <c r="W228" s="14" t="n">
-        <v>3.021E7</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>1216100.0</v>
+        <v>1.001975E7</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>3.14261E7</v>
+        <v>1.43041214E8</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.9396633177849539</v>
+        <v>0.9885363787145819</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>2017900.0</v>
+        <v>1658786.0</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13859,29 +13865,23 @@
       <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I229" s="13" t="inlineStr"/>
-      <c r="J229" s="13" t="inlineStr"/>
-      <c r="K229" s="13" t="inlineStr"/>
-      <c r="L229" s="13" t="inlineStr"/>
-      <c r="M229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N229" s="13" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr"/>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000148. Langganan Internet</t>
+          </r>
+        </is>
+      </c>
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>1.447E8</v>
+        <v>1.1508E8</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13891,23 +13891,23 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>1.044355E8</v>
       </c>
       <c r="X229" s="14" t="n">
         <v>9250750.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>1.42272214E8</v>
+        <v>1.1368625E8</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.9832219350380097</v>
+        <v>0.9878888599235315</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>2427786.0</v>
+        <v>1393750.0</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13931,14 +13931,14 @@
       <c r="N230" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000148. Langganan Internet</t>
+            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
           </r>
         </is>
       </c>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>1.146E8</v>
+        <v>2.962E7</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13948,23 +13948,23 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>9250750.0</v>
+        <v>769000.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>1.1368625E8</v>
+        <v>2.9354964E7</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.9920266143106458</v>
+        <v>0.9910521269412559</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>913750.0</v>
+        <v>265036.0</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -13977,25 +13977,31 @@
       <c r="C231" s="2" t="inlineStr"/>
       <c r="D231" s="2" t="inlineStr"/>
       <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="2" t="inlineStr"/>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr"/>
-      <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr"/>
-      <c r="N231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
-          </r>
-        </is>
-      </c>
+      <c r="F231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DC</t>
+          </r>
+        </is>
+      </c>
+      <c r="G231" s="13" t="inlineStr"/>
+      <c r="H231" s="13" t="inlineStr"/>
+      <c r="I231" s="13" t="inlineStr"/>
+      <c r="J231" s="13" t="inlineStr"/>
+      <c r="K231" s="13" t="inlineStr"/>
+      <c r="L231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pemeliharaan Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M231" s="13" t="inlineStr"/>
+      <c r="N231" s="13" t="inlineStr"/>
       <c r="O231" s="13" t="inlineStr"/>
       <c r="P231" s="13" t="inlineStr"/>
       <c r="Q231" s="14" t="n">
-        <v>3.01E7</v>
+        <v>1.093185E9</v>
       </c>
       <c r="R231" s="14" t="inlineStr"/>
       <c r="S231" s="14" t="n">
@@ -14005,23 +14011,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>6.19636199E8</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>0.0</v>
+        <v>2.6653311E8</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>8.86169309E8</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.9496998006644518</v>
+        <v>0.810630688309847</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>1514036.0</v>
+        <v>2.07015691E8</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14034,31 +14040,31 @@
       <c r="C232" s="2" t="inlineStr"/>
       <c r="D232" s="2" t="inlineStr"/>
       <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DC</t>
-          </r>
-        </is>
-      </c>
-      <c r="G232" s="13" t="inlineStr"/>
-      <c r="H232" s="13" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
       <c r="I232" s="13" t="inlineStr"/>
       <c r="J232" s="13" t="inlineStr"/>
       <c r="K232" s="13" t="inlineStr"/>
-      <c r="L232" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pemeliharaan Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M232" s="13" t="inlineStr"/>
+      <c r="L232" s="13" t="inlineStr"/>
+      <c r="M232" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
       <c r="N232" s="13" t="inlineStr"/>
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>1.10842E9</v>
+        <v>2.4E8</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14068,23 +14074,23 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>6.19636199E8</v>
+        <v>1.9288E8</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>8.6743092E7</v>
+        <v>2.50325E7</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>7.06379291E8</v>
+        <v>2.179125E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.6372848658450768</v>
+        <v>0.90796875</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>4.02040709E8</v>
+        <v>2.20875E7</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14099,29 +14105,23 @@
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I233" s="13" t="inlineStr"/>
-      <c r="J233" s="13" t="inlineStr"/>
-      <c r="K233" s="13" t="inlineStr"/>
-      <c r="L233" s="13" t="inlineStr"/>
-      <c r="M233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N233" s="13" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr"/>
+      <c r="M233" s="2" t="inlineStr"/>
+      <c r="N233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
+          </r>
+        </is>
+      </c>
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>2.4E8</v>
+        <v>1.8E8</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14131,23 +14131,23 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>1.9288E8</v>
+        <v>1.5279E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>2.50325E7</v>
+        <v>1.5125E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>2.179125E8</v>
+        <v>1.67915E8</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.90796875</v>
+        <v>0.9328611111111111</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>2.20875E7</v>
+        <v>1.2085E7</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14171,14 +14171,14 @@
       <c r="N234" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
+            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
           </r>
         </is>
       </c>
       <c r="O234" s="13" t="inlineStr"/>
       <c r="P234" s="13" t="inlineStr"/>
       <c r="Q234" s="14" t="n">
-        <v>1.8E8</v>
+        <v>6.0E7</v>
       </c>
       <c r="R234" s="14" t="inlineStr"/>
       <c r="S234" s="14" t="n">
@@ -14188,23 +14188,23 @@
       <c r="U234" s="14" t="inlineStr"/>
       <c r="V234" s="14" t="inlineStr"/>
       <c r="W234" s="14" t="n">
-        <v>1.5279E8</v>
+        <v>4.009E7</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>1.5125E7</v>
+        <v>9907500.0</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>1.67915E8</v>
+        <v>4.99975E7</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.9328611111111111</v>
+        <v>0.8332916666666667</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>1.2085E7</v>
+        <v>1.00025E7</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14219,23 +14219,29 @@
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr"/>
-      <c r="I235" s="2" t="inlineStr"/>
-      <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="inlineStr"/>
-      <c r="M235" s="2" t="inlineStr"/>
-      <c r="N235" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
-          </r>
-        </is>
-      </c>
+      <c r="H235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I235" s="13" t="inlineStr"/>
+      <c r="J235" s="13" t="inlineStr"/>
+      <c r="K235" s="13" t="inlineStr"/>
+      <c r="L235" s="13" t="inlineStr"/>
+      <c r="M235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N235" s="13" t="inlineStr"/>
       <c r="O235" s="13" t="inlineStr"/>
       <c r="P235" s="13" t="inlineStr"/>
       <c r="Q235" s="14" t="n">
-        <v>6.0E7</v>
+        <v>3.041E7</v>
       </c>
       <c r="R235" s="14" t="inlineStr"/>
       <c r="S235" s="14" t="n">
@@ -14245,23 +14251,23 @@
       <c r="U235" s="14" t="inlineStr"/>
       <c r="V235" s="14" t="inlineStr"/>
       <c r="W235" s="14" t="n">
-        <v>4.009E7</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>9907500.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>4.99975E7</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.8332916666666667</v>
+        <v>0.9998942781979612</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>1.00025E7</v>
+        <v>3215.0</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14276,25 +14282,19 @@
       <c r="E236" s="2" t="inlineStr"/>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I236" s="13" t="inlineStr"/>
-      <c r="J236" s="13" t="inlineStr"/>
-      <c r="K236" s="13" t="inlineStr"/>
-      <c r="L236" s="13" t="inlineStr"/>
-      <c r="M236" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N236" s="13" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr"/>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
+          </r>
+        </is>
+      </c>
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
@@ -14339,23 +14339,29 @@
       <c r="E237" s="2" t="inlineStr"/>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr"/>
-      <c r="I237" s="2" t="inlineStr"/>
-      <c r="J237" s="2" t="inlineStr"/>
-      <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="2" t="inlineStr"/>
-      <c r="M237" s="2" t="inlineStr"/>
-      <c r="N237" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
-          </r>
-        </is>
-      </c>
+      <c r="H237" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I237" s="13" t="inlineStr"/>
+      <c r="J237" s="13" t="inlineStr"/>
+      <c r="K237" s="13" t="inlineStr"/>
+      <c r="L237" s="13" t="inlineStr"/>
+      <c r="M237" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N237" s="13" t="inlineStr"/>
       <c r="O237" s="13" t="inlineStr"/>
       <c r="P237" s="13" t="inlineStr"/>
       <c r="Q237" s="14" t="n">
-        <v>3.041E7</v>
+        <v>3.47E8</v>
       </c>
       <c r="R237" s="14" t="inlineStr"/>
       <c r="S237" s="14" t="n">
@@ -14365,23 +14371,23 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>1.28808533E8</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>0.0</v>
+        <v>8.63665E7</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>2.15175033E8</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.9998942781979612</v>
+        <v>0.6201009596541787</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>3215.0</v>
+        <v>1.31824967E8</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14396,29 +14402,23 @@
       <c r="E238" s="2" t="inlineStr"/>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I238" s="13" t="inlineStr"/>
-      <c r="J238" s="13" t="inlineStr"/>
-      <c r="K238" s="13" t="inlineStr"/>
-      <c r="L238" s="13" t="inlineStr"/>
-      <c r="M238" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N238" s="13" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
+          </r>
+        </is>
+      </c>
       <c r="O238" s="13" t="inlineStr"/>
       <c r="P238" s="13" t="inlineStr"/>
       <c r="Q238" s="14" t="n">
-        <v>3.5259E8</v>
+        <v>1.7E7</v>
       </c>
       <c r="R238" s="14" t="inlineStr"/>
       <c r="S238" s="14" t="n">
@@ -14428,30 +14428,30 @@
       <c r="U238" s="14" t="inlineStr"/>
       <c r="V238" s="14" t="inlineStr"/>
       <c r="W238" s="14" t="n">
-        <v>1.28808533E8</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>3.0489E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>1.59297533E8</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.4517925437476956</v>
+        <v>0.9959777647058824</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>1.93292467E8</v>
+        <v>68378.0</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
       <c r="AH238" s="14" t="inlineStr"/>
       <c r="AI238" s="14" t="inlineStr"/>
     </row>
-    <row r="239" customHeight="1" ht="15">
+    <row r="239" customHeight="1" ht="18">
       <c r="A239" s="2" t="inlineStr"/>
       <c r="B239" s="2" t="inlineStr"/>
       <c r="C239" s="2" t="inlineStr"/>
@@ -14468,14 +14468,14 @@
       <c r="N239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
+            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O239" s="13" t="inlineStr"/>
       <c r="P239" s="13" t="inlineStr"/>
       <c r="Q239" s="14" t="n">
-        <v>1.7E7</v>
+        <v>3.73E7</v>
       </c>
       <c r="R239" s="14" t="inlineStr"/>
       <c r="S239" s="14" t="n">
@@ -14485,30 +14485,30 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="X239" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.9959777647058824</v>
+        <v>0.5723136461126005</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>68378.0</v>
+        <v>1.5952701E7</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
       <c r="AH239" s="14" t="inlineStr"/>
       <c r="AI239" s="14" t="inlineStr"/>
     </row>
-    <row r="240" customHeight="1" ht="18">
+    <row r="240" customHeight="1" ht="15">
       <c r="A240" s="2" t="inlineStr"/>
       <c r="B240" s="2" t="inlineStr"/>
       <c r="C240" s="2" t="inlineStr"/>
@@ -14525,14 +14525,14 @@
       <c r="N240" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
+            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O240" s="13" t="inlineStr"/>
       <c r="P240" s="13" t="inlineStr"/>
       <c r="Q240" s="14" t="n">
-        <v>3.73E7</v>
+        <v>2.595E7</v>
       </c>
       <c r="R240" s="14" t="inlineStr"/>
       <c r="S240" s="14" t="n">
@@ -14542,23 +14542,23 @@
       <c r="U240" s="14" t="inlineStr"/>
       <c r="V240" s="14" t="inlineStr"/>
       <c r="W240" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X240" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.5723136461126005</v>
+        <v>0.9759922928709056</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>1.5952701E7</v>
+        <v>623000.0</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -14582,14 +14582,14 @@
       <c r="N241" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
+            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O241" s="13" t="inlineStr"/>
       <c r="P241" s="13" t="inlineStr"/>
       <c r="Q241" s="14" t="n">
-        <v>2.595E7</v>
+        <v>2170000.0</v>
       </c>
       <c r="R241" s="14" t="inlineStr"/>
       <c r="S241" s="14" t="n">
@@ -14599,23 +14599,23 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="X241" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.9986175115207373</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>623000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14639,14 +14639,14 @@
       <c r="N242" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
+            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>2170000.0</v>
+        <v>1.236E8</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14656,23 +14656,23 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>2167000.0</v>
+        <v>4421000.0</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5076E7</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>2167000.0</v>
+        <v>2.9497E7</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.9986175115207373</v>
+        <v>0.23864886731391585</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>3000.0</v>
+        <v>9.4103E7</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14696,14 +14696,14 @@
       <c r="N243" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
+            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O243" s="13" t="inlineStr"/>
       <c r="P243" s="13" t="inlineStr"/>
       <c r="Q243" s="14" t="n">
-        <v>1.156E8</v>
+        <v>1400000.0</v>
       </c>
       <c r="R243" s="14" t="inlineStr"/>
       <c r="S243" s="14" t="n">
@@ -14713,23 +14713,23 @@
       <c r="U243" s="14" t="inlineStr"/>
       <c r="V243" s="14" t="inlineStr"/>
       <c r="W243" s="14" t="n">
-        <v>4421000.0</v>
+        <v>1360000.0</v>
       </c>
       <c r="X243" s="14" t="n">
-        <v>2.5076E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>2.9497E7</v>
+        <v>1360000.0</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.2551643598615917</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>8.6103E7</v>
+        <v>40000.0</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14753,14 +14753,14 @@
       <c r="N244" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
+            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
           </r>
         </is>
       </c>
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>2800000.0</v>
+        <v>1.66E7</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14770,23 +14770,23 @@
       <c r="U244" s="14" t="inlineStr"/>
       <c r="V244" s="14" t="inlineStr"/>
       <c r="W244" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="X244" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.7315434939759036</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>1440000.0</v>
+        <v>4456378.0</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14810,14 +14810,14 @@
       <c r="N245" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
+            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O245" s="13" t="inlineStr"/>
       <c r="P245" s="13" t="inlineStr"/>
       <c r="Q245" s="14" t="n">
-        <v>2.66E7</v>
+        <v>1.444E7</v>
       </c>
       <c r="R245" s="14" t="inlineStr"/>
       <c r="S245" s="14" t="n">
@@ -14827,23 +14827,23 @@
       <c r="U245" s="14" t="inlineStr"/>
       <c r="V245" s="14" t="inlineStr"/>
       <c r="W245" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1.443E7</v>
       </c>
       <c r="X245" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1.443E7</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.45652714285714285</v>
+        <v>0.9993074792243767</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>1.4456378E7</v>
+        <v>10000.0</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -14867,14 +14867,14 @@
       <c r="N246" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
+            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O246" s="13" t="inlineStr"/>
       <c r="P246" s="13" t="inlineStr"/>
       <c r="Q246" s="14" t="n">
-        <v>1.443E7</v>
+        <v>4150000.0</v>
       </c>
       <c r="R246" s="14" t="inlineStr"/>
       <c r="S246" s="14" t="n">
@@ -14884,23 +14884,23 @@
       <c r="U246" s="14" t="inlineStr"/>
       <c r="V246" s="14" t="inlineStr"/>
       <c r="W246" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1576500.0</v>
       </c>
       <c r="X246" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1576500.0</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>1.0</v>
+        <v>0.37987951807228915</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>0.0</v>
+        <v>2573500.0</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -14924,14 +14924,14 @@
       <c r="N247" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
+            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O247" s="13" t="inlineStr"/>
       <c r="P247" s="13" t="inlineStr"/>
       <c r="Q247" s="14" t="n">
-        <v>4150000.0</v>
+        <v>4400000.0</v>
       </c>
       <c r="R247" s="14" t="inlineStr"/>
       <c r="S247" s="14" t="n">
@@ -14941,23 +14941,23 @@
       <c r="U247" s="14" t="inlineStr"/>
       <c r="V247" s="14" t="inlineStr"/>
       <c r="W247" s="14" t="n">
-        <v>1576500.0</v>
+        <v>4180000.0</v>
       </c>
       <c r="X247" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>1576500.0</v>
+        <v>4180000.0</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.37987951807228915</v>
+        <v>0.95</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>2573500.0</v>
+        <v>220000.0</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
       <c r="N249" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
+            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O249" s="13" t="inlineStr"/>
       <c r="P249" s="13" t="inlineStr"/>
       <c r="Q249" s="14" t="n">
-        <v>4400000.0</v>
+        <v>3.65E7</v>
       </c>
       <c r="R249" s="14" t="inlineStr"/>
       <c r="S249" s="14" t="n">
@@ -15042,23 +15042,23 @@
       <c r="U249" s="14" t="inlineStr"/>
       <c r="V249" s="14" t="inlineStr"/>
       <c r="W249" s="14" t="n">
-        <v>4180000.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X249" s="14" t="n">
-        <v>0.0</v>
+        <v>2.11705E7</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
-        <v>4180000.0</v>
+        <v>3.64545E7</v>
       </c>
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.95</v>
+        <v>0.9987534246575343</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>220000.0</v>
+        <v>45500.0</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15082,14 +15082,14 @@
       <c r="N250" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
+            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O250" s="13" t="inlineStr"/>
       <c r="P250" s="13" t="inlineStr"/>
       <c r="Q250" s="14" t="n">
-        <v>4.21E7</v>
+        <v>3.059E7</v>
       </c>
       <c r="R250" s="14" t="inlineStr"/>
       <c r="S250" s="14" t="n">
@@ -15099,23 +15099,23 @@
       <c r="U250" s="14" t="inlineStr"/>
       <c r="V250" s="14" t="inlineStr"/>
       <c r="W250" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>0.0</v>
       </c>
       <c r="X250" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0407E7</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>3.0407E7</v>
       </c>
       <c r="AA250" s="14" t="inlineStr"/>
       <c r="AB250" s="14" t="inlineStr"/>
       <c r="AC250" s="15" t="n">
-        <v>0.36304038004750594</v>
+        <v>0.9940176528277215</v>
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>2.6816E7</v>
+        <v>183000.0</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15139,14 +15139,14 @@
       <c r="N251" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
+            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
           </r>
         </is>
       </c>
       <c r="O251" s="13" t="inlineStr"/>
       <c r="P251" s="13" t="inlineStr"/>
       <c r="Q251" s="14" t="n">
-        <v>3.059E7</v>
+        <v>1.0E7</v>
       </c>
       <c r="R251" s="14" t="inlineStr"/>
       <c r="S251" s="14" t="n">
@@ -15156,23 +15156,23 @@
       <c r="U251" s="14" t="inlineStr"/>
       <c r="V251" s="14" t="inlineStr"/>
       <c r="W251" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="X251" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.0</v>
+        <v>0.964049</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>3.059E7</v>
+        <v>359510.0</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15196,14 +15196,14 @@
       <c r="N252" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
+            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O252" s="13" t="inlineStr"/>
       <c r="P252" s="13" t="inlineStr"/>
       <c r="Q252" s="14" t="n">
-        <v>1.0E7</v>
+        <v>4300000.0</v>
       </c>
       <c r="R252" s="14" t="inlineStr"/>
       <c r="S252" s="14" t="n">
@@ -15213,23 +15213,23 @@
       <c r="U252" s="14" t="inlineStr"/>
       <c r="V252" s="14" t="inlineStr"/>
       <c r="W252" s="14" t="n">
-        <v>9640490.0</v>
+        <v>0.0</v>
       </c>
       <c r="X252" s="14" t="n">
-        <v>0.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>9640490.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.964049</v>
+        <v>1.0</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>359510.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15253,14 +15253,14 @@
       <c r="N253" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
+            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
           </r>
         </is>
       </c>
       <c r="O253" s="13" t="inlineStr"/>
       <c r="P253" s="13" t="inlineStr"/>
       <c r="Q253" s="14" t="n">
-        <v>4300000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="R253" s="14" t="inlineStr"/>
       <c r="S253" s="14" t="n">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>4300000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15310,14 +15310,14 @@
       <c r="N254" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
+            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
           </r>
         </is>
       </c>
       <c r="O254" s="13" t="inlineStr"/>
       <c r="P254" s="13" t="inlineStr"/>
       <c r="Q254" s="14" t="n">
-        <v>5700000.0</v>
+        <v>9500000.0</v>
       </c>
       <c r="R254" s="14" t="inlineStr"/>
       <c r="S254" s="14" t="n">
@@ -15330,20 +15330,20 @@
         <v>0.0</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>0.0</v>
+        <v>5413000.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>0.0</v>
+        <v>5413000.0</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.0</v>
+        <v>0.5697894736842105</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>5700000.0</v>
+        <v>4087000.0</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>
@@ -15367,14 +15367,14 @@
       <c r="N255" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
+            <t xml:space="preserve">000310. Pemeliharaan Gedung Lab Basah Depok</t>
           </r>
         </is>
       </c>
       <c r="O255" s="13" t="inlineStr"/>
       <c r="P255" s="13" t="inlineStr"/>
       <c r="Q255" s="14" t="n">
-        <v>9500000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="R255" s="14" t="inlineStr"/>
       <c r="S255" s="14" t="n">
@@ -15387,20 +15387,20 @@
         <v>0.0</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>5413000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>5413000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.5697894736842105</v>
+        <v>0.0</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>4087000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15437,7 +15437,7 @@
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>3.325E8</v>
+        <v>3.24415E8</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15450,20 +15450,20 @@
         <v>2.06124881E8</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>1.2086592E7</v>
+        <v>6.602411E7</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>2.18211473E8</v>
+        <v>2.72148991E8</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.6562751067669172</v>
+        <v>0.8388915154971256</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>1.14288527E8</v>
+        <v>5.2266009E7</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15621,20 +15621,20 @@
         <v>2.8040718E7</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>1804500.0</v>
+        <v>1.460255E7</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>2.9845218E7</v>
+        <v>4.2643268E7</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.6632270666666666</v>
+        <v>0.9476281777777777</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>1.5154782E7</v>
+        <v>2356732.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15665,7 +15665,7 @@
       <c r="O260" s="13" t="inlineStr"/>
       <c r="P260" s="13" t="inlineStr"/>
       <c r="Q260" s="14" t="n">
-        <v>1.6975E8</v>
+        <v>1.74265E8</v>
       </c>
       <c r="R260" s="14" t="inlineStr"/>
       <c r="S260" s="14" t="n">
@@ -15678,20 +15678,20 @@
         <v>1.20838496E8</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>2695000.0</v>
+        <v>4.1811668E7</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>1.23533496E8</v>
+        <v>1.62650164E8</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.7277378262150221</v>
+        <v>0.9333495767939632</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>4.6216504E7</v>
+        <v>1.1614836E7</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15779,7 +15779,7 @@
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>2.1E7</v>
+        <v>1.5E7</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15801,11 +15801,11 @@
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.680502619047619</v>
+        <v>0.9527036666666666</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>6709445.0</v>
+        <v>709445.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15893,7 +15893,7 @@
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>4050000.0</v>
+        <v>3050000.0</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15915,11 +15915,11 @@
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.4884953086419753</v>
+        <v>0.6486577049180328</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>2071594.0</v>
+        <v>1071594.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15963,20 +15963,20 @@
         <v>8319256.0</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>131028.0</v>
+        <v>619028.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>8450284.0</v>
+        <v>8938284.0</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.7041903333333334</v>
+        <v>0.744857</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>3549716.0</v>
+        <v>3061716.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -16007,7 +16007,7 @@
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>1500000.0</v>
+        <v>2000000.0</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16029,11 +16029,11 @@
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.778372</v>
+        <v>0.583779</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>332442.0</v>
+        <v>832442.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16077,20 +16077,20 @@
         <v>3760846.0</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>1560138.0</v>
+        <v>2513528.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>5320984.0</v>
+        <v>6274374.0</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>0.3406519846350832</v>
+        <v>0.40168847631242</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>1.0299016E7</v>
+        <v>9345626.0</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16178,7 +16178,7 @@
       <c r="O269" s="13" t="inlineStr"/>
       <c r="P269" s="13" t="inlineStr"/>
       <c r="Q269" s="14" t="n">
-        <v>1.3E7</v>
+        <v>9400000.0</v>
       </c>
       <c r="R269" s="14" t="inlineStr"/>
       <c r="S269" s="14" t="n">
@@ -16191,20 +16191,20 @@
         <v>7889000.0</v>
       </c>
       <c r="X269" s="14" t="n">
-        <v>0.0</v>
+        <v>581410.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>7889000.0</v>
+        <v>8470410.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.6068461538461538</v>
+        <v>0.9011074468085106</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>5111000.0</v>
+        <v>929590.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16228,14 +16228,14 @@
       <c r="N270" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
+            <t xml:space="preserve">000305. Pemeliharaan TV</t>
           </r>
         </is>
       </c>
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>2500000.0</v>
+        <v>1500000.0</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16248,20 +16248,20 @@
         <v>0.0</v>
       </c>
       <c r="X270" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>2500000.0</v>
+        <v>750000.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16285,14 +16285,14 @@
       <c r="N271" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000305. Pemeliharaan TV</t>
+            <t xml:space="preserve">000307. Pemeliharaan Meubelair</t>
           </r>
         </is>
       </c>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>1500000.0</v>
+        <v>4000000.0</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16305,20 +16305,20 @@
         <v>0.0</v>
       </c>
       <c r="X271" s="14" t="n">
-        <v>750000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>750000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>750000.0</v>
+        <v>4000000.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16342,14 +16342,14 @@
       <c r="N272" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000307. Pemeliharaan Meubelair</t>
+            <t xml:space="preserve">000308. Pemeliharaan Genset Portable</t>
           </r>
         </is>
       </c>
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>5000000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>5000000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16412,7 +16412,7 @@
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>1.5292E8</v>
+        <v>1.5136E8</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16425,20 +16425,20 @@
         <v>6.1416E7</v>
       </c>
       <c r="X273" s="14" t="n">
-        <v>1.9135E7</v>
+        <v>8.911E7</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>8.0551E7</v>
+        <v>1.50526E8</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.5267525503531258</v>
+        <v>0.9944899577167019</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>7.2369E7</v>
+        <v>834000.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16469,7 +16469,7 @@
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>6.216E7</v>
+        <v>6.06E7</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16482,20 +16482,20 @@
         <v>3.909E7</v>
       </c>
       <c r="X274" s="14" t="n">
-        <v>0.0</v>
+        <v>2.1185E7</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>3.909E7</v>
+        <v>6.0275E7</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.6288610038610039</v>
+        <v>0.9946369636963697</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>2.307E7</v>
+        <v>325000.0</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16640,20 +16640,20 @@
         <v>1.0776E7</v>
       </c>
       <c r="X277" s="14" t="n">
-        <v>0.0</v>
+        <v>4.879E7</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>5.9566E7</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.17942057942057943</v>
+        <v>0.9917748917748918</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>4.9284E7</v>
+        <v>494000.0</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
@@ -16690,7 +16690,7 @@
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>1.5218E8</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16712,11 +16712,11 @@
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="15" t="n">
-        <v>0.9927371765773945</v>
+        <v>0.8622683664082008</v>
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>960000.0</v>
+        <v>2.096E7</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
@@ -17215,7 +17215,7 @@
       <c r="O287" s="13" t="inlineStr"/>
       <c r="P287" s="13" t="inlineStr"/>
       <c r="Q287" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2.75E7</v>
       </c>
       <c r="R287" s="14" t="inlineStr"/>
       <c r="S287" s="14" t="n">
@@ -17237,11 +17237,11 @@
       <c r="AA287" s="14" t="inlineStr"/>
       <c r="AB287" s="14" t="inlineStr"/>
       <c r="AC287" s="15" t="n">
-        <v>1.0</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AD287" s="15" t="inlineStr"/>
       <c r="AE287" s="14" t="n">
-        <v>0.0</v>
+        <v>2.0E7</v>
       </c>
       <c r="AF287" s="14" t="inlineStr"/>
       <c r="AG287" s="14" t="inlineStr"/>
@@ -17308,254 +17308,248 @@
     <row r="289" customHeight="1" ht="15">
       <c r="A289" s="2" t="inlineStr"/>
       <c r="B289" s="2" t="inlineStr"/>
-      <c r="C289" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D289" s="16" t="inlineStr"/>
-      <c r="E289" s="16" t="inlineStr"/>
-      <c r="F289" s="16" t="inlineStr"/>
-      <c r="G289" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H289" s="16" t="inlineStr"/>
-      <c r="I289" s="16" t="inlineStr"/>
-      <c r="J289" s="16" t="inlineStr"/>
-      <c r="K289" s="16" t="inlineStr"/>
-      <c r="L289" s="16" t="inlineStr"/>
-      <c r="M289" s="16" t="inlineStr"/>
-      <c r="N289" s="16" t="inlineStr"/>
-      <c r="O289" s="16" t="inlineStr"/>
-      <c r="P289" s="16" t="inlineStr"/>
-      <c r="Q289" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R289" s="17" t="inlineStr"/>
-      <c r="S289" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T289" s="17" t="inlineStr"/>
-      <c r="U289" s="17" t="inlineStr"/>
-      <c r="V289" s="17" t="inlineStr"/>
-      <c r="W289" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X289" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y289" s="17" t="inlineStr"/>
-      <c r="Z289" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA289" s="17" t="inlineStr"/>
-      <c r="AB289" s="17" t="inlineStr"/>
-      <c r="AC289" s="18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD289" s="18" t="inlineStr"/>
-      <c r="AE289" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF289" s="17" t="inlineStr"/>
-      <c r="AG289" s="17" t="inlineStr"/>
-      <c r="AH289" s="17" t="inlineStr"/>
-      <c r="AI289" s="17" t="inlineStr"/>
+      <c r="C289" s="2" t="inlineStr"/>
+      <c r="D289" s="2" t="inlineStr"/>
+      <c r="E289" s="2" t="inlineStr"/>
+      <c r="F289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr"/>
+      <c r="I289" s="2" t="inlineStr"/>
+      <c r="J289" s="2" t="inlineStr"/>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr"/>
+      <c r="M289" s="2" t="inlineStr"/>
+      <c r="N289" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000309. Pakaian Lapangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="O289" s="13" t="inlineStr"/>
+      <c r="P289" s="13" t="inlineStr"/>
+      <c r="Q289" s="14" t="n">
+        <v>2.0E7</v>
+      </c>
+      <c r="R289" s="14" t="inlineStr"/>
+      <c r="S289" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T289" s="14" t="inlineStr"/>
+      <c r="U289" s="14" t="inlineStr"/>
+      <c r="V289" s="14" t="inlineStr"/>
+      <c r="W289" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X289" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y289" s="14" t="inlineStr"/>
+      <c r="Z289" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA289" s="14" t="inlineStr"/>
+      <c r="AB289" s="14" t="inlineStr"/>
+      <c r="AC289" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD289" s="15" t="inlineStr"/>
+      <c r="AE289" s="14" t="n">
+        <v>2.0E7</v>
+      </c>
+      <c r="AF289" s="14" t="inlineStr"/>
+      <c r="AG289" s="14" t="inlineStr"/>
+      <c r="AH289" s="14" t="inlineStr"/>
+      <c r="AI289" s="14" t="inlineStr"/>
     </row>
     <row r="290" customHeight="1" ht="15">
       <c r="A290" s="2" t="inlineStr"/>
       <c r="B290" s="2" t="inlineStr"/>
-      <c r="C290" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D290" s="28" t="inlineStr"/>
-      <c r="E290" s="28" t="inlineStr"/>
-      <c r="F290" s="28" t="inlineStr"/>
-      <c r="G290" s="28" t="inlineStr"/>
-      <c r="H290" s="28" t="inlineStr"/>
-      <c r="I290" s="28" t="inlineStr"/>
-      <c r="J290" s="28" t="inlineStr"/>
-      <c r="K290" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L290" s="20" t="inlineStr"/>
-      <c r="M290" s="20" t="inlineStr"/>
-      <c r="N290" s="20" t="inlineStr"/>
-      <c r="O290" s="20" t="inlineStr"/>
-      <c r="P290" s="20" t="inlineStr"/>
-      <c r="Q290" s="21" t="n">
+      <c r="C290" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D290" s="16" t="inlineStr"/>
+      <c r="E290" s="16" t="inlineStr"/>
+      <c r="F290" s="16" t="inlineStr"/>
+      <c r="G290" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H290" s="16" t="inlineStr"/>
+      <c r="I290" s="16" t="inlineStr"/>
+      <c r="J290" s="16" t="inlineStr"/>
+      <c r="K290" s="16" t="inlineStr"/>
+      <c r="L290" s="16" t="inlineStr"/>
+      <c r="M290" s="16" t="inlineStr"/>
+      <c r="N290" s="16" t="inlineStr"/>
+      <c r="O290" s="16" t="inlineStr"/>
+      <c r="P290" s="16" t="inlineStr"/>
+      <c r="Q290" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R290" s="21" t="inlineStr"/>
-      <c r="S290" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T290" s="21" t="inlineStr"/>
-      <c r="U290" s="21" t="inlineStr"/>
-      <c r="V290" s="21" t="inlineStr"/>
-      <c r="W290" s="22" t="n">
+      <c r="R290" s="17" t="inlineStr"/>
+      <c r="S290" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T290" s="17" t="inlineStr"/>
+      <c r="U290" s="17" t="inlineStr"/>
+      <c r="V290" s="17" t="inlineStr"/>
+      <c r="W290" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X290" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y290" s="22" t="inlineStr"/>
-      <c r="Z290" s="21" t="n">
+      <c r="X290" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y290" s="17" t="inlineStr"/>
+      <c r="Z290" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA290" s="21" t="inlineStr"/>
-      <c r="AB290" s="21" t="inlineStr"/>
-      <c r="AC290" s="23" t="n">
+      <c r="AA290" s="17" t="inlineStr"/>
+      <c r="AB290" s="17" t="inlineStr"/>
+      <c r="AC290" s="18" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD290" s="23" t="inlineStr"/>
-      <c r="AE290" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF290" s="21" t="inlineStr"/>
-      <c r="AG290" s="21" t="inlineStr"/>
-      <c r="AH290" s="21" t="inlineStr"/>
-      <c r="AI290" s="21" t="inlineStr"/>
+      <c r="AD290" s="18" t="inlineStr"/>
+      <c r="AE290" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF290" s="17" t="inlineStr"/>
+      <c r="AG290" s="17" t="inlineStr"/>
+      <c r="AH290" s="17" t="inlineStr"/>
+      <c r="AI290" s="17" t="inlineStr"/>
     </row>
     <row r="291" customHeight="1" ht="15">
       <c r="A291" s="2" t="inlineStr"/>
       <c r="B291" s="2" t="inlineStr"/>
-      <c r="C291" s="2" t="inlineStr"/>
-      <c r="D291" s="2" t="inlineStr"/>
-      <c r="E291" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F291" s="24" t="inlineStr"/>
-      <c r="G291" s="24" t="inlineStr"/>
-      <c r="H291" s="24" t="inlineStr"/>
-      <c r="I291" s="24" t="inlineStr"/>
-      <c r="J291" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K291" s="24" t="inlineStr"/>
-      <c r="L291" s="24" t="inlineStr"/>
-      <c r="M291" s="24" t="inlineStr"/>
-      <c r="N291" s="24" t="inlineStr"/>
-      <c r="O291" s="24" t="inlineStr"/>
-      <c r="P291" s="24" t="inlineStr"/>
-      <c r="Q291" s="25" t="n">
+      <c r="C291" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D291" s="28" t="inlineStr"/>
+      <c r="E291" s="28" t="inlineStr"/>
+      <c r="F291" s="28" t="inlineStr"/>
+      <c r="G291" s="28" t="inlineStr"/>
+      <c r="H291" s="28" t="inlineStr"/>
+      <c r="I291" s="28" t="inlineStr"/>
+      <c r="J291" s="28" t="inlineStr"/>
+      <c r="K291" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L291" s="20" t="inlineStr"/>
+      <c r="M291" s="20" t="inlineStr"/>
+      <c r="N291" s="20" t="inlineStr"/>
+      <c r="O291" s="20" t="inlineStr"/>
+      <c r="P291" s="20" t="inlineStr"/>
+      <c r="Q291" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R291" s="25" t="inlineStr"/>
-      <c r="S291" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T291" s="25" t="inlineStr"/>
-      <c r="U291" s="25" t="inlineStr"/>
-      <c r="V291" s="25" t="inlineStr"/>
-      <c r="W291" s="25" t="n">
+      <c r="R291" s="21" t="inlineStr"/>
+      <c r="S291" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T291" s="21" t="inlineStr"/>
+      <c r="U291" s="21" t="inlineStr"/>
+      <c r="V291" s="21" t="inlineStr"/>
+      <c r="W291" s="22" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X291" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y291" s="25" t="inlineStr"/>
-      <c r="Z291" s="25" t="n">
+      <c r="X291" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y291" s="22" t="inlineStr"/>
+      <c r="Z291" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA291" s="25" t="inlineStr"/>
-      <c r="AB291" s="25" t="inlineStr"/>
-      <c r="AC291" s="26" t="n">
+      <c r="AA291" s="21" t="inlineStr"/>
+      <c r="AB291" s="21" t="inlineStr"/>
+      <c r="AC291" s="23" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD291" s="26" t="inlineStr"/>
-      <c r="AE291" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF291" s="25" t="inlineStr"/>
-      <c r="AG291" s="25" t="inlineStr"/>
-      <c r="AH291" s="25" t="inlineStr"/>
-      <c r="AI291" s="25" t="inlineStr"/>
+      <c r="AD291" s="23" t="inlineStr"/>
+      <c r="AE291" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF291" s="21" t="inlineStr"/>
+      <c r="AG291" s="21" t="inlineStr"/>
+      <c r="AH291" s="21" t="inlineStr"/>
+      <c r="AI291" s="21" t="inlineStr"/>
     </row>
     <row r="292" customHeight="1" ht="15">
       <c r="A292" s="2" t="inlineStr"/>
       <c r="B292" s="2" t="inlineStr"/>
       <c r="C292" s="2" t="inlineStr"/>
       <c r="D292" s="2" t="inlineStr"/>
-      <c r="E292" s="2" t="inlineStr"/>
-      <c r="F292" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G292" s="13" t="inlineStr"/>
-      <c r="H292" s="13" t="inlineStr"/>
-      <c r="I292" s="13" t="inlineStr"/>
-      <c r="J292" s="13" t="inlineStr"/>
-      <c r="K292" s="13" t="inlineStr"/>
-      <c r="L292" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M292" s="13" t="inlineStr"/>
-      <c r="N292" s="13" t="inlineStr"/>
-      <c r="O292" s="13" t="inlineStr"/>
-      <c r="P292" s="13" t="inlineStr"/>
-      <c r="Q292" s="14" t="n">
+      <c r="E292" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F292" s="24" t="inlineStr"/>
+      <c r="G292" s="24" t="inlineStr"/>
+      <c r="H292" s="24" t="inlineStr"/>
+      <c r="I292" s="24" t="inlineStr"/>
+      <c r="J292" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K292" s="24" t="inlineStr"/>
+      <c r="L292" s="24" t="inlineStr"/>
+      <c r="M292" s="24" t="inlineStr"/>
+      <c r="N292" s="24" t="inlineStr"/>
+      <c r="O292" s="24" t="inlineStr"/>
+      <c r="P292" s="24" t="inlineStr"/>
+      <c r="Q292" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R292" s="14" t="inlineStr"/>
-      <c r="S292" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T292" s="14" t="inlineStr"/>
-      <c r="U292" s="14" t="inlineStr"/>
-      <c r="V292" s="14" t="inlineStr"/>
-      <c r="W292" s="14" t="n">
+      <c r="R292" s="25" t="inlineStr"/>
+      <c r="S292" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T292" s="25" t="inlineStr"/>
+      <c r="U292" s="25" t="inlineStr"/>
+      <c r="V292" s="25" t="inlineStr"/>
+      <c r="W292" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X292" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y292" s="14" t="inlineStr"/>
-      <c r="Z292" s="14" t="n">
+      <c r="X292" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y292" s="25" t="inlineStr"/>
+      <c r="Z292" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA292" s="14" t="inlineStr"/>
-      <c r="AB292" s="14" t="inlineStr"/>
-      <c r="AC292" s="15" t="n">
+      <c r="AA292" s="25" t="inlineStr"/>
+      <c r="AB292" s="25" t="inlineStr"/>
+      <c r="AC292" s="26" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD292" s="15" t="inlineStr"/>
-      <c r="AE292" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF292" s="14" t="inlineStr"/>
-      <c r="AG292" s="14" t="inlineStr"/>
-      <c r="AH292" s="14" t="inlineStr"/>
-      <c r="AI292" s="14" t="inlineStr"/>
+      <c r="AD292" s="26" t="inlineStr"/>
+      <c r="AE292" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF292" s="25" t="inlineStr"/>
+      <c r="AG292" s="25" t="inlineStr"/>
+      <c r="AH292" s="25" t="inlineStr"/>
+      <c r="AI292" s="25" t="inlineStr"/>
     </row>
     <row r="293" customHeight="1" ht="15">
       <c r="A293" s="2" t="inlineStr"/>
@@ -17563,26 +17557,26 @@
       <c r="C293" s="2" t="inlineStr"/>
       <c r="D293" s="2" t="inlineStr"/>
       <c r="E293" s="2" t="inlineStr"/>
-      <c r="F293" s="2" t="inlineStr"/>
-      <c r="G293" s="2" t="inlineStr"/>
-      <c r="H293" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">524111</t>
-          </r>
-        </is>
-      </c>
+      <c r="F293" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G293" s="13" t="inlineStr"/>
+      <c r="H293" s="13" t="inlineStr"/>
       <c r="I293" s="13" t="inlineStr"/>
       <c r="J293" s="13" t="inlineStr"/>
       <c r="K293" s="13" t="inlineStr"/>
-      <c r="L293" s="13" t="inlineStr"/>
-      <c r="M293" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
-          </r>
-        </is>
-      </c>
+      <c r="L293" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M293" s="13" t="inlineStr"/>
       <c r="N293" s="13" t="inlineStr"/>
       <c r="O293" s="13" t="inlineStr"/>
       <c r="P293" s="13" t="inlineStr"/>
@@ -17628,19 +17622,25 @@
       <c r="E294" s="2" t="inlineStr"/>
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr"/>
-      <c r="H294" s="2" t="inlineStr"/>
-      <c r="I294" s="2" t="inlineStr"/>
-      <c r="J294" s="2" t="inlineStr"/>
-      <c r="K294" s="2" t="inlineStr"/>
-      <c r="L294" s="2" t="inlineStr"/>
-      <c r="M294" s="2" t="inlineStr"/>
-      <c r="N294" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000231. Uang Harian</t>
-          </r>
-        </is>
-      </c>
+      <c r="H294" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I294" s="13" t="inlineStr"/>
+      <c r="J294" s="13" t="inlineStr"/>
+      <c r="K294" s="13" t="inlineStr"/>
+      <c r="L294" s="13" t="inlineStr"/>
+      <c r="M294" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N294" s="13" t="inlineStr"/>
       <c r="O294" s="13" t="inlineStr"/>
       <c r="P294" s="13" t="inlineStr"/>
       <c r="Q294" s="14" t="n">
@@ -17677,9 +17677,66 @@
       <c r="AH294" s="14" t="inlineStr"/>
       <c r="AI294" s="14" t="inlineStr"/>
     </row>
-    <row r="295" customHeight="1" ht="24">
+    <row r="295" customHeight="1" ht="15">
       <c r="A295" s="2" t="inlineStr"/>
-      <c r="B295" s="27" t="inlineStr">
+      <c r="B295" s="2" t="inlineStr"/>
+      <c r="C295" s="2" t="inlineStr"/>
+      <c r="D295" s="2" t="inlineStr"/>
+      <c r="E295" s="2" t="inlineStr"/>
+      <c r="F295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr"/>
+      <c r="H295" s="2" t="inlineStr"/>
+      <c r="I295" s="2" t="inlineStr"/>
+      <c r="J295" s="2" t="inlineStr"/>
+      <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr"/>
+      <c r="M295" s="2" t="inlineStr"/>
+      <c r="N295" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000231. Uang Harian</t>
+          </r>
+        </is>
+      </c>
+      <c r="O295" s="13" t="inlineStr"/>
+      <c r="P295" s="13" t="inlineStr"/>
+      <c r="Q295" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R295" s="14" t="inlineStr"/>
+      <c r="S295" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T295" s="14" t="inlineStr"/>
+      <c r="U295" s="14" t="inlineStr"/>
+      <c r="V295" s="14" t="inlineStr"/>
+      <c r="W295" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X295" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y295" s="14" t="inlineStr"/>
+      <c r="Z295" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA295" s="14" t="inlineStr"/>
+      <c r="AB295" s="14" t="inlineStr"/>
+      <c r="AC295" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD295" s="15" t="inlineStr"/>
+      <c r="AE295" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF295" s="14" t="inlineStr"/>
+      <c r="AG295" s="14" t="inlineStr"/>
+      <c r="AH295" s="14" t="inlineStr"/>
+      <c r="AI295" s="14" t="inlineStr"/>
+    </row>
+    <row r="296" customHeight="1" ht="24">
+      <c r="A296" s="2" t="inlineStr"/>
+      <c r="B296" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.
@@ -17687,39 +17744,39 @@
           </r>
         </is>
       </c>
-      <c r="C295" s="27" t="inlineStr"/>
-      <c r="D295" s="27" t="inlineStr"/>
-      <c r="E295" s="27" t="inlineStr"/>
-      <c r="F295" s="27" t="inlineStr"/>
-      <c r="G295" s="27" t="inlineStr"/>
-      <c r="H295" s="27" t="inlineStr"/>
-      <c r="I295" s="27" t="inlineStr"/>
-      <c r="J295" s="27" t="inlineStr"/>
-      <c r="K295" s="27" t="inlineStr"/>
-      <c r="L295" s="27" t="inlineStr"/>
-      <c r="M295" s="27" t="inlineStr"/>
-      <c r="N295" s="27" t="inlineStr"/>
-      <c r="O295" s="27" t="inlineStr"/>
-      <c r="P295" s="27" t="inlineStr"/>
-      <c r="Q295" s="27" t="inlineStr"/>
-      <c r="R295" s="27" t="inlineStr"/>
-      <c r="S295" s="27" t="inlineStr"/>
-      <c r="T295" s="27" t="inlineStr"/>
-      <c r="U295" s="27" t="inlineStr"/>
-      <c r="V295" s="27" t="inlineStr"/>
-      <c r="W295" s="27" t="inlineStr"/>
-      <c r="X295" s="27" t="inlineStr"/>
-      <c r="Y295" s="27" t="inlineStr"/>
-      <c r="Z295" s="27" t="inlineStr"/>
-      <c r="AA295" s="27" t="inlineStr"/>
-      <c r="AB295" s="27" t="inlineStr"/>
-      <c r="AC295" s="27" t="inlineStr"/>
-      <c r="AD295" s="27" t="inlineStr"/>
-      <c r="AE295" s="27" t="inlineStr"/>
-      <c r="AF295" s="27" t="inlineStr"/>
-      <c r="AG295" s="2" t="inlineStr"/>
-      <c r="AH295" s="2" t="inlineStr"/>
-      <c r="AI295" s="2" t="inlineStr"/>
+      <c r="C296" s="27" t="inlineStr"/>
+      <c r="D296" s="27" t="inlineStr"/>
+      <c r="E296" s="27" t="inlineStr"/>
+      <c r="F296" s="27" t="inlineStr"/>
+      <c r="G296" s="27" t="inlineStr"/>
+      <c r="H296" s="27" t="inlineStr"/>
+      <c r="I296" s="27" t="inlineStr"/>
+      <c r="J296" s="27" t="inlineStr"/>
+      <c r="K296" s="27" t="inlineStr"/>
+      <c r="L296" s="27" t="inlineStr"/>
+      <c r="M296" s="27" t="inlineStr"/>
+      <c r="N296" s="27" t="inlineStr"/>
+      <c r="O296" s="27" t="inlineStr"/>
+      <c r="P296" s="27" t="inlineStr"/>
+      <c r="Q296" s="27" t="inlineStr"/>
+      <c r="R296" s="27" t="inlineStr"/>
+      <c r="S296" s="27" t="inlineStr"/>
+      <c r="T296" s="27" t="inlineStr"/>
+      <c r="U296" s="27" t="inlineStr"/>
+      <c r="V296" s="27" t="inlineStr"/>
+      <c r="W296" s="27" t="inlineStr"/>
+      <c r="X296" s="27" t="inlineStr"/>
+      <c r="Y296" s="27" t="inlineStr"/>
+      <c r="Z296" s="27" t="inlineStr"/>
+      <c r="AA296" s="27" t="inlineStr"/>
+      <c r="AB296" s="27" t="inlineStr"/>
+      <c r="AC296" s="27" t="inlineStr"/>
+      <c r="AD296" s="27" t="inlineStr"/>
+      <c r="AE296" s="27" t="inlineStr"/>
+      <c r="AF296" s="27" t="inlineStr"/>
+      <c r="AG296" s="2" t="inlineStr"/>
+      <c r="AH296" s="2" t="inlineStr"/>
+      <c r="AI296" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -19123,15 +19180,15 @@
     <mergeCell ref="Z202:AB202"/>
     <mergeCell ref="AC202:AD202"/>
     <mergeCell ref="AE202:AI202"/>
-    <mergeCell ref="N203:P203"/>
+    <mergeCell ref="H203:L203"/>
+    <mergeCell ref="M203:P203"/>
     <mergeCell ref="Q203:R203"/>
     <mergeCell ref="S203:V203"/>
     <mergeCell ref="X203:Y203"/>
     <mergeCell ref="Z203:AB203"/>
     <mergeCell ref="AC203:AD203"/>
     <mergeCell ref="AE203:AI203"/>
-    <mergeCell ref="H204:L204"/>
-    <mergeCell ref="M204:P204"/>
+    <mergeCell ref="N204:P204"/>
     <mergeCell ref="Q204:R204"/>
     <mergeCell ref="S204:V204"/>
     <mergeCell ref="X204:Y204"/>
@@ -19145,15 +19202,15 @@
     <mergeCell ref="Z205:AB205"/>
     <mergeCell ref="AC205:AD205"/>
     <mergeCell ref="AE205:AI205"/>
-    <mergeCell ref="N206:P206"/>
+    <mergeCell ref="H206:L206"/>
+    <mergeCell ref="M206:P206"/>
     <mergeCell ref="Q206:R206"/>
     <mergeCell ref="S206:V206"/>
     <mergeCell ref="X206:Y206"/>
     <mergeCell ref="Z206:AB206"/>
     <mergeCell ref="AC206:AD206"/>
     <mergeCell ref="AE206:AI206"/>
-    <mergeCell ref="H207:L207"/>
-    <mergeCell ref="M207:P207"/>
+    <mergeCell ref="N207:P207"/>
     <mergeCell ref="Q207:R207"/>
     <mergeCell ref="S207:V207"/>
     <mergeCell ref="X207:Y207"/>
@@ -19167,15 +19224,15 @@
     <mergeCell ref="Z208:AB208"/>
     <mergeCell ref="AC208:AD208"/>
     <mergeCell ref="AE208:AI208"/>
-    <mergeCell ref="N209:P209"/>
+    <mergeCell ref="H209:L209"/>
+    <mergeCell ref="M209:P209"/>
     <mergeCell ref="Q209:R209"/>
     <mergeCell ref="S209:V209"/>
     <mergeCell ref="X209:Y209"/>
     <mergeCell ref="Z209:AB209"/>
     <mergeCell ref="AC209:AD209"/>
     <mergeCell ref="AE209:AI209"/>
-    <mergeCell ref="H210:L210"/>
-    <mergeCell ref="M210:P210"/>
+    <mergeCell ref="N210:P210"/>
     <mergeCell ref="Q210:R210"/>
     <mergeCell ref="S210:V210"/>
     <mergeCell ref="X210:Y210"/>
@@ -19189,15 +19246,15 @@
     <mergeCell ref="Z211:AB211"/>
     <mergeCell ref="AC211:AD211"/>
     <mergeCell ref="AE211:AI211"/>
-    <mergeCell ref="N212:P212"/>
+    <mergeCell ref="H212:L212"/>
+    <mergeCell ref="M212:P212"/>
     <mergeCell ref="Q212:R212"/>
     <mergeCell ref="S212:V212"/>
     <mergeCell ref="X212:Y212"/>
     <mergeCell ref="Z212:AB212"/>
     <mergeCell ref="AC212:AD212"/>
     <mergeCell ref="AE212:AI212"/>
-    <mergeCell ref="H213:L213"/>
-    <mergeCell ref="M213:P213"/>
+    <mergeCell ref="N213:P213"/>
     <mergeCell ref="Q213:R213"/>
     <mergeCell ref="S213:V213"/>
     <mergeCell ref="X213:Y213"/>
@@ -19246,7 +19303,8 @@
     <mergeCell ref="Z219:AB219"/>
     <mergeCell ref="AC219:AD219"/>
     <mergeCell ref="AE219:AI219"/>
-    <mergeCell ref="N220:P220"/>
+    <mergeCell ref="F220:K220"/>
+    <mergeCell ref="L220:P220"/>
     <mergeCell ref="Q220:R220"/>
     <mergeCell ref="S220:V220"/>
     <mergeCell ref="X220:Y220"/>
@@ -19254,61 +19312,60 @@
     <mergeCell ref="AC220:AD220"/>
     <mergeCell ref="AE220:AI220"/>
     <mergeCell ref="B221:AF221"/>
-    <mergeCell ref="F222:K222"/>
-    <mergeCell ref="L222:P222"/>
+    <mergeCell ref="H222:L222"/>
+    <mergeCell ref="M222:P222"/>
     <mergeCell ref="Q222:R222"/>
     <mergeCell ref="S222:V222"/>
     <mergeCell ref="X222:Y222"/>
     <mergeCell ref="Z222:AB222"/>
     <mergeCell ref="AC222:AD222"/>
     <mergeCell ref="AE222:AI222"/>
-    <mergeCell ref="H223:L223"/>
-    <mergeCell ref="M223:P223"/>
+    <mergeCell ref="N223:P223"/>
     <mergeCell ref="Q223:R223"/>
     <mergeCell ref="S223:V223"/>
     <mergeCell ref="X223:Y223"/>
     <mergeCell ref="Z223:AB223"/>
     <mergeCell ref="AC223:AD223"/>
     <mergeCell ref="AE223:AI223"/>
-    <mergeCell ref="N224:P224"/>
+    <mergeCell ref="H224:L224"/>
+    <mergeCell ref="M224:P224"/>
     <mergeCell ref="Q224:R224"/>
     <mergeCell ref="S224:V224"/>
     <mergeCell ref="X224:Y224"/>
     <mergeCell ref="Z224:AB224"/>
     <mergeCell ref="AC224:AD224"/>
     <mergeCell ref="AE224:AI224"/>
-    <mergeCell ref="H225:L225"/>
-    <mergeCell ref="M225:P225"/>
+    <mergeCell ref="N225:P225"/>
     <mergeCell ref="Q225:R225"/>
     <mergeCell ref="S225:V225"/>
     <mergeCell ref="X225:Y225"/>
     <mergeCell ref="Z225:AB225"/>
     <mergeCell ref="AC225:AD225"/>
     <mergeCell ref="AE225:AI225"/>
-    <mergeCell ref="N226:P226"/>
+    <mergeCell ref="H226:L226"/>
+    <mergeCell ref="M226:P226"/>
     <mergeCell ref="Q226:R226"/>
     <mergeCell ref="S226:V226"/>
     <mergeCell ref="X226:Y226"/>
     <mergeCell ref="Z226:AB226"/>
     <mergeCell ref="AC226:AD226"/>
     <mergeCell ref="AE226:AI226"/>
-    <mergeCell ref="H227:L227"/>
-    <mergeCell ref="M227:P227"/>
+    <mergeCell ref="N227:P227"/>
     <mergeCell ref="Q227:R227"/>
     <mergeCell ref="S227:V227"/>
     <mergeCell ref="X227:Y227"/>
     <mergeCell ref="Z227:AB227"/>
     <mergeCell ref="AC227:AD227"/>
     <mergeCell ref="AE227:AI227"/>
-    <mergeCell ref="N228:P228"/>
+    <mergeCell ref="H228:L228"/>
+    <mergeCell ref="M228:P228"/>
     <mergeCell ref="Q228:R228"/>
     <mergeCell ref="S228:V228"/>
     <mergeCell ref="X228:Y228"/>
     <mergeCell ref="Z228:AB228"/>
     <mergeCell ref="AC228:AD228"/>
     <mergeCell ref="AE228:AI228"/>
-    <mergeCell ref="H229:L229"/>
-    <mergeCell ref="M229:P229"/>
+    <mergeCell ref="N229:P229"/>
     <mergeCell ref="Q229:R229"/>
     <mergeCell ref="S229:V229"/>
     <mergeCell ref="X229:Y229"/>
@@ -19322,23 +19379,23 @@
     <mergeCell ref="Z230:AB230"/>
     <mergeCell ref="AC230:AD230"/>
     <mergeCell ref="AE230:AI230"/>
-    <mergeCell ref="N231:P231"/>
+    <mergeCell ref="F231:K231"/>
+    <mergeCell ref="L231:P231"/>
     <mergeCell ref="Q231:R231"/>
     <mergeCell ref="S231:V231"/>
     <mergeCell ref="X231:Y231"/>
     <mergeCell ref="Z231:AB231"/>
     <mergeCell ref="AC231:AD231"/>
     <mergeCell ref="AE231:AI231"/>
-    <mergeCell ref="F232:K232"/>
-    <mergeCell ref="L232:P232"/>
+    <mergeCell ref="H232:L232"/>
+    <mergeCell ref="M232:P232"/>
     <mergeCell ref="Q232:R232"/>
     <mergeCell ref="S232:V232"/>
     <mergeCell ref="X232:Y232"/>
     <mergeCell ref="Z232:AB232"/>
     <mergeCell ref="AC232:AD232"/>
     <mergeCell ref="AE232:AI232"/>
-    <mergeCell ref="H233:L233"/>
-    <mergeCell ref="M233:P233"/>
+    <mergeCell ref="N233:P233"/>
     <mergeCell ref="Q233:R233"/>
     <mergeCell ref="S233:V233"/>
     <mergeCell ref="X233:Y233"/>
@@ -19352,30 +19409,30 @@
     <mergeCell ref="Z234:AB234"/>
     <mergeCell ref="AC234:AD234"/>
     <mergeCell ref="AE234:AI234"/>
-    <mergeCell ref="N235:P235"/>
+    <mergeCell ref="H235:L235"/>
+    <mergeCell ref="M235:P235"/>
     <mergeCell ref="Q235:R235"/>
     <mergeCell ref="S235:V235"/>
     <mergeCell ref="X235:Y235"/>
     <mergeCell ref="Z235:AB235"/>
     <mergeCell ref="AC235:AD235"/>
     <mergeCell ref="AE235:AI235"/>
-    <mergeCell ref="H236:L236"/>
-    <mergeCell ref="M236:P236"/>
+    <mergeCell ref="N236:P236"/>
     <mergeCell ref="Q236:R236"/>
     <mergeCell ref="S236:V236"/>
     <mergeCell ref="X236:Y236"/>
     <mergeCell ref="Z236:AB236"/>
     <mergeCell ref="AC236:AD236"/>
     <mergeCell ref="AE236:AI236"/>
-    <mergeCell ref="N237:P237"/>
+    <mergeCell ref="H237:L237"/>
+    <mergeCell ref="M237:P237"/>
     <mergeCell ref="Q237:R237"/>
     <mergeCell ref="S237:V237"/>
     <mergeCell ref="X237:Y237"/>
     <mergeCell ref="Z237:AB237"/>
     <mergeCell ref="AC237:AD237"/>
     <mergeCell ref="AE237:AI237"/>
-    <mergeCell ref="H238:L238"/>
-    <mergeCell ref="M238:P238"/>
+    <mergeCell ref="N238:P238"/>
     <mergeCell ref="Q238:R238"/>
     <mergeCell ref="S238:V238"/>
     <mergeCell ref="X238:Y238"/>
@@ -19725,54 +19782,61 @@
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="C289:F289"/>
-    <mergeCell ref="G289:P289"/>
+    <mergeCell ref="N289:P289"/>
     <mergeCell ref="Q289:R289"/>
     <mergeCell ref="S289:V289"/>
     <mergeCell ref="X289:Y289"/>
     <mergeCell ref="Z289:AB289"/>
     <mergeCell ref="AC289:AD289"/>
     <mergeCell ref="AE289:AI289"/>
-    <mergeCell ref="C290:J290"/>
-    <mergeCell ref="K290:P290"/>
+    <mergeCell ref="C290:F290"/>
+    <mergeCell ref="G290:P290"/>
     <mergeCell ref="Q290:R290"/>
     <mergeCell ref="S290:V290"/>
     <mergeCell ref="X290:Y290"/>
     <mergeCell ref="Z290:AB290"/>
     <mergeCell ref="AC290:AD290"/>
     <mergeCell ref="AE290:AI290"/>
-    <mergeCell ref="E291:I291"/>
-    <mergeCell ref="J291:P291"/>
+    <mergeCell ref="C291:J291"/>
+    <mergeCell ref="K291:P291"/>
     <mergeCell ref="Q291:R291"/>
     <mergeCell ref="S291:V291"/>
     <mergeCell ref="X291:Y291"/>
     <mergeCell ref="Z291:AB291"/>
     <mergeCell ref="AC291:AD291"/>
     <mergeCell ref="AE291:AI291"/>
-    <mergeCell ref="F292:K292"/>
-    <mergeCell ref="L292:P292"/>
+    <mergeCell ref="E292:I292"/>
+    <mergeCell ref="J292:P292"/>
     <mergeCell ref="Q292:R292"/>
     <mergeCell ref="S292:V292"/>
     <mergeCell ref="X292:Y292"/>
     <mergeCell ref="Z292:AB292"/>
     <mergeCell ref="AC292:AD292"/>
     <mergeCell ref="AE292:AI292"/>
-    <mergeCell ref="H293:L293"/>
-    <mergeCell ref="M293:P293"/>
+    <mergeCell ref="F293:K293"/>
+    <mergeCell ref="L293:P293"/>
     <mergeCell ref="Q293:R293"/>
     <mergeCell ref="S293:V293"/>
     <mergeCell ref="X293:Y293"/>
     <mergeCell ref="Z293:AB293"/>
     <mergeCell ref="AC293:AD293"/>
     <mergeCell ref="AE293:AI293"/>
-    <mergeCell ref="N294:P294"/>
+    <mergeCell ref="H294:L294"/>
+    <mergeCell ref="M294:P294"/>
     <mergeCell ref="Q294:R294"/>
     <mergeCell ref="S294:V294"/>
     <mergeCell ref="X294:Y294"/>
     <mergeCell ref="Z294:AB294"/>
     <mergeCell ref="AC294:AD294"/>
     <mergeCell ref="AE294:AI294"/>
-    <mergeCell ref="B295:AF295"/>
+    <mergeCell ref="N295:P295"/>
+    <mergeCell ref="Q295:R295"/>
+    <mergeCell ref="S295:V295"/>
+    <mergeCell ref="X295:Y295"/>
+    <mergeCell ref="Z295:AB295"/>
+    <mergeCell ref="AC295:AD295"/>
+    <mergeCell ref="AE295:AI295"/>
+    <mergeCell ref="B296:AF296"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/SP2D.xlsx
+++ b/Database/SP2D.xlsx
@@ -982,19 +982,19 @@
         <v>8.6557047429E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>1.1909697651E10</v>
+        <v>1.2745295011E10</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.846674508E10</v>
+        <v>9.930234244E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9847064648701381</v>
+        <v>0.9930627695469294</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.52929292E9</v>
+        <v>6.9369556E8</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>1.1909697651E10</v>
+        <v>1.2745295011E10</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>9.443337704E10</v>
+        <v>9.52689744E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.98406399623987</v>
+        <v>0.9927715242676008</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.52926096E9</v>
+        <v>6.936636E8</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.2523679389E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>1.1909697651E10</v>
+        <v>1.2745295011E10</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>9.443337704E10</v>
+        <v>9.52689744E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.98406399623987</v>
+        <v>0.9927715242676008</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.52926096E9</v>
+        <v>6.936636E8</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.2523079389E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>1.1909697651E10</v>
+        <v>1.2745295011E10</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>9.443277704E10</v>
+        <v>9.52683744E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9840638966004452</v>
+        <v>0.9927714790717554</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.52926096E9</v>
+        <v>6.936636E8</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3234,20 +3234,20 @@
         <v>8.2505568337E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>1.1908897651E10</v>
+        <v>1.2744495011E10</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>9.4414465988E10</v>
+        <v>9.5250063348E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9840631008405488</v>
+        <v>0.9927723650463145</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.529042012E9</v>
+        <v>6.93444652E8</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3297,20 +3297,20 @@
         <v>7.6753022175E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>1.102235221E10</v>
+        <v>1.156137421E10</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.7775374385E10</v>
+        <v>8.8314396385E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9862764765507153</v>
+        <v>0.9923331265242205</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.221348615E9</v>
+        <v>6.82326615E8</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3360,20 +3360,20 @@
         <v>5.460273892E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>3.99287212E8</v>
+        <v>4.24318212E8</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>5.859561104E9</v>
+        <v>5.884592104E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.9897271972407177</v>
+        <v>0.9939551353122603</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>6.0818896E7</v>
+        <v>3.5787896E7</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -5339,20 +5339,20 @@
         <v>2.77741E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>2.8323E7</v>
+        <v>5.3354E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>3.06064E8</v>
+        <v>3.31095E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.9049900057954559</v>
+        <v>0.9790032998616187</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>3.2132E7</v>
+        <v>7101000.0</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5396,20 +5396,20 @@
         <v>1.554E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1400000.0</v>
+        <v>2870000.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>1.694E7</v>
+        <v>1.841E7</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9962121212121212</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>1540000.0</v>
+        <v>70000.0</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5453,20 +5453,20 @@
         <v>2.28253E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>2.3643E7</v>
+        <v>4.5769E7</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
-        <v>2.51896E8</v>
+        <v>2.74022E8</v>
       </c>
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.9048378522062732</v>
+        <v>0.9843168527379054</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>2.6492E7</v>
+        <v>4366000.0</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5510,20 +5510,20 @@
         <v>3.3948E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>3280000.0</v>
+        <v>4715000.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
-        <v>3.7228E7</v>
+        <v>3.8663E7</v>
       </c>
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.9007936507936508</v>
+        <v>0.935515873015873</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>4100000.0</v>
+        <v>2665000.0</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -6085,20 +6085,20 @@
         <v>4.5358707E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>4.51030727E8</v>
+        <v>4.79946727E8</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>9.04617797E8</v>
+        <v>9.33533797E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.9302087704848075</v>
+        <v>0.9599427829003722</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>6.7871203E7</v>
+        <v>3.8955203E7</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6748,20 +6748,20 @@
         <v>3.0833E7</v>
       </c>
       <c r="X106" s="14" t="n">
-        <v>2.694E7</v>
+        <v>5.5856E7</v>
       </c>
       <c r="Y106" s="14" t="inlineStr"/>
       <c r="Z106" s="14" t="n">
-        <v>5.7773E7</v>
+        <v>8.6689E7</v>
       </c>
       <c r="AA106" s="14" t="inlineStr"/>
       <c r="AB106" s="14" t="inlineStr"/>
       <c r="AC106" s="15" t="n">
-        <v>0.6554908835108978</v>
+        <v>0.9835710314623825</v>
       </c>
       <c r="AD106" s="15" t="inlineStr"/>
       <c r="AE106" s="14" t="n">
-        <v>3.0364E7</v>
+        <v>1448000.0</v>
       </c>
       <c r="AF106" s="14" t="inlineStr"/>
       <c r="AG106" s="14" t="inlineStr"/>
@@ -6805,20 +6805,20 @@
         <v>8855000.0</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>7700000.0</v>
+        <v>1.5785E7</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
-        <v>1.6555E7</v>
+        <v>2.464E7</v>
       </c>
       <c r="AA107" s="14" t="inlineStr"/>
       <c r="AB107" s="14" t="inlineStr"/>
       <c r="AC107" s="15" t="n">
-        <v>0.6569444444444444</v>
+        <v>0.9777777777777777</v>
       </c>
       <c r="AD107" s="15" t="inlineStr"/>
       <c r="AE107" s="14" t="n">
-        <v>8645000.0</v>
+        <v>560000.0</v>
       </c>
       <c r="AF107" s="14" t="inlineStr"/>
       <c r="AG107" s="14" t="inlineStr"/>
@@ -6862,20 +6862,20 @@
         <v>2.1978E7</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>1.924E7</v>
+        <v>4.0071E7</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
-        <v>4.1218E7</v>
+        <v>6.2049E7</v>
       </c>
       <c r="AA108" s="14" t="inlineStr"/>
       <c r="AB108" s="14" t="inlineStr"/>
       <c r="AC108" s="15" t="n">
-        <v>0.6549088771310994</v>
+        <v>0.9858906525573192</v>
       </c>
       <c r="AD108" s="15" t="inlineStr"/>
       <c r="AE108" s="14" t="n">
-        <v>2.1719E7</v>
+        <v>888000.0</v>
       </c>
       <c r="AF108" s="14" t="inlineStr"/>
       <c r="AG108" s="14" t="inlineStr"/>
@@ -7165,20 +7165,20 @@
         <v>4.9091867246E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>5.357253966E9</v>
+        <v>5.586547966E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.4449121212E10</v>
+        <v>5.4678415212E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.987214096723776</v>
+        <v>0.9913714139413089</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>7.05197788E8</v>
+        <v>4.75903788E8</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -8954,20 +8954,20 @@
         <v>2.213268E9</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>2.19192E8</v>
+        <v>4.48486E8</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
-        <v>2.43246E9</v>
+        <v>2.661754E9</v>
       </c>
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.904383945461684</v>
+        <v>0.9896350132657553</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>2.57172E8</v>
+        <v>2.7878E7</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -9011,20 +9011,20 @@
         <v>1.9894E8</v>
       </c>
       <c r="X145" s="14" t="n">
-        <v>3.0567E7</v>
+        <v>5.1952E7</v>
       </c>
       <c r="Y145" s="14" t="inlineStr"/>
       <c r="Z145" s="14" t="n">
-        <v>2.29507E8</v>
+        <v>2.50892E8</v>
       </c>
       <c r="AA145" s="14" t="inlineStr"/>
       <c r="AB145" s="14" t="inlineStr"/>
       <c r="AC145" s="15" t="n">
-        <v>0.9107420634920635</v>
+        <v>0.9956031746031746</v>
       </c>
       <c r="AD145" s="15" t="inlineStr"/>
       <c r="AE145" s="14" t="n">
-        <v>2.2493E7</v>
+        <v>1108000.0</v>
       </c>
       <c r="AF145" s="14" t="inlineStr"/>
       <c r="AG145" s="14" t="inlineStr"/>
@@ -9068,20 +9068,20 @@
         <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>1.60099E8</v>
+        <v>3.29263E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>1.74159E9</v>
+        <v>1.910754E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.9079861111111112</v>
+        <v>0.9961805555555555</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>1.7649E8</v>
+        <v>7326000.0</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9125,20 +9125,20 @@
         <v>4.32837E8</v>
       </c>
       <c r="X147" s="14" t="n">
-        <v>2.8526E7</v>
+        <v>6.7271E7</v>
       </c>
       <c r="Y147" s="14" t="inlineStr"/>
       <c r="Z147" s="14" t="n">
-        <v>4.61363E8</v>
+        <v>5.00108E8</v>
       </c>
       <c r="AA147" s="14" t="inlineStr"/>
       <c r="AB147" s="14" t="inlineStr"/>
       <c r="AC147" s="15" t="n">
-        <v>0.8880015859817689</v>
+        <v>0.9625754496181326</v>
       </c>
       <c r="AD147" s="15" t="inlineStr"/>
       <c r="AE147" s="14" t="n">
-        <v>5.8189E7</v>
+        <v>1.9444E7</v>
       </c>
       <c r="AF147" s="14" t="inlineStr"/>
       <c r="AG147" s="14" t="inlineStr"/>
@@ -9656,20 +9656,20 @@
         <v>2.1747293967E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>4.814780305E9</v>
+        <v>5.070561305E9</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
-        <v>2.6562074272E10</v>
+        <v>2.6817855272E10</v>
       </c>
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.9856227304849602</v>
+        <v>0.9951138404428871</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.87460728E8</v>
+        <v>1.31679728E8</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11167,20 +11167,20 @@
         <v>1.310426E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>2.45185E8</v>
+        <v>5.00966E8</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
-        <v>1.555611E9</v>
+        <v>1.811392E9</v>
       </c>
       <c r="AA182" s="14" t="inlineStr"/>
       <c r="AB182" s="14" t="inlineStr"/>
       <c r="AC182" s="15" t="n">
-        <v>0.8509534593672049</v>
+        <v>0.9908712966609776</v>
       </c>
       <c r="AD182" s="15" t="inlineStr"/>
       <c r="AE182" s="14" t="n">
-        <v>2.72469E8</v>
+        <v>1.6688E7</v>
       </c>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -11224,20 +11224,20 @@
         <v>1.2502E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>2.226E7</v>
+        <v>4.557E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.4728E8</v>
+        <v>1.7059E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.834920634920635</v>
+        <v>0.9670634920634921</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>2.912E7</v>
+        <v>5810000.0</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11281,20 +11281,20 @@
         <v>1.185406E9</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>2.22925E8</v>
+        <v>4.55396E8</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>1.408331E9</v>
+        <v>1.640802E9</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.852665770609319</v>
+        <v>0.9934139784946237</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>2.43349E8</v>
+        <v>1.0878E7</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11578,20 +11578,20 @@
         <v>5.752546162E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>8.86545441E8</v>
+        <v>1.183120801E9</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.639091603E9</v>
+        <v>6.935666963E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.9557070793179867</v>
+        <v>0.9983995420903339</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>3.07693397E8</v>
+        <v>1.1118037E7</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11641,20 +11641,20 @@
         <v>4.382759356E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>5.49326489E8</v>
+        <v>6.21826702E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.932085845E9</v>
+        <v>5.004586058E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.984700638846363</v>
+        <v>0.9991754489573775</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>7.6630155E7</v>
+        <v>4129942.0</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11704,20 +11704,20 @@
         <v>1.752363354E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>1.30338121E8</v>
+        <v>1.40134066E8</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.882701475E9</v>
+        <v>1.89249742E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9946190528013558</v>
+        <v>0.9997941873973459</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>1.0185525E7</v>
+        <v>389580.0</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11875,20 +11875,20 @@
         <v>5.3038114E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>3.2936521E7</v>
+        <v>4.2732466E7</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>8.5974635E7</v>
+        <v>9.577058E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.8955691145833333</v>
+        <v>0.9976102083333334</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>1.0025365E7</v>
+        <v>229420.0</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
         <v>5.3038114E7</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>3.2936521E7</v>
+        <v>4.2732466E7</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="2" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
       <c r="AC196" s="2" t="inlineStr"/>
       <c r="AD196" s="2" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>1.0025365E7</v>
+        <v>229420.0</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12377,20 +12377,20 @@
         <v>9332000.0</v>
       </c>
       <c r="X203" s="14" t="n">
-        <v>1380500.0</v>
+        <v>4155500.0</v>
       </c>
       <c r="Y203" s="14" t="inlineStr"/>
       <c r="Z203" s="14" t="n">
-        <v>1.07125E7</v>
+        <v>1.34875E7</v>
       </c>
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>0.7199260752688172</v>
+        <v>0.9064180107526881</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>4167500.0</v>
+        <v>1392500.0</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12434,20 +12434,20 @@
         <v>5696000.0</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>1380500.0</v>
+        <v>3347500.0</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>7076500.0</v>
+        <v>9043500.0</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.6817437379576108</v>
+        <v>0.871242774566474</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>3303500.0</v>
+        <v>1336500.0</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12491,20 +12491,20 @@
         <v>3636000.0</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>0.0</v>
+        <v>808000.0</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>3636000.0</v>
+        <v>4444000.0</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.808</v>
+        <v>0.9875555555555555</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>864000.0</v>
+        <v>56000.0</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12554,20 +12554,20 @@
         <v>4.907101E7</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>1.15831E7</v>
+        <v>2.77361E7</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
-        <v>6.065411E7</v>
+        <v>7.680711E7</v>
       </c>
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.7718673725200749</v>
+        <v>0.9774259681093395</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>1.792689E7</v>
+        <v>1773890.0</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12611,20 +12611,20 @@
         <v>4.907101E7</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>1.15831E7</v>
+        <v>2.19611E7</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>6.065411E7</v>
+        <v>7.103211E7</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.8365968745258686</v>
+        <v>0.9797397277278934</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>1.184689E7</v>
+        <v>1468890.0</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12668,20 +12668,20 @@
         <v>0.0</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>0.0</v>
+        <v>5775000.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>0.0</v>
+        <v>5775000.0</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.0</v>
+        <v>0.9498355263157895</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>6080000.0</v>
+        <v>305000.0</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12731,20 +12731,20 @@
         <v>4274800.0</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>0.0</v>
+        <v>6724500.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>4274800.0</v>
+        <v>1.09993E7</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.3886181818181818</v>
+        <v>0.9999363636363636</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>6725200.0</v>
+        <v>700.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12788,20 +12788,20 @@
         <v>3964800.0</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>0.0</v>
+        <v>5035000.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>3964800.0</v>
+        <v>8999800.0</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.44053333333333333</v>
+        <v>0.9999777777777777</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>5035200.0</v>
+        <v>200.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12845,20 +12845,20 @@
         <v>310000.0</v>
       </c>
       <c r="X211" s="14" t="n">
-        <v>0.0</v>
+        <v>1689500.0</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>310000.0</v>
+        <v>1999500.0</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.155</v>
+        <v>0.99975</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>1690000.0</v>
+        <v>500.0</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
@@ -12908,20 +12908,20 @@
         <v>2.567718192E9</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>4.06024768E8</v>
+        <v>4.43076536E8</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>2.97374296E9</v>
+        <v>3.010794728E9</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.987505665199338</v>
+        <v>0.9998096307060446</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>3.762504E7</v>
+        <v>573272.0</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
@@ -13022,20 +13022,20 @@
         <v>1.0331888E8</v>
       </c>
       <c r="X214" s="14" t="n">
-        <v>9468528.0</v>
+        <v>1.8937056E7</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
-        <v>1.12787408E8</v>
+        <v>1.22255936E8</v>
       </c>
       <c r="AA214" s="14" t="inlineStr"/>
       <c r="AB214" s="14" t="inlineStr"/>
       <c r="AC214" s="15" t="n">
-        <v>0.9199625448613377</v>
+        <v>0.9971936052202284</v>
       </c>
       <c r="AD214" s="15" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
-        <v>9812592.0</v>
+        <v>344064.0</v>
       </c>
       <c r="AF214" s="14" t="inlineStr"/>
       <c r="AG214" s="14" t="inlineStr"/>
@@ -13250,20 +13250,20 @@
         <v>2.2953312E7</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>4.5906624E7</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>4.5906624E7</v>
+        <v>6.8859936E7</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.6662790130624093</v>
+        <v>0.9994185195936139</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>2.2993376E7</v>
+        <v>40064.0</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13307,20 +13307,20 @@
         <v>4629928.0</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>4629928.0</v>
+        <v>9259856.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>9259856.0</v>
+        <v>1.3889784E7</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.6666562994960403</v>
+        <v>0.9999844492440605</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>4630144.0</v>
+        <v>216.0</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13370,20 +13370,20 @@
         <v>6.39230607E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>5.0385842E7</v>
+        <v>5.2638107E7</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>6.89616449E8</v>
+        <v>6.91868714E8</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.9955427556358849</v>
+        <v>0.9987941660507229</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>3087551.0</v>
+        <v>835286.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13717,20 +13717,20 @@
         <v>3.021E7</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>1216100.0</v>
+        <v>2250900.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>3.14261E7</v>
+        <v>3.24609E7</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9656495821042281</v>
+        <v>0.9974465339233038</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>1117900.0</v>
+        <v>83100.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13774,20 +13774,20 @@
         <v>3.021E7</v>
       </c>
       <c r="X227" s="14" t="n">
-        <v>1216100.0</v>
+        <v>2250900.0</v>
       </c>
       <c r="Y227" s="14" t="inlineStr"/>
       <c r="Z227" s="14" t="n">
-        <v>3.14261E7</v>
+        <v>3.24609E7</v>
       </c>
       <c r="AA227" s="14" t="inlineStr"/>
       <c r="AB227" s="14" t="inlineStr"/>
       <c r="AC227" s="15" t="n">
-        <v>0.9656495821042281</v>
+        <v>0.9974465339233038</v>
       </c>
       <c r="AD227" s="15" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
-        <v>1117900.0</v>
+        <v>83100.0</v>
       </c>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
@@ -13837,20 +13837,20 @@
         <v>1.33021464E8</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>1.001975E7</v>
+        <v>1.1237215E7</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>1.43041214E8</v>
+        <v>1.44258679E8</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.9885363787145819</v>
+        <v>0.9969500967519005</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>1658786.0</v>
+        <v>441321.0</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13894,20 +13894,20 @@
         <v>1.044355E8</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>9250750.0</v>
+        <v>1.029815E7</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>1.1368625E8</v>
+        <v>1.1473365E8</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.9878888599235315</v>
+        <v>0.996990354535975</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1393750.0</v>
+        <v>346350.0</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13951,20 +13951,20 @@
         <v>2.8585964E7</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>769000.0</v>
+        <v>939065.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>2.9354964E7</v>
+        <v>2.9525029E7</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.9910521269412559</v>
+        <v>0.9967936866981769</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>265036.0</v>
+        <v>94971.0</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14014,20 +14014,20 @@
         <v>6.19636199E8</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>2.6653311E8</v>
+        <v>4.67595992E8</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>8.86169309E8</v>
+        <v>1.087232191E9</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.810630688309847</v>
+        <v>0.9945546188431053</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>2.07015691E8</v>
+        <v>5952809.0</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14077,20 +14077,20 @@
         <v>1.9288E8</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>2.50325E7</v>
+        <v>4.70975E7</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>2.179125E8</v>
+        <v>2.399775E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.90796875</v>
+        <v>0.99990625</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>2.20875E7</v>
+        <v>22500.0</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14134,20 +14134,20 @@
         <v>1.5279E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>1.5125E7</v>
+        <v>2.719E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>1.67915E8</v>
+        <v>1.7998E8</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.9328611111111111</v>
+        <v>0.9998888888888889</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>1.2085E7</v>
+        <v>20000.0</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14191,20 +14191,20 @@
         <v>4.009E7</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>9907500.0</v>
+        <v>1.99075E7</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>4.99975E7</v>
+        <v>5.99975E7</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.8332916666666667</v>
+        <v>0.9999583333333333</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>1.00025E7</v>
+        <v>2500.0</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14374,20 +14374,20 @@
         <v>1.28808533E8</v>
       </c>
       <c r="X237" s="14" t="n">
-        <v>8.63665E7</v>
+        <v>2.1620842E8</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>2.15175033E8</v>
+        <v>3.45016953E8</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.6201009596541787</v>
+        <v>0.994285167146974</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>1.31824967E8</v>
+        <v>1983047.0</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14488,20 +14488,20 @@
         <v>2.1347299E7</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>0.0</v>
+        <v>1.57755E7</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>3.7122799E7</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.5723136461126005</v>
+        <v>0.9952493029490617</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>1.5952701E7</v>
+        <v>177201.0</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14545,20 +14545,20 @@
         <v>2.5327E7</v>
       </c>
       <c r="X240" s="14" t="n">
-        <v>0.0</v>
+        <v>595920.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.592292E7</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.9989564547206166</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>623000.0</v>
+        <v>27080.0</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -14659,20 +14659,20 @@
         <v>4421000.0</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>2.5076E7</v>
+        <v>1.18724E8</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>2.9497E7</v>
+        <v>1.23145E8</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.23864886731391585</v>
+        <v>0.9963187702265373</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>9.4103E7</v>
+        <v>455000.0</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14773,20 +14773,20 @@
         <v>1.2143622E7</v>
       </c>
       <c r="X244" s="14" t="n">
-        <v>0.0</v>
+        <v>4395000.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1.6538622E7</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.7315434939759036</v>
+        <v>0.996302530120482</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>4456378.0</v>
+        <v>61378.0</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14887,20 +14887,20 @@
         <v>1576500.0</v>
       </c>
       <c r="X246" s="14" t="n">
-        <v>0.0</v>
+        <v>2400000.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>1576500.0</v>
+        <v>3976500.0</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>0.37987951807228915</v>
+        <v>0.9581927710843373</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>2573500.0</v>
+        <v>173500.0</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -15273,20 +15273,20 @@
         <v>0.0</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>0.0</v>
+        <v>5695000.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>0.0</v>
+        <v>5695000.0</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.0</v>
+        <v>0.9991228070175439</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>5700000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15330,20 +15330,20 @@
         <v>0.0</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>5413000.0</v>
+        <v>9413000.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>5413000.0</v>
+        <v>9413000.0</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.5697894736842105</v>
+        <v>0.9908421052631579</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>4087000.0</v>
+        <v>87000.0</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>
@@ -15387,20 +15387,20 @@
         <v>0.0</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>0.0</v>
+        <v>3332500.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>0.0</v>
+        <v>3332500.0</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.0</v>
+        <v>0.9801470588235294</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>3400000.0</v>
+        <v>67500.0</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15450,20 +15450,20 @@
         <v>2.06124881E8</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>6.602411E7</v>
+        <v>1.15180072E8</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>2.72148991E8</v>
+        <v>3.21304953E8</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.8388915154971256</v>
+        <v>0.9904133686790069</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>5.2266009E7</v>
+        <v>3110047.0</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15507,20 +15507,20 @@
         <v>1.396E7</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>2890000.0</v>
+        <v>8440000.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>1.685E7</v>
+        <v>2.24E7</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.7465662383695171</v>
+        <v>0.9924678777137793</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>5720000.0</v>
+        <v>170000.0</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15564,20 +15564,20 @@
         <v>1287928.0</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>1200000.0</v>
+        <v>3700000.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>2487928.0</v>
+        <v>4987928.0</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.4975856</v>
+        <v>0.9975856</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>2512072.0</v>
+        <v>12072.0</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15621,20 +15621,20 @@
         <v>2.8040718E7</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>1.460255E7</v>
+        <v>1.691255E7</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>4.2643268E7</v>
+        <v>4.4953268E7</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.9476281777777777</v>
+        <v>0.9989615111111111</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>2356732.0</v>
+        <v>46732.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15678,20 +15678,20 @@
         <v>1.20838496E8</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>4.1811668E7</v>
+        <v>5.3021623E7</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>1.62650164E8</v>
+        <v>1.73860119E8</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.9333495767939632</v>
+        <v>0.9976766361575761</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>1.1614836E7</v>
+        <v>404881.0</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15735,20 +15735,20 @@
         <v>3411992.0</v>
       </c>
       <c r="X261" s="14" t="n">
-        <v>736000.0</v>
+        <v>961000.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>4147992.0</v>
+        <v>4372992.0</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.921776</v>
+        <v>0.971776</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>352008.0</v>
+        <v>127008.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15849,20 +15849,20 @@
         <v>1000052.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>0.0</v>
+        <v>7986000.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>1000052.0</v>
+        <v>8986052.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.11099356270810211</v>
+        <v>0.997342064372919</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>8009948.0</v>
+        <v>23948.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15906,20 +15906,20 @@
         <v>1658480.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>319926.0</v>
+        <v>1319926.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>1978406.0</v>
+        <v>2978406.0</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.6486577049180328</v>
+        <v>0.9765265573770492</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>1071594.0</v>
+        <v>71594.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15963,20 +15963,20 @@
         <v>8319256.0</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>619028.0</v>
+        <v>3496969.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>8938284.0</v>
+        <v>1.1816225E7</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.744857</v>
+        <v>0.9846854166666666</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>3061716.0</v>
+        <v>183775.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -16020,20 +16020,20 @@
         <v>1167558.0</v>
       </c>
       <c r="X266" s="14" t="n">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>1167558.0</v>
+        <v>1667558.0</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.583779</v>
+        <v>0.833779</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>832442.0</v>
+        <v>332442.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16077,20 +16077,20 @@
         <v>3760846.0</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>2513528.0</v>
+        <v>1.1772594E7</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>6274374.0</v>
+        <v>1.553344E7</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>0.40168847631242</v>
+        <v>0.9944583866837388</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>9345626.0</v>
+        <v>86560.0</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16191,20 +16191,20 @@
         <v>7889000.0</v>
       </c>
       <c r="X269" s="14" t="n">
-        <v>581410.0</v>
+        <v>666410.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>8470410.0</v>
+        <v>8555410.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.9011074468085106</v>
+        <v>0.91015</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>929590.0</v>
+        <v>844590.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16248,20 +16248,20 @@
         <v>0.0</v>
       </c>
       <c r="X270" s="14" t="n">
-        <v>750000.0</v>
+        <v>1450000.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>750000.0</v>
+        <v>1450000.0</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.5</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>750000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16305,20 +16305,20 @@
         <v>0.0</v>
       </c>
       <c r="X271" s="14" t="n">
-        <v>0.0</v>
+        <v>3955000.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>0.0</v>
+        <v>3955000.0</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.0</v>
+        <v>0.98875</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>4000000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16362,20 +16362,20 @@
         <v>0.0</v>
       </c>
       <c r="X272" s="14" t="n">
-        <v>0.0</v>
+        <v>998000.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>0.0</v>
+        <v>998000.0</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.0</v>
+        <v>0.998</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>1000000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16703,20 +16703,20 @@
         <v>1.1092E8</v>
       </c>
       <c r="X278" s="14" t="n">
-        <v>2.03E7</v>
+        <v>4.106E7</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>1.3122E8</v>
+        <v>1.5198E8</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="15" t="n">
-        <v>0.8622683664082008</v>
+        <v>0.9986857668550401</v>
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>2.096E7</v>
+        <v>200000.0</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
@@ -16766,20 +16766,20 @@
         <v>1.0342E8</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>2.03E7</v>
+        <v>2.126E7</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>1.2372E8</v>
+        <v>1.2468E8</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>0.9923002887391723</v>
+        <v>1.0</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>960000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
@@ -17108,20 +17108,20 @@
         <v>2700000.0</v>
       </c>
       <c r="X285" s="14" t="n">
-        <v>300000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="Y285" s="14" t="inlineStr"/>
       <c r="Z285" s="14" t="n">
-        <v>3000000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="AA285" s="14" t="inlineStr"/>
       <c r="AB285" s="14" t="inlineStr"/>
       <c r="AC285" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD285" s="15" t="inlineStr"/>
       <c r="AE285" s="14" t="n">
-        <v>600000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF285" s="14" t="inlineStr"/>
       <c r="AG285" s="14" t="inlineStr"/>
@@ -17165,20 +17165,20 @@
         <v>3420000.0</v>
       </c>
       <c r="X286" s="14" t="n">
-        <v>540000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="Y286" s="14" t="inlineStr"/>
       <c r="Z286" s="14" t="n">
-        <v>3960000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="AA286" s="14" t="inlineStr"/>
       <c r="AB286" s="14" t="inlineStr"/>
       <c r="AC286" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>1.0</v>
       </c>
       <c r="AD286" s="15" t="inlineStr"/>
       <c r="AE286" s="14" t="n">
-        <v>360000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF286" s="14" t="inlineStr"/>
       <c r="AG286" s="14" t="inlineStr"/>
@@ -17228,20 +17228,20 @@
         <v>7500000.0</v>
       </c>
       <c r="X287" s="14" t="n">
-        <v>0.0</v>
+        <v>1.98E7</v>
       </c>
       <c r="Y287" s="14" t="inlineStr"/>
       <c r="Z287" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2.73E7</v>
       </c>
       <c r="AA287" s="14" t="inlineStr"/>
       <c r="AB287" s="14" t="inlineStr"/>
       <c r="AC287" s="15" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.9927272727272727</v>
       </c>
       <c r="AD287" s="15" t="inlineStr"/>
       <c r="AE287" s="14" t="n">
-        <v>2.0E7</v>
+        <v>200000.0</v>
       </c>
       <c r="AF287" s="14" t="inlineStr"/>
       <c r="AG287" s="14" t="inlineStr"/>
@@ -17342,20 +17342,20 @@
         <v>0.0</v>
       </c>
       <c r="X289" s="14" t="n">
-        <v>0.0</v>
+        <v>1.98E7</v>
       </c>
       <c r="Y289" s="14" t="inlineStr"/>
       <c r="Z289" s="14" t="n">
-        <v>0.0</v>
+        <v>1.98E7</v>
       </c>
       <c r="AA289" s="14" t="inlineStr"/>
       <c r="AB289" s="14" t="inlineStr"/>
       <c r="AC289" s="15" t="n">
-        <v>0.0</v>
+        <v>0.99</v>
       </c>
       <c r="AD289" s="15" t="inlineStr"/>
       <c r="AE289" s="14" t="n">
-        <v>2.0E7</v>
+        <v>200000.0</v>
       </c>
       <c r="AF289" s="14" t="inlineStr"/>
       <c r="AG289" s="14" t="inlineStr"/>
